--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,52 +516,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.2</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>19.91</v>
+        <v>50.49</v>
       </c>
       <c r="E2" t="n">
-        <v>19.79</v>
+        <v>49.92</v>
       </c>
       <c r="F2" t="n">
-        <v>18.66</v>
+        <v>49.9</v>
       </c>
       <c r="G2" t="n">
-        <v>392811029</v>
+        <v>44114173</v>
       </c>
       <c r="H2" t="n">
-        <v>254953321</v>
+        <v>24067636</v>
       </c>
       <c r="I2" t="n">
-        <v>22.2</v>
+        <v>53.9</v>
       </c>
       <c r="J2" t="n">
-        <v>16.6</v>
+        <v>47.35</v>
       </c>
       <c r="K2" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="L2" t="n">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="M2" t="n">
-        <v>20000</v>
+        <v>35000</v>
       </c>
       <c r="N2" t="n">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="O2" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點</t>
+          <t>站上5日線、多頭排列、黃金交叉、爆量、接近20日高點</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -587,52 +587,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>516</v>
+        <v>22.2</v>
       </c>
       <c r="D3" t="n">
-        <v>444.3</v>
+        <v>19.91</v>
       </c>
       <c r="E3" t="n">
-        <v>432.05</v>
+        <v>19.79</v>
       </c>
       <c r="F3" t="n">
-        <v>416.18</v>
+        <v>18.66</v>
       </c>
       <c r="G3" t="n">
-        <v>50890468</v>
+        <v>392811029</v>
       </c>
       <c r="H3" t="n">
-        <v>46138661</v>
+        <v>254953321</v>
       </c>
       <c r="I3" t="n">
-        <v>516</v>
+        <v>22.2</v>
       </c>
       <c r="J3" t="n">
-        <v>331</v>
+        <v>16.6</v>
       </c>
       <c r="K3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L3" t="n">
         <v>12000</v>
       </c>
-      <c r="L3" t="n">
-        <v>25000</v>
-      </c>
       <c r="M3" t="n">
-        <v>45000</v>
+        <v>20000</v>
       </c>
       <c r="N3" t="n">
-        <v>80000</v>
+        <v>35000</v>
       </c>
       <c r="O3" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -658,52 +658,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>629</v>
+        <v>11.85</v>
       </c>
       <c r="D4" t="n">
-        <v>543.8</v>
+        <v>10.6</v>
       </c>
       <c r="E4" t="n">
-        <v>486.75</v>
+        <v>10.53</v>
       </c>
       <c r="F4" t="n">
-        <v>411.23</v>
+        <v>9.52</v>
       </c>
       <c r="G4" t="n">
-        <v>72182688</v>
+        <v>100795639</v>
       </c>
       <c r="H4" t="n">
-        <v>71442747</v>
+        <v>63097678</v>
       </c>
       <c r="I4" t="n">
-        <v>629</v>
+        <v>11.85</v>
       </c>
       <c r="J4" t="n">
-        <v>290</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="L4" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="M4" t="n">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="N4" t="n">
-        <v>70000</v>
+        <v>12000</v>
       </c>
       <c r="O4" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -729,52 +729,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>283</v>
+        <v>516</v>
       </c>
       <c r="D5" t="n">
-        <v>250.4</v>
+        <v>444.3</v>
       </c>
       <c r="E5" t="n">
-        <v>241.3</v>
+        <v>432.05</v>
       </c>
       <c r="F5" t="n">
-        <v>230.18</v>
+        <v>416.18</v>
       </c>
       <c r="G5" t="n">
-        <v>6909104</v>
+        <v>50890468</v>
       </c>
       <c r="H5" t="n">
-        <v>25802698</v>
+        <v>46138661</v>
       </c>
       <c r="I5" t="n">
-        <v>283</v>
+        <v>516</v>
       </c>
       <c r="J5" t="n">
-        <v>201</v>
+        <v>331</v>
       </c>
       <c r="K5" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="L5" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="M5" t="n">
-        <v>18000</v>
+        <v>45000</v>
       </c>
       <c r="N5" t="n">
-        <v>25000</v>
+        <v>80000</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、突破20日高點</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -800,52 +800,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>211</v>
+        <v>629</v>
       </c>
       <c r="D6" t="n">
-        <v>198</v>
+        <v>543.8</v>
       </c>
       <c r="E6" t="n">
-        <v>197.65</v>
+        <v>486.75</v>
       </c>
       <c r="F6" t="n">
-        <v>187.38</v>
+        <v>411.23</v>
       </c>
       <c r="G6" t="n">
-        <v>27951666</v>
+        <v>72182688</v>
       </c>
       <c r="H6" t="n">
-        <v>16214445</v>
+        <v>71442747</v>
       </c>
       <c r="I6" t="n">
-        <v>216.5</v>
+        <v>629</v>
       </c>
       <c r="J6" t="n">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="K6" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="L6" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="M6" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="N6" t="n">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="O6" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量</t>
+          <t>站上5日線、多頭排列、成交量放大、突破20日高點</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -871,52 +871,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>522</v>
+        <v>283</v>
       </c>
       <c r="D7" t="n">
-        <v>467.4</v>
+        <v>250.4</v>
       </c>
       <c r="E7" t="n">
-        <v>454.85</v>
+        <v>241.3</v>
       </c>
       <c r="F7" t="n">
-        <v>429.05</v>
+        <v>230.18</v>
       </c>
       <c r="G7" t="n">
-        <v>4202780</v>
+        <v>6909104</v>
       </c>
       <c r="H7" t="n">
-        <v>4332139</v>
+        <v>25802698</v>
       </c>
       <c r="I7" t="n">
-        <v>528</v>
+        <v>283</v>
       </c>
       <c r="J7" t="n">
-        <v>324.5</v>
+        <v>201</v>
       </c>
       <c r="K7" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="L7" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="M7" t="n">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="N7" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="O7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、成交量未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -942,52 +942,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.4</v>
+        <v>609</v>
       </c>
       <c r="D8" t="n">
-        <v>51.07</v>
+        <v>537</v>
       </c>
       <c r="E8" t="n">
-        <v>50.05</v>
+        <v>518.75</v>
       </c>
       <c r="F8" t="n">
-        <v>49.52</v>
+        <v>513.17</v>
       </c>
       <c r="G8" t="n">
-        <v>9214268</v>
+        <v>10417136</v>
       </c>
       <c r="H8" t="n">
-        <v>6313989</v>
+        <v>27927013</v>
       </c>
       <c r="I8" t="n">
-        <v>57</v>
+        <v>609</v>
       </c>
       <c r="J8" t="n">
-        <v>45.45</v>
+        <v>445.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="L8" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="M8" t="n">
-        <v>8000</v>
+        <v>25000</v>
       </c>
       <c r="N8" t="n">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="O8" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、成交量未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1013,56 +1013,56 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1455</v>
+        <v>522</v>
       </c>
       <c r="D9" t="n">
-        <v>1294</v>
+        <v>467.4</v>
       </c>
       <c r="E9" t="n">
-        <v>1358</v>
+        <v>454.85</v>
       </c>
       <c r="F9" t="n">
-        <v>1251.3</v>
+        <v>429.05</v>
       </c>
       <c r="G9" t="n">
-        <v>1582543</v>
+        <v>4202780</v>
       </c>
       <c r="H9" t="n">
-        <v>1588253</v>
+        <v>4332139</v>
       </c>
       <c r="I9" t="n">
-        <v>1480</v>
+        <v>528</v>
       </c>
       <c r="J9" t="n">
-        <v>941</v>
+        <v>324.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="L9" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="M9" t="n">
-        <v>20000</v>
+        <v>9000</v>
       </c>
       <c r="N9" t="n">
-        <v>35000</v>
+        <v>12000</v>
       </c>
       <c r="O9" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>站上5日線、成交量未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、成交量未放大、接近20日高點</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1084,56 +1084,56 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>120.5</v>
+        <v>198</v>
       </c>
       <c r="E10" t="n">
-        <v>122.7</v>
+        <v>197.65</v>
       </c>
       <c r="F10" t="n">
-        <v>110.54</v>
+        <v>187.38</v>
       </c>
       <c r="G10" t="n">
-        <v>190947918</v>
+        <v>27951666</v>
       </c>
       <c r="H10" t="n">
-        <v>184433553</v>
+        <v>16214445</v>
       </c>
       <c r="I10" t="n">
-        <v>136.5</v>
+        <v>216.5</v>
       </c>
       <c r="J10" t="n">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="K10" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="L10" t="n">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="M10" t="n">
-        <v>12000</v>
+        <v>30000</v>
       </c>
       <c r="N10" t="n">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、多頭排列、爆量</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1155,56 +1155,56 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2255</v>
+        <v>54.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2223</v>
+        <v>51.07</v>
       </c>
       <c r="E11" t="n">
-        <v>2236</v>
+        <v>50.05</v>
       </c>
       <c r="F11" t="n">
-        <v>2235.75</v>
+        <v>49.52</v>
       </c>
       <c r="G11" t="n">
-        <v>24437825</v>
+        <v>9214268</v>
       </c>
       <c r="H11" t="n">
-        <v>27484516</v>
+        <v>6313989</v>
       </c>
       <c r="I11" t="n">
-        <v>2345</v>
+        <v>57</v>
       </c>
       <c r="J11" t="n">
-        <v>2105</v>
+        <v>45.45</v>
       </c>
       <c r="K11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L11" t="n">
         <v>5000</v>
       </c>
-      <c r="L11" t="n">
-        <v>12000</v>
-      </c>
       <c r="M11" t="n">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="N11" t="n">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>站上5日線、成交量未放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1226,37 +1226,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>531</v>
+        <v>1455</v>
       </c>
       <c r="D12" t="n">
-        <v>473.5</v>
+        <v>1294</v>
       </c>
       <c r="E12" t="n">
-        <v>484.3</v>
+        <v>1358</v>
       </c>
       <c r="F12" t="n">
-        <v>499.57</v>
+        <v>1251.3</v>
       </c>
       <c r="G12" t="n">
-        <v>27582138</v>
+        <v>1582543</v>
       </c>
       <c r="H12" t="n">
-        <v>22972476</v>
+        <v>1588253</v>
       </c>
       <c r="I12" t="n">
-        <v>604</v>
+        <v>1480</v>
       </c>
       <c r="J12" t="n">
-        <v>436</v>
+        <v>941</v>
       </c>
       <c r="K12" t="n">
         <v>5000</v>
@@ -1265,27 +1265,27 @@
         <v>10000</v>
       </c>
       <c r="M12" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="N12" t="n">
-        <v>20000</v>
+        <v>35000</v>
       </c>
       <c r="O12" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>可追蹤</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
+          <t>站上5日線、成交量未放大、接近20日高點</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1297,274 +1297,1055 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>310.5</v>
+        <v>33.1</v>
       </c>
       <c r="D13" t="n">
-        <v>291.6</v>
+        <v>29.54</v>
       </c>
       <c r="E13" t="n">
-        <v>305.35</v>
+        <v>29.23</v>
       </c>
       <c r="F13" t="n">
-        <v>275.52</v>
+        <v>28.62</v>
       </c>
       <c r="G13" t="n">
-        <v>154923679</v>
+        <v>134312480</v>
       </c>
       <c r="H13" t="n">
-        <v>131047919</v>
+        <v>58293636</v>
       </c>
       <c r="I13" t="n">
-        <v>353</v>
+        <v>33.1</v>
       </c>
       <c r="J13" t="n">
-        <v>199</v>
+        <v>25.35</v>
       </c>
       <c r="K13" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="L13" t="n">
         <v>-5000</v>
       </c>
-      <c r="L13" t="n">
-        <v>-2000</v>
-      </c>
       <c r="M13" t="n">
-        <v>3000</v>
+        <v>-8000</v>
       </c>
       <c r="N13" t="n">
-        <v>8000</v>
+        <v>-12000</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>可追蹤</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
+          <t>站上5日線、多頭排列、超級爆量、突破20日高點</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>短線賣壓重</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>44.65</v>
+        <v>5525</v>
       </c>
       <c r="D14" t="n">
-        <v>39.67</v>
+        <v>5152</v>
       </c>
       <c r="E14" t="n">
-        <v>37.52</v>
+        <v>5302</v>
       </c>
       <c r="F14" t="n">
-        <v>31.72</v>
+        <v>5076.5</v>
       </c>
       <c r="G14" t="n">
-        <v>386510344</v>
+        <v>1829705</v>
       </c>
       <c r="H14" t="n">
-        <v>636475880</v>
+        <v>1681714</v>
       </c>
       <c r="I14" t="n">
-        <v>44.65</v>
+        <v>5870</v>
       </c>
       <c r="J14" t="n">
-        <v>22.95</v>
+        <v>4320</v>
       </c>
       <c r="K14" t="n">
-        <v>-71547</v>
+        <v>15000</v>
       </c>
       <c r="L14" t="n">
-        <v>-7378</v>
+        <v>30000</v>
       </c>
       <c r="M14" t="n">
-        <v>-219616</v>
+        <v>50000</v>
       </c>
       <c r="N14" t="n">
-        <v>587508</v>
+        <v>80000</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>可追蹤</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量未放大、突破20日高點</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>前期買超但短線轉弱、主力大賣</t>
+          <t>籌碼轉強</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>717</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>683.8</v>
+        <v>80.98</v>
       </c>
       <c r="E15" t="n">
-        <v>728.7</v>
+        <v>81.02</v>
       </c>
       <c r="F15" t="n">
-        <v>688.65</v>
+        <v>78.97</v>
       </c>
       <c r="G15" t="n">
-        <v>6305022</v>
+        <v>15239585</v>
       </c>
       <c r="H15" t="n">
-        <v>4509007</v>
+        <v>11366488</v>
       </c>
       <c r="I15" t="n">
-        <v>849</v>
+        <v>85.5</v>
       </c>
       <c r="J15" t="n">
-        <v>534</v>
+        <v>70.2</v>
       </c>
       <c r="K15" t="n">
-        <v>-3000</v>
+        <v>2000</v>
       </c>
       <c r="L15" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="M15" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="N15" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>站上5日線、死亡交叉、成交量放大</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
+          <t>站上5日線、成交量放大</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>籌碼轉強</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2344.TW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>125</v>
+      </c>
+      <c r="D16" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>110.54</v>
+      </c>
+      <c r="G16" t="n">
+        <v>190947918</v>
+      </c>
+      <c r="H16" t="n">
+        <v>184433553</v>
+      </c>
+      <c r="I16" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O16" t="n">
+        <v>60</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>👀觀察</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>強勢觀察</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>站上5日線、成交量放大</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>籌碼轉強</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2330.TW</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2255</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2223</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2236</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2235.75</v>
+      </c>
+      <c r="G17" t="n">
+        <v>24437825</v>
+      </c>
+      <c r="H17" t="n">
+        <v>27484516</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2345</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2105</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N17" t="n">
+        <v>40000</v>
+      </c>
+      <c r="O17" t="n">
+        <v>50</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>👀觀察</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>強勢觀察</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>站上5日線、成交量未放大</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>籌碼轉強</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3163.TWO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>波若威</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1145</v>
+      </c>
+      <c r="D18" t="n">
+        <v>988.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1005.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1060.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3404797</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1568233</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J18" t="n">
+        <v>865</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30000</v>
+      </c>
+      <c r="O18" t="n">
+        <v>45</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>強勢觀察</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>站上5日線、空頭排列、超級爆量</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>籌碼轉強</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3105.TWO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>531</v>
+      </c>
+      <c r="D19" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>484.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>499.57</v>
+      </c>
+      <c r="G19" t="n">
+        <v>27582138</v>
+      </c>
+      <c r="H19" t="n">
+        <v>22972476</v>
+      </c>
+      <c r="I19" t="n">
+        <v>604</v>
+      </c>
+      <c r="J19" t="n">
+        <v>436</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>15000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>35</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>可追蹤</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>站上5日線、空頭排列、成交量放大</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>籌碼轉強</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046.TW</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>934</v>
+      </c>
+      <c r="D20" t="n">
+        <v>844.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>854.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>895.45</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16635783</v>
+      </c>
+      <c r="H20" t="n">
+        <v>13468721</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1035</v>
+      </c>
+      <c r="J20" t="n">
+        <v>765</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>35000</v>
+      </c>
+      <c r="O20" t="n">
+        <v>35</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>可追蹤</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>站上5日線、空頭排列、成交量放大</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>籌碼轉強</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2408.TW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>305.35</v>
+      </c>
+      <c r="F21" t="n">
+        <v>275.52</v>
+      </c>
+      <c r="G21" t="n">
+        <v>154923679</v>
+      </c>
+      <c r="H21" t="n">
+        <v>131047919</v>
+      </c>
+      <c r="I21" t="n">
+        <v>353</v>
+      </c>
+      <c r="J21" t="n">
+        <v>199</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O21" t="n">
+        <v>30</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>可追蹤</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>站上5日線、成交量放大</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3481.TW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="D22" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="E22" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="F22" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="G22" t="n">
+        <v>386510344</v>
+      </c>
+      <c r="H22" t="n">
+        <v>636475880</v>
+      </c>
+      <c r="I22" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="J22" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-71547</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-7378</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-219616</v>
+      </c>
+      <c r="N22" t="n">
+        <v>587508</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>可追蹤</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、成交量未放大、突破20日高點</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>前期買超但短線轉弱、主力大賣</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5289.TWO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1741</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1765</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1557.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2948990</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4147491</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1935</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1055</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N23" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>跌破5日線、成交量未放大</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>籌碼轉強</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6488.TWO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>717</v>
+      </c>
+      <c r="D24" t="n">
+        <v>683.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>728.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>688.65</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6305022</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4509007</v>
+      </c>
+      <c r="I24" t="n">
+        <v>849</v>
+      </c>
+      <c r="J24" t="n">
+        <v>534</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N24" t="n">
+        <v>30000</v>
+      </c>
+      <c r="O24" t="n">
+        <v>5</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>站上5日線、死亡交叉、成交量放大</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>2317.TW</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>鴻海</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C25" t="n">
         <v>250</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D25" t="n">
         <v>246.2</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E25" t="n">
         <v>247.7</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F25" t="n">
         <v>240.95</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G25" t="n">
         <v>55061095</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H25" t="n">
         <v>59202085</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I25" t="n">
         <v>260</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J25" t="n">
         <v>218</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K25" t="n">
         <v>-3000</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L25" t="n">
         <v>-8000</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M25" t="n">
         <v>-15000</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N25" t="n">
         <v>-20000</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O25" t="n">
         <v>-5</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>避開</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>站上5日線、成交量未放大</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>短線賣壓重</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1802.TW</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>台玻</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="E26" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="F26" t="n">
+        <v>67.67</v>
+      </c>
+      <c r="G26" t="n">
+        <v>124473105</v>
+      </c>
+      <c r="H26" t="n">
+        <v>67843641</v>
+      </c>
+      <c r="I26" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-15</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>避開</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>站上5日線、空頭排列、爆量</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>短線賣壓重</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4960.TW</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>誠美材</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="E27" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="F27" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="G27" t="n">
+        <v>25488550</v>
+      </c>
+      <c r="H27" t="n">
+        <v>17301029</v>
+      </c>
+      <c r="I27" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="J27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-20</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>避開</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>站上5日線、空頭排列、成交量放大</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>短線賣壓重</t>
         </is>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,11 @@
           <t>籌碼面</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>AI評語</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -583,6 +588,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、黃金交叉、爆量、接近20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -654,6 +664,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、爆量、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -725,6 +740,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、爆量、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -796,6 +816,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、成交量放大、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -867,6 +892,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、成交量放大、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -938,6 +968,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、成交量未放大、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1009,6 +1044,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、成交量未放大、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1080,6 +1120,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、成交量未放大、接近20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1151,6 +1196,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、爆量，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1222,6 +1272,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、成交量放大，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1293,6 +1348,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、成交量未放大、接近20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1364,6 +1424,11 @@
           <t>短線賣壓重</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、多頭排列、超級爆量、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1435,6 +1500,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、成交量放大，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1506,6 +1576,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、成交量放大，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1577,6 +1652,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、成交量放大，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1648,6 +1728,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、成交量未放大，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1719,6 +1804,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>短線偏強，站上5日線、空頭排列、超級爆量，可以列入觀察，但仍要注意是否追高。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1790,6 +1880,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>目前有部分轉強訊號，站上5日線、空頭排列、成交量放大，可追蹤但不急著進場。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1861,6 +1956,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>目前有部分轉強訊號，站上5日線、空頭排列、成交量放大，可追蹤但不急著進場。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1928,6 +2028,11 @@
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>目前有部分轉強訊號，站上5日線、成交量放大，可追蹤但不急著進場。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1999,6 +2104,11 @@
           <t>前期買超但短線轉弱、主力大賣</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>目前有部分轉強訊號，站上5日線、多頭排列、成交量未放大、突破20日高點，可追蹤但不急著進場。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2070,6 +2180,11 @@
           <t>籌碼轉強</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>訊號普通，跌破5日線、成交量未放大，目前方向不明，適合先觀察。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2137,6 +2252,11 @@
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>訊號普通，站上5日線、死亡交叉、成交量放大，目前方向不明，適合先觀察。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2208,6 +2328,11 @@
           <t>短線賣壓重</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>目前偏弱，站上5日線、成交量未放大，短線不建議急著進場。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2279,6 +2404,11 @@
           <t>短線賣壓重</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>目前偏弱，站上5日線、空頭排列、爆量，短線不建議急著進場。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2348,6 +2478,11 @@
       <c r="S27" t="inlineStr">
         <is>
           <t>短線賣壓重</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>目前偏弱，站上5日線、空頭排列、成交量放大，短線不建議急著進場。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,52 +521,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>5505</v>
       </c>
       <c r="D2" t="n">
-        <v>50.49</v>
+        <v>4826</v>
       </c>
       <c r="E2" t="n">
-        <v>49.92</v>
+        <v>4804</v>
       </c>
       <c r="F2" t="n">
-        <v>49.9</v>
+        <v>4756.25</v>
       </c>
       <c r="G2" t="n">
-        <v>44114173</v>
+        <v>1801298</v>
       </c>
       <c r="H2" t="n">
-        <v>24067636</v>
+        <v>2244504</v>
       </c>
       <c r="I2" t="n">
-        <v>53.9</v>
+        <v>5505</v>
       </c>
       <c r="J2" t="n">
-        <v>47.35</v>
+        <v>4160</v>
       </c>
       <c r="K2" t="n">
-        <v>10000</v>
+        <v>359818</v>
       </c>
       <c r="L2" t="n">
-        <v>20000</v>
+        <v>1354542</v>
       </c>
       <c r="M2" t="n">
-        <v>35000</v>
+        <v>1447903</v>
       </c>
       <c r="N2" t="n">
-        <v>50000</v>
+        <v>2950399</v>
       </c>
       <c r="O2" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -580,69 +580,69 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、黃金交叉、爆量、接近20日高點</t>
+          <t>站上5日線、多頭排列、黃金交叉、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、黃金交叉、爆量、接近20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、黃金交叉、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.2</v>
+        <v>261</v>
       </c>
       <c r="D3" t="n">
-        <v>19.91</v>
+        <v>248.7</v>
       </c>
       <c r="E3" t="n">
-        <v>19.79</v>
+        <v>248.6</v>
       </c>
       <c r="F3" t="n">
-        <v>18.66</v>
+        <v>242.93</v>
       </c>
       <c r="G3" t="n">
-        <v>392811029</v>
+        <v>122990174</v>
       </c>
       <c r="H3" t="n">
-        <v>254953321</v>
+        <v>72731564</v>
       </c>
       <c r="I3" t="n">
-        <v>22.2</v>
+        <v>263.5</v>
       </c>
       <c r="J3" t="n">
-        <v>16.6</v>
+        <v>219.5</v>
       </c>
       <c r="K3" t="n">
-        <v>8000</v>
+        <v>55787312</v>
       </c>
       <c r="L3" t="n">
-        <v>12000</v>
+        <v>101690979</v>
       </c>
       <c r="M3" t="n">
-        <v>20000</v>
+        <v>84630201</v>
       </c>
       <c r="N3" t="n">
-        <v>35000</v>
+        <v>160089561</v>
       </c>
       <c r="O3" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -656,17 +656,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、爆量、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -682,43 +682,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11.85</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>10.6</v>
+        <v>11.13</v>
       </c>
       <c r="E4" t="n">
-        <v>10.53</v>
+        <v>10.86</v>
       </c>
       <c r="F4" t="n">
-        <v>9.52</v>
+        <v>9.75</v>
       </c>
       <c r="G4" t="n">
-        <v>100795639</v>
+        <v>43724582</v>
       </c>
       <c r="H4" t="n">
-        <v>63097678</v>
+        <v>60470183</v>
       </c>
       <c r="I4" t="n">
-        <v>11.85</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
         <v>8.119999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>3000</v>
+        <v>2108293</v>
       </c>
       <c r="L4" t="n">
-        <v>5000</v>
+        <v>59515291</v>
       </c>
       <c r="M4" t="n">
-        <v>8000</v>
+        <v>56282808</v>
       </c>
       <c r="N4" t="n">
-        <v>12000</v>
+        <v>50628800</v>
       </c>
       <c r="O4" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -732,69 +732,69 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、爆量、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>516</v>
+        <v>24.4</v>
       </c>
       <c r="D5" t="n">
-        <v>444.3</v>
+        <v>20.94</v>
       </c>
       <c r="E5" t="n">
-        <v>432.05</v>
+        <v>20.35</v>
       </c>
       <c r="F5" t="n">
-        <v>416.18</v>
+        <v>19.02</v>
       </c>
       <c r="G5" t="n">
-        <v>50890468</v>
+        <v>82302936</v>
       </c>
       <c r="H5" t="n">
-        <v>46138661</v>
+        <v>230537458</v>
       </c>
       <c r="I5" t="n">
-        <v>516</v>
+        <v>24.4</v>
       </c>
       <c r="J5" t="n">
-        <v>331</v>
+        <v>16.6</v>
       </c>
       <c r="K5" t="n">
-        <v>12000</v>
+        <v>18947923</v>
       </c>
       <c r="L5" t="n">
-        <v>25000</v>
+        <v>211604454</v>
       </c>
       <c r="M5" t="n">
-        <v>45000</v>
+        <v>192942642</v>
       </c>
       <c r="N5" t="n">
-        <v>80000</v>
+        <v>353520387</v>
       </c>
       <c r="O5" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -808,69 +808,69 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、成交量放大、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>629</v>
+        <v>36.4</v>
       </c>
       <c r="D6" t="n">
-        <v>543.8</v>
+        <v>31.13</v>
       </c>
       <c r="E6" t="n">
-        <v>486.75</v>
+        <v>29.88</v>
       </c>
       <c r="F6" t="n">
-        <v>411.23</v>
+        <v>29.14</v>
       </c>
       <c r="G6" t="n">
-        <v>72182688</v>
+        <v>66663284</v>
       </c>
       <c r="H6" t="n">
-        <v>71442747</v>
+        <v>67343380</v>
       </c>
       <c r="I6" t="n">
-        <v>629</v>
+        <v>36.4</v>
       </c>
       <c r="J6" t="n">
-        <v>290</v>
+        <v>25.45</v>
       </c>
       <c r="K6" t="n">
-        <v>15000</v>
+        <v>10178504</v>
       </c>
       <c r="L6" t="n">
-        <v>25000</v>
+        <v>70925202</v>
       </c>
       <c r="M6" t="n">
-        <v>40000</v>
+        <v>76924762</v>
       </c>
       <c r="N6" t="n">
-        <v>70000</v>
+        <v>66944449</v>
       </c>
       <c r="O6" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -884,69 +884,69 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、成交量放大、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>283</v>
+        <v>669</v>
       </c>
       <c r="D7" t="n">
-        <v>250.4</v>
+        <v>569.8</v>
       </c>
       <c r="E7" t="n">
-        <v>241.3</v>
+        <v>535.35</v>
       </c>
       <c r="F7" t="n">
-        <v>230.18</v>
+        <v>520.33</v>
       </c>
       <c r="G7" t="n">
-        <v>6909104</v>
+        <v>8536899</v>
       </c>
       <c r="H7" t="n">
-        <v>25802698</v>
+        <v>26502334</v>
       </c>
       <c r="I7" t="n">
-        <v>283</v>
+        <v>669</v>
       </c>
       <c r="J7" t="n">
-        <v>201</v>
+        <v>445.5</v>
       </c>
       <c r="K7" t="n">
-        <v>6000</v>
+        <v>964619</v>
       </c>
       <c r="L7" t="n">
-        <v>12000</v>
+        <v>17496756</v>
       </c>
       <c r="M7" t="n">
-        <v>18000</v>
+        <v>19603616</v>
       </c>
       <c r="N7" t="n">
-        <v>25000</v>
+        <v>18095930</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -960,69 +960,69 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、成交量未放大、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>609</v>
+        <v>57.1</v>
       </c>
       <c r="D8" t="n">
-        <v>537</v>
+        <v>52.56</v>
       </c>
       <c r="E8" t="n">
-        <v>518.75</v>
+        <v>50.76</v>
       </c>
       <c r="F8" t="n">
-        <v>513.17</v>
+        <v>50.01</v>
       </c>
       <c r="G8" t="n">
-        <v>10417136</v>
+        <v>16550566</v>
       </c>
       <c r="H8" t="n">
-        <v>27927013</v>
+        <v>8831247</v>
       </c>
       <c r="I8" t="n">
-        <v>609</v>
+        <v>58.5</v>
       </c>
       <c r="J8" t="n">
-        <v>445.5</v>
+        <v>45.45</v>
       </c>
       <c r="K8" t="n">
-        <v>8000</v>
+        <v>3454745</v>
       </c>
       <c r="L8" t="n">
-        <v>15000</v>
+        <v>13009409</v>
       </c>
       <c r="M8" t="n">
-        <v>25000</v>
+        <v>14246624</v>
       </c>
       <c r="N8" t="n">
-        <v>40000</v>
+        <v>12266815</v>
       </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1036,69 +1036,69 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、成交量未放大、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>522</v>
+        <v>1600</v>
       </c>
       <c r="D9" t="n">
-        <v>467.4</v>
+        <v>1362</v>
       </c>
       <c r="E9" t="n">
-        <v>454.85</v>
+        <v>1372.5</v>
       </c>
       <c r="F9" t="n">
-        <v>429.05</v>
+        <v>1279.05</v>
       </c>
       <c r="G9" t="n">
-        <v>4202780</v>
+        <v>1486000</v>
       </c>
       <c r="H9" t="n">
-        <v>4332139</v>
+        <v>1401800</v>
       </c>
       <c r="I9" t="n">
-        <v>528</v>
+        <v>1600</v>
       </c>
       <c r="J9" t="n">
-        <v>324.5</v>
+        <v>941</v>
       </c>
       <c r="K9" t="n">
-        <v>2000</v>
+        <v>282254</v>
       </c>
       <c r="L9" t="n">
-        <v>6000</v>
+        <v>969253</v>
       </c>
       <c r="M9" t="n">
-        <v>9000</v>
+        <v>1221688</v>
       </c>
       <c r="N9" t="n">
-        <v>12000</v>
+        <v>2123947</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1112,69 +1112,69 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量未放大、接近20日高點</t>
+          <t>站上5日線、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、成交量未放大、接近20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>990</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>901.2</v>
       </c>
       <c r="E10" t="n">
-        <v>197.65</v>
+        <v>879.1</v>
       </c>
       <c r="F10" t="n">
-        <v>187.38</v>
+        <v>869.4</v>
       </c>
       <c r="G10" t="n">
-        <v>27951666</v>
+        <v>24465071</v>
       </c>
       <c r="H10" t="n">
-        <v>16214445</v>
+        <v>28813042</v>
       </c>
       <c r="I10" t="n">
-        <v>216.5</v>
+        <v>1030</v>
       </c>
       <c r="J10" t="n">
-        <v>167</v>
+        <v>776</v>
       </c>
       <c r="K10" t="n">
-        <v>10000</v>
+        <v>1191293</v>
       </c>
       <c r="L10" t="n">
-        <v>18000</v>
+        <v>14796086</v>
       </c>
       <c r="M10" t="n">
-        <v>30000</v>
+        <v>14042095</v>
       </c>
       <c r="N10" t="n">
-        <v>50000</v>
+        <v>12040296</v>
       </c>
       <c r="O10" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1188,69 +1188,69 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、爆量，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>54.4</v>
+        <v>545</v>
       </c>
       <c r="D11" t="n">
-        <v>51.07</v>
+        <v>490.8</v>
       </c>
       <c r="E11" t="n">
-        <v>50.05</v>
+        <v>463.15</v>
       </c>
       <c r="F11" t="n">
-        <v>49.52</v>
+        <v>438.32</v>
       </c>
       <c r="G11" t="n">
-        <v>9214268</v>
+        <v>2767000</v>
       </c>
       <c r="H11" t="n">
-        <v>6313989</v>
+        <v>4459600</v>
       </c>
       <c r="I11" t="n">
-        <v>57</v>
+        <v>558</v>
       </c>
       <c r="J11" t="n">
-        <v>45.45</v>
+        <v>324.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3000</v>
+        <v>434414</v>
       </c>
       <c r="L11" t="n">
-        <v>5000</v>
+        <v>4299788</v>
       </c>
       <c r="M11" t="n">
-        <v>8000</v>
+        <v>9649180</v>
       </c>
       <c r="N11" t="n">
-        <v>10000</v>
+        <v>9535283</v>
       </c>
       <c r="O11" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1264,73 +1264,73 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、成交量放大，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1455</v>
+        <v>128.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1294</v>
+        <v>120.1</v>
       </c>
       <c r="E12" t="n">
-        <v>1358</v>
+        <v>123.8</v>
       </c>
       <c r="F12" t="n">
-        <v>1251.3</v>
+        <v>117.83</v>
       </c>
       <c r="G12" t="n">
-        <v>1582543</v>
+        <v>357612926</v>
       </c>
       <c r="H12" t="n">
-        <v>1588253</v>
+        <v>219239775</v>
       </c>
       <c r="I12" t="n">
-        <v>1480</v>
+        <v>136.5</v>
       </c>
       <c r="J12" t="n">
-        <v>941</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>5000</v>
+        <v>77651903</v>
       </c>
       <c r="L12" t="n">
-        <v>10000</v>
+        <v>96687402</v>
       </c>
       <c r="M12" t="n">
-        <v>20000</v>
+        <v>61728965</v>
       </c>
       <c r="N12" t="n">
-        <v>35000</v>
+        <v>182119556</v>
       </c>
       <c r="O12" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1340,73 +1340,73 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>站上5日線、成交量未放大、接近20日高點</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、成交量未放大、接近20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33.1</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>29.54</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>29.23</v>
+        <v>67.45</v>
       </c>
       <c r="F13" t="n">
-        <v>28.62</v>
+        <v>68.11</v>
       </c>
       <c r="G13" t="n">
-        <v>134312480</v>
+        <v>185285181</v>
       </c>
       <c r="H13" t="n">
-        <v>58293636</v>
+        <v>96433207</v>
       </c>
       <c r="I13" t="n">
-        <v>33.1</v>
+        <v>76.8</v>
       </c>
       <c r="J13" t="n">
-        <v>25.35</v>
+        <v>61.7</v>
       </c>
       <c r="K13" t="n">
-        <v>-2000</v>
+        <v>44538498</v>
       </c>
       <c r="L13" t="n">
-        <v>-5000</v>
+        <v>88202486</v>
       </c>
       <c r="M13" t="n">
-        <v>-8000</v>
+        <v>75247740</v>
       </c>
       <c r="N13" t="n">
-        <v>-12000</v>
+        <v>32596649</v>
       </c>
       <c r="O13" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1416,73 +1416,73 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、超級爆量、突破20日高點</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>短線賣壓重</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、多頭排列、超級爆量、突破20日高點，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5525</v>
+        <v>617</v>
       </c>
       <c r="D14" t="n">
-        <v>5152</v>
+        <v>527.2</v>
       </c>
       <c r="E14" t="n">
-        <v>5302</v>
+        <v>534.4</v>
       </c>
       <c r="F14" t="n">
-        <v>5076.5</v>
+        <v>523.17</v>
       </c>
       <c r="G14" t="n">
-        <v>1829705</v>
+        <v>26609382</v>
       </c>
       <c r="H14" t="n">
-        <v>1681714</v>
+        <v>28063686</v>
       </c>
       <c r="I14" t="n">
-        <v>5870</v>
+        <v>617</v>
       </c>
       <c r="J14" t="n">
-        <v>4320</v>
+        <v>465</v>
       </c>
       <c r="K14" t="n">
-        <v>15000</v>
+        <v>-1946569</v>
       </c>
       <c r="L14" t="n">
-        <v>30000</v>
+        <v>4398628</v>
       </c>
       <c r="M14" t="n">
-        <v>50000</v>
+        <v>375095</v>
       </c>
       <c r="N14" t="n">
-        <v>80000</v>
+        <v>-4267040</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1492,73 +1492,73 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、黃金交叉、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、成交量放大，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、量能未放大、突破20日高點、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="D15" t="n">
-        <v>80.98</v>
+        <v>51.14</v>
       </c>
       <c r="E15" t="n">
-        <v>81.02</v>
+        <v>50.02</v>
       </c>
       <c r="F15" t="n">
-        <v>78.97</v>
+        <v>49.98</v>
       </c>
       <c r="G15" t="n">
-        <v>15239585</v>
+        <v>29869029</v>
       </c>
       <c r="H15" t="n">
-        <v>11366488</v>
+        <v>27481089</v>
       </c>
       <c r="I15" t="n">
-        <v>85.5</v>
+        <v>53.9</v>
       </c>
       <c r="J15" t="n">
-        <v>70.2</v>
+        <v>47.35</v>
       </c>
       <c r="K15" t="n">
-        <v>2000</v>
+        <v>-7838235</v>
       </c>
       <c r="L15" t="n">
-        <v>4000</v>
+        <v>21017772</v>
       </c>
       <c r="M15" t="n">
-        <v>6000</v>
+        <v>26241510</v>
       </c>
       <c r="N15" t="n">
-        <v>10000</v>
+        <v>-434219</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1568,73 +1568,73 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、成交量放大，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>125</v>
+        <v>218.5</v>
       </c>
       <c r="D16" t="n">
-        <v>120.5</v>
+        <v>203.1</v>
       </c>
       <c r="E16" t="n">
-        <v>122.7</v>
+        <v>199.95</v>
       </c>
       <c r="F16" t="n">
-        <v>110.54</v>
+        <v>189.05</v>
       </c>
       <c r="G16" t="n">
-        <v>190947918</v>
+        <v>30348381</v>
       </c>
       <c r="H16" t="n">
-        <v>184433553</v>
+        <v>20400910</v>
       </c>
       <c r="I16" t="n">
-        <v>136.5</v>
+        <v>231</v>
       </c>
       <c r="J16" t="n">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="K16" t="n">
-        <v>2000</v>
+        <v>-1076740</v>
       </c>
       <c r="L16" t="n">
-        <v>5000</v>
+        <v>6371419</v>
       </c>
       <c r="M16" t="n">
-        <v>12000</v>
+        <v>6997630</v>
       </c>
       <c r="N16" t="n">
-        <v>15000</v>
+        <v>194327</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1644,73 +1644,73 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、成交量放大，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2255</v>
+        <v>317</v>
       </c>
       <c r="D17" t="n">
-        <v>2223</v>
+        <v>313.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2236</v>
+        <v>313.7</v>
       </c>
       <c r="F17" t="n">
-        <v>2235.75</v>
+        <v>299.55</v>
       </c>
       <c r="G17" t="n">
-        <v>24437825</v>
+        <v>35517666</v>
       </c>
       <c r="H17" t="n">
-        <v>27484516</v>
+        <v>36150847</v>
       </c>
       <c r="I17" t="n">
-        <v>2345</v>
+        <v>336.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2105</v>
+        <v>245</v>
       </c>
       <c r="K17" t="n">
-        <v>5000</v>
+        <v>2231528</v>
       </c>
       <c r="L17" t="n">
-        <v>12000</v>
+        <v>3889908</v>
       </c>
       <c r="M17" t="n">
-        <v>25000</v>
+        <v>9359269</v>
       </c>
       <c r="N17" t="n">
-        <v>40000</v>
+        <v>20009905</v>
       </c>
       <c r="O17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1720,73 +1720,73 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>站上5日線、成交量未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、成交量未放大，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1145</v>
+        <v>529</v>
       </c>
       <c r="D18" t="n">
-        <v>988.4</v>
+        <v>472.4</v>
       </c>
       <c r="E18" t="n">
-        <v>1005.2</v>
+        <v>443.75</v>
       </c>
       <c r="F18" t="n">
-        <v>1060.6</v>
+        <v>425.25</v>
       </c>
       <c r="G18" t="n">
-        <v>3404797</v>
+        <v>47336484</v>
       </c>
       <c r="H18" t="n">
-        <v>1568233</v>
+        <v>50597809</v>
       </c>
       <c r="I18" t="n">
-        <v>1300</v>
+        <v>558</v>
       </c>
       <c r="J18" t="n">
-        <v>865</v>
+        <v>331</v>
       </c>
       <c r="K18" t="n">
-        <v>6000</v>
+        <v>-5716319</v>
       </c>
       <c r="L18" t="n">
-        <v>12000</v>
+        <v>-1491026</v>
       </c>
       <c r="M18" t="n">
-        <v>20000</v>
+        <v>13501619</v>
       </c>
       <c r="N18" t="n">
-        <v>30000</v>
+        <v>10633143</v>
       </c>
       <c r="O18" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1796,290 +1796,294 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、超級爆量</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>短線偏強，站上5日線、空頭排列、超級爆量，可以列入觀察，但仍要注意是否追高。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>531</v>
+        <v>2290</v>
       </c>
       <c r="D19" t="n">
-        <v>473.5</v>
+        <v>2049</v>
       </c>
       <c r="E19" t="n">
-        <v>484.3</v>
+        <v>2085.5</v>
       </c>
       <c r="F19" t="n">
-        <v>499.57</v>
+        <v>2132.5</v>
       </c>
       <c r="G19" t="n">
-        <v>27582138</v>
+        <v>12049781</v>
       </c>
       <c r="H19" t="n">
-        <v>22972476</v>
+        <v>11885394</v>
       </c>
       <c r="I19" t="n">
-        <v>604</v>
+        <v>2370</v>
       </c>
       <c r="J19" t="n">
-        <v>436</v>
+        <v>1880</v>
       </c>
       <c r="K19" t="n">
-        <v>5000</v>
+        <v>4917556</v>
       </c>
       <c r="L19" t="n">
-        <v>10000</v>
+        <v>5273927</v>
       </c>
       <c r="M19" t="n">
-        <v>15000</v>
+        <v>1917848</v>
       </c>
       <c r="N19" t="n">
-        <v>20000</v>
+        <v>-4082627</v>
       </c>
       <c r="O19" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>可追蹤</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>目前有部分轉強訊號，站上5日線、空頭排列、成交量放大，可追蹤但不急著進場。</t>
+          <t>偏多觀察：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>934</v>
+        <v>83.7</v>
       </c>
       <c r="D20" t="n">
-        <v>844.8</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>854.5</v>
+        <v>81.34</v>
       </c>
       <c r="F20" t="n">
-        <v>895.45</v>
+        <v>79.59</v>
       </c>
       <c r="G20" t="n">
-        <v>16635783</v>
+        <v>11314147</v>
       </c>
       <c r="H20" t="n">
-        <v>13468721</v>
+        <v>10203164</v>
       </c>
       <c r="I20" t="n">
-        <v>1035</v>
+        <v>85.5</v>
       </c>
       <c r="J20" t="n">
-        <v>765</v>
+        <v>70.2</v>
       </c>
       <c r="K20" t="n">
-        <v>7000</v>
+        <v>-491799</v>
       </c>
       <c r="L20" t="n">
-        <v>15000</v>
+        <v>7106107</v>
       </c>
       <c r="M20" t="n">
-        <v>25000</v>
+        <v>4374099</v>
       </c>
       <c r="N20" t="n">
-        <v>35000</v>
+        <v>9626033</v>
       </c>
       <c r="O20" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>可追蹤</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>目前有部分轉強訊號，站上5日線、空頭排列、成交量放大，可追蹤但不急著進場。</t>
+          <t>偏多觀察：站上5日線、量能溫和放大、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>310.5</v>
+        <v>543</v>
       </c>
       <c r="D21" t="n">
-        <v>291.6</v>
+        <v>492</v>
       </c>
       <c r="E21" t="n">
-        <v>305.35</v>
+        <v>486</v>
       </c>
       <c r="F21" t="n">
-        <v>275.52</v>
+        <v>499.38</v>
       </c>
       <c r="G21" t="n">
-        <v>154923679</v>
+        <v>42354000</v>
       </c>
       <c r="H21" t="n">
-        <v>131047919</v>
+        <v>28553600</v>
       </c>
       <c r="I21" t="n">
-        <v>353</v>
+        <v>566</v>
       </c>
       <c r="J21" t="n">
-        <v>199</v>
+        <v>436</v>
       </c>
       <c r="K21" t="n">
-        <v>-5000</v>
+        <v>-709786</v>
       </c>
       <c r="L21" t="n">
-        <v>-2000</v>
+        <v>7825302</v>
       </c>
       <c r="M21" t="n">
-        <v>3000</v>
+        <v>4382193</v>
       </c>
       <c r="N21" t="n">
-        <v>8000</v>
+        <v>-4637373</v>
       </c>
       <c r="O21" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>可追蹤</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+          <t>站上5日線、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>目前有部分轉強訊號，站上5日線、成交量放大，可追蹤但不急著進場。</t>
+          <t>偏多觀察：站上5日線、量能溫和放大、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44.65</v>
+        <v>5610</v>
       </c>
       <c r="D22" t="n">
-        <v>39.67</v>
+        <v>5256</v>
       </c>
       <c r="E22" t="n">
-        <v>37.52</v>
+        <v>5329</v>
       </c>
       <c r="F22" t="n">
-        <v>31.72</v>
+        <v>5125.25</v>
       </c>
       <c r="G22" t="n">
-        <v>386510344</v>
+        <v>2115890</v>
       </c>
       <c r="H22" t="n">
-        <v>636475880</v>
+        <v>1971387</v>
       </c>
       <c r="I22" t="n">
-        <v>44.65</v>
+        <v>5880</v>
       </c>
       <c r="J22" t="n">
-        <v>22.95</v>
+        <v>4615</v>
       </c>
       <c r="K22" t="n">
-        <v>-71547</v>
+        <v>49559</v>
       </c>
       <c r="L22" t="n">
-        <v>-7378</v>
+        <v>97025</v>
       </c>
       <c r="M22" t="n">
-        <v>-219616</v>
+        <v>-160824</v>
       </c>
       <c r="N22" t="n">
-        <v>587508</v>
+        <v>-364679</v>
       </c>
       <c r="O22" t="n">
         <v>25</v>
@@ -2091,222 +2095,226 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>可追蹤</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量未放大、突破20日高點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>前期買超但短線轉弱、主力大賣</t>
+          <t>短線籌碼止穩、5日法人賣超</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>目前有部分轉強訊號，站上5日線、多頭排列、成交量未放大、突破20日高點，可追蹤但不急著進場。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、短線籌碼止穩、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1725</v>
+        <v>125</v>
       </c>
       <c r="D23" t="n">
-        <v>1741</v>
+        <v>115.2</v>
       </c>
       <c r="E23" t="n">
-        <v>1765</v>
+        <v>110.79</v>
       </c>
       <c r="F23" t="n">
-        <v>1557.75</v>
+        <v>97.3</v>
       </c>
       <c r="G23" t="n">
-        <v>2948990</v>
+        <v>340935766</v>
       </c>
       <c r="H23" t="n">
-        <v>4147491</v>
+        <v>249027598</v>
       </c>
       <c r="I23" t="n">
-        <v>1935</v>
+        <v>125</v>
       </c>
       <c r="J23" t="n">
-        <v>1055</v>
+        <v>70.7</v>
       </c>
       <c r="K23" t="n">
-        <v>4000</v>
+        <v>32836623</v>
       </c>
       <c r="L23" t="n">
-        <v>8000</v>
+        <v>-1979065</v>
       </c>
       <c r="M23" t="n">
-        <v>12000</v>
+        <v>-21222223</v>
       </c>
       <c r="N23" t="n">
-        <v>18000</v>
+        <v>49323216</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>籌碼轉強</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>訊號普通，跌破5日線、成交量未放大，目前方向不明，適合先觀察。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>717</v>
+        <v>2310</v>
       </c>
       <c r="D24" t="n">
-        <v>683.8</v>
+        <v>2237</v>
       </c>
       <c r="E24" t="n">
-        <v>728.7</v>
+        <v>2243.5</v>
       </c>
       <c r="F24" t="n">
-        <v>688.65</v>
+        <v>2242</v>
       </c>
       <c r="G24" t="n">
-        <v>6305022</v>
+        <v>28250944</v>
       </c>
       <c r="H24" t="n">
-        <v>4509007</v>
+        <v>32784457</v>
       </c>
       <c r="I24" t="n">
-        <v>849</v>
+        <v>2345</v>
       </c>
       <c r="J24" t="n">
-        <v>534</v>
+        <v>2135</v>
       </c>
       <c r="K24" t="n">
-        <v>-3000</v>
+        <v>8271589</v>
       </c>
       <c r="L24" t="n">
-        <v>2000</v>
+        <v>10332214</v>
       </c>
       <c r="M24" t="n">
-        <v>12000</v>
+        <v>-12125572</v>
       </c>
       <c r="N24" t="n">
-        <v>30000</v>
+        <v>-16581218</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>站上5日線、死亡交叉、成交量放大</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
+          <t>站上5日線、量能未放大、接近20日高點</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>訊號普通，站上5日線、死亡交叉、成交量放大，目前方向不明，適合先觀察。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日高點、短線籌碼止穩、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>250</v>
+        <v>788</v>
       </c>
       <c r="D25" t="n">
-        <v>246.2</v>
+        <v>701.8</v>
       </c>
       <c r="E25" t="n">
-        <v>247.7</v>
+        <v>724</v>
       </c>
       <c r="F25" t="n">
-        <v>240.95</v>
+        <v>698.95</v>
       </c>
       <c r="G25" t="n">
-        <v>55061095</v>
+        <v>5700000</v>
       </c>
       <c r="H25" t="n">
-        <v>59202085</v>
+        <v>4980000</v>
       </c>
       <c r="I25" t="n">
-        <v>260</v>
+        <v>849</v>
       </c>
       <c r="J25" t="n">
-        <v>218</v>
+        <v>534</v>
       </c>
       <c r="K25" t="n">
-        <v>-3000</v>
+        <v>-261357</v>
       </c>
       <c r="L25" t="n">
-        <v>-8000</v>
+        <v>-3141303</v>
       </c>
       <c r="M25" t="n">
-        <v>-15000</v>
+        <v>-4610982</v>
       </c>
       <c r="N25" t="n">
-        <v>-20000</v>
+        <v>-4787133</v>
       </c>
       <c r="O25" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2315,74 +2323,74 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>避開</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>站上5日線、成交量未放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>短線賣壓重</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>目前偏弱，站上5日線、成交量未放大，短線不建議急著進場。</t>
+          <t>風險偏高：站上5日線、黃金交叉、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>70.5</v>
+        <v>311</v>
       </c>
       <c r="D26" t="n">
-        <v>65.92</v>
+        <v>262.6</v>
       </c>
       <c r="E26" t="n">
-        <v>67.05</v>
+        <v>249.85</v>
       </c>
       <c r="F26" t="n">
-        <v>67.67</v>
+        <v>235.22</v>
       </c>
       <c r="G26" t="n">
-        <v>124473105</v>
+        <v>3433065</v>
       </c>
       <c r="H26" t="n">
-        <v>67843641</v>
+        <v>18105153</v>
       </c>
       <c r="I26" t="n">
-        <v>75.5</v>
+        <v>311</v>
       </c>
       <c r="J26" t="n">
-        <v>61.7</v>
+        <v>201</v>
       </c>
       <c r="K26" t="n">
-        <v>-3000</v>
+        <v>-1465366</v>
       </c>
       <c r="L26" t="n">
-        <v>-6000</v>
+        <v>-160620</v>
       </c>
       <c r="M26" t="n">
-        <v>-10000</v>
+        <v>-5984174</v>
       </c>
       <c r="N26" t="n">
-        <v>-15000</v>
+        <v>5074162</v>
       </c>
       <c r="O26" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2391,98 +2399,554 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>避開</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、爆量</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>短線賣壓重</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>目前偏弱，站上5日線、空頭排列、爆量，短線不建議急著進場。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>3163.TWO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>波若威</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1210</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1050.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1022.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1063.35</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7441000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2940200</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J27" t="n">
+        <v>865</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1014980</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1037784</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1279466</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1723078</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-15</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>站上5日線、爆量</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、爆量、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>8046.TW</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>884</v>
+      </c>
+      <c r="D28" t="n">
+        <v>863.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>852.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>895.95</v>
+      </c>
+      <c r="G28" t="n">
+        <v>30914905</v>
+      </c>
+      <c r="H28" t="n">
+        <v>17982182</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1035</v>
+      </c>
+      <c r="J28" t="n">
+        <v>765</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-8905954</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-4812274</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-4509560</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-8787097</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-20</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>站上5日線、成交量放大</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、成交量放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2408.TW</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>296</v>
+      </c>
+      <c r="D29" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>304.85</v>
+      </c>
+      <c r="F29" t="n">
+        <v>280.02</v>
+      </c>
+      <c r="G29" t="n">
+        <v>155862832</v>
+      </c>
+      <c r="H29" t="n">
+        <v>141256759</v>
+      </c>
+      <c r="I29" t="n">
+        <v>353</v>
+      </c>
+      <c r="J29" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-13921163</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-14185405</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-47727411</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-49157826</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-25</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>站上5日線、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3481.TW</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="D30" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="E30" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="G30" t="n">
+        <v>103739940</v>
+      </c>
+      <c r="H30" t="n">
+        <v>172083654</v>
+      </c>
+      <c r="I30" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="J30" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-2664727</v>
+      </c>
+      <c r="L30" t="n">
+        <v>121233278</v>
+      </c>
+      <c r="M30" t="n">
+        <v>74438491</v>
+      </c>
+      <c r="N30" t="n">
+        <v>153391454</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-25</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>4960.TW</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>誠美材</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>34.69</v>
-      </c>
-      <c r="E27" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="F27" t="n">
-        <v>37.68</v>
-      </c>
-      <c r="G27" t="n">
-        <v>25488550</v>
-      </c>
-      <c r="H27" t="n">
-        <v>17301029</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="C31" t="n">
+        <v>36</v>
+      </c>
+      <c r="D31" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="E31" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="F31" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16699898</v>
+      </c>
+      <c r="H31" t="n">
+        <v>18191883</v>
+      </c>
+      <c r="I31" t="n">
         <v>44.05</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J31" t="n">
         <v>31.1</v>
       </c>
-      <c r="K27" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-25000</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-20</v>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="K31" t="n">
+        <v>-1669951</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-4496950</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-8242967</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-5221995</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-35</v>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>避開</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>短線賣壓重</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>目前偏弱，站上5日線、空頭排列、成交量放大，短線不建議急著進場。</t>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>站上5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6285.TW</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>298</v>
+      </c>
+      <c r="D32" t="n">
+        <v>289.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>248.53</v>
+      </c>
+      <c r="G32" t="n">
+        <v>35285750</v>
+      </c>
+      <c r="H32" t="n">
+        <v>37916640</v>
+      </c>
+      <c r="I32" t="n">
+        <v>317</v>
+      </c>
+      <c r="J32" t="n">
+        <v>168</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-5937776</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-4853792</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-11223101</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1863302</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-35</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5289.TWO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1685</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1705</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1757.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1587.75</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4686000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4122200</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1935</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1115</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-352405</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-707137</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-868509</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-2148559</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-65</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,50 +469,55 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>量價異常</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>籌碼1日</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>籌碼3日</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>籌碼5日</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>籌碼10日</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>技術分數</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>綜合判斷</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>技術面</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>籌碼面</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>AI評語</t>
         </is>
@@ -521,456 +526,486 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5505</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>4826</v>
+        <v>33.58</v>
       </c>
       <c r="E2" t="n">
-        <v>4804</v>
+        <v>30.93</v>
       </c>
       <c r="F2" t="n">
-        <v>4756.25</v>
+        <v>29.77</v>
       </c>
       <c r="G2" t="n">
-        <v>1801298</v>
+        <v>210267926</v>
       </c>
       <c r="H2" t="n">
-        <v>2244504</v>
+        <v>105612204</v>
       </c>
       <c r="I2" t="n">
-        <v>5505</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>4160</v>
-      </c>
-      <c r="K2" t="n">
-        <v>359818</v>
+        <v>26.65</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>帶量突破20日高點</t>
+        </is>
       </c>
       <c r="L2" t="n">
-        <v>1354542</v>
+        <v>10178504</v>
       </c>
       <c r="M2" t="n">
-        <v>1447903</v>
+        <v>70925202</v>
       </c>
       <c r="N2" t="n">
-        <v>2950399</v>
+        <v>76924762</v>
       </c>
       <c r="O2" t="n">
-        <v>155</v>
-      </c>
-      <c r="P2" t="inlineStr">
+        <v>66944449</v>
+      </c>
+      <c r="P2" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、黃金交叉、量能未放大、突破20日高點</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、黃金交叉、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>261</v>
+        <v>13.65</v>
       </c>
       <c r="D3" t="n">
-        <v>248.7</v>
+        <v>11.83</v>
       </c>
       <c r="E3" t="n">
-        <v>248.6</v>
+        <v>11.16</v>
       </c>
       <c r="F3" t="n">
-        <v>242.93</v>
+        <v>10.02</v>
       </c>
       <c r="G3" t="n">
-        <v>122990174</v>
+        <v>478320069</v>
       </c>
       <c r="H3" t="n">
-        <v>72731564</v>
+        <v>148294428</v>
       </c>
       <c r="I3" t="n">
-        <v>263.5</v>
+        <v>14.3</v>
       </c>
       <c r="J3" t="n">
-        <v>219.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>55787312</v>
+        <v>8.130000000000001</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>帶量突破20日高點</t>
+        </is>
       </c>
       <c r="L3" t="n">
-        <v>101690979</v>
+        <v>2108293</v>
       </c>
       <c r="M3" t="n">
-        <v>84630201</v>
+        <v>59515291</v>
       </c>
       <c r="N3" t="n">
-        <v>160089561</v>
+        <v>56282808</v>
       </c>
       <c r="O3" t="n">
-        <v>135</v>
-      </c>
-      <c r="P3" t="inlineStr">
+        <v>50628800</v>
+      </c>
+      <c r="P3" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>696</v>
       </c>
       <c r="D4" t="n">
-        <v>11.13</v>
+        <v>606.4</v>
       </c>
       <c r="E4" t="n">
-        <v>10.86</v>
+        <v>555.55</v>
       </c>
       <c r="F4" t="n">
-        <v>9.75</v>
+        <v>529.38</v>
       </c>
       <c r="G4" t="n">
-        <v>43724582</v>
+        <v>50429815</v>
       </c>
       <c r="H4" t="n">
-        <v>60470183</v>
+        <v>29094105</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>719</v>
       </c>
       <c r="J4" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2108293</v>
+        <v>445.5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>帶量突破20日高點</t>
+        </is>
       </c>
       <c r="L4" t="n">
-        <v>59515291</v>
+        <v>964619</v>
       </c>
       <c r="M4" t="n">
-        <v>56282808</v>
+        <v>17496756</v>
       </c>
       <c r="N4" t="n">
-        <v>50628800</v>
+        <v>19603616</v>
       </c>
       <c r="O4" t="n">
-        <v>130</v>
-      </c>
-      <c r="P4" t="inlineStr">
+        <v>18095930</v>
+      </c>
+      <c r="P4" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.4</v>
+        <v>1085</v>
       </c>
       <c r="D5" t="n">
-        <v>20.94</v>
+        <v>954.6</v>
       </c>
       <c r="E5" t="n">
-        <v>20.35</v>
+        <v>900.1</v>
       </c>
       <c r="F5" t="n">
-        <v>19.02</v>
+        <v>881.7</v>
       </c>
       <c r="G5" t="n">
-        <v>82302936</v>
+        <v>34270461</v>
       </c>
       <c r="H5" t="n">
-        <v>230537458</v>
+        <v>30958709</v>
       </c>
       <c r="I5" t="n">
-        <v>24.4</v>
+        <v>1085</v>
       </c>
       <c r="J5" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>18947923</v>
+        <v>776</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L5" t="n">
-        <v>211604454</v>
+        <v>1191293</v>
       </c>
       <c r="M5" t="n">
-        <v>192942642</v>
+        <v>14796086</v>
       </c>
       <c r="N5" t="n">
-        <v>353520387</v>
+        <v>14042095</v>
       </c>
       <c r="O5" t="n">
-        <v>130</v>
-      </c>
-      <c r="P5" t="inlineStr">
+        <v>12040296</v>
+      </c>
+      <c r="P5" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.4</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>31.13</v>
+        <v>251.5</v>
       </c>
       <c r="E6" t="n">
-        <v>29.88</v>
+        <v>249.5</v>
       </c>
       <c r="F6" t="n">
-        <v>29.14</v>
+        <v>244.47</v>
       </c>
       <c r="G6" t="n">
-        <v>66663284</v>
+        <v>55665305</v>
       </c>
       <c r="H6" t="n">
-        <v>67343380</v>
+        <v>69819957</v>
       </c>
       <c r="I6" t="n">
-        <v>36.4</v>
+        <v>263.5</v>
       </c>
       <c r="J6" t="n">
-        <v>25.45</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10178504</v>
+        <v>219.5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L6" t="n">
-        <v>70925202</v>
+        <v>55787312</v>
       </c>
       <c r="M6" t="n">
-        <v>76924762</v>
+        <v>101690979</v>
       </c>
       <c r="N6" t="n">
-        <v>66944449</v>
+        <v>84630201</v>
       </c>
       <c r="O6" t="n">
-        <v>130</v>
-      </c>
-      <c r="P6" t="inlineStr">
+        <v>160089561</v>
+      </c>
+      <c r="P6" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>669</v>
+        <v>5290</v>
       </c>
       <c r="D7" t="n">
-        <v>569.8</v>
+        <v>4977</v>
       </c>
       <c r="E7" t="n">
-        <v>535.35</v>
+        <v>4843</v>
       </c>
       <c r="F7" t="n">
-        <v>520.33</v>
+        <v>4784.25</v>
       </c>
       <c r="G7" t="n">
-        <v>8536899</v>
+        <v>2917258</v>
       </c>
       <c r="H7" t="n">
-        <v>26502334</v>
+        <v>2443800</v>
       </c>
       <c r="I7" t="n">
-        <v>669</v>
+        <v>5635</v>
       </c>
       <c r="J7" t="n">
-        <v>445.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>964619</v>
+        <v>4160</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L7" t="n">
-        <v>17496756</v>
+        <v>359818</v>
       </c>
       <c r="M7" t="n">
-        <v>19603616</v>
+        <v>1354542</v>
       </c>
       <c r="N7" t="n">
-        <v>18095930</v>
+        <v>1447903</v>
       </c>
       <c r="O7" t="n">
-        <v>130</v>
-      </c>
-      <c r="P7" t="inlineStr">
+        <v>2950399</v>
+      </c>
+      <c r="P7" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -986,141 +1021,151 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57.1</v>
+        <v>55.4</v>
       </c>
       <c r="D8" t="n">
-        <v>52.56</v>
+        <v>53.91</v>
       </c>
       <c r="E8" t="n">
-        <v>50.76</v>
+        <v>51.25</v>
       </c>
       <c r="F8" t="n">
-        <v>50.01</v>
+        <v>50.42</v>
       </c>
       <c r="G8" t="n">
-        <v>16550566</v>
+        <v>15723414</v>
       </c>
       <c r="H8" t="n">
-        <v>8831247</v>
+        <v>11255762</v>
       </c>
       <c r="I8" t="n">
-        <v>58.5</v>
+        <v>60.3</v>
       </c>
       <c r="J8" t="n">
         <v>45.45</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>3454745</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>13009409</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>14246624</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>12266815</v>
       </c>
-      <c r="O8" t="n">
-        <v>120</v>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1600</v>
+        <v>141</v>
       </c>
       <c r="D9" t="n">
-        <v>1362</v>
+        <v>124.8</v>
       </c>
       <c r="E9" t="n">
-        <v>1372.5</v>
+        <v>125.75</v>
       </c>
       <c r="F9" t="n">
-        <v>1279.05</v>
+        <v>114.91</v>
       </c>
       <c r="G9" t="n">
-        <v>1486000</v>
+        <v>336105421</v>
       </c>
       <c r="H9" t="n">
-        <v>1401800</v>
+        <v>249474700</v>
       </c>
       <c r="I9" t="n">
-        <v>1600</v>
+        <v>141</v>
       </c>
       <c r="J9" t="n">
-        <v>941</v>
-      </c>
-      <c r="K9" t="n">
-        <v>282254</v>
+        <v>88.8</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L9" t="n">
-        <v>969253</v>
+        <v>77651903</v>
       </c>
       <c r="M9" t="n">
-        <v>1221688</v>
+        <v>96687402</v>
       </c>
       <c r="N9" t="n">
-        <v>2123947</v>
+        <v>61728965</v>
       </c>
       <c r="O9" t="n">
+        <v>182119556</v>
+      </c>
+      <c r="P9" t="n">
         <v>115</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>站上5日線、量能溫和放大、突破20日高點</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>強勢偏多：站上5日線、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
@@ -1129,74 +1174,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>990</v>
+        <v>533</v>
       </c>
       <c r="D10" t="n">
-        <v>901.2</v>
+        <v>511.6</v>
       </c>
       <c r="E10" t="n">
-        <v>879.1</v>
+        <v>468.75</v>
       </c>
       <c r="F10" t="n">
-        <v>869.4</v>
+        <v>448.2</v>
       </c>
       <c r="G10" t="n">
-        <v>24465071</v>
+        <v>2520000</v>
       </c>
       <c r="H10" t="n">
-        <v>28813042</v>
+        <v>4413800</v>
       </c>
       <c r="I10" t="n">
-        <v>1030</v>
+        <v>558</v>
       </c>
       <c r="J10" t="n">
-        <v>776</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1191293</v>
+        <v>340</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L10" t="n">
-        <v>14796086</v>
+        <v>434414</v>
       </c>
       <c r="M10" t="n">
-        <v>14042095</v>
+        <v>4299788</v>
       </c>
       <c r="N10" t="n">
-        <v>12040296</v>
+        <v>9649180</v>
       </c>
       <c r="O10" t="n">
+        <v>9535283</v>
+      </c>
+      <c r="P10" t="n">
         <v>105</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
@@ -1205,152 +1255,162 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>545</v>
+        <v>1580</v>
       </c>
       <c r="D11" t="n">
-        <v>490.8</v>
+        <v>1433</v>
       </c>
       <c r="E11" t="n">
-        <v>463.15</v>
+        <v>1385.5</v>
       </c>
       <c r="F11" t="n">
-        <v>438.32</v>
+        <v>1308.55</v>
       </c>
       <c r="G11" t="n">
-        <v>2767000</v>
+        <v>9546000</v>
       </c>
       <c r="H11" t="n">
-        <v>4459600</v>
+        <v>3017800</v>
       </c>
       <c r="I11" t="n">
-        <v>558</v>
+        <v>1700</v>
       </c>
       <c r="J11" t="n">
-        <v>324.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>434414</v>
+        <v>941</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>爆量價未漲</t>
+        </is>
       </c>
       <c r="L11" t="n">
-        <v>4299788</v>
+        <v>282254</v>
       </c>
       <c r="M11" t="n">
-        <v>9649180</v>
+        <v>969253</v>
       </c>
       <c r="N11" t="n">
-        <v>9535283</v>
+        <v>1221688</v>
       </c>
       <c r="O11" t="n">
+        <v>2123947</v>
+      </c>
+      <c r="P11" t="n">
         <v>105</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>128.5</v>
+        <v>661</v>
       </c>
       <c r="D12" t="n">
-        <v>120.1</v>
+        <v>614.6</v>
       </c>
       <c r="E12" t="n">
-        <v>123.8</v>
+        <v>540.85</v>
       </c>
       <c r="F12" t="n">
-        <v>117.83</v>
+        <v>448.73</v>
       </c>
       <c r="G12" t="n">
-        <v>357612926</v>
+        <v>29457930</v>
       </c>
       <c r="H12" t="n">
-        <v>219239775</v>
+        <v>56139070</v>
       </c>
       <c r="I12" t="n">
-        <v>136.5</v>
+        <v>691</v>
       </c>
       <c r="J12" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="K12" t="n">
-        <v>77651903</v>
+        <v>307</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L12" t="n">
-        <v>96687402</v>
+        <v>2231528</v>
       </c>
       <c r="M12" t="n">
-        <v>61728965</v>
+        <v>3889908</v>
       </c>
       <c r="N12" t="n">
-        <v>182119556</v>
+        <v>9359269</v>
       </c>
       <c r="O12" t="n">
-        <v>95</v>
-      </c>
-      <c r="P12" t="inlineStr">
+        <v>20009905</v>
+      </c>
+      <c r="P12" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>站上5日線、成交量放大</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -1366,903 +1426,963 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>73.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D13" t="n">
-        <v>67.73999999999999</v>
+        <v>69.12</v>
       </c>
       <c r="E13" t="n">
-        <v>67.45</v>
+        <v>67.56</v>
       </c>
       <c r="F13" t="n">
-        <v>68.11</v>
+        <v>68.52</v>
       </c>
       <c r="G13" t="n">
-        <v>185285181</v>
+        <v>337055872</v>
       </c>
       <c r="H13" t="n">
-        <v>96433207</v>
+        <v>147844553</v>
       </c>
       <c r="I13" t="n">
-        <v>76.8</v>
+        <v>81.2</v>
       </c>
       <c r="J13" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="K13" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>爆量價未漲</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>44538498</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>88202486</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>75247740</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>32596649</v>
       </c>
-      <c r="O13" t="n">
-        <v>95</v>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>站上5日線、成交量放大</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>617</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>527.2</v>
+        <v>21.51</v>
       </c>
       <c r="E14" t="n">
-        <v>534.4</v>
+        <v>20.48</v>
       </c>
       <c r="F14" t="n">
-        <v>523.17</v>
+        <v>19.25</v>
       </c>
       <c r="G14" t="n">
-        <v>26609382</v>
+        <v>818361725</v>
       </c>
       <c r="H14" t="n">
-        <v>28063686</v>
+        <v>356215638</v>
       </c>
       <c r="I14" t="n">
-        <v>617</v>
+        <v>25.8</v>
       </c>
       <c r="J14" t="n">
-        <v>465</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-1946569</v>
+        <v>16.6</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>爆量價未漲</t>
+        </is>
       </c>
       <c r="L14" t="n">
-        <v>4398628</v>
+        <v>18947923</v>
       </c>
       <c r="M14" t="n">
-        <v>375095</v>
+        <v>211604454</v>
       </c>
       <c r="N14" t="n">
-        <v>-4267040</v>
+        <v>192942642</v>
       </c>
       <c r="O14" t="n">
-        <v>90</v>
-      </c>
-      <c r="P14" t="inlineStr">
+        <v>353520387</v>
+      </c>
+      <c r="P14" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>站上5日線、黃金交叉、量能未放大、突破20日高點</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能未放大、突破20日高點、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>51.8</v>
+        <v>562</v>
       </c>
       <c r="D15" t="n">
-        <v>51.14</v>
+        <v>513.1</v>
       </c>
       <c r="E15" t="n">
-        <v>50.02</v>
+        <v>491</v>
       </c>
       <c r="F15" t="n">
-        <v>49.98</v>
+        <v>502.85</v>
       </c>
       <c r="G15" t="n">
-        <v>29869029</v>
+        <v>33746000</v>
       </c>
       <c r="H15" t="n">
-        <v>27481089</v>
+        <v>31597000</v>
       </c>
       <c r="I15" t="n">
-        <v>53.9</v>
+        <v>566</v>
       </c>
       <c r="J15" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-7838235</v>
+        <v>436</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L15" t="n">
-        <v>21017772</v>
+        <v>-709786</v>
       </c>
       <c r="M15" t="n">
-        <v>26241510</v>
+        <v>7825302</v>
       </c>
       <c r="N15" t="n">
-        <v>-434219</v>
+        <v>4382193</v>
       </c>
       <c r="O15" t="n">
-        <v>85</v>
-      </c>
-      <c r="P15" t="inlineStr">
+        <v>-4637373</v>
+      </c>
+      <c r="P15" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、接近20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>218.5</v>
+        <v>2350</v>
       </c>
       <c r="D16" t="n">
-        <v>203.1</v>
+        <v>2136</v>
       </c>
       <c r="E16" t="n">
-        <v>199.95</v>
+        <v>2101</v>
       </c>
       <c r="F16" t="n">
-        <v>189.05</v>
+        <v>2149</v>
       </c>
       <c r="G16" t="n">
-        <v>30348381</v>
+        <v>12198582</v>
       </c>
       <c r="H16" t="n">
-        <v>20400910</v>
+        <v>11067330</v>
       </c>
       <c r="I16" t="n">
-        <v>231</v>
+        <v>2410</v>
       </c>
       <c r="J16" t="n">
-        <v>167</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-1076740</v>
+        <v>1880</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L16" t="n">
-        <v>6371419</v>
+        <v>4917556</v>
       </c>
       <c r="M16" t="n">
-        <v>6997630</v>
+        <v>5273927</v>
       </c>
       <c r="N16" t="n">
-        <v>194327</v>
+        <v>1917848</v>
       </c>
       <c r="O16" t="n">
-        <v>85</v>
-      </c>
-      <c r="P16" t="inlineStr">
+        <v>-4082627</v>
+      </c>
+      <c r="P16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>317</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>313.5</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>313.7</v>
+        <v>81.34</v>
       </c>
       <c r="F17" t="n">
-        <v>299.55</v>
+        <v>80.16</v>
       </c>
       <c r="G17" t="n">
-        <v>35517666</v>
+        <v>12463968</v>
       </c>
       <c r="H17" t="n">
-        <v>36150847</v>
+        <v>10197116</v>
       </c>
       <c r="I17" t="n">
-        <v>336.5</v>
+        <v>85.8</v>
       </c>
       <c r="J17" t="n">
-        <v>245</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2231528</v>
+        <v>70.2</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L17" t="n">
-        <v>3889908</v>
+        <v>-491799</v>
       </c>
       <c r="M17" t="n">
-        <v>9359269</v>
+        <v>7106107</v>
       </c>
       <c r="N17" t="n">
-        <v>20009905</v>
+        <v>4374099</v>
       </c>
       <c r="O17" t="n">
-        <v>80</v>
-      </c>
-      <c r="P17" t="inlineStr">
+        <v>9626033</v>
+      </c>
+      <c r="P17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>站上5日線、量能未放大</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>529</v>
+        <v>611</v>
       </c>
       <c r="D18" t="n">
-        <v>472.4</v>
+        <v>555</v>
       </c>
       <c r="E18" t="n">
-        <v>443.75</v>
+        <v>540</v>
       </c>
       <c r="F18" t="n">
-        <v>425.25</v>
+        <v>528.95</v>
       </c>
       <c r="G18" t="n">
-        <v>47336484</v>
+        <v>39627497</v>
       </c>
       <c r="H18" t="n">
-        <v>50597809</v>
+        <v>28597065</v>
       </c>
       <c r="I18" t="n">
-        <v>558</v>
+        <v>636</v>
       </c>
       <c r="J18" t="n">
-        <v>331</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-5716319</v>
+        <v>465</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L18" t="n">
-        <v>-1491026</v>
+        <v>-1946569</v>
       </c>
       <c r="M18" t="n">
-        <v>13501619</v>
+        <v>4398628</v>
       </c>
       <c r="N18" t="n">
-        <v>10633143</v>
+        <v>375095</v>
       </c>
       <c r="O18" t="n">
+        <v>-4267040</v>
+      </c>
+      <c r="P18" t="n">
         <v>75</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>5日法人買超</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2290</v>
+        <v>45.7</v>
       </c>
       <c r="D19" t="n">
-        <v>2049</v>
+        <v>43.4</v>
       </c>
       <c r="E19" t="n">
-        <v>2085.5</v>
+        <v>40.22</v>
       </c>
       <c r="F19" t="n">
-        <v>2132.5</v>
+        <v>34.08</v>
       </c>
       <c r="G19" t="n">
-        <v>12049781</v>
+        <v>1463227218</v>
       </c>
       <c r="H19" t="n">
-        <v>11885394</v>
+        <v>613882104</v>
       </c>
       <c r="I19" t="n">
-        <v>2370</v>
+        <v>52.2</v>
       </c>
       <c r="J19" t="n">
-        <v>1880</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4917556</v>
+        <v>23.65</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>爆量價未漲</t>
+        </is>
       </c>
       <c r="L19" t="n">
-        <v>5273927</v>
+        <v>-2664727</v>
       </c>
       <c r="M19" t="n">
-        <v>1917848</v>
+        <v>121233278</v>
       </c>
       <c r="N19" t="n">
-        <v>-4082627</v>
+        <v>74438491</v>
       </c>
       <c r="O19" t="n">
-        <v>65</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>👀觀察</t>
-        </is>
+        <v>153391454</v>
+      </c>
+      <c r="P19" t="n">
+        <v>75</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>83.7</v>
+        <v>540</v>
       </c>
       <c r="D20" t="n">
-        <v>81.23999999999999</v>
+        <v>498.7</v>
       </c>
       <c r="E20" t="n">
-        <v>81.34</v>
+        <v>457.05</v>
       </c>
       <c r="F20" t="n">
-        <v>79.59</v>
+        <v>434.32</v>
       </c>
       <c r="G20" t="n">
-        <v>11314147</v>
+        <v>41904053</v>
       </c>
       <c r="H20" t="n">
-        <v>10203164</v>
+        <v>51443369</v>
       </c>
       <c r="I20" t="n">
-        <v>85.5</v>
+        <v>558</v>
       </c>
       <c r="J20" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-491799</v>
+        <v>354</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L20" t="n">
-        <v>7106107</v>
+        <v>-5716319</v>
       </c>
       <c r="M20" t="n">
-        <v>4374099</v>
+        <v>-1491026</v>
       </c>
       <c r="N20" t="n">
-        <v>9626033</v>
+        <v>13501619</v>
       </c>
       <c r="O20" t="n">
-        <v>60</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>👀觀察</t>
-        </is>
+        <v>10633143</v>
+      </c>
+      <c r="P20" t="n">
+        <v>75</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>偏多觀察：站上5日線、量能溫和放大、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>543</v>
+        <v>52</v>
       </c>
       <c r="D21" t="n">
-        <v>492</v>
+        <v>51.64</v>
       </c>
       <c r="E21" t="n">
-        <v>486</v>
+        <v>50.21</v>
       </c>
       <c r="F21" t="n">
-        <v>499.38</v>
+        <v>50.11</v>
       </c>
       <c r="G21" t="n">
-        <v>42354000</v>
+        <v>14910096</v>
       </c>
       <c r="H21" t="n">
-        <v>28553600</v>
+        <v>26622786</v>
       </c>
       <c r="I21" t="n">
-        <v>566</v>
+        <v>53.9</v>
       </c>
       <c r="J21" t="n">
-        <v>436</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-709786</v>
+        <v>47.35</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L21" t="n">
-        <v>7825302</v>
+        <v>-7838235</v>
       </c>
       <c r="M21" t="n">
-        <v>4382193</v>
+        <v>21017772</v>
       </c>
       <c r="N21" t="n">
-        <v>-4637373</v>
+        <v>26241510</v>
       </c>
       <c r="O21" t="n">
-        <v>60</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>👀觀察</t>
-        </is>
+        <v>-434219</v>
+      </c>
+      <c r="P21" t="n">
+        <v>75</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>5日法人明顯買超</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>偏多觀察：站上5日線、量能溫和放大、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5610</v>
+        <v>208</v>
       </c>
       <c r="D22" t="n">
-        <v>5256</v>
+        <v>207</v>
       </c>
       <c r="E22" t="n">
-        <v>5329</v>
+        <v>199.9</v>
       </c>
       <c r="F22" t="n">
-        <v>5125.25</v>
+        <v>190.12</v>
       </c>
       <c r="G22" t="n">
-        <v>2115890</v>
+        <v>20600438</v>
       </c>
       <c r="H22" t="n">
-        <v>1971387</v>
+        <v>22454689</v>
       </c>
       <c r="I22" t="n">
-        <v>5880</v>
+        <v>231</v>
       </c>
       <c r="J22" t="n">
-        <v>4615</v>
-      </c>
-      <c r="K22" t="n">
-        <v>49559</v>
+        <v>167</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L22" t="n">
-        <v>97025</v>
+        <v>-1076740</v>
       </c>
       <c r="M22" t="n">
-        <v>-160824</v>
+        <v>6371419</v>
       </c>
       <c r="N22" t="n">
-        <v>-364679</v>
+        <v>6997630</v>
       </c>
       <c r="O22" t="n">
-        <v>25</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>⚠️整理</t>
-        </is>
+        <v>194327</v>
+      </c>
+      <c r="P22" t="n">
+        <v>75</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、短線籌碼止穩、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>125</v>
+        <v>2270</v>
       </c>
       <c r="D23" t="n">
-        <v>115.2</v>
+        <v>2250</v>
       </c>
       <c r="E23" t="n">
-        <v>110.79</v>
+        <v>2245</v>
       </c>
       <c r="F23" t="n">
-        <v>97.3</v>
+        <v>2242.25</v>
       </c>
       <c r="G23" t="n">
-        <v>340935766</v>
+        <v>32781470</v>
       </c>
       <c r="H23" t="n">
-        <v>249027598</v>
+        <v>30223565</v>
       </c>
       <c r="I23" t="n">
-        <v>125</v>
+        <v>2345</v>
       </c>
       <c r="J23" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>32836623</v>
+        <v>2135</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L23" t="n">
-        <v>-1979065</v>
+        <v>8271589</v>
       </c>
       <c r="M23" t="n">
-        <v>-21222223</v>
+        <v>10332214</v>
       </c>
       <c r="N23" t="n">
-        <v>49323216</v>
+        <v>-12125572</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>⚠️整理</t>
-        </is>
+        <v>-16581218</v>
+      </c>
+      <c r="P23" t="n">
+        <v>65</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>偏多觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、短線籌碼止穩、5日法人明顯賣超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2310</v>
+        <v>342</v>
       </c>
       <c r="D24" t="n">
-        <v>2237</v>
+        <v>285.6</v>
       </c>
       <c r="E24" t="n">
-        <v>2243.5</v>
+        <v>261.4</v>
       </c>
       <c r="F24" t="n">
-        <v>2242</v>
+        <v>241.47</v>
       </c>
       <c r="G24" t="n">
-        <v>28250944</v>
+        <v>57938700</v>
       </c>
       <c r="H24" t="n">
-        <v>32784457</v>
+        <v>22861322</v>
       </c>
       <c r="I24" t="n">
-        <v>2345</v>
+        <v>342</v>
       </c>
       <c r="J24" t="n">
-        <v>2135</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8271589</v>
+        <v>201</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>帶量突破20日高點</t>
+        </is>
       </c>
       <c r="L24" t="n">
-        <v>10332214</v>
+        <v>-1465366</v>
       </c>
       <c r="M24" t="n">
-        <v>-12125572</v>
+        <v>-160620</v>
       </c>
       <c r="N24" t="n">
-        <v>-16581218</v>
+        <v>-5984174</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
-      </c>
-      <c r="P24" t="inlineStr">
+        <v>5074162</v>
+      </c>
+      <c r="P24" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>⚠️整理</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>整理觀察</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>站上5日線、量能未放大、接近20日高點</t>
-        </is>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日高點、短線籌碼止穩、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>整理觀察：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -2278,143 +2398,153 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>788</v>
+        <v>866</v>
       </c>
       <c r="D25" t="n">
-        <v>701.8</v>
+        <v>742</v>
       </c>
       <c r="E25" t="n">
-        <v>724</v>
+        <v>732.1</v>
       </c>
       <c r="F25" t="n">
-        <v>698.95</v>
+        <v>711.25</v>
       </c>
       <c r="G25" t="n">
-        <v>5700000</v>
+        <v>2958000</v>
       </c>
       <c r="H25" t="n">
-        <v>4980000</v>
+        <v>4678000</v>
       </c>
       <c r="I25" t="n">
-        <v>849</v>
+        <v>866</v>
       </c>
       <c r="J25" t="n">
         <v>534</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
         <v>-261357</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-3141303</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-4610982</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>-4787133</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
-        </is>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>風險偏高：站上5日線、黃金交叉、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>311</v>
+        <v>5280</v>
       </c>
       <c r="D26" t="n">
-        <v>262.6</v>
+        <v>5334</v>
       </c>
       <c r="E26" t="n">
-        <v>249.85</v>
+        <v>5278</v>
       </c>
       <c r="F26" t="n">
-        <v>235.22</v>
+        <v>5144.75</v>
       </c>
       <c r="G26" t="n">
-        <v>3433065</v>
+        <v>2655826</v>
       </c>
       <c r="H26" t="n">
-        <v>18105153</v>
+        <v>2172103</v>
       </c>
       <c r="I26" t="n">
-        <v>311</v>
+        <v>5880</v>
       </c>
       <c r="J26" t="n">
-        <v>201</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-1465366</v>
+        <v>4615</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L26" t="n">
-        <v>-160620</v>
+        <v>49559</v>
       </c>
       <c r="M26" t="n">
-        <v>-5984174</v>
+        <v>97025</v>
       </c>
       <c r="N26" t="n">
-        <v>5074162</v>
+        <v>-160824</v>
       </c>
       <c r="O26" t="n">
-        <v>-10</v>
-      </c>
-      <c r="P26" t="inlineStr">
+        <v>-364679</v>
+      </c>
+      <c r="P26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
-        </is>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>短線籌碼止穩、5日法人賣超</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -2430,22 +2560,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1210</v>
+        <v>1220</v>
       </c>
       <c r="D27" t="n">
-        <v>1050.4</v>
+        <v>1114.4</v>
       </c>
       <c r="E27" t="n">
-        <v>1022.2</v>
+        <v>1037.7</v>
       </c>
       <c r="F27" t="n">
-        <v>1063.35</v>
+        <v>1072.35</v>
       </c>
       <c r="G27" t="n">
-        <v>7441000</v>
+        <v>4415000</v>
       </c>
       <c r="H27" t="n">
-        <v>2940200</v>
+        <v>3736800</v>
       </c>
       <c r="I27" t="n">
         <v>1300</v>
@@ -2453,120 +2583,130 @@
       <c r="J27" t="n">
         <v>865</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
         <v>-1014980</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>-1037784</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>-1279466</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>-1723078</v>
       </c>
-      <c r="O27" t="n">
-        <v>-15</v>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>站上5日線、爆量</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>風險偏高：站上5日線、爆量、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、黃金交叉、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>884</v>
+        <v>130.5</v>
       </c>
       <c r="D28" t="n">
-        <v>863.4</v>
+        <v>118.7</v>
       </c>
       <c r="E28" t="n">
-        <v>852.1</v>
+        <v>113.39</v>
       </c>
       <c r="F28" t="n">
-        <v>895.95</v>
+        <v>100.19</v>
       </c>
       <c r="G28" t="n">
-        <v>30914905</v>
+        <v>291896012</v>
       </c>
       <c r="H28" t="n">
-        <v>17982182</v>
+        <v>252641517</v>
       </c>
       <c r="I28" t="n">
-        <v>1035</v>
+        <v>133.5</v>
       </c>
       <c r="J28" t="n">
-        <v>765</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-8905954</v>
+        <v>71.3</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L28" t="n">
-        <v>-4812274</v>
+        <v>32836623</v>
       </c>
       <c r="M28" t="n">
-        <v>-4509560</v>
+        <v>-1979065</v>
       </c>
       <c r="N28" t="n">
-        <v>-8787097</v>
+        <v>-21222223</v>
       </c>
       <c r="O28" t="n">
-        <v>-20</v>
-      </c>
-      <c r="P28" t="inlineStr">
+        <v>49323216</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>站上5日線、成交量放大</t>
-        </is>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -2582,22 +2722,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>296</v>
+        <v>303.5</v>
       </c>
       <c r="D29" t="n">
-        <v>289.8</v>
+        <v>295.6</v>
       </c>
       <c r="E29" t="n">
-        <v>304.85</v>
+        <v>303.1</v>
       </c>
       <c r="F29" t="n">
-        <v>280.02</v>
+        <v>283.88</v>
       </c>
       <c r="G29" t="n">
-        <v>155862832</v>
+        <v>152949355</v>
       </c>
       <c r="H29" t="n">
-        <v>141256759</v>
+        <v>148065232</v>
       </c>
       <c r="I29" t="n">
         <v>353</v>
@@ -2605,42 +2745,47 @@
       <c r="J29" t="n">
         <v>214.5</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
         <v>-13921163</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>-14185405</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>-47727411</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>-49157826</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>-25</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
@@ -2649,228 +2794,243 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23.95</v>
+        <v>922</v>
       </c>
       <c r="D30" t="n">
-        <v>23.99</v>
+        <v>888.2</v>
       </c>
       <c r="E30" t="n">
-        <v>24.77</v>
+        <v>854.3</v>
       </c>
       <c r="F30" t="n">
-        <v>25.45</v>
+        <v>896.4</v>
       </c>
       <c r="G30" t="n">
-        <v>103739940</v>
+        <v>24438087</v>
       </c>
       <c r="H30" t="n">
-        <v>172083654</v>
+        <v>20893593</v>
       </c>
       <c r="I30" t="n">
-        <v>28.9</v>
+        <v>1035</v>
       </c>
       <c r="J30" t="n">
-        <v>22.95</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-2664727</v>
+        <v>765</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L30" t="n">
-        <v>121233278</v>
+        <v>-8905954</v>
       </c>
       <c r="M30" t="n">
-        <v>74438491</v>
+        <v>-4812274</v>
       </c>
       <c r="N30" t="n">
-        <v>153391454</v>
+        <v>-4509560</v>
       </c>
       <c r="O30" t="n">
+        <v>-8787097</v>
+      </c>
+      <c r="P30" t="n">
         <v>-25</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
-        </is>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>36</v>
+        <v>304.5</v>
       </c>
       <c r="D31" t="n">
-        <v>35.19</v>
+        <v>291.6</v>
       </c>
       <c r="E31" t="n">
-        <v>34.98</v>
+        <v>282.85</v>
       </c>
       <c r="F31" t="n">
-        <v>37.5</v>
+        <v>260.6</v>
       </c>
       <c r="G31" t="n">
-        <v>16699898</v>
+        <v>21738108</v>
       </c>
       <c r="H31" t="n">
-        <v>18191883</v>
+        <v>31212343</v>
       </c>
       <c r="I31" t="n">
-        <v>44.05</v>
+        <v>317</v>
       </c>
       <c r="J31" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>-1669951</v>
+        <v>208.5</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L31" t="n">
-        <v>-4496950</v>
+        <v>-5937776</v>
       </c>
       <c r="M31" t="n">
-        <v>-8242967</v>
+        <v>-4853792</v>
       </c>
       <c r="N31" t="n">
-        <v>-5221995</v>
+        <v>-11223101</v>
       </c>
       <c r="O31" t="n">
+        <v>1863302</v>
+      </c>
+      <c r="P31" t="n">
         <v>-35</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>站上5日線、量能未放大</t>
-        </is>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>298</v>
+        <v>34.25</v>
       </c>
       <c r="D32" t="n">
-        <v>289.1</v>
+        <v>35.13</v>
       </c>
       <c r="E32" t="n">
-        <v>280.6</v>
+        <v>34.6</v>
       </c>
       <c r="F32" t="n">
-        <v>248.53</v>
+        <v>37.35</v>
       </c>
       <c r="G32" t="n">
-        <v>35285750</v>
+        <v>11138430</v>
       </c>
       <c r="H32" t="n">
-        <v>37916640</v>
+        <v>16177150</v>
       </c>
       <c r="I32" t="n">
-        <v>317</v>
+        <v>44.05</v>
       </c>
       <c r="J32" t="n">
-        <v>168</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-5937776</v>
+        <v>31.1</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
       </c>
       <c r="L32" t="n">
-        <v>-4853792</v>
+        <v>-1669951</v>
       </c>
       <c r="M32" t="n">
-        <v>-11223101</v>
+        <v>-4496950</v>
       </c>
       <c r="N32" t="n">
-        <v>1863302</v>
+        <v>-8242967</v>
       </c>
       <c r="O32" t="n">
-        <v>-35</v>
-      </c>
-      <c r="P32" t="inlineStr">
+        <v>-5221995</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-75</v>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
-        </is>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -2886,67 +3046,72 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1685</v>
+        <v>1690</v>
       </c>
       <c r="D33" t="n">
-        <v>1705</v>
+        <v>1697</v>
       </c>
       <c r="E33" t="n">
-        <v>1757.5</v>
+        <v>1747</v>
       </c>
       <c r="F33" t="n">
-        <v>1587.75</v>
+        <v>1612.75</v>
       </c>
       <c r="G33" t="n">
-        <v>4686000</v>
+        <v>3178000</v>
       </c>
       <c r="H33" t="n">
-        <v>4122200</v>
+        <v>3603600</v>
       </c>
       <c r="I33" t="n">
         <v>1935</v>
       </c>
       <c r="J33" t="n">
-        <v>1115</v>
-      </c>
-      <c r="K33" t="n">
+        <v>1190</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
         <v>-352405</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>-707137</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>-868509</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>-2148559</v>
       </c>
-      <c r="O33" t="n">
-        <v>-65</v>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" t="n">
+        <v>-75</v>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>跌破5日線、量能溫和放大</t>
-        </is>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:AG33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,30 +494,90 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>外資1日</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>外資3日</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>外資5日</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>外資10日</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>投信1日</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>投信3日</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>投信5日</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>投信10日</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>自營商1日</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>自營商3日</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>自營商5日</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>自營商10日</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>技術分數</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>綜合判斷</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>技術面</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>籌碼面</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>AI評語</t>
         </is>
@@ -564,80 +624,116 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10178504</v>
+        <v>3713763</v>
       </c>
       <c r="M2" t="n">
-        <v>70925202</v>
+        <v>19615583</v>
       </c>
       <c r="N2" t="n">
-        <v>76924762</v>
+        <v>68174224</v>
       </c>
       <c r="O2" t="n">
-        <v>66944449</v>
+        <v>70505841</v>
       </c>
       <c r="P2" t="n">
+        <v>3559089</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>22504498</v>
+      </c>
+      <c r="R2" t="n">
+        <v>72623387</v>
+      </c>
+      <c r="S2" t="n">
+        <v>76471865</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-4063000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-7036000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-7676000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>154674</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1174085</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2586837</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1709976</v>
+      </c>
+      <c r="AB2" t="n">
         <v>170</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13.65</v>
+        <v>696</v>
       </c>
       <c r="D3" t="n">
-        <v>11.83</v>
+        <v>606.4</v>
       </c>
       <c r="E3" t="n">
-        <v>11.16</v>
+        <v>555.55</v>
       </c>
       <c r="F3" t="n">
-        <v>10.02</v>
+        <v>529.38</v>
       </c>
       <c r="G3" t="n">
-        <v>478320069</v>
+        <v>50429815</v>
       </c>
       <c r="H3" t="n">
-        <v>148294428</v>
+        <v>29094105</v>
       </c>
       <c r="I3" t="n">
-        <v>14.3</v>
+        <v>719</v>
       </c>
       <c r="J3" t="n">
-        <v>8.130000000000001</v>
+        <v>445.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -645,161 +741,233 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2108293</v>
+        <v>1039882</v>
       </c>
       <c r="M3" t="n">
-        <v>59515291</v>
+        <v>2873236</v>
       </c>
       <c r="N3" t="n">
-        <v>56282808</v>
+        <v>18611901</v>
       </c>
       <c r="O3" t="n">
-        <v>50628800</v>
+        <v>20676322</v>
       </c>
       <c r="P3" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>17922</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1412705</v>
+      </c>
+      <c r="R3" t="n">
+        <v>13349743</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13948306</v>
+      </c>
+      <c r="T3" t="n">
+        <v>613000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3587000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3764897</v>
+      </c>
+      <c r="X3" t="n">
+        <v>408960</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>263531</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1675158</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2963119</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>165</v>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>696</v>
+        <v>1085</v>
       </c>
       <c r="D4" t="n">
-        <v>606.4</v>
+        <v>954.6</v>
       </c>
       <c r="E4" t="n">
-        <v>555.55</v>
+        <v>900.1</v>
       </c>
       <c r="F4" t="n">
-        <v>529.38</v>
+        <v>881.7</v>
       </c>
       <c r="G4" t="n">
-        <v>50429815</v>
+        <v>34270461</v>
       </c>
       <c r="H4" t="n">
-        <v>29094105</v>
+        <v>30958709</v>
       </c>
       <c r="I4" t="n">
-        <v>719</v>
+        <v>1085</v>
       </c>
       <c r="J4" t="n">
-        <v>445.5</v>
+        <v>776</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>964619</v>
+        <v>290189</v>
       </c>
       <c r="M4" t="n">
-        <v>17496756</v>
+        <v>5536520</v>
       </c>
       <c r="N4" t="n">
-        <v>19603616</v>
+        <v>14185171</v>
       </c>
       <c r="O4" t="n">
-        <v>18095930</v>
+        <v>9049490</v>
       </c>
       <c r="P4" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>226631</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4886174</v>
+      </c>
+      <c r="R4" t="n">
+        <v>11932486</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4161497</v>
+      </c>
+      <c r="T4" t="n">
+        <v>212000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>983843</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1605943</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5737686</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-148442</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-333497</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>646742</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-849693</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1085</v>
+        <v>562</v>
       </c>
       <c r="D5" t="n">
-        <v>954.6</v>
+        <v>513.1</v>
       </c>
       <c r="E5" t="n">
-        <v>900.1</v>
+        <v>491</v>
       </c>
       <c r="F5" t="n">
-        <v>881.7</v>
+        <v>502.85</v>
       </c>
       <c r="G5" t="n">
-        <v>34270461</v>
+        <v>33746000</v>
       </c>
       <c r="H5" t="n">
-        <v>30958709</v>
+        <v>31597000</v>
       </c>
       <c r="I5" t="n">
-        <v>1085</v>
+        <v>566</v>
       </c>
       <c r="J5" t="n">
-        <v>776</v>
+        <v>436</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -807,80 +975,116 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1191293</v>
+        <v>4244062</v>
       </c>
       <c r="M5" t="n">
-        <v>14796086</v>
+        <v>8968342</v>
       </c>
       <c r="N5" t="n">
-        <v>14042095</v>
+        <v>9409867</v>
       </c>
       <c r="O5" t="n">
-        <v>12040296</v>
+        <v>5771807</v>
       </c>
       <c r="P5" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+        <v>3267388</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4671266</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2987230</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2361844</v>
+      </c>
+      <c r="T5" t="n">
+        <v>169999</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1483999</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3688999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2820262</v>
+      </c>
+      <c r="X5" t="n">
+        <v>806675</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2813077</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2733638</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>589701</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>259</v>
+        <v>5290</v>
       </c>
       <c r="D6" t="n">
-        <v>251.5</v>
+        <v>4977</v>
       </c>
       <c r="E6" t="n">
-        <v>249.5</v>
+        <v>4843</v>
       </c>
       <c r="F6" t="n">
-        <v>244.47</v>
+        <v>4784.25</v>
       </c>
       <c r="G6" t="n">
-        <v>55665305</v>
+        <v>2917258</v>
       </c>
       <c r="H6" t="n">
-        <v>69819957</v>
+        <v>2443800</v>
       </c>
       <c r="I6" t="n">
-        <v>263.5</v>
+        <v>5635</v>
       </c>
       <c r="J6" t="n">
-        <v>219.5</v>
+        <v>4160</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -888,161 +1092,233 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55787312</v>
+        <v>358474</v>
       </c>
       <c r="M6" t="n">
-        <v>101690979</v>
+        <v>862813</v>
       </c>
       <c r="N6" t="n">
-        <v>84630201</v>
+        <v>1711672</v>
       </c>
       <c r="O6" t="n">
-        <v>160089561</v>
+        <v>2931478</v>
       </c>
       <c r="P6" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>279663</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>550985</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1390729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2316469</v>
+      </c>
+      <c r="T6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>246834</v>
+      </c>
+      <c r="V6" t="n">
+        <v>147674</v>
+      </c>
+      <c r="W6" t="n">
+        <v>424908</v>
+      </c>
+      <c r="X6" t="n">
+        <v>62811</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>64994</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>173269</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>190101</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>135</v>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5290</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>4977</v>
+        <v>21.51</v>
       </c>
       <c r="E7" t="n">
-        <v>4843</v>
+        <v>20.48</v>
       </c>
       <c r="F7" t="n">
-        <v>4784.25</v>
+        <v>19.25</v>
       </c>
       <c r="G7" t="n">
-        <v>2917258</v>
+        <v>818361725</v>
       </c>
       <c r="H7" t="n">
-        <v>2443800</v>
+        <v>356215638</v>
       </c>
       <c r="I7" t="n">
-        <v>5635</v>
+        <v>25.8</v>
       </c>
       <c r="J7" t="n">
-        <v>4160</v>
+        <v>16.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>359818</v>
+        <v>7043839</v>
       </c>
       <c r="M7" t="n">
-        <v>1354542</v>
+        <v>40455605</v>
       </c>
       <c r="N7" t="n">
-        <v>1447903</v>
+        <v>206744209</v>
       </c>
       <c r="O7" t="n">
-        <v>2950399</v>
+        <v>255008076</v>
       </c>
       <c r="P7" t="n">
-        <v>115</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>6297953</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>34550487</v>
+      </c>
+      <c r="R7" t="n">
+        <v>197817998</v>
+      </c>
+      <c r="S7" t="n">
+        <v>252197139</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-14237</v>
+      </c>
+      <c r="V7" t="n">
+        <v>38763</v>
+      </c>
+      <c r="W7" t="n">
+        <v>20162</v>
+      </c>
+      <c r="X7" t="n">
+        <v>738886</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5919355</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8887448</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2790775</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>125</v>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>55.4</v>
+        <v>533</v>
       </c>
       <c r="D8" t="n">
-        <v>53.91</v>
+        <v>511.6</v>
       </c>
       <c r="E8" t="n">
-        <v>51.25</v>
+        <v>468.75</v>
       </c>
       <c r="F8" t="n">
-        <v>50.42</v>
+        <v>448.2</v>
       </c>
       <c r="G8" t="n">
-        <v>15723414</v>
+        <v>2520000</v>
       </c>
       <c r="H8" t="n">
-        <v>11255762</v>
+        <v>4413800</v>
       </c>
       <c r="I8" t="n">
-        <v>60.3</v>
+        <v>558</v>
       </c>
       <c r="J8" t="n">
-        <v>45.45</v>
+        <v>340</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1050,80 +1326,116 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3454745</v>
+        <v>755377</v>
       </c>
       <c r="M8" t="n">
-        <v>13009409</v>
+        <v>2856804</v>
       </c>
       <c r="N8" t="n">
-        <v>14246624</v>
+        <v>9398836</v>
       </c>
       <c r="O8" t="n">
-        <v>12266815</v>
+        <v>7366124</v>
       </c>
       <c r="P8" t="n">
-        <v>115</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>737962</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2860498</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8822301</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10989591</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1200</v>
+      </c>
+      <c r="U8" t="n">
+        <v>35400</v>
+      </c>
+      <c r="V8" t="n">
+        <v>89400</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-1897400</v>
+      </c>
+      <c r="X8" t="n">
+        <v>18615</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-39094</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>487135</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1726067</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>125</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>124.8</v>
+        <v>251.5</v>
       </c>
       <c r="E9" t="n">
-        <v>125.75</v>
+        <v>249.5</v>
       </c>
       <c r="F9" t="n">
-        <v>114.91</v>
+        <v>244.47</v>
       </c>
       <c r="G9" t="n">
-        <v>336105421</v>
+        <v>55665305</v>
       </c>
       <c r="H9" t="n">
-        <v>249474700</v>
+        <v>69819957</v>
       </c>
       <c r="I9" t="n">
-        <v>141</v>
+        <v>263.5</v>
       </c>
       <c r="J9" t="n">
-        <v>88.8</v>
+        <v>219.5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1131,242 +1443,350 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>77651903</v>
+        <v>1176560</v>
       </c>
       <c r="M9" t="n">
-        <v>96687402</v>
+        <v>22207913</v>
       </c>
       <c r="N9" t="n">
-        <v>61728965</v>
+        <v>48256787</v>
       </c>
       <c r="O9" t="n">
-        <v>182119556</v>
+        <v>103877303</v>
       </c>
       <c r="P9" t="n">
-        <v>115</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>1667042</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>22481766</v>
+      </c>
+      <c r="R9" t="n">
+        <v>48192094</v>
+      </c>
+      <c r="S9" t="n">
+        <v>110732127</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-12810</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-97437</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-273247</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-4762535</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-477672</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-176416</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>337940</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-2092289</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>站上5日線、量能溫和放大、突破20日高點</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>533</v>
+        <v>13.65</v>
       </c>
       <c r="D10" t="n">
-        <v>511.6</v>
+        <v>11.83</v>
       </c>
       <c r="E10" t="n">
-        <v>468.75</v>
+        <v>11.16</v>
       </c>
       <c r="F10" t="n">
-        <v>448.2</v>
+        <v>10.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2520000</v>
+        <v>478320069</v>
       </c>
       <c r="H10" t="n">
-        <v>4413800</v>
+        <v>148294428</v>
       </c>
       <c r="I10" t="n">
-        <v>558</v>
+        <v>14.3</v>
       </c>
       <c r="J10" t="n">
-        <v>340</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>434414</v>
+        <v>-3262412</v>
       </c>
       <c r="M10" t="n">
-        <v>4299788</v>
+        <v>22044344</v>
       </c>
       <c r="N10" t="n">
-        <v>9649180</v>
+        <v>50882174</v>
       </c>
       <c r="O10" t="n">
-        <v>9535283</v>
+        <v>25324386</v>
       </c>
       <c r="P10" t="n">
-        <v>105</v>
-      </c>
-      <c r="Q10" t="inlineStr">
+        <v>-4232242</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>20328525</v>
+      </c>
+      <c r="R10" t="n">
+        <v>47907283</v>
+      </c>
+      <c r="S10" t="n">
+        <v>21954098</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>969830</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1715819</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2974891</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3370288</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1580</v>
+        <v>55.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1433</v>
+        <v>53.91</v>
       </c>
       <c r="E11" t="n">
-        <v>1385.5</v>
+        <v>51.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1308.55</v>
+        <v>50.42</v>
       </c>
       <c r="G11" t="n">
-        <v>9546000</v>
+        <v>15723414</v>
       </c>
       <c r="H11" t="n">
-        <v>3017800</v>
+        <v>11255762</v>
       </c>
       <c r="I11" t="n">
-        <v>1700</v>
+        <v>60.3</v>
       </c>
       <c r="J11" t="n">
-        <v>941</v>
+        <v>45.45</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>282254</v>
+        <v>198200</v>
       </c>
       <c r="M11" t="n">
-        <v>969253</v>
+        <v>4087251</v>
       </c>
       <c r="N11" t="n">
-        <v>1221688</v>
+        <v>9951064</v>
       </c>
       <c r="O11" t="n">
-        <v>2123947</v>
+        <v>7954561</v>
       </c>
       <c r="P11" t="n">
-        <v>105</v>
-      </c>
-      <c r="Q11" t="inlineStr">
+        <v>177415</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3934844</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9678259</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7765339</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>20785</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>152407</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>272805</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>189222</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>115</v>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>661</v>
+        <v>304.5</v>
       </c>
       <c r="D12" t="n">
-        <v>614.6</v>
+        <v>291.6</v>
       </c>
       <c r="E12" t="n">
-        <v>540.85</v>
+        <v>282.85</v>
       </c>
       <c r="F12" t="n">
-        <v>448.73</v>
+        <v>260.6</v>
       </c>
       <c r="G12" t="n">
-        <v>29457930</v>
+        <v>21738108</v>
       </c>
       <c r="H12" t="n">
-        <v>56139070</v>
+        <v>31212343</v>
       </c>
       <c r="I12" t="n">
-        <v>691</v>
+        <v>317</v>
       </c>
       <c r="J12" t="n">
-        <v>307</v>
+        <v>208.5</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1374,404 +1794,584 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2231528</v>
+        <v>4745353</v>
       </c>
       <c r="M12" t="n">
-        <v>3889908</v>
+        <v>9834017</v>
       </c>
       <c r="N12" t="n">
-        <v>9359269</v>
+        <v>10574690</v>
       </c>
       <c r="O12" t="n">
-        <v>20009905</v>
+        <v>20883168</v>
       </c>
       <c r="P12" t="n">
+        <v>4763785</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10787025</v>
+      </c>
+      <c r="R12" t="n">
+        <v>13381377</v>
+      </c>
+      <c r="S12" t="n">
+        <v>26096411</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-101000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1724000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-3525000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-4431464</v>
+      </c>
+      <c r="X12" t="n">
+        <v>82568</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>770992</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>718313</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-781779</v>
+      </c>
+      <c r="AB12" t="n">
         <v>105</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>72.2</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>69.12</v>
+        <v>51.64</v>
       </c>
       <c r="E13" t="n">
-        <v>67.56</v>
+        <v>50.21</v>
       </c>
       <c r="F13" t="n">
-        <v>68.52</v>
+        <v>50.11</v>
       </c>
       <c r="G13" t="n">
-        <v>337055872</v>
+        <v>14910096</v>
       </c>
       <c r="H13" t="n">
-        <v>147844553</v>
+        <v>26622786</v>
       </c>
       <c r="I13" t="n">
-        <v>81.2</v>
+        <v>53.9</v>
       </c>
       <c r="J13" t="n">
-        <v>61.8</v>
+        <v>47.35</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44538498</v>
+        <v>1599308</v>
       </c>
       <c r="M13" t="n">
-        <v>88202486</v>
+        <v>19287277</v>
       </c>
       <c r="N13" t="n">
-        <v>75247740</v>
+        <v>32054623</v>
       </c>
       <c r="O13" t="n">
-        <v>32596649</v>
+        <v>9933706</v>
       </c>
       <c r="P13" t="n">
+        <v>1194273</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>18166886</v>
+      </c>
+      <c r="R13" t="n">
+        <v>30323339</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8970452</v>
+      </c>
+      <c r="T13" t="n">
+        <v>900</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-26066</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-64166</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-341744</v>
+      </c>
+      <c r="X13" t="n">
+        <v>404135</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1146457</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1795450</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1304998</v>
+      </c>
+      <c r="AB13" t="n">
         <v>105</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>661</v>
       </c>
       <c r="D14" t="n">
-        <v>21.51</v>
+        <v>614.6</v>
       </c>
       <c r="E14" t="n">
-        <v>20.48</v>
+        <v>540.85</v>
       </c>
       <c r="F14" t="n">
-        <v>19.25</v>
+        <v>448.73</v>
       </c>
       <c r="G14" t="n">
-        <v>818361725</v>
+        <v>29457930</v>
       </c>
       <c r="H14" t="n">
-        <v>356215638</v>
+        <v>56139070</v>
       </c>
       <c r="I14" t="n">
-        <v>25.8</v>
+        <v>691</v>
       </c>
       <c r="J14" t="n">
-        <v>16.6</v>
+        <v>307</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>18947923</v>
+        <v>1102045</v>
       </c>
       <c r="M14" t="n">
-        <v>211604454</v>
+        <v>4327355</v>
       </c>
       <c r="N14" t="n">
-        <v>192942642</v>
+        <v>3862470</v>
       </c>
       <c r="O14" t="n">
-        <v>353520387</v>
+        <v>14290677</v>
       </c>
       <c r="P14" t="n">
+        <v>-4617135</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-4685625</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-12048132</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-24677774</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6849000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8963449</v>
+      </c>
+      <c r="V14" t="n">
+        <v>16117449</v>
+      </c>
+      <c r="W14" t="n">
+        <v>41742069</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1129820</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>49531</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-206847</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-2773618</v>
+      </c>
+      <c r="AB14" t="n">
         <v>105</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>562</v>
+        <v>72.2</v>
       </c>
       <c r="D15" t="n">
-        <v>513.1</v>
+        <v>69.12</v>
       </c>
       <c r="E15" t="n">
-        <v>491</v>
+        <v>67.56</v>
       </c>
       <c r="F15" t="n">
-        <v>502.85</v>
+        <v>68.52</v>
       </c>
       <c r="G15" t="n">
-        <v>33746000</v>
+        <v>337055872</v>
       </c>
       <c r="H15" t="n">
-        <v>31597000</v>
+        <v>147844553</v>
       </c>
       <c r="I15" t="n">
-        <v>566</v>
+        <v>81.2</v>
       </c>
       <c r="J15" t="n">
-        <v>436</v>
+        <v>61.8</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-709786</v>
+        <v>-8515087</v>
       </c>
       <c r="M15" t="n">
-        <v>7825302</v>
+        <v>28946585</v>
       </c>
       <c r="N15" t="n">
-        <v>4382193</v>
+        <v>26633814</v>
       </c>
       <c r="O15" t="n">
-        <v>-4637373</v>
+        <v>-37000661</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q15" t="inlineStr">
+        <v>-9231376</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>26801156</v>
+      </c>
+      <c r="R15" t="n">
+        <v>23647845</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-36842695</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11000</v>
+      </c>
+      <c r="V15" t="n">
+        <v>33000</v>
+      </c>
+      <c r="W15" t="n">
+        <v>26000</v>
+      </c>
+      <c r="X15" t="n">
+        <v>716289</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2134429</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2952969</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-183966</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、接近20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、黃金交叉、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2350</v>
+        <v>45.7</v>
       </c>
       <c r="D16" t="n">
-        <v>2136</v>
+        <v>43.4</v>
       </c>
       <c r="E16" t="n">
-        <v>2101</v>
+        <v>40.22</v>
       </c>
       <c r="F16" t="n">
-        <v>2149</v>
+        <v>34.08</v>
       </c>
       <c r="G16" t="n">
-        <v>12198582</v>
+        <v>1463227218</v>
       </c>
       <c r="H16" t="n">
-        <v>11067330</v>
+        <v>613882104</v>
       </c>
       <c r="I16" t="n">
-        <v>2410</v>
+        <v>52.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1880</v>
+        <v>23.65</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4917556</v>
+        <v>-20234462</v>
       </c>
       <c r="M16" t="n">
-        <v>5273927</v>
+        <v>-5521196</v>
       </c>
       <c r="N16" t="n">
-        <v>1917848</v>
+        <v>83429081</v>
       </c>
       <c r="O16" t="n">
-        <v>-4082627</v>
+        <v>59378294</v>
       </c>
       <c r="P16" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+        <v>-26508116</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-14599220</v>
+      </c>
+      <c r="R16" t="n">
+        <v>56981613</v>
+      </c>
+      <c r="S16" t="n">
+        <v>16527987</v>
+      </c>
+      <c r="T16" t="n">
+        <v>43100</v>
+      </c>
+      <c r="U16" t="n">
+        <v>13211</v>
+      </c>
+      <c r="V16" t="n">
+        <v>17311</v>
+      </c>
+      <c r="W16" t="n">
+        <v>453089</v>
+      </c>
+      <c r="X16" t="n">
+        <v>6230554</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9064813</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>26430157</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>42397218</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>站上5日線、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>82.40000000000001</v>
+        <v>922</v>
       </c>
       <c r="D17" t="n">
-        <v>81.73999999999999</v>
+        <v>888.2</v>
       </c>
       <c r="E17" t="n">
-        <v>81.34</v>
+        <v>854.3</v>
       </c>
       <c r="F17" t="n">
-        <v>80.16</v>
+        <v>896.4</v>
       </c>
       <c r="G17" t="n">
-        <v>12463968</v>
+        <v>24438087</v>
       </c>
       <c r="H17" t="n">
-        <v>10197116</v>
+        <v>20893593</v>
       </c>
       <c r="I17" t="n">
-        <v>85.8</v>
+        <v>1035</v>
       </c>
       <c r="J17" t="n">
-        <v>70.2</v>
+        <v>765</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1779,80 +2379,116 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-491799</v>
+        <v>-208181</v>
       </c>
       <c r="M17" t="n">
-        <v>7106107</v>
+        <v>3582994</v>
       </c>
       <c r="N17" t="n">
-        <v>4374099</v>
+        <v>3677318</v>
       </c>
       <c r="O17" t="n">
-        <v>9626033</v>
+        <v>-1724114</v>
       </c>
       <c r="P17" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+        <v>39735</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1895312</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1121613</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-12620</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-165000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1591000</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2486000</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-1244694</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-82916</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>96682</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>69705</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-466800</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>站上5日線、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>611</v>
+        <v>540</v>
       </c>
       <c r="D18" t="n">
-        <v>555</v>
+        <v>498.7</v>
       </c>
       <c r="E18" t="n">
-        <v>540</v>
+        <v>457.05</v>
       </c>
       <c r="F18" t="n">
-        <v>528.95</v>
+        <v>434.32</v>
       </c>
       <c r="G18" t="n">
-        <v>39627497</v>
+        <v>41904053</v>
       </c>
       <c r="H18" t="n">
-        <v>28597065</v>
+        <v>51443369</v>
       </c>
       <c r="I18" t="n">
-        <v>636</v>
+        <v>558</v>
       </c>
       <c r="J18" t="n">
-        <v>465</v>
+        <v>354</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1860,80 +2496,116 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1946569</v>
+        <v>-967994</v>
       </c>
       <c r="M18" t="n">
-        <v>4398628</v>
+        <v>-1212400</v>
       </c>
       <c r="N18" t="n">
-        <v>375095</v>
+        <v>2289305</v>
       </c>
       <c r="O18" t="n">
-        <v>-4267040</v>
+        <v>1887707</v>
       </c>
       <c r="P18" t="n">
+        <v>1375340</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2831559</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-676473</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4958845</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-2688000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>848563</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1580563</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-4914501</v>
+      </c>
+      <c r="X18" t="n">
+        <v>344666</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>770596</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1385215</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1843363</v>
+      </c>
+      <c r="AB18" t="n">
         <v>75</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>5日法人買超</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>45.7</v>
+        <v>1580</v>
       </c>
       <c r="D19" t="n">
-        <v>43.4</v>
+        <v>1433</v>
       </c>
       <c r="E19" t="n">
-        <v>40.22</v>
+        <v>1385.5</v>
       </c>
       <c r="F19" t="n">
-        <v>34.08</v>
+        <v>1308.55</v>
       </c>
       <c r="G19" t="n">
-        <v>1463227218</v>
+        <v>9546000</v>
       </c>
       <c r="H19" t="n">
-        <v>613882104</v>
+        <v>3017800</v>
       </c>
       <c r="I19" t="n">
-        <v>52.2</v>
+        <v>1700</v>
       </c>
       <c r="J19" t="n">
-        <v>23.65</v>
+        <v>941</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1941,80 +2613,116 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-2664727</v>
+        <v>-83545</v>
       </c>
       <c r="M19" t="n">
-        <v>121233278</v>
+        <v>660709</v>
       </c>
       <c r="N19" t="n">
-        <v>74438491</v>
+        <v>848398</v>
       </c>
       <c r="O19" t="n">
-        <v>153391454</v>
+        <v>2026953</v>
       </c>
       <c r="P19" t="n">
+        <v>-1100380</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-461658</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-27799</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1154682</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1406000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1457700</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1445700</v>
+      </c>
+      <c r="W19" t="n">
+        <v>427100</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-389165</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-335333</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-569503</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>445171</v>
+      </c>
+      <c r="AB19" t="n">
         <v>75</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>🔥強勢</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>強勢觀察</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>540</v>
+        <v>5280</v>
       </c>
       <c r="D20" t="n">
-        <v>498.7</v>
+        <v>5334</v>
       </c>
       <c r="E20" t="n">
-        <v>457.05</v>
+        <v>5278</v>
       </c>
       <c r="F20" t="n">
-        <v>434.32</v>
+        <v>5144.75</v>
       </c>
       <c r="G20" t="n">
-        <v>41904053</v>
+        <v>2655826</v>
       </c>
       <c r="H20" t="n">
-        <v>51443369</v>
+        <v>2172103</v>
       </c>
       <c r="I20" t="n">
-        <v>558</v>
+        <v>5880</v>
       </c>
       <c r="J20" t="n">
-        <v>354</v>
+        <v>4615</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2022,80 +2730,116 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-5716319</v>
+        <v>15106</v>
       </c>
       <c r="M20" t="n">
-        <v>-1491026</v>
+        <v>117253</v>
       </c>
       <c r="N20" t="n">
-        <v>13501619</v>
+        <v>77678</v>
       </c>
       <c r="O20" t="n">
-        <v>10633143</v>
+        <v>198915</v>
       </c>
       <c r="P20" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>🔥強勢</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>強勢觀察</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+        <v>-44712</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>91809</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-160303</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-526781</v>
+      </c>
+      <c r="T20" t="n">
+        <v>36000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-29006</v>
+      </c>
+      <c r="V20" t="n">
+        <v>78994</v>
+      </c>
+      <c r="W20" t="n">
+        <v>635413</v>
+      </c>
+      <c r="X20" t="n">
+        <v>23818</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>54450</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>158987</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>90283</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>👀觀察</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>偏多觀察</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>法人連續偏買、5日法人小幅買超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人小幅買超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>51.64</v>
+        <v>176.9</v>
       </c>
       <c r="E21" t="n">
-        <v>50.21</v>
+        <v>174.55</v>
       </c>
       <c r="F21" t="n">
-        <v>50.11</v>
+        <v>161.45</v>
       </c>
       <c r="G21" t="n">
-        <v>14910096</v>
+        <v>9878768</v>
       </c>
       <c r="H21" t="n">
-        <v>26622786</v>
+        <v>26306205</v>
       </c>
       <c r="I21" t="n">
-        <v>53.9</v>
+        <v>198.5</v>
       </c>
       <c r="J21" t="n">
-        <v>47.35</v>
+        <v>139</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2103,80 +2847,116 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-7838235</v>
+        <v>836799</v>
       </c>
       <c r="M21" t="n">
-        <v>21017772</v>
+        <v>-413419</v>
       </c>
       <c r="N21" t="n">
-        <v>26241510</v>
+        <v>9121757</v>
       </c>
       <c r="O21" t="n">
-        <v>-434219</v>
+        <v>4176141</v>
       </c>
       <c r="P21" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>🔥強勢</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>強勢觀察</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+        <v>449302</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-565158</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7723967</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3221282</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W21" t="n">
+        <v>6393</v>
+      </c>
+      <c r="X21" t="n">
+        <v>387497</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>151739</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1392790</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>948466</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>👀觀察</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>偏多觀察</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超、外資投信同步買超</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>208</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>207</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>199.9</v>
+        <v>81.34</v>
       </c>
       <c r="F22" t="n">
-        <v>190.12</v>
+        <v>80.16</v>
       </c>
       <c r="G22" t="n">
-        <v>20600438</v>
+        <v>12463968</v>
       </c>
       <c r="H22" t="n">
-        <v>22454689</v>
+        <v>10197116</v>
       </c>
       <c r="I22" t="n">
-        <v>231</v>
+        <v>85.8</v>
       </c>
       <c r="J22" t="n">
-        <v>167</v>
+        <v>70.2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2184,80 +2964,116 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-1076740</v>
+        <v>-4199015</v>
       </c>
       <c r="M22" t="n">
-        <v>6371419</v>
+        <v>2506502</v>
       </c>
       <c r="N22" t="n">
-        <v>6997630</v>
+        <v>-800124</v>
       </c>
       <c r="O22" t="n">
-        <v>194327</v>
+        <v>-4198886</v>
       </c>
       <c r="P22" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>🔥強勢</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>強勢觀察</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>5日法人明顯買超</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+        <v>-4105690</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2163760</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-1000255</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-4318549</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-93325</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>342742</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>200131</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>127663</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>整理觀察</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2270</v>
+        <v>2350</v>
       </c>
       <c r="D23" t="n">
-        <v>2250</v>
+        <v>2136</v>
       </c>
       <c r="E23" t="n">
-        <v>2245</v>
+        <v>2101</v>
       </c>
       <c r="F23" t="n">
-        <v>2242.25</v>
+        <v>2149</v>
       </c>
       <c r="G23" t="n">
-        <v>32781470</v>
+        <v>12198582</v>
       </c>
       <c r="H23" t="n">
-        <v>30223565</v>
+        <v>11067330</v>
       </c>
       <c r="I23" t="n">
-        <v>2345</v>
+        <v>2410</v>
       </c>
       <c r="J23" t="n">
-        <v>2135</v>
+        <v>1880</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2265,161 +3081,233 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>8271589</v>
+        <v>-65912</v>
       </c>
       <c r="M23" t="n">
-        <v>10332214</v>
+        <v>-250347</v>
       </c>
       <c r="N23" t="n">
-        <v>-12125572</v>
+        <v>290459</v>
       </c>
       <c r="O23" t="n">
-        <v>-16581218</v>
+        <v>-1481438</v>
       </c>
       <c r="P23" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>👀觀察</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>偏多觀察</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>偏多觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、短線籌碼止穩、5日法人明顯賣超。條件不差，適合等待拉回或突破確認。</t>
+        <v>121443</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-295</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-145909</v>
+      </c>
+      <c r="S23" t="n">
+        <v>33483</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-120500</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-231968</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-485259</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-1333854</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-66855</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-18084</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>921627</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-181067</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>整理觀察</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>站上5日線、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>5日法人買超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>整理觀察：站上5日線、量能溫和放大、5日法人買超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>342</v>
+        <v>2270</v>
       </c>
       <c r="D24" t="n">
-        <v>285.6</v>
+        <v>2250</v>
       </c>
       <c r="E24" t="n">
-        <v>261.4</v>
+        <v>2245</v>
       </c>
       <c r="F24" t="n">
-        <v>241.47</v>
+        <v>2242.25</v>
       </c>
       <c r="G24" t="n">
-        <v>57938700</v>
+        <v>32781470</v>
       </c>
       <c r="H24" t="n">
-        <v>22861322</v>
+        <v>30223565</v>
       </c>
       <c r="I24" t="n">
-        <v>342</v>
+        <v>2345</v>
       </c>
       <c r="J24" t="n">
-        <v>201</v>
+        <v>2135</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1465366</v>
+        <v>-2572029</v>
       </c>
       <c r="M24" t="n">
-        <v>-160620</v>
+        <v>-2116239</v>
       </c>
       <c r="N24" t="n">
-        <v>-5984174</v>
+        <v>-3083433</v>
       </c>
       <c r="O24" t="n">
-        <v>5074162</v>
+        <v>-10178055</v>
       </c>
       <c r="P24" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q24" t="inlineStr">
+        <v>-9521827</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-8788853</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-17296342</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-51109009</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6429500</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5964652</v>
+      </c>
+      <c r="V24" t="n">
+        <v>12561152</v>
+      </c>
+      <c r="W24" t="n">
+        <v>40136470</v>
+      </c>
+      <c r="X24" t="n">
+        <v>520298</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>707962</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1651757</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>794484</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC24" t="inlineStr">
         <is>
           <t>⚠️整理</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>整理觀察</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>整理觀察：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>整理觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>866</v>
+        <v>141</v>
       </c>
       <c r="D25" t="n">
-        <v>742</v>
+        <v>124.8</v>
       </c>
       <c r="E25" t="n">
-        <v>732.1</v>
+        <v>125.75</v>
       </c>
       <c r="F25" t="n">
-        <v>711.25</v>
+        <v>114.91</v>
       </c>
       <c r="G25" t="n">
-        <v>2958000</v>
+        <v>336105421</v>
       </c>
       <c r="H25" t="n">
-        <v>4678000</v>
+        <v>249474700</v>
       </c>
       <c r="I25" t="n">
-        <v>866</v>
+        <v>141</v>
       </c>
       <c r="J25" t="n">
-        <v>534</v>
+        <v>88.8</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2427,80 +3315,116 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-261357</v>
+        <v>-11962552</v>
       </c>
       <c r="M25" t="n">
-        <v>-3141303</v>
+        <v>40167238</v>
       </c>
       <c r="N25" t="n">
-        <v>-4610982</v>
+        <v>-4889605</v>
       </c>
       <c r="O25" t="n">
-        <v>-4787133</v>
+        <v>68676281</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>❌避開</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>觀望</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        <v>-19138371</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>32303633</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-18031163</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-12020795</v>
+      </c>
+      <c r="T25" t="n">
+        <v>7462000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6270969</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10656969</v>
+      </c>
+      <c r="W25" t="n">
+        <v>76451043</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-286181</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1592636</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2484589</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4246033</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>整理觀察</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>站上5日線、量能溫和放大、突破20日高點</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>整理觀察：站上5日線、量能溫和放大、突破20日高點、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5280</v>
+        <v>1220</v>
       </c>
       <c r="D26" t="n">
-        <v>5334</v>
+        <v>1114.4</v>
       </c>
       <c r="E26" t="n">
-        <v>5278</v>
+        <v>1037.7</v>
       </c>
       <c r="F26" t="n">
-        <v>5144.75</v>
+        <v>1072.35</v>
       </c>
       <c r="G26" t="n">
-        <v>2655826</v>
+        <v>4415000</v>
       </c>
       <c r="H26" t="n">
-        <v>2172103</v>
+        <v>3736800</v>
       </c>
       <c r="I26" t="n">
-        <v>5880</v>
+        <v>1300</v>
       </c>
       <c r="J26" t="n">
-        <v>4615</v>
+        <v>865</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2508,161 +3432,233 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>49559</v>
+        <v>78870</v>
       </c>
       <c r="M26" t="n">
-        <v>97025</v>
+        <v>-1139380</v>
       </c>
       <c r="N26" t="n">
-        <v>-160824</v>
+        <v>-1176252</v>
       </c>
       <c r="O26" t="n">
-        <v>-364679</v>
+        <v>-1740259</v>
       </c>
       <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>❌避開</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>觀望</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>短線籌碼止穩、5日法人賣超</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+        <v>-73248</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1970174</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-2217164</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-2350595</v>
+      </c>
+      <c r="T26" t="n">
+        <v>210000</v>
+      </c>
+      <c r="U26" t="n">
+        <v>871000</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1046000</v>
+      </c>
+      <c r="W26" t="n">
+        <v>567000</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-57882</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-40206</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-5088</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>43336</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>⚠️整理</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>整理觀察</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1220</v>
+        <v>342</v>
       </c>
       <c r="D27" t="n">
-        <v>1114.4</v>
+        <v>285.6</v>
       </c>
       <c r="E27" t="n">
-        <v>1037.7</v>
+        <v>261.4</v>
       </c>
       <c r="F27" t="n">
-        <v>1072.35</v>
+        <v>241.47</v>
       </c>
       <c r="G27" t="n">
-        <v>4415000</v>
+        <v>57938700</v>
       </c>
       <c r="H27" t="n">
-        <v>3736800</v>
+        <v>22861322</v>
       </c>
       <c r="I27" t="n">
-        <v>1300</v>
+        <v>342</v>
       </c>
       <c r="J27" t="n">
-        <v>865</v>
+        <v>201</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-1014980</v>
+        <v>-1834154</v>
       </c>
       <c r="M27" t="n">
-        <v>-1037784</v>
+        <v>-4443864</v>
       </c>
       <c r="N27" t="n">
-        <v>-1279466</v>
+        <v>-2363562</v>
       </c>
       <c r="O27" t="n">
-        <v>-1723078</v>
+        <v>8629303</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="inlineStr">
+        <v>-2734302</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-3531935</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-4279508</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4990232</v>
+      </c>
+      <c r="T27" t="n">
+        <v>94000</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-1715000</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-408000</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-455184</v>
+      </c>
+      <c r="X27" t="n">
+        <v>806148</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>803071</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2323946</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4094255</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC27" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>風險偏高：站上5日線、黃金交叉、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>130.5</v>
+        <v>34.25</v>
       </c>
       <c r="D28" t="n">
-        <v>118.7</v>
+        <v>35.13</v>
       </c>
       <c r="E28" t="n">
-        <v>113.39</v>
+        <v>34.6</v>
       </c>
       <c r="F28" t="n">
-        <v>100.19</v>
+        <v>37.35</v>
       </c>
       <c r="G28" t="n">
-        <v>291896012</v>
+        <v>11138430</v>
       </c>
       <c r="H28" t="n">
-        <v>252641517</v>
+        <v>16177150</v>
       </c>
       <c r="I28" t="n">
-        <v>133.5</v>
+        <v>44.05</v>
       </c>
       <c r="J28" t="n">
-        <v>71.3</v>
+        <v>31.1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2670,80 +3666,116 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>32836623</v>
+        <v>2800000</v>
       </c>
       <c r="M28" t="n">
-        <v>-1979065</v>
+        <v>-2768167</v>
       </c>
       <c r="N28" t="n">
-        <v>-21222223</v>
+        <v>2773001</v>
       </c>
       <c r="O28" t="n">
-        <v>49323216</v>
+        <v>11403137</v>
       </c>
       <c r="P28" t="n">
+        <v>2798000</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-2599000</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2771000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11617136</v>
+      </c>
+      <c r="T28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-169167</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2001</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-213999</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC28" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>303.5</v>
+        <v>866</v>
       </c>
       <c r="D29" t="n">
-        <v>295.6</v>
+        <v>742</v>
       </c>
       <c r="E29" t="n">
-        <v>303.1</v>
+        <v>732.1</v>
       </c>
       <c r="F29" t="n">
-        <v>283.88</v>
+        <v>711.25</v>
       </c>
       <c r="G29" t="n">
-        <v>152949355</v>
+        <v>2958000</v>
       </c>
       <c r="H29" t="n">
-        <v>148065232</v>
+        <v>4678000</v>
       </c>
       <c r="I29" t="n">
-        <v>353</v>
+        <v>866</v>
       </c>
       <c r="J29" t="n">
-        <v>214.5</v>
+        <v>534</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2751,80 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-13921163</v>
+        <v>-541871</v>
       </c>
       <c r="M29" t="n">
-        <v>-14185405</v>
+        <v>-2561156</v>
       </c>
       <c r="N29" t="n">
-        <v>-47727411</v>
+        <v>-4480928</v>
       </c>
       <c r="O29" t="n">
-        <v>-49157826</v>
+        <v>-5069064</v>
       </c>
       <c r="P29" t="n">
-        <v>-25</v>
-      </c>
-      <c r="Q29" t="inlineStr">
+        <v>-566747</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-3254183</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-4533384</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-6369986</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-84038</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-295650</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-946650</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-269880</v>
+      </c>
+      <c r="X29" t="n">
+        <v>108914</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>988677</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>999106</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1570802</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC29" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>站上5日線、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>922</v>
+        <v>130.5</v>
       </c>
       <c r="D30" t="n">
-        <v>888.2</v>
+        <v>118.7</v>
       </c>
       <c r="E30" t="n">
-        <v>854.3</v>
+        <v>113.39</v>
       </c>
       <c r="F30" t="n">
-        <v>896.4</v>
+        <v>100.19</v>
       </c>
       <c r="G30" t="n">
-        <v>24438087</v>
+        <v>291896012</v>
       </c>
       <c r="H30" t="n">
-        <v>20893593</v>
+        <v>252641517</v>
       </c>
       <c r="I30" t="n">
-        <v>1035</v>
+        <v>133.5</v>
       </c>
       <c r="J30" t="n">
-        <v>765</v>
+        <v>71.3</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2832,80 +3900,116 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-8905954</v>
+        <v>-24732790</v>
       </c>
       <c r="M30" t="n">
-        <v>-4812274</v>
+        <v>-79198141</v>
       </c>
       <c r="N30" t="n">
-        <v>-4509560</v>
+        <v>-84281268</v>
       </c>
       <c r="O30" t="n">
-        <v>-8787097</v>
+        <v>-88381049</v>
       </c>
       <c r="P30" t="n">
-        <v>-25</v>
-      </c>
-      <c r="Q30" t="inlineStr">
+        <v>-45921195</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-76267503</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-78400331</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-182437864</v>
+      </c>
+      <c r="T30" t="n">
+        <v>20707132</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-4178019</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-9430887</v>
+      </c>
+      <c r="W30" t="n">
+        <v>94794673</v>
+      </c>
+      <c r="X30" t="n">
+        <v>481273</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1247381</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3549950</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-737858</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>站上5日線、量能溫和放大</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>304.5</v>
+        <v>303.5</v>
       </c>
       <c r="D31" t="n">
-        <v>291.6</v>
+        <v>295.6</v>
       </c>
       <c r="E31" t="n">
-        <v>282.85</v>
+        <v>303.1</v>
       </c>
       <c r="F31" t="n">
-        <v>260.6</v>
+        <v>281.4</v>
       </c>
       <c r="G31" t="n">
-        <v>21738108</v>
+        <v>152949355</v>
       </c>
       <c r="H31" t="n">
-        <v>31212343</v>
+        <v>148065232</v>
       </c>
       <c r="I31" t="n">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="J31" t="n">
-        <v>208.5</v>
+        <v>198.5</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2913,80 +4017,116 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-5937776</v>
+        <v>-7167551</v>
       </c>
       <c r="M31" t="n">
-        <v>-4853792</v>
+        <v>-6915479</v>
       </c>
       <c r="N31" t="n">
-        <v>-11223101</v>
+        <v>-14599344</v>
       </c>
       <c r="O31" t="n">
-        <v>1863302</v>
+        <v>-52051868</v>
       </c>
       <c r="P31" t="n">
-        <v>-35</v>
-      </c>
-      <c r="Q31" t="inlineStr">
+        <v>2181497</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1871943</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2834419</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-21992353</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-8258000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-8507165</v>
+      </c>
+      <c r="V31" t="n">
+        <v>-16981165</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-26831509</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-1091048</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-280257</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-452598</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-3228006</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AC31" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>站上5日線、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>34.25</v>
+        <v>478</v>
       </c>
       <c r="D32" t="n">
-        <v>35.13</v>
+        <v>490.7</v>
       </c>
       <c r="E32" t="n">
-        <v>34.6</v>
+        <v>475.85</v>
       </c>
       <c r="F32" t="n">
-        <v>37.35</v>
+        <v>436.95</v>
       </c>
       <c r="G32" t="n">
-        <v>11138430</v>
+        <v>36584546</v>
       </c>
       <c r="H32" t="n">
-        <v>16177150</v>
+        <v>27861072</v>
       </c>
       <c r="I32" t="n">
-        <v>44.05</v>
+        <v>523</v>
       </c>
       <c r="J32" t="n">
-        <v>31.1</v>
+        <v>344.5</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2994,43 +4134,79 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-1669951</v>
+        <v>-5830786</v>
       </c>
       <c r="M32" t="n">
-        <v>-4496950</v>
+        <v>-1856284</v>
       </c>
       <c r="N32" t="n">
-        <v>-8242967</v>
+        <v>-5316375</v>
       </c>
       <c r="O32" t="n">
-        <v>-5221995</v>
+        <v>-18584918</v>
       </c>
       <c r="P32" t="n">
-        <v>-75</v>
-      </c>
-      <c r="Q32" t="inlineStr">
+        <v>-5948511</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-2968809</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-6389494</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-22409660</v>
+      </c>
+      <c r="T32" t="n">
+        <v>262000</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1510683</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1749683</v>
+      </c>
+      <c r="W32" t="n">
+        <v>4998304</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-144275</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-398158</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-676564</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-1173562</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>跌破5日線、量能未放大</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -3075,43 +4251,79 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-352405</v>
+        <v>-467151</v>
       </c>
       <c r="M33" t="n">
-        <v>-707137</v>
+        <v>-779449</v>
       </c>
       <c r="N33" t="n">
-        <v>-868509</v>
+        <v>-1431458</v>
       </c>
       <c r="O33" t="n">
-        <v>-2148559</v>
+        <v>-2655109</v>
       </c>
       <c r="P33" t="n">
-        <v>-75</v>
-      </c>
-      <c r="Q33" t="inlineStr">
+        <v>-190195</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-247868</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-528542</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-1615246</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-264617</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-524617</v>
+      </c>
+      <c r="V33" t="n">
+        <v>-879117</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-828848</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-12339</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-6964</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-23799</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-211015</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC33" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>跌破5日線、量能未放大</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG33"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,93 +586,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="D2" t="n">
-        <v>33.58</v>
+        <v>124.8</v>
       </c>
       <c r="E2" t="n">
-        <v>30.93</v>
+        <v>125.75</v>
       </c>
       <c r="F2" t="n">
-        <v>29.77</v>
+        <v>114.91</v>
       </c>
       <c r="G2" t="n">
-        <v>210267926</v>
+        <v>336105421</v>
       </c>
       <c r="H2" t="n">
-        <v>105612204</v>
+        <v>249474700</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="J2" t="n">
-        <v>26.65</v>
+        <v>88.8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3713763</v>
+        <v>217385</v>
       </c>
       <c r="M2" t="n">
-        <v>19615583</v>
+        <v>78086673</v>
       </c>
       <c r="N2" t="n">
-        <v>68174224</v>
+        <v>45209767</v>
       </c>
       <c r="O2" t="n">
-        <v>70505841</v>
+        <v>128638416</v>
       </c>
       <c r="P2" t="n">
-        <v>3559089</v>
+        <v>883001</v>
       </c>
       <c r="Q2" t="n">
-        <v>22504498</v>
+        <v>73858010</v>
       </c>
       <c r="R2" t="n">
-        <v>72623387</v>
+        <v>43544586</v>
       </c>
       <c r="S2" t="n">
-        <v>76471865</v>
+        <v>77189599</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-200000</v>
       </c>
       <c r="U2" t="n">
-        <v>-4063000</v>
+        <v>4851000</v>
       </c>
       <c r="V2" t="n">
-        <v>-7036000</v>
+        <v>1575000</v>
       </c>
       <c r="W2" t="n">
-        <v>-7676000</v>
+        <v>52930074</v>
       </c>
       <c r="X2" t="n">
-        <v>154674</v>
+        <v>-465616</v>
       </c>
       <c r="Y2" t="n">
-        <v>1174085</v>
+        <v>-622337</v>
       </c>
       <c r="Z2" t="n">
-        <v>2586837</v>
+        <v>90181</v>
       </c>
       <c r="AA2" t="n">
-        <v>1709976</v>
+        <v>-1481257</v>
       </c>
       <c r="AB2" t="n">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -686,54 +686,54 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>696</v>
+        <v>342</v>
       </c>
       <c r="D3" t="n">
-        <v>606.4</v>
+        <v>285.6</v>
       </c>
       <c r="E3" t="n">
-        <v>555.55</v>
+        <v>261.4</v>
       </c>
       <c r="F3" t="n">
-        <v>529.38</v>
+        <v>241.47</v>
       </c>
       <c r="G3" t="n">
-        <v>50429815</v>
+        <v>57938700</v>
       </c>
       <c r="H3" t="n">
-        <v>29094105</v>
+        <v>22861322</v>
       </c>
       <c r="I3" t="n">
-        <v>719</v>
+        <v>342</v>
       </c>
       <c r="J3" t="n">
-        <v>445.5</v>
+        <v>201</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -741,55 +741,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1039882</v>
+        <v>-781853</v>
       </c>
       <c r="M3" t="n">
-        <v>2873236</v>
+        <v>-3029072</v>
       </c>
       <c r="N3" t="n">
-        <v>18611901</v>
+        <v>103531</v>
       </c>
       <c r="O3" t="n">
-        <v>20676322</v>
+        <v>16962425</v>
       </c>
       <c r="P3" t="n">
-        <v>17922</v>
+        <v>-873853</v>
       </c>
       <c r="Q3" t="n">
-        <v>1412705</v>
+        <v>-2298716</v>
       </c>
       <c r="R3" t="n">
-        <v>13349743</v>
+        <v>-1185840</v>
       </c>
       <c r="S3" t="n">
-        <v>13948306</v>
+        <v>16163768</v>
       </c>
       <c r="T3" t="n">
-        <v>613000</v>
+        <v>89000</v>
       </c>
       <c r="U3" t="n">
-        <v>1197000</v>
+        <v>-787000</v>
       </c>
       <c r="V3" t="n">
-        <v>3587000</v>
+        <v>515000</v>
       </c>
       <c r="W3" t="n">
-        <v>3764897</v>
+        <v>-625000</v>
       </c>
       <c r="X3" t="n">
-        <v>408960</v>
+        <v>3000</v>
       </c>
       <c r="Y3" t="n">
-        <v>263531</v>
+        <v>56644</v>
       </c>
       <c r="Z3" t="n">
-        <v>1675158</v>
+        <v>774371</v>
       </c>
       <c r="AA3" t="n">
-        <v>2963119</v>
+        <v>1423657</v>
       </c>
       <c r="AB3" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,54 +803,54 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1085</v>
+        <v>208</v>
       </c>
       <c r="D4" t="n">
-        <v>954.6</v>
+        <v>207</v>
       </c>
       <c r="E4" t="n">
-        <v>900.1</v>
+        <v>199.9</v>
       </c>
       <c r="F4" t="n">
-        <v>881.7</v>
+        <v>190.12</v>
       </c>
       <c r="G4" t="n">
-        <v>34270461</v>
+        <v>20600438</v>
       </c>
       <c r="H4" t="n">
-        <v>30958709</v>
+        <v>22454689</v>
       </c>
       <c r="I4" t="n">
-        <v>1085</v>
+        <v>231</v>
       </c>
       <c r="J4" t="n">
-        <v>776</v>
+        <v>167</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>290189</v>
+        <v>716000</v>
       </c>
       <c r="M4" t="n">
-        <v>5536520</v>
+        <v>355260</v>
       </c>
       <c r="N4" t="n">
-        <v>14185171</v>
+        <v>9769637</v>
       </c>
       <c r="O4" t="n">
-        <v>9049490</v>
+        <v>10385202</v>
       </c>
       <c r="P4" t="n">
-        <v>226631</v>
+        <v>494000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4886174</v>
+        <v>-466293</v>
       </c>
       <c r="R4" t="n">
-        <v>11932486</v>
+        <v>7867530</v>
       </c>
       <c r="S4" t="n">
-        <v>4161497</v>
+        <v>6928373</v>
       </c>
       <c r="T4" t="n">
-        <v>212000</v>
+        <v>257000</v>
       </c>
       <c r="U4" t="n">
-        <v>983843</v>
+        <v>514000</v>
       </c>
       <c r="V4" t="n">
-        <v>1605943</v>
+        <v>776000</v>
       </c>
       <c r="W4" t="n">
-        <v>5737686</v>
+        <v>2055000</v>
       </c>
       <c r="X4" t="n">
-        <v>-148442</v>
+        <v>-35000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-333497</v>
+        <v>307553</v>
       </c>
       <c r="Z4" t="n">
-        <v>646742</v>
+        <v>1126107</v>
       </c>
       <c r="AA4" t="n">
-        <v>-849693</v>
+        <v>1401829</v>
       </c>
       <c r="AB4" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -930,100 +930,100 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>562</v>
+        <v>72.2</v>
       </c>
       <c r="D5" t="n">
-        <v>513.1</v>
+        <v>69.12</v>
       </c>
       <c r="E5" t="n">
-        <v>491</v>
+        <v>67.56</v>
       </c>
       <c r="F5" t="n">
-        <v>502.85</v>
+        <v>68.52</v>
       </c>
       <c r="G5" t="n">
-        <v>33746000</v>
+        <v>337055872</v>
       </c>
       <c r="H5" t="n">
-        <v>31597000</v>
+        <v>147844553</v>
       </c>
       <c r="I5" t="n">
-        <v>566</v>
+        <v>81.2</v>
       </c>
       <c r="J5" t="n">
-        <v>436</v>
+        <v>61.8</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4244062</v>
+        <v>362000</v>
       </c>
       <c r="M5" t="n">
-        <v>8968342</v>
+        <v>45262498</v>
       </c>
       <c r="N5" t="n">
-        <v>9409867</v>
+        <v>51826814</v>
       </c>
       <c r="O5" t="n">
-        <v>5771807</v>
+        <v>8615439</v>
       </c>
       <c r="P5" t="n">
-        <v>3267388</v>
+        <v>199000</v>
       </c>
       <c r="Q5" t="n">
-        <v>4671266</v>
+        <v>43610609</v>
       </c>
       <c r="R5" t="n">
-        <v>2987230</v>
+        <v>49887674</v>
       </c>
       <c r="S5" t="n">
-        <v>2361844</v>
+        <v>5378285</v>
       </c>
       <c r="T5" t="n">
-        <v>169999</v>
+        <v>190000</v>
       </c>
       <c r="U5" t="n">
-        <v>1483999</v>
+        <v>391000</v>
       </c>
       <c r="V5" t="n">
-        <v>3688999</v>
+        <v>603000</v>
       </c>
       <c r="W5" t="n">
-        <v>2820262</v>
+        <v>1095000</v>
       </c>
       <c r="X5" t="n">
-        <v>806675</v>
+        <v>-27000</v>
       </c>
       <c r="Y5" t="n">
-        <v>2813077</v>
+        <v>1260889</v>
       </c>
       <c r="Z5" t="n">
-        <v>2733638</v>
+        <v>1336140</v>
       </c>
       <c r="AA5" t="n">
-        <v>589701</v>
+        <v>2142154</v>
       </c>
       <c r="AB5" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1047,44 +1047,44 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5290</v>
+        <v>562</v>
       </c>
       <c r="D6" t="n">
-        <v>4977</v>
+        <v>513.1</v>
       </c>
       <c r="E6" t="n">
-        <v>4843</v>
+        <v>491</v>
       </c>
       <c r="F6" t="n">
-        <v>4784.25</v>
+        <v>502.85</v>
       </c>
       <c r="G6" t="n">
-        <v>2917258</v>
+        <v>33746000</v>
       </c>
       <c r="H6" t="n">
-        <v>2443800</v>
+        <v>31597000</v>
       </c>
       <c r="I6" t="n">
-        <v>5635</v>
+        <v>566</v>
       </c>
       <c r="J6" t="n">
-        <v>4160</v>
+        <v>436</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1092,55 +1092,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>358474</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>862813</v>
+        <v>3534276</v>
       </c>
       <c r="N6" t="n">
-        <v>1711672</v>
+        <v>12069364</v>
       </c>
       <c r="O6" t="n">
-        <v>2931478</v>
+        <v>8506456</v>
       </c>
       <c r="P6" t="n">
-        <v>279663</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>550985</v>
+        <v>747528</v>
       </c>
       <c r="R6" t="n">
-        <v>1390729</v>
+        <v>6722185</v>
       </c>
       <c r="S6" t="n">
-        <v>2316469</v>
+        <v>3370593</v>
       </c>
       <c r="T6" t="n">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>246834</v>
+        <v>832999</v>
       </c>
       <c r="V6" t="n">
-        <v>147674</v>
+        <v>2262999</v>
       </c>
       <c r="W6" t="n">
-        <v>424908</v>
+        <v>3387266</v>
       </c>
       <c r="X6" t="n">
-        <v>62811</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>64994</v>
+        <v>1953749</v>
       </c>
       <c r="Z6" t="n">
-        <v>173269</v>
+        <v>3084180</v>
       </c>
       <c r="AA6" t="n">
-        <v>190101</v>
+        <v>1748597</v>
       </c>
       <c r="AB6" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1154,110 +1154,110 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>13.65</v>
       </c>
       <c r="D7" t="n">
-        <v>21.51</v>
+        <v>11.83</v>
       </c>
       <c r="E7" t="n">
-        <v>20.48</v>
+        <v>11.16</v>
       </c>
       <c r="F7" t="n">
-        <v>19.25</v>
+        <v>10.02</v>
       </c>
       <c r="G7" t="n">
-        <v>818361725</v>
+        <v>478320069</v>
       </c>
       <c r="H7" t="n">
-        <v>356215638</v>
+        <v>148294428</v>
       </c>
       <c r="I7" t="n">
-        <v>25.8</v>
+        <v>14.3</v>
       </c>
       <c r="J7" t="n">
-        <v>16.6</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7043839</v>
+        <v>-1323000</v>
       </c>
       <c r="M7" t="n">
-        <v>40455605</v>
+        <v>-537707</v>
       </c>
       <c r="N7" t="n">
-        <v>206744209</v>
+        <v>30239535</v>
       </c>
       <c r="O7" t="n">
-        <v>255008076</v>
+        <v>20838922</v>
       </c>
       <c r="P7" t="n">
-        <v>6297953</v>
+        <v>-2489000</v>
       </c>
       <c r="Q7" t="n">
-        <v>34550487</v>
+        <v>-4522300</v>
       </c>
       <c r="R7" t="n">
-        <v>197817998</v>
+        <v>24799700</v>
       </c>
       <c r="S7" t="n">
-        <v>252197139</v>
+        <v>23134080</v>
       </c>
       <c r="T7" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-14237</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>38763</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>20162</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>738886</v>
+        <v>1166000</v>
       </c>
       <c r="Y7" t="n">
-        <v>5919355</v>
+        <v>3984593</v>
       </c>
       <c r="Z7" t="n">
-        <v>8887448</v>
+        <v>5439835</v>
       </c>
       <c r="AA7" t="n">
-        <v>2790775</v>
+        <v>-2295158</v>
       </c>
       <c r="AB7" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1271,54 +1271,54 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>533</v>
+        <v>29.62</v>
       </c>
       <c r="D8" t="n">
-        <v>511.6</v>
+        <v>28.4</v>
       </c>
       <c r="E8" t="n">
-        <v>468.75</v>
+        <v>28.08</v>
       </c>
       <c r="F8" t="n">
-        <v>448.2</v>
+        <v>27.45</v>
       </c>
       <c r="G8" t="n">
-        <v>2520000</v>
+        <v>84260566</v>
       </c>
       <c r="H8" t="n">
-        <v>4413800</v>
+        <v>87443952</v>
       </c>
       <c r="I8" t="n">
-        <v>558</v>
+        <v>29.83</v>
       </c>
       <c r="J8" t="n">
-        <v>340</v>
+        <v>25.02</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1326,55 +1326,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>755377</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2856804</v>
+        <v>82045272</v>
       </c>
       <c r="N8" t="n">
-        <v>9398836</v>
+        <v>128153177</v>
       </c>
       <c r="O8" t="n">
-        <v>7366124</v>
+        <v>48422713</v>
       </c>
       <c r="P8" t="n">
-        <v>737962</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2860498</v>
+        <v>75375233</v>
       </c>
       <c r="R8" t="n">
-        <v>8822301</v>
+        <v>111222705</v>
       </c>
       <c r="S8" t="n">
-        <v>10989591</v>
+        <v>67486682</v>
       </c>
       <c r="T8" t="n">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>35400</v>
+        <v>2500000</v>
       </c>
       <c r="V8" t="n">
-        <v>89400</v>
+        <v>2500000</v>
       </c>
       <c r="W8" t="n">
-        <v>-1897400</v>
+        <v>5000000</v>
       </c>
       <c r="X8" t="n">
-        <v>18615</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-39094</v>
+        <v>4170039</v>
       </c>
       <c r="Z8" t="n">
-        <v>487135</v>
+        <v>14430472</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1726067</v>
+        <v>-24063969</v>
       </c>
       <c r="AB8" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1388,54 +1388,54 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>661</v>
       </c>
       <c r="D9" t="n">
-        <v>251.5</v>
+        <v>614.6</v>
       </c>
       <c r="E9" t="n">
-        <v>249.5</v>
+        <v>540.85</v>
       </c>
       <c r="F9" t="n">
-        <v>244.47</v>
+        <v>448.73</v>
       </c>
       <c r="G9" t="n">
-        <v>55665305</v>
+        <v>29457930</v>
       </c>
       <c r="H9" t="n">
-        <v>69819957</v>
+        <v>56139070</v>
       </c>
       <c r="I9" t="n">
-        <v>263.5</v>
+        <v>691</v>
       </c>
       <c r="J9" t="n">
-        <v>219.5</v>
+        <v>307</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1176560</v>
+        <v>1772068</v>
       </c>
       <c r="M9" t="n">
-        <v>22207913</v>
+        <v>5775664</v>
       </c>
       <c r="N9" t="n">
-        <v>48256787</v>
+        <v>5980802</v>
       </c>
       <c r="O9" t="n">
-        <v>103877303</v>
+        <v>15355003</v>
       </c>
       <c r="P9" t="n">
-        <v>1667042</v>
+        <v>376068</v>
       </c>
       <c r="Q9" t="n">
-        <v>22481766</v>
+        <v>-174826</v>
       </c>
       <c r="R9" t="n">
-        <v>48192094</v>
+        <v>-2544130</v>
       </c>
       <c r="S9" t="n">
-        <v>110732127</v>
+        <v>-13659032</v>
       </c>
       <c r="T9" t="n">
-        <v>-12810</v>
+        <v>1350000</v>
       </c>
       <c r="U9" t="n">
-        <v>-97437</v>
+        <v>5658000</v>
       </c>
       <c r="V9" t="n">
-        <v>-273247</v>
+        <v>7313000</v>
       </c>
       <c r="W9" t="n">
-        <v>-4762535</v>
+        <v>30055694</v>
       </c>
       <c r="X9" t="n">
-        <v>-477672</v>
+        <v>46000</v>
       </c>
       <c r="Y9" t="n">
-        <v>-176416</v>
+        <v>292490</v>
       </c>
       <c r="Z9" t="n">
-        <v>337940</v>
+        <v>1211932</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2092289</v>
+        <v>-1041659</v>
       </c>
       <c r="AB9" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1505,110 +1505,110 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.65</v>
+        <v>528</v>
       </c>
       <c r="D10" t="n">
-        <v>11.83</v>
+        <v>517</v>
       </c>
       <c r="E10" t="n">
-        <v>11.16</v>
+        <v>485.1</v>
       </c>
       <c r="F10" t="n">
-        <v>10.02</v>
+        <v>427.7</v>
       </c>
       <c r="G10" t="n">
-        <v>478320069</v>
+        <v>49392113</v>
       </c>
       <c r="H10" t="n">
-        <v>148294428</v>
+        <v>45973161</v>
       </c>
       <c r="I10" t="n">
-        <v>14.3</v>
+        <v>556</v>
       </c>
       <c r="J10" t="n">
-        <v>8.130000000000001</v>
+        <v>321</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-3262412</v>
+        <v>-282000</v>
       </c>
       <c r="M10" t="n">
-        <v>22044344</v>
+        <v>400619</v>
       </c>
       <c r="N10" t="n">
-        <v>50882174</v>
+        <v>14817402</v>
       </c>
       <c r="O10" t="n">
-        <v>25324386</v>
+        <v>12471153</v>
       </c>
       <c r="P10" t="n">
-        <v>-4232242</v>
+        <v>-441000</v>
       </c>
       <c r="Q10" t="n">
-        <v>20328525</v>
+        <v>-897406</v>
       </c>
       <c r="R10" t="n">
-        <v>47907283</v>
+        <v>10580710</v>
       </c>
       <c r="S10" t="n">
-        <v>21954098</v>
+        <v>9641815</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>128000</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1415000</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3320000</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>4122277</v>
       </c>
       <c r="X10" t="n">
-        <v>969830</v>
+        <v>31000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1715819</v>
+        <v>-116975</v>
       </c>
       <c r="Z10" t="n">
-        <v>2974891</v>
+        <v>916692</v>
       </c>
       <c r="AA10" t="n">
-        <v>3370288</v>
+        <v>-1292939</v>
       </c>
       <c r="AB10" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>55.4</v>
+        <v>8.16</v>
       </c>
       <c r="D11" t="n">
-        <v>53.91</v>
+        <v>6.81</v>
       </c>
       <c r="E11" t="n">
-        <v>51.25</v>
+        <v>6.24</v>
       </c>
       <c r="F11" t="n">
-        <v>50.42</v>
+        <v>6.03</v>
       </c>
       <c r="G11" t="n">
-        <v>15723414</v>
+        <v>36791094</v>
       </c>
       <c r="H11" t="n">
-        <v>11255762</v>
+        <v>51399518</v>
       </c>
       <c r="I11" t="n">
-        <v>60.3</v>
+        <v>8.16</v>
       </c>
       <c r="J11" t="n">
-        <v>45.45</v>
+        <v>5.55</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,28 +1677,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>198200</v>
+        <v>-249000</v>
       </c>
       <c r="M11" t="n">
-        <v>4087251</v>
+        <v>5235922</v>
       </c>
       <c r="N11" t="n">
-        <v>9951064</v>
+        <v>22920506</v>
       </c>
       <c r="O11" t="n">
-        <v>7954561</v>
+        <v>27546408</v>
       </c>
       <c r="P11" t="n">
-        <v>177415</v>
+        <v>-249000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3934844</v>
+        <v>-170000</v>
       </c>
       <c r="R11" t="n">
-        <v>9678259</v>
+        <v>17295700</v>
       </c>
       <c r="S11" t="n">
-        <v>7765339</v>
+        <v>22198700</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1713,19 +1713,19 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>20785</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>152407</v>
+        <v>5405922</v>
       </c>
       <c r="Z11" t="n">
-        <v>272805</v>
+        <v>5624806</v>
       </c>
       <c r="AA11" t="n">
-        <v>189222</v>
+        <v>5347708</v>
       </c>
       <c r="AB11" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,110 +1739,110 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>304.5</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>291.6</v>
+        <v>21.51</v>
       </c>
       <c r="E12" t="n">
-        <v>282.85</v>
+        <v>20.48</v>
       </c>
       <c r="F12" t="n">
-        <v>260.6</v>
+        <v>19.25</v>
       </c>
       <c r="G12" t="n">
-        <v>21738108</v>
+        <v>818361725</v>
       </c>
       <c r="H12" t="n">
-        <v>31212343</v>
+        <v>356215638</v>
       </c>
       <c r="I12" t="n">
-        <v>317</v>
+        <v>25.8</v>
       </c>
       <c r="J12" t="n">
-        <v>208.5</v>
+        <v>16.6</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4745353</v>
+        <v>-5515203</v>
       </c>
       <c r="M12" t="n">
-        <v>9834017</v>
+        <v>7917517</v>
       </c>
       <c r="N12" t="n">
-        <v>10574690</v>
+        <v>161647079</v>
       </c>
       <c r="O12" t="n">
-        <v>20883168</v>
+        <v>120738088</v>
       </c>
       <c r="P12" t="n">
-        <v>4763785</v>
+        <v>-6347203</v>
       </c>
       <c r="Q12" t="n">
-        <v>10787025</v>
+        <v>5167481</v>
       </c>
       <c r="R12" t="n">
-        <v>13381377</v>
+        <v>155789836</v>
       </c>
       <c r="S12" t="n">
-        <v>26096411</v>
+        <v>130583792</v>
       </c>
       <c r="T12" t="n">
-        <v>-101000</v>
+        <v>754000</v>
       </c>
       <c r="U12" t="n">
-        <v>-1724000</v>
+        <v>1508000</v>
       </c>
       <c r="V12" t="n">
-        <v>-3525000</v>
+        <v>2308000</v>
       </c>
       <c r="W12" t="n">
-        <v>-4431464</v>
+        <v>2256001</v>
       </c>
       <c r="X12" t="n">
-        <v>82568</v>
+        <v>78000</v>
       </c>
       <c r="Y12" t="n">
-        <v>770992</v>
+        <v>1242036</v>
       </c>
       <c r="Z12" t="n">
-        <v>718313</v>
+        <v>3549243</v>
       </c>
       <c r="AA12" t="n">
-        <v>-781779</v>
+        <v>-12101705</v>
       </c>
       <c r="AB12" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,54 +1856,54 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>248</v>
       </c>
       <c r="D13" t="n">
-        <v>51.64</v>
+        <v>251.3</v>
       </c>
       <c r="E13" t="n">
-        <v>50.21</v>
+        <v>235.75</v>
       </c>
       <c r="F13" t="n">
-        <v>50.11</v>
+        <v>221.18</v>
       </c>
       <c r="G13" t="n">
-        <v>14910096</v>
+        <v>131044723</v>
       </c>
       <c r="H13" t="n">
-        <v>26622786</v>
+        <v>130303090</v>
       </c>
       <c r="I13" t="n">
-        <v>53.9</v>
+        <v>272.5</v>
       </c>
       <c r="J13" t="n">
-        <v>47.35</v>
+        <v>183</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1599308</v>
+        <v>2017000</v>
       </c>
       <c r="M13" t="n">
-        <v>19287277</v>
+        <v>15243773</v>
       </c>
       <c r="N13" t="n">
-        <v>32054623</v>
+        <v>17228813</v>
       </c>
       <c r="O13" t="n">
-        <v>9933706</v>
+        <v>31539180</v>
       </c>
       <c r="P13" t="n">
-        <v>1194273</v>
+        <v>1367000</v>
       </c>
       <c r="Q13" t="n">
-        <v>18166886</v>
+        <v>12340014</v>
       </c>
       <c r="R13" t="n">
-        <v>30323339</v>
+        <v>13030797</v>
       </c>
       <c r="S13" t="n">
-        <v>8970452</v>
+        <v>26323861</v>
       </c>
       <c r="T13" t="n">
-        <v>900</v>
+        <v>179000</v>
       </c>
       <c r="U13" t="n">
-        <v>-26066</v>
+        <v>1198000</v>
       </c>
       <c r="V13" t="n">
-        <v>-64166</v>
+        <v>964000</v>
       </c>
       <c r="W13" t="n">
-        <v>-341744</v>
+        <v>4061000</v>
       </c>
       <c r="X13" t="n">
-        <v>404135</v>
+        <v>471000</v>
       </c>
       <c r="Y13" t="n">
-        <v>1146457</v>
+        <v>1705759</v>
       </c>
       <c r="Z13" t="n">
-        <v>1795450</v>
+        <v>3234016</v>
       </c>
       <c r="AA13" t="n">
-        <v>1304998</v>
+        <v>1154319</v>
       </c>
       <c r="AB13" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,54 +1973,54 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>661</v>
+        <v>533</v>
       </c>
       <c r="D14" t="n">
-        <v>614.6</v>
+        <v>511.6</v>
       </c>
       <c r="E14" t="n">
-        <v>540.85</v>
+        <v>468.75</v>
       </c>
       <c r="F14" t="n">
-        <v>448.73</v>
+        <v>448.2</v>
       </c>
       <c r="G14" t="n">
-        <v>29457930</v>
+        <v>2520000</v>
       </c>
       <c r="H14" t="n">
-        <v>56139070</v>
+        <v>4413800</v>
       </c>
       <c r="I14" t="n">
-        <v>691</v>
+        <v>558</v>
       </c>
       <c r="J14" t="n">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2028,55 +2028,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1102045</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4327355</v>
+        <v>1189791</v>
       </c>
       <c r="N14" t="n">
-        <v>3862470</v>
+        <v>5055165</v>
       </c>
       <c r="O14" t="n">
-        <v>14290677</v>
+        <v>8904823</v>
       </c>
       <c r="P14" t="n">
-        <v>-4617135</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4685625</v>
+        <v>1260281</v>
       </c>
       <c r="R14" t="n">
-        <v>-12048132</v>
+        <v>4827711</v>
       </c>
       <c r="S14" t="n">
-        <v>-24677774</v>
+        <v>11582504</v>
       </c>
       <c r="T14" t="n">
-        <v>6849000</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>8963449</v>
+        <v>39800</v>
       </c>
       <c r="V14" t="n">
-        <v>16117449</v>
+        <v>35400</v>
       </c>
       <c r="W14" t="n">
-        <v>41742069</v>
+        <v>-1943400</v>
       </c>
       <c r="X14" t="n">
-        <v>-1129820</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>49531</v>
+        <v>-110290</v>
       </c>
       <c r="Z14" t="n">
-        <v>-206847</v>
+        <v>192054</v>
       </c>
       <c r="AA14" t="n">
-        <v>-2773618</v>
+        <v>-734281</v>
       </c>
       <c r="AB14" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2095,49 +2095,49 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>72.2</v>
+        <v>45.7</v>
       </c>
       <c r="D15" t="n">
-        <v>69.12</v>
+        <v>43.4</v>
       </c>
       <c r="E15" t="n">
-        <v>67.56</v>
+        <v>40.22</v>
       </c>
       <c r="F15" t="n">
-        <v>68.52</v>
+        <v>34.08</v>
       </c>
       <c r="G15" t="n">
-        <v>337055872</v>
+        <v>1463227218</v>
       </c>
       <c r="H15" t="n">
-        <v>147844553</v>
+        <v>613882104</v>
       </c>
       <c r="I15" t="n">
-        <v>81.2</v>
+        <v>52.2</v>
       </c>
       <c r="J15" t="n">
-        <v>61.8</v>
+        <v>23.65</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,52 +2145,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-8515087</v>
+        <v>-5110089</v>
       </c>
       <c r="M15" t="n">
-        <v>28946585</v>
+        <v>-12884905</v>
       </c>
       <c r="N15" t="n">
-        <v>26633814</v>
+        <v>91189745</v>
       </c>
       <c r="O15" t="n">
-        <v>-37000661</v>
+        <v>-49504225</v>
       </c>
       <c r="P15" t="n">
-        <v>-9231376</v>
+        <v>-5330089</v>
       </c>
       <c r="Q15" t="n">
-        <v>26801156</v>
+        <v>-14693634</v>
       </c>
       <c r="R15" t="n">
-        <v>23647845</v>
+        <v>78065226</v>
       </c>
       <c r="S15" t="n">
-        <v>-36842695</v>
+        <v>-50153632</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>424000</v>
       </c>
       <c r="U15" t="n">
-        <v>11000</v>
+        <v>848000</v>
       </c>
       <c r="V15" t="n">
-        <v>33000</v>
+        <v>1233000</v>
       </c>
       <c r="W15" t="n">
-        <v>26000</v>
+        <v>944678</v>
       </c>
       <c r="X15" t="n">
-        <v>716289</v>
+        <v>-204000</v>
       </c>
       <c r="Y15" t="n">
-        <v>2134429</v>
+        <v>960729</v>
       </c>
       <c r="Z15" t="n">
-        <v>2952969</v>
+        <v>11891519</v>
       </c>
       <c r="AA15" t="n">
-        <v>-183966</v>
+        <v>-295271</v>
       </c>
       <c r="AB15" t="n">
         <v>95</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2217,100 +2217,100 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45.7</v>
+        <v>1085</v>
       </c>
       <c r="D16" t="n">
-        <v>43.4</v>
+        <v>954.6</v>
       </c>
       <c r="E16" t="n">
-        <v>40.22</v>
+        <v>900.1</v>
       </c>
       <c r="F16" t="n">
-        <v>34.08</v>
+        <v>881.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1463227218</v>
+        <v>34270461</v>
       </c>
       <c r="H16" t="n">
-        <v>613882104</v>
+        <v>30958709</v>
       </c>
       <c r="I16" t="n">
-        <v>52.2</v>
+        <v>1085</v>
       </c>
       <c r="J16" t="n">
-        <v>23.65</v>
+        <v>776</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-20234462</v>
+        <v>-2521000</v>
       </c>
       <c r="M16" t="n">
-        <v>-5521196</v>
+        <v>-3850707</v>
       </c>
       <c r="N16" t="n">
-        <v>83429081</v>
+        <v>1986755</v>
       </c>
       <c r="O16" t="n">
-        <v>59378294</v>
+        <v>-4361730</v>
       </c>
       <c r="P16" t="n">
-        <v>-26508116</v>
+        <v>-3327000</v>
       </c>
       <c r="Q16" t="n">
-        <v>-14599220</v>
+        <v>-4879031</v>
       </c>
       <c r="R16" t="n">
-        <v>56981613</v>
+        <v>-1386350</v>
       </c>
       <c r="S16" t="n">
-        <v>16527987</v>
+        <v>-11378514</v>
       </c>
       <c r="T16" t="n">
-        <v>43100</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>13211</v>
+        <v>-450000</v>
       </c>
       <c r="V16" t="n">
-        <v>17311</v>
+        <v>-39900</v>
       </c>
       <c r="W16" t="n">
-        <v>453089</v>
+        <v>3133762</v>
       </c>
       <c r="X16" t="n">
-        <v>6230554</v>
+        <v>806000</v>
       </c>
       <c r="Y16" t="n">
-        <v>9064813</v>
+        <v>1478324</v>
       </c>
       <c r="Z16" t="n">
-        <v>26430157</v>
+        <v>3413005</v>
       </c>
       <c r="AA16" t="n">
-        <v>42397218</v>
+        <v>3883022</v>
       </c>
       <c r="AB16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2324,54 +2324,54 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、5日法人明顯買超、外資投信同步賣超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>922</v>
+        <v>48.32</v>
       </c>
       <c r="D17" t="n">
-        <v>888.2</v>
+        <v>46.5</v>
       </c>
       <c r="E17" t="n">
-        <v>854.3</v>
+        <v>45.58</v>
       </c>
       <c r="F17" t="n">
-        <v>896.4</v>
+        <v>43.92</v>
       </c>
       <c r="G17" t="n">
-        <v>24438087</v>
+        <v>49374408</v>
       </c>
       <c r="H17" t="n">
-        <v>20893593</v>
+        <v>49915897</v>
       </c>
       <c r="I17" t="n">
-        <v>1035</v>
+        <v>48.79</v>
       </c>
       <c r="J17" t="n">
-        <v>765</v>
+        <v>37.05</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-208181</v>
+        <v>-259000</v>
       </c>
       <c r="M17" t="n">
-        <v>3582994</v>
+        <v>31868141</v>
       </c>
       <c r="N17" t="n">
-        <v>3677318</v>
+        <v>63466447</v>
       </c>
       <c r="O17" t="n">
-        <v>-1724114</v>
+        <v>87670270</v>
       </c>
       <c r="P17" t="n">
-        <v>39735</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1895312</v>
+        <v>25778945</v>
       </c>
       <c r="R17" t="n">
-        <v>1121613</v>
+        <v>35876034</v>
       </c>
       <c r="S17" t="n">
-        <v>-12620</v>
+        <v>44516303</v>
       </c>
       <c r="T17" t="n">
-        <v>-165000</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1591000</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2486000</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-1244694</v>
+        <v>280000</v>
       </c>
       <c r="X17" t="n">
-        <v>-82916</v>
+        <v>-259000</v>
       </c>
       <c r="Y17" t="n">
-        <v>96682</v>
+        <v>6089196</v>
       </c>
       <c r="Z17" t="n">
-        <v>69705</v>
+        <v>27590413</v>
       </c>
       <c r="AA17" t="n">
-        <v>-466800</v>
+        <v>42873967</v>
       </c>
       <c r="AB17" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2441,54 +2441,54 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>540</v>
+        <v>259</v>
       </c>
       <c r="D18" t="n">
-        <v>498.7</v>
+        <v>251.5</v>
       </c>
       <c r="E18" t="n">
-        <v>457.05</v>
+        <v>249.5</v>
       </c>
       <c r="F18" t="n">
-        <v>434.32</v>
+        <v>244.47</v>
       </c>
       <c r="G18" t="n">
-        <v>41904053</v>
+        <v>55665305</v>
       </c>
       <c r="H18" t="n">
-        <v>51443369</v>
+        <v>69819957</v>
       </c>
       <c r="I18" t="n">
-        <v>558</v>
+        <v>263.5</v>
       </c>
       <c r="J18" t="n">
-        <v>354</v>
+        <v>219.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2496,55 +2496,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-967994</v>
+        <v>-2503792</v>
       </c>
       <c r="M18" t="n">
-        <v>-1212400</v>
+        <v>50779728</v>
       </c>
       <c r="N18" t="n">
-        <v>2289305</v>
+        <v>73148250</v>
       </c>
       <c r="O18" t="n">
-        <v>1887707</v>
+        <v>75733410</v>
       </c>
       <c r="P18" t="n">
-        <v>1375340</v>
+        <v>-1914792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2831559</v>
+        <v>48222621</v>
       </c>
       <c r="R18" t="n">
-        <v>-676473</v>
+        <v>70351115</v>
       </c>
       <c r="S18" t="n">
-        <v>4958845</v>
+        <v>96895915</v>
       </c>
       <c r="T18" t="n">
-        <v>-2688000</v>
+        <v>-376000</v>
       </c>
       <c r="U18" t="n">
-        <v>848563</v>
+        <v>460000</v>
       </c>
       <c r="V18" t="n">
-        <v>1580563</v>
+        <v>-79000</v>
       </c>
       <c r="W18" t="n">
-        <v>-4914501</v>
+        <v>-3081338</v>
       </c>
       <c r="X18" t="n">
-        <v>344666</v>
+        <v>-213000</v>
       </c>
       <c r="Y18" t="n">
-        <v>770596</v>
+        <v>2097107</v>
       </c>
       <c r="Z18" t="n">
-        <v>1385215</v>
+        <v>2876135</v>
       </c>
       <c r="AA18" t="n">
-        <v>1843363</v>
+        <v>-18081167</v>
       </c>
       <c r="AB18" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2558,110 +2558,110 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1580</v>
+        <v>2350</v>
       </c>
       <c r="D19" t="n">
-        <v>1433</v>
+        <v>2136</v>
       </c>
       <c r="E19" t="n">
-        <v>1385.5</v>
+        <v>2101</v>
       </c>
       <c r="F19" t="n">
-        <v>1308.55</v>
+        <v>2045</v>
       </c>
       <c r="G19" t="n">
-        <v>9546000</v>
+        <v>12198582</v>
       </c>
       <c r="H19" t="n">
-        <v>3017800</v>
+        <v>11067330</v>
       </c>
       <c r="I19" t="n">
-        <v>1700</v>
+        <v>2410</v>
       </c>
       <c r="J19" t="n">
-        <v>941</v>
+        <v>1365</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-83545</v>
+        <v>-1206259</v>
       </c>
       <c r="M19" t="n">
-        <v>660709</v>
+        <v>2505038</v>
       </c>
       <c r="N19" t="n">
-        <v>848398</v>
+        <v>1839585</v>
       </c>
       <c r="O19" t="n">
-        <v>2026953</v>
+        <v>-2314653</v>
       </c>
       <c r="P19" t="n">
-        <v>-1100380</v>
+        <v>-1207259</v>
       </c>
       <c r="Q19" t="n">
-        <v>-461658</v>
+        <v>1915878</v>
       </c>
       <c r="R19" t="n">
-        <v>-27799</v>
+        <v>563005</v>
       </c>
       <c r="S19" t="n">
-        <v>1154682</v>
+        <v>146862</v>
       </c>
       <c r="T19" t="n">
-        <v>1406000</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1457700</v>
+        <v>202500</v>
       </c>
       <c r="V19" t="n">
-        <v>1445700</v>
+        <v>-50791</v>
       </c>
       <c r="W19" t="n">
-        <v>427100</v>
+        <v>-1668702</v>
       </c>
       <c r="X19" t="n">
-        <v>-389165</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>-335333</v>
+        <v>386660</v>
       </c>
       <c r="Z19" t="n">
-        <v>-569503</v>
+        <v>1327371</v>
       </c>
       <c r="AA19" t="n">
-        <v>445171</v>
+        <v>-792813</v>
       </c>
       <c r="AB19" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,54 +2675,54 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5280</v>
+        <v>130.5</v>
       </c>
       <c r="D20" t="n">
-        <v>5334</v>
+        <v>118.7</v>
       </c>
       <c r="E20" t="n">
-        <v>5278</v>
+        <v>113.39</v>
       </c>
       <c r="F20" t="n">
-        <v>5144.75</v>
+        <v>100.19</v>
       </c>
       <c r="G20" t="n">
-        <v>2655826</v>
+        <v>291896012</v>
       </c>
       <c r="H20" t="n">
-        <v>2172103</v>
+        <v>252641517</v>
       </c>
       <c r="I20" t="n">
-        <v>5880</v>
+        <v>133.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4615</v>
+        <v>71.3</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,116 +2730,116 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>15106</v>
+        <v>-8985000</v>
       </c>
       <c r="M20" t="n">
-        <v>117253</v>
+        <v>14866623</v>
       </c>
       <c r="N20" t="n">
-        <v>77678</v>
+        <v>25531286</v>
       </c>
       <c r="O20" t="n">
-        <v>198915</v>
+        <v>37917795</v>
       </c>
       <c r="P20" t="n">
-        <v>-44712</v>
+        <v>-8342000</v>
       </c>
       <c r="Q20" t="n">
-        <v>91809</v>
+        <v>31835878</v>
       </c>
       <c r="R20" t="n">
-        <v>-160303</v>
+        <v>67282245</v>
       </c>
       <c r="S20" t="n">
-        <v>-526781</v>
+        <v>108988</v>
       </c>
       <c r="T20" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-29006</v>
+        <v>-21406000</v>
       </c>
       <c r="V20" t="n">
-        <v>78994</v>
+        <v>-47366000</v>
       </c>
       <c r="W20" t="n">
-        <v>635413</v>
+        <v>39084182</v>
       </c>
       <c r="X20" t="n">
-        <v>23818</v>
+        <v>-643000</v>
       </c>
       <c r="Y20" t="n">
-        <v>54450</v>
+        <v>4436745</v>
       </c>
       <c r="Z20" t="n">
-        <v>158987</v>
+        <v>5615041</v>
       </c>
       <c r="AA20" t="n">
-        <v>90283</v>
+        <v>-1275375</v>
       </c>
       <c r="AB20" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人小幅買超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>168</v>
+        <v>55.4</v>
       </c>
       <c r="D21" t="n">
-        <v>176.9</v>
+        <v>53.91</v>
       </c>
       <c r="E21" t="n">
-        <v>174.55</v>
+        <v>51.25</v>
       </c>
       <c r="F21" t="n">
-        <v>161.45</v>
+        <v>50.42</v>
       </c>
       <c r="G21" t="n">
-        <v>9878768</v>
+        <v>15723414</v>
       </c>
       <c r="H21" t="n">
-        <v>26306205</v>
+        <v>11255762</v>
       </c>
       <c r="I21" t="n">
-        <v>198.5</v>
+        <v>60.3</v>
       </c>
       <c r="J21" t="n">
-        <v>139</v>
+        <v>45.45</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,28 +2847,28 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>836799</v>
+        <v>-125000</v>
       </c>
       <c r="M21" t="n">
-        <v>-413419</v>
+        <v>3204745</v>
       </c>
       <c r="N21" t="n">
-        <v>9121757</v>
+        <v>8745358</v>
       </c>
       <c r="O21" t="n">
-        <v>4176141</v>
+        <v>9280503</v>
       </c>
       <c r="P21" t="n">
-        <v>449302</v>
+        <v>-124000</v>
       </c>
       <c r="Q21" t="n">
-        <v>-565158</v>
+        <v>2752020</v>
       </c>
       <c r="R21" t="n">
-        <v>7723967</v>
+        <v>8194020</v>
       </c>
       <c r="S21" t="n">
-        <v>3221282</v>
+        <v>8637435</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2877,86 +2877,86 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>6393</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>387497</v>
+        <v>-1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>151739</v>
+        <v>452725</v>
       </c>
       <c r="Z21" t="n">
-        <v>1392790</v>
+        <v>551338</v>
       </c>
       <c r="AA21" t="n">
-        <v>948466</v>
+        <v>643068</v>
       </c>
       <c r="AB21" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>82.40000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="D22" t="n">
-        <v>81.73999999999999</v>
+        <v>35.15</v>
       </c>
       <c r="E22" t="n">
-        <v>81.34</v>
+        <v>34.84</v>
       </c>
       <c r="F22" t="n">
-        <v>80.16</v>
+        <v>34.65</v>
       </c>
       <c r="G22" t="n">
-        <v>12463968</v>
+        <v>66828833</v>
       </c>
       <c r="H22" t="n">
-        <v>10197116</v>
+        <v>50399647</v>
       </c>
       <c r="I22" t="n">
-        <v>85.8</v>
+        <v>36.2</v>
       </c>
       <c r="J22" t="n">
-        <v>70.2</v>
+        <v>33.25</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,64 +2964,64 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-4199015</v>
+        <v>2059000</v>
       </c>
       <c r="M22" t="n">
-        <v>2506502</v>
+        <v>-3241213</v>
       </c>
       <c r="N22" t="n">
-        <v>-800124</v>
+        <v>11940050</v>
       </c>
       <c r="O22" t="n">
-        <v>-4198886</v>
+        <v>905035</v>
       </c>
       <c r="P22" t="n">
-        <v>-4105690</v>
+        <v>2065000</v>
       </c>
       <c r="Q22" t="n">
-        <v>2163760</v>
+        <v>-13005700</v>
       </c>
       <c r="R22" t="n">
-        <v>-1000255</v>
+        <v>-9403814</v>
       </c>
       <c r="S22" t="n">
-        <v>-4318549</v>
+        <v>-18095890</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-59000</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>9147670</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>20948228</v>
       </c>
       <c r="W22" t="n">
-        <v>-8000</v>
+        <v>17091835</v>
       </c>
       <c r="X22" t="n">
-        <v>-93325</v>
+        <v>53000</v>
       </c>
       <c r="Y22" t="n">
-        <v>342742</v>
+        <v>616817</v>
       </c>
       <c r="Z22" t="n">
-        <v>200131</v>
+        <v>395636</v>
       </c>
       <c r="AA22" t="n">
-        <v>127663</v>
+        <v>1909090</v>
       </c>
       <c r="AB22" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3031,49 +3031,49 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2350</v>
+        <v>41.35</v>
       </c>
       <c r="D23" t="n">
-        <v>2136</v>
+        <v>42.12</v>
       </c>
       <c r="E23" t="n">
-        <v>2101</v>
+        <v>40.77</v>
       </c>
       <c r="F23" t="n">
-        <v>2149</v>
+        <v>39.71</v>
       </c>
       <c r="G23" t="n">
-        <v>12198582</v>
+        <v>37127594</v>
       </c>
       <c r="H23" t="n">
-        <v>11067330</v>
+        <v>36197186</v>
       </c>
       <c r="I23" t="n">
-        <v>2410</v>
+        <v>44.75</v>
       </c>
       <c r="J23" t="n">
-        <v>1880</v>
+        <v>36.6</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,116 +3081,116 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-65912</v>
+        <v>27000</v>
       </c>
       <c r="M23" t="n">
-        <v>-250347</v>
+        <v>12175610</v>
       </c>
       <c r="N23" t="n">
-        <v>290459</v>
+        <v>26928474</v>
       </c>
       <c r="O23" t="n">
-        <v>-1481438</v>
+        <v>107891418</v>
       </c>
       <c r="P23" t="n">
-        <v>121443</v>
+        <v>299000</v>
       </c>
       <c r="Q23" t="n">
-        <v>-295</v>
+        <v>12590135</v>
       </c>
       <c r="R23" t="n">
-        <v>-145909</v>
+        <v>27773538</v>
       </c>
       <c r="S23" t="n">
-        <v>33483</v>
+        <v>113450279</v>
       </c>
       <c r="T23" t="n">
-        <v>-120500</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-231968</v>
+        <v>-620000</v>
       </c>
       <c r="V23" t="n">
-        <v>-485259</v>
+        <v>-943000</v>
       </c>
       <c r="W23" t="n">
-        <v>-1333854</v>
+        <v>-4979000</v>
       </c>
       <c r="X23" t="n">
-        <v>-66855</v>
+        <v>-272000</v>
       </c>
       <c r="Y23" t="n">
-        <v>-18084</v>
+        <v>205475</v>
       </c>
       <c r="Z23" t="n">
-        <v>921627</v>
+        <v>97936</v>
       </c>
       <c r="AA23" t="n">
-        <v>-181067</v>
+        <v>-579861</v>
       </c>
       <c r="AB23" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步賣超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、5日法人買超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2270</v>
+        <v>611</v>
       </c>
       <c r="D24" t="n">
-        <v>2250</v>
+        <v>555</v>
       </c>
       <c r="E24" t="n">
-        <v>2245</v>
+        <v>540</v>
       </c>
       <c r="F24" t="n">
-        <v>2242.25</v>
+        <v>528.95</v>
       </c>
       <c r="G24" t="n">
-        <v>32781470</v>
+        <v>39627497</v>
       </c>
       <c r="H24" t="n">
-        <v>30223565</v>
+        <v>28597065</v>
       </c>
       <c r="I24" t="n">
-        <v>2345</v>
+        <v>636</v>
       </c>
       <c r="J24" t="n">
-        <v>2135</v>
+        <v>465</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,116 +3198,116 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-2572029</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-2116239</v>
+        <v>-1946569</v>
       </c>
       <c r="N24" t="n">
-        <v>-3083433</v>
+        <v>424126</v>
       </c>
       <c r="O24" t="n">
-        <v>-10178055</v>
+        <v>-5704334</v>
       </c>
       <c r="P24" t="n">
-        <v>-9521827</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-8788853</v>
+        <v>-3417636</v>
       </c>
       <c r="R24" t="n">
-        <v>-17296342</v>
+        <v>-889810</v>
       </c>
       <c r="S24" t="n">
-        <v>-51109009</v>
+        <v>-7908244</v>
       </c>
       <c r="T24" t="n">
-        <v>6429500</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>5964652</v>
+        <v>1131000</v>
       </c>
       <c r="V24" t="n">
-        <v>12561152</v>
+        <v>1108000</v>
       </c>
       <c r="W24" t="n">
-        <v>40136470</v>
+        <v>2121901</v>
       </c>
       <c r="X24" t="n">
-        <v>520298</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>707962</v>
+        <v>340067</v>
       </c>
       <c r="Z24" t="n">
-        <v>1651757</v>
+        <v>205936</v>
       </c>
       <c r="AA24" t="n">
-        <v>794484</v>
+        <v>82009</v>
       </c>
       <c r="AB24" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>141</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>124.8</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>125.75</v>
+        <v>81.34</v>
       </c>
       <c r="F25" t="n">
-        <v>114.91</v>
+        <v>80.16</v>
       </c>
       <c r="G25" t="n">
-        <v>336105421</v>
+        <v>12463968</v>
       </c>
       <c r="H25" t="n">
-        <v>249474700</v>
+        <v>10197116</v>
       </c>
       <c r="I25" t="n">
-        <v>141</v>
+        <v>85.8</v>
       </c>
       <c r="J25" t="n">
-        <v>88.8</v>
+        <v>70.2</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,467 +3315,467 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-11962552</v>
+        <v>-45000</v>
       </c>
       <c r="M25" t="n">
-        <v>40167238</v>
+        <v>-581799</v>
       </c>
       <c r="N25" t="n">
-        <v>-4889605</v>
+        <v>265590</v>
       </c>
       <c r="O25" t="n">
-        <v>68676281</v>
+        <v>4734573</v>
       </c>
       <c r="P25" t="n">
-        <v>-19138371</v>
+        <v>-44000</v>
       </c>
       <c r="Q25" t="n">
-        <v>32303633</v>
+        <v>-441520</v>
       </c>
       <c r="R25" t="n">
-        <v>-18031163</v>
+        <v>456155</v>
       </c>
       <c r="S25" t="n">
-        <v>-12020795</v>
+        <v>4667108</v>
       </c>
       <c r="T25" t="n">
-        <v>7462000</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>6270969</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>10656969</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>76451043</v>
+        <v>-2000</v>
       </c>
       <c r="X25" t="n">
-        <v>-286181</v>
+        <v>-1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>1592636</v>
+        <v>-140279</v>
       </c>
       <c r="Z25" t="n">
-        <v>2484589</v>
+        <v>-190565</v>
       </c>
       <c r="AA25" t="n">
-        <v>4246033</v>
+        <v>69465</v>
       </c>
       <c r="AB25" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、突破20日高點、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1220</v>
+        <v>1580</v>
       </c>
       <c r="D26" t="n">
-        <v>1114.4</v>
+        <v>1433</v>
       </c>
       <c r="E26" t="n">
-        <v>1037.7</v>
+        <v>1385.5</v>
       </c>
       <c r="F26" t="n">
-        <v>1072.35</v>
+        <v>1308.55</v>
       </c>
       <c r="G26" t="n">
-        <v>4415000</v>
+        <v>9546000</v>
       </c>
       <c r="H26" t="n">
-        <v>3736800</v>
+        <v>3017800</v>
       </c>
       <c r="I26" t="n">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="J26" t="n">
-        <v>865</v>
+        <v>941</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>78870</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-1139380</v>
+        <v>198709</v>
       </c>
       <c r="N26" t="n">
-        <v>-1176252</v>
+        <v>885708</v>
       </c>
       <c r="O26" t="n">
-        <v>-1740259</v>
+        <v>1548637</v>
       </c>
       <c r="P26" t="n">
-        <v>-73248</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1970174</v>
+        <v>-910598</v>
       </c>
       <c r="R26" t="n">
-        <v>-2217164</v>
+        <v>-196691</v>
       </c>
       <c r="S26" t="n">
-        <v>-2350595</v>
+        <v>1041700</v>
       </c>
       <c r="T26" t="n">
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>871000</v>
+        <v>1445000</v>
       </c>
       <c r="V26" t="n">
-        <v>1046000</v>
+        <v>1410700</v>
       </c>
       <c r="W26" t="n">
-        <v>567000</v>
+        <v>422100</v>
       </c>
       <c r="X26" t="n">
-        <v>-57882</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>-40206</v>
+        <v>-335693</v>
       </c>
       <c r="Z26" t="n">
-        <v>-5088</v>
+        <v>-328301</v>
       </c>
       <c r="AA26" t="n">
-        <v>43336</v>
+        <v>84837</v>
       </c>
       <c r="AB26" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>342</v>
+        <v>52</v>
       </c>
       <c r="D27" t="n">
-        <v>285.6</v>
+        <v>51.64</v>
       </c>
       <c r="E27" t="n">
-        <v>261.4</v>
+        <v>50.21</v>
       </c>
       <c r="F27" t="n">
-        <v>241.47</v>
+        <v>50.11</v>
       </c>
       <c r="G27" t="n">
-        <v>57938700</v>
+        <v>14910096</v>
       </c>
       <c r="H27" t="n">
-        <v>22861322</v>
+        <v>26622786</v>
       </c>
       <c r="I27" t="n">
-        <v>342</v>
+        <v>53.9</v>
       </c>
       <c r="J27" t="n">
-        <v>201</v>
+        <v>47.35</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-1834154</v>
+        <v>-532000</v>
       </c>
       <c r="M27" t="n">
-        <v>-4443864</v>
+        <v>-8902235</v>
       </c>
       <c r="N27" t="n">
-        <v>-2363562</v>
+        <v>1733803</v>
       </c>
       <c r="O27" t="n">
-        <v>8629303</v>
+        <v>-13038195</v>
       </c>
       <c r="P27" t="n">
-        <v>-2734302</v>
+        <v>-482000</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3531935</v>
+        <v>-7779291</v>
       </c>
       <c r="R27" t="n">
-        <v>-4279508</v>
+        <v>2700889</v>
       </c>
       <c r="S27" t="n">
-        <v>4990232</v>
+        <v>-11158828</v>
       </c>
       <c r="T27" t="n">
-        <v>94000</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>-1715000</v>
+        <v>24000</v>
       </c>
       <c r="V27" t="n">
-        <v>-408000</v>
+        <v>-15000</v>
       </c>
       <c r="W27" t="n">
-        <v>-455184</v>
+        <v>-308478</v>
       </c>
       <c r="X27" t="n">
-        <v>806148</v>
+        <v>-50000</v>
       </c>
       <c r="Y27" t="n">
-        <v>803071</v>
+        <v>-1146944</v>
       </c>
       <c r="Z27" t="n">
-        <v>2323946</v>
+        <v>-952086</v>
       </c>
       <c r="AA27" t="n">
-        <v>4094255</v>
+        <v>-1570889</v>
       </c>
       <c r="AB27" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>34.25</v>
+        <v>4265</v>
       </c>
       <c r="D28" t="n">
-        <v>35.13</v>
+        <v>3830</v>
       </c>
       <c r="E28" t="n">
-        <v>34.6</v>
+        <v>3586.5</v>
       </c>
       <c r="F28" t="n">
-        <v>37.35</v>
+        <v>3387.5</v>
       </c>
       <c r="G28" t="n">
-        <v>11138430</v>
+        <v>19540872</v>
       </c>
       <c r="H28" t="n">
-        <v>16177150</v>
+        <v>12055166</v>
       </c>
       <c r="I28" t="n">
-        <v>44.05</v>
+        <v>4440</v>
       </c>
       <c r="J28" t="n">
-        <v>31.1</v>
+        <v>2485</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2800000</v>
+        <v>293052</v>
       </c>
       <c r="M28" t="n">
-        <v>-2768167</v>
+        <v>-1380273</v>
       </c>
       <c r="N28" t="n">
-        <v>2773001</v>
+        <v>-1636442</v>
       </c>
       <c r="O28" t="n">
-        <v>11403137</v>
+        <v>-4694401</v>
       </c>
       <c r="P28" t="n">
-        <v>2798000</v>
+        <v>162052</v>
       </c>
       <c r="Q28" t="n">
-        <v>-2599000</v>
+        <v>-850404</v>
       </c>
       <c r="R28" t="n">
-        <v>2771000</v>
+        <v>-1119173</v>
       </c>
       <c r="S28" t="n">
-        <v>11617136</v>
+        <v>-3218308</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>-129000</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>-1219000</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>-1748000</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>-2439146</v>
       </c>
       <c r="X28" t="n">
-        <v>2000</v>
+        <v>260000</v>
       </c>
       <c r="Y28" t="n">
-        <v>-169167</v>
+        <v>689131</v>
       </c>
       <c r="Z28" t="n">
-        <v>2001</v>
+        <v>1230731</v>
       </c>
       <c r="AA28" t="n">
-        <v>-213999</v>
+        <v>963053</v>
       </c>
       <c r="AB28" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>866</v>
+        <v>27.65</v>
       </c>
       <c r="D29" t="n">
-        <v>742</v>
+        <v>27.96</v>
       </c>
       <c r="E29" t="n">
-        <v>732.1</v>
+        <v>27.3</v>
       </c>
       <c r="F29" t="n">
-        <v>711.25</v>
+        <v>25.02</v>
       </c>
       <c r="G29" t="n">
-        <v>2958000</v>
+        <v>52074412</v>
       </c>
       <c r="H29" t="n">
-        <v>4678000</v>
+        <v>88757521</v>
       </c>
       <c r="I29" t="n">
-        <v>866</v>
+        <v>31.9</v>
       </c>
       <c r="J29" t="n">
-        <v>534</v>
+        <v>21.6</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,116 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-541871</v>
+        <v>-559000</v>
       </c>
       <c r="M29" t="n">
-        <v>-2561156</v>
+        <v>9060504</v>
       </c>
       <c r="N29" t="n">
-        <v>-4480928</v>
+        <v>53346382</v>
       </c>
       <c r="O29" t="n">
-        <v>-5069064</v>
+        <v>50279477</v>
       </c>
       <c r="P29" t="n">
-        <v>-566747</v>
+        <v>-552000</v>
       </c>
       <c r="Q29" t="n">
-        <v>-3254183</v>
+        <v>10488375</v>
       </c>
       <c r="R29" t="n">
-        <v>-4533384</v>
+        <v>56496175</v>
       </c>
       <c r="S29" t="n">
-        <v>-6369986</v>
+        <v>54028264</v>
       </c>
       <c r="T29" t="n">
-        <v>-84038</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>-295650</v>
+        <v>-2772000</v>
       </c>
       <c r="V29" t="n">
-        <v>-946650</v>
+        <v>-5745000</v>
       </c>
       <c r="W29" t="n">
-        <v>-269880</v>
+        <v>-5745000</v>
       </c>
       <c r="X29" t="n">
-        <v>108914</v>
+        <v>-7000</v>
       </c>
       <c r="Y29" t="n">
-        <v>988677</v>
+        <v>1344129</v>
       </c>
       <c r="Z29" t="n">
-        <v>999106</v>
+        <v>2595207</v>
       </c>
       <c r="AA29" t="n">
-        <v>1570802</v>
+        <v>1996213</v>
       </c>
       <c r="AB29" t="n">
-        <v>-5</v>
+        <v>35</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>130.5</v>
+        <v>2270</v>
       </c>
       <c r="D30" t="n">
-        <v>118.7</v>
+        <v>2250</v>
       </c>
       <c r="E30" t="n">
-        <v>113.39</v>
+        <v>2245</v>
       </c>
       <c r="F30" t="n">
-        <v>100.19</v>
+        <v>2242.25</v>
       </c>
       <c r="G30" t="n">
-        <v>291896012</v>
+        <v>32781470</v>
       </c>
       <c r="H30" t="n">
-        <v>252641517</v>
+        <v>30223565</v>
       </c>
       <c r="I30" t="n">
-        <v>133.5</v>
+        <v>2345</v>
       </c>
       <c r="J30" t="n">
-        <v>71.3</v>
+        <v>2135</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,116 +3900,116 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-24732790</v>
+        <v>-5413302</v>
       </c>
       <c r="M30" t="n">
-        <v>-79198141</v>
+        <v>-2555015</v>
       </c>
       <c r="N30" t="n">
-        <v>-84281268</v>
+        <v>-6363482</v>
       </c>
       <c r="O30" t="n">
-        <v>-88381049</v>
+        <v>-19724620</v>
       </c>
       <c r="P30" t="n">
-        <v>-45921195</v>
+        <v>-5003302</v>
       </c>
       <c r="Q30" t="n">
-        <v>-76267503</v>
+        <v>-5961013</v>
       </c>
       <c r="R30" t="n">
-        <v>-78400331</v>
+        <v>-9949977</v>
       </c>
       <c r="S30" t="n">
-        <v>-182437864</v>
+        <v>-33301310</v>
       </c>
       <c r="T30" t="n">
-        <v>20707132</v>
+        <v>-559000</v>
       </c>
       <c r="U30" t="n">
-        <v>-4178019</v>
+        <v>3010500</v>
       </c>
       <c r="V30" t="n">
-        <v>-9430887</v>
+        <v>2618500</v>
       </c>
       <c r="W30" t="n">
-        <v>94794673</v>
+        <v>20518260</v>
       </c>
       <c r="X30" t="n">
-        <v>481273</v>
+        <v>149000</v>
       </c>
       <c r="Y30" t="n">
-        <v>1247381</v>
+        <v>395498</v>
       </c>
       <c r="Z30" t="n">
-        <v>3549950</v>
+        <v>967995</v>
       </c>
       <c r="AA30" t="n">
-        <v>-737858</v>
+        <v>-6941570</v>
       </c>
       <c r="AB30" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>303.5</v>
+        <v>1220</v>
       </c>
       <c r="D31" t="n">
-        <v>295.6</v>
+        <v>1114.4</v>
       </c>
       <c r="E31" t="n">
-        <v>303.1</v>
+        <v>1037.7</v>
       </c>
       <c r="F31" t="n">
-        <v>281.4</v>
+        <v>1072.35</v>
       </c>
       <c r="G31" t="n">
-        <v>152949355</v>
+        <v>4415000</v>
       </c>
       <c r="H31" t="n">
-        <v>148065232</v>
+        <v>3736800</v>
       </c>
       <c r="I31" t="n">
-        <v>353</v>
+        <v>1300</v>
       </c>
       <c r="J31" t="n">
-        <v>198.5</v>
+        <v>865</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,116 +4017,116 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-7167551</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-6915479</v>
+        <v>-936110</v>
       </c>
       <c r="N31" t="n">
-        <v>-14599344</v>
+        <v>-958914</v>
       </c>
       <c r="O31" t="n">
-        <v>-52051868</v>
+        <v>-1688679</v>
       </c>
       <c r="P31" t="n">
-        <v>2181497</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1871943</v>
+        <v>-1253397</v>
       </c>
       <c r="R31" t="n">
-        <v>2834419</v>
+        <v>-2041124</v>
       </c>
       <c r="S31" t="n">
-        <v>-21992353</v>
+        <v>-2328511</v>
       </c>
       <c r="T31" t="n">
-        <v>-8258000</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>-8507165</v>
+        <v>441000</v>
       </c>
       <c r="V31" t="n">
-        <v>-16981165</v>
+        <v>1079000</v>
       </c>
       <c r="W31" t="n">
-        <v>-26831509</v>
+        <v>578000</v>
       </c>
       <c r="X31" t="n">
-        <v>-1091048</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>-280257</v>
+        <v>-123713</v>
       </c>
       <c r="Z31" t="n">
-        <v>-452598</v>
+        <v>3210</v>
       </c>
       <c r="AA31" t="n">
-        <v>-3228006</v>
+        <v>61832</v>
       </c>
       <c r="AB31" t="n">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>478</v>
+        <v>866</v>
       </c>
       <c r="D32" t="n">
-        <v>490.7</v>
+        <v>742</v>
       </c>
       <c r="E32" t="n">
-        <v>475.85</v>
+        <v>732.1</v>
       </c>
       <c r="F32" t="n">
-        <v>436.95</v>
+        <v>711.25</v>
       </c>
       <c r="G32" t="n">
-        <v>36584546</v>
+        <v>2958000</v>
       </c>
       <c r="H32" t="n">
-        <v>27861072</v>
+        <v>4678000</v>
       </c>
       <c r="I32" t="n">
-        <v>523</v>
+        <v>866</v>
       </c>
       <c r="J32" t="n">
-        <v>344.5</v>
+        <v>534</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,196 +4134,1249 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-5830786</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1856284</v>
+        <v>-803228</v>
       </c>
       <c r="N32" t="n">
-        <v>-5316375</v>
+        <v>-3683174</v>
       </c>
       <c r="O32" t="n">
-        <v>-18584918</v>
+        <v>-5411546</v>
       </c>
       <c r="P32" t="n">
-        <v>-5948511</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2968809</v>
+        <v>-992257</v>
       </c>
       <c r="R32" t="n">
-        <v>-6389494</v>
+        <v>-3758390</v>
       </c>
       <c r="S32" t="n">
-        <v>-22409660</v>
+        <v>-6279183</v>
       </c>
       <c r="T32" t="n">
-        <v>262000</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1510683</v>
+        <v>-155038</v>
       </c>
       <c r="V32" t="n">
-        <v>1749683</v>
+        <v>-975650</v>
       </c>
       <c r="W32" t="n">
-        <v>4998304</v>
+        <v>-361372</v>
       </c>
       <c r="X32" t="n">
-        <v>-144275</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>-398158</v>
+        <v>344067</v>
       </c>
       <c r="Z32" t="n">
-        <v>-676564</v>
+        <v>1050866</v>
       </c>
       <c r="AA32" t="n">
-        <v>-1173562</v>
+        <v>1229009</v>
       </c>
       <c r="AB32" t="n">
-        <v>-40</v>
+        <v>20</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>6669.TW</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5280</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5334</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5278</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5144.75</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2655826</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2172103</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5880</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4615</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>49559</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-5122</v>
+      </c>
+      <c r="O33" t="n">
+        <v>218522</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>66174</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-141226</v>
+      </c>
+      <c r="S33" t="n">
+        <v>172333</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-41000</v>
+      </c>
+      <c r="V33" t="n">
+        <v>31000</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-19794</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>24385</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>105104</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>65983</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>籌碼中性、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4960.TW</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>誠美材</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="D34" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="E34" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11138430</v>
+      </c>
+      <c r="H34" t="n">
+        <v>16177150</v>
+      </c>
+      <c r="I34" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="J34" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>7000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-1655951</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1092217</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2552697</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-291000</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-2250951</v>
+      </c>
+      <c r="R34" t="n">
+        <v>30049</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2249529</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>298000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>595000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1062168</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>303168</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>5日法人明顯買超</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2383.TW</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5290</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4977</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4843</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4784.25</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2917258</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2443800</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5635</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4160</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>-963947</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-1568076</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-2041638</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-1613345</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-1039947</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-1763562</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-2243428</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-1532578</v>
+      </c>
+      <c r="T35" t="n">
+        <v>61000</v>
+      </c>
+      <c r="U35" t="n">
+        <v>111000</v>
+      </c>
+      <c r="V35" t="n">
+        <v>56840</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-102507</v>
+      </c>
+      <c r="X35" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>84486</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>144950</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>21740</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6285.TW</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>282.85</v>
+      </c>
+      <c r="F36" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>21738108</v>
+      </c>
+      <c r="H36" t="n">
+        <v>31212343</v>
+      </c>
+      <c r="I36" t="n">
+        <v>317</v>
+      </c>
+      <c r="J36" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-6187776</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-10442456</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-13220030</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-4441053</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-6809486</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-5218997</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-1655000</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-3421000</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-6278404</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-91723</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-211970</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-1722629</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4958.TW</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>540</v>
+      </c>
+      <c r="D37" t="n">
+        <v>498.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>457.05</v>
+      </c>
+      <c r="F37" t="n">
+        <v>434.32</v>
+      </c>
+      <c r="G37" t="n">
+        <v>41904053</v>
+      </c>
+      <c r="H37" t="n">
+        <v>51443369</v>
+      </c>
+      <c r="I37" t="n">
+        <v>558</v>
+      </c>
+      <c r="J37" t="n">
+        <v>354</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>-326000</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-6368319</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-2224620</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-18241428</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-280000</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-7239933</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-6740187</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-21640218</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1551000</v>
+      </c>
+      <c r="V37" t="n">
+        <v>4971000</v>
+      </c>
+      <c r="W37" t="n">
+        <v>5741936</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-46000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-679386</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-455433</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-2343146</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8046.TW</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>922</v>
+      </c>
+      <c r="D38" t="n">
+        <v>888.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>854.3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>24438087</v>
+      </c>
+      <c r="H38" t="n">
+        <v>20893593</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1035</v>
+      </c>
+      <c r="J38" t="n">
+        <v>765</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-8889954</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-8579449</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-14214048</v>
+      </c>
+      <c r="P38" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-6207050</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-7010484</v>
+      </c>
+      <c r="S38" t="n">
+        <v>-8419367</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-2521000</v>
+      </c>
+      <c r="V38" t="n">
+        <v>-1461000</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-4998000</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-161904</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-107965</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-796681</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>站上5日線、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3673.TW</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TPK-KY</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>63.98</v>
+      </c>
+      <c r="F39" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7159433</v>
+      </c>
+      <c r="H39" t="n">
+        <v>9959241</v>
+      </c>
+      <c r="I39" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>-2083000</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-4946314</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-1989195</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-7388088</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-1798000</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-4418778</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-2255766</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-8042719</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>-285000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-527536</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>266571</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>654631</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>站上5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2408.TW</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>303.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>283.88</v>
+      </c>
+      <c r="G40" t="n">
+        <v>152949355</v>
+      </c>
+      <c r="H40" t="n">
+        <v>148065232</v>
+      </c>
+      <c r="I40" t="n">
+        <v>353</v>
+      </c>
+      <c r="J40" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>-542383</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-15005929</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-16064626</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-50822064</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-499000</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-2299220</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-4017241</v>
+      </c>
+      <c r="S40" t="n">
+        <v>-26452241</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-150000</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-12030000</v>
+      </c>
+      <c r="V40" t="n">
+        <v>-12396000</v>
+      </c>
+      <c r="W40" t="n">
+        <v>-19531954</v>
+      </c>
+      <c r="X40" t="n">
+        <v>106617</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-676709</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>348615</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-4837869</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>站上5日線、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2376.TW</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>273</v>
+      </c>
+      <c r="D41" t="n">
+        <v>278</v>
+      </c>
+      <c r="E41" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>266.35</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5636066</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6333129</v>
+      </c>
+      <c r="I41" t="n">
+        <v>292</v>
+      </c>
+      <c r="J41" t="n">
+        <v>222</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>160279</v>
+      </c>
+      <c r="M41" t="n">
+        <v>439864</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-579291</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1925081</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-49721</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>-748363</v>
+      </c>
+      <c r="R41" t="n">
+        <v>-1725679</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-2796137</v>
+      </c>
+      <c r="T41" t="n">
+        <v>109000</v>
+      </c>
+      <c r="U41" t="n">
+        <v>865000</v>
+      </c>
+      <c r="V41" t="n">
+        <v>496000</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4244371</v>
+      </c>
+      <c r="X41" t="n">
+        <v>101000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>323227</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>650388</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>476847</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>5289.TWO</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C42" t="n">
         <v>1690</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D42" t="n">
         <v>1697</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E42" t="n">
         <v>1747</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F42" t="n">
         <v>1612.75</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G42" t="n">
         <v>3178000</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H42" t="n">
         <v>3603600</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I42" t="n">
         <v>1935</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J42" t="n">
         <v>1190</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>無明顯異常</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>-467151</v>
-      </c>
-      <c r="M33" t="n">
-        <v>-779449</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-1431458</v>
-      </c>
-      <c r="O33" t="n">
-        <v>-2655109</v>
-      </c>
-      <c r="P33" t="n">
-        <v>-190195</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>-247868</v>
-      </c>
-      <c r="R33" t="n">
-        <v>-528542</v>
-      </c>
-      <c r="S33" t="n">
-        <v>-1615246</v>
-      </c>
-      <c r="T33" t="n">
-        <v>-264617</v>
-      </c>
-      <c r="U33" t="n">
-        <v>-524617</v>
-      </c>
-      <c r="V33" t="n">
-        <v>-879117</v>
-      </c>
-      <c r="W33" t="n">
-        <v>-828848</v>
-      </c>
-      <c r="X33" t="n">
-        <v>-12339</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>-6964</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>-23799</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>-211015</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>-95</v>
-      </c>
-      <c r="AC33" t="inlineStr">
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-819556</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-1174288</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-2471356</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>-204494</v>
+      </c>
+      <c r="R42" t="n">
+        <v>-479756</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-1654442</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-601617</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-689617</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-637450</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-13445</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-4915</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-179464</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr">
+      <c r="AE42" t="inlineStr">
         <is>
           <t>跌破5日線、量能未放大</t>
         </is>
       </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -586,93 +586,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>124.8</v>
+        <v>33.58</v>
       </c>
       <c r="E2" t="n">
-        <v>125.75</v>
+        <v>30.93</v>
       </c>
       <c r="F2" t="n">
-        <v>114.91</v>
+        <v>29.77</v>
       </c>
       <c r="G2" t="n">
-        <v>336105421</v>
+        <v>210267926</v>
       </c>
       <c r="H2" t="n">
-        <v>249474700</v>
+        <v>105612204</v>
       </c>
       <c r="I2" t="n">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>88.8</v>
+        <v>26.65</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>217385</v>
+        <v>28357859</v>
       </c>
       <c r="M2" t="n">
-        <v>78086673</v>
+        <v>54438183</v>
       </c>
       <c r="N2" t="n">
-        <v>45209767</v>
+        <v>105494658</v>
       </c>
       <c r="O2" t="n">
-        <v>128638416</v>
+        <v>103900475</v>
       </c>
       <c r="P2" t="n">
-        <v>883001</v>
+        <v>30455390</v>
       </c>
       <c r="Q2" t="n">
-        <v>73858010</v>
+        <v>60993174</v>
       </c>
       <c r="R2" t="n">
-        <v>43544586</v>
+        <v>114822974</v>
       </c>
       <c r="S2" t="n">
-        <v>77189599</v>
+        <v>117602284</v>
       </c>
       <c r="T2" t="n">
-        <v>-200000</v>
+        <v>-2772000</v>
       </c>
       <c r="U2" t="n">
-        <v>4851000</v>
+        <v>-9607000</v>
       </c>
       <c r="V2" t="n">
-        <v>1575000</v>
+        <v>-15073000</v>
       </c>
       <c r="W2" t="n">
-        <v>52930074</v>
+        <v>-18394000</v>
       </c>
       <c r="X2" t="n">
-        <v>-465616</v>
+        <v>674469</v>
       </c>
       <c r="Y2" t="n">
-        <v>-622337</v>
+        <v>3052009</v>
       </c>
       <c r="Z2" t="n">
-        <v>90181</v>
+        <v>5744684</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1481257</v>
+        <v>4692191</v>
       </c>
       <c r="AB2" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -686,54 +686,54 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>342</v>
+        <v>696</v>
       </c>
       <c r="D3" t="n">
-        <v>285.6</v>
+        <v>606.4</v>
       </c>
       <c r="E3" t="n">
-        <v>261.4</v>
+        <v>555.55</v>
       </c>
       <c r="F3" t="n">
-        <v>241.47</v>
+        <v>529.38</v>
       </c>
       <c r="G3" t="n">
-        <v>57938700</v>
+        <v>50429815</v>
       </c>
       <c r="H3" t="n">
-        <v>22861322</v>
+        <v>29094105</v>
       </c>
       <c r="I3" t="n">
-        <v>342</v>
+        <v>719</v>
       </c>
       <c r="J3" t="n">
-        <v>201</v>
+        <v>445.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -741,55 +741,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-781853</v>
+        <v>6579882</v>
       </c>
       <c r="M3" t="n">
-        <v>-3029072</v>
+        <v>9377855</v>
       </c>
       <c r="N3" t="n">
-        <v>103531</v>
+        <v>23425392</v>
       </c>
       <c r="O3" t="n">
-        <v>16962425</v>
+        <v>27208037</v>
       </c>
       <c r="P3" t="n">
-        <v>-873853</v>
+        <v>4397554</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2298716</v>
+        <v>5776931</v>
       </c>
       <c r="R3" t="n">
-        <v>-1185840</v>
+        <v>16930530</v>
       </c>
       <c r="S3" t="n">
-        <v>16163768</v>
+        <v>19891809</v>
       </c>
       <c r="T3" t="n">
-        <v>89000</v>
+        <v>2307000</v>
       </c>
       <c r="U3" t="n">
-        <v>-787000</v>
+        <v>4050000</v>
       </c>
       <c r="V3" t="n">
-        <v>515000</v>
+        <v>5962000</v>
       </c>
       <c r="W3" t="n">
-        <v>-625000</v>
+        <v>5955371</v>
       </c>
       <c r="X3" t="n">
-        <v>3000</v>
+        <v>-124672</v>
       </c>
       <c r="Y3" t="n">
-        <v>56644</v>
+        <v>-449076</v>
       </c>
       <c r="Z3" t="n">
-        <v>774371</v>
+        <v>532862</v>
       </c>
       <c r="AA3" t="n">
-        <v>1423657</v>
+        <v>1360857</v>
       </c>
       <c r="AB3" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,54 +803,54 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>208</v>
+        <v>1085</v>
       </c>
       <c r="D4" t="n">
-        <v>207</v>
+        <v>954.6</v>
       </c>
       <c r="E4" t="n">
-        <v>199.9</v>
+        <v>900.1</v>
       </c>
       <c r="F4" t="n">
-        <v>190.12</v>
+        <v>881.7</v>
       </c>
       <c r="G4" t="n">
-        <v>20600438</v>
+        <v>34270461</v>
       </c>
       <c r="H4" t="n">
-        <v>22454689</v>
+        <v>30958709</v>
       </c>
       <c r="I4" t="n">
-        <v>231</v>
+        <v>1085</v>
       </c>
       <c r="J4" t="n">
-        <v>167</v>
+        <v>776</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>716000</v>
+        <v>11776533</v>
       </c>
       <c r="M4" t="n">
-        <v>355260</v>
+        <v>18214157</v>
       </c>
       <c r="N4" t="n">
-        <v>9769637</v>
+        <v>25900315</v>
       </c>
       <c r="O4" t="n">
-        <v>10385202</v>
+        <v>20392758</v>
       </c>
       <c r="P4" t="n">
-        <v>494000</v>
+        <v>8680405</v>
       </c>
       <c r="Q4" t="n">
-        <v>-466293</v>
+        <v>15114917</v>
       </c>
       <c r="R4" t="n">
-        <v>7867530</v>
+        <v>21294781</v>
       </c>
       <c r="S4" t="n">
-        <v>6928373</v>
+        <v>13761982</v>
       </c>
       <c r="T4" t="n">
-        <v>257000</v>
+        <v>2890000</v>
       </c>
       <c r="U4" t="n">
-        <v>514000</v>
+        <v>3211843</v>
       </c>
       <c r="V4" t="n">
-        <v>776000</v>
+        <v>4108943</v>
       </c>
       <c r="W4" t="n">
-        <v>2055000</v>
+        <v>7512686</v>
       </c>
       <c r="X4" t="n">
-        <v>-35000</v>
+        <v>206128</v>
       </c>
       <c r="Y4" t="n">
-        <v>307553</v>
+        <v>-112603</v>
       </c>
       <c r="Z4" t="n">
-        <v>1126107</v>
+        <v>496591</v>
       </c>
       <c r="AA4" t="n">
-        <v>1401829</v>
+        <v>-881910</v>
       </c>
       <c r="AB4" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -930,100 +930,100 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72.2</v>
+        <v>562</v>
       </c>
       <c r="D5" t="n">
-        <v>69.12</v>
+        <v>513.1</v>
       </c>
       <c r="E5" t="n">
-        <v>67.56</v>
+        <v>491</v>
       </c>
       <c r="F5" t="n">
-        <v>68.52</v>
+        <v>502.85</v>
       </c>
       <c r="G5" t="n">
-        <v>337055872</v>
+        <v>33746000</v>
       </c>
       <c r="H5" t="n">
-        <v>147844553</v>
+        <v>31597000</v>
       </c>
       <c r="I5" t="n">
-        <v>81.2</v>
+        <v>566</v>
       </c>
       <c r="J5" t="n">
-        <v>61.8</v>
+        <v>436</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>362000</v>
+        <v>4244062</v>
       </c>
       <c r="M5" t="n">
-        <v>45262498</v>
+        <v>8968342</v>
       </c>
       <c r="N5" t="n">
-        <v>51826814</v>
+        <v>9409867</v>
       </c>
       <c r="O5" t="n">
-        <v>8615439</v>
+        <v>5771807</v>
       </c>
       <c r="P5" t="n">
-        <v>199000</v>
+        <v>3267388</v>
       </c>
       <c r="Q5" t="n">
-        <v>43610609</v>
+        <v>4671266</v>
       </c>
       <c r="R5" t="n">
-        <v>49887674</v>
+        <v>2987230</v>
       </c>
       <c r="S5" t="n">
-        <v>5378285</v>
+        <v>2361844</v>
       </c>
       <c r="T5" t="n">
-        <v>190000</v>
+        <v>169999</v>
       </c>
       <c r="U5" t="n">
-        <v>391000</v>
+        <v>1483999</v>
       </c>
       <c r="V5" t="n">
-        <v>603000</v>
+        <v>3688999</v>
       </c>
       <c r="W5" t="n">
-        <v>1095000</v>
+        <v>2820262</v>
       </c>
       <c r="X5" t="n">
-        <v>-27000</v>
+        <v>806675</v>
       </c>
       <c r="Y5" t="n">
-        <v>1260889</v>
+        <v>2813077</v>
       </c>
       <c r="Z5" t="n">
-        <v>1336140</v>
+        <v>2733638</v>
       </c>
       <c r="AA5" t="n">
-        <v>2142154</v>
+        <v>589701</v>
       </c>
       <c r="AB5" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
+          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1047,100 +1047,100 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>562</v>
+        <v>342</v>
       </c>
       <c r="D6" t="n">
-        <v>513.1</v>
+        <v>285.6</v>
       </c>
       <c r="E6" t="n">
-        <v>491</v>
+        <v>261.4</v>
       </c>
       <c r="F6" t="n">
-        <v>502.85</v>
+        <v>241.47</v>
       </c>
       <c r="G6" t="n">
-        <v>33746000</v>
+        <v>57938700</v>
       </c>
       <c r="H6" t="n">
-        <v>31597000</v>
+        <v>22861322</v>
       </c>
       <c r="I6" t="n">
-        <v>566</v>
+        <v>342</v>
       </c>
       <c r="J6" t="n">
-        <v>436</v>
+        <v>201</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1408279</v>
       </c>
       <c r="M6" t="n">
-        <v>3534276</v>
+        <v>-2666797</v>
       </c>
       <c r="N6" t="n">
-        <v>12069364</v>
+        <v>4636866</v>
       </c>
       <c r="O6" t="n">
-        <v>8506456</v>
+        <v>8251124</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>713763</v>
       </c>
       <c r="Q6" t="n">
-        <v>747528</v>
+        <v>-634880</v>
       </c>
       <c r="R6" t="n">
-        <v>6722185</v>
+        <v>5866112</v>
       </c>
       <c r="S6" t="n">
-        <v>3370593</v>
+        <v>10991058</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-90000</v>
       </c>
       <c r="U6" t="n">
-        <v>832999</v>
+        <v>-2864000</v>
       </c>
       <c r="V6" t="n">
-        <v>2262999</v>
+        <v>-2858000</v>
       </c>
       <c r="W6" t="n">
-        <v>3387266</v>
+        <v>-4145286</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>784516</v>
       </c>
       <c r="Y6" t="n">
-        <v>1953749</v>
+        <v>832083</v>
       </c>
       <c r="Z6" t="n">
-        <v>3084180</v>
+        <v>1628754</v>
       </c>
       <c r="AA6" t="n">
-        <v>1748597</v>
+        <v>1405352</v>
       </c>
       <c r="AB6" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1154,110 +1154,110 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13.65</v>
+        <v>29.62</v>
       </c>
       <c r="D7" t="n">
-        <v>11.83</v>
+        <v>28.4</v>
       </c>
       <c r="E7" t="n">
-        <v>11.16</v>
+        <v>28.08</v>
       </c>
       <c r="F7" t="n">
-        <v>10.02</v>
+        <v>27.45</v>
       </c>
       <c r="G7" t="n">
-        <v>478320069</v>
+        <v>84260566</v>
       </c>
       <c r="H7" t="n">
-        <v>148294428</v>
+        <v>87443952</v>
       </c>
       <c r="I7" t="n">
-        <v>14.3</v>
+        <v>29.83</v>
       </c>
       <c r="J7" t="n">
-        <v>8.130000000000001</v>
+        <v>25.02</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-1323000</v>
+        <v>44993144</v>
       </c>
       <c r="M7" t="n">
-        <v>-537707</v>
+        <v>201974425</v>
       </c>
       <c r="N7" t="n">
-        <v>30239535</v>
+        <v>256280137</v>
       </c>
       <c r="O7" t="n">
-        <v>20838922</v>
+        <v>153202899</v>
       </c>
       <c r="P7" t="n">
-        <v>-2489000</v>
+        <v>7568505</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4522300</v>
+        <v>128594402</v>
       </c>
       <c r="R7" t="n">
-        <v>24799700</v>
+        <v>167888118</v>
       </c>
       <c r="S7" t="n">
-        <v>23134080</v>
+        <v>93494704</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="X7" t="n">
-        <v>1166000</v>
+        <v>37424639</v>
       </c>
       <c r="Y7" t="n">
-        <v>3984593</v>
+        <v>70880023</v>
       </c>
       <c r="Z7" t="n">
-        <v>5439835</v>
+        <v>85892019</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2295158</v>
+        <v>54708195</v>
       </c>
       <c r="AB7" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1271,54 +1271,54 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.62</v>
+        <v>141</v>
       </c>
       <c r="D8" t="n">
-        <v>28.4</v>
+        <v>124.8</v>
       </c>
       <c r="E8" t="n">
-        <v>28.08</v>
+        <v>125.75</v>
       </c>
       <c r="F8" t="n">
-        <v>27.45</v>
+        <v>114.91</v>
       </c>
       <c r="G8" t="n">
-        <v>84260566</v>
+        <v>336105421</v>
       </c>
       <c r="H8" t="n">
-        <v>87443952</v>
+        <v>249474700</v>
       </c>
       <c r="I8" t="n">
-        <v>29.83</v>
+        <v>141</v>
       </c>
       <c r="J8" t="n">
-        <v>25.02</v>
+        <v>88.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1326,55 +1326,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>53874275</v>
       </c>
       <c r="M8" t="n">
-        <v>82045272</v>
+        <v>183655968</v>
       </c>
       <c r="N8" t="n">
-        <v>128153177</v>
+        <v>160960826</v>
       </c>
       <c r="O8" t="n">
-        <v>48422713</v>
+        <v>201131678</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>46872727</v>
       </c>
       <c r="Q8" t="n">
-        <v>75375233</v>
+        <v>170406739</v>
       </c>
       <c r="R8" t="n">
-        <v>111222705</v>
+        <v>151935091</v>
       </c>
       <c r="S8" t="n">
-        <v>67486682</v>
+        <v>128105725</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4364455</v>
       </c>
       <c r="U8" t="n">
-        <v>2500000</v>
+        <v>8424424</v>
       </c>
       <c r="V8" t="n">
-        <v>2500000</v>
+        <v>7094424</v>
       </c>
       <c r="W8" t="n">
-        <v>5000000</v>
+        <v>71647256</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2637093</v>
       </c>
       <c r="Y8" t="n">
-        <v>4170039</v>
+        <v>4824805</v>
       </c>
       <c r="Z8" t="n">
-        <v>14430472</v>
+        <v>1931311</v>
       </c>
       <c r="AA8" t="n">
-        <v>-24063969</v>
+        <v>1378697</v>
       </c>
       <c r="AB8" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1388,54 +1388,54 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>661</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>614.6</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>540.85</v>
+        <v>72.94</v>
       </c>
       <c r="F9" t="n">
-        <v>448.73</v>
+        <v>66.67</v>
       </c>
       <c r="G9" t="n">
-        <v>29457930</v>
+        <v>26030149</v>
       </c>
       <c r="H9" t="n">
-        <v>56139070</v>
+        <v>40319814</v>
       </c>
       <c r="I9" t="n">
-        <v>691</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>307</v>
+        <v>58.1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1772068</v>
+        <v>5391543</v>
       </c>
       <c r="M9" t="n">
-        <v>5775664</v>
+        <v>8356421</v>
       </c>
       <c r="N9" t="n">
-        <v>5980802</v>
+        <v>13622444</v>
       </c>
       <c r="O9" t="n">
-        <v>15355003</v>
+        <v>9083310</v>
       </c>
       <c r="P9" t="n">
-        <v>376068</v>
+        <v>5322203</v>
       </c>
       <c r="Q9" t="n">
-        <v>-174826</v>
+        <v>7569949</v>
       </c>
       <c r="R9" t="n">
-        <v>-2544130</v>
+        <v>11932067</v>
       </c>
       <c r="S9" t="n">
-        <v>-13659032</v>
+        <v>5954226</v>
       </c>
       <c r="T9" t="n">
-        <v>1350000</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>5658000</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7313000</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>30055694</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46000</v>
+        <v>69340</v>
       </c>
       <c r="Y9" t="n">
-        <v>292490</v>
+        <v>786472</v>
       </c>
       <c r="Z9" t="n">
-        <v>1211932</v>
+        <v>1690377</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1041659</v>
+        <v>3129084</v>
       </c>
       <c r="AB9" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1505,54 +1505,54 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>528</v>
+        <v>8.16</v>
       </c>
       <c r="D10" t="n">
-        <v>517</v>
+        <v>6.81</v>
       </c>
       <c r="E10" t="n">
-        <v>485.1</v>
+        <v>6.24</v>
       </c>
       <c r="F10" t="n">
-        <v>427.7</v>
+        <v>6.03</v>
       </c>
       <c r="G10" t="n">
-        <v>49392113</v>
+        <v>36791094</v>
       </c>
       <c r="H10" t="n">
-        <v>45973161</v>
+        <v>51399518</v>
       </c>
       <c r="I10" t="n">
-        <v>556</v>
+        <v>8.16</v>
       </c>
       <c r="J10" t="n">
-        <v>321</v>
+        <v>5.55</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,55 +1560,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-282000</v>
+        <v>2691884</v>
       </c>
       <c r="M10" t="n">
-        <v>400619</v>
+        <v>26374815</v>
       </c>
       <c r="N10" t="n">
-        <v>14817402</v>
+        <v>42618602</v>
       </c>
       <c r="O10" t="n">
-        <v>12471153</v>
+        <v>41909180</v>
       </c>
       <c r="P10" t="n">
-        <v>-441000</v>
+        <v>348000</v>
       </c>
       <c r="Q10" t="n">
-        <v>-897406</v>
+        <v>16153900</v>
       </c>
       <c r="R10" t="n">
-        <v>10580710</v>
+        <v>32270600</v>
       </c>
       <c r="S10" t="n">
-        <v>9641815</v>
+        <v>31915600</v>
       </c>
       <c r="T10" t="n">
-        <v>128000</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1415000</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3320000</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>4122277</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>31000</v>
+        <v>2343884</v>
       </c>
       <c r="Y10" t="n">
-        <v>-116975</v>
+        <v>10220915</v>
       </c>
       <c r="Z10" t="n">
-        <v>916692</v>
+        <v>10348002</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1292939</v>
+        <v>9993580</v>
       </c>
       <c r="AB10" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.16</v>
+        <v>336</v>
       </c>
       <c r="D11" t="n">
-        <v>6.81</v>
+        <v>322.7</v>
       </c>
       <c r="E11" t="n">
-        <v>6.24</v>
+        <v>321.6</v>
       </c>
       <c r="F11" t="n">
-        <v>6.03</v>
+        <v>308.7</v>
       </c>
       <c r="G11" t="n">
-        <v>36791094</v>
+        <v>11025246</v>
       </c>
       <c r="H11" t="n">
-        <v>51399518</v>
+        <v>14171546</v>
       </c>
       <c r="I11" t="n">
-        <v>8.16</v>
+        <v>351</v>
       </c>
       <c r="J11" t="n">
-        <v>5.55</v>
+        <v>270.5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-249000</v>
+        <v>1049326</v>
       </c>
       <c r="M11" t="n">
-        <v>5235922</v>
+        <v>3162148</v>
       </c>
       <c r="N11" t="n">
-        <v>22920506</v>
+        <v>696962</v>
       </c>
       <c r="O11" t="n">
-        <v>27546408</v>
+        <v>233231</v>
       </c>
       <c r="P11" t="n">
-        <v>-249000</v>
+        <v>1140069</v>
       </c>
       <c r="Q11" t="n">
-        <v>-170000</v>
+        <v>2664109</v>
       </c>
       <c r="R11" t="n">
-        <v>17295700</v>
+        <v>170420</v>
       </c>
       <c r="S11" t="n">
-        <v>22198700</v>
+        <v>-2730714</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>489921</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>633921</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3920789</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-80743</v>
       </c>
       <c r="Y11" t="n">
-        <v>5405922</v>
+        <v>8118</v>
       </c>
       <c r="Z11" t="n">
-        <v>5624806</v>
+        <v>-107379</v>
       </c>
       <c r="AA11" t="n">
-        <v>5347708</v>
+        <v>-956844</v>
       </c>
       <c r="AB11" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,54 +1739,54 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>72.2</v>
       </c>
       <c r="D12" t="n">
-        <v>21.51</v>
+        <v>69.12</v>
       </c>
       <c r="E12" t="n">
-        <v>20.48</v>
+        <v>67.56</v>
       </c>
       <c r="F12" t="n">
-        <v>19.25</v>
+        <v>68.52</v>
       </c>
       <c r="G12" t="n">
-        <v>818361725</v>
+        <v>337055872</v>
       </c>
       <c r="H12" t="n">
-        <v>356215638</v>
+        <v>147844553</v>
       </c>
       <c r="I12" t="n">
-        <v>25.8</v>
+        <v>81.2</v>
       </c>
       <c r="J12" t="n">
-        <v>16.6</v>
+        <v>61.8</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,55 +1794,55 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-5515203</v>
+        <v>4624379</v>
       </c>
       <c r="M12" t="n">
-        <v>7917517</v>
+        <v>86624549</v>
       </c>
       <c r="N12" t="n">
-        <v>161647079</v>
+        <v>82459143</v>
       </c>
       <c r="O12" t="n">
-        <v>120738088</v>
+        <v>24752731</v>
       </c>
       <c r="P12" t="n">
-        <v>-6347203</v>
+        <v>3107525</v>
       </c>
       <c r="Q12" t="n">
-        <v>5167481</v>
+        <v>82352666</v>
       </c>
       <c r="R12" t="n">
-        <v>155789836</v>
+        <v>76543284</v>
       </c>
       <c r="S12" t="n">
-        <v>130583792</v>
+        <v>22368852</v>
       </c>
       <c r="T12" t="n">
-        <v>754000</v>
+        <v>762000</v>
       </c>
       <c r="U12" t="n">
-        <v>1508000</v>
+        <v>784000</v>
       </c>
       <c r="V12" t="n">
-        <v>2308000</v>
+        <v>805000</v>
       </c>
       <c r="W12" t="n">
-        <v>2256001</v>
+        <v>798000</v>
       </c>
       <c r="X12" t="n">
-        <v>78000</v>
+        <v>754854</v>
       </c>
       <c r="Y12" t="n">
-        <v>1242036</v>
+        <v>3487883</v>
       </c>
       <c r="Z12" t="n">
-        <v>3549243</v>
+        <v>5110859</v>
       </c>
       <c r="AA12" t="n">
-        <v>-12101705</v>
+        <v>1585879</v>
       </c>
       <c r="AB12" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,54 +1856,54 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>248</v>
+        <v>533</v>
       </c>
       <c r="D13" t="n">
-        <v>251.3</v>
+        <v>511.6</v>
       </c>
       <c r="E13" t="n">
-        <v>235.75</v>
+        <v>468.75</v>
       </c>
       <c r="F13" t="n">
-        <v>221.18</v>
+        <v>448.2</v>
       </c>
       <c r="G13" t="n">
-        <v>131044723</v>
+        <v>2520000</v>
       </c>
       <c r="H13" t="n">
-        <v>130303090</v>
+        <v>4413800</v>
       </c>
       <c r="I13" t="n">
-        <v>272.5</v>
+        <v>558</v>
       </c>
       <c r="J13" t="n">
-        <v>183</v>
+        <v>340</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2017000</v>
+        <v>755377</v>
       </c>
       <c r="M13" t="n">
-        <v>15243773</v>
+        <v>2856804</v>
       </c>
       <c r="N13" t="n">
-        <v>17228813</v>
+        <v>9398836</v>
       </c>
       <c r="O13" t="n">
-        <v>31539180</v>
+        <v>7366124</v>
       </c>
       <c r="P13" t="n">
-        <v>1367000</v>
+        <v>737962</v>
       </c>
       <c r="Q13" t="n">
-        <v>12340014</v>
+        <v>2860498</v>
       </c>
       <c r="R13" t="n">
-        <v>13030797</v>
+        <v>8822301</v>
       </c>
       <c r="S13" t="n">
-        <v>26323861</v>
+        <v>10989591</v>
       </c>
       <c r="T13" t="n">
-        <v>179000</v>
+        <v>-1200</v>
       </c>
       <c r="U13" t="n">
-        <v>1198000</v>
+        <v>35400</v>
       </c>
       <c r="V13" t="n">
-        <v>964000</v>
+        <v>89400</v>
       </c>
       <c r="W13" t="n">
-        <v>4061000</v>
+        <v>-1897400</v>
       </c>
       <c r="X13" t="n">
-        <v>471000</v>
+        <v>18615</v>
       </c>
       <c r="Y13" t="n">
-        <v>1705759</v>
+        <v>-39094</v>
       </c>
       <c r="Z13" t="n">
-        <v>3234016</v>
+        <v>487135</v>
       </c>
       <c r="AA13" t="n">
-        <v>1154319</v>
+        <v>-1726067</v>
       </c>
       <c r="AB13" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -1983,100 +1983,100 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>533</v>
+        <v>13.65</v>
       </c>
       <c r="D14" t="n">
-        <v>511.6</v>
+        <v>11.83</v>
       </c>
       <c r="E14" t="n">
-        <v>468.75</v>
+        <v>11.16</v>
       </c>
       <c r="F14" t="n">
-        <v>448.2</v>
+        <v>10.02</v>
       </c>
       <c r="G14" t="n">
-        <v>2520000</v>
+        <v>478320069</v>
       </c>
       <c r="H14" t="n">
-        <v>4413800</v>
+        <v>148294428</v>
       </c>
       <c r="I14" t="n">
-        <v>558</v>
+        <v>14.3</v>
       </c>
       <c r="J14" t="n">
-        <v>340</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-38167602</v>
       </c>
       <c r="M14" t="n">
-        <v>1189791</v>
+        <v>-10752553</v>
       </c>
       <c r="N14" t="n">
-        <v>5055165</v>
+        <v>18165967</v>
       </c>
       <c r="O14" t="n">
-        <v>8904823</v>
+        <v>-4180170</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-34299664</v>
       </c>
       <c r="Q14" t="n">
-        <v>1260281</v>
+        <v>-9283197</v>
       </c>
       <c r="R14" t="n">
-        <v>4827711</v>
+        <v>19188803</v>
       </c>
       <c r="S14" t="n">
-        <v>11582504</v>
+        <v>-1504190</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>39800</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>35400</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-1943400</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-3867938</v>
       </c>
       <c r="Y14" t="n">
-        <v>-110290</v>
+        <v>-1469356</v>
       </c>
       <c r="Z14" t="n">
-        <v>192054</v>
+        <v>-1022836</v>
       </c>
       <c r="AA14" t="n">
-        <v>-734281</v>
+        <v>-2675980</v>
       </c>
       <c r="AB14" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2090,110 +2090,110 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>45.7</v>
+        <v>48.32</v>
       </c>
       <c r="D15" t="n">
-        <v>43.4</v>
+        <v>46.5</v>
       </c>
       <c r="E15" t="n">
-        <v>40.22</v>
+        <v>45.58</v>
       </c>
       <c r="F15" t="n">
-        <v>34.08</v>
+        <v>44.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1463227218</v>
+        <v>49374408</v>
       </c>
       <c r="H15" t="n">
-        <v>613882104</v>
+        <v>49915897</v>
       </c>
       <c r="I15" t="n">
-        <v>52.2</v>
+        <v>48.79</v>
       </c>
       <c r="J15" t="n">
-        <v>23.65</v>
+        <v>40.71</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-5110089</v>
+        <v>10242115</v>
       </c>
       <c r="M15" t="n">
-        <v>-12884905</v>
+        <v>77728874</v>
       </c>
       <c r="N15" t="n">
-        <v>91189745</v>
+        <v>117379555</v>
       </c>
       <c r="O15" t="n">
-        <v>-49504225</v>
+        <v>159869366</v>
       </c>
       <c r="P15" t="n">
-        <v>-5330089</v>
+        <v>4033935</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14693634</v>
+        <v>40220145</v>
       </c>
       <c r="R15" t="n">
-        <v>78065226</v>
+        <v>57276746</v>
       </c>
       <c r="S15" t="n">
-        <v>-50153632</v>
+        <v>51434271</v>
       </c>
       <c r="T15" t="n">
-        <v>424000</v>
+        <v>-240000</v>
       </c>
       <c r="U15" t="n">
-        <v>848000</v>
+        <v>-240000</v>
       </c>
       <c r="V15" t="n">
-        <v>1233000</v>
+        <v>-340000</v>
       </c>
       <c r="W15" t="n">
-        <v>944678</v>
+        <v>1270000</v>
       </c>
       <c r="X15" t="n">
-        <v>-204000</v>
+        <v>6448180</v>
       </c>
       <c r="Y15" t="n">
-        <v>960729</v>
+        <v>37748729</v>
       </c>
       <c r="Z15" t="n">
-        <v>11891519</v>
+        <v>60442809</v>
       </c>
       <c r="AA15" t="n">
-        <v>-295271</v>
+        <v>107165095</v>
       </c>
       <c r="AB15" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -2207,54 +2207,54 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1085</v>
+        <v>259</v>
       </c>
       <c r="D16" t="n">
-        <v>954.6</v>
+        <v>251.5</v>
       </c>
       <c r="E16" t="n">
-        <v>900.1</v>
+        <v>249.5</v>
       </c>
       <c r="F16" t="n">
-        <v>881.7</v>
+        <v>244.47</v>
       </c>
       <c r="G16" t="n">
-        <v>34270461</v>
+        <v>55665305</v>
       </c>
       <c r="H16" t="n">
-        <v>30958709</v>
+        <v>69819957</v>
       </c>
       <c r="I16" t="n">
-        <v>1085</v>
+        <v>263.5</v>
       </c>
       <c r="J16" t="n">
-        <v>776</v>
+        <v>219.5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,55 +2262,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-2521000</v>
+        <v>8357718</v>
       </c>
       <c r="M16" t="n">
-        <v>-3850707</v>
+        <v>85176383</v>
       </c>
       <c r="N16" t="n">
-        <v>1986755</v>
+        <v>90759559</v>
       </c>
       <c r="O16" t="n">
-        <v>-4361730</v>
+        <v>147431875</v>
       </c>
       <c r="P16" t="n">
-        <v>-3327000</v>
+        <v>9279594</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4879031</v>
+        <v>82146523</v>
       </c>
       <c r="R16" t="n">
-        <v>-1386350</v>
+        <v>93430042</v>
       </c>
       <c r="S16" t="n">
-        <v>-11378514</v>
+        <v>159160299</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-245930</v>
       </c>
       <c r="U16" t="n">
-        <v>-450000</v>
+        <v>881443</v>
       </c>
       <c r="V16" t="n">
-        <v>-39900</v>
+        <v>-1608417</v>
       </c>
       <c r="W16" t="n">
-        <v>3133762</v>
+        <v>-8405701</v>
       </c>
       <c r="X16" t="n">
-        <v>806000</v>
+        <v>-675946</v>
       </c>
       <c r="Y16" t="n">
-        <v>1478324</v>
+        <v>2148417</v>
       </c>
       <c r="Z16" t="n">
-        <v>3413005</v>
+        <v>-1062066</v>
       </c>
       <c r="AA16" t="n">
-        <v>3883022</v>
+        <v>-3322723</v>
       </c>
       <c r="AB16" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2324,54 +2324,54 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步賣超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、5日法人明顯買超、外資投信同步賣超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>48.32</v>
+        <v>130.5</v>
       </c>
       <c r="D17" t="n">
-        <v>46.5</v>
+        <v>118.7</v>
       </c>
       <c r="E17" t="n">
-        <v>45.58</v>
+        <v>113.39</v>
       </c>
       <c r="F17" t="n">
-        <v>43.92</v>
+        <v>100.19</v>
       </c>
       <c r="G17" t="n">
-        <v>49374408</v>
+        <v>291896012</v>
       </c>
       <c r="H17" t="n">
-        <v>49915897</v>
+        <v>252641517</v>
       </c>
       <c r="I17" t="n">
-        <v>48.79</v>
+        <v>133.5</v>
       </c>
       <c r="J17" t="n">
-        <v>37.05</v>
+        <v>71.3</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-259000</v>
+        <v>52531260</v>
       </c>
       <c r="M17" t="n">
-        <v>31868141</v>
+        <v>30902532</v>
       </c>
       <c r="N17" t="n">
-        <v>63466447</v>
+        <v>13031123</v>
       </c>
       <c r="O17" t="n">
-        <v>87670270</v>
+        <v>51942046</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>71870498</v>
       </c>
       <c r="Q17" t="n">
-        <v>25778945</v>
+        <v>90044068</v>
       </c>
       <c r="R17" t="n">
-        <v>35876034</v>
+        <v>78707028</v>
       </c>
       <c r="S17" t="n">
-        <v>44516303</v>
+        <v>9215401</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-19692021</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-65983172</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-70677271</v>
       </c>
       <c r="W17" t="n">
-        <v>280000</v>
+        <v>45097665</v>
       </c>
       <c r="X17" t="n">
-        <v>-259000</v>
+        <v>352783</v>
       </c>
       <c r="Y17" t="n">
-        <v>6089196</v>
+        <v>6841636</v>
       </c>
       <c r="Z17" t="n">
-        <v>27590413</v>
+        <v>5001366</v>
       </c>
       <c r="AA17" t="n">
-        <v>42873967</v>
+        <v>-2371020</v>
       </c>
       <c r="AB17" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2441,54 +2441,54 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>259</v>
+        <v>52</v>
       </c>
       <c r="D18" t="n">
-        <v>251.5</v>
+        <v>51.64</v>
       </c>
       <c r="E18" t="n">
-        <v>249.5</v>
+        <v>50.21</v>
       </c>
       <c r="F18" t="n">
-        <v>244.47</v>
+        <v>50.11</v>
       </c>
       <c r="G18" t="n">
-        <v>55665305</v>
+        <v>14910096</v>
       </c>
       <c r="H18" t="n">
-        <v>69819957</v>
+        <v>26622786</v>
       </c>
       <c r="I18" t="n">
-        <v>263.5</v>
+        <v>53.9</v>
       </c>
       <c r="J18" t="n">
-        <v>219.5</v>
+        <v>47.35</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2496,55 +2496,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-2503792</v>
+        <v>3310380</v>
       </c>
       <c r="M18" t="n">
-        <v>50779728</v>
+        <v>13160114</v>
       </c>
       <c r="N18" t="n">
-        <v>73148250</v>
+        <v>22308713</v>
       </c>
       <c r="O18" t="n">
-        <v>75733410</v>
+        <v>5831665</v>
       </c>
       <c r="P18" t="n">
-        <v>-1914792</v>
+        <v>3325023</v>
       </c>
       <c r="Q18" t="n">
-        <v>48222621</v>
+        <v>13482345</v>
       </c>
       <c r="R18" t="n">
-        <v>70351115</v>
+        <v>22552122</v>
       </c>
       <c r="S18" t="n">
-        <v>96895915</v>
+        <v>6675240</v>
       </c>
       <c r="T18" t="n">
-        <v>-376000</v>
+        <v>-17850</v>
       </c>
       <c r="U18" t="n">
-        <v>460000</v>
+        <v>-20816</v>
       </c>
       <c r="V18" t="n">
-        <v>-79000</v>
+        <v>-81816</v>
       </c>
       <c r="W18" t="n">
-        <v>-3081338</v>
+        <v>-354294</v>
       </c>
       <c r="X18" t="n">
-        <v>-213000</v>
+        <v>3207</v>
       </c>
       <c r="Y18" t="n">
-        <v>2097107</v>
+        <v>-301415</v>
       </c>
       <c r="Z18" t="n">
-        <v>2876135</v>
+        <v>-161593</v>
       </c>
       <c r="AA18" t="n">
-        <v>-18081167</v>
+        <v>-489281</v>
       </c>
       <c r="AB18" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2558,110 +2558,110 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2350</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>2136</v>
+        <v>21.51</v>
       </c>
       <c r="E19" t="n">
-        <v>2101</v>
+        <v>20.48</v>
       </c>
       <c r="F19" t="n">
-        <v>2045</v>
+        <v>19.25</v>
       </c>
       <c r="G19" t="n">
-        <v>12198582</v>
+        <v>818361725</v>
       </c>
       <c r="H19" t="n">
-        <v>11067330</v>
+        <v>356215638</v>
       </c>
       <c r="I19" t="n">
-        <v>2410</v>
+        <v>25.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1365</v>
+        <v>16.6</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1206259</v>
+        <v>-169469205</v>
       </c>
       <c r="M19" t="n">
-        <v>2505038</v>
+        <v>-117109516</v>
       </c>
       <c r="N19" t="n">
-        <v>1839585</v>
+        <v>23750704</v>
       </c>
       <c r="O19" t="n">
-        <v>-2314653</v>
+        <v>64693465</v>
       </c>
       <c r="P19" t="n">
-        <v>-1207259</v>
+        <v>-166129539</v>
       </c>
       <c r="Q19" t="n">
-        <v>1915878</v>
+        <v>-120015118</v>
       </c>
       <c r="R19" t="n">
-        <v>563005</v>
+        <v>20137674</v>
       </c>
       <c r="S19" t="n">
-        <v>146862</v>
+        <v>70298902</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>121946</v>
       </c>
       <c r="U19" t="n">
-        <v>202500</v>
+        <v>100709</v>
       </c>
       <c r="V19" t="n">
-        <v>-50791</v>
+        <v>141311</v>
       </c>
       <c r="W19" t="n">
-        <v>-1668702</v>
+        <v>119654</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>-3461612</v>
       </c>
       <c r="Y19" t="n">
-        <v>386660</v>
+        <v>2804893</v>
       </c>
       <c r="Z19" t="n">
-        <v>1327371</v>
+        <v>3471719</v>
       </c>
       <c r="AA19" t="n">
-        <v>-792813</v>
+        <v>-5725091</v>
       </c>
       <c r="AB19" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,54 +2675,54 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>130.5</v>
+        <v>208</v>
       </c>
       <c r="D20" t="n">
-        <v>118.7</v>
+        <v>207</v>
       </c>
       <c r="E20" t="n">
-        <v>113.39</v>
+        <v>199.9</v>
       </c>
       <c r="F20" t="n">
-        <v>100.19</v>
+        <v>190.12</v>
       </c>
       <c r="G20" t="n">
-        <v>291896012</v>
+        <v>20600438</v>
       </c>
       <c r="H20" t="n">
-        <v>252641517</v>
+        <v>22454689</v>
       </c>
       <c r="I20" t="n">
-        <v>133.5</v>
+        <v>231</v>
       </c>
       <c r="J20" t="n">
-        <v>71.3</v>
+        <v>167</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,55 +2730,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-8985000</v>
+        <v>-3468634</v>
       </c>
       <c r="M20" t="n">
-        <v>14866623</v>
+        <v>-5795592</v>
       </c>
       <c r="N20" t="n">
-        <v>25531286</v>
+        <v>3454457</v>
       </c>
       <c r="O20" t="n">
-        <v>37917795</v>
+        <v>-2253419</v>
       </c>
       <c r="P20" t="n">
-        <v>-8342000</v>
+        <v>-2743550</v>
       </c>
       <c r="Q20" t="n">
-        <v>31835878</v>
+        <v>-5212303</v>
       </c>
       <c r="R20" t="n">
-        <v>67282245</v>
+        <v>2840720</v>
       </c>
       <c r="S20" t="n">
-        <v>108988</v>
+        <v>-2007726</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-21406000</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-47366000</v>
+        <v>5000</v>
       </c>
       <c r="W20" t="n">
-        <v>39084182</v>
+        <v>-55923</v>
       </c>
       <c r="X20" t="n">
-        <v>-643000</v>
+        <v>-725084</v>
       </c>
       <c r="Y20" t="n">
-        <v>4436745</v>
+        <v>-583289</v>
       </c>
       <c r="Z20" t="n">
-        <v>5615041</v>
+        <v>608737</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1275375</v>
+        <v>-189770</v>
       </c>
       <c r="AB20" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -2792,54 +2792,54 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.4</v>
+        <v>2350</v>
       </c>
       <c r="D21" t="n">
-        <v>53.91</v>
+        <v>2136</v>
       </c>
       <c r="E21" t="n">
-        <v>51.25</v>
+        <v>2101</v>
       </c>
       <c r="F21" t="n">
-        <v>50.42</v>
+        <v>2149</v>
       </c>
       <c r="G21" t="n">
-        <v>15723414</v>
+        <v>12198582</v>
       </c>
       <c r="H21" t="n">
-        <v>11255762</v>
+        <v>11067330</v>
       </c>
       <c r="I21" t="n">
-        <v>60.3</v>
+        <v>2410</v>
       </c>
       <c r="J21" t="n">
-        <v>45.45</v>
+        <v>1880</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,55 +2847,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-125000</v>
+        <v>2566512</v>
       </c>
       <c r="M21" t="n">
-        <v>3204745</v>
+        <v>7299633</v>
       </c>
       <c r="N21" t="n">
-        <v>8745358</v>
+        <v>6859678</v>
       </c>
       <c r="O21" t="n">
-        <v>9280503</v>
+        <v>2778375</v>
       </c>
       <c r="P21" t="n">
-        <v>-124000</v>
+        <v>2327539</v>
       </c>
       <c r="Q21" t="n">
-        <v>2752020</v>
+        <v>6536197</v>
       </c>
       <c r="R21" t="n">
-        <v>8194020</v>
+        <v>6492434</v>
       </c>
       <c r="S21" t="n">
-        <v>8637435</v>
+        <v>6207419</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>160900</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>251932</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1011559</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-2905969</v>
       </c>
       <c r="X21" t="n">
-        <v>-1000</v>
+        <v>78073</v>
       </c>
       <c r="Y21" t="n">
-        <v>452725</v>
+        <v>511504</v>
       </c>
       <c r="Z21" t="n">
-        <v>551338</v>
+        <v>1378803</v>
       </c>
       <c r="AA21" t="n">
-        <v>643068</v>
+        <v>-523075</v>
       </c>
       <c r="AB21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -2909,54 +2909,54 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35.2</v>
+        <v>55.4</v>
       </c>
       <c r="D22" t="n">
-        <v>35.15</v>
+        <v>53.91</v>
       </c>
       <c r="E22" t="n">
-        <v>34.84</v>
+        <v>51.25</v>
       </c>
       <c r="F22" t="n">
-        <v>34.65</v>
+        <v>50.42</v>
       </c>
       <c r="G22" t="n">
-        <v>66828833</v>
+        <v>15723414</v>
       </c>
       <c r="H22" t="n">
-        <v>50399647</v>
+        <v>11255762</v>
       </c>
       <c r="I22" t="n">
-        <v>36.2</v>
+        <v>60.3</v>
       </c>
       <c r="J22" t="n">
-        <v>33.25</v>
+        <v>45.45</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,52 +2964,52 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2059000</v>
+        <v>-56389</v>
       </c>
       <c r="M22" t="n">
-        <v>-3241213</v>
+        <v>7287407</v>
       </c>
       <c r="N22" t="n">
-        <v>11940050</v>
+        <v>13802670</v>
       </c>
       <c r="O22" t="n">
-        <v>905035</v>
+        <v>11995532</v>
       </c>
       <c r="P22" t="n">
-        <v>2065000</v>
+        <v>-10151</v>
       </c>
       <c r="Q22" t="n">
-        <v>-13005700</v>
+        <v>6747298</v>
       </c>
       <c r="R22" t="n">
-        <v>-9403814</v>
+        <v>12995298</v>
       </c>
       <c r="S22" t="n">
-        <v>-18095890</v>
+        <v>11249963</v>
       </c>
       <c r="T22" t="n">
-        <v>-59000</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>9147670</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>20948228</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>17091835</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>53000</v>
+        <v>-46238</v>
       </c>
       <c r="Y22" t="n">
-        <v>616817</v>
+        <v>540109</v>
       </c>
       <c r="Z22" t="n">
-        <v>395636</v>
+        <v>807372</v>
       </c>
       <c r="AA22" t="n">
-        <v>1909090</v>
+        <v>745569</v>
       </c>
       <c r="AB22" t="n">
         <v>85</v>
@@ -3031,49 +3031,49 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>41.35</v>
+        <v>5290</v>
       </c>
       <c r="D23" t="n">
-        <v>42.12</v>
+        <v>4977</v>
       </c>
       <c r="E23" t="n">
-        <v>40.77</v>
+        <v>4843</v>
       </c>
       <c r="F23" t="n">
-        <v>39.71</v>
+        <v>4784.25</v>
       </c>
       <c r="G23" t="n">
-        <v>37127594</v>
+        <v>2917258</v>
       </c>
       <c r="H23" t="n">
-        <v>36197186</v>
+        <v>2443800</v>
       </c>
       <c r="I23" t="n">
-        <v>44.75</v>
+        <v>5635</v>
       </c>
       <c r="J23" t="n">
-        <v>36.6</v>
+        <v>4160</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,55 +3081,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>27000</v>
+        <v>-205121</v>
       </c>
       <c r="M23" t="n">
-        <v>12175610</v>
+        <v>659036</v>
       </c>
       <c r="N23" t="n">
-        <v>26928474</v>
+        <v>1183968</v>
       </c>
       <c r="O23" t="n">
-        <v>107891418</v>
+        <v>2104114</v>
       </c>
       <c r="P23" t="n">
-        <v>299000</v>
+        <v>-69967</v>
       </c>
       <c r="Q23" t="n">
-        <v>12590135</v>
+        <v>517687</v>
       </c>
       <c r="R23" t="n">
-        <v>27773538</v>
+        <v>1437059</v>
       </c>
       <c r="S23" t="n">
-        <v>113450279</v>
+        <v>2384479</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-67986</v>
       </c>
       <c r="U23" t="n">
-        <v>-620000</v>
+        <v>151848</v>
       </c>
       <c r="V23" t="n">
-        <v>-943000</v>
+        <v>-132639</v>
       </c>
       <c r="W23" t="n">
-        <v>-4979000</v>
+        <v>-81804</v>
       </c>
       <c r="X23" t="n">
-        <v>-272000</v>
+        <v>-67168</v>
       </c>
       <c r="Y23" t="n">
-        <v>205475</v>
+        <v>-10499</v>
       </c>
       <c r="Z23" t="n">
-        <v>97936</v>
+        <v>-120452</v>
       </c>
       <c r="AA23" t="n">
-        <v>-579861</v>
+        <v>-198561</v>
       </c>
       <c r="AB23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>強勢偏多：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -3198,55 +3198,55 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-1946064</v>
       </c>
       <c r="M24" t="n">
-        <v>-1946569</v>
+        <v>81869</v>
       </c>
       <c r="N24" t="n">
-        <v>424126</v>
+        <v>2179097</v>
       </c>
       <c r="O24" t="n">
-        <v>-5704334</v>
+        <v>-9008726</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-1468340</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3417636</v>
+        <v>-1906274</v>
       </c>
       <c r="R24" t="n">
-        <v>-889810</v>
+        <v>-224958</v>
       </c>
       <c r="S24" t="n">
-        <v>-7908244</v>
+        <v>-14271976</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-42806</v>
       </c>
       <c r="U24" t="n">
-        <v>1131000</v>
+        <v>2336877</v>
       </c>
       <c r="V24" t="n">
-        <v>1108000</v>
+        <v>3001877</v>
       </c>
       <c r="W24" t="n">
-        <v>2121901</v>
+        <v>6006195</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-434918</v>
       </c>
       <c r="Y24" t="n">
-        <v>340067</v>
+        <v>-348734</v>
       </c>
       <c r="Z24" t="n">
-        <v>205936</v>
+        <v>-597822</v>
       </c>
       <c r="AA24" t="n">
-        <v>82009</v>
+        <v>-742945</v>
       </c>
       <c r="AB24" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -3265,12 +3265,12 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>5日法人買超、投信買外資賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -3315,28 +3315,28 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-45000</v>
+        <v>-2446750</v>
       </c>
       <c r="M25" t="n">
-        <v>-581799</v>
+        <v>3766968</v>
       </c>
       <c r="N25" t="n">
-        <v>265590</v>
+        <v>4738685</v>
       </c>
       <c r="O25" t="n">
-        <v>4734573</v>
+        <v>2727602</v>
       </c>
       <c r="P25" t="n">
-        <v>-44000</v>
+        <v>-2360206</v>
       </c>
       <c r="Q25" t="n">
-        <v>-441520</v>
+        <v>3555724</v>
       </c>
       <c r="R25" t="n">
-        <v>456155</v>
+        <v>4717542</v>
       </c>
       <c r="S25" t="n">
-        <v>4667108</v>
+        <v>3116204</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3348,22 +3348,22 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="X25" t="n">
-        <v>-1000</v>
+        <v>-86544</v>
       </c>
       <c r="Y25" t="n">
-        <v>-140279</v>
+        <v>211244</v>
       </c>
       <c r="Z25" t="n">
-        <v>-190565</v>
+        <v>21143</v>
       </c>
       <c r="AA25" t="n">
-        <v>69465</v>
+        <v>-380602</v>
       </c>
       <c r="AB25" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -3382,102 +3382,102 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1580</v>
+        <v>284.5</v>
       </c>
       <c r="D26" t="n">
-        <v>1433</v>
+        <v>274.8</v>
       </c>
       <c r="E26" t="n">
-        <v>1385.5</v>
+        <v>260.7</v>
       </c>
       <c r="F26" t="n">
-        <v>1308.55</v>
+        <v>255.95</v>
       </c>
       <c r="G26" t="n">
-        <v>9546000</v>
+        <v>88509083</v>
       </c>
       <c r="H26" t="n">
-        <v>3017800</v>
+        <v>89776777</v>
       </c>
       <c r="I26" t="n">
-        <v>1700</v>
+        <v>305.5</v>
       </c>
       <c r="J26" t="n">
-        <v>941</v>
+        <v>227.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>-17576165</v>
       </c>
       <c r="M26" t="n">
-        <v>198709</v>
+        <v>25069607</v>
       </c>
       <c r="N26" t="n">
-        <v>885708</v>
+        <v>19890503</v>
       </c>
       <c r="O26" t="n">
-        <v>1548637</v>
+        <v>3740322</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-13228850</v>
       </c>
       <c r="Q26" t="n">
-        <v>-910598</v>
+        <v>25462512</v>
       </c>
       <c r="R26" t="n">
-        <v>-196691</v>
+        <v>21413015</v>
       </c>
       <c r="S26" t="n">
-        <v>1041700</v>
+        <v>4280144</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>-3381000</v>
       </c>
       <c r="U26" t="n">
-        <v>1445000</v>
+        <v>-2422000</v>
       </c>
       <c r="V26" t="n">
-        <v>1410700</v>
+        <v>-2684000</v>
       </c>
       <c r="W26" t="n">
-        <v>422100</v>
+        <v>1997000</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-966315</v>
       </c>
       <c r="Y26" t="n">
-        <v>-335693</v>
+        <v>2029095</v>
       </c>
       <c r="Z26" t="n">
-        <v>-328301</v>
+        <v>1161488</v>
       </c>
       <c r="AA26" t="n">
-        <v>84837</v>
+        <v>-2536822</v>
       </c>
       <c r="AB26" t="n">
         <v>75</v>
@@ -3494,107 +3494,107 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>52</v>
+        <v>1580</v>
       </c>
       <c r="D27" t="n">
-        <v>51.64</v>
+        <v>1433</v>
       </c>
       <c r="E27" t="n">
-        <v>50.21</v>
+        <v>1385.5</v>
       </c>
       <c r="F27" t="n">
-        <v>50.11</v>
+        <v>1308.55</v>
       </c>
       <c r="G27" t="n">
-        <v>14910096</v>
+        <v>9546000</v>
       </c>
       <c r="H27" t="n">
-        <v>26622786</v>
+        <v>3017800</v>
       </c>
       <c r="I27" t="n">
-        <v>53.9</v>
+        <v>1700</v>
       </c>
       <c r="J27" t="n">
-        <v>47.35</v>
+        <v>941</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-532000</v>
+        <v>-83545</v>
       </c>
       <c r="M27" t="n">
-        <v>-8902235</v>
+        <v>660709</v>
       </c>
       <c r="N27" t="n">
-        <v>1733803</v>
+        <v>848398</v>
       </c>
       <c r="O27" t="n">
-        <v>-13038195</v>
+        <v>2026953</v>
       </c>
       <c r="P27" t="n">
-        <v>-482000</v>
+        <v>-1100380</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7779291</v>
+        <v>-461658</v>
       </c>
       <c r="R27" t="n">
-        <v>2700889</v>
+        <v>-27799</v>
       </c>
       <c r="S27" t="n">
-        <v>-11158828</v>
+        <v>1154682</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1406000</v>
       </c>
       <c r="U27" t="n">
-        <v>24000</v>
+        <v>1457700</v>
       </c>
       <c r="V27" t="n">
-        <v>-15000</v>
+        <v>1445700</v>
       </c>
       <c r="W27" t="n">
-        <v>-308478</v>
+        <v>427100</v>
       </c>
       <c r="X27" t="n">
-        <v>-50000</v>
+        <v>-389165</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1146944</v>
+        <v>-335333</v>
       </c>
       <c r="Z27" t="n">
-        <v>-952086</v>
+        <v>-569503</v>
       </c>
       <c r="AA27" t="n">
-        <v>-1570889</v>
+        <v>445171</v>
       </c>
       <c r="AB27" t="n">
         <v>75</v>
@@ -3611,171 +3611,171 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4265</v>
+        <v>540</v>
       </c>
       <c r="D28" t="n">
-        <v>3830</v>
+        <v>498.7</v>
       </c>
       <c r="E28" t="n">
-        <v>3586.5</v>
+        <v>457.05</v>
       </c>
       <c r="F28" t="n">
-        <v>3387.5</v>
+        <v>434.32</v>
       </c>
       <c r="G28" t="n">
-        <v>19540872</v>
+        <v>41904053</v>
       </c>
       <c r="H28" t="n">
-        <v>12055166</v>
+        <v>51443369</v>
       </c>
       <c r="I28" t="n">
-        <v>4440</v>
+        <v>558</v>
       </c>
       <c r="J28" t="n">
-        <v>2485</v>
+        <v>354</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>293052</v>
+        <v>3665357</v>
       </c>
       <c r="M28" t="n">
-        <v>-1380273</v>
+        <v>-2295368</v>
       </c>
       <c r="N28" t="n">
-        <v>-1636442</v>
+        <v>12783506</v>
       </c>
       <c r="O28" t="n">
-        <v>-4694401</v>
+        <v>17733372</v>
       </c>
       <c r="P28" t="n">
-        <v>162052</v>
+        <v>3230273</v>
       </c>
       <c r="Q28" t="n">
-        <v>-850404</v>
+        <v>-7656559</v>
       </c>
       <c r="R28" t="n">
-        <v>-1119173</v>
+        <v>-2064736</v>
       </c>
       <c r="S28" t="n">
-        <v>-3218308</v>
+        <v>3089670</v>
       </c>
       <c r="T28" t="n">
-        <v>-129000</v>
+        <v>272000</v>
       </c>
       <c r="U28" t="n">
-        <v>-1219000</v>
+        <v>5359563</v>
       </c>
       <c r="V28" t="n">
-        <v>-1748000</v>
+        <v>14540563</v>
       </c>
       <c r="W28" t="n">
-        <v>-2439146</v>
+        <v>14286504</v>
       </c>
       <c r="X28" t="n">
-        <v>260000</v>
+        <v>163084</v>
       </c>
       <c r="Y28" t="n">
-        <v>689131</v>
+        <v>1628</v>
       </c>
       <c r="Z28" t="n">
-        <v>1230731</v>
+        <v>307679</v>
       </c>
       <c r="AA28" t="n">
-        <v>963053</v>
+        <v>357198</v>
       </c>
       <c r="AB28" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.65</v>
+        <v>661</v>
       </c>
       <c r="D29" t="n">
-        <v>27.96</v>
+        <v>614.6</v>
       </c>
       <c r="E29" t="n">
-        <v>27.3</v>
+        <v>540.85</v>
       </c>
       <c r="F29" t="n">
-        <v>25.02</v>
+        <v>448.73</v>
       </c>
       <c r="G29" t="n">
-        <v>52074412</v>
+        <v>29457930</v>
       </c>
       <c r="H29" t="n">
-        <v>88757521</v>
+        <v>56139070</v>
       </c>
       <c r="I29" t="n">
-        <v>31.9</v>
+        <v>691</v>
       </c>
       <c r="J29" t="n">
-        <v>21.6</v>
+        <v>307</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,79 +3783,79 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-559000</v>
+        <v>-2424120</v>
       </c>
       <c r="M29" t="n">
-        <v>9060504</v>
+        <v>3032718</v>
       </c>
       <c r="N29" t="n">
-        <v>53346382</v>
+        <v>2749960</v>
       </c>
       <c r="O29" t="n">
-        <v>50279477</v>
+        <v>16261311</v>
       </c>
       <c r="P29" t="n">
-        <v>-552000</v>
+        <v>-3752033</v>
       </c>
       <c r="Q29" t="n">
-        <v>10488375</v>
+        <v>-4747485</v>
       </c>
       <c r="R29" t="n">
-        <v>56496175</v>
+        <v>-15588469</v>
       </c>
       <c r="S29" t="n">
-        <v>54028264</v>
+        <v>-24755153</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>124208</v>
       </c>
       <c r="U29" t="n">
-        <v>-2772000</v>
+        <v>5196657</v>
       </c>
       <c r="V29" t="n">
-        <v>-5745000</v>
+        <v>15549336</v>
       </c>
       <c r="W29" t="n">
-        <v>-5745000</v>
+        <v>39670828</v>
       </c>
       <c r="X29" t="n">
-        <v>-7000</v>
+        <v>1203705</v>
       </c>
       <c r="Y29" t="n">
-        <v>1344129</v>
+        <v>2583546</v>
       </c>
       <c r="Z29" t="n">
-        <v>2595207</v>
+        <v>2789093</v>
       </c>
       <c r="AA29" t="n">
-        <v>1996213</v>
+        <v>1345636</v>
       </c>
       <c r="AB29" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -3900,64 +3900,64 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-5413302</v>
+        <v>-8248077</v>
       </c>
       <c r="M30" t="n">
-        <v>-2555015</v>
+        <v>479302</v>
       </c>
       <c r="N30" t="n">
-        <v>-6363482</v>
+        <v>-7470683</v>
       </c>
       <c r="O30" t="n">
-        <v>-19724620</v>
+        <v>-24896242</v>
       </c>
       <c r="P30" t="n">
-        <v>-5003302</v>
+        <v>-7748559</v>
       </c>
       <c r="Q30" t="n">
-        <v>-5961013</v>
+        <v>-2969994</v>
       </c>
       <c r="R30" t="n">
-        <v>-9949977</v>
+        <v>-12987121</v>
       </c>
       <c r="S30" t="n">
-        <v>-33301310</v>
+        <v>-54524902</v>
       </c>
       <c r="T30" t="n">
-        <v>-559000</v>
+        <v>-597289</v>
       </c>
       <c r="U30" t="n">
-        <v>3010500</v>
+        <v>3066363</v>
       </c>
       <c r="V30" t="n">
-        <v>2618500</v>
+        <v>5422008</v>
       </c>
       <c r="W30" t="n">
-        <v>20518260</v>
+        <v>30712204</v>
       </c>
       <c r="X30" t="n">
-        <v>149000</v>
+        <v>97771</v>
       </c>
       <c r="Y30" t="n">
-        <v>395498</v>
+        <v>382933</v>
       </c>
       <c r="Z30" t="n">
-        <v>967995</v>
+        <v>94430</v>
       </c>
       <c r="AA30" t="n">
-        <v>-6941570</v>
+        <v>-1083544</v>
       </c>
       <c r="AB30" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -3967,49 +3967,49 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1220</v>
+        <v>41.35</v>
       </c>
       <c r="D31" t="n">
-        <v>1114.4</v>
+        <v>42.12</v>
       </c>
       <c r="E31" t="n">
-        <v>1037.7</v>
+        <v>40.77</v>
       </c>
       <c r="F31" t="n">
-        <v>1072.35</v>
+        <v>39.71</v>
       </c>
       <c r="G31" t="n">
-        <v>4415000</v>
+        <v>37127594</v>
       </c>
       <c r="H31" t="n">
-        <v>3736800</v>
+        <v>36197186</v>
       </c>
       <c r="I31" t="n">
-        <v>1300</v>
+        <v>44.75</v>
       </c>
       <c r="J31" t="n">
-        <v>865</v>
+        <v>36.6</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,55 +4017,55 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>-8665361</v>
       </c>
       <c r="M31" t="n">
-        <v>-936110</v>
+        <v>5037507</v>
       </c>
       <c r="N31" t="n">
-        <v>-958914</v>
+        <v>39162139</v>
       </c>
       <c r="O31" t="n">
-        <v>-1688679</v>
+        <v>96951742</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>-7447878</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1253397</v>
+        <v>8643813</v>
       </c>
       <c r="R31" t="n">
-        <v>-2041124</v>
+        <v>44796984</v>
       </c>
       <c r="S31" t="n">
-        <v>-2328511</v>
+        <v>107321474</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-509000</v>
       </c>
       <c r="U31" t="n">
-        <v>441000</v>
+        <v>-1562000</v>
       </c>
       <c r="V31" t="n">
-        <v>1079000</v>
+        <v>-3204000</v>
       </c>
       <c r="W31" t="n">
-        <v>578000</v>
+        <v>-6573000</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>-708483</v>
       </c>
       <c r="Y31" t="n">
-        <v>-123713</v>
+        <v>-2044306</v>
       </c>
       <c r="Z31" t="n">
-        <v>3210</v>
+        <v>-2430845</v>
       </c>
       <c r="AA31" t="n">
-        <v>61832</v>
+        <v>-3796732</v>
       </c>
       <c r="AB31" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -4079,110 +4079,110 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>866</v>
+        <v>4265</v>
       </c>
       <c r="D32" t="n">
-        <v>742</v>
+        <v>3830</v>
       </c>
       <c r="E32" t="n">
-        <v>732.1</v>
+        <v>3586.5</v>
       </c>
       <c r="F32" t="n">
-        <v>711.25</v>
+        <v>3387.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2958000</v>
+        <v>19540872</v>
       </c>
       <c r="H32" t="n">
-        <v>4678000</v>
+        <v>12055166</v>
       </c>
       <c r="I32" t="n">
-        <v>866</v>
+        <v>4440</v>
       </c>
       <c r="J32" t="n">
-        <v>534</v>
+        <v>2485</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>976145</v>
       </c>
       <c r="M32" t="n">
-        <v>-803228</v>
+        <v>-571992</v>
       </c>
       <c r="N32" t="n">
-        <v>-3683174</v>
+        <v>-2678985</v>
       </c>
       <c r="O32" t="n">
-        <v>-5411546</v>
+        <v>-6602075</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1367297</v>
       </c>
       <c r="Q32" t="n">
-        <v>-992257</v>
+        <v>-1377565</v>
       </c>
       <c r="R32" t="n">
-        <v>-3758390</v>
+        <v>-3496640</v>
       </c>
       <c r="S32" t="n">
-        <v>-6279183</v>
+        <v>-5683390</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>-598432</v>
       </c>
       <c r="U32" t="n">
-        <v>-155038</v>
+        <v>-22871</v>
       </c>
       <c r="V32" t="n">
-        <v>-975650</v>
+        <v>-448869</v>
       </c>
       <c r="W32" t="n">
-        <v>-361372</v>
+        <v>-1698175</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>207280</v>
       </c>
       <c r="Y32" t="n">
-        <v>344067</v>
+        <v>828444</v>
       </c>
       <c r="Z32" t="n">
-        <v>1050866</v>
+        <v>1266524</v>
       </c>
       <c r="AA32" t="n">
-        <v>1229009</v>
+        <v>779490</v>
       </c>
       <c r="AB32" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4206,44 +4206,44 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5280</v>
+        <v>922</v>
       </c>
       <c r="D33" t="n">
-        <v>5334</v>
+        <v>888.2</v>
       </c>
       <c r="E33" t="n">
-        <v>5278</v>
+        <v>854.3</v>
       </c>
       <c r="F33" t="n">
-        <v>5144.75</v>
+        <v>896.4</v>
       </c>
       <c r="G33" t="n">
-        <v>2655826</v>
+        <v>24438087</v>
       </c>
       <c r="H33" t="n">
-        <v>2172103</v>
+        <v>20893593</v>
       </c>
       <c r="I33" t="n">
-        <v>5880</v>
+        <v>1035</v>
       </c>
       <c r="J33" t="n">
-        <v>4615</v>
+        <v>765</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,116 +4251,116 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4546421</v>
       </c>
       <c r="M33" t="n">
-        <v>49559</v>
+        <v>-568358</v>
       </c>
       <c r="N33" t="n">
-        <v>-5122</v>
+        <v>13697</v>
       </c>
       <c r="O33" t="n">
-        <v>218522</v>
+        <v>-5156390</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4947217</v>
       </c>
       <c r="Q33" t="n">
-        <v>66174</v>
+        <v>575744</v>
       </c>
       <c r="R33" t="n">
-        <v>-141226</v>
+        <v>492245</v>
       </c>
       <c r="S33" t="n">
-        <v>172333</v>
+        <v>-812010</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>-420000</v>
       </c>
       <c r="U33" t="n">
-        <v>-41000</v>
+        <v>-1185000</v>
       </c>
       <c r="V33" t="n">
-        <v>31000</v>
+        <v>-116000</v>
       </c>
       <c r="W33" t="n">
-        <v>-19794</v>
+        <v>-3507694</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>19204</v>
       </c>
       <c r="Y33" t="n">
-        <v>24385</v>
+        <v>40898</v>
       </c>
       <c r="Z33" t="n">
-        <v>105104</v>
+        <v>-362548</v>
       </c>
       <c r="AA33" t="n">
-        <v>65983</v>
+        <v>-836686</v>
       </c>
       <c r="AB33" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>籌碼中性、投信買外資賣</t>
+          <t>籌碼中性、外資買投信賣</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、籌碼中性、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>34.25</v>
+        <v>1220</v>
       </c>
       <c r="D34" t="n">
-        <v>35.13</v>
+        <v>1114.4</v>
       </c>
       <c r="E34" t="n">
-        <v>34.6</v>
+        <v>1037.7</v>
       </c>
       <c r="F34" t="n">
-        <v>37.35</v>
+        <v>1072.35</v>
       </c>
       <c r="G34" t="n">
-        <v>11138430</v>
+        <v>4415000</v>
       </c>
       <c r="H34" t="n">
-        <v>16177150</v>
+        <v>3736800</v>
       </c>
       <c r="I34" t="n">
-        <v>44.05</v>
+        <v>1300</v>
       </c>
       <c r="J34" t="n">
-        <v>31.1</v>
+        <v>865</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,116 +4368,116 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7000</v>
+        <v>78870</v>
       </c>
       <c r="M34" t="n">
-        <v>-1655951</v>
+        <v>-1139380</v>
       </c>
       <c r="N34" t="n">
-        <v>1092217</v>
+        <v>-1176252</v>
       </c>
       <c r="O34" t="n">
-        <v>2552697</v>
+        <v>-1740259</v>
       </c>
       <c r="P34" t="n">
-        <v>-291000</v>
+        <v>-73248</v>
       </c>
       <c r="Q34" t="n">
-        <v>-2250951</v>
+        <v>-1970174</v>
       </c>
       <c r="R34" t="n">
-        <v>30049</v>
+        <v>-2217164</v>
       </c>
       <c r="S34" t="n">
-        <v>2249529</v>
+        <v>-2350595</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>871000</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1046000</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>567000</v>
       </c>
       <c r="X34" t="n">
-        <v>298000</v>
+        <v>-57882</v>
       </c>
       <c r="Y34" t="n">
-        <v>595000</v>
+        <v>-40206</v>
       </c>
       <c r="Z34" t="n">
-        <v>1062168</v>
+        <v>-5088</v>
       </c>
       <c r="AA34" t="n">
-        <v>303168</v>
+        <v>43336</v>
       </c>
       <c r="AB34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5290</v>
+        <v>304.5</v>
       </c>
       <c r="D35" t="n">
-        <v>4977</v>
+        <v>291.6</v>
       </c>
       <c r="E35" t="n">
-        <v>4843</v>
+        <v>282.85</v>
       </c>
       <c r="F35" t="n">
-        <v>4784.25</v>
+        <v>260.6</v>
       </c>
       <c r="G35" t="n">
-        <v>2917258</v>
+        <v>21738108</v>
       </c>
       <c r="H35" t="n">
-        <v>2443800</v>
+        <v>31212343</v>
       </c>
       <c r="I35" t="n">
-        <v>5635</v>
+        <v>317</v>
       </c>
       <c r="J35" t="n">
-        <v>4160</v>
+        <v>208.5</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,55 +4485,55 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-963947</v>
+        <v>5273184</v>
       </c>
       <c r="M35" t="n">
-        <v>-1568076</v>
+        <v>4424072</v>
       </c>
       <c r="N35" t="n">
-        <v>-2041638</v>
+        <v>-7269690</v>
       </c>
       <c r="O35" t="n">
-        <v>-1613345</v>
+        <v>-386792</v>
       </c>
       <c r="P35" t="n">
-        <v>-1039947</v>
+        <v>4957638</v>
       </c>
       <c r="Q35" t="n">
-        <v>-1763562</v>
+        <v>6738825</v>
       </c>
       <c r="R35" t="n">
-        <v>-2243428</v>
+        <v>-58099</v>
       </c>
       <c r="S35" t="n">
-        <v>-1532578</v>
+        <v>9512556</v>
       </c>
       <c r="T35" t="n">
-        <v>61000</v>
+        <v>215000</v>
       </c>
       <c r="U35" t="n">
-        <v>111000</v>
+        <v>-2997000</v>
       </c>
       <c r="V35" t="n">
-        <v>56840</v>
+        <v>-7252404</v>
       </c>
       <c r="W35" t="n">
-        <v>-102507</v>
+        <v>-7828440</v>
       </c>
       <c r="X35" t="n">
-        <v>15000</v>
+        <v>100546</v>
       </c>
       <c r="Y35" t="n">
-        <v>84486</v>
+        <v>682247</v>
       </c>
       <c r="Z35" t="n">
-        <v>144950</v>
+        <v>40813</v>
       </c>
       <c r="AA35" t="n">
-        <v>21740</v>
+        <v>-2070908</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -4547,54 +4547,54 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>304.5</v>
+        <v>5280</v>
       </c>
       <c r="D36" t="n">
-        <v>291.6</v>
+        <v>5334</v>
       </c>
       <c r="E36" t="n">
-        <v>282.85</v>
+        <v>5278</v>
       </c>
       <c r="F36" t="n">
-        <v>260.6</v>
+        <v>5144.75</v>
       </c>
       <c r="G36" t="n">
-        <v>21738108</v>
+        <v>2655826</v>
       </c>
       <c r="H36" t="n">
-        <v>31212343</v>
+        <v>2172103</v>
       </c>
       <c r="I36" t="n">
-        <v>317</v>
+        <v>5880</v>
       </c>
       <c r="J36" t="n">
-        <v>208.5</v>
+        <v>4615</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,55 +4602,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-130543</v>
       </c>
       <c r="M36" t="n">
-        <v>-6187776</v>
+        <v>21163</v>
       </c>
       <c r="N36" t="n">
-        <v>-10442456</v>
+        <v>-188601</v>
       </c>
       <c r="O36" t="n">
-        <v>-13220030</v>
+        <v>-185236</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>126856</v>
       </c>
       <c r="Q36" t="n">
-        <v>-4441053</v>
+        <v>329551</v>
       </c>
       <c r="R36" t="n">
-        <v>-6809486</v>
+        <v>86316</v>
       </c>
       <c r="S36" t="n">
-        <v>-5218997</v>
+        <v>-193705</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>-207173</v>
       </c>
       <c r="U36" t="n">
-        <v>-1655000</v>
+        <v>-313179</v>
       </c>
       <c r="V36" t="n">
-        <v>-3421000</v>
+        <v>-362179</v>
       </c>
       <c r="W36" t="n">
-        <v>-6278404</v>
+        <v>21040</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>-50226</v>
       </c>
       <c r="Y36" t="n">
-        <v>-91723</v>
+        <v>4791</v>
       </c>
       <c r="Z36" t="n">
-        <v>-211970</v>
+        <v>87262</v>
       </c>
       <c r="AA36" t="n">
-        <v>-1722629</v>
+        <v>-12571</v>
       </c>
       <c r="AB36" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -4664,54 +4664,54 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>短線籌碼止穩、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>540</v>
+        <v>35.2</v>
       </c>
       <c r="D37" t="n">
-        <v>498.7</v>
+        <v>35.15</v>
       </c>
       <c r="E37" t="n">
-        <v>457.05</v>
+        <v>34.84</v>
       </c>
       <c r="F37" t="n">
-        <v>434.32</v>
+        <v>34.65</v>
       </c>
       <c r="G37" t="n">
-        <v>41904053</v>
+        <v>66828833</v>
       </c>
       <c r="H37" t="n">
-        <v>51443369</v>
+        <v>50399647</v>
       </c>
       <c r="I37" t="n">
-        <v>558</v>
+        <v>36.2</v>
       </c>
       <c r="J37" t="n">
-        <v>354</v>
+        <v>33.25</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,56 +4719,56 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-326000</v>
+        <v>-8372402</v>
       </c>
       <c r="M37" t="n">
-        <v>-6368319</v>
+        <v>-14087196</v>
       </c>
       <c r="N37" t="n">
-        <v>-2224620</v>
+        <v>-8308536</v>
       </c>
       <c r="O37" t="n">
-        <v>-18241428</v>
+        <v>-18014475</v>
       </c>
       <c r="P37" t="n">
-        <v>-280000</v>
+        <v>-24050280</v>
       </c>
       <c r="Q37" t="n">
-        <v>-7239933</v>
+        <v>-50514092</v>
       </c>
       <c r="R37" t="n">
-        <v>-6740187</v>
+        <v>-56390017</v>
       </c>
       <c r="S37" t="n">
-        <v>-21640218</v>
+        <v>-59611564</v>
       </c>
       <c r="T37" t="n">
+        <v>14604788</v>
+      </c>
+      <c r="U37" t="n">
+        <v>34824175</v>
+      </c>
+      <c r="V37" t="n">
+        <v>47315290</v>
+      </c>
+      <c r="W37" t="n">
+        <v>42288604</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1073090</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1602721</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>766191</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-691515</v>
+      </c>
+      <c r="AB37" t="n">
         <v>0</v>
       </c>
-      <c r="U37" t="n">
-        <v>1551000</v>
-      </c>
-      <c r="V37" t="n">
-        <v>4971000</v>
-      </c>
-      <c r="W37" t="n">
-        <v>5741936</v>
-      </c>
-      <c r="X37" t="n">
-        <v>-46000</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>-679386</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>-455433</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>-2343146</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>-10</v>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
           <t>❌避開</t>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4791,44 +4791,44 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>922</v>
+        <v>303.5</v>
       </c>
       <c r="D38" t="n">
-        <v>888.2</v>
+        <v>295.6</v>
       </c>
       <c r="E38" t="n">
-        <v>854.3</v>
+        <v>303.1</v>
       </c>
       <c r="F38" t="n">
-        <v>896.4</v>
+        <v>283.88</v>
       </c>
       <c r="G38" t="n">
-        <v>24438087</v>
+        <v>152949355</v>
       </c>
       <c r="H38" t="n">
-        <v>20893593</v>
+        <v>148065232</v>
       </c>
       <c r="I38" t="n">
-        <v>1035</v>
+        <v>353</v>
       </c>
       <c r="J38" t="n">
-        <v>765</v>
+        <v>214.5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,56 +4836,56 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>8000</v>
+        <v>4540718</v>
       </c>
       <c r="M38" t="n">
-        <v>-8889954</v>
+        <v>-9128373</v>
       </c>
       <c r="N38" t="n">
-        <v>-8579449</v>
+        <v>-15757126</v>
       </c>
       <c r="O38" t="n">
-        <v>-14214048</v>
+        <v>-73471666</v>
       </c>
       <c r="P38" t="n">
-        <v>10000</v>
+        <v>7330462</v>
       </c>
       <c r="Q38" t="n">
-        <v>-6207050</v>
+        <v>5719688</v>
       </c>
       <c r="R38" t="n">
-        <v>-7010484</v>
+        <v>3403984</v>
       </c>
       <c r="S38" t="n">
-        <v>-8419367</v>
+        <v>-43979906</v>
       </c>
       <c r="T38" t="n">
+        <v>-3019725</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-14998890</v>
+      </c>
+      <c r="V38" t="n">
+        <v>-17954890</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-22681234</v>
+      </c>
+      <c r="X38" t="n">
+        <v>229981</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>150829</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-1206220</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-6810526</v>
+      </c>
+      <c r="AB38" t="n">
         <v>0</v>
       </c>
-      <c r="U38" t="n">
-        <v>-2521000</v>
-      </c>
-      <c r="V38" t="n">
-        <v>-1461000</v>
-      </c>
-      <c r="W38" t="n">
-        <v>-4998000</v>
-      </c>
-      <c r="X38" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>-161904</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>-107965</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>-796681</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>-20</v>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>❌避開</t>
@@ -4903,49 +4903,49 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>60.4</v>
+        <v>866</v>
       </c>
       <c r="D39" t="n">
-        <v>59.8</v>
+        <v>742</v>
       </c>
       <c r="E39" t="n">
-        <v>63.98</v>
+        <v>732.1</v>
       </c>
       <c r="F39" t="n">
-        <v>58.98</v>
+        <v>711.25</v>
       </c>
       <c r="G39" t="n">
-        <v>7159433</v>
+        <v>2958000</v>
       </c>
       <c r="H39" t="n">
-        <v>9959241</v>
+        <v>4678000</v>
       </c>
       <c r="I39" t="n">
-        <v>75.2</v>
+        <v>866</v>
       </c>
       <c r="J39" t="n">
-        <v>43.45</v>
+        <v>534</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,55 +4953,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-2083000</v>
+        <v>-541871</v>
       </c>
       <c r="M39" t="n">
-        <v>-4946314</v>
+        <v>-2561156</v>
       </c>
       <c r="N39" t="n">
-        <v>-1989195</v>
+        <v>-4480928</v>
       </c>
       <c r="O39" t="n">
-        <v>-7388088</v>
+        <v>-5069064</v>
       </c>
       <c r="P39" t="n">
-        <v>-1798000</v>
+        <v>-566747</v>
       </c>
       <c r="Q39" t="n">
-        <v>-4418778</v>
+        <v>-3254183</v>
       </c>
       <c r="R39" t="n">
-        <v>-2255766</v>
+        <v>-4533384</v>
       </c>
       <c r="S39" t="n">
-        <v>-8042719</v>
+        <v>-6369986</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>-84038</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>-295650</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>-946650</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>-269880</v>
       </c>
       <c r="X39" t="n">
-        <v>-285000</v>
+        <v>108914</v>
       </c>
       <c r="Y39" t="n">
-        <v>-527536</v>
+        <v>988677</v>
       </c>
       <c r="Z39" t="n">
-        <v>266571</v>
+        <v>999106</v>
       </c>
       <c r="AA39" t="n">
-        <v>654631</v>
+        <v>1570802</v>
       </c>
       <c r="AB39" t="n">
-        <v>-35</v>
+        <v>-5</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -5015,110 +5015,110 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>303.5</v>
+        <v>45.7</v>
       </c>
       <c r="D40" t="n">
-        <v>295.6</v>
+        <v>43.4</v>
       </c>
       <c r="E40" t="n">
-        <v>303.1</v>
+        <v>40.22</v>
       </c>
       <c r="F40" t="n">
-        <v>283.88</v>
+        <v>34.08</v>
       </c>
       <c r="G40" t="n">
-        <v>152949355</v>
+        <v>1463227218</v>
       </c>
       <c r="H40" t="n">
-        <v>148065232</v>
+        <v>613882104</v>
       </c>
       <c r="I40" t="n">
-        <v>353</v>
+        <v>52.2</v>
       </c>
       <c r="J40" t="n">
-        <v>214.5</v>
+        <v>23.65</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-542383</v>
+        <v>-219925504</v>
       </c>
       <c r="M40" t="n">
-        <v>-15005929</v>
+        <v>-207876965</v>
       </c>
       <c r="N40" t="n">
-        <v>-16064626</v>
+        <v>-88593142</v>
       </c>
       <c r="O40" t="n">
-        <v>-50822064</v>
+        <v>-149303338</v>
       </c>
       <c r="P40" t="n">
-        <v>-499000</v>
+        <v>-202889796</v>
       </c>
       <c r="Q40" t="n">
-        <v>-2299220</v>
+        <v>-195014356</v>
       </c>
       <c r="R40" t="n">
-        <v>-4017241</v>
+        <v>-83958861</v>
       </c>
       <c r="S40" t="n">
-        <v>-26452241</v>
+        <v>-142866698</v>
       </c>
       <c r="T40" t="n">
-        <v>-150000</v>
+        <v>-2712696</v>
       </c>
       <c r="U40" t="n">
-        <v>-12030000</v>
+        <v>-2742585</v>
       </c>
       <c r="V40" t="n">
-        <v>-12396000</v>
+        <v>-2805585</v>
       </c>
       <c r="W40" t="n">
-        <v>-19531954</v>
+        <v>-1314907</v>
       </c>
       <c r="X40" t="n">
-        <v>106617</v>
+        <v>-14323012</v>
       </c>
       <c r="Y40" t="n">
-        <v>-676709</v>
+        <v>-10120024</v>
       </c>
       <c r="Z40" t="n">
-        <v>348615</v>
+        <v>-1828696</v>
       </c>
       <c r="AA40" t="n">
-        <v>-4837869</v>
+        <v>-5121733</v>
       </c>
       <c r="AB40" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5142,44 +5142,44 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>273</v>
+        <v>34.25</v>
       </c>
       <c r="D41" t="n">
-        <v>278</v>
+        <v>35.13</v>
       </c>
       <c r="E41" t="n">
-        <v>279.9</v>
+        <v>34.6</v>
       </c>
       <c r="F41" t="n">
-        <v>266.35</v>
+        <v>37.35</v>
       </c>
       <c r="G41" t="n">
-        <v>5636066</v>
+        <v>11138430</v>
       </c>
       <c r="H41" t="n">
-        <v>6333129</v>
+        <v>16177150</v>
       </c>
       <c r="I41" t="n">
-        <v>292</v>
+        <v>44.05</v>
       </c>
       <c r="J41" t="n">
-        <v>222</v>
+        <v>31.1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5187,52 +5187,52 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>160279</v>
+        <v>4124</v>
       </c>
       <c r="M41" t="n">
-        <v>439864</v>
+        <v>-7233994</v>
       </c>
       <c r="N41" t="n">
-        <v>-579291</v>
+        <v>-6954756</v>
       </c>
       <c r="O41" t="n">
-        <v>1925081</v>
+        <v>-2408707</v>
       </c>
       <c r="P41" t="n">
-        <v>-49721</v>
+        <v>-128877</v>
       </c>
       <c r="Q41" t="n">
-        <v>-748363</v>
+        <v>-7194828</v>
       </c>
       <c r="R41" t="n">
-        <v>-1725679</v>
+        <v>-7085758</v>
       </c>
       <c r="S41" t="n">
-        <v>-2796137</v>
+        <v>-2314709</v>
       </c>
       <c r="T41" t="n">
-        <v>109000</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>865000</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>496000</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>4244371</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>101000</v>
+        <v>133001</v>
       </c>
       <c r="Y41" t="n">
-        <v>323227</v>
+        <v>-39166</v>
       </c>
       <c r="Z41" t="n">
-        <v>650388</v>
+        <v>131002</v>
       </c>
       <c r="AA41" t="n">
-        <v>476847</v>
+        <v>-93998</v>
       </c>
       <c r="AB41" t="n">
         <v>-50</v>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -5304,55 +5304,55 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-467151</v>
       </c>
       <c r="M42" t="n">
-        <v>-819556</v>
+        <v>-779449</v>
       </c>
       <c r="N42" t="n">
-        <v>-1174288</v>
+        <v>-1431458</v>
       </c>
       <c r="O42" t="n">
-        <v>-2471356</v>
+        <v>-2655109</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>-190195</v>
       </c>
       <c r="Q42" t="n">
-        <v>-204494</v>
+        <v>-247868</v>
       </c>
       <c r="R42" t="n">
-        <v>-479756</v>
+        <v>-528542</v>
       </c>
       <c r="S42" t="n">
-        <v>-1654442</v>
+        <v>-1615246</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>-264617</v>
       </c>
       <c r="U42" t="n">
-        <v>-601617</v>
+        <v>-524617</v>
       </c>
       <c r="V42" t="n">
-        <v>-689617</v>
+        <v>-879117</v>
       </c>
       <c r="W42" t="n">
-        <v>-637450</v>
+        <v>-828848</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>-12339</v>
       </c>
       <c r="Y42" t="n">
-        <v>-13445</v>
+        <v>-6964</v>
       </c>
       <c r="Z42" t="n">
-        <v>-4915</v>
+        <v>-23799</v>
       </c>
       <c r="AA42" t="n">
-        <v>-179464</v>
+        <v>-211015</v>
       </c>
       <c r="AB42" t="n">
-        <v>-70</v>
+        <v>-95</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -586,37 +586,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>357.5</v>
       </c>
       <c r="D2" t="n">
-        <v>33.58</v>
+        <v>326.8</v>
       </c>
       <c r="E2" t="n">
-        <v>30.93</v>
+        <v>285.1</v>
       </c>
       <c r="F2" t="n">
-        <v>29.77</v>
+        <v>255.22</v>
       </c>
       <c r="G2" t="n">
-        <v>210267926</v>
+        <v>83839978</v>
       </c>
       <c r="H2" t="n">
-        <v>105612204</v>
+        <v>45785817</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>374.5</v>
       </c>
       <c r="J2" t="n">
-        <v>26.65</v>
+        <v>201</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -624,55 +624,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>28357859</v>
+        <v>8636152</v>
       </c>
       <c r="M2" t="n">
-        <v>54438183</v>
+        <v>12325598</v>
       </c>
       <c r="N2" t="n">
-        <v>105494658</v>
+        <v>8250522</v>
       </c>
       <c r="O2" t="n">
-        <v>103900475</v>
+        <v>20110538</v>
       </c>
       <c r="P2" t="n">
-        <v>30455390</v>
+        <v>9558879</v>
       </c>
       <c r="Q2" t="n">
-        <v>60993174</v>
+        <v>12129730</v>
       </c>
       <c r="R2" t="n">
-        <v>114822974</v>
+        <v>10781087</v>
       </c>
       <c r="S2" t="n">
-        <v>117602284</v>
+        <v>23238328</v>
       </c>
       <c r="T2" t="n">
-        <v>-2772000</v>
+        <v>-1044391</v>
       </c>
       <c r="U2" t="n">
-        <v>-9607000</v>
+        <v>-329985</v>
       </c>
       <c r="V2" t="n">
-        <v>-15073000</v>
+        <v>-3103985</v>
       </c>
       <c r="W2" t="n">
-        <v>-18394000</v>
+        <v>-4195087</v>
       </c>
       <c r="X2" t="n">
-        <v>674469</v>
+        <v>121664</v>
       </c>
       <c r="Y2" t="n">
-        <v>3052009</v>
+        <v>525853</v>
       </c>
       <c r="Z2" t="n">
-        <v>5744684</v>
+        <v>573420</v>
       </c>
       <c r="AA2" t="n">
-        <v>4692191</v>
+        <v>1067297</v>
       </c>
       <c r="AB2" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -696,100 +696,100 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>696</v>
+        <v>337.5</v>
       </c>
       <c r="D3" t="n">
-        <v>606.4</v>
+        <v>333</v>
       </c>
       <c r="E3" t="n">
-        <v>555.55</v>
+        <v>324.55</v>
       </c>
       <c r="F3" t="n">
-        <v>529.38</v>
+        <v>314.5</v>
       </c>
       <c r="G3" t="n">
-        <v>50429815</v>
+        <v>17174957</v>
       </c>
       <c r="H3" t="n">
-        <v>29094105</v>
+        <v>13518022</v>
       </c>
       <c r="I3" t="n">
-        <v>719</v>
+        <v>351</v>
       </c>
       <c r="J3" t="n">
-        <v>445.5</v>
+        <v>270.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6579882</v>
+        <v>2492158</v>
       </c>
       <c r="M3" t="n">
-        <v>9377855</v>
+        <v>4279948</v>
       </c>
       <c r="N3" t="n">
-        <v>23425392</v>
+        <v>6392770</v>
       </c>
       <c r="O3" t="n">
-        <v>27208037</v>
+        <v>-517809</v>
       </c>
       <c r="P3" t="n">
-        <v>4397554</v>
+        <v>947946</v>
       </c>
       <c r="Q3" t="n">
-        <v>5776931</v>
+        <v>2503565</v>
       </c>
       <c r="R3" t="n">
-        <v>16930530</v>
+        <v>4027605</v>
       </c>
       <c r="S3" t="n">
-        <v>19891809</v>
+        <v>-5067732</v>
       </c>
       <c r="T3" t="n">
-        <v>2307000</v>
+        <v>1370157</v>
       </c>
       <c r="U3" t="n">
-        <v>4050000</v>
+        <v>1602157</v>
       </c>
       <c r="V3" t="n">
-        <v>5962000</v>
+        <v>2102078</v>
       </c>
       <c r="W3" t="n">
-        <v>5955371</v>
+        <v>5427449</v>
       </c>
       <c r="X3" t="n">
-        <v>-124672</v>
+        <v>174055</v>
       </c>
       <c r="Y3" t="n">
-        <v>-449076</v>
+        <v>174226</v>
       </c>
       <c r="Z3" t="n">
-        <v>532862</v>
+        <v>263087</v>
       </c>
       <c r="AA3" t="n">
-        <v>1360857</v>
+        <v>-877526</v>
       </c>
       <c r="AB3" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -813,44 +813,44 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1085</v>
+        <v>48.83</v>
       </c>
       <c r="D4" t="n">
-        <v>954.6</v>
+        <v>48.3</v>
       </c>
       <c r="E4" t="n">
-        <v>900.1</v>
+        <v>46.39</v>
       </c>
       <c r="F4" t="n">
-        <v>881.7</v>
+        <v>45.22</v>
       </c>
       <c r="G4" t="n">
-        <v>34270461</v>
+        <v>62678749</v>
       </c>
       <c r="H4" t="n">
-        <v>30958709</v>
+        <v>59030542</v>
       </c>
       <c r="I4" t="n">
-        <v>1085</v>
+        <v>50.1</v>
       </c>
       <c r="J4" t="n">
-        <v>776</v>
+        <v>40.81</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>11776533</v>
+        <v>3280854</v>
       </c>
       <c r="M4" t="n">
-        <v>18214157</v>
+        <v>38947194</v>
       </c>
       <c r="N4" t="n">
-        <v>25900315</v>
+        <v>106433953</v>
       </c>
       <c r="O4" t="n">
-        <v>20392758</v>
+        <v>152143148</v>
       </c>
       <c r="P4" t="n">
-        <v>8680405</v>
+        <v>2848479</v>
       </c>
       <c r="Q4" t="n">
-        <v>15114917</v>
+        <v>20506074</v>
       </c>
       <c r="R4" t="n">
-        <v>21294781</v>
+        <v>56692284</v>
       </c>
       <c r="S4" t="n">
-        <v>13761982</v>
+        <v>66513956</v>
       </c>
       <c r="T4" t="n">
-        <v>2890000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3211843</v>
+        <v>1860000</v>
       </c>
       <c r="V4" t="n">
-        <v>4108943</v>
+        <v>1860000</v>
       </c>
       <c r="W4" t="n">
-        <v>7512686</v>
+        <v>3370000</v>
       </c>
       <c r="X4" t="n">
-        <v>206128</v>
+        <v>432375</v>
       </c>
       <c r="Y4" t="n">
-        <v>-112603</v>
+        <v>16581120</v>
       </c>
       <c r="Z4" t="n">
-        <v>496591</v>
+        <v>47881669</v>
       </c>
       <c r="AA4" t="n">
-        <v>-881910</v>
+        <v>82259192</v>
       </c>
       <c r="AB4" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -930,44 +930,44 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="D5" t="n">
-        <v>513.1</v>
+        <v>542.6</v>
       </c>
       <c r="E5" t="n">
-        <v>491</v>
+        <v>491.75</v>
       </c>
       <c r="F5" t="n">
-        <v>502.85</v>
+        <v>467.27</v>
       </c>
       <c r="G5" t="n">
-        <v>33746000</v>
+        <v>4871000</v>
       </c>
       <c r="H5" t="n">
-        <v>31597000</v>
+        <v>3824000</v>
       </c>
       <c r="I5" t="n">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="J5" t="n">
-        <v>436</v>
+        <v>368</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -975,55 +975,55 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4244062</v>
+        <v>158732</v>
       </c>
       <c r="M5" t="n">
-        <v>8968342</v>
+        <v>2284475</v>
       </c>
       <c r="N5" t="n">
-        <v>9409867</v>
+        <v>4385902</v>
       </c>
       <c r="O5" t="n">
-        <v>5771807</v>
+        <v>14138913</v>
       </c>
       <c r="P5" t="n">
-        <v>3267388</v>
+        <v>237027</v>
       </c>
       <c r="Q5" t="n">
-        <v>4671266</v>
+        <v>2181838</v>
       </c>
       <c r="R5" t="n">
-        <v>2987230</v>
+        <v>4304374</v>
       </c>
       <c r="S5" t="n">
-        <v>2361844</v>
+        <v>13513579</v>
       </c>
       <c r="T5" t="n">
-        <v>169999</v>
+        <v>-1200</v>
       </c>
       <c r="U5" t="n">
-        <v>1483999</v>
+        <v>-4500</v>
       </c>
       <c r="V5" t="n">
-        <v>3688999</v>
+        <v>32100</v>
       </c>
       <c r="W5" t="n">
-        <v>2820262</v>
+        <v>-25700</v>
       </c>
       <c r="X5" t="n">
-        <v>806675</v>
+        <v>-77095</v>
       </c>
       <c r="Y5" t="n">
-        <v>2813077</v>
+        <v>107137</v>
       </c>
       <c r="Z5" t="n">
-        <v>2733638</v>
+        <v>49428</v>
       </c>
       <c r="AA5" t="n">
-        <v>589701</v>
+        <v>651034</v>
       </c>
       <c r="AB5" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1047,100 +1047,100 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>342</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>285.6</v>
+        <v>259.4</v>
       </c>
       <c r="E6" t="n">
-        <v>261.4</v>
+        <v>252.65</v>
       </c>
       <c r="F6" t="n">
-        <v>241.47</v>
+        <v>248.3</v>
       </c>
       <c r="G6" t="n">
-        <v>57938700</v>
+        <v>73792269</v>
       </c>
       <c r="H6" t="n">
-        <v>22861322</v>
+        <v>77422231</v>
       </c>
       <c r="I6" t="n">
-        <v>342</v>
+        <v>269.5</v>
       </c>
       <c r="J6" t="n">
-        <v>201</v>
+        <v>219.5</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1408279</v>
+        <v>12823739</v>
       </c>
       <c r="M6" t="n">
-        <v>-2666797</v>
+        <v>41307455</v>
       </c>
       <c r="N6" t="n">
-        <v>4636866</v>
+        <v>118126120</v>
       </c>
       <c r="O6" t="n">
-        <v>8251124</v>
+        <v>186495441</v>
       </c>
       <c r="P6" t="n">
-        <v>713763</v>
+        <v>12866010</v>
       </c>
       <c r="Q6" t="n">
-        <v>-634880</v>
+        <v>41761693</v>
       </c>
       <c r="R6" t="n">
-        <v>5866112</v>
+        <v>114628622</v>
       </c>
       <c r="S6" t="n">
-        <v>10991058</v>
+        <v>191610986</v>
       </c>
       <c r="T6" t="n">
-        <v>-90000</v>
+        <v>130253</v>
       </c>
       <c r="U6" t="n">
-        <v>-2864000</v>
+        <v>18189</v>
       </c>
       <c r="V6" t="n">
-        <v>-2858000</v>
+        <v>1145562</v>
       </c>
       <c r="W6" t="n">
-        <v>-4145286</v>
+        <v>-3291773</v>
       </c>
       <c r="X6" t="n">
-        <v>784516</v>
+        <v>-172524</v>
       </c>
       <c r="Y6" t="n">
-        <v>832083</v>
+        <v>-472427</v>
       </c>
       <c r="Z6" t="n">
-        <v>1628754</v>
+        <v>2351936</v>
       </c>
       <c r="AA6" t="n">
-        <v>1405352</v>
+        <v>-1823772</v>
       </c>
       <c r="AB6" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1154,17 +1154,17 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -1180,28 +1180,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29.62</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>28.4</v>
+        <v>29.58</v>
       </c>
       <c r="E7" t="n">
-        <v>28.08</v>
+        <v>28.53</v>
       </c>
       <c r="F7" t="n">
-        <v>27.45</v>
+        <v>27.95</v>
       </c>
       <c r="G7" t="n">
-        <v>84260566</v>
+        <v>90876706</v>
       </c>
       <c r="H7" t="n">
-        <v>87443952</v>
+        <v>104673717</v>
       </c>
       <c r="I7" t="n">
-        <v>29.83</v>
+        <v>30.8</v>
       </c>
       <c r="J7" t="n">
-        <v>25.02</v>
+        <v>25.31</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44993144</v>
+        <v>19641634</v>
       </c>
       <c r="M7" t="n">
-        <v>201974425</v>
+        <v>112895262</v>
       </c>
       <c r="N7" t="n">
-        <v>256280137</v>
+        <v>269876543</v>
       </c>
       <c r="O7" t="n">
-        <v>153202899</v>
+        <v>224551367</v>
       </c>
       <c r="P7" t="n">
-        <v>7568505</v>
+        <v>-2201530</v>
       </c>
       <c r="Q7" t="n">
-        <v>128594402</v>
+        <v>56675133</v>
       </c>
       <c r="R7" t="n">
-        <v>167888118</v>
+        <v>177701030</v>
       </c>
       <c r="S7" t="n">
-        <v>93494704</v>
+        <v>162064919</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2500000</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>2500000</v>
@@ -1245,19 +1245,19 @@
         <v>5000000</v>
       </c>
       <c r="X7" t="n">
-        <v>37424639</v>
+        <v>21843164</v>
       </c>
       <c r="Y7" t="n">
-        <v>70880023</v>
+        <v>56220129</v>
       </c>
       <c r="Z7" t="n">
-        <v>85892019</v>
+        <v>89675513</v>
       </c>
       <c r="AA7" t="n">
-        <v>54708195</v>
+        <v>57486448</v>
       </c>
       <c r="AB7" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1281,44 +1281,44 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>141</v>
+        <v>927</v>
       </c>
       <c r="D8" t="n">
-        <v>124.8</v>
+        <v>845.6</v>
       </c>
       <c r="E8" t="n">
-        <v>125.75</v>
+        <v>764</v>
       </c>
       <c r="F8" t="n">
-        <v>114.91</v>
+        <v>748.3</v>
       </c>
       <c r="G8" t="n">
-        <v>336105421</v>
+        <v>21729000</v>
       </c>
       <c r="H8" t="n">
-        <v>249474700</v>
+        <v>11989800</v>
       </c>
       <c r="I8" t="n">
-        <v>141</v>
+        <v>1020</v>
       </c>
       <c r="J8" t="n">
-        <v>88.8</v>
+        <v>558</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1326,55 +1326,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53874275</v>
+        <v>226965</v>
       </c>
       <c r="M8" t="n">
-        <v>183655968</v>
+        <v>4981166</v>
       </c>
       <c r="N8" t="n">
-        <v>160960826</v>
+        <v>2961881</v>
       </c>
       <c r="O8" t="n">
-        <v>201131678</v>
+        <v>-736509</v>
       </c>
       <c r="P8" t="n">
-        <v>46872727</v>
+        <v>-1670205</v>
       </c>
       <c r="Q8" t="n">
-        <v>170406739</v>
+        <v>-1575056</v>
       </c>
       <c r="R8" t="n">
-        <v>151935091</v>
+        <v>-4262492</v>
       </c>
       <c r="S8" t="n">
-        <v>128105725</v>
+        <v>-8147595</v>
       </c>
       <c r="T8" t="n">
-        <v>4364455</v>
+        <v>2147266</v>
       </c>
       <c r="U8" t="n">
-        <v>8424424</v>
+        <v>6723095</v>
       </c>
       <c r="V8" t="n">
-        <v>7094424</v>
+        <v>6511483</v>
       </c>
       <c r="W8" t="n">
-        <v>71647256</v>
+        <v>6429761</v>
       </c>
       <c r="X8" t="n">
-        <v>2637093</v>
+        <v>-250096</v>
       </c>
       <c r="Y8" t="n">
-        <v>4824805</v>
+        <v>-166873</v>
       </c>
       <c r="Z8" t="n">
-        <v>1931311</v>
+        <v>712890</v>
       </c>
       <c r="AA8" t="n">
-        <v>1378697</v>
+        <v>981325</v>
       </c>
       <c r="AB8" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1388,54 +1388,54 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>87.40000000000001</v>
+        <v>324</v>
       </c>
       <c r="D9" t="n">
-        <v>77.95999999999999</v>
+        <v>309.2</v>
       </c>
       <c r="E9" t="n">
-        <v>72.94</v>
+        <v>300.5</v>
       </c>
       <c r="F9" t="n">
-        <v>66.67</v>
+        <v>292.05</v>
       </c>
       <c r="G9" t="n">
-        <v>26030149</v>
+        <v>226715301</v>
       </c>
       <c r="H9" t="n">
-        <v>40319814</v>
+        <v>179912662</v>
       </c>
       <c r="I9" t="n">
-        <v>87.40000000000001</v>
+        <v>353</v>
       </c>
       <c r="J9" t="n">
-        <v>58.1</v>
+        <v>214.5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5391543</v>
+        <v>63504793</v>
       </c>
       <c r="M9" t="n">
-        <v>8356421</v>
+        <v>72297780</v>
       </c>
       <c r="N9" t="n">
-        <v>13622444</v>
+        <v>58628689</v>
       </c>
       <c r="O9" t="n">
-        <v>9083310</v>
+        <v>-8182073</v>
       </c>
       <c r="P9" t="n">
-        <v>5322203</v>
+        <v>62166974</v>
       </c>
       <c r="Q9" t="n">
-        <v>7569949</v>
+        <v>75244413</v>
       </c>
       <c r="R9" t="n">
-        <v>11932067</v>
+        <v>73633639</v>
       </c>
       <c r="S9" t="n">
-        <v>5954226</v>
+        <v>29396493</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>809330</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-2252395</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-14231560</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-28669514</v>
       </c>
       <c r="X9" t="n">
-        <v>69340</v>
+        <v>528489</v>
       </c>
       <c r="Y9" t="n">
-        <v>786472</v>
+        <v>-694238</v>
       </c>
       <c r="Z9" t="n">
-        <v>1690377</v>
+        <v>-773390</v>
       </c>
       <c r="AA9" t="n">
-        <v>3129084</v>
+        <v>-8909052</v>
       </c>
       <c r="AB9" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1505,54 +1505,54 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.16</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>6.81</v>
+        <v>138.7</v>
       </c>
       <c r="E10" t="n">
-        <v>6.24</v>
+        <v>130.05</v>
       </c>
       <c r="F10" t="n">
-        <v>6.03</v>
+        <v>120.45</v>
       </c>
       <c r="G10" t="n">
-        <v>36791094</v>
+        <v>362557912</v>
       </c>
       <c r="H10" t="n">
-        <v>51399518</v>
+        <v>337690164</v>
       </c>
       <c r="I10" t="n">
-        <v>8.16</v>
+        <v>156.5</v>
       </c>
       <c r="J10" t="n">
-        <v>5.55</v>
+        <v>88.8</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,55 +1560,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2691884</v>
+        <v>-48079023</v>
       </c>
       <c r="M10" t="n">
-        <v>26374815</v>
+        <v>31718900</v>
       </c>
       <c r="N10" t="n">
-        <v>42618602</v>
+        <v>161500593</v>
       </c>
       <c r="O10" t="n">
-        <v>41909180</v>
+        <v>123869559</v>
       </c>
       <c r="P10" t="n">
-        <v>348000</v>
+        <v>-51733715</v>
       </c>
       <c r="Q10" t="n">
-        <v>16153900</v>
+        <v>9912821</v>
       </c>
       <c r="R10" t="n">
-        <v>32270600</v>
+        <v>133446833</v>
       </c>
       <c r="S10" t="n">
-        <v>31915600</v>
+        <v>62908432</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4855777</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>19891384</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>23951353</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>62128185</v>
       </c>
       <c r="X10" t="n">
-        <v>2343884</v>
+        <v>-1201085</v>
       </c>
       <c r="Y10" t="n">
-        <v>10220915</v>
+        <v>1914695</v>
       </c>
       <c r="Z10" t="n">
-        <v>10348002</v>
+        <v>4102407</v>
       </c>
       <c r="AA10" t="n">
-        <v>9993580</v>
+        <v>-1167058</v>
       </c>
       <c r="AB10" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>336</v>
+        <v>681</v>
       </c>
       <c r="D11" t="n">
-        <v>322.7</v>
+        <v>671.4</v>
       </c>
       <c r="E11" t="n">
-        <v>321.6</v>
+        <v>591.9</v>
       </c>
       <c r="F11" t="n">
-        <v>308.7</v>
+        <v>547.73</v>
       </c>
       <c r="G11" t="n">
-        <v>11025246</v>
+        <v>8187338</v>
       </c>
       <c r="H11" t="n">
-        <v>14171546</v>
+        <v>21854333</v>
       </c>
       <c r="I11" t="n">
-        <v>351</v>
+        <v>764</v>
       </c>
       <c r="J11" t="n">
-        <v>270.5</v>
+        <v>445.5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1049326</v>
+        <v>-421266</v>
       </c>
       <c r="M11" t="n">
-        <v>3162148</v>
+        <v>5155057</v>
       </c>
       <c r="N11" t="n">
-        <v>696962</v>
+        <v>7953030</v>
       </c>
       <c r="O11" t="n">
-        <v>233231</v>
+        <v>19094924</v>
       </c>
       <c r="P11" t="n">
-        <v>1140069</v>
+        <v>-70413</v>
       </c>
       <c r="Q11" t="n">
-        <v>2664109</v>
+        <v>2598341</v>
       </c>
       <c r="R11" t="n">
-        <v>170420</v>
+        <v>3977718</v>
       </c>
       <c r="S11" t="n">
-        <v>-2730714</v>
+        <v>10632318</v>
       </c>
       <c r="T11" t="n">
-        <v>-10000</v>
+        <v>2286</v>
       </c>
       <c r="U11" t="n">
-        <v>489921</v>
+        <v>3178477</v>
       </c>
       <c r="V11" t="n">
-        <v>633921</v>
+        <v>4921477</v>
       </c>
       <c r="W11" t="n">
-        <v>3920789</v>
+        <v>8369951</v>
       </c>
       <c r="X11" t="n">
-        <v>-80743</v>
+        <v>-353139</v>
       </c>
       <c r="Y11" t="n">
-        <v>8118</v>
+        <v>-621761</v>
       </c>
       <c r="Z11" t="n">
-        <v>-107379</v>
+        <v>-946165</v>
       </c>
       <c r="AA11" t="n">
-        <v>-956844</v>
+        <v>92655</v>
       </c>
       <c r="AB11" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1744,105 +1744,105 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72.2</v>
+        <v>8.51</v>
       </c>
       <c r="D12" t="n">
-        <v>69.12</v>
+        <v>7.88</v>
       </c>
       <c r="E12" t="n">
-        <v>67.56</v>
+        <v>6.81</v>
       </c>
       <c r="F12" t="n">
-        <v>68.52</v>
+        <v>6.29</v>
       </c>
       <c r="G12" t="n">
-        <v>337055872</v>
+        <v>233675744</v>
       </c>
       <c r="H12" t="n">
-        <v>147844553</v>
+        <v>151879141</v>
       </c>
       <c r="I12" t="n">
-        <v>81.2</v>
+        <v>9.25</v>
       </c>
       <c r="J12" t="n">
-        <v>61.8</v>
+        <v>5.55</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4624379</v>
+        <v>-18978969</v>
       </c>
       <c r="M12" t="n">
-        <v>86624549</v>
+        <v>-10779856</v>
       </c>
       <c r="N12" t="n">
-        <v>82459143</v>
+        <v>12903075</v>
       </c>
       <c r="O12" t="n">
-        <v>24752731</v>
+        <v>28289444</v>
       </c>
       <c r="P12" t="n">
-        <v>3107525</v>
+        <v>-18076800</v>
       </c>
       <c r="Q12" t="n">
-        <v>82352666</v>
+        <v>-7476749</v>
       </c>
       <c r="R12" t="n">
-        <v>76543284</v>
+        <v>8329151</v>
       </c>
       <c r="S12" t="n">
-        <v>22368852</v>
+        <v>23803851</v>
       </c>
       <c r="T12" t="n">
-        <v>762000</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>784000</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>805000</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>798000</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>754854</v>
+        <v>-902169</v>
       </c>
       <c r="Y12" t="n">
-        <v>3487883</v>
+        <v>-3303107</v>
       </c>
       <c r="Z12" t="n">
-        <v>5110859</v>
+        <v>4573924</v>
       </c>
       <c r="AA12" t="n">
-        <v>1585879</v>
+        <v>4485593</v>
       </c>
       <c r="AB12" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,54 +1856,54 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>533</v>
+        <v>1025</v>
       </c>
       <c r="D13" t="n">
-        <v>511.6</v>
+        <v>1030</v>
       </c>
       <c r="E13" t="n">
-        <v>468.75</v>
+        <v>933.3</v>
       </c>
       <c r="F13" t="n">
-        <v>448.2</v>
+        <v>905.55</v>
       </c>
       <c r="G13" t="n">
-        <v>2520000</v>
+        <v>25166670</v>
       </c>
       <c r="H13" t="n">
-        <v>4413800</v>
+        <v>30680111</v>
       </c>
       <c r="I13" t="n">
-        <v>558</v>
+        <v>1130</v>
       </c>
       <c r="J13" t="n">
-        <v>340</v>
+        <v>776</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>755377</v>
+        <v>559160</v>
       </c>
       <c r="M13" t="n">
-        <v>2856804</v>
+        <v>13042301</v>
       </c>
       <c r="N13" t="n">
-        <v>9398836</v>
+        <v>19479925</v>
       </c>
       <c r="O13" t="n">
-        <v>7366124</v>
+        <v>19167141</v>
       </c>
       <c r="P13" t="n">
-        <v>737962</v>
+        <v>344308</v>
       </c>
       <c r="Q13" t="n">
-        <v>2860498</v>
+        <v>9222374</v>
       </c>
       <c r="R13" t="n">
-        <v>8822301</v>
+        <v>15656886</v>
       </c>
       <c r="S13" t="n">
-        <v>10989591</v>
+        <v>16395121</v>
       </c>
       <c r="T13" t="n">
-        <v>-1200</v>
+        <v>469000</v>
       </c>
       <c r="U13" t="n">
-        <v>35400</v>
+        <v>4409000</v>
       </c>
       <c r="V13" t="n">
-        <v>89400</v>
+        <v>4730843</v>
       </c>
       <c r="W13" t="n">
-        <v>-1897400</v>
+        <v>4177943</v>
       </c>
       <c r="X13" t="n">
-        <v>18615</v>
+        <v>-254148</v>
       </c>
       <c r="Y13" t="n">
-        <v>-39094</v>
+        <v>-589073</v>
       </c>
       <c r="Z13" t="n">
-        <v>487135</v>
+        <v>-907804</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1726067</v>
+        <v>-1405923</v>
       </c>
       <c r="AB13" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -1983,73 +1983,73 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13.65</v>
+        <v>55.9</v>
       </c>
       <c r="D14" t="n">
-        <v>11.83</v>
+        <v>55.8</v>
       </c>
       <c r="E14" t="n">
-        <v>11.16</v>
+        <v>52.79</v>
       </c>
       <c r="F14" t="n">
-        <v>10.02</v>
+        <v>51.28</v>
       </c>
       <c r="G14" t="n">
-        <v>478320069</v>
+        <v>15689455</v>
       </c>
       <c r="H14" t="n">
-        <v>148294428</v>
+        <v>13166730</v>
       </c>
       <c r="I14" t="n">
-        <v>14.3</v>
+        <v>61.4</v>
       </c>
       <c r="J14" t="n">
-        <v>8.130000000000001</v>
+        <v>45.45</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-38167602</v>
+        <v>-215295</v>
       </c>
       <c r="M14" t="n">
-        <v>-10752553</v>
+        <v>894319</v>
       </c>
       <c r="N14" t="n">
-        <v>18165967</v>
+        <v>8238115</v>
       </c>
       <c r="O14" t="n">
-        <v>-4180170</v>
+        <v>15157316</v>
       </c>
       <c r="P14" t="n">
-        <v>-34299664</v>
+        <v>-255200</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9283197</v>
+        <v>851649</v>
       </c>
       <c r="R14" t="n">
-        <v>19188803</v>
+        <v>7609098</v>
       </c>
       <c r="S14" t="n">
-        <v>-1504190</v>
+        <v>14264513</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2064,19 +2064,19 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3867938</v>
+        <v>39905</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1469356</v>
+        <v>42670</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1022836</v>
+        <v>629017</v>
       </c>
       <c r="AA14" t="n">
-        <v>-2675980</v>
+        <v>892803</v>
       </c>
       <c r="AB14" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2100,44 +2100,44 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>48.32</v>
+        <v>2295</v>
       </c>
       <c r="D15" t="n">
-        <v>46.5</v>
+        <v>2286</v>
       </c>
       <c r="E15" t="n">
-        <v>45.58</v>
+        <v>2255.5</v>
       </c>
       <c r="F15" t="n">
-        <v>44.4</v>
+        <v>2252.25</v>
       </c>
       <c r="G15" t="n">
-        <v>49374408</v>
+        <v>42313277</v>
       </c>
       <c r="H15" t="n">
-        <v>49915897</v>
+        <v>34088235</v>
       </c>
       <c r="I15" t="n">
-        <v>48.79</v>
+        <v>2360</v>
       </c>
       <c r="J15" t="n">
-        <v>40.71</v>
+        <v>2135</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,55 +2145,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>10242115</v>
+        <v>-6147103</v>
       </c>
       <c r="M15" t="n">
-        <v>77728874</v>
+        <v>-5211815</v>
       </c>
       <c r="N15" t="n">
-        <v>117379555</v>
+        <v>3515564</v>
       </c>
       <c r="O15" t="n">
-        <v>159869366</v>
+        <v>-19942901</v>
       </c>
       <c r="P15" t="n">
-        <v>4033935</v>
+        <v>-7078615</v>
       </c>
       <c r="Q15" t="n">
-        <v>40220145</v>
+        <v>-6016252</v>
       </c>
       <c r="R15" t="n">
-        <v>57276746</v>
+        <v>-1237687</v>
       </c>
       <c r="S15" t="n">
-        <v>51434271</v>
+        <v>-41422107</v>
       </c>
       <c r="T15" t="n">
-        <v>-240000</v>
+        <v>465061</v>
       </c>
       <c r="U15" t="n">
-        <v>-240000</v>
+        <v>-130996</v>
       </c>
       <c r="V15" t="n">
-        <v>-340000</v>
+        <v>3532656</v>
       </c>
       <c r="W15" t="n">
-        <v>1270000</v>
+        <v>19847971</v>
       </c>
       <c r="X15" t="n">
-        <v>6448180</v>
+        <v>466451</v>
       </c>
       <c r="Y15" t="n">
-        <v>37748729</v>
+        <v>935433</v>
       </c>
       <c r="Z15" t="n">
-        <v>60442809</v>
+        <v>1220595</v>
       </c>
       <c r="AA15" t="n">
-        <v>107165095</v>
+        <v>1631235</v>
       </c>
       <c r="AB15" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -2207,54 +2207,54 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="D16" t="n">
-        <v>251.5</v>
+        <v>302.8</v>
       </c>
       <c r="E16" t="n">
-        <v>249.5</v>
+        <v>291.15</v>
       </c>
       <c r="F16" t="n">
-        <v>244.47</v>
+        <v>269.85</v>
       </c>
       <c r="G16" t="n">
-        <v>55665305</v>
+        <v>30735473</v>
       </c>
       <c r="H16" t="n">
-        <v>69819957</v>
+        <v>29590486</v>
       </c>
       <c r="I16" t="n">
-        <v>263.5</v>
+        <v>336.5</v>
       </c>
       <c r="J16" t="n">
-        <v>219.5</v>
+        <v>212.5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,55 +2262,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8357718</v>
+        <v>-719759</v>
       </c>
       <c r="M16" t="n">
-        <v>85176383</v>
+        <v>9819437</v>
       </c>
       <c r="N16" t="n">
-        <v>90759559</v>
+        <v>8970325</v>
       </c>
       <c r="O16" t="n">
-        <v>147431875</v>
+        <v>6462102</v>
       </c>
       <c r="P16" t="n">
-        <v>9279594</v>
+        <v>-574523</v>
       </c>
       <c r="Q16" t="n">
-        <v>82146523</v>
+        <v>8594692</v>
       </c>
       <c r="R16" t="n">
-        <v>93430042</v>
+        <v>10375879</v>
       </c>
       <c r="S16" t="n">
-        <v>159160299</v>
+        <v>13472643</v>
       </c>
       <c r="T16" t="n">
-        <v>-245930</v>
+        <v>20768</v>
       </c>
       <c r="U16" t="n">
-        <v>881443</v>
+        <v>1136768</v>
       </c>
       <c r="V16" t="n">
-        <v>-1608417</v>
+        <v>-2075232</v>
       </c>
       <c r="W16" t="n">
-        <v>-8405701</v>
+        <v>-6262208</v>
       </c>
       <c r="X16" t="n">
-        <v>-675946</v>
+        <v>-166004</v>
       </c>
       <c r="Y16" t="n">
-        <v>2148417</v>
+        <v>87977</v>
       </c>
       <c r="Z16" t="n">
-        <v>-1062066</v>
+        <v>669678</v>
       </c>
       <c r="AA16" t="n">
-        <v>-3322723</v>
+        <v>-748333</v>
       </c>
       <c r="AB16" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2324,17 +2324,17 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -2350,28 +2350,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>130.5</v>
+        <v>142</v>
       </c>
       <c r="D17" t="n">
-        <v>118.7</v>
+        <v>131</v>
       </c>
       <c r="E17" t="n">
-        <v>113.39</v>
+        <v>121.3</v>
       </c>
       <c r="F17" t="n">
-        <v>100.19</v>
+        <v>106.98</v>
       </c>
       <c r="G17" t="n">
-        <v>291896012</v>
+        <v>418286433</v>
       </c>
       <c r="H17" t="n">
-        <v>252641517</v>
+        <v>306975059</v>
       </c>
       <c r="I17" t="n">
-        <v>133.5</v>
+        <v>151</v>
       </c>
       <c r="J17" t="n">
-        <v>71.3</v>
+        <v>76.3</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>52531260</v>
+        <v>-32086948</v>
       </c>
       <c r="M17" t="n">
-        <v>30902532</v>
+        <v>22365239</v>
       </c>
       <c r="N17" t="n">
-        <v>13031123</v>
+        <v>736511</v>
       </c>
       <c r="O17" t="n">
-        <v>51942046</v>
+        <v>21737309</v>
       </c>
       <c r="P17" t="n">
-        <v>71870498</v>
+        <v>59187</v>
       </c>
       <c r="Q17" t="n">
-        <v>90044068</v>
+        <v>93459652</v>
       </c>
       <c r="R17" t="n">
-        <v>78707028</v>
+        <v>111633222</v>
       </c>
       <c r="S17" t="n">
-        <v>9215401</v>
+        <v>52418017</v>
       </c>
       <c r="T17" t="n">
-        <v>-19692021</v>
+        <v>-34484005</v>
       </c>
       <c r="U17" t="n">
-        <v>-65983172</v>
+        <v>-73186855</v>
       </c>
       <c r="V17" t="n">
-        <v>-70677271</v>
+        <v>-119478006</v>
       </c>
       <c r="W17" t="n">
-        <v>45097665</v>
+        <v>-32041152</v>
       </c>
       <c r="X17" t="n">
-        <v>352783</v>
+        <v>2337870</v>
       </c>
       <c r="Y17" t="n">
-        <v>6841636</v>
+        <v>2092442</v>
       </c>
       <c r="Z17" t="n">
-        <v>5001366</v>
+        <v>8581295</v>
       </c>
       <c r="AA17" t="n">
-        <v>-2371020</v>
+        <v>1360444</v>
       </c>
       <c r="AB17" t="n">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2446,49 +2446,49 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>37.7</v>
       </c>
       <c r="D18" t="n">
-        <v>51.64</v>
+        <v>36.91</v>
       </c>
       <c r="E18" t="n">
-        <v>50.21</v>
+        <v>32.7</v>
       </c>
       <c r="F18" t="n">
-        <v>50.11</v>
+        <v>30.59</v>
       </c>
       <c r="G18" t="n">
-        <v>14910096</v>
+        <v>161629606</v>
       </c>
       <c r="H18" t="n">
-        <v>26622786</v>
+        <v>147852468</v>
       </c>
       <c r="I18" t="n">
-        <v>53.9</v>
+        <v>41.05</v>
       </c>
       <c r="J18" t="n">
-        <v>47.35</v>
+        <v>26.65</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2496,55 +2496,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3310380</v>
+        <v>-6582455</v>
       </c>
       <c r="M18" t="n">
-        <v>13160114</v>
+        <v>-3599130</v>
       </c>
       <c r="N18" t="n">
-        <v>22308713</v>
+        <v>22481194</v>
       </c>
       <c r="O18" t="n">
-        <v>5831665</v>
+        <v>80707566</v>
       </c>
       <c r="P18" t="n">
-        <v>3325023</v>
+        <v>-6901985</v>
       </c>
       <c r="Q18" t="n">
-        <v>13482345</v>
+        <v>16026</v>
       </c>
       <c r="R18" t="n">
-        <v>22552122</v>
+        <v>30553810</v>
       </c>
       <c r="S18" t="n">
-        <v>6675240</v>
+        <v>94640620</v>
       </c>
       <c r="T18" t="n">
-        <v>-17850</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-20816</v>
+        <v>-2772000</v>
       </c>
       <c r="V18" t="n">
-        <v>-81816</v>
+        <v>-9607000</v>
       </c>
       <c r="W18" t="n">
-        <v>-354294</v>
+        <v>-17754000</v>
       </c>
       <c r="X18" t="n">
-        <v>3207</v>
+        <v>319530</v>
       </c>
       <c r="Y18" t="n">
-        <v>-301415</v>
+        <v>-843156</v>
       </c>
       <c r="Z18" t="n">
-        <v>-161593</v>
+        <v>1534384</v>
       </c>
       <c r="AA18" t="n">
-        <v>-489281</v>
+        <v>3820946</v>
       </c>
       <c r="AB18" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2558,110 +2558,110 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>2390</v>
       </c>
       <c r="D19" t="n">
-        <v>21.51</v>
+        <v>2329</v>
       </c>
       <c r="E19" t="n">
-        <v>20.48</v>
+        <v>2160</v>
       </c>
       <c r="F19" t="n">
-        <v>19.25</v>
+        <v>2180</v>
       </c>
       <c r="G19" t="n">
-        <v>818361725</v>
+        <v>11721062</v>
       </c>
       <c r="H19" t="n">
-        <v>356215638</v>
+        <v>11680295</v>
       </c>
       <c r="I19" t="n">
-        <v>25.8</v>
+        <v>2585</v>
       </c>
       <c r="J19" t="n">
-        <v>16.6</v>
+        <v>1880</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-169469205</v>
+        <v>-2012884</v>
       </c>
       <c r="M19" t="n">
-        <v>-117109516</v>
+        <v>4362377</v>
       </c>
       <c r="N19" t="n">
-        <v>23750704</v>
+        <v>9095498</v>
       </c>
       <c r="O19" t="n">
-        <v>64693465</v>
+        <v>3705814</v>
       </c>
       <c r="P19" t="n">
-        <v>-166129539</v>
+        <v>-1742544</v>
       </c>
       <c r="Q19" t="n">
-        <v>-120015118</v>
+        <v>4100990</v>
       </c>
       <c r="R19" t="n">
-        <v>20137674</v>
+        <v>8309648</v>
       </c>
       <c r="S19" t="n">
-        <v>70298902</v>
+        <v>6636509</v>
       </c>
       <c r="T19" t="n">
-        <v>121946</v>
+        <v>-121189</v>
       </c>
       <c r="U19" t="n">
-        <v>100709</v>
+        <v>335711</v>
       </c>
       <c r="V19" t="n">
-        <v>141311</v>
+        <v>426743</v>
       </c>
       <c r="W19" t="n">
-        <v>119654</v>
+        <v>-2434762</v>
       </c>
       <c r="X19" t="n">
-        <v>-3461612</v>
+        <v>-149151</v>
       </c>
       <c r="Y19" t="n">
-        <v>2804893</v>
+        <v>-74324</v>
       </c>
       <c r="Z19" t="n">
-        <v>3471719</v>
+        <v>359107</v>
       </c>
       <c r="AA19" t="n">
-        <v>-5725091</v>
+        <v>-495933</v>
       </c>
       <c r="AB19" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2685,44 +2685,44 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>208</v>
+        <v>1540</v>
       </c>
       <c r="D20" t="n">
-        <v>207</v>
+        <v>1561</v>
       </c>
       <c r="E20" t="n">
-        <v>199.9</v>
+        <v>1412.5</v>
       </c>
       <c r="F20" t="n">
-        <v>190.12</v>
+        <v>1370</v>
       </c>
       <c r="G20" t="n">
-        <v>20600438</v>
+        <v>8654000</v>
       </c>
       <c r="H20" t="n">
-        <v>22454689</v>
+        <v>5919200</v>
       </c>
       <c r="I20" t="n">
-        <v>231</v>
+        <v>1735</v>
       </c>
       <c r="J20" t="n">
-        <v>167</v>
+        <v>968</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,55 +2730,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-3468634</v>
+        <v>236344</v>
       </c>
       <c r="M20" t="n">
-        <v>-5795592</v>
+        <v>348209</v>
       </c>
       <c r="N20" t="n">
-        <v>3454457</v>
+        <v>1092463</v>
       </c>
       <c r="O20" t="n">
-        <v>-2253419</v>
+        <v>1932192</v>
       </c>
       <c r="P20" t="n">
-        <v>-2743550</v>
+        <v>-790831</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5212303</v>
+        <v>-2064320</v>
       </c>
       <c r="R20" t="n">
-        <v>2840720</v>
+        <v>-1425598</v>
       </c>
       <c r="S20" t="n">
-        <v>-2007726</v>
+        <v>-602470</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1213000</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3037000</v>
       </c>
       <c r="V20" t="n">
-        <v>5000</v>
+        <v>3088700</v>
       </c>
       <c r="W20" t="n">
-        <v>-55923</v>
+        <v>2947100</v>
       </c>
       <c r="X20" t="n">
-        <v>-725084</v>
+        <v>-185825</v>
       </c>
       <c r="Y20" t="n">
-        <v>-583289</v>
+        <v>-624471</v>
       </c>
       <c r="Z20" t="n">
-        <v>608737</v>
+        <v>-570639</v>
       </c>
       <c r="AA20" t="n">
-        <v>-189770</v>
+        <v>-412438</v>
       </c>
       <c r="AB20" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -2792,54 +2792,54 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2350</v>
+        <v>41.75</v>
       </c>
       <c r="D21" t="n">
-        <v>2136</v>
+        <v>42.26</v>
       </c>
       <c r="E21" t="n">
-        <v>2101</v>
+        <v>41.4</v>
       </c>
       <c r="F21" t="n">
-        <v>2149</v>
+        <v>40.1</v>
       </c>
       <c r="G21" t="n">
-        <v>12198582</v>
+        <v>18913490</v>
       </c>
       <c r="H21" t="n">
-        <v>11067330</v>
+        <v>29044968</v>
       </c>
       <c r="I21" t="n">
-        <v>2410</v>
+        <v>44.75</v>
       </c>
       <c r="J21" t="n">
-        <v>1880</v>
+        <v>37.45</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,69 +2847,69 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2566512</v>
+        <v>1422517</v>
       </c>
       <c r="M21" t="n">
-        <v>7299633</v>
+        <v>4592548</v>
       </c>
       <c r="N21" t="n">
-        <v>6859678</v>
+        <v>18295416</v>
       </c>
       <c r="O21" t="n">
-        <v>2778375</v>
+        <v>89498884</v>
       </c>
       <c r="P21" t="n">
-        <v>2327539</v>
+        <v>3489136</v>
       </c>
       <c r="Q21" t="n">
-        <v>6536197</v>
+        <v>5036903</v>
       </c>
       <c r="R21" t="n">
-        <v>6492434</v>
+        <v>21128594</v>
       </c>
       <c r="S21" t="n">
-        <v>6207419</v>
+        <v>97943601</v>
       </c>
       <c r="T21" t="n">
-        <v>160900</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>251932</v>
+        <v>-509000</v>
       </c>
       <c r="V21" t="n">
-        <v>-1011559</v>
+        <v>-1562000</v>
       </c>
       <c r="W21" t="n">
-        <v>-2905969</v>
+        <v>-5668000</v>
       </c>
       <c r="X21" t="n">
-        <v>78073</v>
+        <v>-2066619</v>
       </c>
       <c r="Y21" t="n">
-        <v>511504</v>
+        <v>64645</v>
       </c>
       <c r="Z21" t="n">
-        <v>1378803</v>
+        <v>-1271178</v>
       </c>
       <c r="AA21" t="n">
-        <v>-523075</v>
+        <v>-2776717</v>
       </c>
       <c r="AB21" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2919,44 +2919,44 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55.4</v>
+        <v>52.3</v>
       </c>
       <c r="D22" t="n">
-        <v>53.91</v>
+        <v>52.34</v>
       </c>
       <c r="E22" t="n">
-        <v>51.25</v>
+        <v>50.92</v>
       </c>
       <c r="F22" t="n">
         <v>50.42</v>
       </c>
       <c r="G22" t="n">
-        <v>15723414</v>
+        <v>16197736</v>
       </c>
       <c r="H22" t="n">
-        <v>11255762</v>
+        <v>27657898</v>
       </c>
       <c r="I22" t="n">
-        <v>60.3</v>
+        <v>53.9</v>
       </c>
       <c r="J22" t="n">
-        <v>45.45</v>
+        <v>47.35</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,79 +2964,79 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-56389</v>
+        <v>3526901</v>
       </c>
       <c r="M22" t="n">
-        <v>7287407</v>
+        <v>20060433</v>
       </c>
       <c r="N22" t="n">
-        <v>13802670</v>
+        <v>29910167</v>
       </c>
       <c r="O22" t="n">
-        <v>11995532</v>
+        <v>42084077</v>
       </c>
       <c r="P22" t="n">
-        <v>-10151</v>
+        <v>3235751</v>
       </c>
       <c r="Q22" t="n">
-        <v>6747298</v>
+        <v>21089420</v>
       </c>
       <c r="R22" t="n">
-        <v>12995298</v>
+        <v>31246742</v>
       </c>
       <c r="S22" t="n">
-        <v>11249963</v>
+        <v>42935899</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-1501318</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1504284</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-1834912</v>
       </c>
       <c r="X22" t="n">
-        <v>-46238</v>
+        <v>290918</v>
       </c>
       <c r="Y22" t="n">
-        <v>540109</v>
+        <v>472331</v>
       </c>
       <c r="Z22" t="n">
-        <v>807372</v>
+        <v>167709</v>
       </c>
       <c r="AA22" t="n">
-        <v>745569</v>
+        <v>983090</v>
       </c>
       <c r="AB22" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
@@ -3052,28 +3052,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5290</v>
+        <v>5055</v>
       </c>
       <c r="D23" t="n">
-        <v>4977</v>
+        <v>5232</v>
       </c>
       <c r="E23" t="n">
-        <v>4843</v>
+        <v>4894</v>
       </c>
       <c r="F23" t="n">
-        <v>4784.25</v>
+        <v>4861.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2917258</v>
+        <v>2289989</v>
       </c>
       <c r="H23" t="n">
-        <v>2443800</v>
+        <v>2477704</v>
       </c>
       <c r="I23" t="n">
         <v>5635</v>
       </c>
       <c r="J23" t="n">
-        <v>4160</v>
+        <v>4300</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,116 +3081,116 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-205121</v>
+        <v>-126362</v>
       </c>
       <c r="M23" t="n">
-        <v>659036</v>
+        <v>162136</v>
       </c>
       <c r="N23" t="n">
-        <v>1183968</v>
+        <v>1026293</v>
       </c>
       <c r="O23" t="n">
-        <v>2104114</v>
+        <v>1614531</v>
       </c>
       <c r="P23" t="n">
-        <v>-69967</v>
+        <v>-136280</v>
       </c>
       <c r="Q23" t="n">
-        <v>517687</v>
+        <v>146118</v>
       </c>
       <c r="R23" t="n">
-        <v>1437059</v>
+        <v>733772</v>
       </c>
       <c r="S23" t="n">
-        <v>2384479</v>
+        <v>2127518</v>
       </c>
       <c r="T23" t="n">
-        <v>-67986</v>
+        <v>48695</v>
       </c>
       <c r="U23" t="n">
-        <v>151848</v>
+        <v>124607</v>
       </c>
       <c r="V23" t="n">
-        <v>-132639</v>
+        <v>344441</v>
       </c>
       <c r="W23" t="n">
-        <v>-81804</v>
+        <v>-313301</v>
       </c>
       <c r="X23" t="n">
-        <v>-67168</v>
+        <v>-38777</v>
       </c>
       <c r="Y23" t="n">
-        <v>-10499</v>
+        <v>-108589</v>
       </c>
       <c r="Z23" t="n">
-        <v>-120452</v>
+        <v>-51920</v>
       </c>
       <c r="AA23" t="n">
-        <v>-198561</v>
+        <v>-199686</v>
       </c>
       <c r="AB23" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>611</v>
+        <v>4410</v>
       </c>
       <c r="D24" t="n">
-        <v>555</v>
+        <v>4284</v>
       </c>
       <c r="E24" t="n">
-        <v>540</v>
+        <v>3801.5</v>
       </c>
       <c r="F24" t="n">
-        <v>528.95</v>
+        <v>3580.5</v>
       </c>
       <c r="G24" t="n">
-        <v>39627497</v>
+        <v>16433052</v>
       </c>
       <c r="H24" t="n">
-        <v>28597065</v>
+        <v>15938104</v>
       </c>
       <c r="I24" t="n">
-        <v>636</v>
+        <v>4690</v>
       </c>
       <c r="J24" t="n">
-        <v>465</v>
+        <v>2565</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,64 +3198,64 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1946064</v>
+        <v>-1552083</v>
       </c>
       <c r="M24" t="n">
-        <v>81869</v>
+        <v>1269665</v>
       </c>
       <c r="N24" t="n">
-        <v>2179097</v>
+        <v>-278472</v>
       </c>
       <c r="O24" t="n">
-        <v>-9008726</v>
+        <v>-5121817</v>
       </c>
       <c r="P24" t="n">
-        <v>-1468340</v>
+        <v>-856431</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1906274</v>
+        <v>3508701</v>
       </c>
       <c r="R24" t="n">
-        <v>-224958</v>
+        <v>763839</v>
       </c>
       <c r="S24" t="n">
-        <v>-14271976</v>
+        <v>-2586431</v>
       </c>
       <c r="T24" t="n">
-        <v>-42806</v>
+        <v>-623680</v>
       </c>
       <c r="U24" t="n">
-        <v>2336877</v>
+        <v>-2501721</v>
       </c>
       <c r="V24" t="n">
-        <v>3001877</v>
+        <v>-1926160</v>
       </c>
       <c r="W24" t="n">
-        <v>6006195</v>
+        <v>-3313614</v>
       </c>
       <c r="X24" t="n">
-        <v>-434918</v>
+        <v>-71972</v>
       </c>
       <c r="Y24" t="n">
-        <v>-348734</v>
+        <v>262685</v>
       </c>
       <c r="Z24" t="n">
-        <v>-597822</v>
+        <v>883849</v>
       </c>
       <c r="AA24" t="n">
-        <v>-742945</v>
+        <v>778228</v>
       </c>
       <c r="AB24" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3265,49 +3265,49 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人賣超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>82.40000000000001</v>
+        <v>528</v>
       </c>
       <c r="D25" t="n">
-        <v>81.73999999999999</v>
+        <v>544.8</v>
       </c>
       <c r="E25" t="n">
-        <v>81.34</v>
+        <v>501.9</v>
       </c>
       <c r="F25" t="n">
-        <v>80.16</v>
+        <v>507.18</v>
       </c>
       <c r="G25" t="n">
-        <v>12463968</v>
+        <v>48754000</v>
       </c>
       <c r="H25" t="n">
-        <v>10197116</v>
+        <v>40401400</v>
       </c>
       <c r="I25" t="n">
-        <v>85.8</v>
+        <v>588</v>
       </c>
       <c r="J25" t="n">
-        <v>70.2</v>
+        <v>436</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,116 +3315,116 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-2446750</v>
+        <v>-1273254</v>
       </c>
       <c r="M25" t="n">
-        <v>3766968</v>
+        <v>3514854</v>
       </c>
       <c r="N25" t="n">
-        <v>4738685</v>
+        <v>8239134</v>
       </c>
       <c r="O25" t="n">
-        <v>2727602</v>
+        <v>10599873</v>
       </c>
       <c r="P25" t="n">
-        <v>-2360206</v>
+        <v>-789147</v>
       </c>
       <c r="Q25" t="n">
-        <v>3555724</v>
+        <v>2658940</v>
       </c>
       <c r="R25" t="n">
-        <v>4717542</v>
+        <v>4062818</v>
       </c>
       <c r="S25" t="n">
-        <v>3116204</v>
+        <v>5103493</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-57163</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>476395</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1790395</v>
       </c>
       <c r="W25" t="n">
-        <v>-8000</v>
+        <v>4017662</v>
       </c>
       <c r="X25" t="n">
-        <v>-86544</v>
+        <v>-426944</v>
       </c>
       <c r="Y25" t="n">
-        <v>211244</v>
+        <v>379519</v>
       </c>
       <c r="Z25" t="n">
-        <v>21143</v>
+        <v>2385921</v>
       </c>
       <c r="AA25" t="n">
-        <v>-380602</v>
+        <v>1478718</v>
       </c>
       <c r="AB25" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>整理觀察：跌破5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>284.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>274.8</v>
+        <v>81.78</v>
       </c>
       <c r="E26" t="n">
-        <v>260.7</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>255.95</v>
+        <v>80.73</v>
       </c>
       <c r="G26" t="n">
-        <v>88509083</v>
+        <v>9188127</v>
       </c>
       <c r="H26" t="n">
-        <v>89776777</v>
+        <v>11612759</v>
       </c>
       <c r="I26" t="n">
-        <v>305.5</v>
+        <v>85.8</v>
       </c>
       <c r="J26" t="n">
-        <v>227.5</v>
+        <v>74.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,233 +3432,233 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-17576165</v>
+        <v>-630748</v>
       </c>
       <c r="M26" t="n">
-        <v>25069607</v>
+        <v>-3684183</v>
       </c>
       <c r="N26" t="n">
-        <v>19890503</v>
+        <v>2529535</v>
       </c>
       <c r="O26" t="n">
-        <v>3740322</v>
+        <v>3650896</v>
       </c>
       <c r="P26" t="n">
-        <v>-13228850</v>
+        <v>-543485</v>
       </c>
       <c r="Q26" t="n">
-        <v>25462512</v>
+        <v>-3419340</v>
       </c>
       <c r="R26" t="n">
-        <v>21413015</v>
+        <v>2496590</v>
       </c>
       <c r="S26" t="n">
-        <v>4280144</v>
+        <v>3814967</v>
       </c>
       <c r="T26" t="n">
-        <v>-3381000</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>-2422000</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>-2684000</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1997000</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-966315</v>
+        <v>-87263</v>
       </c>
       <c r="Y26" t="n">
-        <v>2029095</v>
+        <v>-264843</v>
       </c>
       <c r="Z26" t="n">
-        <v>1161488</v>
+        <v>32945</v>
       </c>
       <c r="AA26" t="n">
-        <v>-2536822</v>
+        <v>-164071</v>
       </c>
       <c r="AB26" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1580</v>
+        <v>81</v>
       </c>
       <c r="D27" t="n">
-        <v>1433</v>
+        <v>82.56</v>
       </c>
       <c r="E27" t="n">
-        <v>1385.5</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>1308.55</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>9546000</v>
+        <v>41573738</v>
       </c>
       <c r="H27" t="n">
-        <v>3017800</v>
+        <v>42495385</v>
       </c>
       <c r="I27" t="n">
-        <v>1700</v>
+        <v>93</v>
       </c>
       <c r="J27" t="n">
-        <v>941</v>
+        <v>58.1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-83545</v>
+        <v>-4660292</v>
       </c>
       <c r="M27" t="n">
-        <v>660709</v>
+        <v>349575</v>
       </c>
       <c r="N27" t="n">
-        <v>848398</v>
+        <v>3314453</v>
       </c>
       <c r="O27" t="n">
-        <v>2026953</v>
+        <v>12704407</v>
       </c>
       <c r="P27" t="n">
-        <v>-1100380</v>
+        <v>-3655765</v>
       </c>
       <c r="Q27" t="n">
-        <v>-461658</v>
+        <v>1503819</v>
       </c>
       <c r="R27" t="n">
-        <v>-27799</v>
+        <v>3751565</v>
       </c>
       <c r="S27" t="n">
-        <v>1154682</v>
+        <v>10597315</v>
       </c>
       <c r="T27" t="n">
-        <v>1406000</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1457700</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1445700</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>427100</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-389165</v>
+        <v>-1004527</v>
       </c>
       <c r="Y27" t="n">
-        <v>-335333</v>
+        <v>-1154244</v>
       </c>
       <c r="Z27" t="n">
-        <v>-569503</v>
+        <v>-437112</v>
       </c>
       <c r="AA27" t="n">
-        <v>445171</v>
+        <v>2107092</v>
       </c>
       <c r="AB27" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、爆量價未漲、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>540</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>498.7</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>457.05</v>
+        <v>68.39</v>
       </c>
       <c r="F28" t="n">
-        <v>434.32</v>
+        <v>68.84</v>
       </c>
       <c r="G28" t="n">
-        <v>41904053</v>
+        <v>152764187</v>
       </c>
       <c r="H28" t="n">
-        <v>51443369</v>
+        <v>190929390</v>
       </c>
       <c r="I28" t="n">
-        <v>558</v>
+        <v>81.2</v>
       </c>
       <c r="J28" t="n">
-        <v>354</v>
+        <v>61.8</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,116 +3666,116 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3665357</v>
+        <v>-10583662</v>
       </c>
       <c r="M28" t="n">
-        <v>-2295368</v>
+        <v>-3776166</v>
       </c>
       <c r="N28" t="n">
-        <v>12783506</v>
+        <v>78224004</v>
       </c>
       <c r="O28" t="n">
-        <v>17733372</v>
+        <v>52848701</v>
       </c>
       <c r="P28" t="n">
-        <v>3230273</v>
+        <v>-10144891</v>
       </c>
       <c r="Q28" t="n">
-        <v>-7656559</v>
+        <v>-6468392</v>
       </c>
       <c r="R28" t="n">
-        <v>-2064736</v>
+        <v>72776749</v>
       </c>
       <c r="S28" t="n">
-        <v>3089670</v>
+        <v>45963423</v>
       </c>
       <c r="T28" t="n">
-        <v>272000</v>
+        <v>610000</v>
       </c>
       <c r="U28" t="n">
-        <v>5359563</v>
+        <v>2342000</v>
       </c>
       <c r="V28" t="n">
-        <v>14540563</v>
+        <v>2364000</v>
       </c>
       <c r="W28" t="n">
-        <v>14286504</v>
+        <v>2385000</v>
       </c>
       <c r="X28" t="n">
-        <v>163084</v>
+        <v>-1048771</v>
       </c>
       <c r="Y28" t="n">
-        <v>1628</v>
+        <v>350226</v>
       </c>
       <c r="Z28" t="n">
-        <v>307679</v>
+        <v>3083255</v>
       </c>
       <c r="AA28" t="n">
-        <v>357198</v>
+        <v>4500278</v>
       </c>
       <c r="AB28" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>整理觀察：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>661</v>
+        <v>35.3</v>
       </c>
       <c r="D29" t="n">
-        <v>614.6</v>
+        <v>35.25</v>
       </c>
       <c r="E29" t="n">
-        <v>540.85</v>
+        <v>34.91</v>
       </c>
       <c r="F29" t="n">
-        <v>448.73</v>
+        <v>34.79</v>
       </c>
       <c r="G29" t="n">
-        <v>29457930</v>
+        <v>86240054</v>
       </c>
       <c r="H29" t="n">
-        <v>56139070</v>
+        <v>66352693</v>
       </c>
       <c r="I29" t="n">
-        <v>691</v>
+        <v>36.25</v>
       </c>
       <c r="J29" t="n">
-        <v>307</v>
+        <v>33.4</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,116 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-2424120</v>
+        <v>13359346</v>
       </c>
       <c r="M29" t="n">
-        <v>3032718</v>
+        <v>-13346318</v>
       </c>
       <c r="N29" t="n">
-        <v>2749960</v>
+        <v>-19061112</v>
       </c>
       <c r="O29" t="n">
-        <v>16261311</v>
+        <v>-16481991</v>
       </c>
       <c r="P29" t="n">
-        <v>-3752033</v>
+        <v>-15338438</v>
       </c>
       <c r="Q29" t="n">
-        <v>-4747485</v>
+        <v>-74761371</v>
       </c>
       <c r="R29" t="n">
-        <v>-15588469</v>
+        <v>-101225183</v>
       </c>
       <c r="S29" t="n">
-        <v>-24755153</v>
+        <v>-108489478</v>
       </c>
       <c r="T29" t="n">
-        <v>124208</v>
+        <v>28288924</v>
       </c>
       <c r="U29" t="n">
-        <v>5196657</v>
+        <v>59776845</v>
       </c>
       <c r="V29" t="n">
-        <v>15549336</v>
+        <v>79996232</v>
       </c>
       <c r="W29" t="n">
-        <v>39670828</v>
+        <v>90968017</v>
       </c>
       <c r="X29" t="n">
-        <v>1203705</v>
+        <v>408860</v>
       </c>
       <c r="Y29" t="n">
-        <v>2583546</v>
+        <v>1638208</v>
       </c>
       <c r="Z29" t="n">
-        <v>2789093</v>
+        <v>2167839</v>
       </c>
       <c r="AA29" t="n">
-        <v>1345636</v>
+        <v>1039470</v>
       </c>
       <c r="AB29" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2270</v>
+        <v>15.55</v>
       </c>
       <c r="D30" t="n">
-        <v>2250</v>
+        <v>13.71</v>
       </c>
       <c r="E30" t="n">
-        <v>2245</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>2242.25</v>
+        <v>10.7</v>
       </c>
       <c r="G30" t="n">
-        <v>32781470</v>
+        <v>326422854</v>
       </c>
       <c r="H30" t="n">
-        <v>30223565</v>
+        <v>248577726</v>
       </c>
       <c r="I30" t="n">
-        <v>2345</v>
+        <v>15.95</v>
       </c>
       <c r="J30" t="n">
-        <v>2135</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,116 +3900,116 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-8248077</v>
+        <v>6591547</v>
       </c>
       <c r="M30" t="n">
-        <v>479302</v>
+        <v>-49947094</v>
       </c>
       <c r="N30" t="n">
-        <v>-7470683</v>
+        <v>-22532045</v>
       </c>
       <c r="O30" t="n">
-        <v>-24896242</v>
+        <v>-5997825</v>
       </c>
       <c r="P30" t="n">
-        <v>-7748559</v>
+        <v>6246231</v>
       </c>
       <c r="Q30" t="n">
-        <v>-2969994</v>
+        <v>-48526796</v>
       </c>
       <c r="R30" t="n">
-        <v>-12987121</v>
+        <v>-23510329</v>
       </c>
       <c r="S30" t="n">
-        <v>-54524902</v>
+        <v>-7405832</v>
       </c>
       <c r="T30" t="n">
-        <v>-597289</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3066363</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5422008</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>30712204</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>97771</v>
+        <v>345316</v>
       </c>
       <c r="Y30" t="n">
-        <v>382933</v>
+        <v>-1420298</v>
       </c>
       <c r="Z30" t="n">
-        <v>94430</v>
+        <v>978284</v>
       </c>
       <c r="AA30" t="n">
-        <v>-1083544</v>
+        <v>1408007</v>
       </c>
       <c r="AB30" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>41.35</v>
+        <v>627</v>
       </c>
       <c r="D31" t="n">
-        <v>42.12</v>
+        <v>611.6</v>
       </c>
       <c r="E31" t="n">
-        <v>40.77</v>
+        <v>557.3</v>
       </c>
       <c r="F31" t="n">
-        <v>39.71</v>
+        <v>543.2</v>
       </c>
       <c r="G31" t="n">
-        <v>37127594</v>
+        <v>35071941</v>
       </c>
       <c r="H31" t="n">
-        <v>36197186</v>
+        <v>32499570</v>
       </c>
       <c r="I31" t="n">
-        <v>44.75</v>
+        <v>669</v>
       </c>
       <c r="J31" t="n">
-        <v>36.6</v>
+        <v>465</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,233 +4017,233 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-8665361</v>
+        <v>-2039263</v>
       </c>
       <c r="M31" t="n">
-        <v>5037507</v>
+        <v>-3779445</v>
       </c>
       <c r="N31" t="n">
-        <v>39162139</v>
+        <v>-1751512</v>
       </c>
       <c r="O31" t="n">
-        <v>96951742</v>
+        <v>-7709520</v>
       </c>
       <c r="P31" t="n">
-        <v>-7447878</v>
+        <v>-2361460</v>
       </c>
       <c r="Q31" t="n">
-        <v>8643813</v>
+        <v>-2995996</v>
       </c>
       <c r="R31" t="n">
-        <v>44796984</v>
+        <v>-3433930</v>
       </c>
       <c r="S31" t="n">
-        <v>107321474</v>
+        <v>-11019195</v>
       </c>
       <c r="T31" t="n">
-        <v>-509000</v>
+        <v>401204</v>
       </c>
       <c r="U31" t="n">
-        <v>-1562000</v>
+        <v>-315554</v>
       </c>
       <c r="V31" t="n">
-        <v>-3204000</v>
+        <v>2064129</v>
       </c>
       <c r="W31" t="n">
-        <v>-6573000</v>
+        <v>3427727</v>
       </c>
       <c r="X31" t="n">
-        <v>-708483</v>
+        <v>-79007</v>
       </c>
       <c r="Y31" t="n">
-        <v>-2044306</v>
+        <v>-467895</v>
       </c>
       <c r="Z31" t="n">
-        <v>-2430845</v>
+        <v>-381711</v>
       </c>
       <c r="AA31" t="n">
-        <v>-3796732</v>
+        <v>-118052</v>
       </c>
       <c r="AB31" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4265</v>
+        <v>742</v>
       </c>
       <c r="D32" t="n">
-        <v>3830</v>
+        <v>684.8</v>
       </c>
       <c r="E32" t="n">
-        <v>3586.5</v>
+        <v>596.95</v>
       </c>
       <c r="F32" t="n">
-        <v>3387.5</v>
+        <v>488.45</v>
       </c>
       <c r="G32" t="n">
-        <v>19540872</v>
+        <v>25023375</v>
       </c>
       <c r="H32" t="n">
-        <v>12055166</v>
+        <v>44221133</v>
       </c>
       <c r="I32" t="n">
-        <v>4440</v>
+        <v>769</v>
       </c>
       <c r="J32" t="n">
-        <v>2485</v>
+        <v>314</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>976145</v>
+        <v>-928538</v>
       </c>
       <c r="M32" t="n">
-        <v>-571992</v>
+        <v>-5487929</v>
       </c>
       <c r="N32" t="n">
-        <v>-2678985</v>
+        <v>-31091</v>
       </c>
       <c r="O32" t="n">
-        <v>-6602075</v>
+        <v>15313036</v>
       </c>
       <c r="P32" t="n">
-        <v>1367297</v>
+        <v>-1412412</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1377565</v>
+        <v>-8554706</v>
       </c>
       <c r="R32" t="n">
-        <v>-3496640</v>
+        <v>-9550158</v>
       </c>
       <c r="S32" t="n">
-        <v>-5683390</v>
+        <v>-20980250</v>
       </c>
       <c r="T32" t="n">
-        <v>-598432</v>
+        <v>26422</v>
       </c>
       <c r="U32" t="n">
-        <v>-22871</v>
+        <v>191630</v>
       </c>
       <c r="V32" t="n">
-        <v>-448869</v>
+        <v>5264079</v>
       </c>
       <c r="W32" t="n">
-        <v>-1698175</v>
+        <v>33822645</v>
       </c>
       <c r="X32" t="n">
-        <v>207280</v>
+        <v>457452</v>
       </c>
       <c r="Y32" t="n">
-        <v>828444</v>
+        <v>2875147</v>
       </c>
       <c r="Z32" t="n">
-        <v>1266524</v>
+        <v>4254988</v>
       </c>
       <c r="AA32" t="n">
-        <v>779490</v>
+        <v>2470641</v>
       </c>
       <c r="AB32" t="n">
-        <v>35</v>
+        <v>-5</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、投信買外資賣</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、帶量突破20日高點、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>922</v>
+        <v>21.2</v>
       </c>
       <c r="D33" t="n">
-        <v>888.2</v>
+        <v>22.32</v>
       </c>
       <c r="E33" t="n">
-        <v>854.3</v>
+        <v>20.8</v>
       </c>
       <c r="F33" t="n">
-        <v>896.4</v>
+        <v>19.68</v>
       </c>
       <c r="G33" t="n">
-        <v>24438087</v>
+        <v>538705306</v>
       </c>
       <c r="H33" t="n">
-        <v>20893593</v>
+        <v>479994202</v>
       </c>
       <c r="I33" t="n">
-        <v>1035</v>
+        <v>25.8</v>
       </c>
       <c r="J33" t="n">
-        <v>765</v>
+        <v>16.6</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,116 +4251,116 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4546421</v>
+        <v>-2648535</v>
       </c>
       <c r="M33" t="n">
-        <v>-568358</v>
+        <v>-259776941</v>
       </c>
       <c r="N33" t="n">
-        <v>13697</v>
+        <v>-207417252</v>
       </c>
       <c r="O33" t="n">
-        <v>-5156390</v>
+        <v>-51477021</v>
       </c>
       <c r="P33" t="n">
-        <v>4947217</v>
+        <v>-840692</v>
       </c>
       <c r="Q33" t="n">
-        <v>575744</v>
+        <v>-255291833</v>
       </c>
       <c r="R33" t="n">
-        <v>492245</v>
+        <v>-209177412</v>
       </c>
       <c r="S33" t="n">
-        <v>-812010</v>
+        <v>-50943264</v>
       </c>
       <c r="T33" t="n">
-        <v>-420000</v>
+        <v>85252</v>
       </c>
       <c r="U33" t="n">
-        <v>-1185000</v>
+        <v>203198</v>
       </c>
       <c r="V33" t="n">
-        <v>-116000</v>
+        <v>181961</v>
       </c>
       <c r="W33" t="n">
-        <v>-3507694</v>
+        <v>219906</v>
       </c>
       <c r="X33" t="n">
-        <v>19204</v>
+        <v>-1893095</v>
       </c>
       <c r="Y33" t="n">
-        <v>40898</v>
+        <v>-4688306</v>
       </c>
       <c r="Z33" t="n">
-        <v>-362548</v>
+        <v>1578199</v>
       </c>
       <c r="AA33" t="n">
-        <v>-836686</v>
+        <v>-753663</v>
       </c>
       <c r="AB33" t="n">
-        <v>30</v>
+        <v>-40</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>籌碼中性、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、籌碼中性、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1220</v>
+        <v>486</v>
       </c>
       <c r="D34" t="n">
-        <v>1114.4</v>
+        <v>520.6</v>
       </c>
       <c r="E34" t="n">
-        <v>1037.7</v>
+        <v>470.95</v>
       </c>
       <c r="F34" t="n">
-        <v>1072.35</v>
+        <v>446.38</v>
       </c>
       <c r="G34" t="n">
-        <v>4415000</v>
+        <v>20687337</v>
       </c>
       <c r="H34" t="n">
-        <v>3736800</v>
+        <v>41287562</v>
       </c>
       <c r="I34" t="n">
-        <v>1300</v>
+        <v>568</v>
       </c>
       <c r="J34" t="n">
-        <v>865</v>
+        <v>372</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,116 +4368,116 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>78870</v>
+        <v>-2839782</v>
       </c>
       <c r="M34" t="n">
-        <v>-1139380</v>
+        <v>-4397424</v>
       </c>
       <c r="N34" t="n">
-        <v>-1176252</v>
+        <v>-10358149</v>
       </c>
       <c r="O34" t="n">
-        <v>-1740259</v>
+        <v>-5458601</v>
       </c>
       <c r="P34" t="n">
-        <v>-73248</v>
+        <v>239975</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1970174</v>
+        <v>760076</v>
       </c>
       <c r="R34" t="n">
-        <v>-2217164</v>
+        <v>-10126756</v>
       </c>
       <c r="S34" t="n">
-        <v>-2350595</v>
+        <v>-12301515</v>
       </c>
       <c r="T34" t="n">
-        <v>210000</v>
+        <v>-2618127</v>
       </c>
       <c r="U34" t="n">
-        <v>871000</v>
+        <v>-4684127</v>
       </c>
       <c r="V34" t="n">
-        <v>1046000</v>
+        <v>403436</v>
       </c>
       <c r="W34" t="n">
-        <v>567000</v>
+        <v>7324377</v>
       </c>
       <c r="X34" t="n">
-        <v>-57882</v>
+        <v>-461630</v>
       </c>
       <c r="Y34" t="n">
-        <v>-40206</v>
+        <v>-473373</v>
       </c>
       <c r="Z34" t="n">
-        <v>-5088</v>
+        <v>-634829</v>
       </c>
       <c r="AA34" t="n">
-        <v>43336</v>
+        <v>-481463</v>
       </c>
       <c r="AB34" t="n">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>304.5</v>
+        <v>4950</v>
       </c>
       <c r="D35" t="n">
-        <v>291.6</v>
+        <v>5288</v>
       </c>
       <c r="E35" t="n">
-        <v>282.85</v>
+        <v>5179</v>
       </c>
       <c r="F35" t="n">
-        <v>260.6</v>
+        <v>5163.75</v>
       </c>
       <c r="G35" t="n">
-        <v>21738108</v>
+        <v>2157834</v>
       </c>
       <c r="H35" t="n">
-        <v>31212343</v>
+        <v>2179434</v>
       </c>
       <c r="I35" t="n">
-        <v>317</v>
+        <v>5880</v>
       </c>
       <c r="J35" t="n">
-        <v>208.5</v>
+        <v>4615</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,55 +4485,55 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5273184</v>
+        <v>-106761</v>
       </c>
       <c r="M35" t="n">
-        <v>4424072</v>
+        <v>-685968</v>
       </c>
       <c r="N35" t="n">
-        <v>-7269690</v>
+        <v>-534262</v>
       </c>
       <c r="O35" t="n">
-        <v>-386792</v>
+        <v>-429822</v>
       </c>
       <c r="P35" t="n">
-        <v>4957638</v>
+        <v>191035</v>
       </c>
       <c r="Q35" t="n">
-        <v>6738825</v>
+        <v>96826</v>
       </c>
       <c r="R35" t="n">
-        <v>-58099</v>
+        <v>299521</v>
       </c>
       <c r="S35" t="n">
-        <v>9512556</v>
+        <v>513578</v>
       </c>
       <c r="T35" t="n">
-        <v>215000</v>
+        <v>-191987</v>
       </c>
       <c r="U35" t="n">
-        <v>-2997000</v>
+        <v>-519310</v>
       </c>
       <c r="V35" t="n">
-        <v>-7252404</v>
+        <v>-625316</v>
       </c>
       <c r="W35" t="n">
-        <v>-7828440</v>
+        <v>-796310</v>
       </c>
       <c r="X35" t="n">
-        <v>100546</v>
+        <v>-105809</v>
       </c>
       <c r="Y35" t="n">
-        <v>682247</v>
+        <v>-263484</v>
       </c>
       <c r="Z35" t="n">
-        <v>40813</v>
+        <v>-208467</v>
       </c>
       <c r="AA35" t="n">
-        <v>-2070908</v>
+        <v>-147090</v>
       </c>
       <c r="AB35" t="n">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -4547,54 +4547,54 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5280</v>
+        <v>208.5</v>
       </c>
       <c r="D36" t="n">
-        <v>5334</v>
+        <v>209.7</v>
       </c>
       <c r="E36" t="n">
-        <v>5278</v>
+        <v>201.75</v>
       </c>
       <c r="F36" t="n">
-        <v>5144.75</v>
+        <v>193.43</v>
       </c>
       <c r="G36" t="n">
-        <v>2655826</v>
+        <v>16061701</v>
       </c>
       <c r="H36" t="n">
-        <v>2172103</v>
+        <v>22429834</v>
       </c>
       <c r="I36" t="n">
-        <v>5880</v>
+        <v>231</v>
       </c>
       <c r="J36" t="n">
-        <v>4615</v>
+        <v>167</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,55 +4602,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-130543</v>
+        <v>2872949</v>
       </c>
       <c r="M36" t="n">
-        <v>21163</v>
+        <v>-2111061</v>
       </c>
       <c r="N36" t="n">
-        <v>-188601</v>
+        <v>-4438019</v>
       </c>
       <c r="O36" t="n">
-        <v>-185236</v>
+        <v>4364176</v>
       </c>
       <c r="P36" t="n">
-        <v>126856</v>
+        <v>2783989</v>
       </c>
       <c r="Q36" t="n">
-        <v>329551</v>
+        <v>-1328616</v>
       </c>
       <c r="R36" t="n">
-        <v>86316</v>
+        <v>-3797369</v>
       </c>
       <c r="S36" t="n">
-        <v>-193705</v>
+        <v>3751038</v>
       </c>
       <c r="T36" t="n">
-        <v>-207173</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-313179</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>-362179</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>21040</v>
+        <v>-57316</v>
       </c>
       <c r="X36" t="n">
-        <v>-50226</v>
+        <v>88960</v>
       </c>
       <c r="Y36" t="n">
-        <v>4791</v>
+        <v>-782445</v>
       </c>
       <c r="Z36" t="n">
-        <v>87262</v>
+        <v>-640650</v>
       </c>
       <c r="AA36" t="n">
-        <v>-12571</v>
+        <v>670454</v>
       </c>
       <c r="AB36" t="n">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -4664,54 +4664,54 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、外資買投信賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>35.2</v>
+        <v>46.4</v>
       </c>
       <c r="D37" t="n">
-        <v>35.15</v>
+        <v>47.21</v>
       </c>
       <c r="E37" t="n">
-        <v>34.84</v>
+        <v>42.59</v>
       </c>
       <c r="F37" t="n">
-        <v>34.65</v>
+        <v>36.49</v>
       </c>
       <c r="G37" t="n">
-        <v>66828833</v>
+        <v>1259689849</v>
       </c>
       <c r="H37" t="n">
-        <v>50399647</v>
+        <v>910026565</v>
       </c>
       <c r="I37" t="n">
-        <v>36.2</v>
+        <v>52.2</v>
       </c>
       <c r="J37" t="n">
-        <v>33.25</v>
+        <v>23.65</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,55 +4719,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-8372402</v>
+        <v>-310027101</v>
       </c>
       <c r="M37" t="n">
-        <v>-14087196</v>
+        <v>-497513859</v>
       </c>
       <c r="N37" t="n">
-        <v>-8308536</v>
+        <v>-485465320</v>
       </c>
       <c r="O37" t="n">
-        <v>-18014475</v>
+        <v>-355479136</v>
       </c>
       <c r="P37" t="n">
-        <v>-24050280</v>
+        <v>-289338059</v>
       </c>
       <c r="Q37" t="n">
-        <v>-50514092</v>
+        <v>-460572143</v>
       </c>
       <c r="R37" t="n">
-        <v>-56390017</v>
+        <v>-452696703</v>
       </c>
       <c r="S37" t="n">
-        <v>-59611564</v>
+        <v>-322095879</v>
       </c>
       <c r="T37" t="n">
-        <v>14604788</v>
+        <v>109777</v>
       </c>
       <c r="U37" t="n">
-        <v>34824175</v>
+        <v>-8132919</v>
       </c>
       <c r="V37" t="n">
-        <v>47315290</v>
+        <v>-8162808</v>
       </c>
       <c r="W37" t="n">
-        <v>42288604</v>
+        <v>-7399130</v>
       </c>
       <c r="X37" t="n">
-        <v>1073090</v>
+        <v>-20798819</v>
       </c>
       <c r="Y37" t="n">
-        <v>1602721</v>
+        <v>-28808797</v>
       </c>
       <c r="Z37" t="n">
-        <v>766191</v>
+        <v>-24605809</v>
       </c>
       <c r="AA37" t="n">
-        <v>-691515</v>
+        <v>-25984127</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -4781,54 +4781,54 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>303.5</v>
+        <v>1700</v>
       </c>
       <c r="D38" t="n">
-        <v>295.6</v>
+        <v>1700</v>
       </c>
       <c r="E38" t="n">
-        <v>303.1</v>
+        <v>1724</v>
       </c>
       <c r="F38" t="n">
-        <v>283.88</v>
+        <v>1651.75</v>
       </c>
       <c r="G38" t="n">
-        <v>152949355</v>
+        <v>3905000</v>
       </c>
       <c r="H38" t="n">
-        <v>148065232</v>
+        <v>3809800</v>
       </c>
       <c r="I38" t="n">
-        <v>353</v>
+        <v>1935</v>
       </c>
       <c r="J38" t="n">
-        <v>214.5</v>
+        <v>1245</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,55 +4836,55 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4540718</v>
+        <v>518754</v>
       </c>
       <c r="M38" t="n">
-        <v>-9128373</v>
+        <v>-619342</v>
       </c>
       <c r="N38" t="n">
-        <v>-15757126</v>
+        <v>-931640</v>
       </c>
       <c r="O38" t="n">
-        <v>-73471666</v>
+        <v>-2033871</v>
       </c>
       <c r="P38" t="n">
-        <v>7330462</v>
+        <v>267535</v>
       </c>
       <c r="Q38" t="n">
-        <v>5719688</v>
+        <v>-542133</v>
       </c>
       <c r="R38" t="n">
-        <v>3403984</v>
+        <v>-599806</v>
       </c>
       <c r="S38" t="n">
-        <v>-43979906</v>
+        <v>-1089279</v>
       </c>
       <c r="T38" t="n">
-        <v>-3019725</v>
+        <v>247000</v>
       </c>
       <c r="U38" t="n">
-        <v>-14998890</v>
+        <v>-60377</v>
       </c>
       <c r="V38" t="n">
-        <v>-17954890</v>
+        <v>-320377</v>
       </c>
       <c r="W38" t="n">
-        <v>-22681234</v>
+        <v>-758210</v>
       </c>
       <c r="X38" t="n">
-        <v>229981</v>
+        <v>4219</v>
       </c>
       <c r="Y38" t="n">
-        <v>150829</v>
+        <v>-16832</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1206220</v>
+        <v>-11457</v>
       </c>
       <c r="AA38" t="n">
-        <v>-6810526</v>
+        <v>-186382</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -4898,54 +4898,54 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資買投信賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>866</v>
+        <v>259</v>
       </c>
       <c r="D39" t="n">
-        <v>742</v>
+        <v>280.4</v>
       </c>
       <c r="E39" t="n">
-        <v>732.1</v>
+        <v>266.55</v>
       </c>
       <c r="F39" t="n">
-        <v>711.25</v>
+        <v>259.52</v>
       </c>
       <c r="G39" t="n">
-        <v>2958000</v>
+        <v>114452978</v>
       </c>
       <c r="H39" t="n">
-        <v>4678000</v>
+        <v>96811115</v>
       </c>
       <c r="I39" t="n">
-        <v>866</v>
+        <v>305.5</v>
       </c>
       <c r="J39" t="n">
-        <v>534</v>
+        <v>227.5</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,55 +4953,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-541871</v>
+        <v>-39324591</v>
       </c>
       <c r="M39" t="n">
-        <v>-2561156</v>
+        <v>-67549430</v>
       </c>
       <c r="N39" t="n">
-        <v>-4480928</v>
+        <v>-24903658</v>
       </c>
       <c r="O39" t="n">
-        <v>-5069064</v>
+        <v>-20464849</v>
       </c>
       <c r="P39" t="n">
-        <v>-566747</v>
+        <v>-33742667</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3254183</v>
+        <v>-52941212</v>
       </c>
       <c r="R39" t="n">
-        <v>-4533384</v>
+        <v>-14249850</v>
       </c>
       <c r="S39" t="n">
-        <v>-6369986</v>
+        <v>-12605493</v>
       </c>
       <c r="T39" t="n">
-        <v>-84038</v>
+        <v>-3001000</v>
       </c>
       <c r="U39" t="n">
-        <v>-295650</v>
+        <v>-10283000</v>
       </c>
       <c r="V39" t="n">
-        <v>-946650</v>
+        <v>-9324000</v>
       </c>
       <c r="W39" t="n">
-        <v>-269880</v>
+        <v>-3905000</v>
       </c>
       <c r="X39" t="n">
-        <v>108914</v>
+        <v>-2580924</v>
       </c>
       <c r="Y39" t="n">
-        <v>988677</v>
+        <v>-4325218</v>
       </c>
       <c r="Z39" t="n">
-        <v>999106</v>
+        <v>-1329808</v>
       </c>
       <c r="AA39" t="n">
-        <v>1570802</v>
+        <v>-3954356</v>
       </c>
       <c r="AB39" t="n">
-        <v>-5</v>
+        <v>-60</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5025,100 +5025,100 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>45.7</v>
+        <v>1050</v>
       </c>
       <c r="D40" t="n">
-        <v>43.4</v>
+        <v>1145</v>
       </c>
       <c r="E40" t="n">
-        <v>40.22</v>
+        <v>1047.2</v>
       </c>
       <c r="F40" t="n">
-        <v>34.08</v>
+        <v>1074.1</v>
       </c>
       <c r="G40" t="n">
-        <v>1463227218</v>
+        <v>3846000</v>
       </c>
       <c r="H40" t="n">
-        <v>613882104</v>
+        <v>5033200</v>
       </c>
       <c r="I40" t="n">
-        <v>52.2</v>
+        <v>1300</v>
       </c>
       <c r="J40" t="n">
-        <v>23.65</v>
+        <v>865</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-219925504</v>
+        <v>-403232</v>
       </c>
       <c r="M40" t="n">
-        <v>-207876965</v>
+        <v>-1794757</v>
       </c>
       <c r="N40" t="n">
-        <v>-88593142</v>
+        <v>-3013007</v>
       </c>
       <c r="O40" t="n">
-        <v>-149303338</v>
+        <v>-3462863</v>
       </c>
       <c r="P40" t="n">
-        <v>-202889796</v>
+        <v>7822</v>
       </c>
       <c r="Q40" t="n">
-        <v>-195014356</v>
+        <v>-256464</v>
       </c>
       <c r="R40" t="n">
-        <v>-83958861</v>
+        <v>-2153390</v>
       </c>
       <c r="S40" t="n">
-        <v>-142866698</v>
+        <v>-2413307</v>
       </c>
       <c r="T40" t="n">
-        <v>-2712696</v>
+        <v>-404050</v>
       </c>
       <c r="U40" t="n">
-        <v>-2742585</v>
+        <v>-1456050</v>
       </c>
       <c r="V40" t="n">
-        <v>-2805585</v>
+        <v>-795050</v>
       </c>
       <c r="W40" t="n">
-        <v>-1314907</v>
+        <v>-1074050</v>
       </c>
       <c r="X40" t="n">
-        <v>-14323012</v>
+        <v>-7004</v>
       </c>
       <c r="Y40" t="n">
-        <v>-10120024</v>
+        <v>-82243</v>
       </c>
       <c r="Z40" t="n">
-        <v>-1828696</v>
+        <v>-64567</v>
       </c>
       <c r="AA40" t="n">
-        <v>-5121733</v>
+        <v>24494</v>
       </c>
       <c r="AB40" t="n">
-        <v>-30</v>
+        <v>-95</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5142,44 +5142,44 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>34.25</v>
+        <v>850</v>
       </c>
       <c r="D41" t="n">
-        <v>35.13</v>
+        <v>899</v>
       </c>
       <c r="E41" t="n">
-        <v>34.6</v>
+        <v>857.1</v>
       </c>
       <c r="F41" t="n">
-        <v>37.35</v>
+        <v>891.75</v>
       </c>
       <c r="G41" t="n">
-        <v>11138430</v>
+        <v>20528191</v>
       </c>
       <c r="H41" t="n">
-        <v>16177150</v>
+        <v>23222431</v>
       </c>
       <c r="I41" t="n">
-        <v>44.05</v>
+        <v>1035</v>
       </c>
       <c r="J41" t="n">
-        <v>31.1</v>
+        <v>765</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5187,55 +5187,55 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4124</v>
+        <v>-6076744</v>
       </c>
       <c r="M41" t="n">
-        <v>-7233994</v>
+        <v>-1783642</v>
       </c>
       <c r="N41" t="n">
-        <v>-6954756</v>
+        <v>-6898421</v>
       </c>
       <c r="O41" t="n">
-        <v>-2408707</v>
+        <v>-6805506</v>
       </c>
       <c r="P41" t="n">
-        <v>-128877</v>
+        <v>-4031693</v>
       </c>
       <c r="Q41" t="n">
-        <v>-7194828</v>
+        <v>1492436</v>
       </c>
       <c r="R41" t="n">
-        <v>-7085758</v>
+        <v>-2879037</v>
       </c>
       <c r="S41" t="n">
-        <v>-2314709</v>
+        <v>-1461358</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>-1987000</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>-3199000</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>-3964000</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>-4634000</v>
       </c>
       <c r="X41" t="n">
-        <v>133001</v>
+        <v>-58051</v>
       </c>
       <c r="Y41" t="n">
-        <v>-39166</v>
+        <v>-77078</v>
       </c>
       <c r="Z41" t="n">
-        <v>131002</v>
+        <v>-55384</v>
       </c>
       <c r="AA41" t="n">
-        <v>-93998</v>
+        <v>-710148</v>
       </c>
       <c r="AB41" t="n">
-        <v>-50</v>
+        <v>-95</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -5254,49 +5254,49 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1690</v>
+        <v>31.95</v>
       </c>
       <c r="D42" t="n">
-        <v>1697</v>
+        <v>34.23</v>
       </c>
       <c r="E42" t="n">
-        <v>1747</v>
+        <v>34.3</v>
       </c>
       <c r="F42" t="n">
-        <v>1612.75</v>
+        <v>36.68</v>
       </c>
       <c r="G42" t="n">
-        <v>3178000</v>
+        <v>9341790</v>
       </c>
       <c r="H42" t="n">
-        <v>3603600</v>
+        <v>14537039</v>
       </c>
       <c r="I42" t="n">
-        <v>1935</v>
+        <v>44.05</v>
       </c>
       <c r="J42" t="n">
-        <v>1190</v>
+        <v>31.1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5304,55 +5304,55 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-467151</v>
+        <v>-540034</v>
       </c>
       <c r="M42" t="n">
-        <v>-779449</v>
+        <v>-953680</v>
       </c>
       <c r="N42" t="n">
-        <v>-1431458</v>
+        <v>-8191798</v>
       </c>
       <c r="O42" t="n">
-        <v>-2655109</v>
+        <v>-6303647</v>
       </c>
       <c r="P42" t="n">
-        <v>-190195</v>
+        <v>-439035</v>
       </c>
       <c r="Q42" t="n">
-        <v>-247868</v>
+        <v>-987680</v>
       </c>
       <c r="R42" t="n">
-        <v>-528542</v>
+        <v>-8053631</v>
       </c>
       <c r="S42" t="n">
-        <v>-1615246</v>
+        <v>-6330648</v>
       </c>
       <c r="T42" t="n">
-        <v>-264617</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>-524617</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>-879117</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>-828848</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>-12339</v>
+        <v>-100999</v>
       </c>
       <c r="Y42" t="n">
-        <v>-6964</v>
+        <v>34000</v>
       </c>
       <c r="Z42" t="n">
-        <v>-23799</v>
+        <v>-138167</v>
       </c>
       <c r="AA42" t="n">
-        <v>-211015</v>
+        <v>27001</v>
       </c>
       <c r="AB42" t="n">
-        <v>-95</v>
+        <v>-110</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -5366,17 +5366,17 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -586,37 +586,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>357.5</v>
+        <v>289</v>
       </c>
       <c r="D2" t="n">
-        <v>326.8</v>
+        <v>267.2</v>
       </c>
       <c r="E2" t="n">
-        <v>285.1</v>
+        <v>256.7</v>
       </c>
       <c r="F2" t="n">
-        <v>255.22</v>
+        <v>251.78</v>
       </c>
       <c r="G2" t="n">
-        <v>83839978</v>
+        <v>289511198</v>
       </c>
       <c r="H2" t="n">
-        <v>45785817</v>
+        <v>124062360</v>
       </c>
       <c r="I2" t="n">
-        <v>374.5</v>
+        <v>289</v>
       </c>
       <c r="J2" t="n">
-        <v>201</v>
+        <v>223.5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -624,55 +624,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8636152</v>
+        <v>92379944</v>
       </c>
       <c r="M2" t="n">
-        <v>12325598</v>
+        <v>125329681</v>
       </c>
       <c r="N2" t="n">
-        <v>8250522</v>
+        <v>189474711</v>
       </c>
       <c r="O2" t="n">
-        <v>20110538</v>
+        <v>213910984</v>
       </c>
       <c r="P2" t="n">
-        <v>9558879</v>
+        <v>80338931</v>
       </c>
       <c r="Q2" t="n">
-        <v>12129730</v>
+        <v>112821030</v>
       </c>
       <c r="R2" t="n">
-        <v>10781087</v>
+        <v>174152829</v>
       </c>
       <c r="S2" t="n">
-        <v>23238328</v>
+        <v>201491861</v>
       </c>
       <c r="T2" t="n">
-        <v>-1044391</v>
+        <v>7423000</v>
       </c>
       <c r="U2" t="n">
-        <v>-329985</v>
+        <v>7687119</v>
       </c>
       <c r="V2" t="n">
-        <v>-3103985</v>
+        <v>8653189</v>
       </c>
       <c r="W2" t="n">
-        <v>-4195087</v>
+        <v>6234946</v>
       </c>
       <c r="X2" t="n">
-        <v>121664</v>
+        <v>4618013</v>
       </c>
       <c r="Y2" t="n">
-        <v>525853</v>
+        <v>4821532</v>
       </c>
       <c r="Z2" t="n">
-        <v>573420</v>
+        <v>6668693</v>
       </c>
       <c r="AA2" t="n">
-        <v>1067297</v>
+        <v>6184177</v>
       </c>
       <c r="AB2" t="n">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -686,17 +686,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -712,84 +712,84 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>337.5</v>
+        <v>370</v>
       </c>
       <c r="D3" t="n">
-        <v>333</v>
+        <v>342.5</v>
       </c>
       <c r="E3" t="n">
-        <v>324.55</v>
+        <v>328.9</v>
       </c>
       <c r="F3" t="n">
-        <v>314.5</v>
+        <v>319.35</v>
       </c>
       <c r="G3" t="n">
-        <v>17174957</v>
+        <v>33434927</v>
       </c>
       <c r="H3" t="n">
-        <v>13518022</v>
+        <v>17559688</v>
       </c>
       <c r="I3" t="n">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="J3" t="n">
         <v>270.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2492158</v>
+        <v>7493623</v>
       </c>
       <c r="M3" t="n">
-        <v>4279948</v>
+        <v>10724245</v>
       </c>
       <c r="N3" t="n">
-        <v>6392770</v>
+        <v>11892877</v>
       </c>
       <c r="O3" t="n">
-        <v>-517809</v>
+        <v>10697364</v>
       </c>
       <c r="P3" t="n">
-        <v>947946</v>
+        <v>5367725</v>
       </c>
       <c r="Q3" t="n">
-        <v>2503565</v>
+        <v>6731221</v>
       </c>
       <c r="R3" t="n">
-        <v>4027605</v>
+        <v>7222369</v>
       </c>
       <c r="S3" t="n">
-        <v>-5067732</v>
+        <v>4091598</v>
       </c>
       <c r="T3" t="n">
-        <v>1370157</v>
+        <v>1539024</v>
       </c>
       <c r="U3" t="n">
-        <v>1602157</v>
+        <v>3151181</v>
       </c>
       <c r="V3" t="n">
-        <v>2102078</v>
+        <v>3788181</v>
       </c>
       <c r="W3" t="n">
-        <v>5427449</v>
+        <v>6858102</v>
       </c>
       <c r="X3" t="n">
-        <v>174055</v>
+        <v>586874</v>
       </c>
       <c r="Y3" t="n">
-        <v>174226</v>
+        <v>841843</v>
       </c>
       <c r="Z3" t="n">
-        <v>263087</v>
+        <v>882327</v>
       </c>
       <c r="AA3" t="n">
-        <v>-877526</v>
+        <v>-252336</v>
       </c>
       <c r="AB3" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -813,100 +813,100 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48.83</v>
+        <v>608</v>
       </c>
       <c r="D4" t="n">
-        <v>48.3</v>
+        <v>559.8</v>
       </c>
       <c r="E4" t="n">
-        <v>46.39</v>
+        <v>513.6</v>
       </c>
       <c r="F4" t="n">
-        <v>45.22</v>
+        <v>478.25</v>
       </c>
       <c r="G4" t="n">
-        <v>62678749</v>
+        <v>20529000</v>
       </c>
       <c r="H4" t="n">
-        <v>59030542</v>
+        <v>7043000</v>
       </c>
       <c r="I4" t="n">
-        <v>50.1</v>
+        <v>608</v>
       </c>
       <c r="J4" t="n">
-        <v>40.81</v>
+        <v>368</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3280854</v>
+        <v>-81732</v>
       </c>
       <c r="M4" t="n">
-        <v>38947194</v>
+        <v>1447366</v>
       </c>
       <c r="N4" t="n">
-        <v>106433953</v>
+        <v>2637157</v>
       </c>
       <c r="O4" t="n">
-        <v>152143148</v>
+        <v>13098622</v>
       </c>
       <c r="P4" t="n">
-        <v>2848479</v>
+        <v>279224</v>
       </c>
       <c r="Q4" t="n">
-        <v>20506074</v>
+        <v>1723100</v>
       </c>
       <c r="R4" t="n">
-        <v>56692284</v>
+        <v>2983381</v>
       </c>
       <c r="S4" t="n">
-        <v>66513956</v>
+        <v>12970541</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="U4" t="n">
-        <v>1860000</v>
+        <v>13700</v>
       </c>
       <c r="V4" t="n">
-        <v>1860000</v>
+        <v>53500</v>
       </c>
       <c r="W4" t="n">
-        <v>3370000</v>
+        <v>83300</v>
       </c>
       <c r="X4" t="n">
-        <v>432375</v>
+        <v>-377956</v>
       </c>
       <c r="Y4" t="n">
-        <v>16581120</v>
+        <v>-289434</v>
       </c>
       <c r="Z4" t="n">
-        <v>47881669</v>
+        <v>-399724</v>
       </c>
       <c r="AA4" t="n">
-        <v>82259192</v>
+        <v>44781</v>
       </c>
       <c r="AB4" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,54 +920,54 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>553</v>
+        <v>2355</v>
       </c>
       <c r="D5" t="n">
-        <v>542.6</v>
+        <v>2306</v>
       </c>
       <c r="E5" t="n">
-        <v>491.75</v>
+        <v>2264.5</v>
       </c>
       <c r="F5" t="n">
-        <v>467.27</v>
+        <v>2263.25</v>
       </c>
       <c r="G5" t="n">
-        <v>4871000</v>
+        <v>104783831</v>
       </c>
       <c r="H5" t="n">
-        <v>3824000</v>
+        <v>49680374</v>
       </c>
       <c r="I5" t="n">
-        <v>578</v>
+        <v>2375</v>
       </c>
       <c r="J5" t="n">
-        <v>368</v>
+        <v>2185</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -975,55 +975,55 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>158732</v>
+        <v>14053662</v>
       </c>
       <c r="M5" t="n">
-        <v>2284475</v>
+        <v>17089924</v>
       </c>
       <c r="N5" t="n">
-        <v>4385902</v>
+        <v>17113436</v>
       </c>
       <c r="O5" t="n">
-        <v>14138913</v>
+        <v>2094231</v>
       </c>
       <c r="P5" t="n">
-        <v>237027</v>
+        <v>13284272</v>
       </c>
       <c r="Q5" t="n">
-        <v>2181838</v>
+        <v>15016579</v>
       </c>
       <c r="R5" t="n">
-        <v>4304374</v>
+        <v>11313611</v>
       </c>
       <c r="S5" t="n">
-        <v>13513579</v>
+        <v>-14722183</v>
       </c>
       <c r="T5" t="n">
-        <v>-1200</v>
+        <v>349249</v>
       </c>
       <c r="U5" t="n">
-        <v>-4500</v>
+        <v>815542</v>
       </c>
       <c r="V5" t="n">
-        <v>32100</v>
+        <v>4346753</v>
       </c>
       <c r="W5" t="n">
-        <v>-25700</v>
+        <v>14455783</v>
       </c>
       <c r="X5" t="n">
-        <v>-77095</v>
+        <v>420141</v>
       </c>
       <c r="Y5" t="n">
-        <v>107137</v>
+        <v>1257803</v>
       </c>
       <c r="Z5" t="n">
-        <v>49428</v>
+        <v>1453072</v>
       </c>
       <c r="AA5" t="n">
-        <v>651034</v>
+        <v>2360631</v>
       </c>
       <c r="AB5" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、爆量、接近20日高點</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1047,44 +1047,44 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>263</v>
+        <v>158</v>
       </c>
       <c r="D6" t="n">
-        <v>259.4</v>
+        <v>145.3</v>
       </c>
       <c r="E6" t="n">
-        <v>252.65</v>
+        <v>132.9</v>
       </c>
       <c r="F6" t="n">
-        <v>248.3</v>
+        <v>123.86</v>
       </c>
       <c r="G6" t="n">
-        <v>73792269</v>
+        <v>249880280</v>
       </c>
       <c r="H6" t="n">
-        <v>77422231</v>
+        <v>349036888</v>
       </c>
       <c r="I6" t="n">
-        <v>269.5</v>
+        <v>158</v>
       </c>
       <c r="J6" t="n">
-        <v>219.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1092,55 +1092,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12823739</v>
+        <v>71837337</v>
       </c>
       <c r="M6" t="n">
-        <v>41307455</v>
+        <v>49681962</v>
       </c>
       <c r="N6" t="n">
-        <v>118126120</v>
+        <v>181208140</v>
       </c>
       <c r="O6" t="n">
-        <v>186495441</v>
+        <v>176017792</v>
       </c>
       <c r="P6" t="n">
-        <v>12866010</v>
+        <v>53583084</v>
       </c>
       <c r="Q6" t="n">
-        <v>41761693</v>
+        <v>16623178</v>
       </c>
       <c r="R6" t="n">
-        <v>114628622</v>
+        <v>135587913</v>
       </c>
       <c r="S6" t="n">
-        <v>191610986</v>
+        <v>118913441</v>
       </c>
       <c r="T6" t="n">
-        <v>130253</v>
+        <v>17253000</v>
       </c>
       <c r="U6" t="n">
-        <v>18189</v>
+        <v>32779929</v>
       </c>
       <c r="V6" t="n">
-        <v>1145562</v>
+        <v>42395384</v>
       </c>
       <c r="W6" t="n">
-        <v>-3291773</v>
+        <v>54887111</v>
       </c>
       <c r="X6" t="n">
-        <v>-172524</v>
+        <v>1001253</v>
       </c>
       <c r="Y6" t="n">
-        <v>-472427</v>
+        <v>278855</v>
       </c>
       <c r="Z6" t="n">
-        <v>2351936</v>
+        <v>3224843</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1823772</v>
+        <v>2217240</v>
       </c>
       <c r="AB6" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -1180,28 +1180,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>30.76</v>
       </c>
       <c r="D7" t="n">
-        <v>29.58</v>
+        <v>30.08</v>
       </c>
       <c r="E7" t="n">
-        <v>28.53</v>
+        <v>28.81</v>
       </c>
       <c r="F7" t="n">
-        <v>27.95</v>
+        <v>28.21</v>
       </c>
       <c r="G7" t="n">
-        <v>90876706</v>
+        <v>71631385</v>
       </c>
       <c r="H7" t="n">
-        <v>104673717</v>
+        <v>99872752</v>
       </c>
       <c r="I7" t="n">
         <v>30.8</v>
       </c>
       <c r="J7" t="n">
-        <v>25.31</v>
+        <v>25.87</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>19641634</v>
+        <v>46044135</v>
       </c>
       <c r="M7" t="n">
-        <v>112895262</v>
+        <v>113946253</v>
       </c>
       <c r="N7" t="n">
-        <v>269876543</v>
+        <v>240984669</v>
       </c>
       <c r="O7" t="n">
-        <v>224551367</v>
+        <v>255508738</v>
       </c>
       <c r="P7" t="n">
-        <v>-2201530</v>
+        <v>20982164</v>
       </c>
       <c r="Q7" t="n">
-        <v>56675133</v>
+        <v>70088792</v>
       </c>
       <c r="R7" t="n">
-        <v>177701030</v>
+        <v>153032530</v>
       </c>
       <c r="S7" t="n">
-        <v>162064919</v>
+        <v>175977696</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1242,22 +1242,22 @@
         <v>2500000</v>
       </c>
       <c r="W7" t="n">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="X7" t="n">
-        <v>21843164</v>
+        <v>25061971</v>
       </c>
       <c r="Y7" t="n">
-        <v>56220129</v>
+        <v>43857461</v>
       </c>
       <c r="Z7" t="n">
-        <v>89675513</v>
+        <v>85452139</v>
       </c>
       <c r="AA7" t="n">
-        <v>57486448</v>
+        <v>77031042</v>
       </c>
       <c r="AB7" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1281,44 +1281,44 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>927</v>
+        <v>50.2</v>
       </c>
       <c r="D8" t="n">
-        <v>845.6</v>
+        <v>49.07</v>
       </c>
       <c r="E8" t="n">
-        <v>764</v>
+        <v>46.97</v>
       </c>
       <c r="F8" t="n">
-        <v>748.3</v>
+        <v>45.69</v>
       </c>
       <c r="G8" t="n">
-        <v>21729000</v>
+        <v>58208526</v>
       </c>
       <c r="H8" t="n">
-        <v>11989800</v>
+        <v>59310605</v>
       </c>
       <c r="I8" t="n">
-        <v>1020</v>
+        <v>50.25</v>
       </c>
       <c r="J8" t="n">
-        <v>558</v>
+        <v>41.51</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1326,55 +1326,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>226965</v>
+        <v>35418265</v>
       </c>
       <c r="M8" t="n">
-        <v>4981166</v>
+        <v>64123344</v>
       </c>
       <c r="N8" t="n">
-        <v>2961881</v>
+        <v>106751600</v>
       </c>
       <c r="O8" t="n">
-        <v>-736509</v>
+        <v>146936913</v>
       </c>
       <c r="P8" t="n">
-        <v>-1670205</v>
+        <v>20836464</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1575056</v>
+        <v>37308603</v>
       </c>
       <c r="R8" t="n">
-        <v>-4262492</v>
+        <v>67121483</v>
       </c>
       <c r="S8" t="n">
-        <v>-8147595</v>
+        <v>78993532</v>
       </c>
       <c r="T8" t="n">
-        <v>2147266</v>
+        <v>100000</v>
       </c>
       <c r="U8" t="n">
-        <v>6723095</v>
+        <v>2200000</v>
       </c>
       <c r="V8" t="n">
-        <v>6511483</v>
+        <v>1960000</v>
       </c>
       <c r="W8" t="n">
-        <v>6429761</v>
+        <v>2340000</v>
       </c>
       <c r="X8" t="n">
-        <v>-250096</v>
+        <v>14481801</v>
       </c>
       <c r="Y8" t="n">
-        <v>-166873</v>
+        <v>24614741</v>
       </c>
       <c r="Z8" t="n">
-        <v>712890</v>
+        <v>37670117</v>
       </c>
       <c r="AA8" t="n">
-        <v>981325</v>
+        <v>65603381</v>
       </c>
       <c r="AB8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1388,54 +1388,54 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>2445</v>
       </c>
       <c r="D9" t="n">
-        <v>309.2</v>
+        <v>2399</v>
       </c>
       <c r="E9" t="n">
-        <v>300.5</v>
+        <v>2197</v>
       </c>
       <c r="F9" t="n">
-        <v>292.05</v>
+        <v>2194</v>
       </c>
       <c r="G9" t="n">
-        <v>226715301</v>
+        <v>17179076</v>
       </c>
       <c r="H9" t="n">
-        <v>179912662</v>
+        <v>13409238</v>
       </c>
       <c r="I9" t="n">
-        <v>353</v>
+        <v>2585</v>
       </c>
       <c r="J9" t="n">
-        <v>214.5</v>
+        <v>1880</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>63504793</v>
+        <v>807932</v>
       </c>
       <c r="M9" t="n">
-        <v>72297780</v>
+        <v>2603797</v>
       </c>
       <c r="N9" t="n">
-        <v>58628689</v>
+        <v>10087865</v>
       </c>
       <c r="O9" t="n">
-        <v>-8182073</v>
+        <v>7462200</v>
       </c>
       <c r="P9" t="n">
-        <v>62166974</v>
+        <v>159559</v>
       </c>
       <c r="Q9" t="n">
-        <v>75244413</v>
+        <v>1933010</v>
       </c>
       <c r="R9" t="n">
-        <v>73633639</v>
+        <v>8590945</v>
       </c>
       <c r="S9" t="n">
-        <v>29396493</v>
+        <v>8247686</v>
       </c>
       <c r="T9" t="n">
-        <v>809330</v>
+        <v>604387</v>
       </c>
       <c r="U9" t="n">
-        <v>-2252395</v>
+        <v>779198</v>
       </c>
       <c r="V9" t="n">
-        <v>-14231560</v>
+        <v>1142598</v>
       </c>
       <c r="W9" t="n">
-        <v>-28669514</v>
+        <v>-255685</v>
       </c>
       <c r="X9" t="n">
-        <v>528489</v>
+        <v>43986</v>
       </c>
       <c r="Y9" t="n">
-        <v>-694238</v>
+        <v>-108411</v>
       </c>
       <c r="Z9" t="n">
-        <v>-773390</v>
+        <v>354322</v>
       </c>
       <c r="AA9" t="n">
-        <v>-8909052</v>
+        <v>-529801</v>
       </c>
       <c r="AB9" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1510,49 +1510,49 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>729</v>
       </c>
       <c r="D10" t="n">
-        <v>138.7</v>
+        <v>695.4</v>
       </c>
       <c r="E10" t="n">
-        <v>130.05</v>
+        <v>616.2</v>
       </c>
       <c r="F10" t="n">
-        <v>120.45</v>
+        <v>557.77</v>
       </c>
       <c r="G10" t="n">
-        <v>362557912</v>
+        <v>7357595</v>
       </c>
       <c r="H10" t="n">
-        <v>337690164</v>
+        <v>21034907</v>
       </c>
       <c r="I10" t="n">
-        <v>156.5</v>
+        <v>764</v>
       </c>
       <c r="J10" t="n">
-        <v>88.8</v>
+        <v>445.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,55 +1560,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-48079023</v>
+        <v>2189073</v>
       </c>
       <c r="M10" t="n">
-        <v>31718900</v>
+        <v>764248</v>
       </c>
       <c r="N10" t="n">
-        <v>161500593</v>
+        <v>8308749</v>
       </c>
       <c r="O10" t="n">
-        <v>123869559</v>
+        <v>13940091</v>
       </c>
       <c r="P10" t="n">
-        <v>-51733715</v>
+        <v>1727169</v>
       </c>
       <c r="Q10" t="n">
-        <v>9912821</v>
+        <v>-72044</v>
       </c>
       <c r="R10" t="n">
-        <v>133446833</v>
+        <v>4310104</v>
       </c>
       <c r="S10" t="n">
-        <v>62908432</v>
+        <v>8103447</v>
       </c>
       <c r="T10" t="n">
-        <v>4855777</v>
+        <v>-905</v>
       </c>
       <c r="U10" t="n">
-        <v>19891384</v>
+        <v>870572</v>
       </c>
       <c r="V10" t="n">
-        <v>23951353</v>
+        <v>4336572</v>
       </c>
       <c r="W10" t="n">
-        <v>62128185</v>
+        <v>5962046</v>
       </c>
       <c r="X10" t="n">
-        <v>-1201085</v>
+        <v>462809</v>
       </c>
       <c r="Y10" t="n">
-        <v>1914695</v>
+        <v>-34280</v>
       </c>
       <c r="Z10" t="n">
-        <v>4102407</v>
+        <v>-337927</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1167058</v>
+        <v>-125402</v>
       </c>
       <c r="AB10" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>681</v>
+        <v>1015</v>
       </c>
       <c r="D11" t="n">
-        <v>671.4</v>
+        <v>905.2</v>
       </c>
       <c r="E11" t="n">
-        <v>591.9</v>
+        <v>794.5</v>
       </c>
       <c r="F11" t="n">
-        <v>547.73</v>
+        <v>770.05</v>
       </c>
       <c r="G11" t="n">
-        <v>8187338</v>
+        <v>11189000</v>
       </c>
       <c r="H11" t="n">
-        <v>21854333</v>
+        <v>12916600</v>
       </c>
       <c r="I11" t="n">
-        <v>764</v>
+        <v>1020</v>
       </c>
       <c r="J11" t="n">
-        <v>445.5</v>
+        <v>597</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>-421266</v>
+        <v>1670438</v>
       </c>
       <c r="M11" t="n">
-        <v>5155057</v>
+        <v>7193475</v>
       </c>
       <c r="N11" t="n">
-        <v>7953030</v>
+        <v>6390247</v>
       </c>
       <c r="O11" t="n">
-        <v>19094924</v>
+        <v>1446388</v>
       </c>
       <c r="P11" t="n">
-        <v>-70413</v>
+        <v>344138</v>
       </c>
       <c r="Q11" t="n">
-        <v>2598341</v>
+        <v>-664171</v>
       </c>
       <c r="R11" t="n">
-        <v>3977718</v>
+        <v>-1656428</v>
       </c>
       <c r="S11" t="n">
-        <v>10632318</v>
+        <v>-7353618</v>
       </c>
       <c r="T11" t="n">
-        <v>2286</v>
+        <v>1146000</v>
       </c>
       <c r="U11" t="n">
-        <v>3178477</v>
+        <v>7953133</v>
       </c>
       <c r="V11" t="n">
-        <v>4921477</v>
+        <v>7798095</v>
       </c>
       <c r="W11" t="n">
-        <v>8369951</v>
+        <v>7456907</v>
       </c>
       <c r="X11" t="n">
-        <v>-353139</v>
+        <v>180300</v>
       </c>
       <c r="Y11" t="n">
-        <v>-621761</v>
+        <v>-95487</v>
       </c>
       <c r="Z11" t="n">
-        <v>-946165</v>
+        <v>248580</v>
       </c>
       <c r="AA11" t="n">
-        <v>92655</v>
+        <v>1343099</v>
       </c>
       <c r="AB11" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,54 +1739,54 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.51</v>
+        <v>347</v>
       </c>
       <c r="D12" t="n">
-        <v>7.88</v>
+        <v>316.5</v>
       </c>
       <c r="E12" t="n">
-        <v>6.81</v>
+        <v>304.05</v>
       </c>
       <c r="F12" t="n">
-        <v>6.29</v>
+        <v>298.62</v>
       </c>
       <c r="G12" t="n">
-        <v>233675744</v>
+        <v>140975644</v>
       </c>
       <c r="H12" t="n">
-        <v>151879141</v>
+        <v>176543954</v>
       </c>
       <c r="I12" t="n">
-        <v>9.25</v>
+        <v>353</v>
       </c>
       <c r="J12" t="n">
-        <v>5.55</v>
+        <v>217</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,55 +1794,55 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-18978969</v>
+        <v>24486580</v>
       </c>
       <c r="M12" t="n">
-        <v>-10779856</v>
+        <v>92243642</v>
       </c>
       <c r="N12" t="n">
-        <v>12903075</v>
+        <v>82863197</v>
       </c>
       <c r="O12" t="n">
-        <v>28289444</v>
+        <v>48518151</v>
       </c>
       <c r="P12" t="n">
-        <v>-18076800</v>
+        <v>19483386</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7476749</v>
+        <v>87397337</v>
       </c>
       <c r="R12" t="n">
-        <v>8329151</v>
+        <v>93426579</v>
       </c>
       <c r="S12" t="n">
-        <v>23803851</v>
+        <v>74922901</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4795000</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5562330</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-9187395</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-20828560</v>
       </c>
       <c r="X12" t="n">
-        <v>-902169</v>
+        <v>208194</v>
       </c>
       <c r="Y12" t="n">
-        <v>-3303107</v>
+        <v>-716025</v>
       </c>
       <c r="Z12" t="n">
-        <v>4573924</v>
+        <v>-1375987</v>
       </c>
       <c r="AA12" t="n">
-        <v>4485593</v>
+        <v>-5576190</v>
       </c>
       <c r="AB12" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,54 +1856,54 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1025</v>
+        <v>52.7</v>
       </c>
       <c r="D13" t="n">
-        <v>1030</v>
+        <v>52.28</v>
       </c>
       <c r="E13" t="n">
-        <v>933.3</v>
+        <v>51.39</v>
       </c>
       <c r="F13" t="n">
-        <v>905.55</v>
+        <v>50.59</v>
       </c>
       <c r="G13" t="n">
-        <v>25166670</v>
+        <v>29776823</v>
       </c>
       <c r="H13" t="n">
-        <v>30680111</v>
+        <v>24715593</v>
       </c>
       <c r="I13" t="n">
-        <v>1130</v>
+        <v>53.9</v>
       </c>
       <c r="J13" t="n">
-        <v>776</v>
+        <v>47.35</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>559160</v>
+        <v>7389461</v>
       </c>
       <c r="M13" t="n">
-        <v>13042301</v>
+        <v>24139514</v>
       </c>
       <c r="N13" t="n">
-        <v>19479925</v>
+        <v>19611659</v>
       </c>
       <c r="O13" t="n">
-        <v>19167141</v>
+        <v>46142113</v>
       </c>
       <c r="P13" t="n">
-        <v>344308</v>
+        <v>7588362</v>
       </c>
       <c r="Q13" t="n">
-        <v>9222374</v>
+        <v>25352759</v>
       </c>
       <c r="R13" t="n">
-        <v>15656886</v>
+        <v>21862491</v>
       </c>
       <c r="S13" t="n">
-        <v>16395121</v>
+        <v>46699655</v>
       </c>
       <c r="T13" t="n">
-        <v>469000</v>
+        <v>-337924</v>
       </c>
       <c r="U13" t="n">
-        <v>4409000</v>
+        <v>-1821392</v>
       </c>
       <c r="V13" t="n">
-        <v>4730843</v>
+        <v>-1815242</v>
       </c>
       <c r="W13" t="n">
-        <v>4177943</v>
+        <v>-1835308</v>
       </c>
       <c r="X13" t="n">
-        <v>-254148</v>
+        <v>139023</v>
       </c>
       <c r="Y13" t="n">
-        <v>-589073</v>
+        <v>608147</v>
       </c>
       <c r="Z13" t="n">
-        <v>-907804</v>
+        <v>-435590</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1405923</v>
+        <v>1277766</v>
       </c>
       <c r="AB13" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,54 +1973,54 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55.9</v>
+        <v>1690</v>
       </c>
       <c r="D14" t="n">
-        <v>55.8</v>
+        <v>1608</v>
       </c>
       <c r="E14" t="n">
-        <v>52.79</v>
+        <v>1451</v>
       </c>
       <c r="F14" t="n">
-        <v>51.28</v>
+        <v>1404</v>
       </c>
       <c r="G14" t="n">
-        <v>15689455</v>
+        <v>9688000</v>
       </c>
       <c r="H14" t="n">
-        <v>13166730</v>
+        <v>7520400</v>
       </c>
       <c r="I14" t="n">
-        <v>61.4</v>
+        <v>1735</v>
       </c>
       <c r="J14" t="n">
-        <v>45.45</v>
+        <v>1060</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2028,55 +2028,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-215295</v>
+        <v>1026806</v>
       </c>
       <c r="M14" t="n">
-        <v>894319</v>
+        <v>1458560</v>
       </c>
       <c r="N14" t="n">
-        <v>8238115</v>
+        <v>1657269</v>
       </c>
       <c r="O14" t="n">
-        <v>15157316</v>
+        <v>2868520</v>
       </c>
       <c r="P14" t="n">
-        <v>-255200</v>
+        <v>80409</v>
       </c>
       <c r="Q14" t="n">
-        <v>851649</v>
+        <v>-883531</v>
       </c>
       <c r="R14" t="n">
-        <v>7609098</v>
+        <v>-1794129</v>
       </c>
       <c r="S14" t="n">
-        <v>14264513</v>
+        <v>-598456</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>977000</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2608000</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4053000</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3920100</v>
       </c>
       <c r="X14" t="n">
-        <v>39905</v>
+        <v>-30603</v>
       </c>
       <c r="Y14" t="n">
-        <v>42670</v>
+        <v>-265909</v>
       </c>
       <c r="Z14" t="n">
-        <v>629017</v>
+        <v>-601602</v>
       </c>
       <c r="AA14" t="n">
-        <v>892803</v>
+        <v>-453124</v>
       </c>
       <c r="AB14" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2095,49 +2095,49 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2295</v>
+        <v>57.9</v>
       </c>
       <c r="D15" t="n">
-        <v>2286</v>
+        <v>56.5</v>
       </c>
       <c r="E15" t="n">
-        <v>2255.5</v>
+        <v>53.79</v>
       </c>
       <c r="F15" t="n">
-        <v>2252.25</v>
+        <v>51.82</v>
       </c>
       <c r="G15" t="n">
-        <v>42313277</v>
+        <v>10061343</v>
       </c>
       <c r="H15" t="n">
-        <v>34088235</v>
+        <v>13310924</v>
       </c>
       <c r="I15" t="n">
-        <v>2360</v>
+        <v>61.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2135</v>
+        <v>45.45</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,55 +2145,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-6147103</v>
+        <v>223942</v>
       </c>
       <c r="M15" t="n">
-        <v>-5211815</v>
+        <v>1174650</v>
       </c>
       <c r="N15" t="n">
-        <v>3515564</v>
+        <v>4573006</v>
       </c>
       <c r="O15" t="n">
-        <v>-19942901</v>
+        <v>9047822</v>
       </c>
       <c r="P15" t="n">
-        <v>-7078615</v>
+        <v>36212</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6016252</v>
+        <v>898012</v>
       </c>
       <c r="R15" t="n">
-        <v>-1237687</v>
+        <v>3887881</v>
       </c>
       <c r="S15" t="n">
-        <v>-41422107</v>
+        <v>8167725</v>
       </c>
       <c r="T15" t="n">
-        <v>465061</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-130996</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>3532656</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>19847971</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>466451</v>
+        <v>187730</v>
       </c>
       <c r="Y15" t="n">
-        <v>935433</v>
+        <v>276638</v>
       </c>
       <c r="Z15" t="n">
-        <v>1220595</v>
+        <v>685125</v>
       </c>
       <c r="AA15" t="n">
-        <v>1631235</v>
+        <v>880097</v>
       </c>
       <c r="AB15" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -2207,17 +2207,17 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -2233,28 +2233,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D16" t="n">
-        <v>302.8</v>
+        <v>307.4</v>
       </c>
       <c r="E16" t="n">
-        <v>291.15</v>
+        <v>297.05</v>
       </c>
       <c r="F16" t="n">
-        <v>269.85</v>
+        <v>275</v>
       </c>
       <c r="G16" t="n">
-        <v>30735473</v>
+        <v>26333214</v>
       </c>
       <c r="H16" t="n">
-        <v>29590486</v>
+        <v>28680323</v>
       </c>
       <c r="I16" t="n">
         <v>336.5</v>
       </c>
       <c r="J16" t="n">
-        <v>212.5</v>
+        <v>217.5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,55 +2262,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-719759</v>
+        <v>1768455</v>
       </c>
       <c r="M16" t="n">
-        <v>9819437</v>
+        <v>6314708</v>
       </c>
       <c r="N16" t="n">
-        <v>8970325</v>
+        <v>5650116</v>
       </c>
       <c r="O16" t="n">
-        <v>6462102</v>
+        <v>16803906</v>
       </c>
       <c r="P16" t="n">
-        <v>-574523</v>
+        <v>1507659</v>
       </c>
       <c r="Q16" t="n">
-        <v>8594692</v>
+        <v>5144713</v>
       </c>
       <c r="R16" t="n">
-        <v>10375879</v>
+        <v>5860298</v>
       </c>
       <c r="S16" t="n">
-        <v>13472643</v>
+        <v>18266729</v>
       </c>
       <c r="T16" t="n">
-        <v>20768</v>
+        <v>139000</v>
       </c>
       <c r="U16" t="n">
-        <v>1136768</v>
+        <v>1060768</v>
       </c>
       <c r="V16" t="n">
-        <v>-2075232</v>
+        <v>-313232</v>
       </c>
       <c r="W16" t="n">
-        <v>-6262208</v>
+        <v>-1807804</v>
       </c>
       <c r="X16" t="n">
-        <v>-166004</v>
+        <v>121796</v>
       </c>
       <c r="Y16" t="n">
-        <v>87977</v>
+        <v>109227</v>
       </c>
       <c r="Z16" t="n">
-        <v>669678</v>
+        <v>103050</v>
       </c>
       <c r="AA16" t="n">
-        <v>-748333</v>
+        <v>344981</v>
       </c>
       <c r="AB16" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2324,54 +2324,54 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>142</v>
+        <v>5445</v>
       </c>
       <c r="D17" t="n">
-        <v>131</v>
+        <v>5272</v>
       </c>
       <c r="E17" t="n">
-        <v>121.3</v>
+        <v>5212</v>
       </c>
       <c r="F17" t="n">
-        <v>106.98</v>
+        <v>5202.25</v>
       </c>
       <c r="G17" t="n">
-        <v>418286433</v>
+        <v>3282663</v>
       </c>
       <c r="H17" t="n">
-        <v>306975059</v>
+        <v>2442013</v>
       </c>
       <c r="I17" t="n">
-        <v>151</v>
+        <v>5880</v>
       </c>
       <c r="J17" t="n">
-        <v>76.3</v>
+        <v>4615</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-32086948</v>
+        <v>816883</v>
       </c>
       <c r="M17" t="n">
-        <v>22365239</v>
+        <v>261458</v>
       </c>
       <c r="N17" t="n">
-        <v>736511</v>
+        <v>180474</v>
       </c>
       <c r="O17" t="n">
-        <v>21737309</v>
+        <v>194961</v>
       </c>
       <c r="P17" t="n">
-        <v>59187</v>
+        <v>625866</v>
       </c>
       <c r="Q17" t="n">
-        <v>93459652</v>
+        <v>595836</v>
       </c>
       <c r="R17" t="n">
-        <v>111633222</v>
+        <v>788866</v>
       </c>
       <c r="S17" t="n">
-        <v>52418017</v>
+        <v>922420</v>
       </c>
       <c r="T17" t="n">
-        <v>-34484005</v>
+        <v>175961</v>
       </c>
       <c r="U17" t="n">
-        <v>-73186855</v>
+        <v>-136176</v>
       </c>
       <c r="V17" t="n">
-        <v>-119478006</v>
+        <v>-384349</v>
       </c>
       <c r="W17" t="n">
-        <v>-32041152</v>
+        <v>-550555</v>
       </c>
       <c r="X17" t="n">
-        <v>2337870</v>
+        <v>15056</v>
       </c>
       <c r="Y17" t="n">
-        <v>2092442</v>
+        <v>-198202</v>
       </c>
       <c r="Z17" t="n">
-        <v>8581295</v>
+        <v>-224043</v>
       </c>
       <c r="AA17" t="n">
-        <v>1360444</v>
+        <v>-176904</v>
       </c>
       <c r="AB17" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2446,49 +2446,49 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37.7</v>
+        <v>1055</v>
       </c>
       <c r="D18" t="n">
-        <v>36.91</v>
+        <v>1047</v>
       </c>
       <c r="E18" t="n">
-        <v>32.7</v>
+        <v>956.7</v>
       </c>
       <c r="F18" t="n">
-        <v>30.59</v>
+        <v>914.15</v>
       </c>
       <c r="G18" t="n">
-        <v>161629606</v>
+        <v>21107426</v>
       </c>
       <c r="H18" t="n">
-        <v>147852468</v>
+        <v>26475004</v>
       </c>
       <c r="I18" t="n">
-        <v>41.05</v>
+        <v>1130</v>
       </c>
       <c r="J18" t="n">
-        <v>26.65</v>
+        <v>776</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2496,55 +2496,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-6582455</v>
+        <v>-1460277</v>
       </c>
       <c r="M18" t="n">
-        <v>-3599130</v>
+        <v>-194509</v>
       </c>
       <c r="N18" t="n">
-        <v>22481194</v>
+        <v>12773317</v>
       </c>
       <c r="O18" t="n">
-        <v>80707566</v>
+        <v>18228150</v>
       </c>
       <c r="P18" t="n">
-        <v>-6901985</v>
+        <v>-1150135</v>
       </c>
       <c r="Q18" t="n">
-        <v>16026</v>
+        <v>-608166</v>
       </c>
       <c r="R18" t="n">
-        <v>30553810</v>
+        <v>9847208</v>
       </c>
       <c r="S18" t="n">
-        <v>94640620</v>
+        <v>15198203</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-225373</v>
       </c>
       <c r="U18" t="n">
-        <v>-2772000</v>
+        <v>1293627</v>
       </c>
       <c r="V18" t="n">
-        <v>-9607000</v>
+        <v>3733627</v>
       </c>
       <c r="W18" t="n">
-        <v>-17754000</v>
+        <v>4201470</v>
       </c>
       <c r="X18" t="n">
-        <v>319530</v>
+        <v>-84769</v>
       </c>
       <c r="Y18" t="n">
-        <v>-843156</v>
+        <v>-879970</v>
       </c>
       <c r="Z18" t="n">
-        <v>1534384</v>
+        <v>-807518</v>
       </c>
       <c r="AA18" t="n">
-        <v>3820946</v>
+        <v>-1171523</v>
       </c>
       <c r="AB18" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2558,54 +2558,54 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2390</v>
+        <v>379</v>
       </c>
       <c r="D19" t="n">
-        <v>2329</v>
+        <v>346</v>
       </c>
       <c r="E19" t="n">
-        <v>2160</v>
+        <v>298.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2180</v>
+        <v>264.02</v>
       </c>
       <c r="G19" t="n">
-        <v>11721062</v>
+        <v>17024627</v>
       </c>
       <c r="H19" t="n">
-        <v>11680295</v>
+        <v>47751060</v>
       </c>
       <c r="I19" t="n">
-        <v>2585</v>
+        <v>387</v>
       </c>
       <c r="J19" t="n">
-        <v>1880</v>
+        <v>208</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2613,55 +2613,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-2012884</v>
+        <v>-1530721</v>
       </c>
       <c r="M19" t="n">
-        <v>4362377</v>
+        <v>9386598</v>
       </c>
       <c r="N19" t="n">
-        <v>9095498</v>
+        <v>9329511</v>
       </c>
       <c r="O19" t="n">
-        <v>3705814</v>
+        <v>-4327114</v>
       </c>
       <c r="P19" t="n">
-        <v>-1742544</v>
+        <v>-1822021</v>
       </c>
       <c r="Q19" t="n">
-        <v>4100990</v>
+        <v>9593946</v>
       </c>
       <c r="R19" t="n">
-        <v>8309648</v>
+        <v>9756699</v>
       </c>
       <c r="S19" t="n">
-        <v>6636509</v>
+        <v>-654332</v>
       </c>
       <c r="T19" t="n">
-        <v>-121189</v>
+        <v>-99797</v>
       </c>
       <c r="U19" t="n">
-        <v>335711</v>
+        <v>-339782</v>
       </c>
       <c r="V19" t="n">
-        <v>426743</v>
+        <v>-1394782</v>
       </c>
       <c r="W19" t="n">
-        <v>-2434762</v>
+        <v>-4255884</v>
       </c>
       <c r="X19" t="n">
-        <v>-149151</v>
+        <v>391097</v>
       </c>
       <c r="Y19" t="n">
-        <v>-74324</v>
+        <v>132434</v>
       </c>
       <c r="Z19" t="n">
-        <v>359107</v>
+        <v>967594</v>
       </c>
       <c r="AA19" t="n">
-        <v>-495933</v>
+        <v>583102</v>
       </c>
       <c r="AB19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,54 +2675,54 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1540</v>
+        <v>41.65</v>
       </c>
       <c r="D20" t="n">
-        <v>1561</v>
+        <v>42.2</v>
       </c>
       <c r="E20" t="n">
-        <v>1412.5</v>
+        <v>41.59</v>
       </c>
       <c r="F20" t="n">
-        <v>1370</v>
+        <v>40.29</v>
       </c>
       <c r="G20" t="n">
-        <v>8654000</v>
+        <v>17386615</v>
       </c>
       <c r="H20" t="n">
-        <v>5919200</v>
+        <v>27652053</v>
       </c>
       <c r="I20" t="n">
-        <v>1735</v>
+        <v>44.75</v>
       </c>
       <c r="J20" t="n">
-        <v>968</v>
+        <v>37.45</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,116 +2730,116 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>236344</v>
+        <v>1337515</v>
       </c>
       <c r="M20" t="n">
-        <v>348209</v>
+        <v>14595424</v>
       </c>
       <c r="N20" t="n">
-        <v>1092463</v>
+        <v>18051673</v>
       </c>
       <c r="O20" t="n">
-        <v>1932192</v>
+        <v>34617848</v>
       </c>
       <c r="P20" t="n">
-        <v>-790831</v>
+        <v>1218184</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2064320</v>
+        <v>13702965</v>
       </c>
       <c r="R20" t="n">
-        <v>-1425598</v>
+        <v>18247222</v>
       </c>
       <c r="S20" t="n">
-        <v>-602470</v>
+        <v>39981740</v>
       </c>
       <c r="T20" t="n">
-        <v>1213000</v>
+        <v>-5000</v>
       </c>
       <c r="U20" t="n">
-        <v>3037000</v>
+        <v>-5000</v>
       </c>
       <c r="V20" t="n">
-        <v>3088700</v>
+        <v>-1134000</v>
       </c>
       <c r="W20" t="n">
-        <v>2947100</v>
+        <v>-2916000</v>
       </c>
       <c r="X20" t="n">
-        <v>-185825</v>
+        <v>124331</v>
       </c>
       <c r="Y20" t="n">
-        <v>-624471</v>
+        <v>897459</v>
       </c>
       <c r="Z20" t="n">
-        <v>-570639</v>
+        <v>938451</v>
       </c>
       <c r="AA20" t="n">
-        <v>-412438</v>
+        <v>-2447892</v>
       </c>
       <c r="AB20" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>41.75</v>
+        <v>36.05</v>
       </c>
       <c r="D21" t="n">
-        <v>42.26</v>
+        <v>35.36</v>
       </c>
       <c r="E21" t="n">
-        <v>41.4</v>
+        <v>35.05</v>
       </c>
       <c r="F21" t="n">
-        <v>40.1</v>
+        <v>34.92</v>
       </c>
       <c r="G21" t="n">
-        <v>18913490</v>
+        <v>122963731</v>
       </c>
       <c r="H21" t="n">
-        <v>29044968</v>
+        <v>81897844</v>
       </c>
       <c r="I21" t="n">
-        <v>44.75</v>
+        <v>36.7</v>
       </c>
       <c r="J21" t="n">
-        <v>37.45</v>
+        <v>33.4</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,55 +2847,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1422517</v>
+        <v>16457567</v>
       </c>
       <c r="M21" t="n">
-        <v>4592548</v>
+        <v>11483651</v>
       </c>
       <c r="N21" t="n">
-        <v>18295416</v>
+        <v>-4247964</v>
       </c>
       <c r="O21" t="n">
-        <v>89498884</v>
+        <v>-463942</v>
       </c>
       <c r="P21" t="n">
-        <v>3489136</v>
+        <v>-20469399</v>
       </c>
       <c r="Q21" t="n">
-        <v>5036903</v>
+        <v>-71180490</v>
       </c>
       <c r="R21" t="n">
-        <v>21128594</v>
+        <v>-112366470</v>
       </c>
       <c r="S21" t="n">
-        <v>97943601</v>
+        <v>-118820427</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>36156345</v>
       </c>
       <c r="U21" t="n">
-        <v>-509000</v>
+        <v>81328402</v>
       </c>
       <c r="V21" t="n">
-        <v>-1562000</v>
+        <v>105198860</v>
       </c>
       <c r="W21" t="n">
-        <v>-5668000</v>
+        <v>115502849</v>
       </c>
       <c r="X21" t="n">
-        <v>-2066619</v>
+        <v>770621</v>
       </c>
       <c r="Y21" t="n">
-        <v>64645</v>
+        <v>1335739</v>
       </c>
       <c r="Z21" t="n">
-        <v>-1271178</v>
+        <v>2919646</v>
       </c>
       <c r="AA21" t="n">
-        <v>-2776717</v>
+        <v>2853636</v>
       </c>
       <c r="AB21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -2909,54 +2909,54 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、成交量放大、接近20日高點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>52.3</v>
+        <v>5120</v>
       </c>
       <c r="D22" t="n">
-        <v>52.34</v>
+        <v>5255</v>
       </c>
       <c r="E22" t="n">
-        <v>50.92</v>
+        <v>4944.5</v>
       </c>
       <c r="F22" t="n">
-        <v>50.42</v>
+        <v>4890.25</v>
       </c>
       <c r="G22" t="n">
-        <v>16197736</v>
+        <v>3687942</v>
       </c>
       <c r="H22" t="n">
-        <v>27657898</v>
+        <v>2607763</v>
       </c>
       <c r="I22" t="n">
-        <v>53.9</v>
+        <v>5635</v>
       </c>
       <c r="J22" t="n">
-        <v>47.35</v>
+        <v>4300</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,55 +2964,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3526901</v>
+        <v>-36426</v>
       </c>
       <c r="M22" t="n">
-        <v>20060433</v>
+        <v>330831</v>
       </c>
       <c r="N22" t="n">
-        <v>29910167</v>
+        <v>485528</v>
       </c>
       <c r="O22" t="n">
-        <v>42084077</v>
+        <v>1407155</v>
       </c>
       <c r="P22" t="n">
-        <v>3235751</v>
+        <v>-148221</v>
       </c>
       <c r="Q22" t="n">
-        <v>21089420</v>
+        <v>67864</v>
       </c>
       <c r="R22" t="n">
-        <v>31246742</v>
+        <v>314229</v>
       </c>
       <c r="S22" t="n">
-        <v>42935899</v>
+        <v>1166557</v>
       </c>
       <c r="T22" t="n">
-        <v>232</v>
+        <v>91082</v>
       </c>
       <c r="U22" t="n">
-        <v>-1501318</v>
+        <v>283675</v>
       </c>
       <c r="V22" t="n">
-        <v>-1504284</v>
+        <v>204689</v>
       </c>
       <c r="W22" t="n">
-        <v>-1834912</v>
+        <v>241124</v>
       </c>
       <c r="X22" t="n">
-        <v>290918</v>
+        <v>20713</v>
       </c>
       <c r="Y22" t="n">
-        <v>472331</v>
+        <v>-20708</v>
       </c>
       <c r="Z22" t="n">
-        <v>167709</v>
+        <v>-33390</v>
       </c>
       <c r="AA22" t="n">
-        <v>983090</v>
+        <v>-526</v>
       </c>
       <c r="AB22" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -3026,54 +3026,54 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5055</v>
+        <v>17.1</v>
       </c>
       <c r="D23" t="n">
-        <v>5232</v>
+        <v>14.76</v>
       </c>
       <c r="E23" t="n">
-        <v>4894</v>
+        <v>12.68</v>
       </c>
       <c r="F23" t="n">
-        <v>4861.5</v>
+        <v>11.15</v>
       </c>
       <c r="G23" t="n">
-        <v>2289989</v>
+        <v>289351189</v>
       </c>
       <c r="H23" t="n">
-        <v>2477704</v>
+        <v>286226550</v>
       </c>
       <c r="I23" t="n">
-        <v>5635</v>
+        <v>17.1</v>
       </c>
       <c r="J23" t="n">
-        <v>4300</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,55 +3081,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-126362</v>
+        <v>5284295</v>
       </c>
       <c r="M23" t="n">
-        <v>162136</v>
+        <v>-6495197</v>
       </c>
       <c r="N23" t="n">
-        <v>1026293</v>
+        <v>-42554506</v>
       </c>
       <c r="O23" t="n">
-        <v>1614531</v>
+        <v>-20560923</v>
       </c>
       <c r="P23" t="n">
-        <v>-136280</v>
+        <v>4366136</v>
       </c>
       <c r="Q23" t="n">
-        <v>146118</v>
+        <v>-9860996</v>
       </c>
       <c r="R23" t="n">
-        <v>733772</v>
+        <v>-43704960</v>
       </c>
       <c r="S23" t="n">
-        <v>2127518</v>
+        <v>-22348485</v>
       </c>
       <c r="T23" t="n">
-        <v>48695</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>124607</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>344441</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-313301</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-38777</v>
+        <v>918159</v>
       </c>
       <c r="Y23" t="n">
-        <v>-108589</v>
+        <v>3365799</v>
       </c>
       <c r="Z23" t="n">
-        <v>-51920</v>
+        <v>1150454</v>
       </c>
       <c r="AA23" t="n">
-        <v>-199686</v>
+        <v>1787562</v>
       </c>
       <c r="AB23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -3143,54 +3143,54 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、5日法人明顯賣超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4410</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>4284</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>3801.5</v>
+        <v>69.08</v>
       </c>
       <c r="F24" t="n">
-        <v>3580.5</v>
+        <v>69.08</v>
       </c>
       <c r="G24" t="n">
-        <v>16433052</v>
+        <v>78210167</v>
       </c>
       <c r="H24" t="n">
-        <v>15938104</v>
+        <v>181489906</v>
       </c>
       <c r="I24" t="n">
-        <v>4690</v>
+        <v>81.2</v>
       </c>
       <c r="J24" t="n">
-        <v>2565</v>
+        <v>61.8</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,116 +3198,116 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1552083</v>
+        <v>-7646631</v>
       </c>
       <c r="M24" t="n">
-        <v>1269665</v>
+        <v>-16047176</v>
       </c>
       <c r="N24" t="n">
-        <v>-278472</v>
+        <v>33115701</v>
       </c>
       <c r="O24" t="n">
-        <v>-5121817</v>
+        <v>59475262</v>
       </c>
       <c r="P24" t="n">
-        <v>-856431</v>
+        <v>-8313549</v>
       </c>
       <c r="Q24" t="n">
-        <v>3508701</v>
+        <v>-17889466</v>
       </c>
       <c r="R24" t="n">
-        <v>763839</v>
+        <v>28430668</v>
       </c>
       <c r="S24" t="n">
-        <v>-2586431</v>
+        <v>52316556</v>
       </c>
       <c r="T24" t="n">
-        <v>-623680</v>
+        <v>-4000</v>
       </c>
       <c r="U24" t="n">
-        <v>-2501721</v>
+        <v>1576000</v>
       </c>
       <c r="V24" t="n">
-        <v>-1926160</v>
+        <v>2349000</v>
       </c>
       <c r="W24" t="n">
-        <v>-3313614</v>
+        <v>2360000</v>
       </c>
       <c r="X24" t="n">
-        <v>-71972</v>
+        <v>670918</v>
       </c>
       <c r="Y24" t="n">
-        <v>262685</v>
+        <v>266290</v>
       </c>
       <c r="Z24" t="n">
-        <v>883849</v>
+        <v>2336033</v>
       </c>
       <c r="AA24" t="n">
-        <v>778228</v>
+        <v>4798706</v>
       </c>
       <c r="AB24" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人賣超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>整理觀察：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>528</v>
+        <v>83.2</v>
       </c>
       <c r="D25" t="n">
-        <v>544.8</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>501.9</v>
+        <v>81.36</v>
       </c>
       <c r="F25" t="n">
-        <v>507.18</v>
+        <v>80.97</v>
       </c>
       <c r="G25" t="n">
-        <v>48754000</v>
+        <v>20794251</v>
       </c>
       <c r="H25" t="n">
-        <v>40401400</v>
+        <v>12683829</v>
       </c>
       <c r="I25" t="n">
-        <v>588</v>
+        <v>85.8</v>
       </c>
       <c r="J25" t="n">
-        <v>436</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,55 +3315,55 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-1273254</v>
+        <v>3075517</v>
       </c>
       <c r="M25" t="n">
-        <v>3514854</v>
+        <v>1838084</v>
       </c>
       <c r="N25" t="n">
-        <v>8239134</v>
+        <v>-1100465</v>
       </c>
       <c r="O25" t="n">
-        <v>10599873</v>
+        <v>-1405299</v>
       </c>
       <c r="P25" t="n">
-        <v>-789147</v>
+        <v>2692586</v>
       </c>
       <c r="Q25" t="n">
-        <v>2658940</v>
+        <v>1633452</v>
       </c>
       <c r="R25" t="n">
-        <v>4062818</v>
+        <v>-1080274</v>
       </c>
       <c r="S25" t="n">
-        <v>5103493</v>
+        <v>-1305248</v>
       </c>
       <c r="T25" t="n">
-        <v>-57163</v>
+        <v>-1000</v>
       </c>
       <c r="U25" t="n">
-        <v>476395</v>
+        <v>-1000</v>
       </c>
       <c r="V25" t="n">
-        <v>1790395</v>
+        <v>-1000</v>
       </c>
       <c r="W25" t="n">
-        <v>4017662</v>
+        <v>-1000</v>
       </c>
       <c r="X25" t="n">
-        <v>-426944</v>
+        <v>383931</v>
       </c>
       <c r="Y25" t="n">
-        <v>379519</v>
+        <v>205632</v>
       </c>
       <c r="Z25" t="n">
-        <v>2385921</v>
+        <v>-19191</v>
       </c>
       <c r="AA25" t="n">
-        <v>1478718</v>
+        <v>-99051</v>
       </c>
       <c r="AB25" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -3377,54 +3377,54 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>78.59999999999999</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
-        <v>81.78</v>
+        <v>22.48</v>
       </c>
       <c r="E26" t="n">
-        <v>81.26000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="F26" t="n">
-        <v>80.73</v>
+        <v>19.97</v>
       </c>
       <c r="G26" t="n">
-        <v>9188127</v>
+        <v>481574851</v>
       </c>
       <c r="H26" t="n">
-        <v>11612759</v>
+        <v>497424018</v>
       </c>
       <c r="I26" t="n">
-        <v>85.8</v>
+        <v>25.8</v>
       </c>
       <c r="J26" t="n">
-        <v>74.5</v>
+        <v>16.6</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,116 +3432,116 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-630748</v>
+        <v>69476213</v>
       </c>
       <c r="M26" t="n">
-        <v>-3684183</v>
+        <v>-20831523</v>
       </c>
       <c r="N26" t="n">
-        <v>2529535</v>
+        <v>-171352805</v>
       </c>
       <c r="O26" t="n">
-        <v>3650896</v>
+        <v>-131174467</v>
       </c>
       <c r="P26" t="n">
-        <v>-543485</v>
+        <v>66341339</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3419340</v>
+        <v>-22820955</v>
       </c>
       <c r="R26" t="n">
-        <v>2496590</v>
+        <v>-171088607</v>
       </c>
       <c r="S26" t="n">
-        <v>3814967</v>
+        <v>-134458080</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>90252</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>212198</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>201905</v>
       </c>
       <c r="X26" t="n">
-        <v>-87263</v>
+        <v>3125874</v>
       </c>
       <c r="Y26" t="n">
-        <v>-264843</v>
+        <v>1899180</v>
       </c>
       <c r="Z26" t="n">
-        <v>32945</v>
+        <v>-476396</v>
       </c>
       <c r="AA26" t="n">
-        <v>-164071</v>
+        <v>3081708</v>
       </c>
       <c r="AB26" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>81</v>
+        <v>144.5</v>
       </c>
       <c r="D27" t="n">
-        <v>82.56</v>
+        <v>137.1</v>
       </c>
       <c r="E27" t="n">
-        <v>76.73999999999999</v>
+        <v>124.75</v>
       </c>
       <c r="F27" t="n">
-        <v>69.09999999999999</v>
+        <v>110.34</v>
       </c>
       <c r="G27" t="n">
-        <v>41573738</v>
+        <v>366515715</v>
       </c>
       <c r="H27" t="n">
-        <v>42495385</v>
+        <v>339579178</v>
       </c>
       <c r="I27" t="n">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="J27" t="n">
-        <v>58.1</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3549,116 +3549,116 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-4660292</v>
+        <v>-56076862</v>
       </c>
       <c r="M27" t="n">
-        <v>349575</v>
+        <v>-86242883</v>
       </c>
       <c r="N27" t="n">
-        <v>3314453</v>
+        <v>-875000</v>
       </c>
       <c r="O27" t="n">
-        <v>12704407</v>
+        <v>-61795227</v>
       </c>
       <c r="P27" t="n">
-        <v>-3655765</v>
+        <v>-28218031</v>
       </c>
       <c r="Q27" t="n">
-        <v>1503819</v>
+        <v>-6628877</v>
       </c>
       <c r="R27" t="n">
-        <v>3751565</v>
+        <v>113761499</v>
       </c>
       <c r="S27" t="n">
-        <v>10597315</v>
+        <v>26118707</v>
       </c>
       <c r="T27" t="n">
+        <v>-28689967</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-82184801</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-123282822</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-95204333</v>
+      </c>
+      <c r="X27" t="n">
+        <v>831136</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2570795</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8646323</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>7290399</v>
+      </c>
+      <c r="AB27" t="n">
         <v>0</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>-1004527</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>-1154244</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>-437112</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2107092</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>35</v>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>70.40000000000001</v>
+        <v>51</v>
       </c>
       <c r="D28" t="n">
-        <v>71.95999999999999</v>
+        <v>48.48</v>
       </c>
       <c r="E28" t="n">
-        <v>68.39</v>
+        <v>44.08</v>
       </c>
       <c r="F28" t="n">
-        <v>68.84</v>
+        <v>37.84</v>
       </c>
       <c r="G28" t="n">
-        <v>152764187</v>
+        <v>897327645</v>
       </c>
       <c r="H28" t="n">
-        <v>190929390</v>
+        <v>1011819780</v>
       </c>
       <c r="I28" t="n">
-        <v>81.2</v>
+        <v>52.2</v>
       </c>
       <c r="J28" t="n">
-        <v>61.8</v>
+        <v>24.05</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,116 +3666,116 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-10583662</v>
+        <v>165040996</v>
       </c>
       <c r="M28" t="n">
-        <v>-3776166</v>
+        <v>-112547359</v>
       </c>
       <c r="N28" t="n">
-        <v>78224004</v>
+        <v>-335137590</v>
       </c>
       <c r="O28" t="n">
-        <v>52848701</v>
+        <v>-397552657</v>
       </c>
       <c r="P28" t="n">
-        <v>-10144891</v>
+        <v>163249451</v>
       </c>
       <c r="Q28" t="n">
-        <v>-6468392</v>
+        <v>-94432896</v>
       </c>
       <c r="R28" t="n">
-        <v>72776749</v>
+        <v>-301356148</v>
       </c>
       <c r="S28" t="n">
-        <v>45963423</v>
+        <v>-360917695</v>
       </c>
       <c r="T28" t="n">
-        <v>610000</v>
+        <v>7444</v>
       </c>
       <c r="U28" t="n">
-        <v>2342000</v>
+        <v>-5412779</v>
       </c>
       <c r="V28" t="n">
-        <v>2364000</v>
+        <v>-8125475</v>
       </c>
       <c r="W28" t="n">
-        <v>2385000</v>
+        <v>-7014264</v>
       </c>
       <c r="X28" t="n">
-        <v>-1048771</v>
+        <v>1784101</v>
       </c>
       <c r="Y28" t="n">
-        <v>350226</v>
+        <v>-12701684</v>
       </c>
       <c r="Z28" t="n">
-        <v>3083255</v>
+        <v>-25655967</v>
       </c>
       <c r="AA28" t="n">
-        <v>4500278</v>
+        <v>-29620698</v>
       </c>
       <c r="AB28" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>35.3</v>
+        <v>86.3</v>
       </c>
       <c r="D29" t="n">
-        <v>35.25</v>
+        <v>84.42</v>
       </c>
       <c r="E29" t="n">
-        <v>34.91</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>34.79</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>86240054</v>
+        <v>41007388</v>
       </c>
       <c r="H29" t="n">
-        <v>66352693</v>
+        <v>41397085</v>
       </c>
       <c r="I29" t="n">
-        <v>36.25</v>
+        <v>93</v>
       </c>
       <c r="J29" t="n">
-        <v>33.4</v>
+        <v>58.1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,116 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>13359346</v>
+        <v>-6462430</v>
       </c>
       <c r="M29" t="n">
-        <v>-13346318</v>
+        <v>-11504398</v>
       </c>
       <c r="N29" t="n">
-        <v>-19061112</v>
+        <v>-6893169</v>
       </c>
       <c r="O29" t="n">
-        <v>-16481991</v>
+        <v>-1205046</v>
       </c>
       <c r="P29" t="n">
-        <v>-15338438</v>
+        <v>-6057541</v>
       </c>
       <c r="Q29" t="n">
-        <v>-74761371</v>
+        <v>-9875925</v>
       </c>
       <c r="R29" t="n">
-        <v>-101225183</v>
+        <v>-5376500</v>
       </c>
       <c r="S29" t="n">
-        <v>-108489478</v>
+        <v>-1907685</v>
       </c>
       <c r="T29" t="n">
-        <v>28288924</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>59776845</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>79996232</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>90968017</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>408860</v>
+        <v>-404889</v>
       </c>
       <c r="Y29" t="n">
-        <v>1638208</v>
+        <v>-1628473</v>
       </c>
       <c r="Z29" t="n">
-        <v>2167839</v>
+        <v>-1516669</v>
       </c>
       <c r="AA29" t="n">
-        <v>1039470</v>
+        <v>702639</v>
       </c>
       <c r="AB29" t="n">
-        <v>25</v>
+        <v>-10</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>13.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>7.12</v>
       </c>
       <c r="F30" t="n">
-        <v>10.7</v>
+        <v>6.44</v>
       </c>
       <c r="G30" t="n">
-        <v>326422854</v>
+        <v>120114525</v>
       </c>
       <c r="H30" t="n">
-        <v>248577726</v>
+        <v>150006859</v>
       </c>
       <c r="I30" t="n">
-        <v>15.95</v>
+        <v>9.25</v>
       </c>
       <c r="J30" t="n">
-        <v>8.130000000000001</v>
+        <v>5.55</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>6591547</v>
+        <v>-8225970</v>
       </c>
       <c r="M30" t="n">
-        <v>-49947094</v>
+        <v>-21697710</v>
       </c>
       <c r="N30" t="n">
-        <v>-22532045</v>
+        <v>-13271904</v>
       </c>
       <c r="O30" t="n">
-        <v>-5997825</v>
+        <v>-999013</v>
       </c>
       <c r="P30" t="n">
-        <v>6246231</v>
+        <v>-8995000</v>
       </c>
       <c r="Q30" t="n">
-        <v>-48526796</v>
+        <v>-16819749</v>
       </c>
       <c r="R30" t="n">
-        <v>-23510329</v>
+        <v>-16143749</v>
       </c>
       <c r="S30" t="n">
-        <v>-7405832</v>
+        <v>-6217849</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -3936,80 +3936,80 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>345316</v>
+        <v>769030</v>
       </c>
       <c r="Y30" t="n">
-        <v>-1420298</v>
+        <v>-4877961</v>
       </c>
       <c r="Z30" t="n">
-        <v>978284</v>
+        <v>2871845</v>
       </c>
       <c r="AA30" t="n">
-        <v>1408007</v>
+        <v>5218836</v>
       </c>
       <c r="AB30" t="n">
-        <v>25</v>
+        <v>-10</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>627</v>
+        <v>1810</v>
       </c>
       <c r="D31" t="n">
-        <v>611.6</v>
+        <v>1717</v>
       </c>
       <c r="E31" t="n">
-        <v>557.3</v>
+        <v>1729</v>
       </c>
       <c r="F31" t="n">
-        <v>543.2</v>
+        <v>1680</v>
       </c>
       <c r="G31" t="n">
-        <v>35071941</v>
+        <v>5120000</v>
       </c>
       <c r="H31" t="n">
-        <v>32499570</v>
+        <v>4208800</v>
       </c>
       <c r="I31" t="n">
-        <v>669</v>
+        <v>1935</v>
       </c>
       <c r="J31" t="n">
-        <v>465</v>
+        <v>1270</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,55 +4017,55 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-2039263</v>
+        <v>129935</v>
       </c>
       <c r="M31" t="n">
-        <v>-3779445</v>
+        <v>-22256</v>
       </c>
       <c r="N31" t="n">
-        <v>-1751512</v>
+        <v>-841812</v>
       </c>
       <c r="O31" t="n">
-        <v>-7709520</v>
+        <v>-2031599</v>
       </c>
       <c r="P31" t="n">
-        <v>-2361460</v>
+        <v>-260532</v>
       </c>
       <c r="Q31" t="n">
-        <v>-2995996</v>
+        <v>-612470</v>
       </c>
       <c r="R31" t="n">
-        <v>-3433930</v>
+        <v>-816964</v>
       </c>
       <c r="S31" t="n">
-        <v>-11019195</v>
+        <v>-1606644</v>
       </c>
       <c r="T31" t="n">
-        <v>401204</v>
+        <v>356500</v>
       </c>
       <c r="U31" t="n">
-        <v>-315554</v>
+        <v>560740</v>
       </c>
       <c r="V31" t="n">
-        <v>2064129</v>
+        <v>-40877</v>
       </c>
       <c r="W31" t="n">
-        <v>3427727</v>
+        <v>-308710</v>
       </c>
       <c r="X31" t="n">
-        <v>-79007</v>
+        <v>33967</v>
       </c>
       <c r="Y31" t="n">
-        <v>-467895</v>
+        <v>29474</v>
       </c>
       <c r="Z31" t="n">
-        <v>-381711</v>
+        <v>16029</v>
       </c>
       <c r="AA31" t="n">
-        <v>-118052</v>
+        <v>-116245</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -4079,54 +4079,54 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>742</v>
+        <v>38.95</v>
       </c>
       <c r="D32" t="n">
-        <v>684.8</v>
+        <v>38.08</v>
       </c>
       <c r="E32" t="n">
-        <v>596.95</v>
+        <v>33.81</v>
       </c>
       <c r="F32" t="n">
-        <v>488.45</v>
+        <v>31.15</v>
       </c>
       <c r="G32" t="n">
-        <v>25023375</v>
+        <v>102606028</v>
       </c>
       <c r="H32" t="n">
-        <v>44221133</v>
+        <v>141383468</v>
       </c>
       <c r="I32" t="n">
-        <v>769</v>
+        <v>41.05</v>
       </c>
       <c r="J32" t="n">
-        <v>314</v>
+        <v>26.65</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,55 +4134,55 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-928538</v>
+        <v>-6910077</v>
       </c>
       <c r="M32" t="n">
-        <v>-5487929</v>
+        <v>-38867066</v>
       </c>
       <c r="N32" t="n">
-        <v>-31091</v>
+        <v>-330703</v>
       </c>
       <c r="O32" t="n">
-        <v>15313036</v>
+        <v>19072843</v>
       </c>
       <c r="P32" t="n">
-        <v>-1412412</v>
+        <v>-6951441</v>
       </c>
       <c r="Q32" t="n">
-        <v>-8554706</v>
+        <v>-37390805</v>
       </c>
       <c r="R32" t="n">
-        <v>-9550158</v>
+        <v>4656960</v>
       </c>
       <c r="S32" t="n">
-        <v>-20980250</v>
+        <v>29651379</v>
       </c>
       <c r="T32" t="n">
-        <v>26422</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>191630</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>5264079</v>
+        <v>-5544000</v>
       </c>
       <c r="W32" t="n">
-        <v>33822645</v>
+        <v>-12288000</v>
       </c>
       <c r="X32" t="n">
-        <v>457452</v>
+        <v>41364</v>
       </c>
       <c r="Y32" t="n">
-        <v>2875147</v>
+        <v>-1476261</v>
       </c>
       <c r="Z32" t="n">
-        <v>4254988</v>
+        <v>556337</v>
       </c>
       <c r="AA32" t="n">
-        <v>2470641</v>
+        <v>1709464</v>
       </c>
       <c r="AB32" t="n">
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -4201,49 +4201,49 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>21.2</v>
+        <v>284.5</v>
       </c>
       <c r="D33" t="n">
-        <v>22.32</v>
+        <v>281.7</v>
       </c>
       <c r="E33" t="n">
-        <v>20.8</v>
+        <v>271.45</v>
       </c>
       <c r="F33" t="n">
-        <v>19.68</v>
+        <v>261.52</v>
       </c>
       <c r="G33" t="n">
-        <v>538705306</v>
+        <v>84156366</v>
       </c>
       <c r="H33" t="n">
-        <v>479994202</v>
+        <v>93692827</v>
       </c>
       <c r="I33" t="n">
-        <v>25.8</v>
+        <v>305.5</v>
       </c>
       <c r="J33" t="n">
-        <v>16.6</v>
+        <v>233.5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,55 +4251,55 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-2648535</v>
+        <v>28384602</v>
       </c>
       <c r="M33" t="n">
-        <v>-259776941</v>
+        <v>-21588663</v>
       </c>
       <c r="N33" t="n">
-        <v>-207417252</v>
+        <v>-27955055</v>
       </c>
       <c r="O33" t="n">
-        <v>-51477021</v>
+        <v>28616720</v>
       </c>
       <c r="P33" t="n">
-        <v>-840692</v>
+        <v>28289321</v>
       </c>
       <c r="Q33" t="n">
-        <v>-255291833</v>
+        <v>-11423041</v>
       </c>
       <c r="R33" t="n">
-        <v>-209177412</v>
+        <v>-15045877</v>
       </c>
       <c r="S33" t="n">
-        <v>-50943264</v>
+        <v>34183158</v>
       </c>
       <c r="T33" t="n">
-        <v>85252</v>
+        <v>-387000</v>
       </c>
       <c r="U33" t="n">
-        <v>203198</v>
+        <v>-7289000</v>
       </c>
       <c r="V33" t="n">
-        <v>181961</v>
+        <v>-9830000</v>
       </c>
       <c r="W33" t="n">
-        <v>219906</v>
+        <v>-4081000</v>
       </c>
       <c r="X33" t="n">
-        <v>-1893095</v>
+        <v>482281</v>
       </c>
       <c r="Y33" t="n">
-        <v>-4688306</v>
+        <v>-2876622</v>
       </c>
       <c r="Z33" t="n">
-        <v>1578199</v>
+        <v>-3079178</v>
       </c>
       <c r="AA33" t="n">
-        <v>-753663</v>
+        <v>-1485438</v>
       </c>
       <c r="AB33" t="n">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -4313,54 +4313,54 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>486</v>
+        <v>738</v>
       </c>
       <c r="D34" t="n">
-        <v>520.6</v>
+        <v>706.6</v>
       </c>
       <c r="E34" t="n">
-        <v>470.95</v>
+        <v>625.2</v>
       </c>
       <c r="F34" t="n">
-        <v>446.38</v>
+        <v>509.5</v>
       </c>
       <c r="G34" t="n">
-        <v>20687337</v>
+        <v>28926802</v>
       </c>
       <c r="H34" t="n">
-        <v>41287562</v>
+        <v>35208144</v>
       </c>
       <c r="I34" t="n">
-        <v>568</v>
+        <v>784</v>
       </c>
       <c r="J34" t="n">
-        <v>372</v>
+        <v>314</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,55 +4368,55 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-2839782</v>
+        <v>-4621281</v>
       </c>
       <c r="M34" t="n">
-        <v>-4397424</v>
+        <v>-7685090</v>
       </c>
       <c r="N34" t="n">
-        <v>-10358149</v>
+        <v>-7877682</v>
       </c>
       <c r="O34" t="n">
-        <v>-5458601</v>
+        <v>634862</v>
       </c>
       <c r="P34" t="n">
-        <v>239975</v>
+        <v>-5437960</v>
       </c>
       <c r="Q34" t="n">
-        <v>760076</v>
+        <v>-10240633</v>
       </c>
       <c r="R34" t="n">
-        <v>-10126756</v>
+        <v>-14919628</v>
       </c>
       <c r="S34" t="n">
-        <v>-12301515</v>
+        <v>-20759430</v>
       </c>
       <c r="T34" t="n">
-        <v>-2618127</v>
+        <v>278110</v>
       </c>
       <c r="U34" t="n">
-        <v>-4684127</v>
+        <v>345532</v>
       </c>
       <c r="V34" t="n">
-        <v>403436</v>
+        <v>3427740</v>
       </c>
       <c r="W34" t="n">
-        <v>7324377</v>
+        <v>17737061</v>
       </c>
       <c r="X34" t="n">
-        <v>-461630</v>
+        <v>538569</v>
       </c>
       <c r="Y34" t="n">
-        <v>-473373</v>
+        <v>2210011</v>
       </c>
       <c r="Z34" t="n">
-        <v>-634829</v>
+        <v>3614206</v>
       </c>
       <c r="AA34" t="n">
-        <v>-481463</v>
+        <v>3657231</v>
       </c>
       <c r="AB34" t="n">
-        <v>-50</v>
+        <v>-35</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -4430,54 +4430,54 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4950</v>
+        <v>4310</v>
       </c>
       <c r="D35" t="n">
-        <v>5288</v>
+        <v>4374</v>
       </c>
       <c r="E35" t="n">
-        <v>5179</v>
+        <v>3906.5</v>
       </c>
       <c r="F35" t="n">
-        <v>5163.75</v>
+        <v>3665.5</v>
       </c>
       <c r="G35" t="n">
-        <v>2157834</v>
+        <v>23109791</v>
       </c>
       <c r="H35" t="n">
-        <v>2179434</v>
+        <v>16392169</v>
       </c>
       <c r="I35" t="n">
-        <v>5880</v>
+        <v>4690</v>
       </c>
       <c r="J35" t="n">
-        <v>4615</v>
+        <v>2870</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,55 +4485,55 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-106761</v>
+        <v>-3475601</v>
       </c>
       <c r="M35" t="n">
-        <v>-685968</v>
+        <v>-3182081</v>
       </c>
       <c r="N35" t="n">
-        <v>-534262</v>
+        <v>-4172313</v>
       </c>
       <c r="O35" t="n">
-        <v>-429822</v>
+        <v>-6209468</v>
       </c>
       <c r="P35" t="n">
-        <v>191035</v>
+        <v>-2324807</v>
       </c>
       <c r="Q35" t="n">
-        <v>96826</v>
+        <v>-183403</v>
       </c>
       <c r="R35" t="n">
-        <v>299521</v>
+        <v>9386</v>
       </c>
       <c r="S35" t="n">
-        <v>513578</v>
+        <v>-3126883</v>
       </c>
       <c r="T35" t="n">
-        <v>-191987</v>
+        <v>-1020510</v>
       </c>
       <c r="U35" t="n">
-        <v>-519310</v>
+        <v>-2923799</v>
       </c>
       <c r="V35" t="n">
-        <v>-625316</v>
+        <v>-4483231</v>
       </c>
       <c r="W35" t="n">
-        <v>-796310</v>
+        <v>-3560413</v>
       </c>
       <c r="X35" t="n">
-        <v>-105809</v>
+        <v>-130284</v>
       </c>
       <c r="Y35" t="n">
-        <v>-263484</v>
+        <v>-74879</v>
       </c>
       <c r="Z35" t="n">
-        <v>-208467</v>
+        <v>301532</v>
       </c>
       <c r="AA35" t="n">
-        <v>-147090</v>
+        <v>477828</v>
       </c>
       <c r="AB35" t="n">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4557,44 +4557,44 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>208.5</v>
+        <v>515</v>
       </c>
       <c r="D36" t="n">
-        <v>209.7</v>
+        <v>520.4</v>
       </c>
       <c r="E36" t="n">
-        <v>201.75</v>
+        <v>482.35</v>
       </c>
       <c r="F36" t="n">
-        <v>193.43</v>
+        <v>451.07</v>
       </c>
       <c r="G36" t="n">
-        <v>16061701</v>
+        <v>11454003</v>
       </c>
       <c r="H36" t="n">
-        <v>22429834</v>
+        <v>32912192</v>
       </c>
       <c r="I36" t="n">
-        <v>231</v>
+        <v>568</v>
       </c>
       <c r="J36" t="n">
-        <v>167</v>
+        <v>372</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,55 +4602,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2872949</v>
+        <v>857140</v>
       </c>
       <c r="M36" t="n">
-        <v>-2111061</v>
+        <v>-7205641</v>
       </c>
       <c r="N36" t="n">
-        <v>-4438019</v>
+        <v>-9256603</v>
       </c>
       <c r="O36" t="n">
-        <v>4364176</v>
+        <v>-6085533</v>
       </c>
       <c r="P36" t="n">
-        <v>2783989</v>
+        <v>1231521</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1328616</v>
+        <v>-1238676</v>
       </c>
       <c r="R36" t="n">
-        <v>-3797369</v>
+        <v>-4688336</v>
       </c>
       <c r="S36" t="n">
-        <v>3751038</v>
+        <v>-6625467</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>-836465</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>-5792592</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>-3969592</v>
       </c>
       <c r="W36" t="n">
-        <v>-57316</v>
+        <v>431976</v>
       </c>
       <c r="X36" t="n">
-        <v>88960</v>
+        <v>462084</v>
       </c>
       <c r="Y36" t="n">
-        <v>-782445</v>
+        <v>-174373</v>
       </c>
       <c r="Z36" t="n">
-        <v>-640650</v>
+        <v>-598675</v>
       </c>
       <c r="AA36" t="n">
-        <v>670454</v>
+        <v>107958</v>
       </c>
       <c r="AB36" t="n">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -4669,49 +4669,49 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46.4</v>
+        <v>207</v>
       </c>
       <c r="D37" t="n">
-        <v>47.21</v>
+        <v>208.9</v>
       </c>
       <c r="E37" t="n">
-        <v>42.59</v>
+        <v>203.45</v>
       </c>
       <c r="F37" t="n">
-        <v>36.49</v>
+        <v>195.38</v>
       </c>
       <c r="G37" t="n">
-        <v>1259689849</v>
+        <v>13700926</v>
       </c>
       <c r="H37" t="n">
-        <v>910026565</v>
+        <v>19496790</v>
       </c>
       <c r="I37" t="n">
-        <v>52.2</v>
+        <v>231</v>
       </c>
       <c r="J37" t="n">
-        <v>23.65</v>
+        <v>168.5</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,55 +4719,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-310027101</v>
+        <v>-2706458</v>
       </c>
       <c r="M37" t="n">
-        <v>-497513859</v>
+        <v>-1348885</v>
       </c>
       <c r="N37" t="n">
-        <v>-485465320</v>
+        <v>-5894259</v>
       </c>
       <c r="O37" t="n">
-        <v>-355479136</v>
+        <v>-6233139</v>
       </c>
       <c r="P37" t="n">
-        <v>-289338059</v>
+        <v>-2716140</v>
       </c>
       <c r="Q37" t="n">
-        <v>-460572143</v>
+        <v>-1301206</v>
       </c>
       <c r="R37" t="n">
-        <v>-452696703</v>
+        <v>-5499049</v>
       </c>
       <c r="S37" t="n">
-        <v>-322095879</v>
+        <v>-5960666</v>
       </c>
       <c r="T37" t="n">
-        <v>109777</v>
+        <v>2000</v>
       </c>
       <c r="U37" t="n">
-        <v>-8132919</v>
+        <v>2000</v>
       </c>
       <c r="V37" t="n">
-        <v>-8162808</v>
+        <v>2000</v>
       </c>
       <c r="W37" t="n">
-        <v>-7399130</v>
+        <v>-60316</v>
       </c>
       <c r="X37" t="n">
-        <v>-20798819</v>
+        <v>7682</v>
       </c>
       <c r="Y37" t="n">
-        <v>-28808797</v>
+        <v>-49679</v>
       </c>
       <c r="Z37" t="n">
-        <v>-24605809</v>
+        <v>-397210</v>
       </c>
       <c r="AA37" t="n">
-        <v>-25984127</v>
+        <v>-212157</v>
       </c>
       <c r="AB37" t="n">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -4781,54 +4781,54 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1700</v>
+        <v>611</v>
       </c>
       <c r="D38" t="n">
-        <v>1700</v>
+        <v>621.6</v>
       </c>
       <c r="E38" t="n">
-        <v>1724</v>
+        <v>563.7</v>
       </c>
       <c r="F38" t="n">
-        <v>1651.75</v>
+        <v>549.85</v>
       </c>
       <c r="G38" t="n">
-        <v>3905000</v>
+        <v>43968378</v>
       </c>
       <c r="H38" t="n">
-        <v>3809800</v>
+        <v>35056581</v>
       </c>
       <c r="I38" t="n">
-        <v>1935</v>
+        <v>669</v>
       </c>
       <c r="J38" t="n">
-        <v>1245</v>
+        <v>465</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,52 +4836,52 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>518754</v>
+        <v>-13838044</v>
       </c>
       <c r="M38" t="n">
-        <v>-619342</v>
+        <v>-15671425</v>
       </c>
       <c r="N38" t="n">
-        <v>-931640</v>
+        <v>-19564058</v>
       </c>
       <c r="O38" t="n">
-        <v>-2033871</v>
+        <v>-25170408</v>
       </c>
       <c r="P38" t="n">
-        <v>267535</v>
+        <v>-10101577</v>
       </c>
       <c r="Q38" t="n">
-        <v>-542133</v>
+        <v>-11629233</v>
       </c>
       <c r="R38" t="n">
-        <v>-599806</v>
+        <v>-16515209</v>
       </c>
       <c r="S38" t="n">
-        <v>-1089279</v>
+        <v>-23459381</v>
       </c>
       <c r="T38" t="n">
-        <v>247000</v>
+        <v>-3776094</v>
       </c>
       <c r="U38" t="n">
-        <v>-60377</v>
+        <v>-4048842</v>
       </c>
       <c r="V38" t="n">
-        <v>-320377</v>
+        <v>-2960648</v>
       </c>
       <c r="W38" t="n">
-        <v>-758210</v>
+        <v>-1432268</v>
       </c>
       <c r="X38" t="n">
-        <v>4219</v>
+        <v>39627</v>
       </c>
       <c r="Y38" t="n">
-        <v>-16832</v>
+        <v>6650</v>
       </c>
       <c r="Z38" t="n">
-        <v>-11457</v>
+        <v>-88201</v>
       </c>
       <c r="AA38" t="n">
-        <v>-186382</v>
+        <v>-278759</v>
       </c>
       <c r="AB38" t="n">
         <v>-60</v>
@@ -4898,54 +4898,54 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>259</v>
+        <v>527</v>
       </c>
       <c r="D39" t="n">
-        <v>280.4</v>
+        <v>544</v>
       </c>
       <c r="E39" t="n">
-        <v>266.55</v>
+        <v>508.75</v>
       </c>
       <c r="F39" t="n">
-        <v>259.52</v>
+        <v>506.73</v>
       </c>
       <c r="G39" t="n">
-        <v>114452978</v>
+        <v>26012000</v>
       </c>
       <c r="H39" t="n">
-        <v>96811115</v>
+        <v>39810000</v>
       </c>
       <c r="I39" t="n">
-        <v>305.5</v>
+        <v>588</v>
       </c>
       <c r="J39" t="n">
-        <v>227.5</v>
+        <v>436</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,55 +4953,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-39324591</v>
+        <v>-4446778</v>
       </c>
       <c r="M39" t="n">
-        <v>-67549430</v>
+        <v>-5175986</v>
       </c>
       <c r="N39" t="n">
-        <v>-24903658</v>
+        <v>-1641710</v>
       </c>
       <c r="O39" t="n">
-        <v>-20464849</v>
+        <v>3127410</v>
       </c>
       <c r="P39" t="n">
-        <v>-33742667</v>
+        <v>-2818118</v>
       </c>
       <c r="Q39" t="n">
-        <v>-52941212</v>
+        <v>-3426566</v>
       </c>
       <c r="R39" t="n">
-        <v>-14249850</v>
+        <v>-2679038</v>
       </c>
       <c r="S39" t="n">
-        <v>-12605493</v>
+        <v>-1518645</v>
       </c>
       <c r="T39" t="n">
-        <v>-3001000</v>
+        <v>-1490721</v>
       </c>
       <c r="U39" t="n">
-        <v>-10283000</v>
+        <v>-1184325</v>
       </c>
       <c r="V39" t="n">
-        <v>-9324000</v>
+        <v>-351326</v>
       </c>
       <c r="W39" t="n">
-        <v>-3905000</v>
+        <v>2432941</v>
       </c>
       <c r="X39" t="n">
-        <v>-2580924</v>
+        <v>-137939</v>
       </c>
       <c r="Y39" t="n">
-        <v>-4325218</v>
+        <v>-565095</v>
       </c>
       <c r="Z39" t="n">
-        <v>-1329808</v>
+        <v>1388654</v>
       </c>
       <c r="AA39" t="n">
-        <v>-3954356</v>
+        <v>2213114</v>
       </c>
       <c r="AB39" t="n">
-        <v>-60</v>
+        <v>-95</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -5015,17 +5015,17 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -5041,22 +5041,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="D40" t="n">
-        <v>1145</v>
+        <v>1122</v>
       </c>
       <c r="E40" t="n">
-        <v>1047.2</v>
+        <v>1055.2</v>
       </c>
       <c r="F40" t="n">
-        <v>1074.1</v>
+        <v>1068.35</v>
       </c>
       <c r="G40" t="n">
-        <v>3846000</v>
+        <v>3335000</v>
       </c>
       <c r="H40" t="n">
-        <v>5033200</v>
+        <v>4981400</v>
       </c>
       <c r="I40" t="n">
         <v>1300</v>
@@ -5070,52 +5070,52 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-403232</v>
+        <v>-758454</v>
       </c>
       <c r="M40" t="n">
-        <v>-1794757</v>
+        <v>-2632081</v>
       </c>
       <c r="N40" t="n">
-        <v>-3013007</v>
+        <v>-3568191</v>
       </c>
       <c r="O40" t="n">
-        <v>-3462863</v>
+        <v>-4121517</v>
       </c>
       <c r="P40" t="n">
-        <v>7822</v>
+        <v>-163282</v>
       </c>
       <c r="Q40" t="n">
-        <v>-256464</v>
+        <v>-346498</v>
       </c>
       <c r="R40" t="n">
-        <v>-2153390</v>
+        <v>-1599895</v>
       </c>
       <c r="S40" t="n">
-        <v>-2413307</v>
+        <v>-2472060</v>
       </c>
       <c r="T40" t="n">
-        <v>-404050</v>
+        <v>-593000</v>
       </c>
       <c r="U40" t="n">
-        <v>-1456050</v>
+        <v>-2259050</v>
       </c>
       <c r="V40" t="n">
-        <v>-795050</v>
+        <v>-1818050</v>
       </c>
       <c r="W40" t="n">
-        <v>-1074050</v>
+        <v>-1656050</v>
       </c>
       <c r="X40" t="n">
-        <v>-7004</v>
+        <v>-2172</v>
       </c>
       <c r="Y40" t="n">
-        <v>-82243</v>
+        <v>-26533</v>
       </c>
       <c r="Z40" t="n">
-        <v>-64567</v>
+        <v>-150246</v>
       </c>
       <c r="AA40" t="n">
-        <v>24494</v>
+        <v>6593</v>
       </c>
       <c r="AB40" t="n">
         <v>-95</v>
@@ -5158,22 +5158,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D41" t="n">
-        <v>899</v>
+        <v>881.8</v>
       </c>
       <c r="E41" t="n">
-        <v>857.1</v>
+        <v>863.3</v>
       </c>
       <c r="F41" t="n">
-        <v>891.75</v>
+        <v>883.9</v>
       </c>
       <c r="G41" t="n">
-        <v>20528191</v>
+        <v>17926232</v>
       </c>
       <c r="H41" t="n">
-        <v>23222431</v>
+        <v>23312290</v>
       </c>
       <c r="I41" t="n">
         <v>1035</v>
@@ -5187,52 +5187,52 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-6076744</v>
+        <v>-2448813</v>
       </c>
       <c r="M41" t="n">
-        <v>-1783642</v>
+        <v>-8778876</v>
       </c>
       <c r="N41" t="n">
-        <v>-6898421</v>
+        <v>-13138409</v>
       </c>
       <c r="O41" t="n">
-        <v>-6805506</v>
+        <v>-9532251</v>
       </c>
       <c r="P41" t="n">
-        <v>-4031693</v>
+        <v>43377</v>
       </c>
       <c r="Q41" t="n">
-        <v>1492436</v>
+        <v>-3411404</v>
       </c>
       <c r="R41" t="n">
-        <v>-2879037</v>
+        <v>-4691237</v>
       </c>
       <c r="S41" t="n">
-        <v>-1461358</v>
+        <v>-2926212</v>
       </c>
       <c r="T41" t="n">
-        <v>-1987000</v>
+        <v>-2413000</v>
       </c>
       <c r="U41" t="n">
-        <v>-3199000</v>
+        <v>-5192000</v>
       </c>
       <c r="V41" t="n">
-        <v>-3964000</v>
+        <v>-8133000</v>
       </c>
       <c r="W41" t="n">
-        <v>-4634000</v>
+        <v>-6368000</v>
       </c>
       <c r="X41" t="n">
-        <v>-58051</v>
+        <v>-79190</v>
       </c>
       <c r="Y41" t="n">
-        <v>-77078</v>
+        <v>-175472</v>
       </c>
       <c r="Z41" t="n">
-        <v>-55384</v>
+        <v>-314172</v>
       </c>
       <c r="AA41" t="n">
-        <v>-710148</v>
+        <v>-238039</v>
       </c>
       <c r="AB41" t="n">
         <v>-95</v>
@@ -5278,19 +5278,19 @@
         <v>31.95</v>
       </c>
       <c r="D42" t="n">
-        <v>34.23</v>
+        <v>33.46</v>
       </c>
       <c r="E42" t="n">
-        <v>34.3</v>
+        <v>34.07</v>
       </c>
       <c r="F42" t="n">
-        <v>36.68</v>
+        <v>36.33</v>
       </c>
       <c r="G42" t="n">
-        <v>9341790</v>
+        <v>7490299</v>
       </c>
       <c r="H42" t="n">
-        <v>14537039</v>
+        <v>10923227</v>
       </c>
       <c r="I42" t="n">
         <v>44.05</v>
@@ -5304,28 +5304,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-540034</v>
+        <v>-830875</v>
       </c>
       <c r="M42" t="n">
-        <v>-953680</v>
+        <v>-1788679</v>
       </c>
       <c r="N42" t="n">
-        <v>-8191798</v>
+        <v>-3454506</v>
       </c>
       <c r="O42" t="n">
-        <v>-6303647</v>
+        <v>-7506760</v>
       </c>
       <c r="P42" t="n">
-        <v>-439035</v>
+        <v>-673979</v>
       </c>
       <c r="Q42" t="n">
-        <v>-987680</v>
+        <v>-1532782</v>
       </c>
       <c r="R42" t="n">
-        <v>-8053631</v>
+        <v>-3330610</v>
       </c>
       <c r="S42" t="n">
-        <v>-6330648</v>
+        <v>-7206697</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -5340,16 +5340,16 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>-100999</v>
+        <v>-156896</v>
       </c>
       <c r="Y42" t="n">
-        <v>34000</v>
+        <v>-255897</v>
       </c>
       <c r="Z42" t="n">
-        <v>-138167</v>
+        <v>-123896</v>
       </c>
       <c r="AA42" t="n">
-        <v>27001</v>
+        <v>-300063</v>
       </c>
       <c r="AB42" t="n">
         <v>-110</v>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AG49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         <v>189474711</v>
       </c>
       <c r="O2" t="n">
-        <v>213910984</v>
+        <v>219494160</v>
       </c>
       <c r="P2" t="n">
         <v>80338931</v>
@@ -645,7 +645,7 @@
         <v>174152829</v>
       </c>
       <c r="S2" t="n">
-        <v>201491861</v>
+        <v>212775380</v>
       </c>
       <c r="T2" t="n">
         <v>7423000</v>
@@ -657,7 +657,7 @@
         <v>8653189</v>
       </c>
       <c r="W2" t="n">
-        <v>6234946</v>
+        <v>3745086</v>
       </c>
       <c r="X2" t="n">
         <v>4618013</v>
@@ -669,7 +669,7 @@
         <v>6668693</v>
       </c>
       <c r="AA2" t="n">
-        <v>6184177</v>
+        <v>2973694</v>
       </c>
       <c r="AB2" t="n">
         <v>195</v>
@@ -750,7 +750,7 @@
         <v>11892877</v>
       </c>
       <c r="O3" t="n">
-        <v>10697364</v>
+        <v>8232178</v>
       </c>
       <c r="P3" t="n">
         <v>5367725</v>
@@ -762,7 +762,7 @@
         <v>7222369</v>
       </c>
       <c r="S3" t="n">
-        <v>4091598</v>
+        <v>1597909</v>
       </c>
       <c r="T3" t="n">
         <v>1539024</v>
@@ -774,7 +774,7 @@
         <v>3788181</v>
       </c>
       <c r="W3" t="n">
-        <v>6858102</v>
+        <v>7002102</v>
       </c>
       <c r="X3" t="n">
         <v>586874</v>
@@ -786,7 +786,7 @@
         <v>882327</v>
       </c>
       <c r="AA3" t="n">
-        <v>-252336</v>
+        <v>-367833</v>
       </c>
       <c r="AB3" t="n">
         <v>180</v>
@@ -984,7 +984,7 @@
         <v>17113436</v>
       </c>
       <c r="O5" t="n">
-        <v>2094231</v>
+        <v>-5855754</v>
       </c>
       <c r="P5" t="n">
         <v>13284272</v>
@@ -996,7 +996,7 @@
         <v>11313611</v>
       </c>
       <c r="S5" t="n">
-        <v>-14722183</v>
+        <v>-24739310</v>
       </c>
       <c r="T5" t="n">
         <v>349249</v>
@@ -1008,7 +1008,7 @@
         <v>4346753</v>
       </c>
       <c r="W5" t="n">
-        <v>14455783</v>
+        <v>16811428</v>
       </c>
       <c r="X5" t="n">
         <v>420141</v>
@@ -1020,7 +1020,7 @@
         <v>1453072</v>
       </c>
       <c r="AA5" t="n">
-        <v>2360631</v>
+        <v>2072128</v>
       </c>
       <c r="AB5" t="n">
         <v>160</v>
@@ -1101,7 +1101,7 @@
         <v>181208140</v>
       </c>
       <c r="O6" t="n">
-        <v>176017792</v>
+        <v>153322650</v>
       </c>
       <c r="P6" t="n">
         <v>53583084</v>
@@ -1113,7 +1113,7 @@
         <v>135587913</v>
       </c>
       <c r="S6" t="n">
-        <v>118913441</v>
+        <v>100441793</v>
       </c>
       <c r="T6" t="n">
         <v>17253000</v>
@@ -1125,7 +1125,7 @@
         <v>42395384</v>
       </c>
       <c r="W6" t="n">
-        <v>54887111</v>
+        <v>53557111</v>
       </c>
       <c r="X6" t="n">
         <v>1001253</v>
@@ -1137,7 +1137,7 @@
         <v>3224843</v>
       </c>
       <c r="AA6" t="n">
-        <v>2217240</v>
+        <v>-676254</v>
       </c>
       <c r="AB6" t="n">
         <v>150</v>
@@ -1218,7 +1218,7 @@
         <v>240984669</v>
       </c>
       <c r="O7" t="n">
-        <v>255508738</v>
+        <v>309814450</v>
       </c>
       <c r="P7" t="n">
         <v>20982164</v>
@@ -1230,7 +1230,7 @@
         <v>153032530</v>
       </c>
       <c r="S7" t="n">
-        <v>175977696</v>
+        <v>215271412</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>85452139</v>
       </c>
       <c r="AA7" t="n">
-        <v>77031042</v>
+        <v>92043038</v>
       </c>
       <c r="AB7" t="n">
         <v>140</v>
@@ -1335,7 +1335,7 @@
         <v>106751600</v>
       </c>
       <c r="O8" t="n">
-        <v>146936913</v>
+        <v>186587594</v>
       </c>
       <c r="P8" t="n">
         <v>20836464</v>
@@ -1347,7 +1347,7 @@
         <v>67121483</v>
       </c>
       <c r="S8" t="n">
-        <v>78993532</v>
+        <v>96050133</v>
       </c>
       <c r="T8" t="n">
         <v>100000</v>
@@ -1359,7 +1359,7 @@
         <v>1960000</v>
       </c>
       <c r="W8" t="n">
-        <v>2340000</v>
+        <v>2240000</v>
       </c>
       <c r="X8" t="n">
         <v>14481801</v>
@@ -1371,7 +1371,7 @@
         <v>37670117</v>
       </c>
       <c r="AA8" t="n">
-        <v>65603381</v>
+        <v>88297461</v>
       </c>
       <c r="AB8" t="n">
         <v>140</v>
@@ -1452,7 +1452,7 @@
         <v>10087865</v>
       </c>
       <c r="O9" t="n">
-        <v>7462200</v>
+        <v>7022245</v>
       </c>
       <c r="P9" t="n">
         <v>159559</v>
@@ -1464,7 +1464,7 @@
         <v>8590945</v>
       </c>
       <c r="S9" t="n">
-        <v>8247686</v>
+        <v>8203923</v>
       </c>
       <c r="T9" t="n">
         <v>604387</v>
@@ -1476,7 +1476,7 @@
         <v>1142598</v>
       </c>
       <c r="W9" t="n">
-        <v>-255685</v>
+        <v>-1519176</v>
       </c>
       <c r="X9" t="n">
         <v>43986</v>
@@ -1488,7 +1488,7 @@
         <v>354322</v>
       </c>
       <c r="AA9" t="n">
-        <v>-529801</v>
+        <v>337498</v>
       </c>
       <c r="AB9" t="n">
         <v>135</v>
@@ -1522,37 +1522,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>729</v>
+        <v>22.8</v>
       </c>
       <c r="D10" t="n">
-        <v>695.4</v>
+        <v>19.54</v>
       </c>
       <c r="E10" t="n">
-        <v>616.2</v>
+        <v>18.19</v>
       </c>
       <c r="F10" t="n">
-        <v>557.77</v>
+        <v>17.56</v>
       </c>
       <c r="G10" t="n">
-        <v>7357595</v>
+        <v>18564858</v>
       </c>
       <c r="H10" t="n">
-        <v>21034907</v>
+        <v>37799302</v>
       </c>
       <c r="I10" t="n">
-        <v>764</v>
+        <v>22.8</v>
       </c>
       <c r="J10" t="n">
-        <v>445.5</v>
+        <v>16.55</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,55 +1560,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2189073</v>
+        <v>1404121</v>
       </c>
       <c r="M10" t="n">
-        <v>764248</v>
+        <v>2904196</v>
       </c>
       <c r="N10" t="n">
-        <v>8308749</v>
+        <v>12727687</v>
       </c>
       <c r="O10" t="n">
-        <v>13940091</v>
+        <v>21149602</v>
       </c>
       <c r="P10" t="n">
-        <v>1727169</v>
+        <v>-1010000</v>
       </c>
       <c r="Q10" t="n">
-        <v>-72044</v>
+        <v>-627327</v>
       </c>
       <c r="R10" t="n">
-        <v>4310104</v>
+        <v>8971673</v>
       </c>
       <c r="S10" t="n">
-        <v>8103447</v>
+        <v>17636025</v>
       </c>
       <c r="T10" t="n">
-        <v>-905</v>
+        <v>-4000</v>
       </c>
       <c r="U10" t="n">
-        <v>870572</v>
+        <v>-8000</v>
       </c>
       <c r="V10" t="n">
-        <v>4336572</v>
+        <v>-12000</v>
       </c>
       <c r="W10" t="n">
-        <v>5962046</v>
+        <v>486000</v>
       </c>
       <c r="X10" t="n">
-        <v>462809</v>
+        <v>2418121</v>
       </c>
       <c r="Y10" t="n">
-        <v>-34280</v>
+        <v>3539523</v>
       </c>
       <c r="Z10" t="n">
-        <v>-337927</v>
+        <v>3768014</v>
       </c>
       <c r="AA10" t="n">
-        <v>-125402</v>
+        <v>3027577</v>
       </c>
       <c r="AB10" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1015</v>
+        <v>729</v>
       </c>
       <c r="D11" t="n">
-        <v>905.2</v>
+        <v>695.4</v>
       </c>
       <c r="E11" t="n">
-        <v>794.5</v>
+        <v>616.2</v>
       </c>
       <c r="F11" t="n">
-        <v>770.05</v>
+        <v>557.77</v>
       </c>
       <c r="G11" t="n">
-        <v>11189000</v>
+        <v>7357595</v>
       </c>
       <c r="H11" t="n">
-        <v>12916600</v>
+        <v>21034907</v>
       </c>
       <c r="I11" t="n">
-        <v>1020</v>
+        <v>764</v>
       </c>
       <c r="J11" t="n">
-        <v>597</v>
+        <v>445.5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1670438</v>
+        <v>2189073</v>
       </c>
       <c r="M11" t="n">
-        <v>7193475</v>
+        <v>764248</v>
       </c>
       <c r="N11" t="n">
-        <v>6390247</v>
+        <v>8308749</v>
       </c>
       <c r="O11" t="n">
-        <v>1446388</v>
+        <v>27987628</v>
       </c>
       <c r="P11" t="n">
-        <v>344138</v>
+        <v>1727169</v>
       </c>
       <c r="Q11" t="n">
-        <v>-664171</v>
+        <v>-72044</v>
       </c>
       <c r="R11" t="n">
-        <v>-1656428</v>
+        <v>4310104</v>
       </c>
       <c r="S11" t="n">
-        <v>-7353618</v>
+        <v>19257046</v>
       </c>
       <c r="T11" t="n">
-        <v>1146000</v>
+        <v>-905</v>
       </c>
       <c r="U11" t="n">
-        <v>7953133</v>
+        <v>870572</v>
       </c>
       <c r="V11" t="n">
-        <v>7798095</v>
+        <v>4336572</v>
       </c>
       <c r="W11" t="n">
-        <v>7456907</v>
+        <v>7874046</v>
       </c>
       <c r="X11" t="n">
-        <v>180300</v>
+        <v>462809</v>
       </c>
       <c r="Y11" t="n">
-        <v>-95487</v>
+        <v>-34280</v>
       </c>
       <c r="Z11" t="n">
-        <v>248580</v>
+        <v>-337927</v>
       </c>
       <c r="AA11" t="n">
-        <v>1343099</v>
+        <v>856536</v>
       </c>
       <c r="AB11" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,54 +1739,54 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>347</v>
+        <v>1015</v>
       </c>
       <c r="D12" t="n">
-        <v>316.5</v>
+        <v>905.2</v>
       </c>
       <c r="E12" t="n">
-        <v>304.05</v>
+        <v>794.5</v>
       </c>
       <c r="F12" t="n">
-        <v>298.62</v>
+        <v>770.05</v>
       </c>
       <c r="G12" t="n">
-        <v>140975644</v>
+        <v>11189000</v>
       </c>
       <c r="H12" t="n">
-        <v>176543954</v>
+        <v>12916600</v>
       </c>
       <c r="I12" t="n">
-        <v>353</v>
+        <v>1020</v>
       </c>
       <c r="J12" t="n">
-        <v>217</v>
+        <v>597</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,52 +1794,52 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>24486580</v>
+        <v>1670438</v>
       </c>
       <c r="M12" t="n">
-        <v>92243642</v>
+        <v>7193475</v>
       </c>
       <c r="N12" t="n">
-        <v>82863197</v>
+        <v>6390247</v>
       </c>
       <c r="O12" t="n">
-        <v>48518151</v>
+        <v>1446388</v>
       </c>
       <c r="P12" t="n">
-        <v>19483386</v>
+        <v>344138</v>
       </c>
       <c r="Q12" t="n">
-        <v>87397337</v>
+        <v>-664171</v>
       </c>
       <c r="R12" t="n">
-        <v>93426579</v>
+        <v>-1656428</v>
       </c>
       <c r="S12" t="n">
-        <v>74922901</v>
+        <v>-7353618</v>
       </c>
       <c r="T12" t="n">
-        <v>4795000</v>
+        <v>1146000</v>
       </c>
       <c r="U12" t="n">
-        <v>5562330</v>
+        <v>7953133</v>
       </c>
       <c r="V12" t="n">
-        <v>-9187395</v>
+        <v>7798095</v>
       </c>
       <c r="W12" t="n">
-        <v>-20828560</v>
+        <v>7456907</v>
       </c>
       <c r="X12" t="n">
-        <v>208194</v>
+        <v>180300</v>
       </c>
       <c r="Y12" t="n">
-        <v>-716025</v>
+        <v>-95487</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1375987</v>
+        <v>248580</v>
       </c>
       <c r="AA12" t="n">
-        <v>-5576190</v>
+        <v>1343099</v>
       </c>
       <c r="AB12" t="n">
         <v>120</v>
@@ -1861,49 +1861,49 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>52.7</v>
+        <v>347</v>
       </c>
       <c r="D13" t="n">
-        <v>52.28</v>
+        <v>316.5</v>
       </c>
       <c r="E13" t="n">
-        <v>51.39</v>
+        <v>304.05</v>
       </c>
       <c r="F13" t="n">
-        <v>50.59</v>
+        <v>298.62</v>
       </c>
       <c r="G13" t="n">
-        <v>29776823</v>
+        <v>140975644</v>
       </c>
       <c r="H13" t="n">
-        <v>24715593</v>
+        <v>176543954</v>
       </c>
       <c r="I13" t="n">
-        <v>53.9</v>
+        <v>353</v>
       </c>
       <c r="J13" t="n">
-        <v>47.35</v>
+        <v>217</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7389461</v>
+        <v>24486580</v>
       </c>
       <c r="M13" t="n">
-        <v>24139514</v>
+        <v>92243642</v>
       </c>
       <c r="N13" t="n">
-        <v>19611659</v>
+        <v>82863197</v>
       </c>
       <c r="O13" t="n">
-        <v>46142113</v>
+        <v>41889398</v>
       </c>
       <c r="P13" t="n">
-        <v>7588362</v>
+        <v>19483386</v>
       </c>
       <c r="Q13" t="n">
-        <v>25352759</v>
+        <v>87397337</v>
       </c>
       <c r="R13" t="n">
-        <v>21862491</v>
+        <v>93426579</v>
       </c>
       <c r="S13" t="n">
-        <v>46699655</v>
+        <v>72607197</v>
       </c>
       <c r="T13" t="n">
-        <v>-337924</v>
+        <v>4795000</v>
       </c>
       <c r="U13" t="n">
-        <v>-1821392</v>
+        <v>5562330</v>
       </c>
       <c r="V13" t="n">
-        <v>-1815242</v>
+        <v>-9187395</v>
       </c>
       <c r="W13" t="n">
-        <v>-1835308</v>
+        <v>-23784560</v>
       </c>
       <c r="X13" t="n">
-        <v>139023</v>
+        <v>208194</v>
       </c>
       <c r="Y13" t="n">
-        <v>608147</v>
+        <v>-716025</v>
       </c>
       <c r="Z13" t="n">
-        <v>-435590</v>
+        <v>-1375987</v>
       </c>
       <c r="AA13" t="n">
-        <v>1277766</v>
+        <v>-6933239</v>
       </c>
       <c r="AB13" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -1983,44 +1983,44 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1690</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>1608</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1451</v>
+        <v>88.27</v>
       </c>
       <c r="F14" t="n">
-        <v>1404</v>
+        <v>88.78</v>
       </c>
       <c r="G14" t="n">
-        <v>9688000</v>
+        <v>150486779</v>
       </c>
       <c r="H14" t="n">
-        <v>7520400</v>
+        <v>99920545</v>
       </c>
       <c r="I14" t="n">
-        <v>1735</v>
+        <v>101.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1060</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2028,52 +2028,52 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1026806</v>
+        <v>63814268</v>
       </c>
       <c r="M14" t="n">
-        <v>1458560</v>
+        <v>84945508</v>
       </c>
       <c r="N14" t="n">
-        <v>1657269</v>
+        <v>122013685</v>
       </c>
       <c r="O14" t="n">
-        <v>2868520</v>
+        <v>106076369</v>
       </c>
       <c r="P14" t="n">
-        <v>80409</v>
+        <v>59319659</v>
       </c>
       <c r="Q14" t="n">
-        <v>-883531</v>
+        <v>79980257</v>
       </c>
       <c r="R14" t="n">
-        <v>-1794129</v>
+        <v>115454226</v>
       </c>
       <c r="S14" t="n">
-        <v>-598456</v>
+        <v>104358632</v>
       </c>
       <c r="T14" t="n">
-        <v>977000</v>
+        <v>2301457</v>
       </c>
       <c r="U14" t="n">
-        <v>2608000</v>
+        <v>3965189</v>
       </c>
       <c r="V14" t="n">
-        <v>4053000</v>
+        <v>2988189</v>
       </c>
       <c r="W14" t="n">
-        <v>3920100</v>
+        <v>2977289</v>
       </c>
       <c r="X14" t="n">
-        <v>-30603</v>
+        <v>2193152</v>
       </c>
       <c r="Y14" t="n">
-        <v>-265909</v>
+        <v>1000062</v>
       </c>
       <c r="Z14" t="n">
-        <v>-601602</v>
+        <v>3571270</v>
       </c>
       <c r="AA14" t="n">
-        <v>-453124</v>
+        <v>-1259552</v>
       </c>
       <c r="AB14" t="n">
         <v>115</v>
@@ -2090,54 +2090,54 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57.9</v>
+        <v>52.7</v>
       </c>
       <c r="D15" t="n">
-        <v>56.5</v>
+        <v>52.28</v>
       </c>
       <c r="E15" t="n">
-        <v>53.79</v>
+        <v>51.39</v>
       </c>
       <c r="F15" t="n">
-        <v>51.82</v>
+        <v>50.59</v>
       </c>
       <c r="G15" t="n">
-        <v>10061343</v>
+        <v>29776823</v>
       </c>
       <c r="H15" t="n">
-        <v>13310924</v>
+        <v>24715593</v>
       </c>
       <c r="I15" t="n">
-        <v>61.4</v>
+        <v>53.9</v>
       </c>
       <c r="J15" t="n">
-        <v>45.45</v>
+        <v>47.35</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,55 +2145,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>223942</v>
+        <v>7389461</v>
       </c>
       <c r="M15" t="n">
-        <v>1174650</v>
+        <v>24139514</v>
       </c>
       <c r="N15" t="n">
-        <v>4573006</v>
+        <v>19611659</v>
       </c>
       <c r="O15" t="n">
-        <v>9047822</v>
+        <v>55290712</v>
       </c>
       <c r="P15" t="n">
-        <v>36212</v>
+        <v>7588362</v>
       </c>
       <c r="Q15" t="n">
-        <v>898012</v>
+        <v>25352759</v>
       </c>
       <c r="R15" t="n">
-        <v>3887881</v>
+        <v>21862491</v>
       </c>
       <c r="S15" t="n">
-        <v>8167725</v>
+        <v>55769432</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-337924</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-1821392</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1815242</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-1896308</v>
       </c>
       <c r="X15" t="n">
-        <v>187730</v>
+        <v>139023</v>
       </c>
       <c r="Y15" t="n">
-        <v>276638</v>
+        <v>608147</v>
       </c>
       <c r="Z15" t="n">
-        <v>685125</v>
+        <v>-435590</v>
       </c>
       <c r="AA15" t="n">
-        <v>880097</v>
+        <v>1417588</v>
       </c>
       <c r="AB15" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -2207,54 +2207,54 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>319</v>
+        <v>1690</v>
       </c>
       <c r="D16" t="n">
-        <v>307.4</v>
+        <v>1608</v>
       </c>
       <c r="E16" t="n">
-        <v>297.05</v>
+        <v>1451</v>
       </c>
       <c r="F16" t="n">
-        <v>275</v>
+        <v>1404</v>
       </c>
       <c r="G16" t="n">
-        <v>26333214</v>
+        <v>9688000</v>
       </c>
       <c r="H16" t="n">
-        <v>28680323</v>
+        <v>7520400</v>
       </c>
       <c r="I16" t="n">
-        <v>336.5</v>
+        <v>1735</v>
       </c>
       <c r="J16" t="n">
-        <v>217.5</v>
+        <v>1060</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,55 +2262,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1768455</v>
+        <v>1026806</v>
       </c>
       <c r="M16" t="n">
-        <v>6314708</v>
+        <v>1458560</v>
       </c>
       <c r="N16" t="n">
-        <v>5650116</v>
+        <v>1657269</v>
       </c>
       <c r="O16" t="n">
-        <v>16803906</v>
+        <v>2868520</v>
       </c>
       <c r="P16" t="n">
-        <v>1507659</v>
+        <v>80409</v>
       </c>
       <c r="Q16" t="n">
-        <v>5144713</v>
+        <v>-883531</v>
       </c>
       <c r="R16" t="n">
-        <v>5860298</v>
+        <v>-1794129</v>
       </c>
       <c r="S16" t="n">
-        <v>18266729</v>
+        <v>-598456</v>
       </c>
       <c r="T16" t="n">
-        <v>139000</v>
+        <v>977000</v>
       </c>
       <c r="U16" t="n">
-        <v>1060768</v>
+        <v>2608000</v>
       </c>
       <c r="V16" t="n">
-        <v>-313232</v>
+        <v>4053000</v>
       </c>
       <c r="W16" t="n">
-        <v>-1807804</v>
+        <v>3920100</v>
       </c>
       <c r="X16" t="n">
-        <v>121796</v>
+        <v>-30603</v>
       </c>
       <c r="Y16" t="n">
-        <v>109227</v>
+        <v>-265909</v>
       </c>
       <c r="Z16" t="n">
-        <v>103050</v>
+        <v>-601602</v>
       </c>
       <c r="AA16" t="n">
-        <v>344981</v>
+        <v>-453124</v>
       </c>
       <c r="AB16" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2324,54 +2324,54 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>7769.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5445</v>
+        <v>8260</v>
       </c>
       <c r="D17" t="n">
-        <v>5272</v>
+        <v>7861</v>
       </c>
       <c r="E17" t="n">
-        <v>5212</v>
+        <v>7494.5</v>
       </c>
       <c r="F17" t="n">
-        <v>5202.25</v>
+        <v>6920.5</v>
       </c>
       <c r="G17" t="n">
-        <v>3282663</v>
+        <v>1880557</v>
       </c>
       <c r="H17" t="n">
-        <v>2442013</v>
+        <v>878607</v>
       </c>
       <c r="I17" t="n">
-        <v>5880</v>
+        <v>8465</v>
       </c>
       <c r="J17" t="n">
-        <v>4615</v>
+        <v>5030</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>816883</v>
+        <v>102468</v>
       </c>
       <c r="M17" t="n">
-        <v>261458</v>
+        <v>234245</v>
       </c>
       <c r="N17" t="n">
-        <v>180474</v>
+        <v>165465</v>
       </c>
       <c r="O17" t="n">
-        <v>194961</v>
+        <v>87623</v>
       </c>
       <c r="P17" t="n">
-        <v>625866</v>
+        <v>-49388</v>
       </c>
       <c r="Q17" t="n">
-        <v>595836</v>
+        <v>-273656</v>
       </c>
       <c r="R17" t="n">
-        <v>788866</v>
+        <v>-310537</v>
       </c>
       <c r="S17" t="n">
-        <v>922420</v>
+        <v>-250052</v>
       </c>
       <c r="T17" t="n">
-        <v>175961</v>
+        <v>160004</v>
       </c>
       <c r="U17" t="n">
-        <v>-136176</v>
+        <v>511004</v>
       </c>
       <c r="V17" t="n">
-        <v>-384349</v>
+        <v>471853</v>
       </c>
       <c r="W17" t="n">
-        <v>-550555</v>
+        <v>361853</v>
       </c>
       <c r="X17" t="n">
-        <v>15056</v>
+        <v>-8148</v>
       </c>
       <c r="Y17" t="n">
-        <v>-198202</v>
+        <v>-3103</v>
       </c>
       <c r="Z17" t="n">
-        <v>-224043</v>
+        <v>4149</v>
       </c>
       <c r="AA17" t="n">
-        <v>-176904</v>
+        <v>-24178</v>
       </c>
       <c r="AB17" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2441,54 +2441,54 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、爆量</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、法人連續偏買、5日法人買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1055</v>
+        <v>57.9</v>
       </c>
       <c r="D18" t="n">
-        <v>1047</v>
+        <v>56.5</v>
       </c>
       <c r="E18" t="n">
-        <v>956.7</v>
+        <v>53.79</v>
       </c>
       <c r="F18" t="n">
-        <v>914.15</v>
+        <v>51.82</v>
       </c>
       <c r="G18" t="n">
-        <v>21107426</v>
+        <v>10061343</v>
       </c>
       <c r="H18" t="n">
-        <v>26475004</v>
+        <v>13310924</v>
       </c>
       <c r="I18" t="n">
-        <v>1130</v>
+        <v>61.4</v>
       </c>
       <c r="J18" t="n">
-        <v>776</v>
+        <v>45.45</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2496,55 +2496,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1460277</v>
+        <v>223942</v>
       </c>
       <c r="M18" t="n">
-        <v>-194509</v>
+        <v>1174650</v>
       </c>
       <c r="N18" t="n">
-        <v>12773317</v>
+        <v>4573006</v>
       </c>
       <c r="O18" t="n">
-        <v>18228150</v>
+        <v>15563085</v>
       </c>
       <c r="P18" t="n">
-        <v>-1150135</v>
+        <v>36212</v>
       </c>
       <c r="Q18" t="n">
-        <v>-608166</v>
+        <v>898012</v>
       </c>
       <c r="R18" t="n">
-        <v>9847208</v>
+        <v>3887881</v>
       </c>
       <c r="S18" t="n">
-        <v>15198203</v>
+        <v>14415725</v>
       </c>
       <c r="T18" t="n">
-        <v>-225373</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1293627</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3733627</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4201470</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-84769</v>
+        <v>187730</v>
       </c>
       <c r="Y18" t="n">
-        <v>-879970</v>
+        <v>276638</v>
       </c>
       <c r="Z18" t="n">
-        <v>-807518</v>
+        <v>685125</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1171523</v>
+        <v>1147360</v>
       </c>
       <c r="AB18" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2563,49 +2563,49 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>379</v>
+        <v>5445</v>
       </c>
       <c r="D19" t="n">
-        <v>346</v>
+        <v>5272</v>
       </c>
       <c r="E19" t="n">
-        <v>298.2</v>
+        <v>5212</v>
       </c>
       <c r="F19" t="n">
-        <v>264.02</v>
+        <v>5202.25</v>
       </c>
       <c r="G19" t="n">
-        <v>17024627</v>
+        <v>3282663</v>
       </c>
       <c r="H19" t="n">
-        <v>47751060</v>
+        <v>2442013</v>
       </c>
       <c r="I19" t="n">
-        <v>387</v>
+        <v>5880</v>
       </c>
       <c r="J19" t="n">
-        <v>208</v>
+        <v>4615</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2613,55 +2613,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1530721</v>
+        <v>816883</v>
       </c>
       <c r="M19" t="n">
-        <v>9386598</v>
+        <v>261458</v>
       </c>
       <c r="N19" t="n">
-        <v>9329511</v>
+        <v>180474</v>
       </c>
       <c r="O19" t="n">
-        <v>-4327114</v>
+        <v>-14803</v>
       </c>
       <c r="P19" t="n">
-        <v>-1822021</v>
+        <v>625866</v>
       </c>
       <c r="Q19" t="n">
-        <v>9593946</v>
+        <v>595836</v>
       </c>
       <c r="R19" t="n">
-        <v>9756699</v>
+        <v>788866</v>
       </c>
       <c r="S19" t="n">
-        <v>-654332</v>
+        <v>679185</v>
       </c>
       <c r="T19" t="n">
-        <v>-99797</v>
+        <v>175961</v>
       </c>
       <c r="U19" t="n">
-        <v>-339782</v>
+        <v>-136176</v>
       </c>
       <c r="V19" t="n">
-        <v>-1394782</v>
+        <v>-384349</v>
       </c>
       <c r="W19" t="n">
-        <v>-4255884</v>
+        <v>-599555</v>
       </c>
       <c r="X19" t="n">
-        <v>391097</v>
+        <v>15056</v>
       </c>
       <c r="Y19" t="n">
-        <v>132434</v>
+        <v>-198202</v>
       </c>
       <c r="Z19" t="n">
-        <v>967594</v>
+        <v>-224043</v>
       </c>
       <c r="AA19" t="n">
-        <v>583102</v>
+        <v>-94433</v>
       </c>
       <c r="AB19" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,54 +2675,54 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41.65</v>
+        <v>319</v>
       </c>
       <c r="D20" t="n">
-        <v>42.2</v>
+        <v>307.4</v>
       </c>
       <c r="E20" t="n">
-        <v>41.59</v>
+        <v>297.05</v>
       </c>
       <c r="F20" t="n">
-        <v>40.29</v>
+        <v>275</v>
       </c>
       <c r="G20" t="n">
-        <v>17386615</v>
+        <v>26333214</v>
       </c>
       <c r="H20" t="n">
-        <v>27652053</v>
+        <v>28680323</v>
       </c>
       <c r="I20" t="n">
-        <v>44.75</v>
+        <v>336.5</v>
       </c>
       <c r="J20" t="n">
-        <v>37.45</v>
+        <v>217.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,69 +2730,69 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1337515</v>
+        <v>1768455</v>
       </c>
       <c r="M20" t="n">
-        <v>14595424</v>
+        <v>6314708</v>
       </c>
       <c r="N20" t="n">
-        <v>18051673</v>
+        <v>5650116</v>
       </c>
       <c r="O20" t="n">
-        <v>34617848</v>
+        <v>5110144</v>
       </c>
       <c r="P20" t="n">
-        <v>1218184</v>
+        <v>1507659</v>
       </c>
       <c r="Q20" t="n">
-        <v>13702965</v>
+        <v>5144713</v>
       </c>
       <c r="R20" t="n">
-        <v>18247222</v>
+        <v>5860298</v>
       </c>
       <c r="S20" t="n">
-        <v>39981740</v>
+        <v>11469805</v>
       </c>
       <c r="T20" t="n">
-        <v>-5000</v>
+        <v>139000</v>
       </c>
       <c r="U20" t="n">
-        <v>-5000</v>
+        <v>1060768</v>
       </c>
       <c r="V20" t="n">
-        <v>-1134000</v>
+        <v>-313232</v>
       </c>
       <c r="W20" t="n">
-        <v>-2916000</v>
+        <v>-6063208</v>
       </c>
       <c r="X20" t="n">
-        <v>124331</v>
+        <v>121796</v>
       </c>
       <c r="Y20" t="n">
-        <v>897459</v>
+        <v>109227</v>
       </c>
       <c r="Z20" t="n">
-        <v>938451</v>
+        <v>103050</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2447892</v>
+        <v>-296453</v>
       </c>
       <c r="AB20" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2802,44 +2802,44 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>36.05</v>
+        <v>1055</v>
       </c>
       <c r="D21" t="n">
-        <v>35.36</v>
+        <v>1047</v>
       </c>
       <c r="E21" t="n">
-        <v>35.05</v>
+        <v>956.7</v>
       </c>
       <c r="F21" t="n">
-        <v>34.92</v>
+        <v>914.15</v>
       </c>
       <c r="G21" t="n">
-        <v>122963731</v>
+        <v>21107426</v>
       </c>
       <c r="H21" t="n">
-        <v>81897844</v>
+        <v>26475004</v>
       </c>
       <c r="I21" t="n">
-        <v>36.7</v>
+        <v>1130</v>
       </c>
       <c r="J21" t="n">
-        <v>33.4</v>
+        <v>776</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,233 +2847,233 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>16457567</v>
+        <v>-1460277</v>
       </c>
       <c r="M21" t="n">
-        <v>11483651</v>
+        <v>-194509</v>
       </c>
       <c r="N21" t="n">
-        <v>-4247964</v>
+        <v>12773317</v>
       </c>
       <c r="O21" t="n">
-        <v>-463942</v>
+        <v>25914308</v>
       </c>
       <c r="P21" t="n">
-        <v>-20469399</v>
+        <v>-1150135</v>
       </c>
       <c r="Q21" t="n">
-        <v>-71180490</v>
+        <v>-608166</v>
       </c>
       <c r="R21" t="n">
-        <v>-112366470</v>
+        <v>9847208</v>
       </c>
       <c r="S21" t="n">
-        <v>-118820427</v>
+        <v>21378067</v>
       </c>
       <c r="T21" t="n">
-        <v>36156345</v>
+        <v>-225373</v>
       </c>
       <c r="U21" t="n">
-        <v>81328402</v>
+        <v>1293627</v>
       </c>
       <c r="V21" t="n">
-        <v>105198860</v>
+        <v>3733627</v>
       </c>
       <c r="W21" t="n">
-        <v>115502849</v>
+        <v>5098570</v>
       </c>
       <c r="X21" t="n">
-        <v>770621</v>
+        <v>-84769</v>
       </c>
       <c r="Y21" t="n">
-        <v>1335739</v>
+        <v>-879970</v>
       </c>
       <c r="Z21" t="n">
-        <v>2919646</v>
+        <v>-807518</v>
       </c>
       <c r="AA21" t="n">
-        <v>2853636</v>
+        <v>-562329</v>
       </c>
       <c r="AB21" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、成交量放大、接近20日高點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5120</v>
+        <v>834</v>
       </c>
       <c r="D22" t="n">
-        <v>5255</v>
+        <v>834.8</v>
       </c>
       <c r="E22" t="n">
-        <v>4944.5</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>4890.25</v>
+        <v>745.65</v>
       </c>
       <c r="G22" t="n">
-        <v>3687942</v>
+        <v>9119000</v>
       </c>
       <c r="H22" t="n">
-        <v>2607763</v>
+        <v>4059200</v>
       </c>
       <c r="I22" t="n">
-        <v>5635</v>
+        <v>929</v>
       </c>
       <c r="J22" t="n">
-        <v>4300</v>
+        <v>553</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-36426</v>
+        <v>725160</v>
       </c>
       <c r="M22" t="n">
-        <v>330831</v>
+        <v>2193908</v>
       </c>
       <c r="N22" t="n">
-        <v>485528</v>
+        <v>1256711</v>
       </c>
       <c r="O22" t="n">
-        <v>1407155</v>
+        <v>1527094</v>
       </c>
       <c r="P22" t="n">
-        <v>-148221</v>
+        <v>-520625</v>
       </c>
       <c r="Q22" t="n">
-        <v>67864</v>
+        <v>834333</v>
       </c>
       <c r="R22" t="n">
-        <v>314229</v>
+        <v>70799</v>
       </c>
       <c r="S22" t="n">
-        <v>1166557</v>
+        <v>357165</v>
       </c>
       <c r="T22" t="n">
-        <v>91082</v>
+        <v>1195000</v>
       </c>
       <c r="U22" t="n">
-        <v>283675</v>
+        <v>1192000</v>
       </c>
       <c r="V22" t="n">
-        <v>204689</v>
+        <v>995000</v>
       </c>
       <c r="W22" t="n">
-        <v>241124</v>
+        <v>976000</v>
       </c>
       <c r="X22" t="n">
-        <v>20713</v>
+        <v>50785</v>
       </c>
       <c r="Y22" t="n">
-        <v>-20708</v>
+        <v>167575</v>
       </c>
       <c r="Z22" t="n">
-        <v>-33390</v>
+        <v>190912</v>
       </c>
       <c r="AA22" t="n">
-        <v>-526</v>
+        <v>193929</v>
       </c>
       <c r="AB22" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：跌破5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.1</v>
+        <v>379</v>
       </c>
       <c r="D23" t="n">
-        <v>14.76</v>
+        <v>346</v>
       </c>
       <c r="E23" t="n">
-        <v>12.68</v>
+        <v>298.2</v>
       </c>
       <c r="F23" t="n">
-        <v>11.15</v>
+        <v>264.02</v>
       </c>
       <c r="G23" t="n">
-        <v>289351189</v>
+        <v>17024627</v>
       </c>
       <c r="H23" t="n">
-        <v>286226550</v>
+        <v>47751060</v>
       </c>
       <c r="I23" t="n">
-        <v>17.1</v>
+        <v>387</v>
       </c>
       <c r="J23" t="n">
-        <v>8.220000000000001</v>
+        <v>208</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,116 +3081,116 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5284295</v>
+        <v>-1530721</v>
       </c>
       <c r="M23" t="n">
-        <v>-6495197</v>
+        <v>9386598</v>
       </c>
       <c r="N23" t="n">
-        <v>-42554506</v>
+        <v>9329511</v>
       </c>
       <c r="O23" t="n">
-        <v>-20560923</v>
+        <v>2976549</v>
       </c>
       <c r="P23" t="n">
-        <v>4366136</v>
+        <v>-1822021</v>
       </c>
       <c r="Q23" t="n">
-        <v>-9860996</v>
+        <v>9593946</v>
       </c>
       <c r="R23" t="n">
-        <v>-43704960</v>
+        <v>9756699</v>
       </c>
       <c r="S23" t="n">
-        <v>-22348485</v>
+        <v>5846660</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-99797</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>-339782</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1394782</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-4249884</v>
       </c>
       <c r="X23" t="n">
-        <v>918159</v>
+        <v>391097</v>
       </c>
       <c r="Y23" t="n">
-        <v>3365799</v>
+        <v>132434</v>
       </c>
       <c r="Z23" t="n">
-        <v>1150454</v>
+        <v>967594</v>
       </c>
       <c r="AA23" t="n">
-        <v>1787562</v>
+        <v>1379773</v>
       </c>
       <c r="AB23" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、5日法人明顯賣超。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>71.90000000000001</v>
+        <v>41.65</v>
       </c>
       <c r="D24" t="n">
-        <v>72.23999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="E24" t="n">
-        <v>69.08</v>
+        <v>41.59</v>
       </c>
       <c r="F24" t="n">
-        <v>69.08</v>
+        <v>40.29</v>
       </c>
       <c r="G24" t="n">
-        <v>78210167</v>
+        <v>17386615</v>
       </c>
       <c r="H24" t="n">
-        <v>181489906</v>
+        <v>27652053</v>
       </c>
       <c r="I24" t="n">
-        <v>81.2</v>
+        <v>44.75</v>
       </c>
       <c r="J24" t="n">
-        <v>61.8</v>
+        <v>37.45</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,116 +3198,116 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-7646631</v>
+        <v>1337515</v>
       </c>
       <c r="M24" t="n">
-        <v>-16047176</v>
+        <v>14595424</v>
       </c>
       <c r="N24" t="n">
-        <v>33115701</v>
+        <v>18051673</v>
       </c>
       <c r="O24" t="n">
-        <v>59475262</v>
+        <v>68742480</v>
       </c>
       <c r="P24" t="n">
-        <v>-8313549</v>
+        <v>1218184</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17889466</v>
+        <v>13702965</v>
       </c>
       <c r="R24" t="n">
-        <v>28430668</v>
+        <v>18247222</v>
       </c>
       <c r="S24" t="n">
-        <v>52316556</v>
+        <v>76134911</v>
       </c>
       <c r="T24" t="n">
-        <v>-4000</v>
+        <v>-5000</v>
       </c>
       <c r="U24" t="n">
-        <v>1576000</v>
+        <v>-5000</v>
       </c>
       <c r="V24" t="n">
-        <v>2349000</v>
+        <v>-1134000</v>
       </c>
       <c r="W24" t="n">
-        <v>2360000</v>
+        <v>-4558000</v>
       </c>
       <c r="X24" t="n">
-        <v>670918</v>
+        <v>124331</v>
       </c>
       <c r="Y24" t="n">
-        <v>266290</v>
+        <v>897459</v>
       </c>
       <c r="Z24" t="n">
-        <v>2336033</v>
+        <v>938451</v>
       </c>
       <c r="AA24" t="n">
-        <v>4798706</v>
+        <v>-2834431</v>
       </c>
       <c r="AB24" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>83.2</v>
+        <v>5120</v>
       </c>
       <c r="D25" t="n">
-        <v>81.73999999999999</v>
+        <v>5255</v>
       </c>
       <c r="E25" t="n">
-        <v>81.36</v>
+        <v>4944.5</v>
       </c>
       <c r="F25" t="n">
-        <v>80.97</v>
+        <v>4890.25</v>
       </c>
       <c r="G25" t="n">
-        <v>20794251</v>
+        <v>3687942</v>
       </c>
       <c r="H25" t="n">
-        <v>12683829</v>
+        <v>2607763</v>
       </c>
       <c r="I25" t="n">
-        <v>85.8</v>
+        <v>5635</v>
       </c>
       <c r="J25" t="n">
-        <v>77.09999999999999</v>
+        <v>4300</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,116 +3315,116 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3075517</v>
+        <v>-36426</v>
       </c>
       <c r="M25" t="n">
-        <v>1838084</v>
+        <v>330831</v>
       </c>
       <c r="N25" t="n">
-        <v>-1100465</v>
+        <v>485528</v>
       </c>
       <c r="O25" t="n">
-        <v>-1405299</v>
+        <v>1932087</v>
       </c>
       <c r="P25" t="n">
-        <v>2692586</v>
+        <v>-148221</v>
       </c>
       <c r="Q25" t="n">
-        <v>1633452</v>
+        <v>67864</v>
       </c>
       <c r="R25" t="n">
-        <v>-1080274</v>
+        <v>314229</v>
       </c>
       <c r="S25" t="n">
-        <v>-1305248</v>
+        <v>2085929</v>
       </c>
       <c r="T25" t="n">
-        <v>-1000</v>
+        <v>91082</v>
       </c>
       <c r="U25" t="n">
-        <v>-1000</v>
+        <v>283675</v>
       </c>
       <c r="V25" t="n">
-        <v>-1000</v>
+        <v>204689</v>
       </c>
       <c r="W25" t="n">
-        <v>-1000</v>
+        <v>-43363</v>
       </c>
       <c r="X25" t="n">
-        <v>383931</v>
+        <v>20713</v>
       </c>
       <c r="Y25" t="n">
-        <v>205632</v>
+        <v>-20708</v>
       </c>
       <c r="Z25" t="n">
-        <v>-19191</v>
+        <v>-33390</v>
       </c>
       <c r="AA25" t="n">
-        <v>-99051</v>
+        <v>-110479</v>
       </c>
       <c r="AB25" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>36.05</v>
       </c>
       <c r="D26" t="n">
-        <v>22.48</v>
+        <v>35.36</v>
       </c>
       <c r="E26" t="n">
-        <v>21.2</v>
+        <v>35.05</v>
       </c>
       <c r="F26" t="n">
-        <v>19.97</v>
+        <v>34.92</v>
       </c>
       <c r="G26" t="n">
-        <v>481574851</v>
+        <v>122963731</v>
       </c>
       <c r="H26" t="n">
-        <v>497424018</v>
+        <v>81897844</v>
       </c>
       <c r="I26" t="n">
-        <v>25.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>16.6</v>
+        <v>33.4</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,69 +3432,69 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>69476213</v>
+        <v>16457567</v>
       </c>
       <c r="M26" t="n">
-        <v>-20831523</v>
+        <v>11483651</v>
       </c>
       <c r="N26" t="n">
-        <v>-171352805</v>
+        <v>-4247964</v>
       </c>
       <c r="O26" t="n">
-        <v>-131174467</v>
+        <v>5314718</v>
       </c>
       <c r="P26" t="n">
-        <v>66341339</v>
+        <v>-20469399</v>
       </c>
       <c r="Q26" t="n">
-        <v>-22820955</v>
+        <v>-71180490</v>
       </c>
       <c r="R26" t="n">
-        <v>-171088607</v>
+        <v>-112366470</v>
       </c>
       <c r="S26" t="n">
-        <v>-134458080</v>
+        <v>-124696352</v>
       </c>
       <c r="T26" t="n">
-        <v>9000</v>
+        <v>36156345</v>
       </c>
       <c r="U26" t="n">
-        <v>90252</v>
+        <v>81328402</v>
       </c>
       <c r="V26" t="n">
-        <v>212198</v>
+        <v>105198860</v>
       </c>
       <c r="W26" t="n">
-        <v>201905</v>
+        <v>127993964</v>
       </c>
       <c r="X26" t="n">
-        <v>3125874</v>
+        <v>770621</v>
       </c>
       <c r="Y26" t="n">
-        <v>1899180</v>
+        <v>1335739</v>
       </c>
       <c r="Z26" t="n">
-        <v>-476396</v>
+        <v>2919646</v>
       </c>
       <c r="AA26" t="n">
-        <v>3081708</v>
+        <v>2017106</v>
       </c>
       <c r="AB26" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3504,44 +3504,44 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、接近20日高點、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>144.5</v>
+        <v>436</v>
       </c>
       <c r="D27" t="n">
-        <v>137.1</v>
+        <v>447.6</v>
       </c>
       <c r="E27" t="n">
-        <v>124.75</v>
+        <v>405.25</v>
       </c>
       <c r="F27" t="n">
-        <v>110.34</v>
+        <v>392.2</v>
       </c>
       <c r="G27" t="n">
-        <v>366515715</v>
+        <v>10858000</v>
       </c>
       <c r="H27" t="n">
-        <v>339579178</v>
+        <v>16704800</v>
       </c>
       <c r="I27" t="n">
-        <v>151</v>
+        <v>492.5</v>
       </c>
       <c r="J27" t="n">
-        <v>79.40000000000001</v>
+        <v>343</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3549,116 +3549,116 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-56076862</v>
+        <v>-2759531</v>
       </c>
       <c r="M27" t="n">
-        <v>-86242883</v>
+        <v>-1248331</v>
       </c>
       <c r="N27" t="n">
-        <v>-875000</v>
+        <v>10551657</v>
       </c>
       <c r="O27" t="n">
-        <v>-61795227</v>
+        <v>9369379</v>
       </c>
       <c r="P27" t="n">
-        <v>-28218031</v>
+        <v>-2821709</v>
       </c>
       <c r="Q27" t="n">
-        <v>-6628877</v>
+        <v>-647260</v>
       </c>
       <c r="R27" t="n">
-        <v>113761499</v>
+        <v>12234799</v>
       </c>
       <c r="S27" t="n">
-        <v>26118707</v>
+        <v>13596569</v>
       </c>
       <c r="T27" t="n">
-        <v>-28689967</v>
+        <v>-12000</v>
       </c>
       <c r="U27" t="n">
-        <v>-82184801</v>
+        <v>-330000</v>
       </c>
       <c r="V27" t="n">
-        <v>-123282822</v>
+        <v>-1959000</v>
       </c>
       <c r="W27" t="n">
-        <v>-95204333</v>
+        <v>-5111631</v>
       </c>
       <c r="X27" t="n">
-        <v>831136</v>
+        <v>74178</v>
       </c>
       <c r="Y27" t="n">
-        <v>2570795</v>
+        <v>-271071</v>
       </c>
       <c r="Z27" t="n">
-        <v>8646323</v>
+        <v>275858</v>
       </c>
       <c r="AA27" t="n">
-        <v>7290399</v>
+        <v>884441</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>51</v>
+        <v>1065</v>
       </c>
       <c r="D28" t="n">
-        <v>48.48</v>
+        <v>1031</v>
       </c>
       <c r="E28" t="n">
-        <v>44.08</v>
+        <v>1005.2</v>
       </c>
       <c r="F28" t="n">
-        <v>37.84</v>
+        <v>1042.85</v>
       </c>
       <c r="G28" t="n">
-        <v>897327645</v>
+        <v>2917000</v>
       </c>
       <c r="H28" t="n">
-        <v>1011819780</v>
+        <v>2821000</v>
       </c>
       <c r="I28" t="n">
-        <v>52.2</v>
+        <v>1210</v>
       </c>
       <c r="J28" t="n">
-        <v>24.05</v>
+        <v>936</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,116 +3666,116 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>165040996</v>
+        <v>666681</v>
       </c>
       <c r="M28" t="n">
-        <v>-112547359</v>
+        <v>219838</v>
       </c>
       <c r="N28" t="n">
-        <v>-335137590</v>
+        <v>-77355</v>
       </c>
       <c r="O28" t="n">
-        <v>-397552657</v>
+        <v>-2233620</v>
       </c>
       <c r="P28" t="n">
-        <v>163249451</v>
+        <v>471617</v>
       </c>
       <c r="Q28" t="n">
-        <v>-94432896</v>
+        <v>102185</v>
       </c>
       <c r="R28" t="n">
-        <v>-301356148</v>
+        <v>-240846</v>
       </c>
       <c r="S28" t="n">
-        <v>-360917695</v>
+        <v>-1830072</v>
       </c>
       <c r="T28" t="n">
-        <v>7444</v>
+        <v>2000</v>
       </c>
       <c r="U28" t="n">
-        <v>-5412779</v>
+        <v>10000</v>
       </c>
       <c r="V28" t="n">
-        <v>-8125475</v>
+        <v>3617</v>
       </c>
       <c r="W28" t="n">
-        <v>-7014264</v>
+        <v>-232427</v>
       </c>
       <c r="X28" t="n">
-        <v>1784101</v>
+        <v>193064</v>
       </c>
       <c r="Y28" t="n">
-        <v>-12701684</v>
+        <v>107653</v>
       </c>
       <c r="Z28" t="n">
-        <v>-25655967</v>
+        <v>159874</v>
       </c>
       <c r="AA28" t="n">
-        <v>-29620698</v>
+        <v>-171121</v>
       </c>
       <c r="AB28" t="n">
-        <v>-5</v>
+        <v>35</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>短線籌碼止穩、5日法人小幅賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、短線籌碼止穩、5日法人小幅賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>86.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>84.42</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>78.90000000000001</v>
+        <v>69.08</v>
       </c>
       <c r="F29" t="n">
-        <v>70.40000000000001</v>
+        <v>69.08</v>
       </c>
       <c r="G29" t="n">
-        <v>41007388</v>
+        <v>78210167</v>
       </c>
       <c r="H29" t="n">
-        <v>41397085</v>
+        <v>181489906</v>
       </c>
       <c r="I29" t="n">
-        <v>93</v>
+        <v>81.2</v>
       </c>
       <c r="J29" t="n">
-        <v>58.1</v>
+        <v>61.8</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,116 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-6462430</v>
+        <v>-7646631</v>
       </c>
       <c r="M29" t="n">
-        <v>-11504398</v>
+        <v>-16047176</v>
       </c>
       <c r="N29" t="n">
-        <v>-6893169</v>
+        <v>33115701</v>
       </c>
       <c r="O29" t="n">
-        <v>-1205046</v>
+        <v>55309856</v>
       </c>
       <c r="P29" t="n">
-        <v>-6057541</v>
+        <v>-8313549</v>
       </c>
       <c r="Q29" t="n">
-        <v>-9875925</v>
+        <v>-17889466</v>
       </c>
       <c r="R29" t="n">
-        <v>-5376500</v>
+        <v>28430668</v>
       </c>
       <c r="S29" t="n">
-        <v>-1907685</v>
+        <v>46507174</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1576000</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>2349000</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2381000</v>
       </c>
       <c r="X29" t="n">
-        <v>-404889</v>
+        <v>670918</v>
       </c>
       <c r="Y29" t="n">
-        <v>-1628473</v>
+        <v>266290</v>
       </c>
       <c r="Z29" t="n">
-        <v>-1516669</v>
+        <v>2336033</v>
       </c>
       <c r="AA29" t="n">
-        <v>702639</v>
+        <v>6421682</v>
       </c>
       <c r="AB29" t="n">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.800000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="D30" t="n">
-        <v>8.289999999999999</v>
+        <v>14.76</v>
       </c>
       <c r="E30" t="n">
-        <v>7.12</v>
+        <v>12.68</v>
       </c>
       <c r="F30" t="n">
-        <v>6.44</v>
+        <v>11.15</v>
       </c>
       <c r="G30" t="n">
-        <v>120114525</v>
+        <v>289351189</v>
       </c>
       <c r="H30" t="n">
-        <v>150006859</v>
+        <v>286226550</v>
       </c>
       <c r="I30" t="n">
-        <v>9.25</v>
+        <v>17.1</v>
       </c>
       <c r="J30" t="n">
-        <v>5.55</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-8225970</v>
+        <v>5284295</v>
       </c>
       <c r="M30" t="n">
-        <v>-21697710</v>
+        <v>-6495197</v>
       </c>
       <c r="N30" t="n">
-        <v>-13271904</v>
+        <v>-42554506</v>
       </c>
       <c r="O30" t="n">
-        <v>-999013</v>
+        <v>8357597</v>
       </c>
       <c r="P30" t="n">
-        <v>-8995000</v>
+        <v>4366136</v>
       </c>
       <c r="Q30" t="n">
-        <v>-16819749</v>
+        <v>-9860996</v>
       </c>
       <c r="R30" t="n">
-        <v>-16143749</v>
+        <v>-43704960</v>
       </c>
       <c r="S30" t="n">
-        <v>-6217849</v>
+        <v>6123515</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -3936,80 +3936,80 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>769030</v>
+        <v>918159</v>
       </c>
       <c r="Y30" t="n">
-        <v>-4877961</v>
+        <v>3365799</v>
       </c>
       <c r="Z30" t="n">
-        <v>2871845</v>
+        <v>1150454</v>
       </c>
       <c r="AA30" t="n">
-        <v>5218836</v>
+        <v>2234082</v>
       </c>
       <c r="AB30" t="n">
-        <v>-10</v>
+        <v>25</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1810</v>
+        <v>83.2</v>
       </c>
       <c r="D31" t="n">
-        <v>1717</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1729</v>
+        <v>81.36</v>
       </c>
       <c r="F31" t="n">
-        <v>1680</v>
+        <v>80.97</v>
       </c>
       <c r="G31" t="n">
-        <v>5120000</v>
+        <v>20794251</v>
       </c>
       <c r="H31" t="n">
-        <v>4208800</v>
+        <v>12683829</v>
       </c>
       <c r="I31" t="n">
-        <v>1935</v>
+        <v>85.8</v>
       </c>
       <c r="J31" t="n">
-        <v>1270</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,116 +4017,116 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>129935</v>
+        <v>3075517</v>
       </c>
       <c r="M31" t="n">
-        <v>-22256</v>
+        <v>1838084</v>
       </c>
       <c r="N31" t="n">
-        <v>-841812</v>
+        <v>-1100465</v>
       </c>
       <c r="O31" t="n">
-        <v>-2031599</v>
+        <v>-433582</v>
       </c>
       <c r="P31" t="n">
-        <v>-260532</v>
+        <v>2692586</v>
       </c>
       <c r="Q31" t="n">
-        <v>-612470</v>
+        <v>1633452</v>
       </c>
       <c r="R31" t="n">
-        <v>-816964</v>
+        <v>-1080274</v>
       </c>
       <c r="S31" t="n">
-        <v>-1606644</v>
+        <v>-143430</v>
       </c>
       <c r="T31" t="n">
-        <v>356500</v>
+        <v>-1000</v>
       </c>
       <c r="U31" t="n">
-        <v>560740</v>
+        <v>-1000</v>
       </c>
       <c r="V31" t="n">
-        <v>-40877</v>
+        <v>-1000</v>
       </c>
       <c r="W31" t="n">
-        <v>-308710</v>
+        <v>-1000</v>
       </c>
       <c r="X31" t="n">
-        <v>33967</v>
+        <v>383931</v>
       </c>
       <c r="Y31" t="n">
-        <v>29474</v>
+        <v>205632</v>
       </c>
       <c r="Z31" t="n">
-        <v>16029</v>
+        <v>-19191</v>
       </c>
       <c r="AA31" t="n">
-        <v>-116245</v>
+        <v>-289152</v>
       </c>
       <c r="AB31" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38.95</v>
+        <v>144.5</v>
       </c>
       <c r="D32" t="n">
-        <v>38.08</v>
+        <v>137.1</v>
       </c>
       <c r="E32" t="n">
-        <v>33.81</v>
+        <v>124.75</v>
       </c>
       <c r="F32" t="n">
-        <v>31.15</v>
+        <v>110.34</v>
       </c>
       <c r="G32" t="n">
-        <v>102606028</v>
+        <v>366515715</v>
       </c>
       <c r="H32" t="n">
-        <v>141383468</v>
+        <v>339579178</v>
       </c>
       <c r="I32" t="n">
-        <v>41.05</v>
+        <v>151</v>
       </c>
       <c r="J32" t="n">
-        <v>26.65</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,56 +4134,56 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-6910077</v>
+        <v>-56076862</v>
       </c>
       <c r="M32" t="n">
-        <v>-38867066</v>
+        <v>-86242883</v>
       </c>
       <c r="N32" t="n">
-        <v>-330703</v>
+        <v>-875000</v>
       </c>
       <c r="O32" t="n">
-        <v>19072843</v>
+        <v>-79666636</v>
       </c>
       <c r="P32" t="n">
-        <v>-6951441</v>
+        <v>-28218031</v>
       </c>
       <c r="Q32" t="n">
-        <v>-37390805</v>
+        <v>-6628877</v>
       </c>
       <c r="R32" t="n">
-        <v>4656960</v>
+        <v>113761499</v>
       </c>
       <c r="S32" t="n">
-        <v>29651379</v>
+        <v>14781667</v>
       </c>
       <c r="T32" t="n">
+        <v>-28689967</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-82184801</v>
+      </c>
+      <c r="V32" t="n">
+        <v>-123282822</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-99898432</v>
+      </c>
+      <c r="X32" t="n">
+        <v>831136</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2570795</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>8646323</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>5450129</v>
+      </c>
+      <c r="AB32" t="n">
         <v>0</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>-5544000</v>
-      </c>
-      <c r="W32" t="n">
-        <v>-12288000</v>
-      </c>
-      <c r="X32" t="n">
-        <v>41364</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>-1476261</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>556337</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1709464</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>-25</v>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
           <t>❌避開</t>
@@ -4196,54 +4196,54 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>284.5</v>
+        <v>51</v>
       </c>
       <c r="D33" t="n">
-        <v>281.7</v>
+        <v>48.48</v>
       </c>
       <c r="E33" t="n">
-        <v>271.45</v>
+        <v>44.08</v>
       </c>
       <c r="F33" t="n">
-        <v>261.52</v>
+        <v>37.84</v>
       </c>
       <c r="G33" t="n">
-        <v>84156366</v>
+        <v>897327645</v>
       </c>
       <c r="H33" t="n">
-        <v>93692827</v>
+        <v>1011819780</v>
       </c>
       <c r="I33" t="n">
-        <v>305.5</v>
+        <v>52.2</v>
       </c>
       <c r="J33" t="n">
-        <v>233.5</v>
+        <v>24.05</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,55 +4251,55 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>28384602</v>
+        <v>165040996</v>
       </c>
       <c r="M33" t="n">
-        <v>-21588663</v>
+        <v>-112547359</v>
       </c>
       <c r="N33" t="n">
-        <v>-27955055</v>
+        <v>-335137590</v>
       </c>
       <c r="O33" t="n">
-        <v>28616720</v>
+        <v>-278268834</v>
       </c>
       <c r="P33" t="n">
-        <v>28289321</v>
+        <v>163249451</v>
       </c>
       <c r="Q33" t="n">
-        <v>-11423041</v>
+        <v>-94432896</v>
       </c>
       <c r="R33" t="n">
-        <v>-15045877</v>
+        <v>-301356148</v>
       </c>
       <c r="S33" t="n">
-        <v>34183158</v>
+        <v>-249862200</v>
       </c>
       <c r="T33" t="n">
-        <v>-387000</v>
+        <v>7444</v>
       </c>
       <c r="U33" t="n">
-        <v>-7289000</v>
+        <v>-5412779</v>
       </c>
       <c r="V33" t="n">
-        <v>-9830000</v>
+        <v>-8125475</v>
       </c>
       <c r="W33" t="n">
-        <v>-4081000</v>
+        <v>-7077264</v>
       </c>
       <c r="X33" t="n">
-        <v>482281</v>
+        <v>1784101</v>
       </c>
       <c r="Y33" t="n">
-        <v>-2876622</v>
+        <v>-12701684</v>
       </c>
       <c r="Z33" t="n">
-        <v>-3079178</v>
+        <v>-25655967</v>
       </c>
       <c r="AA33" t="n">
-        <v>-1485438</v>
+        <v>-21329370</v>
       </c>
       <c r="AB33" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -4318,49 +4318,49 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>738</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>706.6</v>
+        <v>22.48</v>
       </c>
       <c r="E34" t="n">
-        <v>625.2</v>
+        <v>21.2</v>
       </c>
       <c r="F34" t="n">
-        <v>509.5</v>
+        <v>19.97</v>
       </c>
       <c r="G34" t="n">
-        <v>28926802</v>
+        <v>481574851</v>
       </c>
       <c r="H34" t="n">
-        <v>35208144</v>
+        <v>497424018</v>
       </c>
       <c r="I34" t="n">
-        <v>784</v>
+        <v>25.8</v>
       </c>
       <c r="J34" t="n">
-        <v>314</v>
+        <v>16.6</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,55 +4368,55 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-4621281</v>
+        <v>69476213</v>
       </c>
       <c r="M34" t="n">
-        <v>-7685090</v>
+        <v>-20831523</v>
       </c>
       <c r="N34" t="n">
-        <v>-7877682</v>
+        <v>-171352805</v>
       </c>
       <c r="O34" t="n">
-        <v>634862</v>
+        <v>9685753</v>
       </c>
       <c r="P34" t="n">
-        <v>-5437960</v>
+        <v>66341339</v>
       </c>
       <c r="Q34" t="n">
-        <v>-10240633</v>
+        <v>-22820955</v>
       </c>
       <c r="R34" t="n">
-        <v>-14919628</v>
+        <v>-171088607</v>
       </c>
       <c r="S34" t="n">
-        <v>-20759430</v>
+        <v>5694712</v>
       </c>
       <c r="T34" t="n">
-        <v>278110</v>
+        <v>9000</v>
       </c>
       <c r="U34" t="n">
-        <v>345532</v>
+        <v>90252</v>
       </c>
       <c r="V34" t="n">
-        <v>3427740</v>
+        <v>212198</v>
       </c>
       <c r="W34" t="n">
-        <v>17737061</v>
+        <v>242507</v>
       </c>
       <c r="X34" t="n">
-        <v>538569</v>
+        <v>3125874</v>
       </c>
       <c r="Y34" t="n">
-        <v>2210011</v>
+        <v>1899180</v>
       </c>
       <c r="Z34" t="n">
-        <v>3614206</v>
+        <v>-476396</v>
       </c>
       <c r="AA34" t="n">
-        <v>3657231</v>
+        <v>3748534</v>
       </c>
       <c r="AB34" t="n">
-        <v>-35</v>
+        <v>-10</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -4435,49 +4435,49 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4310</v>
+        <v>1810</v>
       </c>
       <c r="D35" t="n">
-        <v>4374</v>
+        <v>1717</v>
       </c>
       <c r="E35" t="n">
-        <v>3906.5</v>
+        <v>1729</v>
       </c>
       <c r="F35" t="n">
-        <v>3665.5</v>
+        <v>1680</v>
       </c>
       <c r="G35" t="n">
-        <v>23109791</v>
+        <v>5120000</v>
       </c>
       <c r="H35" t="n">
-        <v>16392169</v>
+        <v>4208800</v>
       </c>
       <c r="I35" t="n">
-        <v>4690</v>
+        <v>1935</v>
       </c>
       <c r="J35" t="n">
-        <v>2870</v>
+        <v>1270</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,55 +4485,55 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-3475601</v>
+        <v>129935</v>
       </c>
       <c r="M35" t="n">
-        <v>-3182081</v>
+        <v>-22256</v>
       </c>
       <c r="N35" t="n">
-        <v>-4172313</v>
+        <v>-841812</v>
       </c>
       <c r="O35" t="n">
-        <v>-6209468</v>
+        <v>-2031599</v>
       </c>
       <c r="P35" t="n">
-        <v>-2324807</v>
+        <v>-260532</v>
       </c>
       <c r="Q35" t="n">
-        <v>-183403</v>
+        <v>-612470</v>
       </c>
       <c r="R35" t="n">
-        <v>9386</v>
+        <v>-816964</v>
       </c>
       <c r="S35" t="n">
-        <v>-3126883</v>
+        <v>-1606644</v>
       </c>
       <c r="T35" t="n">
-        <v>-1020510</v>
+        <v>356500</v>
       </c>
       <c r="U35" t="n">
-        <v>-2923799</v>
+        <v>560740</v>
       </c>
       <c r="V35" t="n">
-        <v>-4483231</v>
+        <v>-40877</v>
       </c>
       <c r="W35" t="n">
-        <v>-3560413</v>
+        <v>-308710</v>
       </c>
       <c r="X35" t="n">
-        <v>-130284</v>
+        <v>33967</v>
       </c>
       <c r="Y35" t="n">
-        <v>-74879</v>
+        <v>29474</v>
       </c>
       <c r="Z35" t="n">
-        <v>301532</v>
+        <v>16029</v>
       </c>
       <c r="AA35" t="n">
-        <v>477828</v>
+        <v>-116245</v>
       </c>
       <c r="AB35" t="n">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -4547,54 +4547,54 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>515</v>
+        <v>38.95</v>
       </c>
       <c r="D36" t="n">
-        <v>520.4</v>
+        <v>38.08</v>
       </c>
       <c r="E36" t="n">
-        <v>482.35</v>
+        <v>33.81</v>
       </c>
       <c r="F36" t="n">
-        <v>451.07</v>
+        <v>31.15</v>
       </c>
       <c r="G36" t="n">
-        <v>11454003</v>
+        <v>102606028</v>
       </c>
       <c r="H36" t="n">
-        <v>32912192</v>
+        <v>141383468</v>
       </c>
       <c r="I36" t="n">
-        <v>568</v>
+        <v>41.05</v>
       </c>
       <c r="J36" t="n">
-        <v>372</v>
+        <v>26.65</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,55 +4602,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>857140</v>
+        <v>-6910077</v>
       </c>
       <c r="M36" t="n">
-        <v>-7205641</v>
+        <v>-38867066</v>
       </c>
       <c r="N36" t="n">
-        <v>-9256603</v>
+        <v>-330703</v>
       </c>
       <c r="O36" t="n">
-        <v>-6085533</v>
+        <v>70129318</v>
       </c>
       <c r="P36" t="n">
-        <v>1231521</v>
+        <v>-6951441</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1238676</v>
+        <v>-37390805</v>
       </c>
       <c r="R36" t="n">
-        <v>-4688336</v>
+        <v>4656960</v>
       </c>
       <c r="S36" t="n">
-        <v>-6625467</v>
+        <v>83481179</v>
       </c>
       <c r="T36" t="n">
-        <v>-836465</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-5792592</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>-3969592</v>
+        <v>-5544000</v>
       </c>
       <c r="W36" t="n">
-        <v>431976</v>
+        <v>-17754000</v>
       </c>
       <c r="X36" t="n">
-        <v>462084</v>
+        <v>41364</v>
       </c>
       <c r="Y36" t="n">
-        <v>-174373</v>
+        <v>-1476261</v>
       </c>
       <c r="Z36" t="n">
-        <v>-598675</v>
+        <v>556337</v>
       </c>
       <c r="AA36" t="n">
-        <v>107958</v>
+        <v>4402139</v>
       </c>
       <c r="AB36" t="n">
-        <v>-45</v>
+        <v>-25</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -4664,54 +4664,54 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>207</v>
+        <v>284.5</v>
       </c>
       <c r="D37" t="n">
-        <v>208.9</v>
+        <v>281.7</v>
       </c>
       <c r="E37" t="n">
-        <v>203.45</v>
+        <v>271.45</v>
       </c>
       <c r="F37" t="n">
-        <v>195.38</v>
+        <v>261.52</v>
       </c>
       <c r="G37" t="n">
-        <v>13700926</v>
+        <v>84156366</v>
       </c>
       <c r="H37" t="n">
-        <v>19496790</v>
+        <v>93692827</v>
       </c>
       <c r="I37" t="n">
-        <v>231</v>
+        <v>305.5</v>
       </c>
       <c r="J37" t="n">
-        <v>168.5</v>
+        <v>233.5</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,55 +4719,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-2706458</v>
+        <v>28384602</v>
       </c>
       <c r="M37" t="n">
-        <v>-1348885</v>
+        <v>-21588663</v>
       </c>
       <c r="N37" t="n">
-        <v>-5894259</v>
+        <v>-27955055</v>
       </c>
       <c r="O37" t="n">
-        <v>-6233139</v>
+        <v>23437616</v>
       </c>
       <c r="P37" t="n">
-        <v>-2716140</v>
+        <v>28289321</v>
       </c>
       <c r="Q37" t="n">
-        <v>-1301206</v>
+        <v>-11423041</v>
       </c>
       <c r="R37" t="n">
-        <v>-5499049</v>
+        <v>-15045877</v>
       </c>
       <c r="S37" t="n">
-        <v>-5960666</v>
+        <v>30133661</v>
       </c>
       <c r="T37" t="n">
-        <v>2000</v>
+        <v>-387000</v>
       </c>
       <c r="U37" t="n">
-        <v>2000</v>
+        <v>-7289000</v>
       </c>
       <c r="V37" t="n">
-        <v>2000</v>
+        <v>-9830000</v>
       </c>
       <c r="W37" t="n">
-        <v>-60316</v>
+        <v>-4343000</v>
       </c>
       <c r="X37" t="n">
-        <v>7682</v>
+        <v>482281</v>
       </c>
       <c r="Y37" t="n">
-        <v>-49679</v>
+        <v>-2876622</v>
       </c>
       <c r="Z37" t="n">
-        <v>-397210</v>
+        <v>-3079178</v>
       </c>
       <c r="AA37" t="n">
-        <v>-212157</v>
+        <v>-2353045</v>
       </c>
       <c r="AB37" t="n">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -4781,54 +4781,54 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>611</v>
+        <v>86.3</v>
       </c>
       <c r="D38" t="n">
-        <v>621.6</v>
+        <v>84.42</v>
       </c>
       <c r="E38" t="n">
-        <v>563.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>549.85</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>43968378</v>
+        <v>41007388</v>
       </c>
       <c r="H38" t="n">
-        <v>35056581</v>
+        <v>41397085</v>
       </c>
       <c r="I38" t="n">
-        <v>669</v>
+        <v>93</v>
       </c>
       <c r="J38" t="n">
-        <v>465</v>
+        <v>58.1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,55 +4836,55 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-13838044</v>
+        <v>-6462430</v>
       </c>
       <c r="M38" t="n">
-        <v>-15671425</v>
+        <v>-11504398</v>
       </c>
       <c r="N38" t="n">
-        <v>-19564058</v>
+        <v>-6893169</v>
       </c>
       <c r="O38" t="n">
-        <v>-25170408</v>
+        <v>4060977</v>
       </c>
       <c r="P38" t="n">
-        <v>-10101577</v>
+        <v>-6057541</v>
       </c>
       <c r="Q38" t="n">
-        <v>-11629233</v>
+        <v>-9875925</v>
       </c>
       <c r="R38" t="n">
-        <v>-16515209</v>
+        <v>-5376500</v>
       </c>
       <c r="S38" t="n">
-        <v>-23459381</v>
+        <v>2454433</v>
       </c>
       <c r="T38" t="n">
-        <v>-3776094</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>-4048842</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>-2960648</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>-1432268</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>39627</v>
+        <v>-404889</v>
       </c>
       <c r="Y38" t="n">
-        <v>6650</v>
+        <v>-1628473</v>
       </c>
       <c r="Z38" t="n">
-        <v>-88201</v>
+        <v>-1516669</v>
       </c>
       <c r="AA38" t="n">
-        <v>-278759</v>
+        <v>1606544</v>
       </c>
       <c r="AB38" t="n">
-        <v>-60</v>
+        <v>-35</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -4898,54 +4898,54 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>527</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>544</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>508.75</v>
+        <v>7.12</v>
       </c>
       <c r="F39" t="n">
-        <v>506.73</v>
+        <v>6.44</v>
       </c>
       <c r="G39" t="n">
-        <v>26012000</v>
+        <v>120114525</v>
       </c>
       <c r="H39" t="n">
-        <v>39810000</v>
+        <v>150006859</v>
       </c>
       <c r="I39" t="n">
-        <v>588</v>
+        <v>9.25</v>
       </c>
       <c r="J39" t="n">
-        <v>436</v>
+        <v>5.55</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,55 +4953,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-4446778</v>
+        <v>-8225970</v>
       </c>
       <c r="M39" t="n">
-        <v>-5175986</v>
+        <v>-21697710</v>
       </c>
       <c r="N39" t="n">
-        <v>-1641710</v>
+        <v>-13271904</v>
       </c>
       <c r="O39" t="n">
-        <v>3127410</v>
+        <v>15244774</v>
       </c>
       <c r="P39" t="n">
-        <v>-2818118</v>
+        <v>-8995000</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3426566</v>
+        <v>-16819749</v>
       </c>
       <c r="R39" t="n">
-        <v>-2679038</v>
+        <v>-16143749</v>
       </c>
       <c r="S39" t="n">
-        <v>-1518645</v>
+        <v>9898851</v>
       </c>
       <c r="T39" t="n">
-        <v>-1490721</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>-1184325</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>-351326</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2432941</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>-137939</v>
+        <v>769030</v>
       </c>
       <c r="Y39" t="n">
-        <v>-565095</v>
+        <v>-4877961</v>
       </c>
       <c r="Z39" t="n">
-        <v>1388654</v>
+        <v>2871845</v>
       </c>
       <c r="AA39" t="n">
-        <v>2213114</v>
+        <v>5345923</v>
       </c>
       <c r="AB39" t="n">
-        <v>-95</v>
+        <v>-35</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -5015,54 +5015,54 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1030</v>
+        <v>738</v>
       </c>
       <c r="D40" t="n">
-        <v>1122</v>
+        <v>706.6</v>
       </c>
       <c r="E40" t="n">
-        <v>1055.2</v>
+        <v>625.2</v>
       </c>
       <c r="F40" t="n">
-        <v>1068.35</v>
+        <v>509.5</v>
       </c>
       <c r="G40" t="n">
-        <v>3335000</v>
+        <v>28926802</v>
       </c>
       <c r="H40" t="n">
-        <v>4981400</v>
+        <v>35208144</v>
       </c>
       <c r="I40" t="n">
-        <v>1300</v>
+        <v>784</v>
       </c>
       <c r="J40" t="n">
-        <v>865</v>
+        <v>314</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5070,55 +5070,55 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-758454</v>
+        <v>-4621281</v>
       </c>
       <c r="M40" t="n">
-        <v>-2632081</v>
+        <v>-7685090</v>
       </c>
       <c r="N40" t="n">
-        <v>-3568191</v>
+        <v>-7877682</v>
       </c>
       <c r="O40" t="n">
-        <v>-4121517</v>
+        <v>352104</v>
       </c>
       <c r="P40" t="n">
-        <v>-163282</v>
+        <v>-5437960</v>
       </c>
       <c r="Q40" t="n">
-        <v>-346498</v>
+        <v>-10240633</v>
       </c>
       <c r="R40" t="n">
-        <v>-1599895</v>
+        <v>-14919628</v>
       </c>
       <c r="S40" t="n">
-        <v>-2472060</v>
+        <v>-31600414</v>
       </c>
       <c r="T40" t="n">
-        <v>-593000</v>
+        <v>278110</v>
       </c>
       <c r="U40" t="n">
-        <v>-2259050</v>
+        <v>345532</v>
       </c>
       <c r="V40" t="n">
-        <v>-1818050</v>
+        <v>3427740</v>
       </c>
       <c r="W40" t="n">
-        <v>-1656050</v>
+        <v>28089740</v>
       </c>
       <c r="X40" t="n">
-        <v>-2172</v>
+        <v>538569</v>
       </c>
       <c r="Y40" t="n">
-        <v>-26533</v>
+        <v>2210011</v>
       </c>
       <c r="Z40" t="n">
-        <v>-150246</v>
+        <v>3614206</v>
       </c>
       <c r="AA40" t="n">
-        <v>6593</v>
+        <v>3862778</v>
       </c>
       <c r="AB40" t="n">
-        <v>-95</v>
+        <v>-35</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -5132,54 +5132,54 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>848</v>
+        <v>4310</v>
       </c>
       <c r="D41" t="n">
-        <v>881.8</v>
+        <v>4374</v>
       </c>
       <c r="E41" t="n">
-        <v>863.3</v>
+        <v>3906.5</v>
       </c>
       <c r="F41" t="n">
-        <v>883.9</v>
+        <v>3665.5</v>
       </c>
       <c r="G41" t="n">
-        <v>17926232</v>
+        <v>23109791</v>
       </c>
       <c r="H41" t="n">
-        <v>23312290</v>
+        <v>16392169</v>
       </c>
       <c r="I41" t="n">
-        <v>1035</v>
+        <v>4690</v>
       </c>
       <c r="J41" t="n">
-        <v>765</v>
+        <v>2870</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5187,55 +5187,55 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-2448813</v>
+        <v>-3475601</v>
       </c>
       <c r="M41" t="n">
-        <v>-8778876</v>
+        <v>-3182081</v>
       </c>
       <c r="N41" t="n">
-        <v>-13138409</v>
+        <v>-4172313</v>
       </c>
       <c r="O41" t="n">
-        <v>-9532251</v>
+        <v>-8316461</v>
       </c>
       <c r="P41" t="n">
-        <v>43377</v>
+        <v>-2324807</v>
       </c>
       <c r="Q41" t="n">
-        <v>-3411404</v>
+        <v>-183403</v>
       </c>
       <c r="R41" t="n">
-        <v>-4691237</v>
+        <v>9386</v>
       </c>
       <c r="S41" t="n">
-        <v>-2926212</v>
+        <v>-5245958</v>
       </c>
       <c r="T41" t="n">
-        <v>-2413000</v>
+        <v>-1020510</v>
       </c>
       <c r="U41" t="n">
-        <v>-5192000</v>
+        <v>-2923799</v>
       </c>
       <c r="V41" t="n">
-        <v>-8133000</v>
+        <v>-4483231</v>
       </c>
       <c r="W41" t="n">
-        <v>-6368000</v>
+        <v>-3986411</v>
       </c>
       <c r="X41" t="n">
-        <v>-79190</v>
+        <v>-130284</v>
       </c>
       <c r="Y41" t="n">
-        <v>-175472</v>
+        <v>-74879</v>
       </c>
       <c r="Z41" t="n">
-        <v>-314172</v>
+        <v>301532</v>
       </c>
       <c r="AA41" t="n">
-        <v>-238039</v>
+        <v>915908</v>
       </c>
       <c r="AB41" t="n">
-        <v>-95</v>
+        <v>-40</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -5249,54 +5249,54 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>31.95</v>
+        <v>233</v>
       </c>
       <c r="D42" t="n">
-        <v>33.46</v>
+        <v>262.3</v>
       </c>
       <c r="E42" t="n">
-        <v>34.07</v>
+        <v>253.5</v>
       </c>
       <c r="F42" t="n">
-        <v>36.33</v>
+        <v>245.8</v>
       </c>
       <c r="G42" t="n">
-        <v>7490299</v>
+        <v>3160000</v>
       </c>
       <c r="H42" t="n">
-        <v>10923227</v>
+        <v>3905800</v>
       </c>
       <c r="I42" t="n">
-        <v>44.05</v>
+        <v>312.5</v>
       </c>
       <c r="J42" t="n">
-        <v>31.1</v>
+        <v>220</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5304,28 +5304,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-830875</v>
+        <v>-692891</v>
       </c>
       <c r="M42" t="n">
-        <v>-1788679</v>
+        <v>-2049758</v>
       </c>
       <c r="N42" t="n">
-        <v>-3454506</v>
+        <v>-2651177</v>
       </c>
       <c r="O42" t="n">
-        <v>-7506760</v>
+        <v>-2133865</v>
       </c>
       <c r="P42" t="n">
-        <v>-673979</v>
+        <v>-680878</v>
       </c>
       <c r="Q42" t="n">
-        <v>-1532782</v>
+        <v>-1994325</v>
       </c>
       <c r="R42" t="n">
-        <v>-3330610</v>
+        <v>-2544572</v>
       </c>
       <c r="S42" t="n">
-        <v>-7206697</v>
+        <v>-1885020</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -5340,41 +5340,860 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
+        <v>-12013</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-55433</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-106605</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-248845</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3711.TW</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>611</v>
+      </c>
+      <c r="D43" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="E43" t="n">
+        <v>563.7</v>
+      </c>
+      <c r="F43" t="n">
+        <v>549.85</v>
+      </c>
+      <c r="G43" t="n">
+        <v>43968378</v>
+      </c>
+      <c r="H43" t="n">
+        <v>35056581</v>
+      </c>
+      <c r="I43" t="n">
+        <v>669</v>
+      </c>
+      <c r="J43" t="n">
+        <v>465</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>-13838044</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-15671425</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-19564058</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-23073180</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-10101577</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>-11629233</v>
+      </c>
+      <c r="R43" t="n">
+        <v>-16515209</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-21778065</v>
+      </c>
+      <c r="T43" t="n">
+        <v>-3776094</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-4048842</v>
+      </c>
+      <c r="V43" t="n">
+        <v>-2960648</v>
+      </c>
+      <c r="W43" t="n">
+        <v>-767268</v>
+      </c>
+      <c r="X43" t="n">
+        <v>39627</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>6650</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-88201</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-527847</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4958.TW</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>515</v>
+      </c>
+      <c r="D44" t="n">
+        <v>520.4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>482.35</v>
+      </c>
+      <c r="F44" t="n">
+        <v>451.07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>11454003</v>
+      </c>
+      <c r="H44" t="n">
+        <v>32912192</v>
+      </c>
+      <c r="I44" t="n">
+        <v>568</v>
+      </c>
+      <c r="J44" t="n">
+        <v>372</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>857140</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-7205641</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-9256603</v>
+      </c>
+      <c r="O44" t="n">
+        <v>8993341</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1231521</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>-1238676</v>
+      </c>
+      <c r="R44" t="n">
+        <v>-4688336</v>
+      </c>
+      <c r="S44" t="n">
+        <v>-1033644</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-836465</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-5792592</v>
+      </c>
+      <c r="V44" t="n">
+        <v>-3969592</v>
+      </c>
+      <c r="W44" t="n">
+        <v>9612976</v>
+      </c>
+      <c r="X44" t="n">
+        <v>462084</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>-174373</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-598675</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>414009</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3035.TW</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>207</v>
+      </c>
+      <c r="D45" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="E45" t="n">
+        <v>203.45</v>
+      </c>
+      <c r="F45" t="n">
+        <v>195.38</v>
+      </c>
+      <c r="G45" t="n">
+        <v>13700926</v>
+      </c>
+      <c r="H45" t="n">
+        <v>19496790</v>
+      </c>
+      <c r="I45" t="n">
+        <v>231</v>
+      </c>
+      <c r="J45" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>-2706458</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-1348885</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-5894259</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3016910</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-2716140</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>-1301206</v>
+      </c>
+      <c r="R45" t="n">
+        <v>-5499049</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2092357</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-55316</v>
+      </c>
+      <c r="X45" t="n">
+        <v>7682</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>-49679</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-397210</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>979869</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3105.TWO</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>527</v>
+      </c>
+      <c r="D46" t="n">
+        <v>544</v>
+      </c>
+      <c r="E46" t="n">
+        <v>508.75</v>
+      </c>
+      <c r="F46" t="n">
+        <v>506.73</v>
+      </c>
+      <c r="G46" t="n">
+        <v>26012000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>39810000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>588</v>
+      </c>
+      <c r="J46" t="n">
+        <v>436</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>-4446778</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-5175986</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-1641710</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3127410</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-2818118</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>-3426566</v>
+      </c>
+      <c r="R46" t="n">
+        <v>-2679038</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-1518645</v>
+      </c>
+      <c r="T46" t="n">
+        <v>-1490721</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-1184325</v>
+      </c>
+      <c r="V46" t="n">
+        <v>-351326</v>
+      </c>
+      <c r="W46" t="n">
+        <v>2432941</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-137939</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>-565095</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1388654</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2213114</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3163.TWO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>波若威</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1030</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1122</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1055.2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1068.35</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3335000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4981400</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J47" t="n">
+        <v>865</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>-758454</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-2632081</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-3568191</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-4121517</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-163282</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>-346498</v>
+      </c>
+      <c r="R47" t="n">
+        <v>-1599895</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-2472060</v>
+      </c>
+      <c r="T47" t="n">
+        <v>-593000</v>
+      </c>
+      <c r="U47" t="n">
+        <v>-2259050</v>
+      </c>
+      <c r="V47" t="n">
+        <v>-1818050</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-1656050</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-2172</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-26533</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-150246</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>6593</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8046.TW</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>848</v>
+      </c>
+      <c r="D48" t="n">
+        <v>881.8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>863.3</v>
+      </c>
+      <c r="F48" t="n">
+        <v>883.9</v>
+      </c>
+      <c r="G48" t="n">
+        <v>17926232</v>
+      </c>
+      <c r="H48" t="n">
+        <v>23312290</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1035</v>
+      </c>
+      <c r="J48" t="n">
+        <v>765</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>-2448813</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-8778876</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-13138409</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-8950196</v>
+      </c>
+      <c r="P48" t="n">
+        <v>43377</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>-3411404</v>
+      </c>
+      <c r="R48" t="n">
+        <v>-4691237</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-3009711</v>
+      </c>
+      <c r="T48" t="n">
+        <v>-2413000</v>
+      </c>
+      <c r="U48" t="n">
+        <v>-5192000</v>
+      </c>
+      <c r="V48" t="n">
+        <v>-8133000</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-5299000</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-79190</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-175472</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-314172</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-641485</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4960.TW</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>誠美材</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="D49" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="E49" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="F49" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7490299</v>
+      </c>
+      <c r="H49" t="n">
+        <v>10923227</v>
+      </c>
+      <c r="I49" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="J49" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>-830875</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-1788679</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-3454506</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-7227522</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-673979</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-1532782</v>
+      </c>
+      <c r="R49" t="n">
+        <v>-3330610</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-7097627</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
         <v>-156896</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y49" t="n">
         <v>-255897</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="Z49" t="n">
         <v>-123896</v>
       </c>
-      <c r="AA42" t="n">
-        <v>-300063</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="AA49" t="n">
+        <v>-129895</v>
+      </c>
+      <c r="AB49" t="n">
         <v>-110</v>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="AD42" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="AE42" t="inlineStr">
+      <c r="AE49" t="inlineStr">
         <is>
           <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr">
+      <c r="AF49" t="inlineStr">
         <is>
           <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
-      <c r="AG42" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG49"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,37 +703,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>370</v>
+        <v>158.5</v>
       </c>
       <c r="D3" t="n">
-        <v>342.5</v>
+        <v>148.6</v>
       </c>
       <c r="E3" t="n">
-        <v>328.9</v>
+        <v>142.8</v>
       </c>
       <c r="F3" t="n">
-        <v>319.35</v>
+        <v>142.2</v>
       </c>
       <c r="G3" t="n">
-        <v>33434927</v>
+        <v>114139019</v>
       </c>
       <c r="H3" t="n">
-        <v>17559688</v>
+        <v>59875721</v>
       </c>
       <c r="I3" t="n">
-        <v>371</v>
+        <v>158.5</v>
       </c>
       <c r="J3" t="n">
-        <v>270.5</v>
+        <v>132</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -741,55 +741,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7493623</v>
+        <v>19559990</v>
       </c>
       <c r="M3" t="n">
-        <v>10724245</v>
+        <v>27974328</v>
       </c>
       <c r="N3" t="n">
-        <v>11892877</v>
+        <v>38419154</v>
       </c>
       <c r="O3" t="n">
-        <v>8232178</v>
+        <v>78188089</v>
       </c>
       <c r="P3" t="n">
-        <v>5367725</v>
+        <v>16846337</v>
       </c>
       <c r="Q3" t="n">
-        <v>6731221</v>
+        <v>22233669</v>
       </c>
       <c r="R3" t="n">
-        <v>7222369</v>
+        <v>32517682</v>
       </c>
       <c r="S3" t="n">
-        <v>1597909</v>
+        <v>67694424</v>
       </c>
       <c r="T3" t="n">
-        <v>1539024</v>
+        <v>440000</v>
       </c>
       <c r="U3" t="n">
-        <v>3151181</v>
+        <v>3161568</v>
       </c>
       <c r="V3" t="n">
-        <v>3788181</v>
+        <v>3176098</v>
       </c>
       <c r="W3" t="n">
-        <v>7002102</v>
+        <v>4262814</v>
       </c>
       <c r="X3" t="n">
-        <v>586874</v>
+        <v>2273653</v>
       </c>
       <c r="Y3" t="n">
-        <v>841843</v>
+        <v>2579091</v>
       </c>
       <c r="Z3" t="n">
-        <v>882327</v>
+        <v>2725374</v>
       </c>
       <c r="AA3" t="n">
-        <v>-367833</v>
+        <v>6230851</v>
       </c>
       <c r="AB3" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -813,44 +813,44 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>608</v>
+        <v>370</v>
       </c>
       <c r="D4" t="n">
-        <v>559.8</v>
+        <v>342.5</v>
       </c>
       <c r="E4" t="n">
-        <v>513.6</v>
+        <v>328.9</v>
       </c>
       <c r="F4" t="n">
-        <v>478.25</v>
+        <v>319.35</v>
       </c>
       <c r="G4" t="n">
-        <v>20529000</v>
+        <v>33434927</v>
       </c>
       <c r="H4" t="n">
-        <v>7043000</v>
+        <v>17559688</v>
       </c>
       <c r="I4" t="n">
-        <v>608</v>
+        <v>371</v>
       </c>
       <c r="J4" t="n">
-        <v>368</v>
+        <v>270.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-81732</v>
+        <v>7493623</v>
       </c>
       <c r="M4" t="n">
-        <v>1447366</v>
+        <v>10724245</v>
       </c>
       <c r="N4" t="n">
-        <v>2637157</v>
+        <v>11892877</v>
       </c>
       <c r="O4" t="n">
-        <v>13098622</v>
+        <v>8232178</v>
       </c>
       <c r="P4" t="n">
-        <v>279224</v>
+        <v>5367725</v>
       </c>
       <c r="Q4" t="n">
-        <v>1723100</v>
+        <v>6731221</v>
       </c>
       <c r="R4" t="n">
-        <v>2983381</v>
+        <v>7222369</v>
       </c>
       <c r="S4" t="n">
-        <v>12970541</v>
+        <v>1597909</v>
       </c>
       <c r="T4" t="n">
-        <v>17000</v>
+        <v>1539024</v>
       </c>
       <c r="U4" t="n">
-        <v>13700</v>
+        <v>3151181</v>
       </c>
       <c r="V4" t="n">
-        <v>53500</v>
+        <v>3788181</v>
       </c>
       <c r="W4" t="n">
-        <v>83300</v>
+        <v>7002102</v>
       </c>
       <c r="X4" t="n">
-        <v>-377956</v>
+        <v>586874</v>
       </c>
       <c r="Y4" t="n">
-        <v>-289434</v>
+        <v>841843</v>
       </c>
       <c r="Z4" t="n">
-        <v>-399724</v>
+        <v>882327</v>
       </c>
       <c r="AA4" t="n">
-        <v>44781</v>
+        <v>-367833</v>
       </c>
       <c r="AB4" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,110 +920,110 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2355</v>
+        <v>608</v>
       </c>
       <c r="D5" t="n">
-        <v>2306</v>
+        <v>559.8</v>
       </c>
       <c r="E5" t="n">
-        <v>2264.5</v>
+        <v>513.6</v>
       </c>
       <c r="F5" t="n">
-        <v>2263.25</v>
+        <v>478.25</v>
       </c>
       <c r="G5" t="n">
-        <v>104783831</v>
+        <v>20529000</v>
       </c>
       <c r="H5" t="n">
-        <v>49680374</v>
+        <v>7043000</v>
       </c>
       <c r="I5" t="n">
-        <v>2375</v>
+        <v>608</v>
       </c>
       <c r="J5" t="n">
-        <v>2185</v>
+        <v>368</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>14053662</v>
+        <v>-81732</v>
       </c>
       <c r="M5" t="n">
-        <v>17089924</v>
+        <v>1447366</v>
       </c>
       <c r="N5" t="n">
-        <v>17113436</v>
+        <v>2637157</v>
       </c>
       <c r="O5" t="n">
-        <v>-5855754</v>
+        <v>13098622</v>
       </c>
       <c r="P5" t="n">
-        <v>13284272</v>
+        <v>279224</v>
       </c>
       <c r="Q5" t="n">
-        <v>15016579</v>
+        <v>1723100</v>
       </c>
       <c r="R5" t="n">
-        <v>11313611</v>
+        <v>2983381</v>
       </c>
       <c r="S5" t="n">
-        <v>-24739310</v>
+        <v>12970541</v>
       </c>
       <c r="T5" t="n">
-        <v>349249</v>
+        <v>17000</v>
       </c>
       <c r="U5" t="n">
-        <v>815542</v>
+        <v>13700</v>
       </c>
       <c r="V5" t="n">
-        <v>4346753</v>
+        <v>53500</v>
       </c>
       <c r="W5" t="n">
-        <v>16811428</v>
+        <v>83300</v>
       </c>
       <c r="X5" t="n">
-        <v>420141</v>
+        <v>-377956</v>
       </c>
       <c r="Y5" t="n">
-        <v>1257803</v>
+        <v>-289434</v>
       </c>
       <c r="Z5" t="n">
-        <v>1453072</v>
+        <v>-399724</v>
       </c>
       <c r="AA5" t="n">
-        <v>2072128</v>
+        <v>44781</v>
       </c>
       <c r="AB5" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,54 +1037,54 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、接近20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>158</v>
+        <v>2355</v>
       </c>
       <c r="D6" t="n">
-        <v>145.3</v>
+        <v>2306</v>
       </c>
       <c r="E6" t="n">
-        <v>132.9</v>
+        <v>2264.5</v>
       </c>
       <c r="F6" t="n">
-        <v>123.86</v>
+        <v>2263.25</v>
       </c>
       <c r="G6" t="n">
-        <v>249880280</v>
+        <v>104783831</v>
       </c>
       <c r="H6" t="n">
-        <v>349036888</v>
+        <v>49680374</v>
       </c>
       <c r="I6" t="n">
-        <v>158</v>
+        <v>2375</v>
       </c>
       <c r="J6" t="n">
-        <v>91.09999999999999</v>
+        <v>2185</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1092,55 +1092,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>71837337</v>
+        <v>14053662</v>
       </c>
       <c r="M6" t="n">
-        <v>49681962</v>
+        <v>17089924</v>
       </c>
       <c r="N6" t="n">
-        <v>181208140</v>
+        <v>17113436</v>
       </c>
       <c r="O6" t="n">
-        <v>153322650</v>
+        <v>-5855754</v>
       </c>
       <c r="P6" t="n">
-        <v>53583084</v>
+        <v>13284272</v>
       </c>
       <c r="Q6" t="n">
-        <v>16623178</v>
+        <v>15016579</v>
       </c>
       <c r="R6" t="n">
-        <v>135587913</v>
+        <v>11313611</v>
       </c>
       <c r="S6" t="n">
-        <v>100441793</v>
+        <v>-24739310</v>
       </c>
       <c r="T6" t="n">
-        <v>17253000</v>
+        <v>349249</v>
       </c>
       <c r="U6" t="n">
-        <v>32779929</v>
+        <v>815542</v>
       </c>
       <c r="V6" t="n">
-        <v>42395384</v>
+        <v>4346753</v>
       </c>
       <c r="W6" t="n">
-        <v>53557111</v>
+        <v>16811428</v>
       </c>
       <c r="X6" t="n">
-        <v>1001253</v>
+        <v>420141</v>
       </c>
       <c r="Y6" t="n">
-        <v>278855</v>
+        <v>1257803</v>
       </c>
       <c r="Z6" t="n">
-        <v>3224843</v>
+        <v>1453072</v>
       </c>
       <c r="AA6" t="n">
-        <v>-676254</v>
+        <v>2072128</v>
       </c>
       <c r="AB6" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、接近20日高點</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1164,44 +1164,44 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.76</v>
+        <v>158</v>
       </c>
       <c r="D7" t="n">
-        <v>30.08</v>
+        <v>145.3</v>
       </c>
       <c r="E7" t="n">
-        <v>28.81</v>
+        <v>132.9</v>
       </c>
       <c r="F7" t="n">
-        <v>28.21</v>
+        <v>123.86</v>
       </c>
       <c r="G7" t="n">
-        <v>71631385</v>
+        <v>249880280</v>
       </c>
       <c r="H7" t="n">
-        <v>99872752</v>
+        <v>349036888</v>
       </c>
       <c r="I7" t="n">
-        <v>30.8</v>
+        <v>158</v>
       </c>
       <c r="J7" t="n">
-        <v>25.87</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1209,55 +1209,55 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46044135</v>
+        <v>71837337</v>
       </c>
       <c r="M7" t="n">
-        <v>113946253</v>
+        <v>49681962</v>
       </c>
       <c r="N7" t="n">
-        <v>240984669</v>
+        <v>181208140</v>
       </c>
       <c r="O7" t="n">
-        <v>309814450</v>
+        <v>153322650</v>
       </c>
       <c r="P7" t="n">
-        <v>20982164</v>
+        <v>53583084</v>
       </c>
       <c r="Q7" t="n">
-        <v>70088792</v>
+        <v>16623178</v>
       </c>
       <c r="R7" t="n">
-        <v>153032530</v>
+        <v>135587913</v>
       </c>
       <c r="S7" t="n">
-        <v>215271412</v>
+        <v>100441793</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>17253000</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>32779929</v>
       </c>
       <c r="V7" t="n">
-        <v>2500000</v>
+        <v>42395384</v>
       </c>
       <c r="W7" t="n">
-        <v>2500000</v>
+        <v>53557111</v>
       </c>
       <c r="X7" t="n">
-        <v>25061971</v>
+        <v>1001253</v>
       </c>
       <c r="Y7" t="n">
-        <v>43857461</v>
+        <v>278855</v>
       </c>
       <c r="Z7" t="n">
-        <v>85452139</v>
+        <v>3224843</v>
       </c>
       <c r="AA7" t="n">
-        <v>92043038</v>
+        <v>-676254</v>
       </c>
       <c r="AB7" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -1405,37 +1405,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2445</v>
+        <v>30.76</v>
       </c>
       <c r="D9" t="n">
-        <v>2399</v>
+        <v>30.08</v>
       </c>
       <c r="E9" t="n">
-        <v>2197</v>
+        <v>28.81</v>
       </c>
       <c r="F9" t="n">
-        <v>2194</v>
+        <v>28.21</v>
       </c>
       <c r="G9" t="n">
-        <v>17179076</v>
+        <v>71631385</v>
       </c>
       <c r="H9" t="n">
-        <v>13409238</v>
+        <v>99872752</v>
       </c>
       <c r="I9" t="n">
-        <v>2585</v>
+        <v>30.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1880</v>
+        <v>25.87</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>807932</v>
+        <v>46044135</v>
       </c>
       <c r="M9" t="n">
-        <v>2603797</v>
+        <v>113946253</v>
       </c>
       <c r="N9" t="n">
-        <v>10087865</v>
+        <v>240984669</v>
       </c>
       <c r="O9" t="n">
-        <v>7022245</v>
+        <v>309814450</v>
       </c>
       <c r="P9" t="n">
-        <v>159559</v>
+        <v>20982164</v>
       </c>
       <c r="Q9" t="n">
-        <v>1933010</v>
+        <v>70088792</v>
       </c>
       <c r="R9" t="n">
-        <v>8590945</v>
+        <v>153032530</v>
       </c>
       <c r="S9" t="n">
-        <v>8203923</v>
+        <v>215271412</v>
       </c>
       <c r="T9" t="n">
-        <v>604387</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>779198</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1142598</v>
+        <v>2500000</v>
       </c>
       <c r="W9" t="n">
-        <v>-1519176</v>
+        <v>2500000</v>
       </c>
       <c r="X9" t="n">
-        <v>43986</v>
+        <v>25061971</v>
       </c>
       <c r="Y9" t="n">
-        <v>-108411</v>
+        <v>43857461</v>
       </c>
       <c r="Z9" t="n">
-        <v>354322</v>
+        <v>85452139</v>
       </c>
       <c r="AA9" t="n">
-        <v>337498</v>
+        <v>92043038</v>
       </c>
       <c r="AB9" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1515,44 +1515,44 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.8</v>
+        <v>2445</v>
       </c>
       <c r="D10" t="n">
-        <v>19.54</v>
+        <v>2399</v>
       </c>
       <c r="E10" t="n">
-        <v>18.19</v>
+        <v>2197</v>
       </c>
       <c r="F10" t="n">
-        <v>17.56</v>
+        <v>2194</v>
       </c>
       <c r="G10" t="n">
-        <v>18564858</v>
+        <v>17179076</v>
       </c>
       <c r="H10" t="n">
-        <v>37799302</v>
+        <v>13409238</v>
       </c>
       <c r="I10" t="n">
-        <v>22.8</v>
+        <v>2585</v>
       </c>
       <c r="J10" t="n">
-        <v>16.55</v>
+        <v>1880</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,55 +1560,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1404121</v>
+        <v>807932</v>
       </c>
       <c r="M10" t="n">
-        <v>2904196</v>
+        <v>2603797</v>
       </c>
       <c r="N10" t="n">
-        <v>12727687</v>
+        <v>10087865</v>
       </c>
       <c r="O10" t="n">
-        <v>21149602</v>
+        <v>7022245</v>
       </c>
       <c r="P10" t="n">
-        <v>-1010000</v>
+        <v>159559</v>
       </c>
       <c r="Q10" t="n">
-        <v>-627327</v>
+        <v>1933010</v>
       </c>
       <c r="R10" t="n">
-        <v>8971673</v>
+        <v>8590945</v>
       </c>
       <c r="S10" t="n">
-        <v>17636025</v>
+        <v>8203923</v>
       </c>
       <c r="T10" t="n">
-        <v>-4000</v>
+        <v>604387</v>
       </c>
       <c r="U10" t="n">
-        <v>-8000</v>
+        <v>779198</v>
       </c>
       <c r="V10" t="n">
-        <v>-12000</v>
+        <v>1142598</v>
       </c>
       <c r="W10" t="n">
-        <v>486000</v>
+        <v>-1519176</v>
       </c>
       <c r="X10" t="n">
-        <v>2418121</v>
+        <v>43986</v>
       </c>
       <c r="Y10" t="n">
-        <v>3539523</v>
+        <v>-108411</v>
       </c>
       <c r="Z10" t="n">
-        <v>3768014</v>
+        <v>354322</v>
       </c>
       <c r="AA10" t="n">
-        <v>3027577</v>
+        <v>337498</v>
       </c>
       <c r="AB10" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>729</v>
+        <v>22.8</v>
       </c>
       <c r="D11" t="n">
-        <v>695.4</v>
+        <v>19.54</v>
       </c>
       <c r="E11" t="n">
-        <v>616.2</v>
+        <v>18.19</v>
       </c>
       <c r="F11" t="n">
-        <v>557.77</v>
+        <v>17.56</v>
       </c>
       <c r="G11" t="n">
-        <v>7357595</v>
+        <v>18564858</v>
       </c>
       <c r="H11" t="n">
-        <v>21034907</v>
+        <v>37799302</v>
       </c>
       <c r="I11" t="n">
-        <v>764</v>
+        <v>22.8</v>
       </c>
       <c r="J11" t="n">
-        <v>445.5</v>
+        <v>16.55</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2189073</v>
+        <v>1404121</v>
       </c>
       <c r="M11" t="n">
-        <v>764248</v>
+        <v>2904196</v>
       </c>
       <c r="N11" t="n">
-        <v>8308749</v>
+        <v>12727687</v>
       </c>
       <c r="O11" t="n">
-        <v>27987628</v>
+        <v>21149602</v>
       </c>
       <c r="P11" t="n">
-        <v>1727169</v>
+        <v>-1010000</v>
       </c>
       <c r="Q11" t="n">
-        <v>-72044</v>
+        <v>-627327</v>
       </c>
       <c r="R11" t="n">
-        <v>4310104</v>
+        <v>8971673</v>
       </c>
       <c r="S11" t="n">
-        <v>19257046</v>
+        <v>17636025</v>
       </c>
       <c r="T11" t="n">
-        <v>-905</v>
+        <v>-4000</v>
       </c>
       <c r="U11" t="n">
-        <v>870572</v>
+        <v>-8000</v>
       </c>
       <c r="V11" t="n">
-        <v>4336572</v>
+        <v>-12000</v>
       </c>
       <c r="W11" t="n">
-        <v>7874046</v>
+        <v>486000</v>
       </c>
       <c r="X11" t="n">
-        <v>462809</v>
+        <v>2418121</v>
       </c>
       <c r="Y11" t="n">
-        <v>-34280</v>
+        <v>3539523</v>
       </c>
       <c r="Z11" t="n">
-        <v>-337927</v>
+        <v>3768014</v>
       </c>
       <c r="AA11" t="n">
-        <v>856536</v>
+        <v>3027577</v>
       </c>
       <c r="AB11" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,54 +1739,54 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1015</v>
+        <v>166.5</v>
       </c>
       <c r="D12" t="n">
-        <v>905.2</v>
+        <v>159</v>
       </c>
       <c r="E12" t="n">
-        <v>794.5</v>
+        <v>153.05</v>
       </c>
       <c r="F12" t="n">
-        <v>770.05</v>
+        <v>157.35</v>
       </c>
       <c r="G12" t="n">
-        <v>11189000</v>
+        <v>170917629</v>
       </c>
       <c r="H12" t="n">
-        <v>12916600</v>
+        <v>186682969</v>
       </c>
       <c r="I12" t="n">
-        <v>1020</v>
+        <v>178.5</v>
       </c>
       <c r="J12" t="n">
-        <v>597</v>
+        <v>136.5</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,55 +1794,55 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1670438</v>
+        <v>8055757</v>
       </c>
       <c r="M12" t="n">
-        <v>7193475</v>
+        <v>42604570</v>
       </c>
       <c r="N12" t="n">
-        <v>6390247</v>
+        <v>86425911</v>
       </c>
       <c r="O12" t="n">
-        <v>1446388</v>
+        <v>14319682</v>
       </c>
       <c r="P12" t="n">
-        <v>344138</v>
+        <v>8184461</v>
       </c>
       <c r="Q12" t="n">
-        <v>-664171</v>
+        <v>44126812</v>
       </c>
       <c r="R12" t="n">
-        <v>-1656428</v>
+        <v>85615640</v>
       </c>
       <c r="S12" t="n">
-        <v>-7353618</v>
+        <v>29588979</v>
       </c>
       <c r="T12" t="n">
-        <v>1146000</v>
+        <v>23000</v>
       </c>
       <c r="U12" t="n">
-        <v>7953133</v>
+        <v>-284000</v>
       </c>
       <c r="V12" t="n">
-        <v>7798095</v>
+        <v>2026000</v>
       </c>
       <c r="W12" t="n">
-        <v>7456907</v>
+        <v>-11302000</v>
       </c>
       <c r="X12" t="n">
-        <v>180300</v>
+        <v>-151704</v>
       </c>
       <c r="Y12" t="n">
-        <v>-95487</v>
+        <v>-1238242</v>
       </c>
       <c r="Z12" t="n">
-        <v>248580</v>
+        <v>-1215729</v>
       </c>
       <c r="AA12" t="n">
-        <v>1343099</v>
+        <v>-3967297</v>
       </c>
       <c r="AB12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,54 +1856,54 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、黃金交叉、量能未放大</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>347</v>
+        <v>729</v>
       </c>
       <c r="D13" t="n">
-        <v>316.5</v>
+        <v>695.4</v>
       </c>
       <c r="E13" t="n">
-        <v>304.05</v>
+        <v>616.2</v>
       </c>
       <c r="F13" t="n">
-        <v>298.62</v>
+        <v>557.77</v>
       </c>
       <c r="G13" t="n">
-        <v>140975644</v>
+        <v>7357595</v>
       </c>
       <c r="H13" t="n">
-        <v>176543954</v>
+        <v>21034907</v>
       </c>
       <c r="I13" t="n">
-        <v>353</v>
+        <v>764</v>
       </c>
       <c r="J13" t="n">
-        <v>217</v>
+        <v>445.5</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>24486580</v>
+        <v>2189073</v>
       </c>
       <c r="M13" t="n">
-        <v>92243642</v>
+        <v>764248</v>
       </c>
       <c r="N13" t="n">
-        <v>82863197</v>
+        <v>8308749</v>
       </c>
       <c r="O13" t="n">
-        <v>41889398</v>
+        <v>27987628</v>
       </c>
       <c r="P13" t="n">
-        <v>19483386</v>
+        <v>1727169</v>
       </c>
       <c r="Q13" t="n">
-        <v>87397337</v>
+        <v>-72044</v>
       </c>
       <c r="R13" t="n">
-        <v>93426579</v>
+        <v>4310104</v>
       </c>
       <c r="S13" t="n">
-        <v>72607197</v>
+        <v>19257046</v>
       </c>
       <c r="T13" t="n">
-        <v>4795000</v>
+        <v>-905</v>
       </c>
       <c r="U13" t="n">
-        <v>5562330</v>
+        <v>870572</v>
       </c>
       <c r="V13" t="n">
-        <v>-9187395</v>
+        <v>4336572</v>
       </c>
       <c r="W13" t="n">
-        <v>-23784560</v>
+        <v>7874046</v>
       </c>
       <c r="X13" t="n">
-        <v>208194</v>
+        <v>462809</v>
       </c>
       <c r="Y13" t="n">
-        <v>-716025</v>
+        <v>-34280</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1375987</v>
+        <v>-337927</v>
       </c>
       <c r="AA13" t="n">
-        <v>-6933239</v>
+        <v>856536</v>
       </c>
       <c r="AB13" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,54 +1973,54 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>98.09999999999999</v>
+        <v>347</v>
       </c>
       <c r="D14" t="n">
-        <v>92.40000000000001</v>
+        <v>316.5</v>
       </c>
       <c r="E14" t="n">
-        <v>88.27</v>
+        <v>304.05</v>
       </c>
       <c r="F14" t="n">
-        <v>88.78</v>
+        <v>298.62</v>
       </c>
       <c r="G14" t="n">
-        <v>150486779</v>
+        <v>140975644</v>
       </c>
       <c r="H14" t="n">
-        <v>99920545</v>
+        <v>176543954</v>
       </c>
       <c r="I14" t="n">
-        <v>101.5</v>
+        <v>353</v>
       </c>
       <c r="J14" t="n">
-        <v>80.40000000000001</v>
+        <v>217</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2028,55 +2028,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>63814268</v>
+        <v>24486580</v>
       </c>
       <c r="M14" t="n">
-        <v>84945508</v>
+        <v>92243642</v>
       </c>
       <c r="N14" t="n">
-        <v>122013685</v>
+        <v>82863197</v>
       </c>
       <c r="O14" t="n">
-        <v>106076369</v>
+        <v>41889398</v>
       </c>
       <c r="P14" t="n">
-        <v>59319659</v>
+        <v>19483386</v>
       </c>
       <c r="Q14" t="n">
-        <v>79980257</v>
+        <v>87397337</v>
       </c>
       <c r="R14" t="n">
-        <v>115454226</v>
+        <v>93426579</v>
       </c>
       <c r="S14" t="n">
-        <v>104358632</v>
+        <v>72607197</v>
       </c>
       <c r="T14" t="n">
-        <v>2301457</v>
+        <v>4795000</v>
       </c>
       <c r="U14" t="n">
-        <v>3965189</v>
+        <v>5562330</v>
       </c>
       <c r="V14" t="n">
-        <v>2988189</v>
+        <v>-9187395</v>
       </c>
       <c r="W14" t="n">
-        <v>2977289</v>
+        <v>-23784560</v>
       </c>
       <c r="X14" t="n">
-        <v>2193152</v>
+        <v>208194</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000062</v>
+        <v>-716025</v>
       </c>
       <c r="Z14" t="n">
-        <v>3571270</v>
+        <v>-1375987</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1259552</v>
+        <v>-6933239</v>
       </c>
       <c r="AB14" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2090,54 +2090,54 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>52.7</v>
+        <v>1015</v>
       </c>
       <c r="D15" t="n">
-        <v>52.28</v>
+        <v>905.2</v>
       </c>
       <c r="E15" t="n">
-        <v>51.39</v>
+        <v>794.5</v>
       </c>
       <c r="F15" t="n">
-        <v>50.59</v>
+        <v>770.05</v>
       </c>
       <c r="G15" t="n">
-        <v>29776823</v>
+        <v>11189000</v>
       </c>
       <c r="H15" t="n">
-        <v>24715593</v>
+        <v>12916600</v>
       </c>
       <c r="I15" t="n">
-        <v>53.9</v>
+        <v>1020</v>
       </c>
       <c r="J15" t="n">
-        <v>47.35</v>
+        <v>597</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,55 +2145,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7389461</v>
+        <v>1670438</v>
       </c>
       <c r="M15" t="n">
-        <v>24139514</v>
+        <v>7193475</v>
       </c>
       <c r="N15" t="n">
-        <v>19611659</v>
+        <v>6390247</v>
       </c>
       <c r="O15" t="n">
-        <v>55290712</v>
+        <v>1446388</v>
       </c>
       <c r="P15" t="n">
-        <v>7588362</v>
+        <v>344138</v>
       </c>
       <c r="Q15" t="n">
-        <v>25352759</v>
+        <v>-664171</v>
       </c>
       <c r="R15" t="n">
-        <v>21862491</v>
+        <v>-1656428</v>
       </c>
       <c r="S15" t="n">
-        <v>55769432</v>
+        <v>-7353618</v>
       </c>
       <c r="T15" t="n">
-        <v>-337924</v>
+        <v>1146000</v>
       </c>
       <c r="U15" t="n">
-        <v>-1821392</v>
+        <v>7953133</v>
       </c>
       <c r="V15" t="n">
-        <v>-1815242</v>
+        <v>7798095</v>
       </c>
       <c r="W15" t="n">
-        <v>-1896308</v>
+        <v>7456907</v>
       </c>
       <c r="X15" t="n">
-        <v>139023</v>
+        <v>180300</v>
       </c>
       <c r="Y15" t="n">
-        <v>608147</v>
+        <v>-95487</v>
       </c>
       <c r="Z15" t="n">
-        <v>-435590</v>
+        <v>248580</v>
       </c>
       <c r="AA15" t="n">
-        <v>1417588</v>
+        <v>1343099</v>
       </c>
       <c r="AB15" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -2207,54 +2207,54 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1690</v>
+        <v>52.7</v>
       </c>
       <c r="D16" t="n">
-        <v>1608</v>
+        <v>52.28</v>
       </c>
       <c r="E16" t="n">
-        <v>1451</v>
+        <v>51.39</v>
       </c>
       <c r="F16" t="n">
-        <v>1404</v>
+        <v>50.59</v>
       </c>
       <c r="G16" t="n">
-        <v>9688000</v>
+        <v>29776823</v>
       </c>
       <c r="H16" t="n">
-        <v>7520400</v>
+        <v>24715593</v>
       </c>
       <c r="I16" t="n">
-        <v>1735</v>
+        <v>53.9</v>
       </c>
       <c r="J16" t="n">
-        <v>1060</v>
+        <v>47.35</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,52 +2262,52 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1026806</v>
+        <v>7389461</v>
       </c>
       <c r="M16" t="n">
-        <v>1458560</v>
+        <v>24139514</v>
       </c>
       <c r="N16" t="n">
-        <v>1657269</v>
+        <v>19611659</v>
       </c>
       <c r="O16" t="n">
-        <v>2868520</v>
+        <v>55290712</v>
       </c>
       <c r="P16" t="n">
-        <v>80409</v>
+        <v>7588362</v>
       </c>
       <c r="Q16" t="n">
-        <v>-883531</v>
+        <v>25352759</v>
       </c>
       <c r="R16" t="n">
-        <v>-1794129</v>
+        <v>21862491</v>
       </c>
       <c r="S16" t="n">
-        <v>-598456</v>
+        <v>55769432</v>
       </c>
       <c r="T16" t="n">
-        <v>977000</v>
+        <v>-337924</v>
       </c>
       <c r="U16" t="n">
-        <v>2608000</v>
+        <v>-1821392</v>
       </c>
       <c r="V16" t="n">
-        <v>4053000</v>
+        <v>-1815242</v>
       </c>
       <c r="W16" t="n">
-        <v>3920100</v>
+        <v>-1896308</v>
       </c>
       <c r="X16" t="n">
-        <v>-30603</v>
+        <v>139023</v>
       </c>
       <c r="Y16" t="n">
-        <v>-265909</v>
+        <v>608147</v>
       </c>
       <c r="Z16" t="n">
-        <v>-601602</v>
+        <v>-435590</v>
       </c>
       <c r="AA16" t="n">
-        <v>-453124</v>
+        <v>1417588</v>
       </c>
       <c r="AB16" t="n">
         <v>115</v>
@@ -2329,49 +2329,49 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7769.TW</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8260</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>7861</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>7494.5</v>
+        <v>88.27</v>
       </c>
       <c r="F17" t="n">
-        <v>6920.5</v>
+        <v>88.78</v>
       </c>
       <c r="G17" t="n">
-        <v>1880557</v>
+        <v>150486779</v>
       </c>
       <c r="H17" t="n">
-        <v>878607</v>
+        <v>99920545</v>
       </c>
       <c r="I17" t="n">
-        <v>8465</v>
+        <v>101.5</v>
       </c>
       <c r="J17" t="n">
-        <v>5030</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,52 +2379,52 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>102468</v>
+        <v>63814268</v>
       </c>
       <c r="M17" t="n">
-        <v>234245</v>
+        <v>84945508</v>
       </c>
       <c r="N17" t="n">
-        <v>165465</v>
+        <v>122013685</v>
       </c>
       <c r="O17" t="n">
-        <v>87623</v>
+        <v>106076369</v>
       </c>
       <c r="P17" t="n">
-        <v>-49388</v>
+        <v>59319659</v>
       </c>
       <c r="Q17" t="n">
-        <v>-273656</v>
+        <v>79980257</v>
       </c>
       <c r="R17" t="n">
-        <v>-310537</v>
+        <v>115454226</v>
       </c>
       <c r="S17" t="n">
-        <v>-250052</v>
+        <v>104358632</v>
       </c>
       <c r="T17" t="n">
-        <v>160004</v>
+        <v>2301457</v>
       </c>
       <c r="U17" t="n">
-        <v>511004</v>
+        <v>3965189</v>
       </c>
       <c r="V17" t="n">
-        <v>471853</v>
+        <v>2988189</v>
       </c>
       <c r="W17" t="n">
-        <v>361853</v>
+        <v>2977289</v>
       </c>
       <c r="X17" t="n">
-        <v>-8148</v>
+        <v>2193152</v>
       </c>
       <c r="Y17" t="n">
-        <v>-3103</v>
+        <v>1000062</v>
       </c>
       <c r="Z17" t="n">
-        <v>4149</v>
+        <v>3571270</v>
       </c>
       <c r="AA17" t="n">
-        <v>-24178</v>
+        <v>-1259552</v>
       </c>
       <c r="AB17" t="n">
         <v>115</v>
@@ -2441,54 +2441,54 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、法人連續偏買、5日法人買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>7769.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57.9</v>
+        <v>8260</v>
       </c>
       <c r="D18" t="n">
-        <v>56.5</v>
+        <v>7861</v>
       </c>
       <c r="E18" t="n">
-        <v>53.79</v>
+        <v>7494.5</v>
       </c>
       <c r="F18" t="n">
-        <v>51.82</v>
+        <v>6920.5</v>
       </c>
       <c r="G18" t="n">
-        <v>10061343</v>
+        <v>1880557</v>
       </c>
       <c r="H18" t="n">
-        <v>13310924</v>
+        <v>878607</v>
       </c>
       <c r="I18" t="n">
-        <v>61.4</v>
+        <v>8465</v>
       </c>
       <c r="J18" t="n">
-        <v>45.45</v>
+        <v>5030</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2496,55 +2496,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>223942</v>
+        <v>102468</v>
       </c>
       <c r="M18" t="n">
-        <v>1174650</v>
+        <v>234245</v>
       </c>
       <c r="N18" t="n">
-        <v>4573006</v>
+        <v>165465</v>
       </c>
       <c r="O18" t="n">
-        <v>15563085</v>
+        <v>87623</v>
       </c>
       <c r="P18" t="n">
-        <v>36212</v>
+        <v>-49388</v>
       </c>
       <c r="Q18" t="n">
-        <v>898012</v>
+        <v>-273656</v>
       </c>
       <c r="R18" t="n">
-        <v>3887881</v>
+        <v>-310537</v>
       </c>
       <c r="S18" t="n">
-        <v>14415725</v>
+        <v>-250052</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>160004</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>511004</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>471853</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>361853</v>
       </c>
       <c r="X18" t="n">
-        <v>187730</v>
+        <v>-8148</v>
       </c>
       <c r="Y18" t="n">
-        <v>276638</v>
+        <v>-3103</v>
       </c>
       <c r="Z18" t="n">
-        <v>685125</v>
+        <v>4149</v>
       </c>
       <c r="AA18" t="n">
-        <v>1147360</v>
+        <v>-24178</v>
       </c>
       <c r="AB18" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2558,54 +2558,54 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、法人連續偏買、5日法人買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5445</v>
+        <v>1690</v>
       </c>
       <c r="D19" t="n">
-        <v>5272</v>
+        <v>1608</v>
       </c>
       <c r="E19" t="n">
-        <v>5212</v>
+        <v>1451</v>
       </c>
       <c r="F19" t="n">
-        <v>5202.25</v>
+        <v>1404</v>
       </c>
       <c r="G19" t="n">
-        <v>3282663</v>
+        <v>9688000</v>
       </c>
       <c r="H19" t="n">
-        <v>2442013</v>
+        <v>7520400</v>
       </c>
       <c r="I19" t="n">
-        <v>5880</v>
+        <v>1735</v>
       </c>
       <c r="J19" t="n">
-        <v>4615</v>
+        <v>1060</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2613,55 +2613,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>816883</v>
+        <v>1026806</v>
       </c>
       <c r="M19" t="n">
-        <v>261458</v>
+        <v>1458560</v>
       </c>
       <c r="N19" t="n">
-        <v>180474</v>
+        <v>1657269</v>
       </c>
       <c r="O19" t="n">
-        <v>-14803</v>
+        <v>2868520</v>
       </c>
       <c r="P19" t="n">
-        <v>625866</v>
+        <v>80409</v>
       </c>
       <c r="Q19" t="n">
-        <v>595836</v>
+        <v>-883531</v>
       </c>
       <c r="R19" t="n">
-        <v>788866</v>
+        <v>-1794129</v>
       </c>
       <c r="S19" t="n">
-        <v>679185</v>
+        <v>-598456</v>
       </c>
       <c r="T19" t="n">
-        <v>175961</v>
+        <v>977000</v>
       </c>
       <c r="U19" t="n">
-        <v>-136176</v>
+        <v>2608000</v>
       </c>
       <c r="V19" t="n">
-        <v>-384349</v>
+        <v>4053000</v>
       </c>
       <c r="W19" t="n">
-        <v>-599555</v>
+        <v>3920100</v>
       </c>
       <c r="X19" t="n">
-        <v>15056</v>
+        <v>-30603</v>
       </c>
       <c r="Y19" t="n">
-        <v>-198202</v>
+        <v>-265909</v>
       </c>
       <c r="Z19" t="n">
-        <v>-224043</v>
+        <v>-601602</v>
       </c>
       <c r="AA19" t="n">
-        <v>-94433</v>
+        <v>-453124</v>
       </c>
       <c r="AB19" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2680,49 +2680,49 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>319</v>
+        <v>2665</v>
       </c>
       <c r="D20" t="n">
-        <v>307.4</v>
+        <v>2649</v>
       </c>
       <c r="E20" t="n">
-        <v>297.05</v>
+        <v>2542.5</v>
       </c>
       <c r="F20" t="n">
-        <v>275</v>
+        <v>2549</v>
       </c>
       <c r="G20" t="n">
-        <v>26333214</v>
+        <v>9351169</v>
       </c>
       <c r="H20" t="n">
-        <v>28680323</v>
+        <v>6152175</v>
       </c>
       <c r="I20" t="n">
-        <v>336.5</v>
+        <v>2975</v>
       </c>
       <c r="J20" t="n">
-        <v>217.5</v>
+        <v>2300</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,55 +2730,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1768455</v>
+        <v>574826</v>
       </c>
       <c r="M20" t="n">
-        <v>6314708</v>
+        <v>491421</v>
       </c>
       <c r="N20" t="n">
-        <v>5650116</v>
+        <v>1482876</v>
       </c>
       <c r="O20" t="n">
-        <v>5110144</v>
+        <v>-108322</v>
       </c>
       <c r="P20" t="n">
-        <v>1507659</v>
+        <v>232388</v>
       </c>
       <c r="Q20" t="n">
-        <v>5144713</v>
+        <v>-19731</v>
       </c>
       <c r="R20" t="n">
-        <v>5860298</v>
+        <v>302816</v>
       </c>
       <c r="S20" t="n">
-        <v>11469805</v>
+        <v>-2201792</v>
       </c>
       <c r="T20" t="n">
-        <v>139000</v>
+        <v>298876</v>
       </c>
       <c r="U20" t="n">
-        <v>1060768</v>
+        <v>654876</v>
       </c>
       <c r="V20" t="n">
-        <v>-313232</v>
+        <v>1217899</v>
       </c>
       <c r="W20" t="n">
-        <v>-6063208</v>
+        <v>2179460</v>
       </c>
       <c r="X20" t="n">
-        <v>121796</v>
+        <v>43562</v>
       </c>
       <c r="Y20" t="n">
-        <v>109227</v>
+        <v>-143724</v>
       </c>
       <c r="Z20" t="n">
-        <v>103050</v>
+        <v>-37839</v>
       </c>
       <c r="AA20" t="n">
-        <v>-296453</v>
+        <v>-85990</v>
       </c>
       <c r="AB20" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -2792,54 +2792,54 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1055</v>
+        <v>5445</v>
       </c>
       <c r="D21" t="n">
-        <v>1047</v>
+        <v>5272</v>
       </c>
       <c r="E21" t="n">
-        <v>956.7</v>
+        <v>5212</v>
       </c>
       <c r="F21" t="n">
-        <v>914.15</v>
+        <v>5202.25</v>
       </c>
       <c r="G21" t="n">
-        <v>21107426</v>
+        <v>3282663</v>
       </c>
       <c r="H21" t="n">
-        <v>26475004</v>
+        <v>2442013</v>
       </c>
       <c r="I21" t="n">
-        <v>1130</v>
+        <v>5880</v>
       </c>
       <c r="J21" t="n">
-        <v>776</v>
+        <v>4615</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,55 +2847,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1460277</v>
+        <v>816883</v>
       </c>
       <c r="M21" t="n">
-        <v>-194509</v>
+        <v>261458</v>
       </c>
       <c r="N21" t="n">
-        <v>12773317</v>
+        <v>180474</v>
       </c>
       <c r="O21" t="n">
-        <v>25914308</v>
+        <v>-14803</v>
       </c>
       <c r="P21" t="n">
-        <v>-1150135</v>
+        <v>625866</v>
       </c>
       <c r="Q21" t="n">
-        <v>-608166</v>
+        <v>595836</v>
       </c>
       <c r="R21" t="n">
-        <v>9847208</v>
+        <v>788866</v>
       </c>
       <c r="S21" t="n">
-        <v>21378067</v>
+        <v>679185</v>
       </c>
       <c r="T21" t="n">
-        <v>-225373</v>
+        <v>175961</v>
       </c>
       <c r="U21" t="n">
-        <v>1293627</v>
+        <v>-136176</v>
       </c>
       <c r="V21" t="n">
-        <v>3733627</v>
+        <v>-384349</v>
       </c>
       <c r="W21" t="n">
-        <v>5098570</v>
+        <v>-599555</v>
       </c>
       <c r="X21" t="n">
-        <v>-84769</v>
+        <v>15056</v>
       </c>
       <c r="Y21" t="n">
-        <v>-879970</v>
+        <v>-198202</v>
       </c>
       <c r="Z21" t="n">
-        <v>-807518</v>
+        <v>-224043</v>
       </c>
       <c r="AA21" t="n">
-        <v>-562329</v>
+        <v>-94433</v>
       </c>
       <c r="AB21" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -2909,110 +2909,110 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>834</v>
+        <v>319</v>
       </c>
       <c r="D22" t="n">
-        <v>834.8</v>
+        <v>307.4</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>297.05</v>
       </c>
       <c r="F22" t="n">
-        <v>745.65</v>
+        <v>275</v>
       </c>
       <c r="G22" t="n">
-        <v>9119000</v>
+        <v>26333214</v>
       </c>
       <c r="H22" t="n">
-        <v>4059200</v>
+        <v>28680323</v>
       </c>
       <c r="I22" t="n">
-        <v>929</v>
+        <v>336.5</v>
       </c>
       <c r="J22" t="n">
-        <v>553</v>
+        <v>217.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>725160</v>
+        <v>1768455</v>
       </c>
       <c r="M22" t="n">
-        <v>2193908</v>
+        <v>6314708</v>
       </c>
       <c r="N22" t="n">
-        <v>1256711</v>
+        <v>5650116</v>
       </c>
       <c r="O22" t="n">
-        <v>1527094</v>
+        <v>5110144</v>
       </c>
       <c r="P22" t="n">
-        <v>-520625</v>
+        <v>1507659</v>
       </c>
       <c r="Q22" t="n">
-        <v>834333</v>
+        <v>5144713</v>
       </c>
       <c r="R22" t="n">
-        <v>70799</v>
+        <v>5860298</v>
       </c>
       <c r="S22" t="n">
-        <v>357165</v>
+        <v>11469805</v>
       </c>
       <c r="T22" t="n">
-        <v>1195000</v>
+        <v>139000</v>
       </c>
       <c r="U22" t="n">
-        <v>1192000</v>
+        <v>1060768</v>
       </c>
       <c r="V22" t="n">
-        <v>995000</v>
+        <v>-313232</v>
       </c>
       <c r="W22" t="n">
-        <v>976000</v>
+        <v>-6063208</v>
       </c>
       <c r="X22" t="n">
-        <v>50785</v>
+        <v>121796</v>
       </c>
       <c r="Y22" t="n">
-        <v>167575</v>
+        <v>109227</v>
       </c>
       <c r="Z22" t="n">
-        <v>190912</v>
+        <v>103050</v>
       </c>
       <c r="AA22" t="n">
-        <v>193929</v>
+        <v>-296453</v>
       </c>
       <c r="AB22" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -3026,54 +3026,54 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>強勢偏多：跌破5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>379</v>
+        <v>229.5</v>
       </c>
       <c r="D23" t="n">
-        <v>346</v>
+        <v>216.8</v>
       </c>
       <c r="E23" t="n">
-        <v>298.2</v>
+        <v>204.9</v>
       </c>
       <c r="F23" t="n">
-        <v>264.02</v>
+        <v>191.4</v>
       </c>
       <c r="G23" t="n">
-        <v>17024627</v>
+        <v>11072000</v>
       </c>
       <c r="H23" t="n">
-        <v>47751060</v>
+        <v>12985800</v>
       </c>
       <c r="I23" t="n">
-        <v>387</v>
+        <v>238</v>
       </c>
       <c r="J23" t="n">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,55 +3081,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1530721</v>
+        <v>1922480</v>
       </c>
       <c r="M23" t="n">
-        <v>9386598</v>
+        <v>928804</v>
       </c>
       <c r="N23" t="n">
-        <v>9329511</v>
+        <v>1930767</v>
       </c>
       <c r="O23" t="n">
-        <v>2976549</v>
+        <v>3221267</v>
       </c>
       <c r="P23" t="n">
-        <v>-1822021</v>
+        <v>1883000</v>
       </c>
       <c r="Q23" t="n">
-        <v>9593946</v>
+        <v>795795</v>
       </c>
       <c r="R23" t="n">
-        <v>9756699</v>
+        <v>1868268</v>
       </c>
       <c r="S23" t="n">
-        <v>5846660</v>
+        <v>2928312</v>
       </c>
       <c r="T23" t="n">
-        <v>-99797</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-339782</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-1394782</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-4249884</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>391097</v>
+        <v>39480</v>
       </c>
       <c r="Y23" t="n">
-        <v>132434</v>
+        <v>133009</v>
       </c>
       <c r="Z23" t="n">
-        <v>967594</v>
+        <v>62499</v>
       </c>
       <c r="AA23" t="n">
-        <v>1379773</v>
+        <v>292955</v>
       </c>
       <c r="AB23" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -3148,49 +3148,49 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41.65</v>
+        <v>57.9</v>
       </c>
       <c r="D24" t="n">
-        <v>42.2</v>
+        <v>56.5</v>
       </c>
       <c r="E24" t="n">
-        <v>41.59</v>
+        <v>53.79</v>
       </c>
       <c r="F24" t="n">
-        <v>40.29</v>
+        <v>51.82</v>
       </c>
       <c r="G24" t="n">
-        <v>17386615</v>
+        <v>10061343</v>
       </c>
       <c r="H24" t="n">
-        <v>27652053</v>
+        <v>13310924</v>
       </c>
       <c r="I24" t="n">
-        <v>44.75</v>
+        <v>61.4</v>
       </c>
       <c r="J24" t="n">
-        <v>37.45</v>
+        <v>45.45</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,116 +3198,116 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1337515</v>
+        <v>223942</v>
       </c>
       <c r="M24" t="n">
-        <v>14595424</v>
+        <v>1174650</v>
       </c>
       <c r="N24" t="n">
-        <v>18051673</v>
+        <v>4573006</v>
       </c>
       <c r="O24" t="n">
-        <v>68742480</v>
+        <v>15563085</v>
       </c>
       <c r="P24" t="n">
-        <v>1218184</v>
+        <v>36212</v>
       </c>
       <c r="Q24" t="n">
-        <v>13702965</v>
+        <v>898012</v>
       </c>
       <c r="R24" t="n">
-        <v>18247222</v>
+        <v>3887881</v>
       </c>
       <c r="S24" t="n">
-        <v>76134911</v>
+        <v>14415725</v>
       </c>
       <c r="T24" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-1134000</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-4558000</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>124331</v>
+        <v>187730</v>
       </c>
       <c r="Y24" t="n">
-        <v>897459</v>
+        <v>276638</v>
       </c>
       <c r="Z24" t="n">
-        <v>938451</v>
+        <v>685125</v>
       </c>
       <c r="AA24" t="n">
-        <v>-2834431</v>
+        <v>1147360</v>
       </c>
       <c r="AB24" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5120</v>
+        <v>1055</v>
       </c>
       <c r="D25" t="n">
-        <v>5255</v>
+        <v>1047</v>
       </c>
       <c r="E25" t="n">
-        <v>4944.5</v>
+        <v>956.7</v>
       </c>
       <c r="F25" t="n">
-        <v>4890.25</v>
+        <v>914.15</v>
       </c>
       <c r="G25" t="n">
-        <v>3687942</v>
+        <v>21107426</v>
       </c>
       <c r="H25" t="n">
-        <v>2607763</v>
+        <v>26475004</v>
       </c>
       <c r="I25" t="n">
-        <v>5635</v>
+        <v>1130</v>
       </c>
       <c r="J25" t="n">
-        <v>4300</v>
+        <v>776</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,116 +3315,116 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-36426</v>
+        <v>-1460277</v>
       </c>
       <c r="M25" t="n">
-        <v>330831</v>
+        <v>-194509</v>
       </c>
       <c r="N25" t="n">
-        <v>485528</v>
+        <v>12773317</v>
       </c>
       <c r="O25" t="n">
-        <v>1932087</v>
+        <v>25914308</v>
       </c>
       <c r="P25" t="n">
-        <v>-148221</v>
+        <v>-1150135</v>
       </c>
       <c r="Q25" t="n">
-        <v>67864</v>
+        <v>-608166</v>
       </c>
       <c r="R25" t="n">
-        <v>314229</v>
+        <v>9847208</v>
       </c>
       <c r="S25" t="n">
-        <v>2085929</v>
+        <v>21378067</v>
       </c>
       <c r="T25" t="n">
-        <v>91082</v>
+        <v>-225373</v>
       </c>
       <c r="U25" t="n">
-        <v>283675</v>
+        <v>1293627</v>
       </c>
       <c r="V25" t="n">
-        <v>204689</v>
+        <v>3733627</v>
       </c>
       <c r="W25" t="n">
-        <v>-43363</v>
+        <v>5098570</v>
       </c>
       <c r="X25" t="n">
-        <v>20713</v>
+        <v>-84769</v>
       </c>
       <c r="Y25" t="n">
-        <v>-20708</v>
+        <v>-879970</v>
       </c>
       <c r="Z25" t="n">
-        <v>-33390</v>
+        <v>-807518</v>
       </c>
       <c r="AA25" t="n">
-        <v>-110479</v>
+        <v>-562329</v>
       </c>
       <c r="AB25" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>36.05</v>
+        <v>213</v>
       </c>
       <c r="D26" t="n">
-        <v>35.36</v>
+        <v>212.2</v>
       </c>
       <c r="E26" t="n">
-        <v>35.05</v>
+        <v>209.9</v>
       </c>
       <c r="F26" t="n">
-        <v>34.92</v>
+        <v>210</v>
       </c>
       <c r="G26" t="n">
-        <v>122963731</v>
+        <v>30658046</v>
       </c>
       <c r="H26" t="n">
-        <v>81897844</v>
+        <v>30267084</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>222</v>
       </c>
       <c r="J26" t="n">
-        <v>33.4</v>
+        <v>195.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,233 +3432,233 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>16457567</v>
+        <v>4499672</v>
       </c>
       <c r="M26" t="n">
-        <v>11483651</v>
+        <v>5440527</v>
       </c>
       <c r="N26" t="n">
-        <v>-4247964</v>
+        <v>4632636</v>
       </c>
       <c r="O26" t="n">
-        <v>5314718</v>
+        <v>30344824</v>
       </c>
       <c r="P26" t="n">
-        <v>-20469399</v>
+        <v>-7914383</v>
       </c>
       <c r="Q26" t="n">
-        <v>-71180490</v>
+        <v>-28514697</v>
       </c>
       <c r="R26" t="n">
-        <v>-112366470</v>
+        <v>-41309715</v>
       </c>
       <c r="S26" t="n">
-        <v>-124696352</v>
+        <v>-16655106</v>
       </c>
       <c r="T26" t="n">
-        <v>36156345</v>
+        <v>12001461</v>
       </c>
       <c r="U26" t="n">
-        <v>81328402</v>
+        <v>32272051</v>
       </c>
       <c r="V26" t="n">
-        <v>105198860</v>
+        <v>43663057</v>
       </c>
       <c r="W26" t="n">
-        <v>127993964</v>
+        <v>42882125</v>
       </c>
       <c r="X26" t="n">
-        <v>770621</v>
+        <v>412594</v>
       </c>
       <c r="Y26" t="n">
-        <v>1335739</v>
+        <v>1683173</v>
       </c>
       <c r="Z26" t="n">
-        <v>2919646</v>
+        <v>2279294</v>
       </c>
       <c r="AA26" t="n">
-        <v>2017106</v>
+        <v>4117805</v>
       </c>
       <c r="AB26" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、接近20日高點、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>436</v>
+        <v>834</v>
       </c>
       <c r="D27" t="n">
-        <v>447.6</v>
+        <v>834.8</v>
       </c>
       <c r="E27" t="n">
-        <v>405.25</v>
+        <v>800</v>
       </c>
       <c r="F27" t="n">
-        <v>392.2</v>
+        <v>745.65</v>
       </c>
       <c r="G27" t="n">
-        <v>10858000</v>
+        <v>9119000</v>
       </c>
       <c r="H27" t="n">
-        <v>16704800</v>
+        <v>4059200</v>
       </c>
       <c r="I27" t="n">
-        <v>492.5</v>
+        <v>929</v>
       </c>
       <c r="J27" t="n">
-        <v>343</v>
+        <v>553</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-2759531</v>
+        <v>725160</v>
       </c>
       <c r="M27" t="n">
-        <v>-1248331</v>
+        <v>2193908</v>
       </c>
       <c r="N27" t="n">
-        <v>10551657</v>
+        <v>1256711</v>
       </c>
       <c r="O27" t="n">
-        <v>9369379</v>
+        <v>1527094</v>
       </c>
       <c r="P27" t="n">
-        <v>-2821709</v>
+        <v>-520625</v>
       </c>
       <c r="Q27" t="n">
-        <v>-647260</v>
+        <v>834333</v>
       </c>
       <c r="R27" t="n">
-        <v>12234799</v>
+        <v>70799</v>
       </c>
       <c r="S27" t="n">
-        <v>13596569</v>
+        <v>357165</v>
       </c>
       <c r="T27" t="n">
-        <v>-12000</v>
+        <v>1195000</v>
       </c>
       <c r="U27" t="n">
-        <v>-330000</v>
+        <v>1192000</v>
       </c>
       <c r="V27" t="n">
-        <v>-1959000</v>
+        <v>995000</v>
       </c>
       <c r="W27" t="n">
-        <v>-5111631</v>
+        <v>976000</v>
       </c>
       <c r="X27" t="n">
-        <v>74178</v>
+        <v>50785</v>
       </c>
       <c r="Y27" t="n">
-        <v>-271071</v>
+        <v>167575</v>
       </c>
       <c r="Z27" t="n">
-        <v>275858</v>
+        <v>190912</v>
       </c>
       <c r="AA27" t="n">
-        <v>884441</v>
+        <v>193929</v>
       </c>
       <c r="AB27" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：跌破5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1065</v>
+        <v>61.1</v>
       </c>
       <c r="D28" t="n">
-        <v>1031</v>
+        <v>58.86</v>
       </c>
       <c r="E28" t="n">
-        <v>1005.2</v>
+        <v>55.86</v>
       </c>
       <c r="F28" t="n">
-        <v>1042.85</v>
+        <v>57.81</v>
       </c>
       <c r="G28" t="n">
-        <v>2917000</v>
+        <v>27262250</v>
       </c>
       <c r="H28" t="n">
-        <v>2821000</v>
+        <v>25237882</v>
       </c>
       <c r="I28" t="n">
-        <v>1210</v>
+        <v>65</v>
       </c>
       <c r="J28" t="n">
-        <v>936</v>
+        <v>50.2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,64 +3666,64 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>666681</v>
+        <v>-752451</v>
       </c>
       <c r="M28" t="n">
-        <v>219838</v>
+        <v>11256922</v>
       </c>
       <c r="N28" t="n">
-        <v>-77355</v>
+        <v>14269862</v>
       </c>
       <c r="O28" t="n">
-        <v>-2233620</v>
+        <v>3604234</v>
       </c>
       <c r="P28" t="n">
-        <v>471617</v>
+        <v>-1494770</v>
       </c>
       <c r="Q28" t="n">
-        <v>102185</v>
+        <v>10057089</v>
       </c>
       <c r="R28" t="n">
-        <v>-240846</v>
+        <v>12526503</v>
       </c>
       <c r="S28" t="n">
-        <v>-1830072</v>
+        <v>3576706</v>
       </c>
       <c r="T28" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>3617</v>
+        <v>39000</v>
       </c>
       <c r="W28" t="n">
-        <v>-232427</v>
+        <v>192000</v>
       </c>
       <c r="X28" t="n">
-        <v>193064</v>
+        <v>742319</v>
       </c>
       <c r="Y28" t="n">
-        <v>107653</v>
+        <v>1199833</v>
       </c>
       <c r="Z28" t="n">
-        <v>159874</v>
+        <v>1704359</v>
       </c>
       <c r="AA28" t="n">
-        <v>-171121</v>
+        <v>-164472</v>
       </c>
       <c r="AB28" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -3733,49 +3733,49 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人小幅賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、短線籌碼止穩、5日法人小幅賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>71.90000000000001</v>
+        <v>379</v>
       </c>
       <c r="D29" t="n">
-        <v>72.23999999999999</v>
+        <v>346</v>
       </c>
       <c r="E29" t="n">
-        <v>69.08</v>
+        <v>298.2</v>
       </c>
       <c r="F29" t="n">
-        <v>69.08</v>
+        <v>264.02</v>
       </c>
       <c r="G29" t="n">
-        <v>78210167</v>
+        <v>17024627</v>
       </c>
       <c r="H29" t="n">
-        <v>181489906</v>
+        <v>47751060</v>
       </c>
       <c r="I29" t="n">
-        <v>81.2</v>
+        <v>387</v>
       </c>
       <c r="J29" t="n">
-        <v>61.8</v>
+        <v>208</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,116 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-7646631</v>
+        <v>-1530721</v>
       </c>
       <c r="M29" t="n">
-        <v>-16047176</v>
+        <v>9386598</v>
       </c>
       <c r="N29" t="n">
-        <v>33115701</v>
+        <v>9329511</v>
       </c>
       <c r="O29" t="n">
-        <v>55309856</v>
+        <v>2976549</v>
       </c>
       <c r="P29" t="n">
-        <v>-8313549</v>
+        <v>-1822021</v>
       </c>
       <c r="Q29" t="n">
-        <v>-17889466</v>
+        <v>9593946</v>
       </c>
       <c r="R29" t="n">
-        <v>28430668</v>
+        <v>9756699</v>
       </c>
       <c r="S29" t="n">
-        <v>46507174</v>
+        <v>5846660</v>
       </c>
       <c r="T29" t="n">
-        <v>-4000</v>
+        <v>-99797</v>
       </c>
       <c r="U29" t="n">
-        <v>1576000</v>
+        <v>-339782</v>
       </c>
       <c r="V29" t="n">
-        <v>2349000</v>
+        <v>-1394782</v>
       </c>
       <c r="W29" t="n">
-        <v>2381000</v>
+        <v>-4249884</v>
       </c>
       <c r="X29" t="n">
-        <v>670918</v>
+        <v>391097</v>
       </c>
       <c r="Y29" t="n">
-        <v>266290</v>
+        <v>132434</v>
       </c>
       <c r="Z29" t="n">
-        <v>2336033</v>
+        <v>967594</v>
       </c>
       <c r="AA29" t="n">
-        <v>6421682</v>
+        <v>1379773</v>
       </c>
       <c r="AB29" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.1</v>
+        <v>41.65</v>
       </c>
       <c r="D30" t="n">
-        <v>14.76</v>
+        <v>42.2</v>
       </c>
       <c r="E30" t="n">
-        <v>12.68</v>
+        <v>41.59</v>
       </c>
       <c r="F30" t="n">
-        <v>11.15</v>
+        <v>40.29</v>
       </c>
       <c r="G30" t="n">
-        <v>289351189</v>
+        <v>17386615</v>
       </c>
       <c r="H30" t="n">
-        <v>286226550</v>
+        <v>27652053</v>
       </c>
       <c r="I30" t="n">
-        <v>17.1</v>
+        <v>44.75</v>
       </c>
       <c r="J30" t="n">
-        <v>8.220000000000001</v>
+        <v>37.45</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,116 +3900,116 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5284295</v>
+        <v>1337515</v>
       </c>
       <c r="M30" t="n">
-        <v>-6495197</v>
+        <v>14595424</v>
       </c>
       <c r="N30" t="n">
-        <v>-42554506</v>
+        <v>18051673</v>
       </c>
       <c r="O30" t="n">
-        <v>8357597</v>
+        <v>68742480</v>
       </c>
       <c r="P30" t="n">
-        <v>4366136</v>
+        <v>1218184</v>
       </c>
       <c r="Q30" t="n">
-        <v>-9860996</v>
+        <v>13702965</v>
       </c>
       <c r="R30" t="n">
-        <v>-43704960</v>
+        <v>18247222</v>
       </c>
       <c r="S30" t="n">
-        <v>6123515</v>
+        <v>76134911</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>-1134000</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>-4558000</v>
       </c>
       <c r="X30" t="n">
-        <v>918159</v>
+        <v>124331</v>
       </c>
       <c r="Y30" t="n">
-        <v>3365799</v>
+        <v>897459</v>
       </c>
       <c r="Z30" t="n">
-        <v>1150454</v>
+        <v>938451</v>
       </c>
       <c r="AA30" t="n">
-        <v>2234082</v>
+        <v>-2834431</v>
       </c>
       <c r="AB30" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>83.2</v>
+        <v>74.2</v>
       </c>
       <c r="D31" t="n">
-        <v>81.73999999999999</v>
+        <v>74.28</v>
       </c>
       <c r="E31" t="n">
-        <v>81.36</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>80.97</v>
+        <v>70.41</v>
       </c>
       <c r="G31" t="n">
-        <v>20794251</v>
+        <v>26575995</v>
       </c>
       <c r="H31" t="n">
-        <v>12683829</v>
+        <v>38350375</v>
       </c>
       <c r="I31" t="n">
-        <v>85.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>77.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,116 +4017,116 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3075517</v>
+        <v>4210340</v>
       </c>
       <c r="M31" t="n">
-        <v>1838084</v>
+        <v>1375380</v>
       </c>
       <c r="N31" t="n">
-        <v>-1100465</v>
+        <v>852875</v>
       </c>
       <c r="O31" t="n">
-        <v>-433582</v>
+        <v>6784140</v>
       </c>
       <c r="P31" t="n">
-        <v>2692586</v>
+        <v>3876592</v>
       </c>
       <c r="Q31" t="n">
-        <v>1633452</v>
+        <v>1371933</v>
       </c>
       <c r="R31" t="n">
-        <v>-1080274</v>
+        <v>-342602</v>
       </c>
       <c r="S31" t="n">
-        <v>-143430</v>
+        <v>4302843</v>
       </c>
       <c r="T31" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>-1000</v>
+        <v>-11000</v>
       </c>
       <c r="X31" t="n">
-        <v>383931</v>
+        <v>333748</v>
       </c>
       <c r="Y31" t="n">
-        <v>205632</v>
+        <v>3447</v>
       </c>
       <c r="Z31" t="n">
-        <v>-19191</v>
+        <v>1195477</v>
       </c>
       <c r="AA31" t="n">
-        <v>-289152</v>
+        <v>2492297</v>
       </c>
       <c r="AB31" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>144.5</v>
+        <v>5120</v>
       </c>
       <c r="D32" t="n">
-        <v>137.1</v>
+        <v>5255</v>
       </c>
       <c r="E32" t="n">
-        <v>124.75</v>
+        <v>4944.5</v>
       </c>
       <c r="F32" t="n">
-        <v>110.34</v>
+        <v>4890.25</v>
       </c>
       <c r="G32" t="n">
-        <v>366515715</v>
+        <v>3687942</v>
       </c>
       <c r="H32" t="n">
-        <v>339579178</v>
+        <v>2607763</v>
       </c>
       <c r="I32" t="n">
-        <v>151</v>
+        <v>5635</v>
       </c>
       <c r="J32" t="n">
-        <v>79.40000000000001</v>
+        <v>4300</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,116 +4134,116 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-56076862</v>
+        <v>-36426</v>
       </c>
       <c r="M32" t="n">
-        <v>-86242883</v>
+        <v>330831</v>
       </c>
       <c r="N32" t="n">
-        <v>-875000</v>
+        <v>485528</v>
       </c>
       <c r="O32" t="n">
-        <v>-79666636</v>
+        <v>1932087</v>
       </c>
       <c r="P32" t="n">
-        <v>-28218031</v>
+        <v>-148221</v>
       </c>
       <c r="Q32" t="n">
-        <v>-6628877</v>
+        <v>67864</v>
       </c>
       <c r="R32" t="n">
-        <v>113761499</v>
+        <v>314229</v>
       </c>
       <c r="S32" t="n">
-        <v>14781667</v>
+        <v>2085929</v>
       </c>
       <c r="T32" t="n">
-        <v>-28689967</v>
+        <v>91082</v>
       </c>
       <c r="U32" t="n">
-        <v>-82184801</v>
+        <v>283675</v>
       </c>
       <c r="V32" t="n">
-        <v>-123282822</v>
+        <v>204689</v>
       </c>
       <c r="W32" t="n">
-        <v>-99898432</v>
+        <v>-43363</v>
       </c>
       <c r="X32" t="n">
-        <v>831136</v>
+        <v>20713</v>
       </c>
       <c r="Y32" t="n">
-        <v>2570795</v>
+        <v>-20708</v>
       </c>
       <c r="Z32" t="n">
-        <v>8646323</v>
+        <v>-33390</v>
       </c>
       <c r="AA32" t="n">
-        <v>5450129</v>
+        <v>-110479</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>51</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>48.48</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>44.08</v>
+        <v>69.08</v>
       </c>
       <c r="F33" t="n">
-        <v>37.84</v>
+        <v>69.08</v>
       </c>
       <c r="G33" t="n">
-        <v>897327645</v>
+        <v>78210167</v>
       </c>
       <c r="H33" t="n">
-        <v>1011819780</v>
+        <v>181489906</v>
       </c>
       <c r="I33" t="n">
-        <v>52.2</v>
+        <v>81.2</v>
       </c>
       <c r="J33" t="n">
-        <v>24.05</v>
+        <v>61.8</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,116 +4251,116 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>165040996</v>
+        <v>-7646631</v>
       </c>
       <c r="M33" t="n">
-        <v>-112547359</v>
+        <v>-16047176</v>
       </c>
       <c r="N33" t="n">
-        <v>-335137590</v>
+        <v>33115701</v>
       </c>
       <c r="O33" t="n">
-        <v>-278268834</v>
+        <v>55309856</v>
       </c>
       <c r="P33" t="n">
-        <v>163249451</v>
+        <v>-8313549</v>
       </c>
       <c r="Q33" t="n">
-        <v>-94432896</v>
+        <v>-17889466</v>
       </c>
       <c r="R33" t="n">
-        <v>-301356148</v>
+        <v>28430668</v>
       </c>
       <c r="S33" t="n">
-        <v>-249862200</v>
+        <v>46507174</v>
       </c>
       <c r="T33" t="n">
-        <v>7444</v>
+        <v>-4000</v>
       </c>
       <c r="U33" t="n">
-        <v>-5412779</v>
+        <v>1576000</v>
       </c>
       <c r="V33" t="n">
-        <v>-8125475</v>
+        <v>2349000</v>
       </c>
       <c r="W33" t="n">
-        <v>-7077264</v>
+        <v>2381000</v>
       </c>
       <c r="X33" t="n">
-        <v>1784101</v>
+        <v>670918</v>
       </c>
       <c r="Y33" t="n">
-        <v>-12701684</v>
+        <v>266290</v>
       </c>
       <c r="Z33" t="n">
-        <v>-25655967</v>
+        <v>2336033</v>
       </c>
       <c r="AA33" t="n">
-        <v>-21329370</v>
+        <v>6421682</v>
       </c>
       <c r="AB33" t="n">
-        <v>-5</v>
+        <v>55</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>23</v>
+        <v>36.05</v>
       </c>
       <c r="D34" t="n">
-        <v>22.48</v>
+        <v>35.36</v>
       </c>
       <c r="E34" t="n">
-        <v>21.2</v>
+        <v>35.05</v>
       </c>
       <c r="F34" t="n">
-        <v>19.97</v>
+        <v>34.91</v>
       </c>
       <c r="G34" t="n">
-        <v>481574851</v>
+        <v>122963731</v>
       </c>
       <c r="H34" t="n">
-        <v>497424018</v>
+        <v>81897844</v>
       </c>
       <c r="I34" t="n">
-        <v>25.8</v>
+        <v>36.7</v>
       </c>
       <c r="J34" t="n">
-        <v>16.6</v>
+        <v>33.4</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,116 +4368,116 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>69476213</v>
+        <v>16457567</v>
       </c>
       <c r="M34" t="n">
-        <v>-20831523</v>
+        <v>11483651</v>
       </c>
       <c r="N34" t="n">
-        <v>-171352805</v>
+        <v>-4247964</v>
       </c>
       <c r="O34" t="n">
-        <v>9685753</v>
+        <v>5314718</v>
       </c>
       <c r="P34" t="n">
-        <v>66341339</v>
+        <v>-20469399</v>
       </c>
       <c r="Q34" t="n">
-        <v>-22820955</v>
+        <v>-71180490</v>
       </c>
       <c r="R34" t="n">
-        <v>-171088607</v>
+        <v>-112366470</v>
       </c>
       <c r="S34" t="n">
-        <v>5694712</v>
+        <v>-124696352</v>
       </c>
       <c r="T34" t="n">
-        <v>9000</v>
+        <v>36156345</v>
       </c>
       <c r="U34" t="n">
-        <v>90252</v>
+        <v>81328402</v>
       </c>
       <c r="V34" t="n">
-        <v>212198</v>
+        <v>105198860</v>
       </c>
       <c r="W34" t="n">
-        <v>242507</v>
+        <v>127993964</v>
       </c>
       <c r="X34" t="n">
-        <v>3125874</v>
+        <v>770621</v>
       </c>
       <c r="Y34" t="n">
-        <v>1899180</v>
+        <v>1335739</v>
       </c>
       <c r="Z34" t="n">
-        <v>-476396</v>
+        <v>2919646</v>
       </c>
       <c r="AA34" t="n">
-        <v>3748534</v>
+        <v>2017106</v>
       </c>
       <c r="AB34" t="n">
-        <v>-10</v>
+        <v>45</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、接近20日高點、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1810</v>
+        <v>436</v>
       </c>
       <c r="D35" t="n">
-        <v>1717</v>
+        <v>447.6</v>
       </c>
       <c r="E35" t="n">
-        <v>1729</v>
+        <v>405.25</v>
       </c>
       <c r="F35" t="n">
-        <v>1680</v>
+        <v>392.2</v>
       </c>
       <c r="G35" t="n">
-        <v>5120000</v>
+        <v>10858000</v>
       </c>
       <c r="H35" t="n">
-        <v>4208800</v>
+        <v>16704800</v>
       </c>
       <c r="I35" t="n">
-        <v>1935</v>
+        <v>492.5</v>
       </c>
       <c r="J35" t="n">
-        <v>1270</v>
+        <v>343</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,116 +4485,116 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>129935</v>
+        <v>-2759531</v>
       </c>
       <c r="M35" t="n">
-        <v>-22256</v>
+        <v>-1248331</v>
       </c>
       <c r="N35" t="n">
-        <v>-841812</v>
+        <v>10551657</v>
       </c>
       <c r="O35" t="n">
-        <v>-2031599</v>
+        <v>9369379</v>
       </c>
       <c r="P35" t="n">
-        <v>-260532</v>
+        <v>-2821709</v>
       </c>
       <c r="Q35" t="n">
-        <v>-612470</v>
+        <v>-647260</v>
       </c>
       <c r="R35" t="n">
-        <v>-816964</v>
+        <v>12234799</v>
       </c>
       <c r="S35" t="n">
-        <v>-1606644</v>
+        <v>13596569</v>
       </c>
       <c r="T35" t="n">
-        <v>356500</v>
+        <v>-12000</v>
       </c>
       <c r="U35" t="n">
-        <v>560740</v>
+        <v>-330000</v>
       </c>
       <c r="V35" t="n">
-        <v>-40877</v>
+        <v>-1959000</v>
       </c>
       <c r="W35" t="n">
-        <v>-308710</v>
+        <v>-5111631</v>
       </c>
       <c r="X35" t="n">
-        <v>33967</v>
+        <v>74178</v>
       </c>
       <c r="Y35" t="n">
-        <v>29474</v>
+        <v>-271071</v>
       </c>
       <c r="Z35" t="n">
-        <v>16029</v>
+        <v>275858</v>
       </c>
       <c r="AA35" t="n">
-        <v>-116245</v>
+        <v>884441</v>
       </c>
       <c r="AB35" t="n">
-        <v>-20</v>
+        <v>35</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.95</v>
+        <v>1065</v>
       </c>
       <c r="D36" t="n">
-        <v>38.08</v>
+        <v>1031</v>
       </c>
       <c r="E36" t="n">
-        <v>33.81</v>
+        <v>1005.2</v>
       </c>
       <c r="F36" t="n">
-        <v>31.15</v>
+        <v>1042.85</v>
       </c>
       <c r="G36" t="n">
-        <v>102606028</v>
+        <v>2917000</v>
       </c>
       <c r="H36" t="n">
-        <v>141383468</v>
+        <v>2821000</v>
       </c>
       <c r="I36" t="n">
-        <v>41.05</v>
+        <v>1210</v>
       </c>
       <c r="J36" t="n">
-        <v>26.65</v>
+        <v>936</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,116 +4602,116 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-6910077</v>
+        <v>666681</v>
       </c>
       <c r="M36" t="n">
-        <v>-38867066</v>
+        <v>219838</v>
       </c>
       <c r="N36" t="n">
-        <v>-330703</v>
+        <v>-77355</v>
       </c>
       <c r="O36" t="n">
-        <v>70129318</v>
+        <v>-2233620</v>
       </c>
       <c r="P36" t="n">
-        <v>-6951441</v>
+        <v>471617</v>
       </c>
       <c r="Q36" t="n">
-        <v>-37390805</v>
+        <v>102185</v>
       </c>
       <c r="R36" t="n">
-        <v>4656960</v>
+        <v>-240846</v>
       </c>
       <c r="S36" t="n">
-        <v>83481179</v>
+        <v>-1830072</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V36" t="n">
-        <v>-5544000</v>
+        <v>3617</v>
       </c>
       <c r="W36" t="n">
-        <v>-17754000</v>
+        <v>-232427</v>
       </c>
       <c r="X36" t="n">
-        <v>41364</v>
+        <v>193064</v>
       </c>
       <c r="Y36" t="n">
-        <v>-1476261</v>
+        <v>107653</v>
       </c>
       <c r="Z36" t="n">
-        <v>556337</v>
+        <v>159874</v>
       </c>
       <c r="AA36" t="n">
-        <v>4402139</v>
+        <v>-171121</v>
       </c>
       <c r="AB36" t="n">
-        <v>-25</v>
+        <v>35</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
+          <t>短線籌碼止穩、5日法人小幅賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、短線籌碼止穩、5日法人小幅賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>284.5</v>
+        <v>173</v>
       </c>
       <c r="D37" t="n">
-        <v>281.7</v>
+        <v>172.5</v>
       </c>
       <c r="E37" t="n">
-        <v>271.45</v>
+        <v>173</v>
       </c>
       <c r="F37" t="n">
-        <v>261.52</v>
+        <v>172.3</v>
       </c>
       <c r="G37" t="n">
-        <v>84156366</v>
+        <v>306256</v>
       </c>
       <c r="H37" t="n">
-        <v>93692827</v>
+        <v>207649</v>
       </c>
       <c r="I37" t="n">
-        <v>305.5</v>
+        <v>176.5</v>
       </c>
       <c r="J37" t="n">
-        <v>233.5</v>
+        <v>167</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,116 +4719,116 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>28384602</v>
+        <v>-7000</v>
       </c>
       <c r="M37" t="n">
-        <v>-21588663</v>
+        <v>10064</v>
       </c>
       <c r="N37" t="n">
-        <v>-27955055</v>
+        <v>-17038</v>
       </c>
       <c r="O37" t="n">
-        <v>23437616</v>
+        <v>36745</v>
       </c>
       <c r="P37" t="n">
-        <v>28289321</v>
+        <v>-6000</v>
       </c>
       <c r="Q37" t="n">
-        <v>-11423041</v>
+        <v>10110</v>
       </c>
       <c r="R37" t="n">
-        <v>-15045877</v>
+        <v>-19890</v>
       </c>
       <c r="S37" t="n">
-        <v>30133661</v>
+        <v>36110</v>
       </c>
       <c r="T37" t="n">
-        <v>-387000</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>-7289000</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>-9830000</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>-4343000</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>482281</v>
+        <v>-1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>-2876622</v>
+        <v>-46</v>
       </c>
       <c r="Z37" t="n">
-        <v>-3079178</v>
+        <v>2852</v>
       </c>
       <c r="AA37" t="n">
-        <v>-2353045</v>
+        <v>635</v>
       </c>
       <c r="AB37" t="n">
-        <v>-30</v>
+        <v>35</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、接近20日高點、接近20日低點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>86.3</v>
+        <v>17.1</v>
       </c>
       <c r="D38" t="n">
-        <v>84.42</v>
+        <v>14.76</v>
       </c>
       <c r="E38" t="n">
-        <v>78.90000000000001</v>
+        <v>12.68</v>
       </c>
       <c r="F38" t="n">
-        <v>70.40000000000001</v>
+        <v>11.15</v>
       </c>
       <c r="G38" t="n">
-        <v>41007388</v>
+        <v>289351189</v>
       </c>
       <c r="H38" t="n">
-        <v>41397085</v>
+        <v>286226550</v>
       </c>
       <c r="I38" t="n">
-        <v>93</v>
+        <v>17.1</v>
       </c>
       <c r="J38" t="n">
-        <v>58.1</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,28 +4836,28 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-6462430</v>
+        <v>5284295</v>
       </c>
       <c r="M38" t="n">
-        <v>-11504398</v>
+        <v>-6495197</v>
       </c>
       <c r="N38" t="n">
-        <v>-6893169</v>
+        <v>-42554506</v>
       </c>
       <c r="O38" t="n">
-        <v>4060977</v>
+        <v>8357597</v>
       </c>
       <c r="P38" t="n">
-        <v>-6057541</v>
+        <v>4366136</v>
       </c>
       <c r="Q38" t="n">
-        <v>-9875925</v>
+        <v>-9860996</v>
       </c>
       <c r="R38" t="n">
-        <v>-5376500</v>
+        <v>-43704960</v>
       </c>
       <c r="S38" t="n">
-        <v>2454433</v>
+        <v>6123515</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -4872,80 +4872,80 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>-404889</v>
+        <v>918159</v>
       </c>
       <c r="Y38" t="n">
-        <v>-1628473</v>
+        <v>3365799</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1516669</v>
+        <v>1150454</v>
       </c>
       <c r="AA38" t="n">
-        <v>1606544</v>
+        <v>2234082</v>
       </c>
       <c r="AB38" t="n">
-        <v>-35</v>
+        <v>25</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8.800000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="D39" t="n">
-        <v>8.289999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>7.12</v>
+        <v>81.36</v>
       </c>
       <c r="F39" t="n">
-        <v>6.44</v>
+        <v>80.97</v>
       </c>
       <c r="G39" t="n">
-        <v>120114525</v>
+        <v>20794251</v>
       </c>
       <c r="H39" t="n">
-        <v>150006859</v>
+        <v>12683829</v>
       </c>
       <c r="I39" t="n">
-        <v>9.25</v>
+        <v>85.8</v>
       </c>
       <c r="J39" t="n">
-        <v>5.55</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,116 +4953,116 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-8225970</v>
+        <v>3075517</v>
       </c>
       <c r="M39" t="n">
-        <v>-21697710</v>
+        <v>1838084</v>
       </c>
       <c r="N39" t="n">
-        <v>-13271904</v>
+        <v>-1100465</v>
       </c>
       <c r="O39" t="n">
-        <v>15244774</v>
+        <v>-433582</v>
       </c>
       <c r="P39" t="n">
-        <v>-8995000</v>
+        <v>2692586</v>
       </c>
       <c r="Q39" t="n">
-        <v>-16819749</v>
+        <v>1633452</v>
       </c>
       <c r="R39" t="n">
-        <v>-16143749</v>
+        <v>-1080274</v>
       </c>
       <c r="S39" t="n">
-        <v>9898851</v>
+        <v>-143430</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="X39" t="n">
-        <v>769030</v>
+        <v>383931</v>
       </c>
       <c r="Y39" t="n">
-        <v>-4877961</v>
+        <v>205632</v>
       </c>
       <c r="Z39" t="n">
-        <v>2871845</v>
+        <v>-19191</v>
       </c>
       <c r="AA39" t="n">
-        <v>5345923</v>
+        <v>-289152</v>
       </c>
       <c r="AB39" t="n">
-        <v>-35</v>
+        <v>25</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>2382.TW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>738</v>
+        <v>339</v>
       </c>
       <c r="D40" t="n">
-        <v>706.6</v>
+        <v>318.5</v>
       </c>
       <c r="E40" t="n">
-        <v>625.2</v>
+        <v>309.65</v>
       </c>
       <c r="F40" t="n">
-        <v>509.5</v>
+        <v>321.55</v>
       </c>
       <c r="G40" t="n">
-        <v>28926802</v>
+        <v>87792646</v>
       </c>
       <c r="H40" t="n">
-        <v>35208144</v>
+        <v>53491202</v>
       </c>
       <c r="I40" t="n">
-        <v>784</v>
+        <v>352.5</v>
       </c>
       <c r="J40" t="n">
-        <v>314</v>
+        <v>288.5</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5070,116 +5070,116 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-4621281</v>
+        <v>18426643</v>
       </c>
       <c r="M40" t="n">
-        <v>-7685090</v>
+        <v>4857962</v>
       </c>
       <c r="N40" t="n">
-        <v>-7877682</v>
+        <v>-7418190</v>
       </c>
       <c r="O40" t="n">
-        <v>352104</v>
+        <v>-11242885</v>
       </c>
       <c r="P40" t="n">
-        <v>-5437960</v>
+        <v>1857292</v>
       </c>
       <c r="Q40" t="n">
-        <v>-10240633</v>
+        <v>-37240811</v>
       </c>
       <c r="R40" t="n">
-        <v>-14919628</v>
+        <v>-73071969</v>
       </c>
       <c r="S40" t="n">
-        <v>-31600414</v>
+        <v>-93637825</v>
       </c>
       <c r="T40" t="n">
-        <v>278110</v>
+        <v>15430000</v>
       </c>
       <c r="U40" t="n">
-        <v>345532</v>
+        <v>40595562</v>
       </c>
       <c r="V40" t="n">
-        <v>3427740</v>
+        <v>63535404</v>
       </c>
       <c r="W40" t="n">
-        <v>28089740</v>
+        <v>81935830</v>
       </c>
       <c r="X40" t="n">
-        <v>538569</v>
+        <v>1139351</v>
       </c>
       <c r="Y40" t="n">
-        <v>2210011</v>
+        <v>1503211</v>
       </c>
       <c r="Z40" t="n">
-        <v>3614206</v>
+        <v>2118375</v>
       </c>
       <c r="AA40" t="n">
-        <v>3862778</v>
+        <v>459110</v>
       </c>
       <c r="AB40" t="n">
-        <v>-35</v>
+        <v>20</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、成交量放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4310</v>
+        <v>268.5</v>
       </c>
       <c r="D41" t="n">
-        <v>4374</v>
+        <v>269.5</v>
       </c>
       <c r="E41" t="n">
-        <v>3906.5</v>
+        <v>257.8</v>
       </c>
       <c r="F41" t="n">
-        <v>3665.5</v>
+        <v>270.23</v>
       </c>
       <c r="G41" t="n">
-        <v>23109791</v>
+        <v>20471464</v>
       </c>
       <c r="H41" t="n">
-        <v>16392169</v>
+        <v>21957355</v>
       </c>
       <c r="I41" t="n">
-        <v>4690</v>
+        <v>322</v>
       </c>
       <c r="J41" t="n">
-        <v>2870</v>
+        <v>230</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5187,55 +5187,55 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-3475601</v>
+        <v>3812763</v>
       </c>
       <c r="M41" t="n">
-        <v>-3182081</v>
+        <v>1123097</v>
       </c>
       <c r="N41" t="n">
-        <v>-4172313</v>
+        <v>347639</v>
       </c>
       <c r="O41" t="n">
-        <v>-8316461</v>
+        <v>527185</v>
       </c>
       <c r="P41" t="n">
-        <v>-2324807</v>
+        <v>3517937</v>
       </c>
       <c r="Q41" t="n">
-        <v>-183403</v>
+        <v>926109</v>
       </c>
       <c r="R41" t="n">
-        <v>9386</v>
+        <v>-793608</v>
       </c>
       <c r="S41" t="n">
-        <v>-5245958</v>
+        <v>153796</v>
       </c>
       <c r="T41" t="n">
-        <v>-1020510</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>-2923799</v>
+        <v>-71000</v>
       </c>
       <c r="V41" t="n">
-        <v>-4483231</v>
+        <v>-238000</v>
       </c>
       <c r="W41" t="n">
-        <v>-3986411</v>
+        <v>-291000</v>
       </c>
       <c r="X41" t="n">
-        <v>-130284</v>
+        <v>294826</v>
       </c>
       <c r="Y41" t="n">
-        <v>-74879</v>
+        <v>267988</v>
       </c>
       <c r="Z41" t="n">
-        <v>301532</v>
+        <v>1379247</v>
       </c>
       <c r="AA41" t="n">
-        <v>915908</v>
+        <v>664389</v>
       </c>
       <c r="AB41" t="n">
-        <v>-40</v>
+        <v>10</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -5249,54 +5249,54 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>233</v>
+        <v>2430</v>
       </c>
       <c r="D42" t="n">
-        <v>262.3</v>
+        <v>2529</v>
       </c>
       <c r="E42" t="n">
-        <v>253.5</v>
+        <v>2483.5</v>
       </c>
       <c r="F42" t="n">
-        <v>245.8</v>
+        <v>2499.25</v>
       </c>
       <c r="G42" t="n">
-        <v>3160000</v>
+        <v>6396739</v>
       </c>
       <c r="H42" t="n">
-        <v>3905800</v>
+        <v>4345204</v>
       </c>
       <c r="I42" t="n">
-        <v>312.5</v>
+        <v>2695</v>
       </c>
       <c r="J42" t="n">
-        <v>220</v>
+        <v>2305</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5304,55 +5304,55 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-692891</v>
+        <v>128711</v>
       </c>
       <c r="M42" t="n">
-        <v>-2049758</v>
+        <v>-730234</v>
       </c>
       <c r="N42" t="n">
-        <v>-2651177</v>
+        <v>247300</v>
       </c>
       <c r="O42" t="n">
-        <v>-2133865</v>
+        <v>-292221</v>
       </c>
       <c r="P42" t="n">
-        <v>-680878</v>
+        <v>601853</v>
       </c>
       <c r="Q42" t="n">
-        <v>-1994325</v>
+        <v>-16438</v>
       </c>
       <c r="R42" t="n">
-        <v>-2544572</v>
+        <v>617257</v>
       </c>
       <c r="S42" t="n">
-        <v>-1885020</v>
+        <v>85631</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>-457677</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>-581267</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>-290072</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>-96630</v>
       </c>
       <c r="X42" t="n">
-        <v>-12013</v>
+        <v>-15465</v>
       </c>
       <c r="Y42" t="n">
-        <v>-55433</v>
+        <v>-132529</v>
       </c>
       <c r="Z42" t="n">
-        <v>-106605</v>
+        <v>-79885</v>
       </c>
       <c r="AA42" t="n">
-        <v>-248845</v>
+        <v>-281222</v>
       </c>
       <c r="AB42" t="n">
-        <v>-50</v>
+        <v>10</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -5366,54 +5366,54 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>611</v>
+        <v>144.5</v>
       </c>
       <c r="D43" t="n">
-        <v>621.6</v>
+        <v>137.1</v>
       </c>
       <c r="E43" t="n">
-        <v>563.7</v>
+        <v>124.75</v>
       </c>
       <c r="F43" t="n">
-        <v>549.85</v>
+        <v>110.34</v>
       </c>
       <c r="G43" t="n">
-        <v>43968378</v>
+        <v>366515715</v>
       </c>
       <c r="H43" t="n">
-        <v>35056581</v>
+        <v>339579178</v>
       </c>
       <c r="I43" t="n">
-        <v>669</v>
+        <v>151</v>
       </c>
       <c r="J43" t="n">
-        <v>465</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5421,55 +5421,55 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-13838044</v>
+        <v>-56076862</v>
       </c>
       <c r="M43" t="n">
-        <v>-15671425</v>
+        <v>-86242883</v>
       </c>
       <c r="N43" t="n">
-        <v>-19564058</v>
+        <v>-875000</v>
       </c>
       <c r="O43" t="n">
-        <v>-23073180</v>
+        <v>-79666636</v>
       </c>
       <c r="P43" t="n">
-        <v>-10101577</v>
+        <v>-28218031</v>
       </c>
       <c r="Q43" t="n">
-        <v>-11629233</v>
+        <v>-6628877</v>
       </c>
       <c r="R43" t="n">
-        <v>-16515209</v>
+        <v>113761499</v>
       </c>
       <c r="S43" t="n">
-        <v>-21778065</v>
+        <v>14781667</v>
       </c>
       <c r="T43" t="n">
-        <v>-3776094</v>
+        <v>-28689967</v>
       </c>
       <c r="U43" t="n">
-        <v>-4048842</v>
+        <v>-82184801</v>
       </c>
       <c r="V43" t="n">
-        <v>-2960648</v>
+        <v>-123282822</v>
       </c>
       <c r="W43" t="n">
-        <v>-767268</v>
+        <v>-99898432</v>
       </c>
       <c r="X43" t="n">
-        <v>39627</v>
+        <v>831136</v>
       </c>
       <c r="Y43" t="n">
-        <v>6650</v>
+        <v>2570795</v>
       </c>
       <c r="Z43" t="n">
-        <v>-88201</v>
+        <v>8646323</v>
       </c>
       <c r="AA43" t="n">
-        <v>-527847</v>
+        <v>5450129</v>
       </c>
       <c r="AB43" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -5483,54 +5483,54 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>515</v>
+        <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>520.4</v>
+        <v>48.48</v>
       </c>
       <c r="E44" t="n">
-        <v>482.35</v>
+        <v>44.08</v>
       </c>
       <c r="F44" t="n">
-        <v>451.07</v>
+        <v>37.84</v>
       </c>
       <c r="G44" t="n">
-        <v>11454003</v>
+        <v>897327645</v>
       </c>
       <c r="H44" t="n">
-        <v>32912192</v>
+        <v>1011819780</v>
       </c>
       <c r="I44" t="n">
-        <v>568</v>
+        <v>52.2</v>
       </c>
       <c r="J44" t="n">
-        <v>372</v>
+        <v>24.05</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5538,55 +5538,55 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>857140</v>
+        <v>165040996</v>
       </c>
       <c r="M44" t="n">
-        <v>-7205641</v>
+        <v>-112547359</v>
       </c>
       <c r="N44" t="n">
-        <v>-9256603</v>
+        <v>-335137590</v>
       </c>
       <c r="O44" t="n">
-        <v>8993341</v>
+        <v>-278268834</v>
       </c>
       <c r="P44" t="n">
-        <v>1231521</v>
+        <v>163249451</v>
       </c>
       <c r="Q44" t="n">
-        <v>-1238676</v>
+        <v>-94432896</v>
       </c>
       <c r="R44" t="n">
-        <v>-4688336</v>
+        <v>-301356148</v>
       </c>
       <c r="S44" t="n">
-        <v>-1033644</v>
+        <v>-249862200</v>
       </c>
       <c r="T44" t="n">
-        <v>-836465</v>
+        <v>7444</v>
       </c>
       <c r="U44" t="n">
-        <v>-5792592</v>
+        <v>-5412779</v>
       </c>
       <c r="V44" t="n">
-        <v>-3969592</v>
+        <v>-8125475</v>
       </c>
       <c r="W44" t="n">
-        <v>9612976</v>
+        <v>-7077264</v>
       </c>
       <c r="X44" t="n">
-        <v>462084</v>
+        <v>1784101</v>
       </c>
       <c r="Y44" t="n">
-        <v>-174373</v>
+        <v>-12701684</v>
       </c>
       <c r="Z44" t="n">
-        <v>-598675</v>
+        <v>-25655967</v>
       </c>
       <c r="AA44" t="n">
-        <v>414009</v>
+        <v>-21329370</v>
       </c>
       <c r="AB44" t="n">
-        <v>-70</v>
+        <v>-5</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -5600,54 +5600,54 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>207</v>
+        <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>208.9</v>
+        <v>22.48</v>
       </c>
       <c r="E45" t="n">
-        <v>203.45</v>
+        <v>21.2</v>
       </c>
       <c r="F45" t="n">
-        <v>195.38</v>
+        <v>19.97</v>
       </c>
       <c r="G45" t="n">
-        <v>13700926</v>
+        <v>481574851</v>
       </c>
       <c r="H45" t="n">
-        <v>19496790</v>
+        <v>497424018</v>
       </c>
       <c r="I45" t="n">
-        <v>231</v>
+        <v>25.8</v>
       </c>
       <c r="J45" t="n">
-        <v>168.5</v>
+        <v>16.6</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5655,55 +5655,55 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-2706458</v>
+        <v>69476213</v>
       </c>
       <c r="M45" t="n">
-        <v>-1348885</v>
+        <v>-20831523</v>
       </c>
       <c r="N45" t="n">
-        <v>-5894259</v>
+        <v>-171352805</v>
       </c>
       <c r="O45" t="n">
-        <v>3016910</v>
+        <v>9685753</v>
       </c>
       <c r="P45" t="n">
-        <v>-2716140</v>
+        <v>66341339</v>
       </c>
       <c r="Q45" t="n">
-        <v>-1301206</v>
+        <v>-22820955</v>
       </c>
       <c r="R45" t="n">
-        <v>-5499049</v>
+        <v>-171088607</v>
       </c>
       <c r="S45" t="n">
-        <v>2092357</v>
+        <v>5694712</v>
       </c>
       <c r="T45" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="U45" t="n">
-        <v>2000</v>
+        <v>90252</v>
       </c>
       <c r="V45" t="n">
-        <v>2000</v>
+        <v>212198</v>
       </c>
       <c r="W45" t="n">
-        <v>-55316</v>
+        <v>242507</v>
       </c>
       <c r="X45" t="n">
-        <v>7682</v>
+        <v>3125874</v>
       </c>
       <c r="Y45" t="n">
-        <v>-49679</v>
+        <v>1899180</v>
       </c>
       <c r="Z45" t="n">
-        <v>-397210</v>
+        <v>-476396</v>
       </c>
       <c r="AA45" t="n">
-        <v>979869</v>
+        <v>3748534</v>
       </c>
       <c r="AB45" t="n">
-        <v>-75</v>
+        <v>-10</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -5717,54 +5717,54 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>527</v>
+        <v>1810</v>
       </c>
       <c r="D46" t="n">
-        <v>544</v>
+        <v>1717</v>
       </c>
       <c r="E46" t="n">
-        <v>508.75</v>
+        <v>1729</v>
       </c>
       <c r="F46" t="n">
-        <v>506.73</v>
+        <v>1680</v>
       </c>
       <c r="G46" t="n">
-        <v>26012000</v>
+        <v>5120000</v>
       </c>
       <c r="H46" t="n">
-        <v>39810000</v>
+        <v>4208800</v>
       </c>
       <c r="I46" t="n">
-        <v>588</v>
+        <v>1935</v>
       </c>
       <c r="J46" t="n">
-        <v>436</v>
+        <v>1270</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5772,55 +5772,55 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-4446778</v>
+        <v>129935</v>
       </c>
       <c r="M46" t="n">
-        <v>-5175986</v>
+        <v>-22256</v>
       </c>
       <c r="N46" t="n">
-        <v>-1641710</v>
+        <v>-841812</v>
       </c>
       <c r="O46" t="n">
-        <v>3127410</v>
+        <v>-2031599</v>
       </c>
       <c r="P46" t="n">
-        <v>-2818118</v>
+        <v>-260532</v>
       </c>
       <c r="Q46" t="n">
-        <v>-3426566</v>
+        <v>-612470</v>
       </c>
       <c r="R46" t="n">
-        <v>-2679038</v>
+        <v>-816964</v>
       </c>
       <c r="S46" t="n">
-        <v>-1518645</v>
+        <v>-1606644</v>
       </c>
       <c r="T46" t="n">
-        <v>-1490721</v>
+        <v>356500</v>
       </c>
       <c r="U46" t="n">
-        <v>-1184325</v>
+        <v>560740</v>
       </c>
       <c r="V46" t="n">
-        <v>-351326</v>
+        <v>-40877</v>
       </c>
       <c r="W46" t="n">
-        <v>2432941</v>
+        <v>-308710</v>
       </c>
       <c r="X46" t="n">
-        <v>-137939</v>
+        <v>33967</v>
       </c>
       <c r="Y46" t="n">
-        <v>-565095</v>
+        <v>29474</v>
       </c>
       <c r="Z46" t="n">
-        <v>1388654</v>
+        <v>16029</v>
       </c>
       <c r="AA46" t="n">
-        <v>2213114</v>
+        <v>-116245</v>
       </c>
       <c r="AB46" t="n">
-        <v>-95</v>
+        <v>-20</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -5834,54 +5834,54 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1030</v>
+        <v>383</v>
       </c>
       <c r="D47" t="n">
-        <v>1122</v>
+        <v>382.9</v>
       </c>
       <c r="E47" t="n">
-        <v>1055.2</v>
+        <v>380.3</v>
       </c>
       <c r="F47" t="n">
-        <v>1068.35</v>
+        <v>387.38</v>
       </c>
       <c r="G47" t="n">
-        <v>3335000</v>
+        <v>2025000</v>
       </c>
       <c r="H47" t="n">
-        <v>4981400</v>
+        <v>2763200</v>
       </c>
       <c r="I47" t="n">
-        <v>1300</v>
+        <v>439</v>
       </c>
       <c r="J47" t="n">
-        <v>865</v>
+        <v>353.5</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5889,55 +5889,55 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-758454</v>
+        <v>417838</v>
       </c>
       <c r="M47" t="n">
-        <v>-2632081</v>
+        <v>-808089</v>
       </c>
       <c r="N47" t="n">
-        <v>-3568191</v>
+        <v>-498298</v>
       </c>
       <c r="O47" t="n">
-        <v>-4121517</v>
+        <v>-602879</v>
       </c>
       <c r="P47" t="n">
-        <v>-163282</v>
+        <v>403639</v>
       </c>
       <c r="Q47" t="n">
-        <v>-346498</v>
+        <v>-684818</v>
       </c>
       <c r="R47" t="n">
-        <v>-1599895</v>
+        <v>-343953</v>
       </c>
       <c r="S47" t="n">
-        <v>-2472060</v>
+        <v>-475298</v>
       </c>
       <c r="T47" t="n">
-        <v>-593000</v>
+        <v>-22000</v>
       </c>
       <c r="U47" t="n">
-        <v>-2259050</v>
+        <v>-38000</v>
       </c>
       <c r="V47" t="n">
-        <v>-1818050</v>
+        <v>-38000</v>
       </c>
       <c r="W47" t="n">
-        <v>-1656050</v>
+        <v>-13000</v>
       </c>
       <c r="X47" t="n">
-        <v>-2172</v>
+        <v>36199</v>
       </c>
       <c r="Y47" t="n">
-        <v>-26533</v>
+        <v>-85271</v>
       </c>
       <c r="Z47" t="n">
-        <v>-150246</v>
+        <v>-116345</v>
       </c>
       <c r="AA47" t="n">
-        <v>6593</v>
+        <v>-114581</v>
       </c>
       <c r="AB47" t="n">
-        <v>-95</v>
+        <v>-20</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -5951,54 +5951,54 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>848</v>
+        <v>38.95</v>
       </c>
       <c r="D48" t="n">
-        <v>881.8</v>
+        <v>38.08</v>
       </c>
       <c r="E48" t="n">
-        <v>863.3</v>
+        <v>33.81</v>
       </c>
       <c r="F48" t="n">
-        <v>883.9</v>
+        <v>31.16</v>
       </c>
       <c r="G48" t="n">
-        <v>17926232</v>
+        <v>102606028</v>
       </c>
       <c r="H48" t="n">
-        <v>23312290</v>
+        <v>141383468</v>
       </c>
       <c r="I48" t="n">
-        <v>1035</v>
+        <v>41.05</v>
       </c>
       <c r="J48" t="n">
-        <v>765</v>
+        <v>26.65</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6006,55 +6006,55 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-2448813</v>
+        <v>-6910077</v>
       </c>
       <c r="M48" t="n">
-        <v>-8778876</v>
+        <v>-38867066</v>
       </c>
       <c r="N48" t="n">
-        <v>-13138409</v>
+        <v>-330703</v>
       </c>
       <c r="O48" t="n">
-        <v>-8950196</v>
+        <v>70129318</v>
       </c>
       <c r="P48" t="n">
-        <v>43377</v>
+        <v>-6951441</v>
       </c>
       <c r="Q48" t="n">
-        <v>-3411404</v>
+        <v>-37390805</v>
       </c>
       <c r="R48" t="n">
-        <v>-4691237</v>
+        <v>4656960</v>
       </c>
       <c r="S48" t="n">
-        <v>-3009711</v>
+        <v>83481179</v>
       </c>
       <c r="T48" t="n">
-        <v>-2413000</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>-5192000</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>-8133000</v>
+        <v>-5544000</v>
       </c>
       <c r="W48" t="n">
-        <v>-5299000</v>
+        <v>-17754000</v>
       </c>
       <c r="X48" t="n">
-        <v>-79190</v>
+        <v>41364</v>
       </c>
       <c r="Y48" t="n">
-        <v>-175472</v>
+        <v>-1476261</v>
       </c>
       <c r="Z48" t="n">
-        <v>-314172</v>
+        <v>556337</v>
       </c>
       <c r="AA48" t="n">
-        <v>-641485</v>
+        <v>4402139</v>
       </c>
       <c r="AB48" t="n">
-        <v>-95</v>
+        <v>-25</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -6068,132 +6068,1887 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2002.TW</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>中鋼</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="F49" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="G49" t="n">
+        <v>79358213</v>
+      </c>
+      <c r="H49" t="n">
+        <v>150683540</v>
+      </c>
+      <c r="I49" t="n">
+        <v>21</v>
+      </c>
+      <c r="J49" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2360364</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-41161627</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-36694284</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-80349749</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2193070</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-38809547</v>
+      </c>
+      <c r="R49" t="n">
+        <v>-38351405</v>
+      </c>
+      <c r="S49" t="n">
+        <v>-83656663</v>
+      </c>
+      <c r="T49" t="n">
+        <v>27525</v>
+      </c>
+      <c r="U49" t="n">
+        <v>6525</v>
+      </c>
+      <c r="V49" t="n">
+        <v>16525</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1070525</v>
+      </c>
+      <c r="X49" t="n">
+        <v>139769</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>-2358605</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1640596</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2236389</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2313.TW</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="D50" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>271.45</v>
+      </c>
+      <c r="F50" t="n">
+        <v>261.52</v>
+      </c>
+      <c r="G50" t="n">
+        <v>84156366</v>
+      </c>
+      <c r="H50" t="n">
+        <v>93692827</v>
+      </c>
+      <c r="I50" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>28384602</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-21588663</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-27955055</v>
+      </c>
+      <c r="O50" t="n">
+        <v>23437616</v>
+      </c>
+      <c r="P50" t="n">
+        <v>28289321</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-11423041</v>
+      </c>
+      <c r="R50" t="n">
+        <v>-15045877</v>
+      </c>
+      <c r="S50" t="n">
+        <v>30133661</v>
+      </c>
+      <c r="T50" t="n">
+        <v>-387000</v>
+      </c>
+      <c r="U50" t="n">
+        <v>-7289000</v>
+      </c>
+      <c r="V50" t="n">
+        <v>-9830000</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-4343000</v>
+      </c>
+      <c r="X50" t="n">
+        <v>482281</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>-2876622</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-3079178</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-2353045</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>9105.TW</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>泰金寶-DR</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="E51" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G51" t="n">
+        <v>120114525</v>
+      </c>
+      <c r="H51" t="n">
+        <v>150006859</v>
+      </c>
+      <c r="I51" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>-8225970</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-21697710</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-13271904</v>
+      </c>
+      <c r="O51" t="n">
+        <v>15244774</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-8995000</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>-16819749</v>
+      </c>
+      <c r="R51" t="n">
+        <v>-16143749</v>
+      </c>
+      <c r="S51" t="n">
+        <v>9898851</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>769030</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-4877961</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2871845</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>5345923</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3673.TW</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TPK-KY</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="E52" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="F52" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="G52" t="n">
+        <v>41007388</v>
+      </c>
+      <c r="H52" t="n">
+        <v>41397085</v>
+      </c>
+      <c r="I52" t="n">
+        <v>93</v>
+      </c>
+      <c r="J52" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>-6462430</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-11504398</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-6893169</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4060977</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-6057541</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-9875925</v>
+      </c>
+      <c r="R52" t="n">
+        <v>-5376500</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2454433</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-404889</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>-1628473</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-1516669</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1606544</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2327.TW</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>738</v>
+      </c>
+      <c r="D53" t="n">
+        <v>706.6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>625.2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>509.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>28926802</v>
+      </c>
+      <c r="H53" t="n">
+        <v>35208144</v>
+      </c>
+      <c r="I53" t="n">
+        <v>784</v>
+      </c>
+      <c r="J53" t="n">
+        <v>314</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>-4621281</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-7685090</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-7877682</v>
+      </c>
+      <c r="O53" t="n">
+        <v>352104</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-5437960</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-10240633</v>
+      </c>
+      <c r="R53" t="n">
+        <v>-14919628</v>
+      </c>
+      <c r="S53" t="n">
+        <v>-31600414</v>
+      </c>
+      <c r="T53" t="n">
+        <v>278110</v>
+      </c>
+      <c r="U53" t="n">
+        <v>345532</v>
+      </c>
+      <c r="V53" t="n">
+        <v>3427740</v>
+      </c>
+      <c r="W53" t="n">
+        <v>28089740</v>
+      </c>
+      <c r="X53" t="n">
+        <v>538569</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2210011</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>3614206</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3862778</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>站上5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2454.TW</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4310</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4374</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3906.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3665.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>23109791</v>
+      </c>
+      <c r="H54" t="n">
+        <v>16392169</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4690</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2870</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>-3475601</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-3182081</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-4172313</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-8316461</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-2324807</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>-183403</v>
+      </c>
+      <c r="R54" t="n">
+        <v>9386</v>
+      </c>
+      <c r="S54" t="n">
+        <v>-5245958</v>
+      </c>
+      <c r="T54" t="n">
+        <v>-1020510</v>
+      </c>
+      <c r="U54" t="n">
+        <v>-2923799</v>
+      </c>
+      <c r="V54" t="n">
+        <v>-4483231</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-3986411</v>
+      </c>
+      <c r="X54" t="n">
+        <v>-130284</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-74879</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>301532</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>915908</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4908.TWO</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>前鼎</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>233</v>
+      </c>
+      <c r="D55" t="n">
+        <v>262.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>245.8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3160000</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3905800</v>
+      </c>
+      <c r="I55" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>220</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>-692891</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-2049758</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-2651177</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-2133865</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-680878</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>-1994325</v>
+      </c>
+      <c r="R55" t="n">
+        <v>-2544572</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-1885020</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>-12013</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>-55433</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-106605</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-248845</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3711.TW</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>611</v>
+      </c>
+      <c r="D56" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>563.7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>549.85</v>
+      </c>
+      <c r="G56" t="n">
+        <v>43968378</v>
+      </c>
+      <c r="H56" t="n">
+        <v>35056581</v>
+      </c>
+      <c r="I56" t="n">
+        <v>669</v>
+      </c>
+      <c r="J56" t="n">
+        <v>465</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>-13838044</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-15671425</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-19564058</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-23073180</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-10101577</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>-11629233</v>
+      </c>
+      <c r="R56" t="n">
+        <v>-16515209</v>
+      </c>
+      <c r="S56" t="n">
+        <v>-21778065</v>
+      </c>
+      <c r="T56" t="n">
+        <v>-3776094</v>
+      </c>
+      <c r="U56" t="n">
+        <v>-4048842</v>
+      </c>
+      <c r="V56" t="n">
+        <v>-2960648</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-767268</v>
+      </c>
+      <c r="X56" t="n">
+        <v>39627</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>6650</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-88201</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>-527847</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4958.TW</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>515</v>
+      </c>
+      <c r="D57" t="n">
+        <v>520.4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>482.35</v>
+      </c>
+      <c r="F57" t="n">
+        <v>451.07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>11454003</v>
+      </c>
+      <c r="H57" t="n">
+        <v>32912192</v>
+      </c>
+      <c r="I57" t="n">
+        <v>568</v>
+      </c>
+      <c r="J57" t="n">
+        <v>372</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>857140</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-7205641</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-9256603</v>
+      </c>
+      <c r="O57" t="n">
+        <v>8993341</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1231521</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-1238676</v>
+      </c>
+      <c r="R57" t="n">
+        <v>-4688336</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-1033644</v>
+      </c>
+      <c r="T57" t="n">
+        <v>-836465</v>
+      </c>
+      <c r="U57" t="n">
+        <v>-5792592</v>
+      </c>
+      <c r="V57" t="n">
+        <v>-3969592</v>
+      </c>
+      <c r="W57" t="n">
+        <v>9612976</v>
+      </c>
+      <c r="X57" t="n">
+        <v>462084</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>-174373</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-598675</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>414009</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3035.TW</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>207</v>
+      </c>
+      <c r="D58" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>203.45</v>
+      </c>
+      <c r="F58" t="n">
+        <v>195.38</v>
+      </c>
+      <c r="G58" t="n">
+        <v>13700926</v>
+      </c>
+      <c r="H58" t="n">
+        <v>19496790</v>
+      </c>
+      <c r="I58" t="n">
+        <v>231</v>
+      </c>
+      <c r="J58" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>-2706458</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-1348885</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-5894259</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3016910</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-2716140</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>-1301206</v>
+      </c>
+      <c r="R58" t="n">
+        <v>-5499049</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2092357</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V58" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-55316</v>
+      </c>
+      <c r="X58" t="n">
+        <v>7682</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-49679</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-397210</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>979869</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2748.TW</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>雲品</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E59" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="F59" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="G59" t="n">
+        <v>137768</v>
+      </c>
+      <c r="H59" t="n">
+        <v>157686</v>
+      </c>
+      <c r="I59" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="J59" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>33000</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-118572</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-134572</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-185104</v>
+      </c>
+      <c r="P59" t="n">
+        <v>33000</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>-116001</v>
+      </c>
+      <c r="R59" t="n">
+        <v>-133001</v>
+      </c>
+      <c r="S59" t="n">
+        <v>-182001</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-2571</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-1571</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-3103</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>5日法人賣超</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3081.TWO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2615</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2847</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2728</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2752.25</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2144000</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2878200</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3215</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2460</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>-529511</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-1519482</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-720570</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-274473</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-279830</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>-1153921</v>
+      </c>
+      <c r="R60" t="n">
+        <v>-971555</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-523379</v>
+      </c>
+      <c r="T60" t="n">
+        <v>-234000</v>
+      </c>
+      <c r="U60" t="n">
+        <v>-302900</v>
+      </c>
+      <c r="V60" t="n">
+        <v>241578</v>
+      </c>
+      <c r="W60" t="n">
+        <v>309464</v>
+      </c>
+      <c r="X60" t="n">
+        <v>-15681</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-62661</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>9407</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>-60558</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3163.TWO</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>波若威</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1030</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1122</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1055.2</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1068.35</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3335000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4981400</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J61" t="n">
+        <v>865</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>-758454</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-2632081</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-3568191</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-4121517</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-163282</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>-346498</v>
+      </c>
+      <c r="R61" t="n">
+        <v>-1599895</v>
+      </c>
+      <c r="S61" t="n">
+        <v>-2472060</v>
+      </c>
+      <c r="T61" t="n">
+        <v>-593000</v>
+      </c>
+      <c r="U61" t="n">
+        <v>-2259050</v>
+      </c>
+      <c r="V61" t="n">
+        <v>-1818050</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-1656050</v>
+      </c>
+      <c r="X61" t="n">
+        <v>-2172</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>-26533</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-150246</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>6593</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>8046.TW</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>848</v>
+      </c>
+      <c r="D62" t="n">
+        <v>881.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>863.3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>883.9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>17926232</v>
+      </c>
+      <c r="H62" t="n">
+        <v>23312290</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1035</v>
+      </c>
+      <c r="J62" t="n">
+        <v>765</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>-2448813</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-8778876</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-13138409</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-8950196</v>
+      </c>
+      <c r="P62" t="n">
+        <v>43377</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>-3411404</v>
+      </c>
+      <c r="R62" t="n">
+        <v>-4691237</v>
+      </c>
+      <c r="S62" t="n">
+        <v>-3009711</v>
+      </c>
+      <c r="T62" t="n">
+        <v>-2413000</v>
+      </c>
+      <c r="U62" t="n">
+        <v>-5192000</v>
+      </c>
+      <c r="V62" t="n">
+        <v>-8133000</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-5299000</v>
+      </c>
+      <c r="X62" t="n">
+        <v>-79190</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-175472</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-314172</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-641485</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3105.TWO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>527</v>
+      </c>
+      <c r="D63" t="n">
+        <v>544</v>
+      </c>
+      <c r="E63" t="n">
+        <v>508.75</v>
+      </c>
+      <c r="F63" t="n">
+        <v>506.73</v>
+      </c>
+      <c r="G63" t="n">
+        <v>26012000</v>
+      </c>
+      <c r="H63" t="n">
+        <v>39810000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>588</v>
+      </c>
+      <c r="J63" t="n">
+        <v>436</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>-4446778</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-5175986</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-1641710</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3127410</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-2818118</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>-3426566</v>
+      </c>
+      <c r="R63" t="n">
+        <v>-2679038</v>
+      </c>
+      <c r="S63" t="n">
+        <v>-1518645</v>
+      </c>
+      <c r="T63" t="n">
+        <v>-1490721</v>
+      </c>
+      <c r="U63" t="n">
+        <v>-1184325</v>
+      </c>
+      <c r="V63" t="n">
+        <v>-351326</v>
+      </c>
+      <c r="W63" t="n">
+        <v>2432941</v>
+      </c>
+      <c r="X63" t="n">
+        <v>-137939</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-565095</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1388654</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2213114</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>4960.TW</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>誠美材</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C64" t="n">
         <v>31.95</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D64" t="n">
         <v>33.46</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E64" t="n">
         <v>34.07</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F64" t="n">
         <v>36.33</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G64" t="n">
         <v>7490299</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H64" t="n">
         <v>10923227</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I64" t="n">
         <v>44.05</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J64" t="n">
         <v>31.1</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>無明顯異常</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="L64" t="n">
         <v>-830875</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M64" t="n">
         <v>-1788679</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N64" t="n">
         <v>-3454506</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O64" t="n">
         <v>-7227522</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P64" t="n">
         <v>-673979</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q64" t="n">
         <v>-1532782</v>
       </c>
-      <c r="R49" t="n">
+      <c r="R64" t="n">
         <v>-3330610</v>
       </c>
-      <c r="S49" t="n">
+      <c r="S64" t="n">
         <v>-7097627</v>
       </c>
-      <c r="T49" t="n">
+      <c r="T64" t="n">
         <v>0</v>
       </c>
-      <c r="U49" t="n">
+      <c r="U64" t="n">
         <v>0</v>
       </c>
-      <c r="V49" t="n">
+      <c r="V64" t="n">
         <v>0</v>
       </c>
-      <c r="W49" t="n">
+      <c r="W64" t="n">
         <v>0</v>
       </c>
-      <c r="X49" t="n">
+      <c r="X64" t="n">
         <v>-156896</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y64" t="n">
         <v>-255897</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="Z64" t="n">
         <v>-123896</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AA64" t="n">
         <v>-129895</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AB64" t="n">
         <v>-110</v>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="AE49" t="inlineStr">
+      <c r="AE64" t="inlineStr">
         <is>
           <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr">
+      <c r="AF64" t="inlineStr">
         <is>
           <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
-      <c r="AG49" t="inlineStr">
+      <c r="AG64" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -586,37 +586,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>289</v>
+        <v>387</v>
       </c>
       <c r="D2" t="n">
-        <v>267.2</v>
+        <v>352.6</v>
       </c>
       <c r="E2" t="n">
-        <v>256.7</v>
+        <v>334.55</v>
       </c>
       <c r="F2" t="n">
-        <v>251.78</v>
+        <v>324.75</v>
       </c>
       <c r="G2" t="n">
-        <v>289511198</v>
+        <v>38916483</v>
       </c>
       <c r="H2" t="n">
-        <v>124062360</v>
+        <v>21917377</v>
       </c>
       <c r="I2" t="n">
-        <v>289</v>
+        <v>396</v>
       </c>
       <c r="J2" t="n">
-        <v>223.5</v>
+        <v>275.5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -624,55 +624,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>92379944</v>
+        <v>200379</v>
       </c>
       <c r="M2" t="n">
-        <v>125329681</v>
+        <v>10186160</v>
       </c>
       <c r="N2" t="n">
-        <v>189474711</v>
+        <v>11973950</v>
       </c>
       <c r="O2" t="n">
-        <v>219494160</v>
+        <v>4905137</v>
       </c>
       <c r="P2" t="n">
-        <v>80338931</v>
+        <v>-4462178</v>
       </c>
       <c r="Q2" t="n">
-        <v>112821030</v>
+        <v>1853493</v>
       </c>
       <c r="R2" t="n">
-        <v>174152829</v>
+        <v>3409112</v>
       </c>
       <c r="S2" t="n">
-        <v>212775380</v>
+        <v>-3558687</v>
       </c>
       <c r="T2" t="n">
-        <v>7423000</v>
+        <v>4171000</v>
       </c>
       <c r="U2" t="n">
-        <v>7687119</v>
+        <v>7080181</v>
       </c>
       <c r="V2" t="n">
-        <v>8653189</v>
+        <v>7312181</v>
       </c>
       <c r="W2" t="n">
-        <v>3745086</v>
+        <v>8119102</v>
       </c>
       <c r="X2" t="n">
-        <v>4618013</v>
+        <v>491557</v>
       </c>
       <c r="Y2" t="n">
-        <v>4821532</v>
+        <v>1252486</v>
       </c>
       <c r="Z2" t="n">
-        <v>6668693</v>
+        <v>1252657</v>
       </c>
       <c r="AA2" t="n">
-        <v>2973694</v>
+        <v>344722</v>
       </c>
       <c r="AB2" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -696,100 +696,100 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>158.5</v>
+        <v>51.9</v>
       </c>
       <c r="D3" t="n">
-        <v>148.6</v>
+        <v>49.78</v>
       </c>
       <c r="E3" t="n">
-        <v>142.8</v>
+        <v>47.71</v>
       </c>
       <c r="F3" t="n">
-        <v>142.2</v>
+        <v>46.19</v>
       </c>
       <c r="G3" t="n">
-        <v>114139019</v>
+        <v>58919831</v>
       </c>
       <c r="H3" t="n">
-        <v>59875721</v>
+        <v>58169853</v>
       </c>
       <c r="I3" t="n">
-        <v>158.5</v>
+        <v>51.9</v>
       </c>
       <c r="J3" t="n">
-        <v>132</v>
+        <v>42.15</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>19559990</v>
+        <v>12833515</v>
       </c>
       <c r="M3" t="n">
-        <v>27974328</v>
+        <v>51532634</v>
       </c>
       <c r="N3" t="n">
-        <v>38419154</v>
+        <v>87198974</v>
       </c>
       <c r="O3" t="n">
-        <v>78188089</v>
+        <v>193273136</v>
       </c>
       <c r="P3" t="n">
-        <v>16846337</v>
+        <v>6462117</v>
       </c>
       <c r="Q3" t="n">
-        <v>22233669</v>
+        <v>30147060</v>
       </c>
       <c r="R3" t="n">
-        <v>32517682</v>
+        <v>47804655</v>
       </c>
       <c r="S3" t="n">
-        <v>67694424</v>
+        <v>96884073</v>
       </c>
       <c r="T3" t="n">
-        <v>440000</v>
+        <v>130000</v>
       </c>
       <c r="U3" t="n">
-        <v>3161568</v>
+        <v>230000</v>
       </c>
       <c r="V3" t="n">
-        <v>3176098</v>
+        <v>2090000</v>
       </c>
       <c r="W3" t="n">
-        <v>4262814</v>
+        <v>1990000</v>
       </c>
       <c r="X3" t="n">
-        <v>2273653</v>
+        <v>6241398</v>
       </c>
       <c r="Y3" t="n">
-        <v>2579091</v>
+        <v>21155574</v>
       </c>
       <c r="Z3" t="n">
-        <v>2725374</v>
+        <v>37304319</v>
       </c>
       <c r="AA3" t="n">
-        <v>6230851</v>
+        <v>94399063</v>
       </c>
       <c r="AB3" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -813,44 +813,44 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>370</v>
+        <v>54.9</v>
       </c>
       <c r="D4" t="n">
-        <v>342.5</v>
+        <v>52.9</v>
       </c>
       <c r="E4" t="n">
-        <v>328.9</v>
+        <v>52.02</v>
       </c>
       <c r="F4" t="n">
-        <v>319.35</v>
+        <v>50.84</v>
       </c>
       <c r="G4" t="n">
-        <v>33434927</v>
+        <v>51690436</v>
       </c>
       <c r="H4" t="n">
-        <v>17559688</v>
+        <v>29079875</v>
       </c>
       <c r="I4" t="n">
-        <v>371</v>
+        <v>55.7</v>
       </c>
       <c r="J4" t="n">
-        <v>270.5</v>
+        <v>47.35</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7493623</v>
+        <v>14945901</v>
       </c>
       <c r="M4" t="n">
-        <v>10724245</v>
+        <v>25862263</v>
       </c>
       <c r="N4" t="n">
-        <v>11892877</v>
+        <v>42395795</v>
       </c>
       <c r="O4" t="n">
-        <v>8232178</v>
+        <v>68637305</v>
       </c>
       <c r="P4" t="n">
-        <v>5367725</v>
+        <v>20142573</v>
       </c>
       <c r="Q4" t="n">
-        <v>6731221</v>
+        <v>30966686</v>
       </c>
       <c r="R4" t="n">
-        <v>7222369</v>
+        <v>48820355</v>
       </c>
       <c r="S4" t="n">
-        <v>1597909</v>
+        <v>74717732</v>
       </c>
       <c r="T4" t="n">
-        <v>1539024</v>
+        <v>-6005850</v>
       </c>
       <c r="U4" t="n">
-        <v>3151181</v>
+        <v>-6343542</v>
       </c>
       <c r="V4" t="n">
-        <v>3788181</v>
+        <v>-7845092</v>
       </c>
       <c r="W4" t="n">
-        <v>7002102</v>
+        <v>-7903058</v>
       </c>
       <c r="X4" t="n">
-        <v>586874</v>
+        <v>809178</v>
       </c>
       <c r="Y4" t="n">
-        <v>841843</v>
+        <v>1239119</v>
       </c>
       <c r="Z4" t="n">
-        <v>882327</v>
+        <v>1420532</v>
       </c>
       <c r="AA4" t="n">
-        <v>-367833</v>
+        <v>1822631</v>
       </c>
       <c r="AB4" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -925,105 +925,105 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>608</v>
+        <v>174</v>
       </c>
       <c r="D5" t="n">
-        <v>559.8</v>
+        <v>153.6</v>
       </c>
       <c r="E5" t="n">
-        <v>513.6</v>
+        <v>146.65</v>
       </c>
       <c r="F5" t="n">
-        <v>478.25</v>
+        <v>143.88</v>
       </c>
       <c r="G5" t="n">
-        <v>20529000</v>
+        <v>94609409</v>
       </c>
       <c r="H5" t="n">
-        <v>7043000</v>
+        <v>64772226</v>
       </c>
       <c r="I5" t="n">
-        <v>608</v>
+        <v>174</v>
       </c>
       <c r="J5" t="n">
-        <v>368</v>
+        <v>132</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-81732</v>
+        <v>25906440</v>
       </c>
       <c r="M5" t="n">
-        <v>1447366</v>
+        <v>49814393</v>
       </c>
       <c r="N5" t="n">
-        <v>2637157</v>
+        <v>52471124</v>
       </c>
       <c r="O5" t="n">
-        <v>13098622</v>
+        <v>110525706</v>
       </c>
       <c r="P5" t="n">
-        <v>279224</v>
+        <v>24686613</v>
       </c>
       <c r="Q5" t="n">
-        <v>1723100</v>
+        <v>44469682</v>
       </c>
       <c r="R5" t="n">
-        <v>2983381</v>
+        <v>46006122</v>
       </c>
       <c r="S5" t="n">
-        <v>12970541</v>
+        <v>99485352</v>
       </c>
       <c r="T5" t="n">
-        <v>17000</v>
+        <v>1488000</v>
       </c>
       <c r="U5" t="n">
-        <v>13700</v>
+        <v>3052568</v>
       </c>
       <c r="V5" t="n">
-        <v>53500</v>
+        <v>4610098</v>
       </c>
       <c r="W5" t="n">
-        <v>83300</v>
+        <v>5383814</v>
       </c>
       <c r="X5" t="n">
-        <v>-377956</v>
+        <v>-268173</v>
       </c>
       <c r="Y5" t="n">
-        <v>-289434</v>
+        <v>2292143</v>
       </c>
       <c r="Z5" t="n">
-        <v>-399724</v>
+        <v>1854904</v>
       </c>
       <c r="AA5" t="n">
-        <v>44781</v>
+        <v>5656540</v>
       </c>
       <c r="AB5" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,54 +1037,54 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2355</v>
+        <v>107.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2306</v>
+        <v>96.48</v>
       </c>
       <c r="E6" t="n">
-        <v>2264.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>2263.25</v>
+        <v>89.73</v>
       </c>
       <c r="G6" t="n">
-        <v>104783831</v>
+        <v>111908983</v>
       </c>
       <c r="H6" t="n">
-        <v>49680374</v>
+        <v>115784711</v>
       </c>
       <c r="I6" t="n">
-        <v>2375</v>
+        <v>107.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2185</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1092,55 +1092,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>14053662</v>
+        <v>15245712</v>
       </c>
       <c r="M6" t="n">
-        <v>17089924</v>
+        <v>53204084</v>
       </c>
       <c r="N6" t="n">
-        <v>17113436</v>
+        <v>135527278</v>
       </c>
       <c r="O6" t="n">
-        <v>-5855754</v>
+        <v>134335684</v>
       </c>
       <c r="P6" t="n">
-        <v>13284272</v>
+        <v>13945743</v>
       </c>
       <c r="Q6" t="n">
-        <v>15016579</v>
+        <v>48241698</v>
       </c>
       <c r="R6" t="n">
-        <v>11313611</v>
+        <v>128023662</v>
       </c>
       <c r="S6" t="n">
-        <v>-24739310</v>
+        <v>129685447</v>
       </c>
       <c r="T6" t="n">
-        <v>349249</v>
+        <v>696000</v>
       </c>
       <c r="U6" t="n">
-        <v>815542</v>
+        <v>3360457</v>
       </c>
       <c r="V6" t="n">
-        <v>4346753</v>
+        <v>3504189</v>
       </c>
       <c r="W6" t="n">
-        <v>16811428</v>
+        <v>3673289</v>
       </c>
       <c r="X6" t="n">
-        <v>420141</v>
+        <v>603969</v>
       </c>
       <c r="Y6" t="n">
-        <v>1257803</v>
+        <v>1601929</v>
       </c>
       <c r="Z6" t="n">
-        <v>1453072</v>
+        <v>3999427</v>
       </c>
       <c r="AA6" t="n">
-        <v>2072128</v>
+        <v>976948</v>
       </c>
       <c r="AB6" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1164,44 +1164,44 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>158</v>
+        <v>381.5</v>
       </c>
       <c r="D7" t="n">
-        <v>145.3</v>
+        <v>333.6</v>
       </c>
       <c r="E7" t="n">
-        <v>132.9</v>
+        <v>311.7</v>
       </c>
       <c r="F7" t="n">
-        <v>123.86</v>
+        <v>305.85</v>
       </c>
       <c r="G7" t="n">
-        <v>249880280</v>
+        <v>129059908</v>
       </c>
       <c r="H7" t="n">
-        <v>349036888</v>
+        <v>171183369</v>
       </c>
       <c r="I7" t="n">
-        <v>158</v>
+        <v>381.5</v>
       </c>
       <c r="J7" t="n">
-        <v>91.09999999999999</v>
+        <v>242.5</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1209,52 +1209,52 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>71837337</v>
+        <v>29714770</v>
       </c>
       <c r="M7" t="n">
-        <v>49681962</v>
+        <v>117706143</v>
       </c>
       <c r="N7" t="n">
-        <v>181208140</v>
+        <v>126499130</v>
       </c>
       <c r="O7" t="n">
-        <v>153322650</v>
+        <v>78771719</v>
       </c>
       <c r="P7" t="n">
-        <v>53583084</v>
+        <v>27016483</v>
       </c>
       <c r="Q7" t="n">
-        <v>16623178</v>
+        <v>108666843</v>
       </c>
       <c r="R7" t="n">
-        <v>135587913</v>
+        <v>121744282</v>
       </c>
       <c r="S7" t="n">
-        <v>100441793</v>
+        <v>97442183</v>
       </c>
       <c r="T7" t="n">
-        <v>17253000</v>
+        <v>2178001</v>
       </c>
       <c r="U7" t="n">
-        <v>32779929</v>
+        <v>7782331</v>
       </c>
       <c r="V7" t="n">
-        <v>42395384</v>
+        <v>4720606</v>
       </c>
       <c r="W7" t="n">
-        <v>53557111</v>
+        <v>-13348559</v>
       </c>
       <c r="X7" t="n">
-        <v>1001253</v>
+        <v>520286</v>
       </c>
       <c r="Y7" t="n">
-        <v>278855</v>
+        <v>1256969</v>
       </c>
       <c r="Z7" t="n">
-        <v>3224843</v>
+        <v>34242</v>
       </c>
       <c r="AA7" t="n">
-        <v>-676254</v>
+        <v>-5321905</v>
       </c>
       <c r="AB7" t="n">
         <v>150</v>
@@ -1288,37 +1288,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50.2</v>
+        <v>774</v>
       </c>
       <c r="D8" t="n">
-        <v>49.07</v>
+        <v>716.4</v>
       </c>
       <c r="E8" t="n">
-        <v>46.97</v>
+        <v>643.1</v>
       </c>
       <c r="F8" t="n">
-        <v>45.69</v>
+        <v>569.92</v>
       </c>
       <c r="G8" t="n">
-        <v>58208526</v>
+        <v>6218324</v>
       </c>
       <c r="H8" t="n">
-        <v>59310605</v>
+        <v>20571192</v>
       </c>
       <c r="I8" t="n">
-        <v>50.25</v>
+        <v>775</v>
       </c>
       <c r="J8" t="n">
-        <v>41.51</v>
+        <v>445.5</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1326,52 +1326,52 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>35418265</v>
+        <v>1303982</v>
       </c>
       <c r="M8" t="n">
-        <v>64123344</v>
+        <v>3071789</v>
       </c>
       <c r="N8" t="n">
-        <v>106751600</v>
+        <v>8648112</v>
       </c>
       <c r="O8" t="n">
-        <v>186587594</v>
+        <v>28251728</v>
       </c>
       <c r="P8" t="n">
-        <v>20836464</v>
+        <v>934957</v>
       </c>
       <c r="Q8" t="n">
-        <v>37308603</v>
+        <v>2591713</v>
       </c>
       <c r="R8" t="n">
-        <v>67121483</v>
+        <v>5260467</v>
       </c>
       <c r="S8" t="n">
-        <v>96050133</v>
+        <v>20174081</v>
       </c>
       <c r="T8" t="n">
-        <v>100000</v>
+        <v>15191</v>
       </c>
       <c r="U8" t="n">
-        <v>2200000</v>
+        <v>16572</v>
       </c>
       <c r="V8" t="n">
-        <v>1960000</v>
+        <v>3192763</v>
       </c>
       <c r="W8" t="n">
-        <v>2240000</v>
+        <v>7276237</v>
       </c>
       <c r="X8" t="n">
-        <v>14481801</v>
+        <v>353834</v>
       </c>
       <c r="Y8" t="n">
-        <v>24614741</v>
+        <v>463504</v>
       </c>
       <c r="Z8" t="n">
-        <v>37670117</v>
+        <v>194882</v>
       </c>
       <c r="AA8" t="n">
-        <v>88297461</v>
+        <v>801410</v>
       </c>
       <c r="AB8" t="n">
         <v>140</v>
@@ -1405,37 +1405,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.76</v>
+        <v>1145</v>
       </c>
       <c r="D9" t="n">
-        <v>30.08</v>
+        <v>1058</v>
       </c>
       <c r="E9" t="n">
-        <v>28.81</v>
+        <v>1021.5</v>
       </c>
       <c r="F9" t="n">
-        <v>28.21</v>
+        <v>1040.6</v>
       </c>
       <c r="G9" t="n">
-        <v>71631385</v>
+        <v>6075000</v>
       </c>
       <c r="H9" t="n">
-        <v>99872752</v>
+        <v>3574000</v>
       </c>
       <c r="I9" t="n">
-        <v>30.8</v>
+        <v>1210</v>
       </c>
       <c r="J9" t="n">
-        <v>25.87</v>
+        <v>936</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,52 +1443,52 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>46044135</v>
+        <v>1189926</v>
       </c>
       <c r="M9" t="n">
-        <v>113946253</v>
+        <v>1922078</v>
       </c>
       <c r="N9" t="n">
-        <v>240984669</v>
+        <v>1409764</v>
       </c>
       <c r="O9" t="n">
-        <v>309814450</v>
+        <v>-745756</v>
       </c>
       <c r="P9" t="n">
-        <v>20982164</v>
+        <v>1047554</v>
       </c>
       <c r="Q9" t="n">
-        <v>70088792</v>
+        <v>1654327</v>
       </c>
       <c r="R9" t="n">
-        <v>153032530</v>
+        <v>1149739</v>
       </c>
       <c r="S9" t="n">
-        <v>215271412</v>
+        <v>-560167</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V9" t="n">
-        <v>2500000</v>
+        <v>10000</v>
       </c>
       <c r="W9" t="n">
-        <v>2500000</v>
+        <v>-233044</v>
       </c>
       <c r="X9" t="n">
-        <v>25061971</v>
+        <v>142372</v>
       </c>
       <c r="Y9" t="n">
-        <v>43857461</v>
+        <v>257751</v>
       </c>
       <c r="Z9" t="n">
-        <v>85452139</v>
+        <v>250025</v>
       </c>
       <c r="AA9" t="n">
-        <v>92043038</v>
+        <v>47455</v>
       </c>
       <c r="AB9" t="n">
         <v>140</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、黃金交叉、成交量放大</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1515,44 +1515,44 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>2382.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2445</v>
+        <v>372.5</v>
       </c>
       <c r="D10" t="n">
-        <v>2399</v>
+        <v>329.7</v>
       </c>
       <c r="E10" t="n">
-        <v>2197</v>
+        <v>316.9</v>
       </c>
       <c r="F10" t="n">
-        <v>2194</v>
+        <v>324.27</v>
       </c>
       <c r="G10" t="n">
-        <v>17179076</v>
+        <v>76692327</v>
       </c>
       <c r="H10" t="n">
-        <v>13409238</v>
+        <v>59474501</v>
       </c>
       <c r="I10" t="n">
-        <v>2585</v>
+        <v>372.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1880</v>
+        <v>288.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,55 +1560,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>807932</v>
+        <v>4874370</v>
       </c>
       <c r="M10" t="n">
-        <v>2603797</v>
+        <v>18267163</v>
       </c>
       <c r="N10" t="n">
-        <v>10087865</v>
+        <v>6680948</v>
       </c>
       <c r="O10" t="n">
-        <v>7022245</v>
+        <v>2310404</v>
       </c>
       <c r="P10" t="n">
-        <v>159559</v>
+        <v>-2613127</v>
       </c>
       <c r="Q10" t="n">
-        <v>1933010</v>
+        <v>-18440356</v>
       </c>
       <c r="R10" t="n">
-        <v>8590945</v>
+        <v>-55857239</v>
       </c>
       <c r="S10" t="n">
-        <v>8203923</v>
+        <v>-87301189</v>
       </c>
       <c r="T10" t="n">
-        <v>604387</v>
+        <v>7281000</v>
       </c>
       <c r="U10" t="n">
-        <v>779198</v>
+        <v>35323352</v>
       </c>
       <c r="V10" t="n">
-        <v>1142598</v>
+        <v>60624404</v>
       </c>
       <c r="W10" t="n">
-        <v>-1519176</v>
+        <v>89314165</v>
       </c>
       <c r="X10" t="n">
-        <v>43986</v>
+        <v>206497</v>
       </c>
       <c r="Y10" t="n">
-        <v>-108411</v>
+        <v>1384167</v>
       </c>
       <c r="Z10" t="n">
-        <v>354322</v>
+        <v>1913783</v>
       </c>
       <c r="AA10" t="n">
-        <v>337498</v>
+        <v>297428</v>
       </c>
       <c r="AB10" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.8</v>
+        <v>74.8</v>
       </c>
       <c r="D11" t="n">
-        <v>19.54</v>
+        <v>72.42</v>
       </c>
       <c r="E11" t="n">
-        <v>18.19</v>
+        <v>70.08</v>
       </c>
       <c r="F11" t="n">
-        <v>17.56</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>18564858</v>
+        <v>180789702</v>
       </c>
       <c r="H11" t="n">
-        <v>37799302</v>
+        <v>180590810</v>
       </c>
       <c r="I11" t="n">
-        <v>22.8</v>
+        <v>81.2</v>
       </c>
       <c r="J11" t="n">
-        <v>16.55</v>
+        <v>61.8</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1404121</v>
+        <v>36235379</v>
       </c>
       <c r="M11" t="n">
-        <v>2904196</v>
+        <v>18005086</v>
       </c>
       <c r="N11" t="n">
-        <v>12727687</v>
+        <v>24812582</v>
       </c>
       <c r="O11" t="n">
-        <v>21149602</v>
+        <v>100060322</v>
       </c>
       <c r="P11" t="n">
-        <v>-1010000</v>
+        <v>35838589</v>
       </c>
       <c r="Q11" t="n">
-        <v>-627327</v>
+        <v>17380149</v>
       </c>
       <c r="R11" t="n">
-        <v>8971673</v>
+        <v>21056648</v>
       </c>
       <c r="S11" t="n">
-        <v>17636025</v>
+        <v>91577139</v>
       </c>
       <c r="T11" t="n">
-        <v>-4000</v>
+        <v>421000</v>
       </c>
       <c r="U11" t="n">
-        <v>-8000</v>
+        <v>1027000</v>
       </c>
       <c r="V11" t="n">
-        <v>-12000</v>
+        <v>2759000</v>
       </c>
       <c r="W11" t="n">
-        <v>486000</v>
+        <v>2802000</v>
       </c>
       <c r="X11" t="n">
-        <v>2418121</v>
+        <v>-24210</v>
       </c>
       <c r="Y11" t="n">
-        <v>3539523</v>
+        <v>-402063</v>
       </c>
       <c r="Z11" t="n">
-        <v>3768014</v>
+        <v>996934</v>
       </c>
       <c r="AA11" t="n">
-        <v>3027577</v>
+        <v>5681183</v>
       </c>
       <c r="AB11" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,54 +1739,54 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>166.5</v>
+        <v>43.2</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>42.08</v>
       </c>
       <c r="E12" t="n">
-        <v>153.05</v>
+        <v>41.97</v>
       </c>
       <c r="F12" t="n">
-        <v>157.35</v>
+        <v>40.57</v>
       </c>
       <c r="G12" t="n">
-        <v>170917629</v>
+        <v>28077068</v>
       </c>
       <c r="H12" t="n">
-        <v>186682969</v>
+        <v>25742972</v>
       </c>
       <c r="I12" t="n">
-        <v>178.5</v>
+        <v>44.75</v>
       </c>
       <c r="J12" t="n">
-        <v>136.5</v>
+        <v>37.45</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,55 +1794,55 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8055757</v>
+        <v>9525842</v>
       </c>
       <c r="M12" t="n">
-        <v>42604570</v>
+        <v>12285874</v>
       </c>
       <c r="N12" t="n">
-        <v>86425911</v>
+        <v>15455905</v>
       </c>
       <c r="O12" t="n">
-        <v>14319682</v>
+        <v>72915018</v>
       </c>
       <c r="P12" t="n">
-        <v>8184461</v>
+        <v>2233303</v>
       </c>
       <c r="Q12" t="n">
-        <v>44126812</v>
+        <v>6940623</v>
       </c>
       <c r="R12" t="n">
-        <v>85615640</v>
+        <v>8488390</v>
       </c>
       <c r="S12" t="n">
-        <v>29588979</v>
+        <v>71670898</v>
       </c>
       <c r="T12" t="n">
-        <v>23000</v>
+        <v>5724000</v>
       </c>
       <c r="U12" t="n">
-        <v>-284000</v>
+        <v>5719000</v>
       </c>
       <c r="V12" t="n">
-        <v>2026000</v>
+        <v>5210000</v>
       </c>
       <c r="W12" t="n">
-        <v>-11302000</v>
+        <v>1863000</v>
       </c>
       <c r="X12" t="n">
-        <v>-151704</v>
+        <v>1568539</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1238242</v>
+        <v>-373749</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1215729</v>
+        <v>1757515</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3967297</v>
+        <v>-618880</v>
       </c>
       <c r="AB12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1866,44 +1866,44 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>729</v>
+        <v>25.05</v>
       </c>
       <c r="D13" t="n">
-        <v>695.4</v>
+        <v>21.03</v>
       </c>
       <c r="E13" t="n">
-        <v>616.2</v>
+        <v>19.02</v>
       </c>
       <c r="F13" t="n">
-        <v>557.77</v>
+        <v>17.98</v>
       </c>
       <c r="G13" t="n">
-        <v>7357595</v>
+        <v>8617355</v>
       </c>
       <c r="H13" t="n">
-        <v>21034907</v>
+        <v>36908518</v>
       </c>
       <c r="I13" t="n">
-        <v>764</v>
+        <v>25.05</v>
       </c>
       <c r="J13" t="n">
-        <v>445.5</v>
+        <v>16.55</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2189073</v>
+        <v>109130</v>
       </c>
       <c r="M13" t="n">
-        <v>764248</v>
+        <v>4838885</v>
       </c>
       <c r="N13" t="n">
-        <v>8308749</v>
+        <v>6388241</v>
       </c>
       <c r="O13" t="n">
-        <v>27987628</v>
+        <v>23449524</v>
       </c>
       <c r="P13" t="n">
-        <v>1727169</v>
+        <v>-530000</v>
       </c>
       <c r="Q13" t="n">
-        <v>-72044</v>
+        <v>1641838</v>
       </c>
       <c r="R13" t="n">
-        <v>4310104</v>
+        <v>2170673</v>
       </c>
       <c r="S13" t="n">
-        <v>19257046</v>
+        <v>18702025</v>
       </c>
       <c r="T13" t="n">
-        <v>-905</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>870572</v>
+        <v>-4000</v>
       </c>
       <c r="V13" t="n">
-        <v>4336572</v>
+        <v>-12000</v>
       </c>
       <c r="W13" t="n">
-        <v>7874046</v>
+        <v>486000</v>
       </c>
       <c r="X13" t="n">
-        <v>462809</v>
+        <v>639130</v>
       </c>
       <c r="Y13" t="n">
-        <v>-34280</v>
+        <v>3201047</v>
       </c>
       <c r="Z13" t="n">
-        <v>-337927</v>
+        <v>4229568</v>
       </c>
       <c r="AA13" t="n">
-        <v>856536</v>
+        <v>4261499</v>
       </c>
       <c r="AB13" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,54 +1973,54 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>347</v>
+        <v>668</v>
       </c>
       <c r="D14" t="n">
-        <v>316.5</v>
+        <v>584.4</v>
       </c>
       <c r="E14" t="n">
-        <v>304.05</v>
+        <v>537.6</v>
       </c>
       <c r="F14" t="n">
-        <v>298.62</v>
+        <v>491.52</v>
       </c>
       <c r="G14" t="n">
-        <v>140975644</v>
+        <v>10003000</v>
       </c>
       <c r="H14" t="n">
-        <v>176543954</v>
+        <v>8490200</v>
       </c>
       <c r="I14" t="n">
-        <v>353</v>
+        <v>668</v>
       </c>
       <c r="J14" t="n">
-        <v>217</v>
+        <v>368</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2028,55 +2028,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>24486580</v>
+        <v>-525244</v>
       </c>
       <c r="M14" t="n">
-        <v>92243642</v>
+        <v>-448244</v>
       </c>
       <c r="N14" t="n">
-        <v>82863197</v>
+        <v>922122</v>
       </c>
       <c r="O14" t="n">
-        <v>41889398</v>
+        <v>10571302</v>
       </c>
       <c r="P14" t="n">
-        <v>19483386</v>
+        <v>-93101</v>
       </c>
       <c r="Q14" t="n">
-        <v>87397337</v>
+        <v>423150</v>
       </c>
       <c r="R14" t="n">
-        <v>93426579</v>
+        <v>1629999</v>
       </c>
       <c r="S14" t="n">
-        <v>72607197</v>
+        <v>10820777</v>
       </c>
       <c r="T14" t="n">
-        <v>4795000</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>5562330</v>
+        <v>15800</v>
       </c>
       <c r="V14" t="n">
-        <v>-9187395</v>
+        <v>13700</v>
       </c>
       <c r="W14" t="n">
-        <v>-23784560</v>
+        <v>84500</v>
       </c>
       <c r="X14" t="n">
-        <v>208194</v>
+        <v>-432143</v>
       </c>
       <c r="Y14" t="n">
-        <v>-716025</v>
+        <v>-887194</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1375987</v>
+        <v>-721577</v>
       </c>
       <c r="AA14" t="n">
-        <v>-6933239</v>
+        <v>-333975</v>
       </c>
       <c r="AB14" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2090,54 +2090,54 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1015</v>
+        <v>224</v>
       </c>
       <c r="D15" t="n">
-        <v>905.2</v>
+        <v>214.2</v>
       </c>
       <c r="E15" t="n">
-        <v>794.5</v>
+        <v>212.55</v>
       </c>
       <c r="F15" t="n">
-        <v>770.05</v>
+        <v>210.9</v>
       </c>
       <c r="G15" t="n">
-        <v>11189000</v>
+        <v>38077211</v>
       </c>
       <c r="H15" t="n">
-        <v>12916600</v>
+        <v>31670603</v>
       </c>
       <c r="I15" t="n">
-        <v>1020</v>
+        <v>225</v>
       </c>
       <c r="J15" t="n">
-        <v>597</v>
+        <v>195.5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,55 +2145,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1670438</v>
+        <v>15949739</v>
       </c>
       <c r="M15" t="n">
-        <v>7193475</v>
+        <v>21698905</v>
       </c>
       <c r="N15" t="n">
-        <v>6390247</v>
+        <v>20009420</v>
       </c>
       <c r="O15" t="n">
-        <v>1446388</v>
+        <v>57007750</v>
       </c>
       <c r="P15" t="n">
-        <v>344138</v>
+        <v>2159299</v>
       </c>
       <c r="Q15" t="n">
-        <v>-664171</v>
+        <v>-16404349</v>
       </c>
       <c r="R15" t="n">
-        <v>-1656428</v>
+        <v>-35593846</v>
       </c>
       <c r="S15" t="n">
-        <v>-7353618</v>
+        <v>-3428806</v>
       </c>
       <c r="T15" t="n">
-        <v>1146000</v>
+        <v>12843785</v>
       </c>
       <c r="U15" t="n">
-        <v>7953133</v>
+        <v>36165345</v>
       </c>
       <c r="V15" t="n">
-        <v>7798095</v>
+        <v>52647181</v>
       </c>
       <c r="W15" t="n">
-        <v>7456907</v>
+        <v>55898201</v>
       </c>
       <c r="X15" t="n">
-        <v>180300</v>
+        <v>946655</v>
       </c>
       <c r="Y15" t="n">
-        <v>-95487</v>
+        <v>1937909</v>
       </c>
       <c r="Z15" t="n">
-        <v>248580</v>
+        <v>2956085</v>
       </c>
       <c r="AA15" t="n">
-        <v>1343099</v>
+        <v>4538355</v>
       </c>
       <c r="AB15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2217,44 +2217,44 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>52.7</v>
+        <v>31.99</v>
       </c>
       <c r="D16" t="n">
-        <v>52.28</v>
+        <v>30.58</v>
       </c>
       <c r="E16" t="n">
-        <v>51.39</v>
+        <v>29.23</v>
       </c>
       <c r="F16" t="n">
-        <v>50.59</v>
+        <v>28.51</v>
       </c>
       <c r="G16" t="n">
-        <v>29776823</v>
+        <v>103435481</v>
       </c>
       <c r="H16" t="n">
-        <v>24715593</v>
+        <v>92135431</v>
       </c>
       <c r="I16" t="n">
-        <v>53.9</v>
+        <v>32.05</v>
       </c>
       <c r="J16" t="n">
-        <v>47.35</v>
+        <v>26.25</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,55 +2262,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7389461</v>
+        <v>44716877</v>
       </c>
       <c r="M16" t="n">
-        <v>24139514</v>
+        <v>110402646</v>
       </c>
       <c r="N16" t="n">
-        <v>19611659</v>
+        <v>203656274</v>
       </c>
       <c r="O16" t="n">
-        <v>55290712</v>
+        <v>410699566</v>
       </c>
       <c r="P16" t="n">
-        <v>7588362</v>
+        <v>22071009</v>
       </c>
       <c r="Q16" t="n">
-        <v>25352759</v>
+        <v>40851643</v>
       </c>
       <c r="R16" t="n">
-        <v>21862491</v>
+        <v>99728306</v>
       </c>
       <c r="S16" t="n">
-        <v>55769432</v>
+        <v>256639718</v>
       </c>
       <c r="T16" t="n">
-        <v>-337924</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-1821392</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1815242</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-1896308</v>
+        <v>2500000</v>
       </c>
       <c r="X16" t="n">
-        <v>139023</v>
+        <v>22645868</v>
       </c>
       <c r="Y16" t="n">
-        <v>608147</v>
+        <v>69551003</v>
       </c>
       <c r="Z16" t="n">
-        <v>-435590</v>
+        <v>103927968</v>
       </c>
       <c r="AA16" t="n">
-        <v>1417588</v>
+        <v>151559848</v>
       </c>
       <c r="AB16" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2324,54 +2324,54 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>98.09999999999999</v>
+        <v>950</v>
       </c>
       <c r="D17" t="n">
-        <v>92.40000000000001</v>
+        <v>937.6</v>
       </c>
       <c r="E17" t="n">
-        <v>88.27</v>
+        <v>819.7</v>
       </c>
       <c r="F17" t="n">
-        <v>88.78</v>
+        <v>787.25</v>
       </c>
       <c r="G17" t="n">
-        <v>150486779</v>
+        <v>4452000</v>
       </c>
       <c r="H17" t="n">
-        <v>99920545</v>
+        <v>12667000</v>
       </c>
       <c r="I17" t="n">
-        <v>101.5</v>
+        <v>1040</v>
       </c>
       <c r="J17" t="n">
-        <v>80.40000000000001</v>
+        <v>615</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>63814268</v>
+        <v>798638</v>
       </c>
       <c r="M17" t="n">
-        <v>84945508</v>
+        <v>2696041</v>
       </c>
       <c r="N17" t="n">
-        <v>122013685</v>
+        <v>7992113</v>
       </c>
       <c r="O17" t="n">
-        <v>106076369</v>
+        <v>3381131</v>
       </c>
       <c r="P17" t="n">
-        <v>59319659</v>
+        <v>989046</v>
       </c>
       <c r="Q17" t="n">
-        <v>79980257</v>
+        <v>-337021</v>
       </c>
       <c r="R17" t="n">
-        <v>115454226</v>
+        <v>324875</v>
       </c>
       <c r="S17" t="n">
-        <v>104358632</v>
+        <v>-4750182</v>
       </c>
       <c r="T17" t="n">
-        <v>2301457</v>
+        <v>-792857</v>
       </c>
       <c r="U17" t="n">
-        <v>3965189</v>
+        <v>2500409</v>
       </c>
       <c r="V17" t="n">
-        <v>2988189</v>
+        <v>7160276</v>
       </c>
       <c r="W17" t="n">
-        <v>2977289</v>
+        <v>6585088</v>
       </c>
       <c r="X17" t="n">
-        <v>2193152</v>
+        <v>602449</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000062</v>
+        <v>532653</v>
       </c>
       <c r="Z17" t="n">
-        <v>3571270</v>
+        <v>506962</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1259552</v>
+        <v>1546225</v>
       </c>
       <c r="AB17" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2451,44 +2451,44 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7769.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8260</v>
+        <v>2785</v>
       </c>
       <c r="D18" t="n">
-        <v>7861</v>
+        <v>2691</v>
       </c>
       <c r="E18" t="n">
-        <v>7494.5</v>
+        <v>2580</v>
       </c>
       <c r="F18" t="n">
-        <v>6920.5</v>
+        <v>2544</v>
       </c>
       <c r="G18" t="n">
-        <v>1880557</v>
+        <v>5090031</v>
       </c>
       <c r="H18" t="n">
-        <v>878607</v>
+        <v>6032552</v>
       </c>
       <c r="I18" t="n">
-        <v>8465</v>
+        <v>2845</v>
       </c>
       <c r="J18" t="n">
-        <v>5030</v>
+        <v>2300</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2496,55 +2496,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>102468</v>
+        <v>776741</v>
       </c>
       <c r="M18" t="n">
-        <v>234245</v>
+        <v>883124</v>
       </c>
       <c r="N18" t="n">
-        <v>165465</v>
+        <v>3077948</v>
       </c>
       <c r="O18" t="n">
-        <v>87623</v>
+        <v>1234520</v>
       </c>
       <c r="P18" t="n">
-        <v>-49388</v>
+        <v>645540</v>
       </c>
       <c r="Q18" t="n">
-        <v>-273656</v>
+        <v>418807</v>
       </c>
       <c r="R18" t="n">
-        <v>-310537</v>
+        <v>1748863</v>
       </c>
       <c r="S18" t="n">
-        <v>-250052</v>
+        <v>-780799</v>
       </c>
       <c r="T18" t="n">
-        <v>160004</v>
+        <v>67001</v>
       </c>
       <c r="U18" t="n">
-        <v>511004</v>
+        <v>430877</v>
       </c>
       <c r="V18" t="n">
-        <v>471853</v>
+        <v>1316900</v>
       </c>
       <c r="W18" t="n">
-        <v>361853</v>
+        <v>2045460</v>
       </c>
       <c r="X18" t="n">
-        <v>-8148</v>
+        <v>64200</v>
       </c>
       <c r="Y18" t="n">
-        <v>-3103</v>
+        <v>33440</v>
       </c>
       <c r="Z18" t="n">
-        <v>4149</v>
+        <v>12185</v>
       </c>
       <c r="AA18" t="n">
-        <v>-24178</v>
+        <v>-30141</v>
       </c>
       <c r="AB18" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2558,54 +2558,54 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、法人連續偏買、5日法人買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1690</v>
+        <v>168</v>
       </c>
       <c r="D19" t="n">
-        <v>1608</v>
+        <v>153.2</v>
       </c>
       <c r="E19" t="n">
-        <v>1451</v>
+        <v>136.65</v>
       </c>
       <c r="F19" t="n">
-        <v>1404</v>
+        <v>127.49</v>
       </c>
       <c r="G19" t="n">
-        <v>9688000</v>
+        <v>295190831</v>
       </c>
       <c r="H19" t="n">
-        <v>7520400</v>
+        <v>336552469</v>
       </c>
       <c r="I19" t="n">
-        <v>1735</v>
+        <v>173.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1060</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2613,55 +2613,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1026806</v>
+        <v>146059</v>
       </c>
       <c r="M19" t="n">
-        <v>1458560</v>
+        <v>23904373</v>
       </c>
       <c r="N19" t="n">
-        <v>1657269</v>
+        <v>103702296</v>
       </c>
       <c r="O19" t="n">
-        <v>2868520</v>
+        <v>165431261</v>
       </c>
       <c r="P19" t="n">
-        <v>80409</v>
+        <v>-6767657</v>
       </c>
       <c r="Q19" t="n">
-        <v>-883531</v>
+        <v>-4918288</v>
       </c>
       <c r="R19" t="n">
-        <v>-1794129</v>
+        <v>56728248</v>
       </c>
       <c r="S19" t="n">
-        <v>-598456</v>
+        <v>112812507</v>
       </c>
       <c r="T19" t="n">
-        <v>977000</v>
+        <v>5952147</v>
       </c>
       <c r="U19" t="n">
-        <v>2608000</v>
+        <v>28060924</v>
       </c>
       <c r="V19" t="n">
-        <v>4053000</v>
+        <v>43096531</v>
       </c>
       <c r="W19" t="n">
-        <v>3920100</v>
+        <v>52047258</v>
       </c>
       <c r="X19" t="n">
-        <v>-30603</v>
+        <v>961569</v>
       </c>
       <c r="Y19" t="n">
-        <v>-265909</v>
+        <v>761737</v>
       </c>
       <c r="Z19" t="n">
-        <v>-601602</v>
+        <v>3877517</v>
       </c>
       <c r="AA19" t="n">
-        <v>-453124</v>
+        <v>571496</v>
       </c>
       <c r="AB19" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,54 +2675,54 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2665</v>
+        <v>37.7</v>
       </c>
       <c r="D20" t="n">
-        <v>2649</v>
+        <v>35.81</v>
       </c>
       <c r="E20" t="n">
-        <v>2542.5</v>
+        <v>35.41</v>
       </c>
       <c r="F20" t="n">
-        <v>2549</v>
+        <v>35.11</v>
       </c>
       <c r="G20" t="n">
-        <v>9351169</v>
+        <v>82974354</v>
       </c>
       <c r="H20" t="n">
-        <v>6152175</v>
+        <v>85265386</v>
       </c>
       <c r="I20" t="n">
-        <v>2975</v>
+        <v>37.85</v>
       </c>
       <c r="J20" t="n">
-        <v>2300</v>
+        <v>33.4</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,55 +2730,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>574826</v>
+        <v>13546260</v>
       </c>
       <c r="M20" t="n">
-        <v>491421</v>
+        <v>43363173</v>
       </c>
       <c r="N20" t="n">
-        <v>1482876</v>
+        <v>16657509</v>
       </c>
       <c r="O20" t="n">
-        <v>-108322</v>
+        <v>21226516</v>
       </c>
       <c r="P20" t="n">
-        <v>232388</v>
+        <v>-24438582</v>
       </c>
       <c r="Q20" t="n">
-        <v>-19731</v>
+        <v>-60246419</v>
       </c>
       <c r="R20" t="n">
-        <v>302816</v>
+        <v>-119669352</v>
       </c>
       <c r="S20" t="n">
-        <v>-2201792</v>
+        <v>-148193516</v>
       </c>
       <c r="T20" t="n">
-        <v>298876</v>
+        <v>37712898</v>
       </c>
       <c r="U20" t="n">
-        <v>654876</v>
+        <v>102158167</v>
       </c>
       <c r="V20" t="n">
-        <v>1217899</v>
+        <v>133646088</v>
       </c>
       <c r="W20" t="n">
-        <v>2179460</v>
+        <v>166814366</v>
       </c>
       <c r="X20" t="n">
-        <v>43562</v>
+        <v>271944</v>
       </c>
       <c r="Y20" t="n">
-        <v>-143724</v>
+        <v>1451425</v>
       </c>
       <c r="Z20" t="n">
-        <v>-37839</v>
+        <v>2680773</v>
       </c>
       <c r="AA20" t="n">
-        <v>-85990</v>
+        <v>2605666</v>
       </c>
       <c r="AB20" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -2792,54 +2792,54 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5445</v>
+        <v>295</v>
       </c>
       <c r="D21" t="n">
-        <v>5272</v>
+        <v>275.1</v>
       </c>
       <c r="E21" t="n">
-        <v>5212</v>
+        <v>262.8</v>
       </c>
       <c r="F21" t="n">
-        <v>5202.25</v>
+        <v>270.48</v>
       </c>
       <c r="G21" t="n">
-        <v>3282663</v>
+        <v>31063246</v>
       </c>
       <c r="H21" t="n">
-        <v>2442013</v>
+        <v>25090063</v>
       </c>
       <c r="I21" t="n">
-        <v>5880</v>
+        <v>322</v>
       </c>
       <c r="J21" t="n">
-        <v>4615</v>
+        <v>230</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,55 +2847,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>816883</v>
+        <v>12348068</v>
       </c>
       <c r="M21" t="n">
-        <v>261458</v>
+        <v>8160032</v>
       </c>
       <c r="N21" t="n">
-        <v>180474</v>
+        <v>15069872</v>
       </c>
       <c r="O21" t="n">
-        <v>-14803</v>
+        <v>12457873</v>
       </c>
       <c r="P21" t="n">
-        <v>625866</v>
+        <v>11994537</v>
       </c>
       <c r="Q21" t="n">
-        <v>595836</v>
+        <v>7819120</v>
       </c>
       <c r="R21" t="n">
-        <v>788866</v>
+        <v>13707371</v>
       </c>
       <c r="S21" t="n">
-        <v>679185</v>
+        <v>11456171</v>
       </c>
       <c r="T21" t="n">
-        <v>175961</v>
+        <v>-3000</v>
       </c>
       <c r="U21" t="n">
-        <v>-136176</v>
+        <v>-3000</v>
       </c>
       <c r="V21" t="n">
-        <v>-384349</v>
+        <v>-241000</v>
       </c>
       <c r="W21" t="n">
-        <v>-599555</v>
+        <v>-251000</v>
       </c>
       <c r="X21" t="n">
-        <v>15056</v>
+        <v>356531</v>
       </c>
       <c r="Y21" t="n">
-        <v>-198202</v>
+        <v>343912</v>
       </c>
       <c r="Z21" t="n">
-        <v>-224043</v>
+        <v>1603501</v>
       </c>
       <c r="AA21" t="n">
-        <v>-94433</v>
+        <v>1252702</v>
       </c>
       <c r="AB21" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -2909,54 +2909,54 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>319</v>
+        <v>293.5</v>
       </c>
       <c r="D22" t="n">
-        <v>307.4</v>
+        <v>273.7</v>
       </c>
       <c r="E22" t="n">
-        <v>297.05</v>
+        <v>261.2</v>
       </c>
       <c r="F22" t="n">
-        <v>275</v>
+        <v>255.07</v>
       </c>
       <c r="G22" t="n">
-        <v>26333214</v>
+        <v>205766647</v>
       </c>
       <c r="H22" t="n">
-        <v>28680323</v>
+        <v>140617655</v>
       </c>
       <c r="I22" t="n">
-        <v>336.5</v>
+        <v>304.5</v>
       </c>
       <c r="J22" t="n">
-        <v>217.5</v>
+        <v>227</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,52 +2964,52 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1768455</v>
+        <v>-5143876</v>
       </c>
       <c r="M22" t="n">
-        <v>6314708</v>
+        <v>100059807</v>
       </c>
       <c r="N22" t="n">
-        <v>5650116</v>
+        <v>128543523</v>
       </c>
       <c r="O22" t="n">
-        <v>5110144</v>
+        <v>213173724</v>
       </c>
       <c r="P22" t="n">
-        <v>1507659</v>
+        <v>-6575097</v>
       </c>
       <c r="Q22" t="n">
-        <v>5144713</v>
+        <v>86629844</v>
       </c>
       <c r="R22" t="n">
-        <v>5860298</v>
+        <v>115525527</v>
       </c>
       <c r="S22" t="n">
-        <v>11469805</v>
+        <v>204533241</v>
       </c>
       <c r="T22" t="n">
-        <v>139000</v>
+        <v>1808000</v>
       </c>
       <c r="U22" t="n">
-        <v>1060768</v>
+        <v>9361253</v>
       </c>
       <c r="V22" t="n">
-        <v>-313232</v>
+        <v>9249189</v>
       </c>
       <c r="W22" t="n">
-        <v>-6063208</v>
+        <v>5565896</v>
       </c>
       <c r="X22" t="n">
-        <v>121796</v>
+        <v>-376779</v>
       </c>
       <c r="Y22" t="n">
-        <v>109227</v>
+        <v>4068710</v>
       </c>
       <c r="Z22" t="n">
-        <v>103050</v>
+        <v>3768807</v>
       </c>
       <c r="AA22" t="n">
-        <v>-296453</v>
+        <v>3074587</v>
       </c>
       <c r="AB22" t="n">
         <v>105</v>
@@ -3026,54 +3026,54 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>229.5</v>
+        <v>2355</v>
       </c>
       <c r="D23" t="n">
-        <v>216.8</v>
+        <v>2315</v>
       </c>
       <c r="E23" t="n">
-        <v>204.9</v>
+        <v>2276</v>
       </c>
       <c r="F23" t="n">
-        <v>191.4</v>
+        <v>2267.25</v>
       </c>
       <c r="G23" t="n">
-        <v>11072000</v>
+        <v>60942792</v>
       </c>
       <c r="H23" t="n">
-        <v>12985800</v>
+        <v>56218744</v>
       </c>
       <c r="I23" t="n">
-        <v>238</v>
+        <v>2415</v>
       </c>
       <c r="J23" t="n">
-        <v>152</v>
+        <v>2185</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,52 +3081,52 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1922480</v>
+        <v>-1931448</v>
       </c>
       <c r="M23" t="n">
-        <v>928804</v>
+        <v>5975111</v>
       </c>
       <c r="N23" t="n">
-        <v>1930767</v>
+        <v>6910399</v>
       </c>
       <c r="O23" t="n">
-        <v>3221267</v>
+        <v>-5215173</v>
       </c>
       <c r="P23" t="n">
-        <v>1883000</v>
+        <v>-3311663</v>
       </c>
       <c r="Q23" t="n">
-        <v>795795</v>
+        <v>2893994</v>
       </c>
       <c r="R23" t="n">
-        <v>1868268</v>
+        <v>3956357</v>
       </c>
       <c r="S23" t="n">
-        <v>2928312</v>
+        <v>-18529146</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>458215</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1272525</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>676468</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>10840143</v>
       </c>
       <c r="X23" t="n">
-        <v>39480</v>
+        <v>922000</v>
       </c>
       <c r="Y23" t="n">
-        <v>133009</v>
+        <v>1808592</v>
       </c>
       <c r="Z23" t="n">
-        <v>62499</v>
+        <v>2277574</v>
       </c>
       <c r="AA23" t="n">
-        <v>292955</v>
+        <v>2473830</v>
       </c>
       <c r="AB23" t="n">
         <v>105</v>
@@ -3143,54 +3143,54 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.9</v>
+        <v>1705</v>
       </c>
       <c r="D24" t="n">
-        <v>56.5</v>
+        <v>1629</v>
       </c>
       <c r="E24" t="n">
-        <v>53.79</v>
+        <v>1495.5</v>
       </c>
       <c r="F24" t="n">
-        <v>51.82</v>
+        <v>1433.75</v>
       </c>
       <c r="G24" t="n">
-        <v>10061343</v>
+        <v>8984000</v>
       </c>
       <c r="H24" t="n">
-        <v>13310924</v>
+        <v>9020000</v>
       </c>
       <c r="I24" t="n">
-        <v>61.4</v>
+        <v>1815</v>
       </c>
       <c r="J24" t="n">
-        <v>45.45</v>
+        <v>1125</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,52 +3198,52 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>223942</v>
+        <v>379477</v>
       </c>
       <c r="M24" t="n">
-        <v>1174650</v>
+        <v>1642627</v>
       </c>
       <c r="N24" t="n">
-        <v>4573006</v>
+        <v>1838037</v>
       </c>
       <c r="O24" t="n">
-        <v>15563085</v>
+        <v>3059725</v>
       </c>
       <c r="P24" t="n">
-        <v>36212</v>
+        <v>-548848</v>
       </c>
       <c r="Q24" t="n">
-        <v>898012</v>
+        <v>-1259270</v>
       </c>
       <c r="R24" t="n">
-        <v>3887881</v>
+        <v>-1432379</v>
       </c>
       <c r="S24" t="n">
-        <v>14415725</v>
+        <v>-33796</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>968000</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3158000</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3576000</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3569100</v>
       </c>
       <c r="X24" t="n">
-        <v>187730</v>
+        <v>-39675</v>
       </c>
       <c r="Y24" t="n">
-        <v>276638</v>
+        <v>-256103</v>
       </c>
       <c r="Z24" t="n">
-        <v>685125</v>
+        <v>-305584</v>
       </c>
       <c r="AA24" t="n">
-        <v>1147360</v>
+        <v>-475579</v>
       </c>
       <c r="AB24" t="n">
         <v>105</v>
@@ -3265,49 +3265,49 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1055</v>
+        <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>1047</v>
+        <v>59.78</v>
       </c>
       <c r="E25" t="n">
-        <v>956.7</v>
+        <v>56.55</v>
       </c>
       <c r="F25" t="n">
-        <v>914.15</v>
+        <v>57.85</v>
       </c>
       <c r="G25" t="n">
-        <v>21107426</v>
+        <v>16891552</v>
       </c>
       <c r="H25" t="n">
-        <v>26475004</v>
+        <v>26352455</v>
       </c>
       <c r="I25" t="n">
-        <v>1130</v>
+        <v>65</v>
       </c>
       <c r="J25" t="n">
-        <v>776</v>
+        <v>50.2</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,55 +3315,55 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-1460277</v>
+        <v>1051605</v>
       </c>
       <c r="M25" t="n">
-        <v>-194509</v>
+        <v>12258933</v>
       </c>
       <c r="N25" t="n">
-        <v>12773317</v>
+        <v>14444946</v>
       </c>
       <c r="O25" t="n">
-        <v>25914308</v>
+        <v>9009446</v>
       </c>
       <c r="P25" t="n">
-        <v>-1150135</v>
+        <v>1587498</v>
       </c>
       <c r="Q25" t="n">
-        <v>-608166</v>
+        <v>11720020</v>
       </c>
       <c r="R25" t="n">
-        <v>9847208</v>
+        <v>13446507</v>
       </c>
       <c r="S25" t="n">
-        <v>21378067</v>
+        <v>8915008</v>
       </c>
       <c r="T25" t="n">
-        <v>-225373</v>
+        <v>12000</v>
       </c>
       <c r="U25" t="n">
-        <v>1293627</v>
+        <v>12000</v>
       </c>
       <c r="V25" t="n">
-        <v>3733627</v>
+        <v>12000</v>
       </c>
       <c r="W25" t="n">
-        <v>5098570</v>
+        <v>204000</v>
       </c>
       <c r="X25" t="n">
-        <v>-84769</v>
+        <v>-547893</v>
       </c>
       <c r="Y25" t="n">
-        <v>-879970</v>
+        <v>526913</v>
       </c>
       <c r="Z25" t="n">
-        <v>-807518</v>
+        <v>986439</v>
       </c>
       <c r="AA25" t="n">
-        <v>-562329</v>
+        <v>-109562</v>
       </c>
       <c r="AB25" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -3377,54 +3377,54 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>213</v>
+        <v>167.5</v>
       </c>
       <c r="D26" t="n">
-        <v>212.2</v>
+        <v>162</v>
       </c>
       <c r="E26" t="n">
-        <v>209.9</v>
+        <v>153.8</v>
       </c>
       <c r="F26" t="n">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="G26" t="n">
-        <v>30658046</v>
+        <v>190490552</v>
       </c>
       <c r="H26" t="n">
-        <v>30267084</v>
+        <v>197619129</v>
       </c>
       <c r="I26" t="n">
-        <v>222</v>
+        <v>178.5</v>
       </c>
       <c r="J26" t="n">
-        <v>195.5</v>
+        <v>136.5</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,55 +3432,55 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4499672</v>
+        <v>18724442</v>
       </c>
       <c r="M26" t="n">
-        <v>5440527</v>
+        <v>108932425</v>
       </c>
       <c r="N26" t="n">
-        <v>4632636</v>
+        <v>93713452</v>
       </c>
       <c r="O26" t="n">
-        <v>30344824</v>
+        <v>40901700</v>
       </c>
       <c r="P26" t="n">
-        <v>-7914383</v>
+        <v>14372572</v>
       </c>
       <c r="Q26" t="n">
-        <v>-28514697</v>
+        <v>104191240</v>
       </c>
       <c r="R26" t="n">
-        <v>-41309715</v>
+        <v>87837822</v>
       </c>
       <c r="S26" t="n">
-        <v>-16655106</v>
+        <v>51829461</v>
       </c>
       <c r="T26" t="n">
-        <v>12001461</v>
+        <v>3088000</v>
       </c>
       <c r="U26" t="n">
-        <v>32272051</v>
+        <v>2964000</v>
       </c>
       <c r="V26" t="n">
-        <v>43663057</v>
+        <v>5773000</v>
       </c>
       <c r="W26" t="n">
-        <v>42882125</v>
+        <v>-8247000</v>
       </c>
       <c r="X26" t="n">
-        <v>412594</v>
+        <v>1263870</v>
       </c>
       <c r="Y26" t="n">
-        <v>1683173</v>
+        <v>1777185</v>
       </c>
       <c r="Z26" t="n">
-        <v>2279294</v>
+        <v>102630</v>
       </c>
       <c r="AA26" t="n">
-        <v>4117805</v>
+        <v>-2680761</v>
       </c>
       <c r="AB26" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -3494,110 +3494,110 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>834</v>
+        <v>314</v>
       </c>
       <c r="D27" t="n">
-        <v>834.8</v>
+        <v>310.6</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>299.85</v>
       </c>
       <c r="F27" t="n">
-        <v>745.65</v>
+        <v>279.38</v>
       </c>
       <c r="G27" t="n">
-        <v>9119000</v>
+        <v>17008580</v>
       </c>
       <c r="H27" t="n">
-        <v>4059200</v>
+        <v>25024889</v>
       </c>
       <c r="I27" t="n">
-        <v>929</v>
+        <v>336.5</v>
       </c>
       <c r="J27" t="n">
-        <v>553</v>
+        <v>221.5</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>725160</v>
+        <v>-3145576</v>
       </c>
       <c r="M27" t="n">
-        <v>2193908</v>
+        <v>-2096880</v>
       </c>
       <c r="N27" t="n">
-        <v>1256711</v>
+        <v>8442316</v>
       </c>
       <c r="O27" t="n">
-        <v>1527094</v>
+        <v>-2780785</v>
       </c>
       <c r="P27" t="n">
-        <v>-520625</v>
+        <v>-3049921</v>
       </c>
       <c r="Q27" t="n">
-        <v>834333</v>
+        <v>-2116785</v>
       </c>
       <c r="R27" t="n">
-        <v>70799</v>
+        <v>7052430</v>
       </c>
       <c r="S27" t="n">
-        <v>357165</v>
+        <v>3656099</v>
       </c>
       <c r="T27" t="n">
-        <v>1195000</v>
+        <v>152000</v>
       </c>
       <c r="U27" t="n">
-        <v>1192000</v>
+        <v>311768</v>
       </c>
       <c r="V27" t="n">
-        <v>995000</v>
+        <v>1427768</v>
       </c>
       <c r="W27" t="n">
-        <v>976000</v>
+        <v>-5810208</v>
       </c>
       <c r="X27" t="n">
-        <v>50785</v>
+        <v>-247655</v>
       </c>
       <c r="Y27" t="n">
-        <v>167575</v>
+        <v>-291863</v>
       </c>
       <c r="Z27" t="n">
-        <v>190912</v>
+        <v>-37882</v>
       </c>
       <c r="AA27" t="n">
-        <v>193929</v>
+        <v>-626676</v>
       </c>
       <c r="AB27" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -3611,54 +3611,54 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>強勢偏多：跌破5日線、多頭排列、爆量、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>61.1</v>
+        <v>905</v>
       </c>
       <c r="D28" t="n">
-        <v>58.86</v>
+        <v>886</v>
       </c>
       <c r="E28" t="n">
-        <v>55.86</v>
+        <v>874.7</v>
       </c>
       <c r="F28" t="n">
-        <v>57.81</v>
+        <v>879.85</v>
       </c>
       <c r="G28" t="n">
-        <v>27262250</v>
+        <v>21446815</v>
       </c>
       <c r="H28" t="n">
-        <v>25237882</v>
+        <v>21418672</v>
       </c>
       <c r="I28" t="n">
-        <v>65</v>
+        <v>1035</v>
       </c>
       <c r="J28" t="n">
-        <v>50.2</v>
+        <v>765</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,55 +3666,55 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-752451</v>
+        <v>6489767</v>
       </c>
       <c r="M28" t="n">
-        <v>11256922</v>
+        <v>-2035790</v>
       </c>
       <c r="N28" t="n">
-        <v>14269862</v>
+        <v>2257312</v>
       </c>
       <c r="O28" t="n">
-        <v>3604234</v>
+        <v>-2252248</v>
       </c>
       <c r="P28" t="n">
-        <v>-1494770</v>
+        <v>5749529</v>
       </c>
       <c r="Q28" t="n">
-        <v>10057089</v>
+        <v>1761213</v>
       </c>
       <c r="R28" t="n">
-        <v>12526503</v>
+        <v>7285342</v>
       </c>
       <c r="S28" t="n">
-        <v>3576706</v>
+        <v>2700083</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>764000</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>-3636000</v>
       </c>
       <c r="V28" t="n">
-        <v>39000</v>
+        <v>-4848000</v>
       </c>
       <c r="W28" t="n">
-        <v>192000</v>
+        <v>-4370000</v>
       </c>
       <c r="X28" t="n">
-        <v>742319</v>
+        <v>-23762</v>
       </c>
       <c r="Y28" t="n">
-        <v>1199833</v>
+        <v>-161003</v>
       </c>
       <c r="Z28" t="n">
-        <v>1704359</v>
+        <v>-180030</v>
       </c>
       <c r="AA28" t="n">
-        <v>-164472</v>
+        <v>-582331</v>
       </c>
       <c r="AB28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -3728,54 +3728,54 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>379</v>
+        <v>4555</v>
       </c>
       <c r="D29" t="n">
-        <v>346</v>
+        <v>4436</v>
       </c>
       <c r="E29" t="n">
-        <v>298.2</v>
+        <v>4022</v>
       </c>
       <c r="F29" t="n">
-        <v>264.02</v>
+        <v>3749.75</v>
       </c>
       <c r="G29" t="n">
-        <v>17024627</v>
+        <v>20083897</v>
       </c>
       <c r="H29" t="n">
-        <v>47751060</v>
+        <v>19485690</v>
       </c>
       <c r="I29" t="n">
-        <v>387</v>
+        <v>4710</v>
       </c>
       <c r="J29" t="n">
-        <v>208</v>
+        <v>3100</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,55 +3783,55 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-1530721</v>
+        <v>3148836</v>
       </c>
       <c r="M29" t="n">
-        <v>9386598</v>
+        <v>-1878848</v>
       </c>
       <c r="N29" t="n">
-        <v>9329511</v>
+        <v>942900</v>
       </c>
       <c r="O29" t="n">
-        <v>2976549</v>
+        <v>-4597456</v>
       </c>
       <c r="P29" t="n">
-        <v>-1822021</v>
+        <v>3786804</v>
       </c>
       <c r="Q29" t="n">
-        <v>9593946</v>
+        <v>605566</v>
       </c>
       <c r="R29" t="n">
-        <v>9756699</v>
+        <v>4970698</v>
       </c>
       <c r="S29" t="n">
-        <v>5846660</v>
+        <v>-976834</v>
       </c>
       <c r="T29" t="n">
-        <v>-99797</v>
+        <v>-461186</v>
       </c>
       <c r="U29" t="n">
-        <v>-339782</v>
+        <v>-2105376</v>
       </c>
       <c r="V29" t="n">
-        <v>-1394782</v>
+        <v>-3983417</v>
       </c>
       <c r="W29" t="n">
-        <v>-4249884</v>
+        <v>-4323474</v>
       </c>
       <c r="X29" t="n">
-        <v>391097</v>
+        <v>-176782</v>
       </c>
       <c r="Y29" t="n">
-        <v>132434</v>
+        <v>-379038</v>
       </c>
       <c r="Z29" t="n">
-        <v>967594</v>
+        <v>-44381</v>
       </c>
       <c r="AA29" t="n">
-        <v>1379773</v>
+        <v>702852</v>
       </c>
       <c r="AB29" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3855,44 +3855,44 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>41.65</v>
+        <v>173.5</v>
       </c>
       <c r="D30" t="n">
-        <v>42.2</v>
+        <v>172.8</v>
       </c>
       <c r="E30" t="n">
-        <v>41.59</v>
+        <v>173.1</v>
       </c>
       <c r="F30" t="n">
-        <v>40.29</v>
+        <v>172.38</v>
       </c>
       <c r="G30" t="n">
-        <v>17386615</v>
+        <v>253542</v>
       </c>
       <c r="H30" t="n">
-        <v>27652053</v>
+        <v>215296</v>
       </c>
       <c r="I30" t="n">
-        <v>44.75</v>
+        <v>176.5</v>
       </c>
       <c r="J30" t="n">
-        <v>37.45</v>
+        <v>168.5</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,116 +3900,116 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1337515</v>
+        <v>149000</v>
       </c>
       <c r="M30" t="n">
-        <v>14595424</v>
+        <v>118979</v>
       </c>
       <c r="N30" t="n">
-        <v>18051673</v>
+        <v>180064</v>
       </c>
       <c r="O30" t="n">
-        <v>68742480</v>
+        <v>203745</v>
       </c>
       <c r="P30" t="n">
-        <v>1218184</v>
+        <v>149000</v>
       </c>
       <c r="Q30" t="n">
-        <v>13702965</v>
+        <v>121025</v>
       </c>
       <c r="R30" t="n">
-        <v>18247222</v>
+        <v>180110</v>
       </c>
       <c r="S30" t="n">
-        <v>76134911</v>
+        <v>203110</v>
       </c>
       <c r="T30" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>-1134000</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>-4558000</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>124331</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>897459</v>
+        <v>-2046</v>
       </c>
       <c r="Z30" t="n">
-        <v>938451</v>
+        <v>-46</v>
       </c>
       <c r="AA30" t="n">
-        <v>-2834431</v>
+        <v>635</v>
       </c>
       <c r="AB30" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>74.2</v>
+        <v>859</v>
       </c>
       <c r="D31" t="n">
-        <v>74.28</v>
+        <v>843</v>
       </c>
       <c r="E31" t="n">
-        <v>73.04000000000001</v>
+        <v>810.2</v>
       </c>
       <c r="F31" t="n">
-        <v>70.41</v>
+        <v>759.85</v>
       </c>
       <c r="G31" t="n">
-        <v>26575995</v>
+        <v>6258000</v>
       </c>
       <c r="H31" t="n">
-        <v>38350375</v>
+        <v>4776400</v>
       </c>
       <c r="I31" t="n">
-        <v>78.59999999999999</v>
+        <v>929</v>
       </c>
       <c r="J31" t="n">
-        <v>58.1</v>
+        <v>553</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,116 +4017,116 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4210340</v>
+        <v>-615906</v>
       </c>
       <c r="M31" t="n">
-        <v>1375380</v>
+        <v>317162</v>
       </c>
       <c r="N31" t="n">
-        <v>852875</v>
+        <v>1578002</v>
       </c>
       <c r="O31" t="n">
-        <v>6784140</v>
+        <v>1322984</v>
       </c>
       <c r="P31" t="n">
-        <v>3876592</v>
+        <v>-931819</v>
       </c>
       <c r="Q31" t="n">
-        <v>1371933</v>
+        <v>-1205698</v>
       </c>
       <c r="R31" t="n">
-        <v>-342602</v>
+        <v>-97486</v>
       </c>
       <c r="S31" t="n">
-        <v>4302843</v>
+        <v>-269001</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1549000</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1549000</v>
       </c>
       <c r="W31" t="n">
-        <v>-11000</v>
+        <v>1349000</v>
       </c>
       <c r="X31" t="n">
-        <v>333748</v>
+        <v>-41087</v>
       </c>
       <c r="Y31" t="n">
-        <v>3447</v>
+        <v>-26140</v>
       </c>
       <c r="Z31" t="n">
-        <v>1195477</v>
+        <v>126488</v>
       </c>
       <c r="AA31" t="n">
-        <v>2492297</v>
+        <v>242985</v>
       </c>
       <c r="AB31" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5120</v>
+        <v>366</v>
       </c>
       <c r="D32" t="n">
-        <v>5255</v>
+        <v>357</v>
       </c>
       <c r="E32" t="n">
-        <v>4944.5</v>
+        <v>309.8</v>
       </c>
       <c r="F32" t="n">
-        <v>4890.25</v>
+        <v>271.18</v>
       </c>
       <c r="G32" t="n">
-        <v>3687942</v>
+        <v>14415513</v>
       </c>
       <c r="H32" t="n">
-        <v>2607763</v>
+        <v>49947550</v>
       </c>
       <c r="I32" t="n">
-        <v>5635</v>
+        <v>387</v>
       </c>
       <c r="J32" t="n">
-        <v>4300</v>
+        <v>217.5</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,116 +4134,116 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-36426</v>
+        <v>-1423317</v>
       </c>
       <c r="M32" t="n">
-        <v>330831</v>
+        <v>5682114</v>
       </c>
       <c r="N32" t="n">
-        <v>485528</v>
+        <v>9371560</v>
       </c>
       <c r="O32" t="n">
-        <v>1932087</v>
+        <v>3387386</v>
       </c>
       <c r="P32" t="n">
-        <v>-148221</v>
+        <v>-496203</v>
       </c>
       <c r="Q32" t="n">
-        <v>67864</v>
+        <v>7240655</v>
       </c>
       <c r="R32" t="n">
-        <v>314229</v>
+        <v>9811506</v>
       </c>
       <c r="S32" t="n">
-        <v>2085929</v>
+        <v>8084759</v>
       </c>
       <c r="T32" t="n">
-        <v>91082</v>
+        <v>-570594</v>
       </c>
       <c r="U32" t="n">
-        <v>283675</v>
+        <v>-1714782</v>
       </c>
       <c r="V32" t="n">
-        <v>204689</v>
+        <v>-1000376</v>
       </c>
       <c r="W32" t="n">
-        <v>-43363</v>
+        <v>-4914478</v>
       </c>
       <c r="X32" t="n">
-        <v>20713</v>
+        <v>-356520</v>
       </c>
       <c r="Y32" t="n">
-        <v>-20708</v>
+        <v>156241</v>
       </c>
       <c r="Z32" t="n">
-        <v>-33390</v>
+        <v>560430</v>
       </c>
       <c r="AA32" t="n">
-        <v>-110479</v>
+        <v>217105</v>
       </c>
       <c r="AB32" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>71.90000000000001</v>
+        <v>1380</v>
       </c>
       <c r="D33" t="n">
-        <v>72.23999999999999</v>
+        <v>1488</v>
       </c>
       <c r="E33" t="n">
-        <v>69.08</v>
+        <v>1466</v>
       </c>
       <c r="F33" t="n">
-        <v>69.08</v>
+        <v>1401.75</v>
       </c>
       <c r="G33" t="n">
-        <v>78210167</v>
+        <v>21389778</v>
       </c>
       <c r="H33" t="n">
-        <v>181489906</v>
+        <v>14839667</v>
       </c>
       <c r="I33" t="n">
-        <v>81.2</v>
+        <v>1565</v>
       </c>
       <c r="J33" t="n">
-        <v>61.8</v>
+        <v>1195</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,55 +4251,55 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-7646631</v>
+        <v>-769525</v>
       </c>
       <c r="M33" t="n">
-        <v>-16047176</v>
+        <v>-1974477</v>
       </c>
       <c r="N33" t="n">
-        <v>33115701</v>
+        <v>4400784</v>
       </c>
       <c r="O33" t="n">
-        <v>55309856</v>
+        <v>6318632</v>
       </c>
       <c r="P33" t="n">
-        <v>-8313549</v>
+        <v>-821342</v>
       </c>
       <c r="Q33" t="n">
-        <v>-17889466</v>
+        <v>-2404327</v>
       </c>
       <c r="R33" t="n">
-        <v>28430668</v>
+        <v>3439207</v>
       </c>
       <c r="S33" t="n">
-        <v>46507174</v>
+        <v>7261138</v>
       </c>
       <c r="T33" t="n">
-        <v>-4000</v>
+        <v>133000</v>
       </c>
       <c r="U33" t="n">
-        <v>1576000</v>
+        <v>616198</v>
       </c>
       <c r="V33" t="n">
-        <v>2349000</v>
+        <v>1073098</v>
       </c>
       <c r="W33" t="n">
-        <v>2381000</v>
+        <v>-1265676</v>
       </c>
       <c r="X33" t="n">
-        <v>670918</v>
+        <v>-81183</v>
       </c>
       <c r="Y33" t="n">
-        <v>266290</v>
+        <v>-186348</v>
       </c>
       <c r="Z33" t="n">
-        <v>2336033</v>
+        <v>-111521</v>
       </c>
       <c r="AA33" t="n">
-        <v>6421682</v>
+        <v>323170</v>
       </c>
       <c r="AB33" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4323,44 +4323,44 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>36.05</v>
+        <v>1050</v>
       </c>
       <c r="D34" t="n">
-        <v>35.36</v>
+        <v>1059</v>
       </c>
       <c r="E34" t="n">
-        <v>35.05</v>
+        <v>980.1</v>
       </c>
       <c r="F34" t="n">
-        <v>34.91</v>
+        <v>921.1</v>
       </c>
       <c r="G34" t="n">
-        <v>122963731</v>
+        <v>19127603</v>
       </c>
       <c r="H34" t="n">
-        <v>81897844</v>
+        <v>25407511</v>
       </c>
       <c r="I34" t="n">
-        <v>36.7</v>
+        <v>1130</v>
       </c>
       <c r="J34" t="n">
-        <v>33.4</v>
+        <v>776</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,116 +4368,116 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>16457567</v>
+        <v>-709629</v>
       </c>
       <c r="M34" t="n">
-        <v>11483651</v>
+        <v>-1610746</v>
       </c>
       <c r="N34" t="n">
-        <v>-4247964</v>
+        <v>10872395</v>
       </c>
       <c r="O34" t="n">
-        <v>5314718</v>
+        <v>24914490</v>
       </c>
       <c r="P34" t="n">
-        <v>-20469399</v>
+        <v>261132</v>
       </c>
       <c r="Q34" t="n">
-        <v>-71180490</v>
+        <v>-544695</v>
       </c>
       <c r="R34" t="n">
-        <v>-112366470</v>
+        <v>8333371</v>
       </c>
       <c r="S34" t="n">
-        <v>-124696352</v>
+        <v>21412568</v>
       </c>
       <c r="T34" t="n">
-        <v>36156345</v>
+        <v>-917999</v>
       </c>
       <c r="U34" t="n">
-        <v>81328402</v>
+        <v>-674372</v>
       </c>
       <c r="V34" t="n">
-        <v>105198860</v>
+        <v>3265628</v>
       </c>
       <c r="W34" t="n">
-        <v>127993964</v>
+        <v>3968571</v>
       </c>
       <c r="X34" t="n">
-        <v>770621</v>
+        <v>-52762</v>
       </c>
       <c r="Y34" t="n">
-        <v>1335739</v>
+        <v>-391679</v>
       </c>
       <c r="Z34" t="n">
-        <v>2919646</v>
+        <v>-726604</v>
       </c>
       <c r="AA34" t="n">
-        <v>2017106</v>
+        <v>-466649</v>
       </c>
       <c r="AB34" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、接近20日高點、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>436</v>
+        <v>1905</v>
       </c>
       <c r="D35" t="n">
-        <v>447.6</v>
+        <v>1761</v>
       </c>
       <c r="E35" t="n">
-        <v>405.25</v>
+        <v>1733</v>
       </c>
       <c r="F35" t="n">
-        <v>392.2</v>
+        <v>1710.5</v>
       </c>
       <c r="G35" t="n">
-        <v>10858000</v>
+        <v>4954000</v>
       </c>
       <c r="H35" t="n">
-        <v>16704800</v>
+        <v>4262400</v>
       </c>
       <c r="I35" t="n">
-        <v>492.5</v>
+        <v>1950</v>
       </c>
       <c r="J35" t="n">
-        <v>343</v>
+        <v>1310</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,116 +4485,116 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-2759531</v>
+        <v>-327662</v>
       </c>
       <c r="M35" t="n">
-        <v>-1248331</v>
+        <v>321027</v>
       </c>
       <c r="N35" t="n">
-        <v>10551657</v>
+        <v>-349918</v>
       </c>
       <c r="O35" t="n">
-        <v>9369379</v>
+        <v>-1218427</v>
       </c>
       <c r="P35" t="n">
-        <v>-2821709</v>
+        <v>-356590</v>
       </c>
       <c r="Q35" t="n">
-        <v>-647260</v>
+        <v>-349587</v>
       </c>
       <c r="R35" t="n">
-        <v>12234799</v>
+        <v>-969060</v>
       </c>
       <c r="S35" t="n">
-        <v>13596569</v>
+        <v>-1105299</v>
       </c>
       <c r="T35" t="n">
-        <v>-12000</v>
+        <v>23000</v>
       </c>
       <c r="U35" t="n">
-        <v>-330000</v>
+        <v>626500</v>
       </c>
       <c r="V35" t="n">
-        <v>-1959000</v>
+        <v>583740</v>
       </c>
       <c r="W35" t="n">
-        <v>-5111631</v>
+        <v>-48093</v>
       </c>
       <c r="X35" t="n">
-        <v>74178</v>
+        <v>5928</v>
       </c>
       <c r="Y35" t="n">
-        <v>-271071</v>
+        <v>44114</v>
       </c>
       <c r="Z35" t="n">
-        <v>275858</v>
+        <v>35402</v>
       </c>
       <c r="AA35" t="n">
-        <v>884441</v>
+        <v>-65035</v>
       </c>
       <c r="AB35" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1065</v>
+        <v>84.7</v>
       </c>
       <c r="D36" t="n">
-        <v>1031</v>
+        <v>81.94</v>
       </c>
       <c r="E36" t="n">
-        <v>1005.2</v>
+        <v>81.59</v>
       </c>
       <c r="F36" t="n">
-        <v>1042.85</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>2917000</v>
+        <v>21521256</v>
       </c>
       <c r="H36" t="n">
-        <v>2821000</v>
+        <v>14725250</v>
       </c>
       <c r="I36" t="n">
-        <v>1210</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>936</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,55 +4602,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>666681</v>
+        <v>525384</v>
       </c>
       <c r="M36" t="n">
-        <v>219838</v>
+        <v>2970153</v>
       </c>
       <c r="N36" t="n">
-        <v>-77355</v>
+        <v>-83282</v>
       </c>
       <c r="O36" t="n">
-        <v>-2233620</v>
+        <v>4290817</v>
       </c>
       <c r="P36" t="n">
-        <v>471617</v>
+        <v>244033</v>
       </c>
       <c r="Q36" t="n">
-        <v>102185</v>
+        <v>2393134</v>
       </c>
       <c r="R36" t="n">
-        <v>-240846</v>
+        <v>-482721</v>
       </c>
       <c r="S36" t="n">
-        <v>-1830072</v>
+        <v>4206293</v>
       </c>
       <c r="T36" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>10000</v>
+        <v>-1000</v>
       </c>
       <c r="V36" t="n">
-        <v>3617</v>
+        <v>-1000</v>
       </c>
       <c r="W36" t="n">
-        <v>-232427</v>
+        <v>-1000</v>
       </c>
       <c r="X36" t="n">
-        <v>193064</v>
+        <v>281351</v>
       </c>
       <c r="Y36" t="n">
-        <v>107653</v>
+        <v>578019</v>
       </c>
       <c r="Z36" t="n">
-        <v>159874</v>
+        <v>400439</v>
       </c>
       <c r="AA36" t="n">
-        <v>-171121</v>
+        <v>85524</v>
       </c>
       <c r="AB36" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -4664,54 +4664,54 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人小幅賣超、投信買外資賣</t>
+          <t>5日法人小幅賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、短線籌碼止穩、5日法人小幅賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、5日法人小幅賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>173</v>
+        <v>18.8</v>
       </c>
       <c r="D37" t="n">
-        <v>172.5</v>
+        <v>15.92</v>
       </c>
       <c r="E37" t="n">
-        <v>173</v>
+        <v>13.53</v>
       </c>
       <c r="F37" t="n">
-        <v>172.3</v>
+        <v>11.68</v>
       </c>
       <c r="G37" t="n">
-        <v>306256</v>
+        <v>58323262</v>
       </c>
       <c r="H37" t="n">
-        <v>207649</v>
+        <v>289146286</v>
       </c>
       <c r="I37" t="n">
-        <v>176.5</v>
+        <v>18.8</v>
       </c>
       <c r="J37" t="n">
-        <v>167</v>
+        <v>8.32</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,28 +4719,28 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-7000</v>
+        <v>-2827260</v>
       </c>
       <c r="M37" t="n">
-        <v>10064</v>
+        <v>9048582</v>
       </c>
       <c r="N37" t="n">
-        <v>-17038</v>
+        <v>-47490059</v>
       </c>
       <c r="O37" t="n">
-        <v>36745</v>
+        <v>8792749</v>
       </c>
       <c r="P37" t="n">
-        <v>-6000</v>
+        <v>-3854960</v>
       </c>
       <c r="Q37" t="n">
-        <v>10110</v>
+        <v>6757407</v>
       </c>
       <c r="R37" t="n">
-        <v>-19890</v>
+        <v>-48015620</v>
       </c>
       <c r="S37" t="n">
-        <v>36110</v>
+        <v>6500797</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -4755,19 +4755,19 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>-1000</v>
+        <v>1027700</v>
       </c>
       <c r="Y37" t="n">
-        <v>-46</v>
+        <v>2291175</v>
       </c>
       <c r="Z37" t="n">
-        <v>2852</v>
+        <v>525561</v>
       </c>
       <c r="AA37" t="n">
-        <v>635</v>
+        <v>2291952</v>
       </c>
       <c r="AB37" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -4781,54 +4781,54 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、接近20日高點、接近20日低點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>17.1</v>
+        <v>238.5</v>
       </c>
       <c r="D38" t="n">
-        <v>14.76</v>
+        <v>219.8</v>
       </c>
       <c r="E38" t="n">
-        <v>12.68</v>
+        <v>210</v>
       </c>
       <c r="F38" t="n">
-        <v>11.15</v>
+        <v>195.62</v>
       </c>
       <c r="G38" t="n">
-        <v>289351189</v>
+        <v>19177000</v>
       </c>
       <c r="H38" t="n">
-        <v>286226550</v>
+        <v>13984200</v>
       </c>
       <c r="I38" t="n">
-        <v>17.1</v>
+        <v>249.5</v>
       </c>
       <c r="J38" t="n">
-        <v>8.220000000000001</v>
+        <v>152</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,28 +4836,28 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5284295</v>
+        <v>-1234497</v>
       </c>
       <c r="M38" t="n">
-        <v>-6495197</v>
+        <v>349950</v>
       </c>
       <c r="N38" t="n">
-        <v>-42554506</v>
+        <v>-305693</v>
       </c>
       <c r="O38" t="n">
-        <v>8357597</v>
+        <v>3706687</v>
       </c>
       <c r="P38" t="n">
-        <v>4366136</v>
+        <v>-1242784</v>
       </c>
       <c r="Q38" t="n">
-        <v>-9860996</v>
+        <v>172281</v>
       </c>
       <c r="R38" t="n">
-        <v>-43704960</v>
+        <v>-446989</v>
       </c>
       <c r="S38" t="n">
-        <v>6123515</v>
+        <v>3430365</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -4872,19 +4872,19 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>918159</v>
+        <v>8287</v>
       </c>
       <c r="Y38" t="n">
-        <v>3365799</v>
+        <v>177669</v>
       </c>
       <c r="Z38" t="n">
-        <v>1150454</v>
+        <v>141296</v>
       </c>
       <c r="AA38" t="n">
-        <v>2234082</v>
+        <v>276322</v>
       </c>
       <c r="AB38" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -4898,54 +4898,54 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>5日法人賣超</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>83.2</v>
+        <v>5515</v>
       </c>
       <c r="D39" t="n">
-        <v>81.73999999999999</v>
+        <v>5253</v>
       </c>
       <c r="E39" t="n">
-        <v>81.36</v>
+        <v>5254.5</v>
       </c>
       <c r="F39" t="n">
-        <v>80.97</v>
+        <v>5235</v>
       </c>
       <c r="G39" t="n">
-        <v>20794251</v>
+        <v>2252805</v>
       </c>
       <c r="H39" t="n">
-        <v>12683829</v>
+        <v>2469396</v>
       </c>
       <c r="I39" t="n">
-        <v>85.8</v>
+        <v>5880</v>
       </c>
       <c r="J39" t="n">
-        <v>77.09999999999999</v>
+        <v>4630</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,55 +4953,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3075517</v>
+        <v>-53222</v>
       </c>
       <c r="M39" t="n">
-        <v>1838084</v>
+        <v>656900</v>
       </c>
       <c r="N39" t="n">
-        <v>-1100465</v>
+        <v>77693</v>
       </c>
       <c r="O39" t="n">
-        <v>-433582</v>
+        <v>-83131</v>
       </c>
       <c r="P39" t="n">
-        <v>2692586</v>
+        <v>-133821</v>
       </c>
       <c r="Q39" t="n">
-        <v>1633452</v>
+        <v>683080</v>
       </c>
       <c r="R39" t="n">
-        <v>-1080274</v>
+        <v>588871</v>
       </c>
       <c r="S39" t="n">
-        <v>-143430</v>
+        <v>590076</v>
       </c>
       <c r="T39" t="n">
-        <v>-1000</v>
+        <v>83002</v>
       </c>
       <c r="U39" t="n">
-        <v>-1000</v>
+        <v>66976</v>
       </c>
       <c r="V39" t="n">
-        <v>-1000</v>
+        <v>-260347</v>
       </c>
       <c r="W39" t="n">
-        <v>-1000</v>
+        <v>-552553</v>
       </c>
       <c r="X39" t="n">
-        <v>383931</v>
+        <v>-2403</v>
       </c>
       <c r="Y39" t="n">
-        <v>205632</v>
+        <v>-93156</v>
       </c>
       <c r="Z39" t="n">
-        <v>-19191</v>
+        <v>-250831</v>
       </c>
       <c r="AA39" t="n">
-        <v>-289152</v>
+        <v>-120654</v>
       </c>
       <c r="AB39" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -5015,54 +5015,54 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人小幅買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人小幅買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2382.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>339</v>
+        <v>9.68</v>
       </c>
       <c r="D40" t="n">
-        <v>318.5</v>
+        <v>8.74</v>
       </c>
       <c r="E40" t="n">
-        <v>309.65</v>
+        <v>7.52</v>
       </c>
       <c r="F40" t="n">
-        <v>321.55</v>
+        <v>6.63</v>
       </c>
       <c r="G40" t="n">
-        <v>87792646</v>
+        <v>192788160</v>
       </c>
       <c r="H40" t="n">
-        <v>53491202</v>
+        <v>184651629</v>
       </c>
       <c r="I40" t="n">
-        <v>352.5</v>
+        <v>9.68</v>
       </c>
       <c r="J40" t="n">
-        <v>288.5</v>
+        <v>5.55</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5070,55 +5070,55 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>18426643</v>
+        <v>17102138</v>
       </c>
       <c r="M40" t="n">
-        <v>4857962</v>
+        <v>-10102801</v>
       </c>
       <c r="N40" t="n">
-        <v>-7418190</v>
+        <v>-1903688</v>
       </c>
       <c r="O40" t="n">
-        <v>-11242885</v>
+        <v>32520599</v>
       </c>
       <c r="P40" t="n">
-        <v>1857292</v>
+        <v>16867220</v>
       </c>
       <c r="Q40" t="n">
-        <v>-37240811</v>
+        <v>-10204580</v>
       </c>
       <c r="R40" t="n">
-        <v>-73071969</v>
+        <v>395471</v>
       </c>
       <c r="S40" t="n">
-        <v>-93637825</v>
+        <v>26845071</v>
       </c>
       <c r="T40" t="n">
-        <v>15430000</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>40595562</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>63535404</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>81935830</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1139351</v>
+        <v>234918</v>
       </c>
       <c r="Y40" t="n">
-        <v>1503211</v>
+        <v>101779</v>
       </c>
       <c r="Z40" t="n">
-        <v>2118375</v>
+        <v>-2299159</v>
       </c>
       <c r="AA40" t="n">
-        <v>459110</v>
+        <v>5675528</v>
       </c>
       <c r="AB40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -5132,54 +5132,54 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、成交量放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6213.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>268.5</v>
+        <v>5070</v>
       </c>
       <c r="D41" t="n">
-        <v>269.5</v>
+        <v>5168</v>
       </c>
       <c r="E41" t="n">
-        <v>257.8</v>
+        <v>4997</v>
       </c>
       <c r="F41" t="n">
-        <v>270.23</v>
+        <v>4906</v>
       </c>
       <c r="G41" t="n">
-        <v>20471464</v>
+        <v>2273627</v>
       </c>
       <c r="H41" t="n">
-        <v>21957355</v>
+        <v>2702229</v>
       </c>
       <c r="I41" t="n">
-        <v>322</v>
+        <v>5635</v>
       </c>
       <c r="J41" t="n">
-        <v>230</v>
+        <v>4300</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5187,116 +5187,116 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3812763</v>
+        <v>40320</v>
       </c>
       <c r="M41" t="n">
-        <v>1123097</v>
+        <v>-122468</v>
       </c>
       <c r="N41" t="n">
-        <v>347639</v>
+        <v>166030</v>
       </c>
       <c r="O41" t="n">
-        <v>527185</v>
+        <v>1613933</v>
       </c>
       <c r="P41" t="n">
-        <v>3517937</v>
+        <v>718402</v>
       </c>
       <c r="Q41" t="n">
-        <v>926109</v>
+        <v>433901</v>
       </c>
       <c r="R41" t="n">
-        <v>-793608</v>
+        <v>716299</v>
       </c>
       <c r="S41" t="n">
-        <v>153796</v>
+        <v>2524668</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>-654000</v>
       </c>
       <c r="U41" t="n">
-        <v>-71000</v>
+        <v>-514223</v>
       </c>
       <c r="V41" t="n">
-        <v>-238000</v>
+        <v>-438311</v>
       </c>
       <c r="W41" t="n">
-        <v>-291000</v>
+        <v>-713363</v>
       </c>
       <c r="X41" t="n">
-        <v>294826</v>
+        <v>-24082</v>
       </c>
       <c r="Y41" t="n">
-        <v>267988</v>
+        <v>-42146</v>
       </c>
       <c r="Z41" t="n">
-        <v>1379247</v>
+        <v>-111958</v>
       </c>
       <c r="AA41" t="n">
-        <v>664389</v>
+        <v>-197372</v>
       </c>
       <c r="AB41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步賣超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2430</v>
+        <v>56.1</v>
       </c>
       <c r="D42" t="n">
-        <v>2529</v>
+        <v>49.88</v>
       </c>
       <c r="E42" t="n">
-        <v>2483.5</v>
+        <v>45.82</v>
       </c>
       <c r="F42" t="n">
-        <v>2499.25</v>
+        <v>39.41</v>
       </c>
       <c r="G42" t="n">
-        <v>6396739</v>
+        <v>478118322</v>
       </c>
       <c r="H42" t="n">
-        <v>4345204</v>
+        <v>1093754873</v>
       </c>
       <c r="I42" t="n">
-        <v>2695</v>
+        <v>56.1</v>
       </c>
       <c r="J42" t="n">
-        <v>2305</v>
+        <v>25.15</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5304,116 +5304,116 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>128711</v>
+        <v>85817793</v>
       </c>
       <c r="M42" t="n">
-        <v>-730234</v>
+        <v>-59168312</v>
       </c>
       <c r="N42" t="n">
-        <v>247300</v>
+        <v>-246655070</v>
       </c>
       <c r="O42" t="n">
-        <v>-292221</v>
+        <v>-172216579</v>
       </c>
       <c r="P42" t="n">
-        <v>601853</v>
+        <v>80703305</v>
       </c>
       <c r="Q42" t="n">
-        <v>-16438</v>
+        <v>-45385303</v>
       </c>
       <c r="R42" t="n">
-        <v>617257</v>
+        <v>-216619387</v>
       </c>
       <c r="S42" t="n">
-        <v>85631</v>
+        <v>-142650779</v>
       </c>
       <c r="T42" t="n">
-        <v>-457677</v>
+        <v>5100000</v>
       </c>
       <c r="U42" t="n">
-        <v>-581267</v>
+        <v>5217221</v>
       </c>
       <c r="V42" t="n">
-        <v>-290072</v>
+        <v>-3025475</v>
       </c>
       <c r="W42" t="n">
-        <v>-96630</v>
+        <v>-2020364</v>
       </c>
       <c r="X42" t="n">
-        <v>-15465</v>
+        <v>14488</v>
       </c>
       <c r="Y42" t="n">
-        <v>-132529</v>
+        <v>-19000230</v>
       </c>
       <c r="Z42" t="n">
-        <v>-79885</v>
+        <v>-27010208</v>
       </c>
       <c r="AA42" t="n">
-        <v>-281222</v>
+        <v>-27545436</v>
       </c>
       <c r="AB42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>144.5</v>
+        <v>211</v>
       </c>
       <c r="D43" t="n">
-        <v>137.1</v>
+        <v>207.4</v>
       </c>
       <c r="E43" t="n">
-        <v>124.75</v>
+        <v>205.25</v>
       </c>
       <c r="F43" t="n">
-        <v>110.34</v>
+        <v>197.47</v>
       </c>
       <c r="G43" t="n">
-        <v>366515715</v>
+        <v>11475001</v>
       </c>
       <c r="H43" t="n">
-        <v>339579178</v>
+        <v>15722114</v>
       </c>
       <c r="I43" t="n">
-        <v>151</v>
+        <v>231</v>
       </c>
       <c r="J43" t="n">
-        <v>79.40000000000001</v>
+        <v>169</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5421,55 +5421,55 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-56076862</v>
+        <v>638592</v>
       </c>
       <c r="M43" t="n">
-        <v>-86242883</v>
+        <v>805083</v>
       </c>
       <c r="N43" t="n">
-        <v>-875000</v>
+        <v>-4178927</v>
       </c>
       <c r="O43" t="n">
-        <v>-79666636</v>
+        <v>2818703</v>
       </c>
       <c r="P43" t="n">
-        <v>-28218031</v>
+        <v>238712</v>
       </c>
       <c r="Q43" t="n">
-        <v>-6628877</v>
+        <v>306561</v>
       </c>
       <c r="R43" t="n">
-        <v>113761499</v>
+        <v>-3806044</v>
       </c>
       <c r="S43" t="n">
-        <v>14781667</v>
+        <v>1881767</v>
       </c>
       <c r="T43" t="n">
-        <v>-28689967</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>-82184801</v>
+        <v>2000</v>
       </c>
       <c r="V43" t="n">
-        <v>-123282822</v>
+        <v>2000</v>
       </c>
       <c r="W43" t="n">
-        <v>-99898432</v>
+        <v>-55316</v>
       </c>
       <c r="X43" t="n">
-        <v>831136</v>
+        <v>399880</v>
       </c>
       <c r="Y43" t="n">
-        <v>2570795</v>
+        <v>496522</v>
       </c>
       <c r="Z43" t="n">
-        <v>8646323</v>
+        <v>-374883</v>
       </c>
       <c r="AA43" t="n">
-        <v>5450129</v>
+        <v>992252</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -5483,54 +5483,54 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>51</v>
+        <v>790</v>
       </c>
       <c r="D44" t="n">
-        <v>48.48</v>
+        <v>726.4</v>
       </c>
       <c r="E44" t="n">
-        <v>44.08</v>
+        <v>654.1</v>
       </c>
       <c r="F44" t="n">
-        <v>37.84</v>
+        <v>531.88</v>
       </c>
       <c r="G44" t="n">
-        <v>897327645</v>
+        <v>32143661</v>
       </c>
       <c r="H44" t="n">
-        <v>1011819780</v>
+        <v>28104227</v>
       </c>
       <c r="I44" t="n">
-        <v>52.2</v>
+        <v>811</v>
       </c>
       <c r="J44" t="n">
-        <v>24.05</v>
+        <v>331</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5538,55 +5538,55 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>165040996</v>
+        <v>2783607</v>
       </c>
       <c r="M44" t="n">
-        <v>-112547359</v>
+        <v>-2766212</v>
       </c>
       <c r="N44" t="n">
-        <v>-335137590</v>
+        <v>-7325603</v>
       </c>
       <c r="O44" t="n">
-        <v>-278268834</v>
+        <v>2033666</v>
       </c>
       <c r="P44" t="n">
-        <v>163249451</v>
+        <v>2259367</v>
       </c>
       <c r="Q44" t="n">
-        <v>-94432896</v>
+        <v>-4591005</v>
       </c>
       <c r="R44" t="n">
-        <v>-301356148</v>
+        <v>-11733299</v>
       </c>
       <c r="S44" t="n">
-        <v>-249862200</v>
+        <v>-24723912</v>
       </c>
       <c r="T44" t="n">
-        <v>7444</v>
+        <v>-13000</v>
       </c>
       <c r="U44" t="n">
-        <v>-5412779</v>
+        <v>291532</v>
       </c>
       <c r="V44" t="n">
-        <v>-8125475</v>
+        <v>456740</v>
       </c>
       <c r="W44" t="n">
-        <v>-7077264</v>
+        <v>21227740</v>
       </c>
       <c r="X44" t="n">
-        <v>1784101</v>
+        <v>537240</v>
       </c>
       <c r="Y44" t="n">
-        <v>-12701684</v>
+        <v>1533261</v>
       </c>
       <c r="Z44" t="n">
-        <v>-25655967</v>
+        <v>3950956</v>
       </c>
       <c r="AA44" t="n">
-        <v>-21329370</v>
+        <v>5529838</v>
       </c>
       <c r="AB44" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -5600,54 +5600,54 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>23</v>
+        <v>144.5</v>
       </c>
       <c r="D45" t="n">
-        <v>22.48</v>
+        <v>137.1</v>
       </c>
       <c r="E45" t="n">
-        <v>21.2</v>
+        <v>124.75</v>
       </c>
       <c r="F45" t="n">
-        <v>19.97</v>
+        <v>110.34</v>
       </c>
       <c r="G45" t="n">
-        <v>481574851</v>
+        <v>366515715</v>
       </c>
       <c r="H45" t="n">
-        <v>497424018</v>
+        <v>339579178</v>
       </c>
       <c r="I45" t="n">
-        <v>25.8</v>
+        <v>151</v>
       </c>
       <c r="J45" t="n">
-        <v>16.6</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5655,55 +5655,55 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>69476213</v>
+        <v>-17686627</v>
       </c>
       <c r="M45" t="n">
-        <v>-20831523</v>
+        <v>-105850437</v>
       </c>
       <c r="N45" t="n">
-        <v>-171352805</v>
+        <v>-51398250</v>
       </c>
       <c r="O45" t="n">
-        <v>9685753</v>
+        <v>-72620473</v>
       </c>
       <c r="P45" t="n">
-        <v>66341339</v>
+        <v>20426659</v>
       </c>
       <c r="Q45" t="n">
-        <v>-22820955</v>
+        <v>-7732185</v>
       </c>
       <c r="R45" t="n">
-        <v>-171088607</v>
+        <v>85668280</v>
       </c>
       <c r="S45" t="n">
-        <v>5694712</v>
+        <v>81129521</v>
       </c>
       <c r="T45" t="n">
-        <v>9000</v>
+        <v>-38025561</v>
       </c>
       <c r="U45" t="n">
-        <v>90252</v>
+        <v>-101199533</v>
       </c>
       <c r="V45" t="n">
-        <v>212198</v>
+        <v>-139902383</v>
       </c>
       <c r="W45" t="n">
-        <v>242507</v>
+        <v>-158631125</v>
       </c>
       <c r="X45" t="n">
-        <v>3125874</v>
+        <v>-87725</v>
       </c>
       <c r="Y45" t="n">
-        <v>1899180</v>
+        <v>3081281</v>
       </c>
       <c r="Z45" t="n">
-        <v>-476396</v>
+        <v>2835853</v>
       </c>
       <c r="AA45" t="n">
-        <v>3748534</v>
+        <v>4881131</v>
       </c>
       <c r="AB45" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -5717,54 +5717,54 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1810</v>
+        <v>2510</v>
       </c>
       <c r="D46" t="n">
-        <v>1717</v>
+        <v>2523</v>
       </c>
       <c r="E46" t="n">
-        <v>1729</v>
+        <v>2485</v>
       </c>
       <c r="F46" t="n">
-        <v>1680</v>
+        <v>2499.5</v>
       </c>
       <c r="G46" t="n">
-        <v>5120000</v>
+        <v>3363120</v>
       </c>
       <c r="H46" t="n">
-        <v>4208800</v>
+        <v>4491058</v>
       </c>
       <c r="I46" t="n">
-        <v>1935</v>
+        <v>2695</v>
       </c>
       <c r="J46" t="n">
-        <v>1270</v>
+        <v>2305</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5772,55 +5772,55 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>129935</v>
+        <v>324990</v>
       </c>
       <c r="M46" t="n">
-        <v>-22256</v>
+        <v>-446327</v>
       </c>
       <c r="N46" t="n">
-        <v>-841812</v>
+        <v>291378</v>
       </c>
       <c r="O46" t="n">
-        <v>-2031599</v>
+        <v>296867</v>
       </c>
       <c r="P46" t="n">
-        <v>-260532</v>
+        <v>356765</v>
       </c>
       <c r="Q46" t="n">
-        <v>-612470</v>
+        <v>193259</v>
       </c>
       <c r="R46" t="n">
-        <v>-816964</v>
+        <v>717536</v>
       </c>
       <c r="S46" t="n">
-        <v>-1606644</v>
+        <v>1053276</v>
       </c>
       <c r="T46" t="n">
-        <v>356500</v>
+        <v>33000</v>
       </c>
       <c r="U46" t="n">
-        <v>560740</v>
+        <v>-482677</v>
       </c>
       <c r="V46" t="n">
-        <v>-40877</v>
+        <v>-254072</v>
       </c>
       <c r="W46" t="n">
-        <v>-308710</v>
+        <v>-361630</v>
       </c>
       <c r="X46" t="n">
-        <v>33967</v>
+        <v>-64775</v>
       </c>
       <c r="Y46" t="n">
-        <v>29474</v>
+        <v>-156909</v>
       </c>
       <c r="Z46" t="n">
-        <v>16029</v>
+        <v>-172086</v>
       </c>
       <c r="AA46" t="n">
-        <v>-116245</v>
+        <v>-394779</v>
       </c>
       <c r="AB46" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -5834,54 +5834,54 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>383</v>
+        <v>23.8</v>
       </c>
       <c r="D47" t="n">
-        <v>382.9</v>
+        <v>22.36</v>
       </c>
       <c r="E47" t="n">
-        <v>380.3</v>
+        <v>21.65</v>
       </c>
       <c r="F47" t="n">
-        <v>387.38</v>
+        <v>20.31</v>
       </c>
       <c r="G47" t="n">
-        <v>2025000</v>
+        <v>564845158</v>
       </c>
       <c r="H47" t="n">
-        <v>2763200</v>
+        <v>593932462</v>
       </c>
       <c r="I47" t="n">
-        <v>439</v>
+        <v>25.8</v>
       </c>
       <c r="J47" t="n">
-        <v>353.5</v>
+        <v>17.2</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5889,55 +5889,55 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>417838</v>
+        <v>-112395402</v>
       </c>
       <c r="M47" t="n">
-        <v>-808089</v>
+        <v>-45567724</v>
       </c>
       <c r="N47" t="n">
-        <v>-498298</v>
+        <v>-302696130</v>
       </c>
       <c r="O47" t="n">
-        <v>-602879</v>
+        <v>-109753488</v>
       </c>
       <c r="P47" t="n">
-        <v>403639</v>
+        <v>-110354526</v>
       </c>
       <c r="Q47" t="n">
-        <v>-684818</v>
+        <v>-44853879</v>
       </c>
       <c r="R47" t="n">
-        <v>-343953</v>
+        <v>-299305020</v>
       </c>
       <c r="S47" t="n">
-        <v>-475298</v>
+        <v>-110957767</v>
       </c>
       <c r="T47" t="n">
-        <v>-22000</v>
+        <v>99000</v>
       </c>
       <c r="U47" t="n">
-        <v>-38000</v>
+        <v>193252</v>
       </c>
       <c r="V47" t="n">
-        <v>-38000</v>
+        <v>311198</v>
       </c>
       <c r="W47" t="n">
-        <v>-13000</v>
+        <v>334507</v>
       </c>
       <c r="X47" t="n">
-        <v>36199</v>
+        <v>-2139876</v>
       </c>
       <c r="Y47" t="n">
-        <v>-85271</v>
+        <v>-907097</v>
       </c>
       <c r="Z47" t="n">
-        <v>-116345</v>
+        <v>-3702308</v>
       </c>
       <c r="AA47" t="n">
-        <v>-114581</v>
+        <v>869772</v>
       </c>
       <c r="AB47" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -5951,54 +5951,54 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38.95</v>
+        <v>548</v>
       </c>
       <c r="D48" t="n">
-        <v>38.08</v>
+        <v>524.2</v>
       </c>
       <c r="E48" t="n">
-        <v>33.81</v>
+        <v>498.3</v>
       </c>
       <c r="F48" t="n">
-        <v>31.16</v>
+        <v>456.85</v>
       </c>
       <c r="G48" t="n">
-        <v>102606028</v>
+        <v>12673360</v>
       </c>
       <c r="H48" t="n">
-        <v>141383468</v>
+        <v>25979568</v>
       </c>
       <c r="I48" t="n">
-        <v>41.05</v>
+        <v>568</v>
       </c>
       <c r="J48" t="n">
-        <v>26.65</v>
+        <v>372</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6006,55 +6006,55 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-6910077</v>
+        <v>278726</v>
       </c>
       <c r="M48" t="n">
-        <v>-38867066</v>
+        <v>-1703916</v>
       </c>
       <c r="N48" t="n">
-        <v>-330703</v>
+        <v>-3261558</v>
       </c>
       <c r="O48" t="n">
-        <v>70129318</v>
+        <v>10240061</v>
       </c>
       <c r="P48" t="n">
-        <v>-6951441</v>
+        <v>1967821</v>
       </c>
       <c r="Q48" t="n">
-        <v>-37390805</v>
+        <v>3439317</v>
       </c>
       <c r="R48" t="n">
-        <v>4656960</v>
+        <v>3959418</v>
       </c>
       <c r="S48" t="n">
-        <v>83481179</v>
+        <v>-441163</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>-1331000</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>-4785592</v>
       </c>
       <c r="V48" t="n">
-        <v>-5544000</v>
+        <v>-6851592</v>
       </c>
       <c r="W48" t="n">
-        <v>-17754000</v>
+        <v>10969976</v>
       </c>
       <c r="X48" t="n">
-        <v>41364</v>
+        <v>-358095</v>
       </c>
       <c r="Y48" t="n">
-        <v>-1476261</v>
+        <v>-357641</v>
       </c>
       <c r="Z48" t="n">
-        <v>556337</v>
+        <v>-369384</v>
       </c>
       <c r="AA48" t="n">
-        <v>4402139</v>
+        <v>-288752</v>
       </c>
       <c r="AB48" t="n">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -6073,49 +6073,49 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2002.TW</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>19.1</v>
+        <v>39.4</v>
       </c>
       <c r="D49" t="n">
-        <v>19.3</v>
+        <v>39.03</v>
       </c>
       <c r="E49" t="n">
-        <v>18.73</v>
+        <v>39.15</v>
       </c>
       <c r="F49" t="n">
-        <v>18.64</v>
+        <v>39.7</v>
       </c>
       <c r="G49" t="n">
-        <v>79358213</v>
+        <v>143898</v>
       </c>
       <c r="H49" t="n">
-        <v>150683540</v>
+        <v>157896</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>42.45</v>
       </c>
       <c r="J49" t="n">
-        <v>18.05</v>
+        <v>38.5</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6123,52 +6123,52 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2360364</v>
+        <v>41000</v>
       </c>
       <c r="M49" t="n">
-        <v>-41161627</v>
+        <v>-47024</v>
       </c>
       <c r="N49" t="n">
-        <v>-36694284</v>
+        <v>-69572</v>
       </c>
       <c r="O49" t="n">
-        <v>-80349749</v>
+        <v>-172104</v>
       </c>
       <c r="P49" t="n">
-        <v>2193070</v>
+        <v>42000</v>
       </c>
       <c r="Q49" t="n">
-        <v>-38809547</v>
+        <v>-43024</v>
       </c>
       <c r="R49" t="n">
-        <v>-38351405</v>
+        <v>-66001</v>
       </c>
       <c r="S49" t="n">
-        <v>-83656663</v>
+        <v>-168001</v>
       </c>
       <c r="T49" t="n">
-        <v>27525</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>6525</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>16525</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1070525</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>139769</v>
+        <v>-1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>-2358605</v>
+        <v>-4000</v>
       </c>
       <c r="Z49" t="n">
-        <v>1640596</v>
+        <v>-3571</v>
       </c>
       <c r="AA49" t="n">
-        <v>2236389</v>
+        <v>-4103</v>
       </c>
       <c r="AB49" t="n">
         <v>-25</v>
@@ -6185,54 +6185,54 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人小幅賣超</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>284.5</v>
+        <v>33.75</v>
       </c>
       <c r="D50" t="n">
-        <v>281.7</v>
+        <v>33.01</v>
       </c>
       <c r="E50" t="n">
-        <v>271.45</v>
+        <v>34.1</v>
       </c>
       <c r="F50" t="n">
-        <v>261.52</v>
+        <v>36.06</v>
       </c>
       <c r="G50" t="n">
-        <v>84156366</v>
+        <v>12317380</v>
       </c>
       <c r="H50" t="n">
-        <v>93692827</v>
+        <v>10046723</v>
       </c>
       <c r="I50" t="n">
-        <v>305.5</v>
+        <v>44.05</v>
       </c>
       <c r="J50" t="n">
-        <v>233.5</v>
+        <v>31.1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6240,55 +6240,55 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>28384602</v>
+        <v>401986</v>
       </c>
       <c r="M50" t="n">
-        <v>-21588663</v>
+        <v>-968923</v>
       </c>
       <c r="N50" t="n">
-        <v>-27955055</v>
+        <v>-1382569</v>
       </c>
       <c r="O50" t="n">
-        <v>23437616</v>
+        <v>-9625536</v>
       </c>
       <c r="P50" t="n">
-        <v>28289321</v>
+        <v>403001</v>
       </c>
       <c r="Q50" t="n">
-        <v>-11423041</v>
+        <v>-710013</v>
       </c>
       <c r="R50" t="n">
-        <v>-15045877</v>
+        <v>-1258658</v>
       </c>
       <c r="S50" t="n">
-        <v>30133661</v>
+        <v>-9492626</v>
       </c>
       <c r="T50" t="n">
-        <v>-387000</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>-7289000</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>-9830000</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>-4343000</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>482281</v>
+        <v>-1015</v>
       </c>
       <c r="Y50" t="n">
-        <v>-2876622</v>
+        <v>-258910</v>
       </c>
       <c r="Z50" t="n">
-        <v>-3079178</v>
+        <v>-123911</v>
       </c>
       <c r="AA50" t="n">
-        <v>-2353045</v>
+        <v>-132910</v>
       </c>
       <c r="AB50" t="n">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -6302,54 +6302,54 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8.800000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="D51" t="n">
-        <v>8.289999999999999</v>
+        <v>86.42</v>
       </c>
       <c r="E51" t="n">
-        <v>7.12</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>6.44</v>
+        <v>71.8</v>
       </c>
       <c r="G51" t="n">
-        <v>120114525</v>
+        <v>48207223</v>
       </c>
       <c r="H51" t="n">
-        <v>150006859</v>
+        <v>44364436</v>
       </c>
       <c r="I51" t="n">
-        <v>9.25</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>5.55</v>
+        <v>58.1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6357,28 +6357,28 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-8225970</v>
+        <v>-1055982</v>
       </c>
       <c r="M51" t="n">
-        <v>-21697710</v>
+        <v>-12178704</v>
       </c>
       <c r="N51" t="n">
-        <v>-13271904</v>
+        <v>-7168837</v>
       </c>
       <c r="O51" t="n">
-        <v>15244774</v>
+        <v>2700112</v>
       </c>
       <c r="P51" t="n">
-        <v>-8995000</v>
+        <v>-1636146</v>
       </c>
       <c r="Q51" t="n">
-        <v>-16819749</v>
+        <v>-11349452</v>
       </c>
       <c r="R51" t="n">
-        <v>-16143749</v>
+        <v>-6189868</v>
       </c>
       <c r="S51" t="n">
-        <v>9898851</v>
+        <v>1485814</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -6393,19 +6393,19 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>769030</v>
+        <v>580164</v>
       </c>
       <c r="Y51" t="n">
-        <v>-4877961</v>
+        <v>-829252</v>
       </c>
       <c r="Z51" t="n">
-        <v>2871845</v>
+        <v>-978969</v>
       </c>
       <c r="AA51" t="n">
-        <v>5345923</v>
+        <v>1214298</v>
       </c>
       <c r="AB51" t="n">
-        <v>-35</v>
+        <v>-25</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6429,44 +6429,44 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>86.3</v>
+        <v>282</v>
       </c>
       <c r="D52" t="n">
-        <v>84.42</v>
+        <v>278.4</v>
       </c>
       <c r="E52" t="n">
-        <v>78.90000000000001</v>
+        <v>273.75</v>
       </c>
       <c r="F52" t="n">
-        <v>70.40000000000001</v>
+        <v>262.2</v>
       </c>
       <c r="G52" t="n">
-        <v>41007388</v>
+        <v>72392478</v>
       </c>
       <c r="H52" t="n">
-        <v>41397085</v>
+        <v>88077285</v>
       </c>
       <c r="I52" t="n">
-        <v>93</v>
+        <v>305.5</v>
       </c>
       <c r="J52" t="n">
-        <v>58.1</v>
+        <v>233.5</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6474,55 +6474,55 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-6462430</v>
+        <v>-13602165</v>
       </c>
       <c r="M52" t="n">
-        <v>-11504398</v>
+        <v>-24542154</v>
       </c>
       <c r="N52" t="n">
-        <v>-6893169</v>
+        <v>-52766993</v>
       </c>
       <c r="O52" t="n">
-        <v>4060977</v>
+        <v>-6377479</v>
       </c>
       <c r="P52" t="n">
-        <v>-6057541</v>
+        <v>-13708813</v>
       </c>
       <c r="Q52" t="n">
-        <v>-9875925</v>
+        <v>-19162159</v>
       </c>
       <c r="R52" t="n">
-        <v>-5376500</v>
+        <v>-38360704</v>
       </c>
       <c r="S52" t="n">
-        <v>2454433</v>
+        <v>3177875</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>-3363000</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>-10645000</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>-6615000</v>
       </c>
       <c r="X52" t="n">
-        <v>-404889</v>
+        <v>81648</v>
       </c>
       <c r="Y52" t="n">
-        <v>-1628473</v>
+        <v>-2016995</v>
       </c>
       <c r="Z52" t="n">
-        <v>-1516669</v>
+        <v>-3761289</v>
       </c>
       <c r="AA52" t="n">
-        <v>1606544</v>
+        <v>-2940354</v>
       </c>
       <c r="AB52" t="n">
-        <v>-35</v>
+        <v>-30</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -6541,49 +6541,49 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>7769.TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>738</v>
+        <v>7515</v>
       </c>
       <c r="D53" t="n">
-        <v>706.6</v>
+        <v>7835</v>
       </c>
       <c r="E53" t="n">
-        <v>625.2</v>
+        <v>7580.5</v>
       </c>
       <c r="F53" t="n">
-        <v>509.5</v>
+        <v>7027.25</v>
       </c>
       <c r="G53" t="n">
-        <v>28926802</v>
+        <v>1264343</v>
       </c>
       <c r="H53" t="n">
-        <v>35208144</v>
+        <v>1056621</v>
       </c>
       <c r="I53" t="n">
-        <v>784</v>
+        <v>8465</v>
       </c>
       <c r="J53" t="n">
-        <v>314</v>
+        <v>5370</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6591,55 +6591,55 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-4621281</v>
+        <v>-372998</v>
       </c>
       <c r="M53" t="n">
-        <v>-7685090</v>
+        <v>-43384</v>
       </c>
       <c r="N53" t="n">
-        <v>-7877682</v>
+        <v>-157277</v>
       </c>
       <c r="O53" t="n">
-        <v>352104</v>
+        <v>-130635</v>
       </c>
       <c r="P53" t="n">
-        <v>-5437960</v>
+        <v>-409313</v>
       </c>
       <c r="Q53" t="n">
-        <v>-10240633</v>
+        <v>-624960</v>
       </c>
       <c r="R53" t="n">
-        <v>-14919628</v>
+        <v>-695082</v>
       </c>
       <c r="S53" t="n">
-        <v>-31600414</v>
+        <v>-519645</v>
       </c>
       <c r="T53" t="n">
-        <v>278110</v>
+        <v>37000</v>
       </c>
       <c r="U53" t="n">
-        <v>345532</v>
+        <v>590504</v>
       </c>
       <c r="V53" t="n">
-        <v>3427740</v>
+        <v>541853</v>
       </c>
       <c r="W53" t="n">
-        <v>28089740</v>
+        <v>401853</v>
       </c>
       <c r="X53" t="n">
-        <v>538569</v>
+        <v>-685</v>
       </c>
       <c r="Y53" t="n">
-        <v>2210011</v>
+        <v>-8928</v>
       </c>
       <c r="Z53" t="n">
-        <v>3614206</v>
+        <v>-4048</v>
       </c>
       <c r="AA53" t="n">
-        <v>3862778</v>
+        <v>-12843</v>
       </c>
       <c r="AB53" t="n">
-        <v>-35</v>
+        <v>-30</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -6653,54 +6653,54 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4310</v>
+        <v>57.2</v>
       </c>
       <c r="D54" t="n">
-        <v>4374</v>
+        <v>56.52</v>
       </c>
       <c r="E54" t="n">
-        <v>3906.5</v>
+        <v>54.54</v>
       </c>
       <c r="F54" t="n">
-        <v>3665.5</v>
+        <v>52.29</v>
       </c>
       <c r="G54" t="n">
-        <v>23109791</v>
+        <v>11246181</v>
       </c>
       <c r="H54" t="n">
-        <v>16392169</v>
+        <v>12250047</v>
       </c>
       <c r="I54" t="n">
-        <v>4690</v>
+        <v>61.4</v>
       </c>
       <c r="J54" t="n">
-        <v>2870</v>
+        <v>45.45</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -6708,55 +6708,55 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-3475601</v>
+        <v>-3130536</v>
       </c>
       <c r="M54" t="n">
-        <v>-3182081</v>
+        <v>-3121889</v>
       </c>
       <c r="N54" t="n">
-        <v>-4172313</v>
+        <v>-2012275</v>
       </c>
       <c r="O54" t="n">
-        <v>-8316461</v>
+        <v>12234349</v>
       </c>
       <c r="P54" t="n">
-        <v>-2324807</v>
+        <v>-3219650</v>
       </c>
       <c r="Q54" t="n">
-        <v>-183403</v>
+        <v>-3438638</v>
       </c>
       <c r="R54" t="n">
-        <v>9386</v>
+        <v>-2331789</v>
       </c>
       <c r="S54" t="n">
-        <v>-5245958</v>
+        <v>11018660</v>
       </c>
       <c r="T54" t="n">
-        <v>-1020510</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>-2923799</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>-4483231</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>-3986411</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>-130284</v>
+        <v>89114</v>
       </c>
       <c r="Y54" t="n">
-        <v>-74879</v>
+        <v>316749</v>
       </c>
       <c r="Z54" t="n">
-        <v>301532</v>
+        <v>319514</v>
       </c>
       <c r="AA54" t="n">
-        <v>915908</v>
+        <v>1215689</v>
       </c>
       <c r="AB54" t="n">
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -6770,54 +6770,54 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>233</v>
+        <v>530</v>
       </c>
       <c r="D55" t="n">
-        <v>262.3</v>
+        <v>541.4</v>
       </c>
       <c r="E55" t="n">
-        <v>253.5</v>
+        <v>516.7</v>
       </c>
       <c r="F55" t="n">
-        <v>245.8</v>
+        <v>507.02</v>
       </c>
       <c r="G55" t="n">
-        <v>3160000</v>
+        <v>23733000</v>
       </c>
       <c r="H55" t="n">
-        <v>3905800</v>
+        <v>36085800</v>
       </c>
       <c r="I55" t="n">
-        <v>312.5</v>
+        <v>588</v>
       </c>
       <c r="J55" t="n">
-        <v>220</v>
+        <v>436</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-692891</v>
+        <v>600244</v>
       </c>
       <c r="M55" t="n">
-        <v>-2049758</v>
+        <v>-5119788</v>
       </c>
       <c r="N55" t="n">
-        <v>-2651177</v>
+        <v>-4575742</v>
       </c>
       <c r="O55" t="n">
-        <v>-2133865</v>
+        <v>-193549</v>
       </c>
       <c r="P55" t="n">
-        <v>-680878</v>
+        <v>516617</v>
       </c>
       <c r="Q55" t="n">
-        <v>-1994325</v>
+        <v>-3090648</v>
       </c>
       <c r="R55" t="n">
-        <v>-2544572</v>
+        <v>-2909949</v>
       </c>
       <c r="S55" t="n">
-        <v>-1885020</v>
+        <v>-4937545</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>-26441</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>-1574325</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>-1210766</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>3170501</v>
       </c>
       <c r="X55" t="n">
-        <v>-12013</v>
+        <v>110068</v>
       </c>
       <c r="Y55" t="n">
-        <v>-55433</v>
+        <v>-454815</v>
       </c>
       <c r="Z55" t="n">
-        <v>-106605</v>
+        <v>-455027</v>
       </c>
       <c r="AA55" t="n">
-        <v>-248845</v>
+        <v>1573495</v>
       </c>
       <c r="AB55" t="n">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -6892,49 +6892,49 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>611</v>
+        <v>19.1</v>
       </c>
       <c r="D56" t="n">
-        <v>621.6</v>
+        <v>19.13</v>
       </c>
       <c r="E56" t="n">
-        <v>563.7</v>
+        <v>18.82</v>
       </c>
       <c r="F56" t="n">
-        <v>549.85</v>
+        <v>18.67</v>
       </c>
       <c r="G56" t="n">
-        <v>43968378</v>
+        <v>66981679</v>
       </c>
       <c r="H56" t="n">
-        <v>35056581</v>
+        <v>122093397</v>
       </c>
       <c r="I56" t="n">
-        <v>669</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>465</v>
+        <v>18.05</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -6942,55 +6942,55 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-13838044</v>
+        <v>-6821957</v>
       </c>
       <c r="M56" t="n">
-        <v>-15671425</v>
+        <v>-19778248</v>
       </c>
       <c r="N56" t="n">
-        <v>-19564058</v>
+        <v>-73161846</v>
       </c>
       <c r="O56" t="n">
-        <v>-23073180</v>
+        <v>-80580628</v>
       </c>
       <c r="P56" t="n">
-        <v>-10101577</v>
+        <v>-7595418</v>
       </c>
       <c r="Q56" t="n">
-        <v>-11629233</v>
+        <v>-19948956</v>
       </c>
       <c r="R56" t="n">
-        <v>-16515209</v>
+        <v>-71816977</v>
       </c>
       <c r="S56" t="n">
-        <v>-21778065</v>
+        <v>-84800855</v>
       </c>
       <c r="T56" t="n">
-        <v>-3776094</v>
+        <v>5000</v>
       </c>
       <c r="U56" t="n">
-        <v>-4048842</v>
+        <v>-8475</v>
       </c>
       <c r="V56" t="n">
-        <v>-2960648</v>
+        <v>21525</v>
       </c>
       <c r="W56" t="n">
-        <v>-767268</v>
+        <v>1075525</v>
       </c>
       <c r="X56" t="n">
-        <v>39627</v>
+        <v>768461</v>
       </c>
       <c r="Y56" t="n">
-        <v>6650</v>
+        <v>179183</v>
       </c>
       <c r="Z56" t="n">
-        <v>-88201</v>
+        <v>-1366394</v>
       </c>
       <c r="AA56" t="n">
-        <v>-527847</v>
+        <v>3144702</v>
       </c>
       <c r="AB56" t="n">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -7004,54 +7004,54 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>515</v>
+        <v>40.6</v>
       </c>
       <c r="D57" t="n">
-        <v>520.4</v>
+        <v>38.92</v>
       </c>
       <c r="E57" t="n">
-        <v>482.35</v>
+        <v>35.03</v>
       </c>
       <c r="F57" t="n">
-        <v>451.07</v>
+        <v>31.79</v>
       </c>
       <c r="G57" t="n">
-        <v>11454003</v>
+        <v>120797558</v>
       </c>
       <c r="H57" t="n">
-        <v>32912192</v>
+        <v>152210323</v>
       </c>
       <c r="I57" t="n">
-        <v>568</v>
+        <v>42</v>
       </c>
       <c r="J57" t="n">
-        <v>372</v>
+        <v>26.65</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7059,55 +7059,55 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>857140</v>
+        <v>-5247740</v>
       </c>
       <c r="M57" t="n">
-        <v>-7205641</v>
+        <v>-18740272</v>
       </c>
       <c r="N57" t="n">
-        <v>-9256603</v>
+        <v>-15756947</v>
       </c>
       <c r="O57" t="n">
-        <v>8993341</v>
+        <v>61167815</v>
       </c>
       <c r="P57" t="n">
-        <v>1231521</v>
+        <v>-6375791</v>
       </c>
       <c r="Q57" t="n">
-        <v>-1238676</v>
+        <v>-20229217</v>
       </c>
       <c r="R57" t="n">
-        <v>-4688336</v>
+        <v>-13311206</v>
       </c>
       <c r="S57" t="n">
-        <v>-1033644</v>
+        <v>73546299</v>
       </c>
       <c r="T57" t="n">
-        <v>-836465</v>
+        <v>593000</v>
       </c>
       <c r="U57" t="n">
-        <v>-5792592</v>
+        <v>593000</v>
       </c>
       <c r="V57" t="n">
-        <v>-3969592</v>
+        <v>-2179000</v>
       </c>
       <c r="W57" t="n">
-        <v>9612976</v>
+        <v>-17161000</v>
       </c>
       <c r="X57" t="n">
-        <v>462084</v>
+        <v>535051</v>
       </c>
       <c r="Y57" t="n">
-        <v>-174373</v>
+        <v>895945</v>
       </c>
       <c r="Z57" t="n">
-        <v>-598675</v>
+        <v>-266741</v>
       </c>
       <c r="AA57" t="n">
-        <v>414009</v>
+        <v>4782516</v>
       </c>
       <c r="AB57" t="n">
-        <v>-70</v>
+        <v>-55</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -7121,54 +7121,54 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>207</v>
+        <v>1060</v>
       </c>
       <c r="D58" t="n">
-        <v>208.9</v>
+        <v>1092</v>
       </c>
       <c r="E58" t="n">
-        <v>203.45</v>
+        <v>1071.2</v>
       </c>
       <c r="F58" t="n">
-        <v>195.38</v>
+        <v>1058.6</v>
       </c>
       <c r="G58" t="n">
-        <v>13700926</v>
+        <v>2924000</v>
       </c>
       <c r="H58" t="n">
-        <v>19496790</v>
+        <v>4078000</v>
       </c>
       <c r="I58" t="n">
-        <v>231</v>
+        <v>1300</v>
       </c>
       <c r="J58" t="n">
-        <v>168.5</v>
+        <v>865</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7176,55 +7176,55 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-2706458</v>
+        <v>-420978</v>
       </c>
       <c r="M58" t="n">
-        <v>-1348885</v>
+        <v>-1582664</v>
       </c>
       <c r="N58" t="n">
-        <v>-5894259</v>
+        <v>-3053059</v>
       </c>
       <c r="O58" t="n">
-        <v>3016910</v>
+        <v>-4332525</v>
       </c>
       <c r="P58" t="n">
-        <v>-2716140</v>
+        <v>60766</v>
       </c>
       <c r="Q58" t="n">
-        <v>-1301206</v>
+        <v>-94694</v>
       </c>
       <c r="R58" t="n">
-        <v>-5499049</v>
+        <v>-285732</v>
       </c>
       <c r="S58" t="n">
-        <v>2092357</v>
+        <v>-2406108</v>
       </c>
       <c r="T58" t="n">
-        <v>2000</v>
+        <v>-478000</v>
       </c>
       <c r="U58" t="n">
-        <v>2000</v>
+        <v>-1475050</v>
       </c>
       <c r="V58" t="n">
-        <v>2000</v>
+        <v>-2737050</v>
       </c>
       <c r="W58" t="n">
-        <v>-55316</v>
+        <v>-1947050</v>
       </c>
       <c r="X58" t="n">
-        <v>7682</v>
+        <v>-3744</v>
       </c>
       <c r="Y58" t="n">
-        <v>-49679</v>
+        <v>-12920</v>
       </c>
       <c r="Z58" t="n">
-        <v>-397210</v>
+        <v>-30277</v>
       </c>
       <c r="AA58" t="n">
-        <v>979869</v>
+        <v>20633</v>
       </c>
       <c r="AB58" t="n">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -7243,49 +7243,49 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38.8</v>
+        <v>601</v>
       </c>
       <c r="D59" t="n">
-        <v>38.99</v>
+        <v>618.4</v>
       </c>
       <c r="E59" t="n">
-        <v>39.16</v>
+        <v>572.8</v>
       </c>
       <c r="F59" t="n">
-        <v>39.74</v>
+        <v>553.65</v>
       </c>
       <c r="G59" t="n">
-        <v>137768</v>
+        <v>25834856</v>
       </c>
       <c r="H59" t="n">
-        <v>157686</v>
+        <v>34901676</v>
       </c>
       <c r="I59" t="n">
-        <v>42.45</v>
+        <v>669</v>
       </c>
       <c r="J59" t="n">
-        <v>38.5</v>
+        <v>465</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -7293,55 +7293,55 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>33000</v>
+        <v>-2269811</v>
       </c>
       <c r="M59" t="n">
-        <v>-118572</v>
+        <v>-18147118</v>
       </c>
       <c r="N59" t="n">
-        <v>-134572</v>
+        <v>-19887300</v>
       </c>
       <c r="O59" t="n">
-        <v>-185104</v>
+        <v>-19512205</v>
       </c>
       <c r="P59" t="n">
-        <v>33000</v>
+        <v>2284150</v>
       </c>
       <c r="Q59" t="n">
-        <v>-116001</v>
+        <v>-10178887</v>
       </c>
       <c r="R59" t="n">
-        <v>-133001</v>
+        <v>-10813423</v>
       </c>
       <c r="S59" t="n">
-        <v>-182001</v>
+        <v>-13545404</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>-4656953</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>-8031843</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>-8748601</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>-5686221</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>102992</v>
       </c>
       <c r="Y59" t="n">
-        <v>-2571</v>
+        <v>63612</v>
       </c>
       <c r="Z59" t="n">
-        <v>-1571</v>
+        <v>-325276</v>
       </c>
       <c r="AA59" t="n">
-        <v>-3103</v>
+        <v>-280580</v>
       </c>
       <c r="AB59" t="n">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -7355,54 +7355,54 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>5日法人賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2615</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>2847</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>2728</v>
+        <v>73</v>
       </c>
       <c r="F60" t="n">
-        <v>2752.25</v>
+        <v>70.81</v>
       </c>
       <c r="G60" t="n">
-        <v>2144000</v>
+        <v>21901665</v>
       </c>
       <c r="H60" t="n">
-        <v>2878200</v>
+        <v>28640442</v>
       </c>
       <c r="I60" t="n">
-        <v>3215</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>2460</v>
+        <v>64.7</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -7410,55 +7410,55 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-529511</v>
+        <v>-3353884</v>
       </c>
       <c r="M60" t="n">
-        <v>-1519482</v>
+        <v>-1927633</v>
       </c>
       <c r="N60" t="n">
-        <v>-720570</v>
+        <v>-5620421</v>
       </c>
       <c r="O60" t="n">
-        <v>-274473</v>
+        <v>-5122068</v>
       </c>
       <c r="P60" t="n">
-        <v>-279830</v>
+        <v>-3281171</v>
       </c>
       <c r="Q60" t="n">
-        <v>-1153921</v>
+        <v>-1786681</v>
       </c>
       <c r="R60" t="n">
-        <v>-971555</v>
+        <v>-5657186</v>
       </c>
       <c r="S60" t="n">
-        <v>-523379</v>
+        <v>-7066444</v>
       </c>
       <c r="T60" t="n">
-        <v>-234000</v>
+        <v>-3000</v>
       </c>
       <c r="U60" t="n">
-        <v>-302900</v>
+        <v>-3000</v>
       </c>
       <c r="V60" t="n">
-        <v>241578</v>
+        <v>-3000</v>
       </c>
       <c r="W60" t="n">
-        <v>309464</v>
+        <v>-14000</v>
       </c>
       <c r="X60" t="n">
-        <v>-15681</v>
+        <v>-69713</v>
       </c>
       <c r="Y60" t="n">
-        <v>-62661</v>
+        <v>-137952</v>
       </c>
       <c r="Z60" t="n">
-        <v>9407</v>
+        <v>39765</v>
       </c>
       <c r="AA60" t="n">
-        <v>-60558</v>
+        <v>1958376</v>
       </c>
       <c r="AB60" t="n">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -7472,54 +7472,54 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1030</v>
+        <v>227.5</v>
       </c>
       <c r="D61" t="n">
-        <v>1122</v>
+        <v>249.1</v>
       </c>
       <c r="E61" t="n">
-        <v>1055.2</v>
+        <v>252.75</v>
       </c>
       <c r="F61" t="n">
-        <v>1068.35</v>
+        <v>245.43</v>
       </c>
       <c r="G61" t="n">
-        <v>3335000</v>
+        <v>2817000</v>
       </c>
       <c r="H61" t="n">
-        <v>4981400</v>
+        <v>4227000</v>
       </c>
       <c r="I61" t="n">
-        <v>1300</v>
+        <v>312.5</v>
       </c>
       <c r="J61" t="n">
-        <v>865</v>
+        <v>220</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -7527,55 +7527,55 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-758454</v>
+        <v>-27233</v>
       </c>
       <c r="M61" t="n">
-        <v>-2632081</v>
+        <v>-1281879</v>
       </c>
       <c r="N61" t="n">
-        <v>-3568191</v>
+        <v>-2076991</v>
       </c>
       <c r="O61" t="n">
-        <v>-4121517</v>
+        <v>-1310509</v>
       </c>
       <c r="P61" t="n">
-        <v>-163282</v>
+        <v>2802</v>
       </c>
       <c r="Q61" t="n">
-        <v>-346498</v>
+        <v>-1219573</v>
       </c>
       <c r="R61" t="n">
-        <v>-1599895</v>
+        <v>-1991523</v>
       </c>
       <c r="S61" t="n">
-        <v>-2472060</v>
+        <v>-1080981</v>
       </c>
       <c r="T61" t="n">
-        <v>-593000</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>-2259050</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>-1818050</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>-1656050</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>-2172</v>
+        <v>-30035</v>
       </c>
       <c r="Y61" t="n">
-        <v>-26533</v>
+        <v>-62306</v>
       </c>
       <c r="Z61" t="n">
-        <v>-150246</v>
+        <v>-85468</v>
       </c>
       <c r="AA61" t="n">
-        <v>6593</v>
+        <v>-229528</v>
       </c>
       <c r="AB61" t="n">
-        <v>-95</v>
+        <v>-85</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -7589,54 +7589,54 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>848</v>
+        <v>436</v>
       </c>
       <c r="D62" t="n">
-        <v>881.8</v>
+        <v>449.5</v>
       </c>
       <c r="E62" t="n">
-        <v>863.3</v>
+        <v>412.1</v>
       </c>
       <c r="F62" t="n">
-        <v>883.9</v>
+        <v>396.05</v>
       </c>
       <c r="G62" t="n">
-        <v>17926232</v>
+        <v>7911000</v>
       </c>
       <c r="H62" t="n">
-        <v>23312290</v>
+        <v>13922400</v>
       </c>
       <c r="I62" t="n">
-        <v>1035</v>
+        <v>492.5</v>
       </c>
       <c r="J62" t="n">
-        <v>765</v>
+        <v>343</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7644,52 +7644,52 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-2448813</v>
+        <v>-683330</v>
       </c>
       <c r="M62" t="n">
-        <v>-8778876</v>
+        <v>-4127623</v>
       </c>
       <c r="N62" t="n">
-        <v>-13138409</v>
+        <v>-1931661</v>
       </c>
       <c r="O62" t="n">
-        <v>-8950196</v>
+        <v>4419564</v>
       </c>
       <c r="P62" t="n">
-        <v>43377</v>
+        <v>-556866</v>
       </c>
       <c r="Q62" t="n">
-        <v>-3411404</v>
+        <v>-3731197</v>
       </c>
       <c r="R62" t="n">
-        <v>-4691237</v>
+        <v>-1204126</v>
       </c>
       <c r="S62" t="n">
-        <v>-3009711</v>
+        <v>9111328</v>
       </c>
       <c r="T62" t="n">
-        <v>-2413000</v>
+        <v>-75000</v>
       </c>
       <c r="U62" t="n">
-        <v>-5192000</v>
+        <v>-331000</v>
       </c>
       <c r="V62" t="n">
-        <v>-8133000</v>
+        <v>-405000</v>
       </c>
       <c r="W62" t="n">
-        <v>-5299000</v>
+        <v>-5156631</v>
       </c>
       <c r="X62" t="n">
-        <v>-79190</v>
+        <v>-51464</v>
       </c>
       <c r="Y62" t="n">
-        <v>-175472</v>
+        <v>-65426</v>
       </c>
       <c r="Z62" t="n">
-        <v>-314172</v>
+        <v>-322535</v>
       </c>
       <c r="AA62" t="n">
-        <v>-641485</v>
+        <v>464867</v>
       </c>
       <c r="AB62" t="n">
         <v>-95</v>
@@ -7706,54 +7706,54 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>527</v>
+        <v>380</v>
       </c>
       <c r="D63" t="n">
-        <v>544</v>
+        <v>381.9</v>
       </c>
       <c r="E63" t="n">
-        <v>508.75</v>
+        <v>380.2</v>
       </c>
       <c r="F63" t="n">
-        <v>506.73</v>
+        <v>386.75</v>
       </c>
       <c r="G63" t="n">
-        <v>26012000</v>
+        <v>1813000</v>
       </c>
       <c r="H63" t="n">
-        <v>39810000</v>
+        <v>2419400</v>
       </c>
       <c r="I63" t="n">
-        <v>588</v>
+        <v>439</v>
       </c>
       <c r="J63" t="n">
-        <v>436</v>
+        <v>353.5</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7761,52 +7761,52 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-4446778</v>
+        <v>-305157</v>
       </c>
       <c r="M63" t="n">
-        <v>-5175986</v>
+        <v>-406036</v>
       </c>
       <c r="N63" t="n">
-        <v>-1641710</v>
+        <v>-1113246</v>
       </c>
       <c r="O63" t="n">
-        <v>3127410</v>
+        <v>-768189</v>
       </c>
       <c r="P63" t="n">
-        <v>-2818118</v>
+        <v>-320812</v>
       </c>
       <c r="Q63" t="n">
-        <v>-3426566</v>
+        <v>-337057</v>
       </c>
       <c r="R63" t="n">
-        <v>-2679038</v>
+        <v>-1005630</v>
       </c>
       <c r="S63" t="n">
-        <v>-1518645</v>
+        <v>-667187</v>
       </c>
       <c r="T63" t="n">
-        <v>-1490721</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>-1184325</v>
+        <v>-22000</v>
       </c>
       <c r="V63" t="n">
-        <v>-351326</v>
+        <v>-38000</v>
       </c>
       <c r="W63" t="n">
-        <v>2432941</v>
+        <v>-13000</v>
       </c>
       <c r="X63" t="n">
-        <v>-137939</v>
+        <v>15655</v>
       </c>
       <c r="Y63" t="n">
-        <v>-565095</v>
+        <v>-46979</v>
       </c>
       <c r="Z63" t="n">
-        <v>1388654</v>
+        <v>-69616</v>
       </c>
       <c r="AA63" t="n">
-        <v>2213114</v>
+        <v>-88002</v>
       </c>
       <c r="AB63" t="n">
         <v>-95</v>
@@ -7823,54 +7823,54 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>31.95</v>
+        <v>2685</v>
       </c>
       <c r="D64" t="n">
-        <v>33.46</v>
+        <v>2799</v>
       </c>
       <c r="E64" t="n">
-        <v>34.07</v>
+        <v>2725.5</v>
       </c>
       <c r="F64" t="n">
-        <v>36.33</v>
+        <v>2749.25</v>
       </c>
       <c r="G64" t="n">
-        <v>7490299</v>
+        <v>1639000</v>
       </c>
       <c r="H64" t="n">
-        <v>10923227</v>
+        <v>2676600</v>
       </c>
       <c r="I64" t="n">
-        <v>44.05</v>
+        <v>3215</v>
       </c>
       <c r="J64" t="n">
-        <v>31.1</v>
+        <v>2460</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -7878,55 +7878,55 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-830875</v>
+        <v>-152795</v>
       </c>
       <c r="M64" t="n">
-        <v>-1788679</v>
+        <v>-1422809</v>
       </c>
       <c r="N64" t="n">
-        <v>-3454506</v>
+        <v>-1672277</v>
       </c>
       <c r="O64" t="n">
-        <v>-7227522</v>
+        <v>-1018978</v>
       </c>
       <c r="P64" t="n">
-        <v>-673979</v>
+        <v>10864</v>
       </c>
       <c r="Q64" t="n">
-        <v>-1532782</v>
+        <v>-835828</v>
       </c>
       <c r="R64" t="n">
-        <v>-3330610</v>
+        <v>-1143057</v>
       </c>
       <c r="S64" t="n">
-        <v>-7097627</v>
+        <v>-952988</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>-161400</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>-531500</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>-464300</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>-60415</v>
       </c>
       <c r="X64" t="n">
-        <v>-156896</v>
+        <v>-2259</v>
       </c>
       <c r="Y64" t="n">
-        <v>-255897</v>
+        <v>-55481</v>
       </c>
       <c r="Z64" t="n">
-        <v>-123896</v>
+        <v>-64920</v>
       </c>
       <c r="AA64" t="n">
-        <v>-129895</v>
+        <v>-5575</v>
       </c>
       <c r="AB64" t="n">
-        <v>-110</v>
+        <v>-95</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,37 +586,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>387</v>
+        <v>191</v>
       </c>
       <c r="D2" t="n">
-        <v>352.6</v>
+        <v>162.6</v>
       </c>
       <c r="E2" t="n">
-        <v>334.55</v>
+        <v>152.5</v>
       </c>
       <c r="F2" t="n">
-        <v>324.75</v>
+        <v>146.32</v>
       </c>
       <c r="G2" t="n">
-        <v>38916483</v>
+        <v>279090000</v>
       </c>
       <c r="H2" t="n">
-        <v>21917377</v>
+        <v>113431112</v>
       </c>
       <c r="I2" t="n">
-        <v>396</v>
+        <v>191</v>
       </c>
       <c r="J2" t="n">
-        <v>275.5</v>
+        <v>132</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -624,55 +624,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>200379</v>
+        <v>25906440</v>
       </c>
       <c r="M2" t="n">
-        <v>10186160</v>
+        <v>49814393</v>
       </c>
       <c r="N2" t="n">
-        <v>11973950</v>
+        <v>52471124</v>
       </c>
       <c r="O2" t="n">
-        <v>4905137</v>
+        <v>110525706</v>
       </c>
       <c r="P2" t="n">
-        <v>-4462178</v>
+        <v>24686613</v>
       </c>
       <c r="Q2" t="n">
-        <v>1853493</v>
+        <v>44469682</v>
       </c>
       <c r="R2" t="n">
-        <v>3409112</v>
+        <v>46006122</v>
       </c>
       <c r="S2" t="n">
-        <v>-3558687</v>
+        <v>99485352</v>
       </c>
       <c r="T2" t="n">
-        <v>4171000</v>
+        <v>1488000</v>
       </c>
       <c r="U2" t="n">
-        <v>7080181</v>
+        <v>3052568</v>
       </c>
       <c r="V2" t="n">
-        <v>7312181</v>
+        <v>4610098</v>
       </c>
       <c r="W2" t="n">
-        <v>8119102</v>
+        <v>5383814</v>
       </c>
       <c r="X2" t="n">
-        <v>491557</v>
+        <v>-268173</v>
       </c>
       <c r="Y2" t="n">
-        <v>1252486</v>
+        <v>2292143</v>
       </c>
       <c r="Z2" t="n">
-        <v>1252657</v>
+        <v>1854904</v>
       </c>
       <c r="AA2" t="n">
-        <v>344722</v>
+        <v>5656540</v>
       </c>
       <c r="AB2" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>51.9</v>
+        <v>52.8</v>
       </c>
       <c r="D3" t="n">
-        <v>49.78</v>
+        <v>50.67</v>
       </c>
       <c r="E3" t="n">
-        <v>47.71</v>
+        <v>48.59</v>
       </c>
       <c r="F3" t="n">
-        <v>46.19</v>
+        <v>46.7</v>
       </c>
       <c r="G3" t="n">
-        <v>58919831</v>
+        <v>67755000</v>
       </c>
       <c r="H3" t="n">
-        <v>58169853</v>
+        <v>61845972</v>
       </c>
       <c r="I3" t="n">
-        <v>51.9</v>
+        <v>52.8</v>
       </c>
       <c r="J3" t="n">
-        <v>42.15</v>
+        <v>43.16</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -820,93 +820,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54.9</v>
+        <v>419.5</v>
       </c>
       <c r="D4" t="n">
-        <v>52.9</v>
+        <v>356.8</v>
       </c>
       <c r="E4" t="n">
-        <v>52.02</v>
+        <v>326.2</v>
       </c>
       <c r="F4" t="n">
-        <v>50.84</v>
+        <v>314</v>
       </c>
       <c r="G4" t="n">
-        <v>51690436</v>
+        <v>168804000</v>
       </c>
       <c r="H4" t="n">
-        <v>29079875</v>
+        <v>174354298</v>
       </c>
       <c r="I4" t="n">
-        <v>55.7</v>
+        <v>419.5</v>
       </c>
       <c r="J4" t="n">
-        <v>47.35</v>
+        <v>260</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>14945901</v>
+        <v>29714770</v>
       </c>
       <c r="M4" t="n">
-        <v>25862263</v>
+        <v>117706143</v>
       </c>
       <c r="N4" t="n">
-        <v>42395795</v>
+        <v>126499130</v>
       </c>
       <c r="O4" t="n">
-        <v>68637305</v>
+        <v>78771719</v>
       </c>
       <c r="P4" t="n">
-        <v>20142573</v>
+        <v>27016483</v>
       </c>
       <c r="Q4" t="n">
-        <v>30966686</v>
+        <v>108666843</v>
       </c>
       <c r="R4" t="n">
-        <v>48820355</v>
+        <v>121744282</v>
       </c>
       <c r="S4" t="n">
-        <v>74717732</v>
+        <v>97442183</v>
       </c>
       <c r="T4" t="n">
-        <v>-6005850</v>
+        <v>2178001</v>
       </c>
       <c r="U4" t="n">
-        <v>-6343542</v>
+        <v>7782331</v>
       </c>
       <c r="V4" t="n">
-        <v>-7845092</v>
+        <v>4720606</v>
       </c>
       <c r="W4" t="n">
-        <v>-7903058</v>
+        <v>-13348559</v>
       </c>
       <c r="X4" t="n">
-        <v>809178</v>
+        <v>520286</v>
       </c>
       <c r="Y4" t="n">
-        <v>1239119</v>
+        <v>1256969</v>
       </c>
       <c r="Z4" t="n">
-        <v>1420532</v>
+        <v>34242</v>
       </c>
       <c r="AA4" t="n">
-        <v>1822631</v>
+        <v>-5321905</v>
       </c>
       <c r="AB4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,54 +920,54 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>174</v>
+        <v>184.5</v>
       </c>
       <c r="D5" t="n">
-        <v>153.6</v>
+        <v>161.9</v>
       </c>
       <c r="E5" t="n">
-        <v>146.65</v>
+        <v>143.35</v>
       </c>
       <c r="F5" t="n">
-        <v>143.88</v>
+        <v>131.78</v>
       </c>
       <c r="G5" t="n">
-        <v>94609409</v>
+        <v>267752000</v>
       </c>
       <c r="H5" t="n">
-        <v>64772226</v>
+        <v>322881785</v>
       </c>
       <c r="I5" t="n">
-        <v>174</v>
+        <v>184.5</v>
       </c>
       <c r="J5" t="n">
-        <v>132</v>
+        <v>103.5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -975,55 +975,55 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>25906440</v>
+        <v>146059</v>
       </c>
       <c r="M5" t="n">
-        <v>49814393</v>
+        <v>23904373</v>
       </c>
       <c r="N5" t="n">
-        <v>52471124</v>
+        <v>103702296</v>
       </c>
       <c r="O5" t="n">
-        <v>110525706</v>
+        <v>165431261</v>
       </c>
       <c r="P5" t="n">
-        <v>24686613</v>
+        <v>-6767657</v>
       </c>
       <c r="Q5" t="n">
-        <v>44469682</v>
+        <v>-4918288</v>
       </c>
       <c r="R5" t="n">
-        <v>46006122</v>
+        <v>56728248</v>
       </c>
       <c r="S5" t="n">
-        <v>99485352</v>
+        <v>112812507</v>
       </c>
       <c r="T5" t="n">
-        <v>1488000</v>
+        <v>5952147</v>
       </c>
       <c r="U5" t="n">
-        <v>3052568</v>
+        <v>28060924</v>
       </c>
       <c r="V5" t="n">
-        <v>4610098</v>
+        <v>43096531</v>
       </c>
       <c r="W5" t="n">
-        <v>5383814</v>
+        <v>52047258</v>
       </c>
       <c r="X5" t="n">
-        <v>-268173</v>
+        <v>961569</v>
       </c>
       <c r="Y5" t="n">
-        <v>2292143</v>
+        <v>761737</v>
       </c>
       <c r="Z5" t="n">
-        <v>1854904</v>
+        <v>3877517</v>
       </c>
       <c r="AA5" t="n">
-        <v>5656540</v>
+        <v>571496</v>
       </c>
       <c r="AB5" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1047,44 +1047,44 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>107.5</v>
+        <v>390.5</v>
       </c>
       <c r="D6" t="n">
-        <v>96.48</v>
+        <v>363.5</v>
       </c>
       <c r="E6" t="n">
-        <v>90.59999999999999</v>
+        <v>343.1</v>
       </c>
       <c r="F6" t="n">
-        <v>89.73</v>
+        <v>330.3</v>
       </c>
       <c r="G6" t="n">
-        <v>111908983</v>
+        <v>25117000</v>
       </c>
       <c r="H6" t="n">
-        <v>115784711</v>
+        <v>24735728</v>
       </c>
       <c r="I6" t="n">
-        <v>107.5</v>
+        <v>396</v>
       </c>
       <c r="J6" t="n">
-        <v>80.40000000000001</v>
+        <v>283</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1092,52 +1092,52 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>15245712</v>
+        <v>200379</v>
       </c>
       <c r="M6" t="n">
-        <v>53204084</v>
+        <v>10186160</v>
       </c>
       <c r="N6" t="n">
-        <v>135527278</v>
+        <v>11973950</v>
       </c>
       <c r="O6" t="n">
-        <v>134335684</v>
+        <v>4905137</v>
       </c>
       <c r="P6" t="n">
-        <v>13945743</v>
+        <v>-4462178</v>
       </c>
       <c r="Q6" t="n">
-        <v>48241698</v>
+        <v>1853493</v>
       </c>
       <c r="R6" t="n">
-        <v>128023662</v>
+        <v>3409112</v>
       </c>
       <c r="S6" t="n">
-        <v>129685447</v>
+        <v>-3558687</v>
       </c>
       <c r="T6" t="n">
-        <v>696000</v>
+        <v>4171000</v>
       </c>
       <c r="U6" t="n">
-        <v>3360457</v>
+        <v>7080181</v>
       </c>
       <c r="V6" t="n">
-        <v>3504189</v>
+        <v>7312181</v>
       </c>
       <c r="W6" t="n">
-        <v>3673289</v>
+        <v>8119102</v>
       </c>
       <c r="X6" t="n">
-        <v>603969</v>
+        <v>491557</v>
       </c>
       <c r="Y6" t="n">
-        <v>1601929</v>
+        <v>1252486</v>
       </c>
       <c r="Z6" t="n">
-        <v>3999427</v>
+        <v>1252657</v>
       </c>
       <c r="AA6" t="n">
-        <v>976948</v>
+        <v>344722</v>
       </c>
       <c r="AB6" t="n">
         <v>150</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1164,97 +1164,97 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>2331.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>381.5</v>
+        <v>25.6</v>
       </c>
       <c r="D7" t="n">
-        <v>333.6</v>
+        <v>22.59</v>
       </c>
       <c r="E7" t="n">
-        <v>311.7</v>
+        <v>21.5</v>
       </c>
       <c r="F7" t="n">
-        <v>305.85</v>
+        <v>20.79</v>
       </c>
       <c r="G7" t="n">
-        <v>129059908</v>
+        <v>36432000</v>
       </c>
       <c r="H7" t="n">
-        <v>171183369</v>
+        <v>12702445</v>
       </c>
       <c r="I7" t="n">
-        <v>381.5</v>
+        <v>26.5</v>
       </c>
       <c r="J7" t="n">
-        <v>242.5</v>
+        <v>18.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>29714770</v>
+        <v>1377969</v>
       </c>
       <c r="M7" t="n">
-        <v>117706143</v>
+        <v>4043082</v>
       </c>
       <c r="N7" t="n">
-        <v>126499130</v>
+        <v>2610639</v>
       </c>
       <c r="O7" t="n">
-        <v>78771719</v>
+        <v>-1385945</v>
       </c>
       <c r="P7" t="n">
-        <v>27016483</v>
+        <v>1064000</v>
       </c>
       <c r="Q7" t="n">
-        <v>108666843</v>
+        <v>3708885</v>
       </c>
       <c r="R7" t="n">
-        <v>121744282</v>
+        <v>2317990</v>
       </c>
       <c r="S7" t="n">
-        <v>97442183</v>
+        <v>-1718010</v>
       </c>
       <c r="T7" t="n">
-        <v>2178001</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>7782331</v>
+        <v>-13000</v>
       </c>
       <c r="V7" t="n">
-        <v>4720606</v>
+        <v>-23000</v>
       </c>
       <c r="W7" t="n">
-        <v>-13348559</v>
+        <v>-94000</v>
       </c>
       <c r="X7" t="n">
-        <v>520286</v>
+        <v>313969</v>
       </c>
       <c r="Y7" t="n">
-        <v>1256969</v>
+        <v>347197</v>
       </c>
       <c r="Z7" t="n">
-        <v>34242</v>
+        <v>315649</v>
       </c>
       <c r="AA7" t="n">
-        <v>-5321905</v>
+        <v>426065</v>
       </c>
       <c r="AB7" t="n">
         <v>150</v>
@@ -1271,110 +1271,110 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>774</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>716.4</v>
+        <v>45.86</v>
       </c>
       <c r="E8" t="n">
-        <v>643.1</v>
+        <v>45.72</v>
       </c>
       <c r="F8" t="n">
-        <v>569.92</v>
+        <v>43.9</v>
       </c>
       <c r="G8" t="n">
-        <v>6218324</v>
+        <v>36966000</v>
       </c>
       <c r="H8" t="n">
-        <v>20571192</v>
+        <v>16015045</v>
       </c>
       <c r="I8" t="n">
-        <v>775</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>445.5</v>
+        <v>38.65</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1303982</v>
+        <v>-248474</v>
       </c>
       <c r="M8" t="n">
-        <v>3071789</v>
+        <v>3362503</v>
       </c>
       <c r="N8" t="n">
-        <v>8648112</v>
+        <v>4230839</v>
       </c>
       <c r="O8" t="n">
-        <v>28251728</v>
+        <v>8730275</v>
       </c>
       <c r="P8" t="n">
-        <v>934957</v>
+        <v>-224389</v>
       </c>
       <c r="Q8" t="n">
-        <v>2591713</v>
+        <v>3328000</v>
       </c>
       <c r="R8" t="n">
-        <v>5260467</v>
+        <v>4484001</v>
       </c>
       <c r="S8" t="n">
-        <v>20174081</v>
+        <v>8296993</v>
       </c>
       <c r="T8" t="n">
-        <v>15191</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>16572</v>
+        <v>-6000</v>
       </c>
       <c r="V8" t="n">
-        <v>3192763</v>
+        <v>-8000</v>
       </c>
       <c r="W8" t="n">
-        <v>7276237</v>
+        <v>-40000</v>
       </c>
       <c r="X8" t="n">
-        <v>353834</v>
+        <v>-24085</v>
       </c>
       <c r="Y8" t="n">
-        <v>463504</v>
+        <v>40503</v>
       </c>
       <c r="Z8" t="n">
-        <v>194882</v>
+        <v>-245162</v>
       </c>
       <c r="AA8" t="n">
-        <v>801410</v>
+        <v>473282</v>
       </c>
       <c r="AB8" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1388,54 +1388,54 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1145</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>1058</v>
+        <v>218.1</v>
       </c>
       <c r="E9" t="n">
-        <v>1021.5</v>
+        <v>215.95</v>
       </c>
       <c r="F9" t="n">
-        <v>1040.6</v>
+        <v>212.05</v>
       </c>
       <c r="G9" t="n">
-        <v>6075000</v>
+        <v>35182000</v>
       </c>
       <c r="H9" t="n">
-        <v>3574000</v>
+        <v>33126359</v>
       </c>
       <c r="I9" t="n">
-        <v>1210</v>
+        <v>231</v>
       </c>
       <c r="J9" t="n">
-        <v>936</v>
+        <v>195.5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,52 +1443,52 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1189926</v>
+        <v>15949739</v>
       </c>
       <c r="M9" t="n">
-        <v>1922078</v>
+        <v>21698905</v>
       </c>
       <c r="N9" t="n">
-        <v>1409764</v>
+        <v>20009420</v>
       </c>
       <c r="O9" t="n">
-        <v>-745756</v>
+        <v>57007750</v>
       </c>
       <c r="P9" t="n">
-        <v>1047554</v>
+        <v>2159299</v>
       </c>
       <c r="Q9" t="n">
-        <v>1654327</v>
+        <v>-16404349</v>
       </c>
       <c r="R9" t="n">
-        <v>1149739</v>
+        <v>-35593846</v>
       </c>
       <c r="S9" t="n">
-        <v>-560167</v>
+        <v>-3428806</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>12843785</v>
       </c>
       <c r="U9" t="n">
-        <v>10000</v>
+        <v>36165345</v>
       </c>
       <c r="V9" t="n">
-        <v>10000</v>
+        <v>52647181</v>
       </c>
       <c r="W9" t="n">
-        <v>-233044</v>
+        <v>55898201</v>
       </c>
       <c r="X9" t="n">
-        <v>142372</v>
+        <v>946655</v>
       </c>
       <c r="Y9" t="n">
-        <v>257751</v>
+        <v>1937909</v>
       </c>
       <c r="Z9" t="n">
-        <v>250025</v>
+        <v>2956085</v>
       </c>
       <c r="AA9" t="n">
-        <v>47455</v>
+        <v>4538355</v>
       </c>
       <c r="AB9" t="n">
         <v>140</v>
@@ -1505,54 +1505,54 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、成交量放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2382.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>372.5</v>
+        <v>1145</v>
       </c>
       <c r="D10" t="n">
-        <v>329.7</v>
+        <v>1058</v>
       </c>
       <c r="E10" t="n">
-        <v>316.9</v>
+        <v>1021.5</v>
       </c>
       <c r="F10" t="n">
-        <v>324.27</v>
+        <v>1040.6</v>
       </c>
       <c r="G10" t="n">
-        <v>76692327</v>
+        <v>6075000</v>
       </c>
       <c r="H10" t="n">
-        <v>59474501</v>
+        <v>3574000</v>
       </c>
       <c r="I10" t="n">
-        <v>372.5</v>
+        <v>1210</v>
       </c>
       <c r="J10" t="n">
-        <v>288.5</v>
+        <v>936</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,52 +1560,52 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4874370</v>
+        <v>1189926</v>
       </c>
       <c r="M10" t="n">
-        <v>18267163</v>
+        <v>1922078</v>
       </c>
       <c r="N10" t="n">
-        <v>6680948</v>
+        <v>1594701</v>
       </c>
       <c r="O10" t="n">
-        <v>2310404</v>
+        <v>-560819</v>
       </c>
       <c r="P10" t="n">
-        <v>-2613127</v>
+        <v>1047554</v>
       </c>
       <c r="Q10" t="n">
-        <v>-18440356</v>
+        <v>1654327</v>
       </c>
       <c r="R10" t="n">
-        <v>-55857239</v>
+        <v>1282771</v>
       </c>
       <c r="S10" t="n">
-        <v>-87301189</v>
+        <v>-427135</v>
       </c>
       <c r="T10" t="n">
-        <v>7281000</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>35323352</v>
+        <v>10000</v>
       </c>
       <c r="V10" t="n">
-        <v>60624404</v>
+        <v>9617</v>
       </c>
       <c r="W10" t="n">
-        <v>89314165</v>
+        <v>-233427</v>
       </c>
       <c r="X10" t="n">
-        <v>206497</v>
+        <v>142372</v>
       </c>
       <c r="Y10" t="n">
-        <v>1384167</v>
+        <v>257751</v>
       </c>
       <c r="Z10" t="n">
-        <v>1913783</v>
+        <v>302313</v>
       </c>
       <c r="AA10" t="n">
-        <v>297428</v>
+        <v>99743</v>
       </c>
       <c r="AB10" t="n">
         <v>140</v>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、黃金交叉、成交量放大</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74.8</v>
+        <v>43.65</v>
       </c>
       <c r="D11" t="n">
-        <v>72.42</v>
+        <v>42.54</v>
       </c>
       <c r="E11" t="n">
-        <v>70.08</v>
+        <v>42.33</v>
       </c>
       <c r="F11" t="n">
-        <v>69.51000000000001</v>
+        <v>40.86</v>
       </c>
       <c r="G11" t="n">
-        <v>180789702</v>
+        <v>33550000</v>
       </c>
       <c r="H11" t="n">
-        <v>180590810</v>
+        <v>25027453</v>
       </c>
       <c r="I11" t="n">
-        <v>81.2</v>
+        <v>44.75</v>
       </c>
       <c r="J11" t="n">
-        <v>61.8</v>
+        <v>37.6</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,52 +1677,52 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36235379</v>
+        <v>9525842</v>
       </c>
       <c r="M11" t="n">
-        <v>18005086</v>
+        <v>12285874</v>
       </c>
       <c r="N11" t="n">
-        <v>24812582</v>
+        <v>15455905</v>
       </c>
       <c r="O11" t="n">
-        <v>100060322</v>
+        <v>72915018</v>
       </c>
       <c r="P11" t="n">
-        <v>35838589</v>
+        <v>2233303</v>
       </c>
       <c r="Q11" t="n">
-        <v>17380149</v>
+        <v>6940623</v>
       </c>
       <c r="R11" t="n">
-        <v>21056648</v>
+        <v>8488390</v>
       </c>
       <c r="S11" t="n">
-        <v>91577139</v>
+        <v>71670898</v>
       </c>
       <c r="T11" t="n">
-        <v>421000</v>
+        <v>5724000</v>
       </c>
       <c r="U11" t="n">
-        <v>1027000</v>
+        <v>5719000</v>
       </c>
       <c r="V11" t="n">
-        <v>2759000</v>
+        <v>5210000</v>
       </c>
       <c r="W11" t="n">
-        <v>2802000</v>
+        <v>1863000</v>
       </c>
       <c r="X11" t="n">
-        <v>-24210</v>
+        <v>1568539</v>
       </c>
       <c r="Y11" t="n">
-        <v>-402063</v>
+        <v>-373749</v>
       </c>
       <c r="Z11" t="n">
-        <v>996934</v>
+        <v>1757515</v>
       </c>
       <c r="AA11" t="n">
-        <v>5681183</v>
+        <v>-618880</v>
       </c>
       <c r="AB11" t="n">
         <v>135</v>
@@ -1756,37 +1756,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43.2</v>
+        <v>31.45</v>
       </c>
       <c r="D12" t="n">
-        <v>42.08</v>
+        <v>30.23</v>
       </c>
       <c r="E12" t="n">
-        <v>41.97</v>
+        <v>29.41</v>
       </c>
       <c r="F12" t="n">
-        <v>40.57</v>
+        <v>28.62</v>
       </c>
       <c r="G12" t="n">
-        <v>28077068</v>
+        <v>9275000</v>
       </c>
       <c r="H12" t="n">
-        <v>25742972</v>
+        <v>7956861</v>
       </c>
       <c r="I12" t="n">
-        <v>44.75</v>
+        <v>32.55</v>
       </c>
       <c r="J12" t="n">
-        <v>37.45</v>
+        <v>26.3</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,52 +1794,52 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9525842</v>
+        <v>4038854</v>
       </c>
       <c r="M12" t="n">
-        <v>12285874</v>
+        <v>3654670</v>
       </c>
       <c r="N12" t="n">
-        <v>15455905</v>
+        <v>2441059</v>
       </c>
       <c r="O12" t="n">
-        <v>72915018</v>
+        <v>5292939</v>
       </c>
       <c r="P12" t="n">
-        <v>2233303</v>
+        <v>3928241</v>
       </c>
       <c r="Q12" t="n">
-        <v>6940623</v>
+        <v>3532684</v>
       </c>
       <c r="R12" t="n">
-        <v>8488390</v>
+        <v>2297050</v>
       </c>
       <c r="S12" t="n">
-        <v>71670898</v>
+        <v>5243514</v>
       </c>
       <c r="T12" t="n">
-        <v>5724000</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5719000</v>
+        <v>8000</v>
       </c>
       <c r="V12" t="n">
-        <v>5210000</v>
+        <v>6000</v>
       </c>
       <c r="W12" t="n">
-        <v>1863000</v>
+        <v>68000</v>
       </c>
       <c r="X12" t="n">
-        <v>1568539</v>
+        <v>110613</v>
       </c>
       <c r="Y12" t="n">
-        <v>-373749</v>
+        <v>113986</v>
       </c>
       <c r="Z12" t="n">
-        <v>1757515</v>
+        <v>138009</v>
       </c>
       <c r="AA12" t="n">
-        <v>-618880</v>
+        <v>-18575</v>
       </c>
       <c r="AB12" t="n">
         <v>135</v>
@@ -1873,37 +1873,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.05</v>
+        <v>112.5</v>
       </c>
       <c r="D13" t="n">
-        <v>21.03</v>
+        <v>100.82</v>
       </c>
       <c r="E13" t="n">
-        <v>19.02</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>17.98</v>
+        <v>90.66</v>
       </c>
       <c r="G13" t="n">
-        <v>8617355</v>
+        <v>150731000</v>
       </c>
       <c r="H13" t="n">
-        <v>36908518</v>
+        <v>125003851</v>
       </c>
       <c r="I13" t="n">
-        <v>25.05</v>
+        <v>118</v>
       </c>
       <c r="J13" t="n">
-        <v>16.55</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>109130</v>
+        <v>15245712</v>
       </c>
       <c r="M13" t="n">
-        <v>4838885</v>
+        <v>53204084</v>
       </c>
       <c r="N13" t="n">
-        <v>6388241</v>
+        <v>135527278</v>
       </c>
       <c r="O13" t="n">
-        <v>23449524</v>
+        <v>134335684</v>
       </c>
       <c r="P13" t="n">
-        <v>-530000</v>
+        <v>13945743</v>
       </c>
       <c r="Q13" t="n">
-        <v>1641838</v>
+        <v>48241698</v>
       </c>
       <c r="R13" t="n">
-        <v>2170673</v>
+        <v>128023662</v>
       </c>
       <c r="S13" t="n">
-        <v>18702025</v>
+        <v>129685447</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>696000</v>
       </c>
       <c r="U13" t="n">
-        <v>-4000</v>
+        <v>3360457</v>
       </c>
       <c r="V13" t="n">
-        <v>-12000</v>
+        <v>3504189</v>
       </c>
       <c r="W13" t="n">
-        <v>486000</v>
+        <v>3673289</v>
       </c>
       <c r="X13" t="n">
-        <v>639130</v>
+        <v>603969</v>
       </c>
       <c r="Y13" t="n">
-        <v>3201047</v>
+        <v>1601929</v>
       </c>
       <c r="Z13" t="n">
-        <v>4229568</v>
+        <v>3999427</v>
       </c>
       <c r="AA13" t="n">
-        <v>4261499</v>
+        <v>976948</v>
       </c>
       <c r="AB13" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -2034,10 +2034,10 @@
         <v>-448244</v>
       </c>
       <c r="N14" t="n">
-        <v>922122</v>
+        <v>1677499</v>
       </c>
       <c r="O14" t="n">
-        <v>10571302</v>
+        <v>11326679</v>
       </c>
       <c r="P14" t="n">
         <v>-93101</v>
@@ -2046,10 +2046,10 @@
         <v>423150</v>
       </c>
       <c r="R14" t="n">
-        <v>1629999</v>
+        <v>2367961</v>
       </c>
       <c r="S14" t="n">
-        <v>10820777</v>
+        <v>11558739</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2058,10 +2058,10 @@
         <v>15800</v>
       </c>
       <c r="V14" t="n">
-        <v>13700</v>
+        <v>12500</v>
       </c>
       <c r="W14" t="n">
-        <v>84500</v>
+        <v>83300</v>
       </c>
       <c r="X14" t="n">
         <v>-432143</v>
@@ -2070,10 +2070,10 @@
         <v>-887194</v>
       </c>
       <c r="Z14" t="n">
-        <v>-721577</v>
+        <v>-702962</v>
       </c>
       <c r="AA14" t="n">
-        <v>-333975</v>
+        <v>-315360</v>
       </c>
       <c r="AB14" t="n">
         <v>130</v>
@@ -2107,37 +2107,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>224</v>
+        <v>27.55</v>
       </c>
       <c r="D15" t="n">
-        <v>214.2</v>
+        <v>23.01</v>
       </c>
       <c r="E15" t="n">
-        <v>212.55</v>
+        <v>20.11</v>
       </c>
       <c r="F15" t="n">
-        <v>210.9</v>
+        <v>18.5</v>
       </c>
       <c r="G15" t="n">
-        <v>38077211</v>
+        <v>25659000</v>
       </c>
       <c r="H15" t="n">
-        <v>31670603</v>
+        <v>38896094</v>
       </c>
       <c r="I15" t="n">
-        <v>225</v>
+        <v>27.55</v>
       </c>
       <c r="J15" t="n">
-        <v>195.5</v>
+        <v>16.6</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,52 +2145,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>15949739</v>
+        <v>109130</v>
       </c>
       <c r="M15" t="n">
-        <v>21698905</v>
+        <v>4838885</v>
       </c>
       <c r="N15" t="n">
-        <v>20009420</v>
+        <v>6388241</v>
       </c>
       <c r="O15" t="n">
-        <v>57007750</v>
+        <v>23449524</v>
       </c>
       <c r="P15" t="n">
-        <v>2159299</v>
+        <v>-530000</v>
       </c>
       <c r="Q15" t="n">
-        <v>-16404349</v>
+        <v>1641838</v>
       </c>
       <c r="R15" t="n">
-        <v>-35593846</v>
+        <v>2170673</v>
       </c>
       <c r="S15" t="n">
-        <v>-3428806</v>
+        <v>18702025</v>
       </c>
       <c r="T15" t="n">
-        <v>12843785</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>36165345</v>
+        <v>-4000</v>
       </c>
       <c r="V15" t="n">
-        <v>52647181</v>
+        <v>-12000</v>
       </c>
       <c r="W15" t="n">
-        <v>55898201</v>
+        <v>486000</v>
       </c>
       <c r="X15" t="n">
-        <v>946655</v>
+        <v>639130</v>
       </c>
       <c r="Y15" t="n">
-        <v>1937909</v>
+        <v>3201047</v>
       </c>
       <c r="Z15" t="n">
-        <v>2956085</v>
+        <v>4229568</v>
       </c>
       <c r="AA15" t="n">
-        <v>4538355</v>
+        <v>4261499</v>
       </c>
       <c r="AB15" t="n">
         <v>130</v>
@@ -2207,17 +2207,17 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -2233,28 +2233,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31.99</v>
+        <v>32.49</v>
       </c>
       <c r="D16" t="n">
-        <v>30.58</v>
+        <v>31.16</v>
       </c>
       <c r="E16" t="n">
-        <v>29.23</v>
+        <v>29.78</v>
       </c>
       <c r="F16" t="n">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="G16" t="n">
-        <v>103435481</v>
+        <v>110270000</v>
       </c>
       <c r="H16" t="n">
-        <v>92135431</v>
+        <v>97337318</v>
       </c>
       <c r="I16" t="n">
-        <v>32.05</v>
+        <v>32.5</v>
       </c>
       <c r="J16" t="n">
-        <v>26.25</v>
+        <v>26.9</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2341,37 +2341,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>950</v>
+        <v>743</v>
       </c>
       <c r="D17" t="n">
-        <v>937.6</v>
+        <v>725.8</v>
       </c>
       <c r="E17" t="n">
-        <v>819.7</v>
+        <v>666.1</v>
       </c>
       <c r="F17" t="n">
-        <v>787.25</v>
+        <v>580.73</v>
       </c>
       <c r="G17" t="n">
-        <v>4452000</v>
+        <v>6058000</v>
       </c>
       <c r="H17" t="n">
-        <v>12667000</v>
+        <v>11696829</v>
       </c>
       <c r="I17" t="n">
-        <v>1040</v>
+        <v>778</v>
       </c>
       <c r="J17" t="n">
-        <v>615</v>
+        <v>445.5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,52 +2379,52 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>798638</v>
+        <v>1303982</v>
       </c>
       <c r="M17" t="n">
-        <v>2696041</v>
+        <v>3071789</v>
       </c>
       <c r="N17" t="n">
-        <v>7992113</v>
+        <v>8648112</v>
       </c>
       <c r="O17" t="n">
-        <v>3381131</v>
+        <v>28251728</v>
       </c>
       <c r="P17" t="n">
-        <v>989046</v>
+        <v>934957</v>
       </c>
       <c r="Q17" t="n">
-        <v>-337021</v>
+        <v>2591713</v>
       </c>
       <c r="R17" t="n">
-        <v>324875</v>
+        <v>5260467</v>
       </c>
       <c r="S17" t="n">
-        <v>-4750182</v>
+        <v>20174081</v>
       </c>
       <c r="T17" t="n">
-        <v>-792857</v>
+        <v>15191</v>
       </c>
       <c r="U17" t="n">
-        <v>2500409</v>
+        <v>16572</v>
       </c>
       <c r="V17" t="n">
-        <v>7160276</v>
+        <v>3192763</v>
       </c>
       <c r="W17" t="n">
-        <v>6585088</v>
+        <v>7276237</v>
       </c>
       <c r="X17" t="n">
-        <v>602449</v>
+        <v>353834</v>
       </c>
       <c r="Y17" t="n">
-        <v>532653</v>
+        <v>463504</v>
       </c>
       <c r="Z17" t="n">
-        <v>506962</v>
+        <v>194882</v>
       </c>
       <c r="AA17" t="n">
-        <v>1546225</v>
+        <v>801410</v>
       </c>
       <c r="AB17" t="n">
         <v>125</v>
@@ -2467,25 +2467,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2785</v>
+        <v>2700</v>
       </c>
       <c r="D18" t="n">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="E18" t="n">
-        <v>2580</v>
+        <v>2611</v>
       </c>
       <c r="F18" t="n">
-        <v>2544</v>
+        <v>2543.75</v>
       </c>
       <c r="G18" t="n">
-        <v>5090031</v>
+        <v>3832000</v>
       </c>
       <c r="H18" t="n">
-        <v>6032552</v>
+        <v>5550967</v>
       </c>
       <c r="I18" t="n">
-        <v>2845</v>
+        <v>2835</v>
       </c>
       <c r="J18" t="n">
         <v>2300</v>
@@ -2575,37 +2575,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>168</v>
+        <v>53.6</v>
       </c>
       <c r="D19" t="n">
-        <v>153.2</v>
+        <v>53.22</v>
       </c>
       <c r="E19" t="n">
-        <v>136.65</v>
+        <v>52.43</v>
       </c>
       <c r="F19" t="n">
-        <v>127.49</v>
+        <v>51.02</v>
       </c>
       <c r="G19" t="n">
-        <v>295190831</v>
+        <v>71610000</v>
       </c>
       <c r="H19" t="n">
-        <v>336552469</v>
+        <v>40419855</v>
       </c>
       <c r="I19" t="n">
-        <v>173.5</v>
+        <v>55.7</v>
       </c>
       <c r="J19" t="n">
-        <v>96.59999999999999</v>
+        <v>47.35</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2613,55 +2613,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>146059</v>
+        <v>14945901</v>
       </c>
       <c r="M19" t="n">
-        <v>23904373</v>
+        <v>25862263</v>
       </c>
       <c r="N19" t="n">
-        <v>103702296</v>
+        <v>42395795</v>
       </c>
       <c r="O19" t="n">
-        <v>165431261</v>
+        <v>68637305</v>
       </c>
       <c r="P19" t="n">
-        <v>-6767657</v>
+        <v>20142573</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4918288</v>
+        <v>30966686</v>
       </c>
       <c r="R19" t="n">
-        <v>56728248</v>
+        <v>48820355</v>
       </c>
       <c r="S19" t="n">
-        <v>112812507</v>
+        <v>74717732</v>
       </c>
       <c r="T19" t="n">
-        <v>5952147</v>
+        <v>-6005850</v>
       </c>
       <c r="U19" t="n">
-        <v>28060924</v>
+        <v>-6343542</v>
       </c>
       <c r="V19" t="n">
-        <v>43096531</v>
+        <v>-7845092</v>
       </c>
       <c r="W19" t="n">
-        <v>52047258</v>
+        <v>-7903058</v>
       </c>
       <c r="X19" t="n">
-        <v>961569</v>
+        <v>809178</v>
       </c>
       <c r="Y19" t="n">
-        <v>761737</v>
+        <v>1239119</v>
       </c>
       <c r="Z19" t="n">
-        <v>3877517</v>
+        <v>1420532</v>
       </c>
       <c r="AA19" t="n">
-        <v>571496</v>
+        <v>1822631</v>
       </c>
       <c r="AB19" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,107 +2675,107 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>2382.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37.7</v>
+        <v>400.5</v>
       </c>
       <c r="D20" t="n">
-        <v>35.81</v>
+        <v>346.5</v>
       </c>
       <c r="E20" t="n">
-        <v>35.41</v>
+        <v>327.95</v>
       </c>
       <c r="F20" t="n">
-        <v>35.11</v>
+        <v>328.25</v>
       </c>
       <c r="G20" t="n">
-        <v>82974354</v>
+        <v>149166000</v>
       </c>
       <c r="H20" t="n">
-        <v>85265386</v>
+        <v>80090604</v>
       </c>
       <c r="I20" t="n">
-        <v>37.85</v>
+        <v>409.5</v>
       </c>
       <c r="J20" t="n">
-        <v>33.4</v>
+        <v>288.5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>13546260</v>
+        <v>4874370</v>
       </c>
       <c r="M20" t="n">
-        <v>43363173</v>
+        <v>18267163</v>
       </c>
       <c r="N20" t="n">
-        <v>16657509</v>
+        <v>6680948</v>
       </c>
       <c r="O20" t="n">
-        <v>21226516</v>
+        <v>2310404</v>
       </c>
       <c r="P20" t="n">
-        <v>-24438582</v>
+        <v>-2613127</v>
       </c>
       <c r="Q20" t="n">
-        <v>-60246419</v>
+        <v>-18440356</v>
       </c>
       <c r="R20" t="n">
-        <v>-119669352</v>
+        <v>-55857239</v>
       </c>
       <c r="S20" t="n">
-        <v>-148193516</v>
+        <v>-87301189</v>
       </c>
       <c r="T20" t="n">
-        <v>37712898</v>
+        <v>7281000</v>
       </c>
       <c r="U20" t="n">
-        <v>102158167</v>
+        <v>35323352</v>
       </c>
       <c r="V20" t="n">
-        <v>133646088</v>
+        <v>60624404</v>
       </c>
       <c r="W20" t="n">
-        <v>166814366</v>
+        <v>89314165</v>
       </c>
       <c r="X20" t="n">
-        <v>271944</v>
+        <v>206497</v>
       </c>
       <c r="Y20" t="n">
-        <v>1451425</v>
+        <v>1384167</v>
       </c>
       <c r="Z20" t="n">
-        <v>2680773</v>
+        <v>1913783</v>
       </c>
       <c r="AA20" t="n">
-        <v>2605666</v>
+        <v>297428</v>
       </c>
       <c r="AB20" t="n">
         <v>120</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2802,44 +2802,44 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6213.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>295</v>
+        <v>37.25</v>
       </c>
       <c r="D21" t="n">
-        <v>275.1</v>
+        <v>36.22</v>
       </c>
       <c r="E21" t="n">
-        <v>262.8</v>
+        <v>35.68</v>
       </c>
       <c r="F21" t="n">
-        <v>270.48</v>
+        <v>35.27</v>
       </c>
       <c r="G21" t="n">
-        <v>31063246</v>
+        <v>84226000</v>
       </c>
       <c r="H21" t="n">
-        <v>25090063</v>
+        <v>88744819</v>
       </c>
       <c r="I21" t="n">
-        <v>322</v>
+        <v>37.85</v>
       </c>
       <c r="J21" t="n">
-        <v>230</v>
+        <v>33.7</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,55 +2847,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>12348068</v>
+        <v>13546260</v>
       </c>
       <c r="M21" t="n">
-        <v>8160032</v>
+        <v>43363173</v>
       </c>
       <c r="N21" t="n">
-        <v>15069872</v>
+        <v>16657509</v>
       </c>
       <c r="O21" t="n">
-        <v>12457873</v>
+        <v>21226516</v>
       </c>
       <c r="P21" t="n">
-        <v>11994537</v>
+        <v>-24438582</v>
       </c>
       <c r="Q21" t="n">
-        <v>7819120</v>
+        <v>-60246419</v>
       </c>
       <c r="R21" t="n">
-        <v>13707371</v>
+        <v>-119669352</v>
       </c>
       <c r="S21" t="n">
-        <v>11456171</v>
+        <v>-148193516</v>
       </c>
       <c r="T21" t="n">
-        <v>-3000</v>
+        <v>37712898</v>
       </c>
       <c r="U21" t="n">
-        <v>-3000</v>
+        <v>102158167</v>
       </c>
       <c r="V21" t="n">
-        <v>-241000</v>
+        <v>133646088</v>
       </c>
       <c r="W21" t="n">
-        <v>-251000</v>
+        <v>166814366</v>
       </c>
       <c r="X21" t="n">
-        <v>356531</v>
+        <v>271944</v>
       </c>
       <c r="Y21" t="n">
-        <v>343912</v>
+        <v>1451425</v>
       </c>
       <c r="Z21" t="n">
-        <v>1603501</v>
+        <v>2680773</v>
       </c>
       <c r="AA21" t="n">
-        <v>1252702</v>
+        <v>2605666</v>
       </c>
       <c r="AB21" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -2909,54 +2909,54 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>293.5</v>
+        <v>175.5</v>
       </c>
       <c r="D22" t="n">
-        <v>273.7</v>
+        <v>165</v>
       </c>
       <c r="E22" t="n">
-        <v>261.2</v>
+        <v>156.95</v>
       </c>
       <c r="F22" t="n">
-        <v>255.07</v>
+        <v>158.75</v>
       </c>
       <c r="G22" t="n">
-        <v>205766647</v>
+        <v>244618000</v>
       </c>
       <c r="H22" t="n">
-        <v>140617655</v>
+        <v>213809989</v>
       </c>
       <c r="I22" t="n">
-        <v>304.5</v>
+        <v>180</v>
       </c>
       <c r="J22" t="n">
-        <v>227</v>
+        <v>136.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,55 +2964,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-5143876</v>
+        <v>18724442</v>
       </c>
       <c r="M22" t="n">
-        <v>100059807</v>
+        <v>108932425</v>
       </c>
       <c r="N22" t="n">
-        <v>128543523</v>
+        <v>93713452</v>
       </c>
       <c r="O22" t="n">
-        <v>213173724</v>
+        <v>40901700</v>
       </c>
       <c r="P22" t="n">
-        <v>-6575097</v>
+        <v>14372572</v>
       </c>
       <c r="Q22" t="n">
-        <v>86629844</v>
+        <v>104191240</v>
       </c>
       <c r="R22" t="n">
-        <v>115525527</v>
+        <v>87837822</v>
       </c>
       <c r="S22" t="n">
-        <v>204533241</v>
+        <v>51829461</v>
       </c>
       <c r="T22" t="n">
-        <v>1808000</v>
+        <v>3088000</v>
       </c>
       <c r="U22" t="n">
-        <v>9361253</v>
+        <v>2964000</v>
       </c>
       <c r="V22" t="n">
-        <v>9249189</v>
+        <v>5773000</v>
       </c>
       <c r="W22" t="n">
-        <v>5565896</v>
+        <v>-8247000</v>
       </c>
       <c r="X22" t="n">
-        <v>-376779</v>
+        <v>1263870</v>
       </c>
       <c r="Y22" t="n">
-        <v>4068710</v>
+        <v>1777185</v>
       </c>
       <c r="Z22" t="n">
-        <v>3768807</v>
+        <v>102630</v>
       </c>
       <c r="AA22" t="n">
-        <v>3074587</v>
+        <v>-2680761</v>
       </c>
       <c r="AB22" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -3026,17 +3026,17 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2355</v>
+        <v>2380</v>
       </c>
       <c r="D23" t="n">
-        <v>2315</v>
+        <v>2337</v>
       </c>
       <c r="E23" t="n">
-        <v>2276</v>
+        <v>2293.5</v>
       </c>
       <c r="F23" t="n">
-        <v>2267.25</v>
+        <v>2273.75</v>
       </c>
       <c r="G23" t="n">
-        <v>60942792</v>
+        <v>29548000</v>
       </c>
       <c r="H23" t="n">
-        <v>56218744</v>
+        <v>55572050</v>
       </c>
       <c r="I23" t="n">
         <v>2415</v>
@@ -3129,7 +3129,7 @@
         <v>2473830</v>
       </c>
       <c r="AB23" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3153,44 +3153,44 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1705</v>
+        <v>301.5</v>
       </c>
       <c r="D24" t="n">
-        <v>1629</v>
+        <v>282.2</v>
       </c>
       <c r="E24" t="n">
-        <v>1495.5</v>
+        <v>266.85</v>
       </c>
       <c r="F24" t="n">
-        <v>1433.75</v>
+        <v>258.18</v>
       </c>
       <c r="G24" t="n">
-        <v>8984000</v>
+        <v>110029000</v>
       </c>
       <c r="H24" t="n">
-        <v>9020000</v>
+        <v>151490394</v>
       </c>
       <c r="I24" t="n">
-        <v>1815</v>
+        <v>304.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1125</v>
+        <v>239.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,55 +3198,55 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>379477</v>
+        <v>-5143876</v>
       </c>
       <c r="M24" t="n">
-        <v>1642627</v>
+        <v>100059807</v>
       </c>
       <c r="N24" t="n">
-        <v>1838037</v>
+        <v>128543523</v>
       </c>
       <c r="O24" t="n">
-        <v>3059725</v>
+        <v>213173724</v>
       </c>
       <c r="P24" t="n">
-        <v>-548848</v>
+        <v>-6575097</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1259270</v>
+        <v>86629844</v>
       </c>
       <c r="R24" t="n">
-        <v>-1432379</v>
+        <v>115525527</v>
       </c>
       <c r="S24" t="n">
-        <v>-33796</v>
+        <v>204533241</v>
       </c>
       <c r="T24" t="n">
-        <v>968000</v>
+        <v>1808000</v>
       </c>
       <c r="U24" t="n">
-        <v>3158000</v>
+        <v>9361253</v>
       </c>
       <c r="V24" t="n">
-        <v>3576000</v>
+        <v>9249189</v>
       </c>
       <c r="W24" t="n">
-        <v>3569100</v>
+        <v>5565896</v>
       </c>
       <c r="X24" t="n">
-        <v>-39675</v>
+        <v>-376779</v>
       </c>
       <c r="Y24" t="n">
-        <v>-256103</v>
+        <v>4068710</v>
       </c>
       <c r="Z24" t="n">
-        <v>-305584</v>
+        <v>3768807</v>
       </c>
       <c r="AA24" t="n">
-        <v>-475579</v>
+        <v>3074587</v>
       </c>
       <c r="AB24" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -3260,54 +3260,54 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>61</v>
+        <v>1705</v>
       </c>
       <c r="D25" t="n">
-        <v>59.78</v>
+        <v>1629</v>
       </c>
       <c r="E25" t="n">
-        <v>56.55</v>
+        <v>1495.5</v>
       </c>
       <c r="F25" t="n">
-        <v>57.85</v>
+        <v>1433.75</v>
       </c>
       <c r="G25" t="n">
-        <v>16891552</v>
+        <v>8984000</v>
       </c>
       <c r="H25" t="n">
-        <v>26352455</v>
+        <v>9020000</v>
       </c>
       <c r="I25" t="n">
-        <v>65</v>
+        <v>1815</v>
       </c>
       <c r="J25" t="n">
-        <v>50.2</v>
+        <v>1125</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,55 +3315,55 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1051605</v>
+        <v>379477</v>
       </c>
       <c r="M25" t="n">
-        <v>12258933</v>
+        <v>1642627</v>
       </c>
       <c r="N25" t="n">
-        <v>14444946</v>
+        <v>1754492</v>
       </c>
       <c r="O25" t="n">
-        <v>9009446</v>
+        <v>2976180</v>
       </c>
       <c r="P25" t="n">
-        <v>1587498</v>
+        <v>-548848</v>
       </c>
       <c r="Q25" t="n">
-        <v>11720020</v>
+        <v>-1259270</v>
       </c>
       <c r="R25" t="n">
-        <v>13446507</v>
+        <v>-2532759</v>
       </c>
       <c r="S25" t="n">
-        <v>8915008</v>
+        <v>-1134176</v>
       </c>
       <c r="T25" t="n">
-        <v>12000</v>
+        <v>968000</v>
       </c>
       <c r="U25" t="n">
-        <v>12000</v>
+        <v>3158000</v>
       </c>
       <c r="V25" t="n">
-        <v>12000</v>
+        <v>4982000</v>
       </c>
       <c r="W25" t="n">
-        <v>204000</v>
+        <v>4975100</v>
       </c>
       <c r="X25" t="n">
-        <v>-547893</v>
+        <v>-39675</v>
       </c>
       <c r="Y25" t="n">
-        <v>526913</v>
+        <v>-256103</v>
       </c>
       <c r="Z25" t="n">
-        <v>986439</v>
+        <v>-694749</v>
       </c>
       <c r="AA25" t="n">
-        <v>-109562</v>
+        <v>-864744</v>
       </c>
       <c r="AB25" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -3377,54 +3377,54 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>167.5</v>
+        <v>950</v>
       </c>
       <c r="D26" t="n">
-        <v>162</v>
+        <v>937.6</v>
       </c>
       <c r="E26" t="n">
-        <v>153.8</v>
+        <v>819.7</v>
       </c>
       <c r="F26" t="n">
-        <v>158</v>
+        <v>787.25</v>
       </c>
       <c r="G26" t="n">
-        <v>190490552</v>
+        <v>4452000</v>
       </c>
       <c r="H26" t="n">
-        <v>197619129</v>
+        <v>12667000</v>
       </c>
       <c r="I26" t="n">
-        <v>178.5</v>
+        <v>1040</v>
       </c>
       <c r="J26" t="n">
-        <v>136.5</v>
+        <v>615</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,55 +3432,55 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>18724442</v>
+        <v>798638</v>
       </c>
       <c r="M26" t="n">
-        <v>108932425</v>
+        <v>2696041</v>
       </c>
       <c r="N26" t="n">
-        <v>93713452</v>
+        <v>7450242</v>
       </c>
       <c r="O26" t="n">
-        <v>40901700</v>
+        <v>2839260</v>
       </c>
       <c r="P26" t="n">
-        <v>14372572</v>
+        <v>989046</v>
       </c>
       <c r="Q26" t="n">
-        <v>104191240</v>
+        <v>-337021</v>
       </c>
       <c r="R26" t="n">
-        <v>87837822</v>
+        <v>-241872</v>
       </c>
       <c r="S26" t="n">
-        <v>51829461</v>
+        <v>-5316929</v>
       </c>
       <c r="T26" t="n">
-        <v>3088000</v>
+        <v>-792857</v>
       </c>
       <c r="U26" t="n">
-        <v>2964000</v>
+        <v>2500409</v>
       </c>
       <c r="V26" t="n">
-        <v>5773000</v>
+        <v>7076238</v>
       </c>
       <c r="W26" t="n">
-        <v>-8247000</v>
+        <v>6501050</v>
       </c>
       <c r="X26" t="n">
-        <v>1263870</v>
+        <v>602449</v>
       </c>
       <c r="Y26" t="n">
-        <v>1777185</v>
+        <v>532653</v>
       </c>
       <c r="Z26" t="n">
-        <v>102630</v>
+        <v>615876</v>
       </c>
       <c r="AA26" t="n">
-        <v>-2680761</v>
+        <v>1655139</v>
       </c>
       <c r="AB26" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -3494,54 +3494,54 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>314</v>
+        <v>31.4</v>
       </c>
       <c r="D27" t="n">
-        <v>310.6</v>
+        <v>30.36</v>
       </c>
       <c r="E27" t="n">
-        <v>299.85</v>
+        <v>29.89</v>
       </c>
       <c r="F27" t="n">
-        <v>279.38</v>
+        <v>28.67</v>
       </c>
       <c r="G27" t="n">
-        <v>17008580</v>
+        <v>14102000</v>
       </c>
       <c r="H27" t="n">
-        <v>25024889</v>
+        <v>12680986</v>
       </c>
       <c r="I27" t="n">
-        <v>336.5</v>
+        <v>31.95</v>
       </c>
       <c r="J27" t="n">
-        <v>221.5</v>
+        <v>25.55</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3549,55 +3549,55 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-3145576</v>
+        <v>-1578569</v>
       </c>
       <c r="M27" t="n">
-        <v>-2096880</v>
+        <v>4003880</v>
       </c>
       <c r="N27" t="n">
-        <v>8442316</v>
+        <v>5342063</v>
       </c>
       <c r="O27" t="n">
-        <v>-2780785</v>
+        <v>14183692</v>
       </c>
       <c r="P27" t="n">
-        <v>-3049921</v>
+        <v>-1656460</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2116785</v>
+        <v>3489598</v>
       </c>
       <c r="R27" t="n">
-        <v>7052430</v>
+        <v>4830671</v>
       </c>
       <c r="S27" t="n">
-        <v>3656099</v>
+        <v>13065591</v>
       </c>
       <c r="T27" t="n">
-        <v>152000</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>311768</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1427768</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>-5810208</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-247655</v>
+        <v>77891</v>
       </c>
       <c r="Y27" t="n">
-        <v>-291863</v>
+        <v>514282</v>
       </c>
       <c r="Z27" t="n">
-        <v>-37882</v>
+        <v>511392</v>
       </c>
       <c r="AA27" t="n">
-        <v>-626676</v>
+        <v>1118101</v>
       </c>
       <c r="AB27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -3611,54 +3611,54 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>905</v>
+        <v>71</v>
       </c>
       <c r="D28" t="n">
-        <v>886</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>874.7</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>879.85</v>
+        <v>69.42</v>
       </c>
       <c r="G28" t="n">
-        <v>21446815</v>
+        <v>148186000</v>
       </c>
       <c r="H28" t="n">
-        <v>21418672</v>
+        <v>142816836</v>
       </c>
       <c r="I28" t="n">
-        <v>1035</v>
+        <v>81.2</v>
       </c>
       <c r="J28" t="n">
-        <v>765</v>
+        <v>61.8</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,55 +3666,55 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>6489767</v>
+        <v>36235379</v>
       </c>
       <c r="M28" t="n">
-        <v>-2035790</v>
+        <v>18005086</v>
       </c>
       <c r="N28" t="n">
-        <v>2257312</v>
+        <v>24812582</v>
       </c>
       <c r="O28" t="n">
-        <v>-2252248</v>
+        <v>100060322</v>
       </c>
       <c r="P28" t="n">
-        <v>5749529</v>
+        <v>35838589</v>
       </c>
       <c r="Q28" t="n">
-        <v>1761213</v>
+        <v>17380149</v>
       </c>
       <c r="R28" t="n">
-        <v>7285342</v>
+        <v>21056648</v>
       </c>
       <c r="S28" t="n">
-        <v>2700083</v>
+        <v>91577139</v>
       </c>
       <c r="T28" t="n">
-        <v>764000</v>
+        <v>421000</v>
       </c>
       <c r="U28" t="n">
-        <v>-3636000</v>
+        <v>1027000</v>
       </c>
       <c r="V28" t="n">
-        <v>-4848000</v>
+        <v>2759000</v>
       </c>
       <c r="W28" t="n">
-        <v>-4370000</v>
+        <v>2802000</v>
       </c>
       <c r="X28" t="n">
-        <v>-23762</v>
+        <v>-24210</v>
       </c>
       <c r="Y28" t="n">
-        <v>-161003</v>
+        <v>-402063</v>
       </c>
       <c r="Z28" t="n">
-        <v>-180030</v>
+        <v>996934</v>
       </c>
       <c r="AA28" t="n">
-        <v>-582331</v>
+        <v>5681183</v>
       </c>
       <c r="AB28" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -3728,54 +3728,54 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4555</v>
+        <v>859</v>
       </c>
       <c r="D29" t="n">
-        <v>4436</v>
+        <v>843</v>
       </c>
       <c r="E29" t="n">
-        <v>4022</v>
+        <v>810.2</v>
       </c>
       <c r="F29" t="n">
-        <v>3749.75</v>
+        <v>759.85</v>
       </c>
       <c r="G29" t="n">
-        <v>20083897</v>
+        <v>6258000</v>
       </c>
       <c r="H29" t="n">
-        <v>19485690</v>
+        <v>4776400</v>
       </c>
       <c r="I29" t="n">
-        <v>4710</v>
+        <v>929</v>
       </c>
       <c r="J29" t="n">
-        <v>3100</v>
+        <v>553</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,52 +3783,52 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3148836</v>
+        <v>-615906</v>
       </c>
       <c r="M29" t="n">
-        <v>-1878848</v>
+        <v>317162</v>
       </c>
       <c r="N29" t="n">
-        <v>942900</v>
+        <v>1069118</v>
       </c>
       <c r="O29" t="n">
-        <v>-4597456</v>
+        <v>814100</v>
       </c>
       <c r="P29" t="n">
-        <v>3786804</v>
+        <v>-931819</v>
       </c>
       <c r="Q29" t="n">
-        <v>605566</v>
+        <v>-1205698</v>
       </c>
       <c r="R29" t="n">
-        <v>4970698</v>
+        <v>-564120</v>
       </c>
       <c r="S29" t="n">
-        <v>-976834</v>
+        <v>-735635</v>
       </c>
       <c r="T29" t="n">
-        <v>-461186</v>
+        <v>357000</v>
       </c>
       <c r="U29" t="n">
-        <v>-2105376</v>
+        <v>1549000</v>
       </c>
       <c r="V29" t="n">
-        <v>-3983417</v>
+        <v>1533000</v>
       </c>
       <c r="W29" t="n">
-        <v>-4323474</v>
+        <v>1333000</v>
       </c>
       <c r="X29" t="n">
-        <v>-176782</v>
+        <v>-41087</v>
       </c>
       <c r="Y29" t="n">
-        <v>-379038</v>
+        <v>-26140</v>
       </c>
       <c r="Z29" t="n">
-        <v>-44381</v>
+        <v>100238</v>
       </c>
       <c r="AA29" t="n">
-        <v>702852</v>
+        <v>216735</v>
       </c>
       <c r="AB29" t="n">
         <v>85</v>
@@ -3850,12 +3850,12 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -3871,22 +3871,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>173.5</v>
+        <v>174.5</v>
       </c>
       <c r="D30" t="n">
-        <v>172.8</v>
+        <v>173.1</v>
       </c>
       <c r="E30" t="n">
-        <v>173.1</v>
+        <v>173.15</v>
       </c>
       <c r="F30" t="n">
-        <v>172.38</v>
+        <v>172.62</v>
       </c>
       <c r="G30" t="n">
-        <v>253542</v>
+        <v>243000</v>
       </c>
       <c r="H30" t="n">
-        <v>215296</v>
+        <v>234301</v>
       </c>
       <c r="I30" t="n">
         <v>176.5</v>
@@ -3979,37 +3979,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>859</v>
+        <v>4525</v>
       </c>
       <c r="D31" t="n">
-        <v>843</v>
+        <v>4488</v>
       </c>
       <c r="E31" t="n">
-        <v>810.2</v>
+        <v>4159</v>
       </c>
       <c r="F31" t="n">
-        <v>759.85</v>
+        <v>3818.25</v>
       </c>
       <c r="G31" t="n">
-        <v>6258000</v>
+        <v>14126000</v>
       </c>
       <c r="H31" t="n">
-        <v>4776400</v>
+        <v>18402716</v>
       </c>
       <c r="I31" t="n">
-        <v>929</v>
+        <v>4970</v>
       </c>
       <c r="J31" t="n">
-        <v>553</v>
+        <v>3100</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,55 +4017,55 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-615906</v>
+        <v>3148836</v>
       </c>
       <c r="M31" t="n">
-        <v>317162</v>
+        <v>-1878848</v>
       </c>
       <c r="N31" t="n">
-        <v>1578002</v>
+        <v>942900</v>
       </c>
       <c r="O31" t="n">
-        <v>1322984</v>
+        <v>-4597456</v>
       </c>
       <c r="P31" t="n">
-        <v>-931819</v>
+        <v>3786804</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1205698</v>
+        <v>605566</v>
       </c>
       <c r="R31" t="n">
-        <v>-97486</v>
+        <v>4970698</v>
       </c>
       <c r="S31" t="n">
-        <v>-269001</v>
+        <v>-976834</v>
       </c>
       <c r="T31" t="n">
-        <v>357000</v>
+        <v>-461186</v>
       </c>
       <c r="U31" t="n">
-        <v>1549000</v>
+        <v>-2105376</v>
       </c>
       <c r="V31" t="n">
-        <v>1549000</v>
+        <v>-3983417</v>
       </c>
       <c r="W31" t="n">
-        <v>1349000</v>
+        <v>-4323474</v>
       </c>
       <c r="X31" t="n">
-        <v>-41087</v>
+        <v>-176782</v>
       </c>
       <c r="Y31" t="n">
-        <v>-26140</v>
+        <v>-379038</v>
       </c>
       <c r="Z31" t="n">
-        <v>126488</v>
+        <v>-44381</v>
       </c>
       <c r="AA31" t="n">
-        <v>242985</v>
+        <v>702852</v>
       </c>
       <c r="AB31" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -4079,54 +4079,54 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>366</v>
+        <v>975</v>
       </c>
       <c r="D32" t="n">
-        <v>357</v>
+        <v>1037</v>
       </c>
       <c r="E32" t="n">
-        <v>309.8</v>
+        <v>995.8</v>
       </c>
       <c r="F32" t="n">
-        <v>271.18</v>
+        <v>924.7</v>
       </c>
       <c r="G32" t="n">
-        <v>14415513</v>
+        <v>25680000</v>
       </c>
       <c r="H32" t="n">
-        <v>49947550</v>
+        <v>23689418</v>
       </c>
       <c r="I32" t="n">
-        <v>387</v>
+        <v>1130</v>
       </c>
       <c r="J32" t="n">
-        <v>217.5</v>
+        <v>776</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,116 +4134,116 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-1423317</v>
+        <v>-709629</v>
       </c>
       <c r="M32" t="n">
-        <v>5682114</v>
+        <v>-1610746</v>
       </c>
       <c r="N32" t="n">
-        <v>9371560</v>
+        <v>10872395</v>
       </c>
       <c r="O32" t="n">
-        <v>3387386</v>
+        <v>24914490</v>
       </c>
       <c r="P32" t="n">
-        <v>-496203</v>
+        <v>261132</v>
       </c>
       <c r="Q32" t="n">
-        <v>7240655</v>
+        <v>-544695</v>
       </c>
       <c r="R32" t="n">
-        <v>9811506</v>
+        <v>8333371</v>
       </c>
       <c r="S32" t="n">
-        <v>8084759</v>
+        <v>21412568</v>
       </c>
       <c r="T32" t="n">
-        <v>-570594</v>
+        <v>-917999</v>
       </c>
       <c r="U32" t="n">
-        <v>-1714782</v>
+        <v>-674372</v>
       </c>
       <c r="V32" t="n">
-        <v>-1000376</v>
+        <v>3265628</v>
       </c>
       <c r="W32" t="n">
-        <v>-4914478</v>
+        <v>3968571</v>
       </c>
       <c r="X32" t="n">
-        <v>-356520</v>
+        <v>-52762</v>
       </c>
       <c r="Y32" t="n">
-        <v>156241</v>
+        <v>-391679</v>
       </c>
       <c r="Z32" t="n">
-        <v>560430</v>
+        <v>-726604</v>
       </c>
       <c r="AA32" t="n">
-        <v>217105</v>
+        <v>-466649</v>
       </c>
       <c r="AB32" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1380</v>
+        <v>58.9</v>
       </c>
       <c r="D33" t="n">
-        <v>1488</v>
+        <v>59.88</v>
       </c>
       <c r="E33" t="n">
-        <v>1466</v>
+        <v>57.31</v>
       </c>
       <c r="F33" t="n">
-        <v>1401.75</v>
+        <v>57.69</v>
       </c>
       <c r="G33" t="n">
-        <v>21389778</v>
+        <v>15299000</v>
       </c>
       <c r="H33" t="n">
-        <v>14839667</v>
+        <v>25700112</v>
       </c>
       <c r="I33" t="n">
-        <v>1565</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>1195</v>
+        <v>50.2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,55 +4251,55 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-769525</v>
+        <v>1051605</v>
       </c>
       <c r="M33" t="n">
-        <v>-1974477</v>
+        <v>12258933</v>
       </c>
       <c r="N33" t="n">
-        <v>4400784</v>
+        <v>14444946</v>
       </c>
       <c r="O33" t="n">
-        <v>6318632</v>
+        <v>9009446</v>
       </c>
       <c r="P33" t="n">
-        <v>-821342</v>
+        <v>1587498</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2404327</v>
+        <v>11720020</v>
       </c>
       <c r="R33" t="n">
-        <v>3439207</v>
+        <v>13446507</v>
       </c>
       <c r="S33" t="n">
-        <v>7261138</v>
+        <v>8915008</v>
       </c>
       <c r="T33" t="n">
-        <v>133000</v>
+        <v>12000</v>
       </c>
       <c r="U33" t="n">
-        <v>616198</v>
+        <v>12000</v>
       </c>
       <c r="V33" t="n">
-        <v>1073098</v>
+        <v>12000</v>
       </c>
       <c r="W33" t="n">
-        <v>-1265676</v>
+        <v>204000</v>
       </c>
       <c r="X33" t="n">
-        <v>-81183</v>
+        <v>-547893</v>
       </c>
       <c r="Y33" t="n">
-        <v>-186348</v>
+        <v>526913</v>
       </c>
       <c r="Z33" t="n">
-        <v>-111521</v>
+        <v>986439</v>
       </c>
       <c r="AA33" t="n">
-        <v>323170</v>
+        <v>-109562</v>
       </c>
       <c r="AB33" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -4313,54 +4313,54 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1050</v>
+        <v>2360</v>
       </c>
       <c r="D34" t="n">
-        <v>1059</v>
+        <v>2427</v>
       </c>
       <c r="E34" t="n">
-        <v>980.1</v>
+        <v>2281.5</v>
       </c>
       <c r="F34" t="n">
-        <v>921.1</v>
+        <v>2213.75</v>
       </c>
       <c r="G34" t="n">
-        <v>19127603</v>
+        <v>10966000</v>
       </c>
       <c r="H34" t="n">
-        <v>25407511</v>
+        <v>12720939</v>
       </c>
       <c r="I34" t="n">
-        <v>1130</v>
+        <v>2585</v>
       </c>
       <c r="J34" t="n">
-        <v>776</v>
+        <v>1880</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,52 +4368,52 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-709629</v>
+        <v>-769525</v>
       </c>
       <c r="M34" t="n">
-        <v>-1610746</v>
+        <v>-1974477</v>
       </c>
       <c r="N34" t="n">
-        <v>10872395</v>
+        <v>4400784</v>
       </c>
       <c r="O34" t="n">
-        <v>24914490</v>
+        <v>6318632</v>
       </c>
       <c r="P34" t="n">
-        <v>261132</v>
+        <v>-821342</v>
       </c>
       <c r="Q34" t="n">
-        <v>-544695</v>
+        <v>-2404327</v>
       </c>
       <c r="R34" t="n">
-        <v>8333371</v>
+        <v>3439207</v>
       </c>
       <c r="S34" t="n">
-        <v>21412568</v>
+        <v>7261138</v>
       </c>
       <c r="T34" t="n">
-        <v>-917999</v>
+        <v>133000</v>
       </c>
       <c r="U34" t="n">
-        <v>-674372</v>
+        <v>616198</v>
       </c>
       <c r="V34" t="n">
-        <v>3265628</v>
+        <v>1073098</v>
       </c>
       <c r="W34" t="n">
-        <v>3968571</v>
+        <v>-1265676</v>
       </c>
       <c r="X34" t="n">
-        <v>-52762</v>
+        <v>-81183</v>
       </c>
       <c r="Y34" t="n">
-        <v>-391679</v>
+        <v>-186348</v>
       </c>
       <c r="Z34" t="n">
-        <v>-726604</v>
+        <v>-111521</v>
       </c>
       <c r="AA34" t="n">
-        <v>-466649</v>
+        <v>323170</v>
       </c>
       <c r="AB34" t="n">
         <v>55</v>
@@ -4447,37 +4447,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1905</v>
+        <v>306</v>
       </c>
       <c r="D35" t="n">
-        <v>1761</v>
+        <v>310.9</v>
       </c>
       <c r="E35" t="n">
-        <v>1733</v>
+        <v>301.25</v>
       </c>
       <c r="F35" t="n">
-        <v>1710.5</v>
+        <v>283.02</v>
       </c>
       <c r="G35" t="n">
-        <v>4954000</v>
+        <v>12811000</v>
       </c>
       <c r="H35" t="n">
-        <v>4262400</v>
+        <v>23239467</v>
       </c>
       <c r="I35" t="n">
-        <v>1950</v>
+        <v>336.5</v>
       </c>
       <c r="J35" t="n">
-        <v>1310</v>
+        <v>222</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,55 +4485,55 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-327662</v>
+        <v>-3145576</v>
       </c>
       <c r="M35" t="n">
-        <v>321027</v>
+        <v>-2096880</v>
       </c>
       <c r="N35" t="n">
-        <v>-349918</v>
+        <v>8442316</v>
       </c>
       <c r="O35" t="n">
-        <v>-1218427</v>
+        <v>-2780785</v>
       </c>
       <c r="P35" t="n">
-        <v>-356590</v>
+        <v>-3049921</v>
       </c>
       <c r="Q35" t="n">
-        <v>-349587</v>
+        <v>-2116785</v>
       </c>
       <c r="R35" t="n">
-        <v>-969060</v>
+        <v>7052430</v>
       </c>
       <c r="S35" t="n">
-        <v>-1105299</v>
+        <v>3656099</v>
       </c>
       <c r="T35" t="n">
-        <v>23000</v>
+        <v>152000</v>
       </c>
       <c r="U35" t="n">
-        <v>626500</v>
+        <v>311768</v>
       </c>
       <c r="V35" t="n">
-        <v>583740</v>
+        <v>1427768</v>
       </c>
       <c r="W35" t="n">
-        <v>-48093</v>
+        <v>-5810208</v>
       </c>
       <c r="X35" t="n">
-        <v>5928</v>
+        <v>-247655</v>
       </c>
       <c r="Y35" t="n">
-        <v>44114</v>
+        <v>-291863</v>
       </c>
       <c r="Z35" t="n">
-        <v>35402</v>
+        <v>-37882</v>
       </c>
       <c r="AA35" t="n">
-        <v>-65035</v>
+        <v>-626676</v>
       </c>
       <c r="AB35" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -4547,54 +4547,54 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>2401.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>84.7</v>
+        <v>28.9</v>
       </c>
       <c r="D36" t="n">
-        <v>81.94</v>
+        <v>29.93</v>
       </c>
       <c r="E36" t="n">
-        <v>81.59</v>
+        <v>29.64</v>
       </c>
       <c r="F36" t="n">
-        <v>81.09999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="G36" t="n">
-        <v>21521256</v>
+        <v>11749000</v>
       </c>
       <c r="H36" t="n">
-        <v>14725250</v>
+        <v>16666452</v>
       </c>
       <c r="I36" t="n">
-        <v>86.40000000000001</v>
+        <v>33</v>
       </c>
       <c r="J36" t="n">
-        <v>77.09999999999999</v>
+        <v>23.45</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,55 +4602,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>525384</v>
+        <v>-603883</v>
       </c>
       <c r="M36" t="n">
-        <v>2970153</v>
+        <v>-278540</v>
       </c>
       <c r="N36" t="n">
-        <v>-83282</v>
+        <v>144595</v>
       </c>
       <c r="O36" t="n">
-        <v>4290817</v>
+        <v>-2240107</v>
       </c>
       <c r="P36" t="n">
-        <v>244033</v>
+        <v>-599884</v>
       </c>
       <c r="Q36" t="n">
-        <v>2393134</v>
+        <v>112872</v>
       </c>
       <c r="R36" t="n">
-        <v>-482721</v>
+        <v>376871</v>
       </c>
       <c r="S36" t="n">
-        <v>4206293</v>
+        <v>-3761253</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="V36" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="W36" t="n">
-        <v>-1000</v>
+        <v>234000</v>
       </c>
       <c r="X36" t="n">
-        <v>281351</v>
+        <v>-3999</v>
       </c>
       <c r="Y36" t="n">
-        <v>578019</v>
+        <v>-392412</v>
       </c>
       <c r="Z36" t="n">
-        <v>400439</v>
+        <v>-233276</v>
       </c>
       <c r="AA36" t="n">
-        <v>85524</v>
+        <v>1287146</v>
       </c>
       <c r="AB36" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -4664,54 +4664,54 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>5日法人小幅賣超、外資投信同步賣超</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、5日法人小幅賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18.8</v>
+        <v>273</v>
       </c>
       <c r="D37" t="n">
-        <v>15.92</v>
+        <v>274.8</v>
       </c>
       <c r="E37" t="n">
-        <v>13.53</v>
+        <v>266.05</v>
       </c>
       <c r="F37" t="n">
-        <v>11.68</v>
+        <v>269.93</v>
       </c>
       <c r="G37" t="n">
-        <v>58323262</v>
+        <v>25826000</v>
       </c>
       <c r="H37" t="n">
-        <v>289146286</v>
+        <v>26137740</v>
       </c>
       <c r="I37" t="n">
-        <v>18.8</v>
+        <v>322</v>
       </c>
       <c r="J37" t="n">
-        <v>8.32</v>
+        <v>230</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,52 +4719,52 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-2827260</v>
+        <v>12348068</v>
       </c>
       <c r="M37" t="n">
-        <v>9048582</v>
+        <v>8160032</v>
       </c>
       <c r="N37" t="n">
-        <v>-47490059</v>
+        <v>15069872</v>
       </c>
       <c r="O37" t="n">
-        <v>8792749</v>
+        <v>12457873</v>
       </c>
       <c r="P37" t="n">
-        <v>-3854960</v>
+        <v>11994537</v>
       </c>
       <c r="Q37" t="n">
-        <v>6757407</v>
+        <v>7819120</v>
       </c>
       <c r="R37" t="n">
-        <v>-48015620</v>
+        <v>13707371</v>
       </c>
       <c r="S37" t="n">
-        <v>6500797</v>
+        <v>11456171</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>-241000</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>-251000</v>
       </c>
       <c r="X37" t="n">
-        <v>1027700</v>
+        <v>356531</v>
       </c>
       <c r="Y37" t="n">
-        <v>2291175</v>
+        <v>343912</v>
       </c>
       <c r="Z37" t="n">
-        <v>525561</v>
+        <v>1603501</v>
       </c>
       <c r="AA37" t="n">
-        <v>2291952</v>
+        <v>1252702</v>
       </c>
       <c r="AB37" t="n">
         <v>40</v>
@@ -4781,54 +4781,54 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>238.5</v>
+        <v>1905</v>
       </c>
       <c r="D38" t="n">
-        <v>219.8</v>
+        <v>1761</v>
       </c>
       <c r="E38" t="n">
-        <v>210</v>
+        <v>1733</v>
       </c>
       <c r="F38" t="n">
-        <v>195.62</v>
+        <v>1710.5</v>
       </c>
       <c r="G38" t="n">
-        <v>19177000</v>
+        <v>4954000</v>
       </c>
       <c r="H38" t="n">
-        <v>13984200</v>
+        <v>4262400</v>
       </c>
       <c r="I38" t="n">
-        <v>249.5</v>
+        <v>1950</v>
       </c>
       <c r="J38" t="n">
-        <v>152</v>
+        <v>1310</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,55 +4836,55 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-1234497</v>
+        <v>-327662</v>
       </c>
       <c r="M38" t="n">
-        <v>349950</v>
+        <v>321027</v>
       </c>
       <c r="N38" t="n">
-        <v>-305693</v>
+        <v>-817069</v>
       </c>
       <c r="O38" t="n">
-        <v>3706687</v>
+        <v>-1685578</v>
       </c>
       <c r="P38" t="n">
-        <v>-1242784</v>
+        <v>-356590</v>
       </c>
       <c r="Q38" t="n">
-        <v>172281</v>
+        <v>-349587</v>
       </c>
       <c r="R38" t="n">
-        <v>-446989</v>
+        <v>-1159255</v>
       </c>
       <c r="S38" t="n">
-        <v>3430365</v>
+        <v>-1295494</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>626500</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>319123</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>-312710</v>
       </c>
       <c r="X38" t="n">
-        <v>8287</v>
+        <v>5928</v>
       </c>
       <c r="Y38" t="n">
-        <v>177669</v>
+        <v>44114</v>
       </c>
       <c r="Z38" t="n">
-        <v>141296</v>
+        <v>23063</v>
       </c>
       <c r="AA38" t="n">
-        <v>276322</v>
+        <v>-77374</v>
       </c>
       <c r="AB38" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -4903,49 +4903,49 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>5日法人賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5515</v>
+        <v>20.65</v>
       </c>
       <c r="D39" t="n">
-        <v>5253</v>
+        <v>17.32</v>
       </c>
       <c r="E39" t="n">
-        <v>5254.5</v>
+        <v>14.57</v>
       </c>
       <c r="F39" t="n">
-        <v>5235</v>
+        <v>12.28</v>
       </c>
       <c r="G39" t="n">
-        <v>2252805</v>
+        <v>197735000</v>
       </c>
       <c r="H39" t="n">
-        <v>2469396</v>
+        <v>233029272</v>
       </c>
       <c r="I39" t="n">
-        <v>5880</v>
+        <v>20.65</v>
       </c>
       <c r="J39" t="n">
-        <v>4630</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,55 +4953,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-53222</v>
+        <v>-2827260</v>
       </c>
       <c r="M39" t="n">
-        <v>656900</v>
+        <v>9048582</v>
       </c>
       <c r="N39" t="n">
-        <v>77693</v>
+        <v>-47490059</v>
       </c>
       <c r="O39" t="n">
-        <v>-83131</v>
+        <v>8792749</v>
       </c>
       <c r="P39" t="n">
-        <v>-133821</v>
+        <v>-3854960</v>
       </c>
       <c r="Q39" t="n">
-        <v>683080</v>
+        <v>6757407</v>
       </c>
       <c r="R39" t="n">
-        <v>588871</v>
+        <v>-48015620</v>
       </c>
       <c r="S39" t="n">
-        <v>590076</v>
+        <v>6500797</v>
       </c>
       <c r="T39" t="n">
-        <v>83002</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>66976</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>-260347</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>-552553</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>-2403</v>
+        <v>1027700</v>
       </c>
       <c r="Y39" t="n">
-        <v>-93156</v>
+        <v>2291175</v>
       </c>
       <c r="Z39" t="n">
-        <v>-250831</v>
+        <v>525561</v>
       </c>
       <c r="AA39" t="n">
-        <v>-120654</v>
+        <v>2291952</v>
       </c>
       <c r="AB39" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -5015,54 +5015,54 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>5日法人小幅買超、外資買投信賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、5日法人小幅買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.68</v>
+        <v>347</v>
       </c>
       <c r="D40" t="n">
-        <v>8.74</v>
+        <v>358</v>
       </c>
       <c r="E40" t="n">
-        <v>7.52</v>
+        <v>321.8</v>
       </c>
       <c r="F40" t="n">
-        <v>6.63</v>
+        <v>277.15</v>
       </c>
       <c r="G40" t="n">
-        <v>192788160</v>
+        <v>22914000</v>
       </c>
       <c r="H40" t="n">
-        <v>184651629</v>
+        <v>42942610</v>
       </c>
       <c r="I40" t="n">
-        <v>9.68</v>
+        <v>387</v>
       </c>
       <c r="J40" t="n">
-        <v>5.55</v>
+        <v>217.5</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5070,55 +5070,55 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>17102138</v>
+        <v>-1423317</v>
       </c>
       <c r="M40" t="n">
-        <v>-10102801</v>
+        <v>5682114</v>
       </c>
       <c r="N40" t="n">
-        <v>-1903688</v>
+        <v>9371560</v>
       </c>
       <c r="O40" t="n">
-        <v>32520599</v>
+        <v>3387386</v>
       </c>
       <c r="P40" t="n">
-        <v>16867220</v>
+        <v>-496203</v>
       </c>
       <c r="Q40" t="n">
-        <v>-10204580</v>
+        <v>7240655</v>
       </c>
       <c r="R40" t="n">
-        <v>395471</v>
+        <v>9811506</v>
       </c>
       <c r="S40" t="n">
-        <v>26845071</v>
+        <v>8084759</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>-570594</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>-1714782</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>-1000376</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>-4914478</v>
       </c>
       <c r="X40" t="n">
-        <v>234918</v>
+        <v>-356520</v>
       </c>
       <c r="Y40" t="n">
-        <v>101779</v>
+        <v>156241</v>
       </c>
       <c r="Z40" t="n">
-        <v>-2299159</v>
+        <v>560430</v>
       </c>
       <c r="AA40" t="n">
-        <v>5675528</v>
+        <v>217105</v>
       </c>
       <c r="AB40" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -5132,54 +5132,54 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5070</v>
+        <v>436</v>
       </c>
       <c r="D41" t="n">
-        <v>5168</v>
+        <v>449.5</v>
       </c>
       <c r="E41" t="n">
-        <v>4997</v>
+        <v>412.1</v>
       </c>
       <c r="F41" t="n">
-        <v>4906</v>
+        <v>396.05</v>
       </c>
       <c r="G41" t="n">
-        <v>2273627</v>
+        <v>7911000</v>
       </c>
       <c r="H41" t="n">
-        <v>2702229</v>
+        <v>13922400</v>
       </c>
       <c r="I41" t="n">
-        <v>5635</v>
+        <v>492.5</v>
       </c>
       <c r="J41" t="n">
-        <v>4300</v>
+        <v>343</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5187,55 +5187,55 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>40320</v>
+        <v>-683330</v>
       </c>
       <c r="M41" t="n">
-        <v>-122468</v>
+        <v>-4127623</v>
       </c>
       <c r="N41" t="n">
-        <v>166030</v>
+        <v>2298622</v>
       </c>
       <c r="O41" t="n">
-        <v>1613933</v>
+        <v>8649847</v>
       </c>
       <c r="P41" t="n">
-        <v>718402</v>
+        <v>-556866</v>
       </c>
       <c r="Q41" t="n">
-        <v>433901</v>
+        <v>-3731197</v>
       </c>
       <c r="R41" t="n">
-        <v>716299</v>
+        <v>2723249</v>
       </c>
       <c r="S41" t="n">
-        <v>2524668</v>
+        <v>13038703</v>
       </c>
       <c r="T41" t="n">
-        <v>-654000</v>
+        <v>-75000</v>
       </c>
       <c r="U41" t="n">
-        <v>-514223</v>
+        <v>-331000</v>
       </c>
       <c r="V41" t="n">
-        <v>-438311</v>
+        <v>-434000</v>
       </c>
       <c r="W41" t="n">
-        <v>-713363</v>
+        <v>-5185631</v>
       </c>
       <c r="X41" t="n">
-        <v>-24082</v>
+        <v>-51464</v>
       </c>
       <c r="Y41" t="n">
-        <v>-42146</v>
+        <v>-65426</v>
       </c>
       <c r="Z41" t="n">
-        <v>-111958</v>
+        <v>9373</v>
       </c>
       <c r="AA41" t="n">
-        <v>-197372</v>
+        <v>796775</v>
       </c>
       <c r="AB41" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -5254,49 +5254,49 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>56.1</v>
+        <v>5475</v>
       </c>
       <c r="D42" t="n">
-        <v>49.88</v>
+        <v>5292</v>
       </c>
       <c r="E42" t="n">
-        <v>45.82</v>
+        <v>5313</v>
       </c>
       <c r="F42" t="n">
-        <v>39.41</v>
+        <v>5271</v>
       </c>
       <c r="G42" t="n">
-        <v>478118322</v>
+        <v>1735000</v>
       </c>
       <c r="H42" t="n">
-        <v>1093754873</v>
+        <v>2285230</v>
       </c>
       <c r="I42" t="n">
-        <v>56.1</v>
+        <v>5880</v>
       </c>
       <c r="J42" t="n">
-        <v>25.15</v>
+        <v>4630</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5304,55 +5304,55 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>85817793</v>
+        <v>-53222</v>
       </c>
       <c r="M42" t="n">
-        <v>-59168312</v>
+        <v>656900</v>
       </c>
       <c r="N42" t="n">
-        <v>-246655070</v>
+        <v>77693</v>
       </c>
       <c r="O42" t="n">
-        <v>-172216579</v>
+        <v>-83131</v>
       </c>
       <c r="P42" t="n">
-        <v>80703305</v>
+        <v>-133821</v>
       </c>
       <c r="Q42" t="n">
-        <v>-45385303</v>
+        <v>683080</v>
       </c>
       <c r="R42" t="n">
-        <v>-216619387</v>
+        <v>588871</v>
       </c>
       <c r="S42" t="n">
-        <v>-142650779</v>
+        <v>590076</v>
       </c>
       <c r="T42" t="n">
-        <v>5100000</v>
+        <v>83002</v>
       </c>
       <c r="U42" t="n">
-        <v>5217221</v>
+        <v>66976</v>
       </c>
       <c r="V42" t="n">
-        <v>-3025475</v>
+        <v>-260347</v>
       </c>
       <c r="W42" t="n">
-        <v>-2020364</v>
+        <v>-552553</v>
       </c>
       <c r="X42" t="n">
-        <v>14488</v>
+        <v>-2403</v>
       </c>
       <c r="Y42" t="n">
-        <v>-19000230</v>
+        <v>-93156</v>
       </c>
       <c r="Z42" t="n">
-        <v>-27010208</v>
+        <v>-250831</v>
       </c>
       <c r="AA42" t="n">
-        <v>-27545436</v>
+        <v>-120654</v>
       </c>
       <c r="AB42" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -5366,54 +5366,54 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人小幅買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人小幅買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>211</v>
+        <v>26.15</v>
       </c>
       <c r="D43" t="n">
-        <v>207.4</v>
+        <v>23.19</v>
       </c>
       <c r="E43" t="n">
-        <v>205.25</v>
+        <v>22.35</v>
       </c>
       <c r="F43" t="n">
-        <v>197.47</v>
+        <v>20.73</v>
       </c>
       <c r="G43" t="n">
-        <v>11475001</v>
+        <v>717899000</v>
       </c>
       <c r="H43" t="n">
-        <v>15722114</v>
+        <v>573839917</v>
       </c>
       <c r="I43" t="n">
-        <v>231</v>
+        <v>26.15</v>
       </c>
       <c r="J43" t="n">
-        <v>169</v>
+        <v>17.5</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5421,116 +5421,116 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>638592</v>
+        <v>-112395402</v>
       </c>
       <c r="M43" t="n">
-        <v>805083</v>
+        <v>-45567724</v>
       </c>
       <c r="N43" t="n">
-        <v>-4178927</v>
+        <v>-302696130</v>
       </c>
       <c r="O43" t="n">
-        <v>2818703</v>
+        <v>-109753488</v>
       </c>
       <c r="P43" t="n">
-        <v>238712</v>
+        <v>-110354526</v>
       </c>
       <c r="Q43" t="n">
-        <v>306561</v>
+        <v>-44853879</v>
       </c>
       <c r="R43" t="n">
-        <v>-3806044</v>
+        <v>-299305020</v>
       </c>
       <c r="S43" t="n">
-        <v>1881767</v>
+        <v>-110957767</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="U43" t="n">
-        <v>2000</v>
+        <v>193252</v>
       </c>
       <c r="V43" t="n">
-        <v>2000</v>
+        <v>311198</v>
       </c>
       <c r="W43" t="n">
-        <v>-55316</v>
+        <v>334507</v>
       </c>
       <c r="X43" t="n">
-        <v>399880</v>
+        <v>-2139876</v>
       </c>
       <c r="Y43" t="n">
-        <v>496522</v>
+        <v>-907097</v>
       </c>
       <c r="Z43" t="n">
-        <v>-374883</v>
+        <v>-3702308</v>
       </c>
       <c r="AA43" t="n">
-        <v>992252</v>
+        <v>869772</v>
       </c>
       <c r="AB43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>790</v>
+        <v>4860</v>
       </c>
       <c r="D44" t="n">
-        <v>726.4</v>
+        <v>5082</v>
       </c>
       <c r="E44" t="n">
-        <v>654.1</v>
+        <v>5029.5</v>
       </c>
       <c r="F44" t="n">
-        <v>531.88</v>
+        <v>4912.5</v>
       </c>
       <c r="G44" t="n">
-        <v>32143661</v>
+        <v>1861000</v>
       </c>
       <c r="H44" t="n">
-        <v>28104227</v>
+        <v>2490977</v>
       </c>
       <c r="I44" t="n">
-        <v>811</v>
+        <v>5635</v>
       </c>
       <c r="J44" t="n">
-        <v>331</v>
+        <v>4300</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5538,116 +5538,116 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2783607</v>
+        <v>40320</v>
       </c>
       <c r="M44" t="n">
-        <v>-2766212</v>
+        <v>-122468</v>
       </c>
       <c r="N44" t="n">
-        <v>-7325603</v>
+        <v>166030</v>
       </c>
       <c r="O44" t="n">
-        <v>2033666</v>
+        <v>1613933</v>
       </c>
       <c r="P44" t="n">
-        <v>2259367</v>
+        <v>718402</v>
       </c>
       <c r="Q44" t="n">
-        <v>-4591005</v>
+        <v>433901</v>
       </c>
       <c r="R44" t="n">
-        <v>-11733299</v>
+        <v>716299</v>
       </c>
       <c r="S44" t="n">
-        <v>-24723912</v>
+        <v>2524668</v>
       </c>
       <c r="T44" t="n">
-        <v>-13000</v>
+        <v>-654000</v>
       </c>
       <c r="U44" t="n">
-        <v>291532</v>
+        <v>-514223</v>
       </c>
       <c r="V44" t="n">
-        <v>456740</v>
+        <v>-438311</v>
       </c>
       <c r="W44" t="n">
-        <v>21227740</v>
+        <v>-713363</v>
       </c>
       <c r="X44" t="n">
-        <v>537240</v>
+        <v>-24082</v>
       </c>
       <c r="Y44" t="n">
-        <v>1533261</v>
+        <v>-42146</v>
       </c>
       <c r="Z44" t="n">
-        <v>3950956</v>
+        <v>-111958</v>
       </c>
       <c r="AA44" t="n">
-        <v>5529838</v>
+        <v>-197372</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>144.5</v>
+        <v>238.5</v>
       </c>
       <c r="D45" t="n">
-        <v>137.1</v>
+        <v>219.8</v>
       </c>
       <c r="E45" t="n">
-        <v>124.75</v>
+        <v>210</v>
       </c>
       <c r="F45" t="n">
-        <v>110.34</v>
+        <v>195.62</v>
       </c>
       <c r="G45" t="n">
-        <v>366515715</v>
+        <v>19177000</v>
       </c>
       <c r="H45" t="n">
-        <v>339579178</v>
+        <v>13984200</v>
       </c>
       <c r="I45" t="n">
-        <v>151</v>
+        <v>249.5</v>
       </c>
       <c r="J45" t="n">
-        <v>79.40000000000001</v>
+        <v>152</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5655,64 +5655,64 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-17686627</v>
+        <v>-1234497</v>
       </c>
       <c r="M45" t="n">
-        <v>-105850437</v>
+        <v>349950</v>
       </c>
       <c r="N45" t="n">
-        <v>-51398250</v>
+        <v>-1644077</v>
       </c>
       <c r="O45" t="n">
-        <v>-72620473</v>
+        <v>2368303</v>
       </c>
       <c r="P45" t="n">
-        <v>20426659</v>
+        <v>-1242784</v>
       </c>
       <c r="Q45" t="n">
-        <v>-7732185</v>
+        <v>172281</v>
       </c>
       <c r="R45" t="n">
-        <v>85668280</v>
+        <v>-1748758</v>
       </c>
       <c r="S45" t="n">
-        <v>81129521</v>
+        <v>2128596</v>
       </c>
       <c r="T45" t="n">
-        <v>-38025561</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>-101199533</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>-139902383</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>-158631125</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>-87725</v>
+        <v>8287</v>
       </c>
       <c r="Y45" t="n">
-        <v>3081281</v>
+        <v>177669</v>
       </c>
       <c r="Z45" t="n">
-        <v>2835853</v>
+        <v>104681</v>
       </c>
       <c r="AA45" t="n">
-        <v>4881131</v>
+        <v>239707</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -5722,49 +5722,49 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2510</v>
+        <v>209.5</v>
       </c>
       <c r="D46" t="n">
-        <v>2523</v>
+        <v>207.7</v>
       </c>
       <c r="E46" t="n">
-        <v>2485</v>
+        <v>207.35</v>
       </c>
       <c r="F46" t="n">
-        <v>2499.5</v>
+        <v>199.1</v>
       </c>
       <c r="G46" t="n">
-        <v>3363120</v>
+        <v>14218000</v>
       </c>
       <c r="H46" t="n">
-        <v>4491058</v>
+        <v>14445626</v>
       </c>
       <c r="I46" t="n">
-        <v>2695</v>
+        <v>231</v>
       </c>
       <c r="J46" t="n">
-        <v>2305</v>
+        <v>173</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5772,55 +5772,55 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>324990</v>
+        <v>638592</v>
       </c>
       <c r="M46" t="n">
-        <v>-446327</v>
+        <v>805083</v>
       </c>
       <c r="N46" t="n">
-        <v>291378</v>
+        <v>-4178927</v>
       </c>
       <c r="O46" t="n">
-        <v>296867</v>
+        <v>2818703</v>
       </c>
       <c r="P46" t="n">
-        <v>356765</v>
+        <v>238712</v>
       </c>
       <c r="Q46" t="n">
-        <v>193259</v>
+        <v>306561</v>
       </c>
       <c r="R46" t="n">
-        <v>717536</v>
+        <v>-3806044</v>
       </c>
       <c r="S46" t="n">
-        <v>1053276</v>
+        <v>1881767</v>
       </c>
       <c r="T46" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>-482677</v>
+        <v>2000</v>
       </c>
       <c r="V46" t="n">
-        <v>-254072</v>
+        <v>2000</v>
       </c>
       <c r="W46" t="n">
-        <v>-361630</v>
+        <v>-55316</v>
       </c>
       <c r="X46" t="n">
-        <v>-64775</v>
+        <v>399880</v>
       </c>
       <c r="Y46" t="n">
-        <v>-156909</v>
+        <v>496522</v>
       </c>
       <c r="Z46" t="n">
-        <v>-172086</v>
+        <v>-374883</v>
       </c>
       <c r="AA46" t="n">
-        <v>-394779</v>
+        <v>992252</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -5834,54 +5834,54 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23.8</v>
+        <v>82.5</v>
       </c>
       <c r="D47" t="n">
-        <v>22.36</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>21.65</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>20.31</v>
+        <v>81.17</v>
       </c>
       <c r="G47" t="n">
-        <v>564845158</v>
+        <v>14116000</v>
       </c>
       <c r="H47" t="n">
-        <v>593932462</v>
+        <v>15055657</v>
       </c>
       <c r="I47" t="n">
-        <v>25.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>17.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5889,55 +5889,55 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-112395402</v>
+        <v>525384</v>
       </c>
       <c r="M47" t="n">
-        <v>-45567724</v>
+        <v>2970153</v>
       </c>
       <c r="N47" t="n">
-        <v>-302696130</v>
+        <v>-83282</v>
       </c>
       <c r="O47" t="n">
-        <v>-109753488</v>
+        <v>4290817</v>
       </c>
       <c r="P47" t="n">
-        <v>-110354526</v>
+        <v>244033</v>
       </c>
       <c r="Q47" t="n">
-        <v>-44853879</v>
+        <v>2393134</v>
       </c>
       <c r="R47" t="n">
-        <v>-299305020</v>
+        <v>-482721</v>
       </c>
       <c r="S47" t="n">
-        <v>-110957767</v>
+        <v>4206293</v>
       </c>
       <c r="T47" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>193252</v>
+        <v>-1000</v>
       </c>
       <c r="V47" t="n">
-        <v>311198</v>
+        <v>-1000</v>
       </c>
       <c r="W47" t="n">
-        <v>334507</v>
+        <v>-1000</v>
       </c>
       <c r="X47" t="n">
-        <v>-2139876</v>
+        <v>281351</v>
       </c>
       <c r="Y47" t="n">
-        <v>-907097</v>
+        <v>578019</v>
       </c>
       <c r="Z47" t="n">
-        <v>-3702308</v>
+        <v>400439</v>
       </c>
       <c r="AA47" t="n">
-        <v>869772</v>
+        <v>85524</v>
       </c>
       <c r="AB47" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -5956,49 +5956,49 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人小幅賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人小幅賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>548</v>
+        <v>10.5</v>
       </c>
       <c r="D48" t="n">
-        <v>524.2</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>498.3</v>
+        <v>8.01</v>
       </c>
       <c r="F48" t="n">
-        <v>456.85</v>
+        <v>6.86</v>
       </c>
       <c r="G48" t="n">
-        <v>12673360</v>
+        <v>270390000</v>
       </c>
       <c r="H48" t="n">
-        <v>25979568</v>
+        <v>231371410</v>
       </c>
       <c r="I48" t="n">
-        <v>568</v>
+        <v>10.6</v>
       </c>
       <c r="J48" t="n">
-        <v>372</v>
+        <v>5.55</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6006,55 +6006,55 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>278726</v>
+        <v>17102138</v>
       </c>
       <c r="M48" t="n">
-        <v>-1703916</v>
+        <v>-10102801</v>
       </c>
       <c r="N48" t="n">
-        <v>-3261558</v>
+        <v>-1903688</v>
       </c>
       <c r="O48" t="n">
-        <v>10240061</v>
+        <v>32520599</v>
       </c>
       <c r="P48" t="n">
-        <v>1967821</v>
+        <v>16867220</v>
       </c>
       <c r="Q48" t="n">
-        <v>3439317</v>
+        <v>-10204580</v>
       </c>
       <c r="R48" t="n">
-        <v>3959418</v>
+        <v>395471</v>
       </c>
       <c r="S48" t="n">
-        <v>-441163</v>
+        <v>26845071</v>
       </c>
       <c r="T48" t="n">
-        <v>-1331000</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>-4785592</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>-6851592</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>10969976</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>-358095</v>
+        <v>234918</v>
       </c>
       <c r="Y48" t="n">
-        <v>-357641</v>
+        <v>101779</v>
       </c>
       <c r="Z48" t="n">
-        <v>-369384</v>
+        <v>-2299159</v>
       </c>
       <c r="AA48" t="n">
-        <v>-288752</v>
+        <v>5675528</v>
       </c>
       <c r="AB48" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -6068,54 +6068,54 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>39.4</v>
+        <v>862</v>
       </c>
       <c r="D49" t="n">
-        <v>39.03</v>
+        <v>874</v>
       </c>
       <c r="E49" t="n">
-        <v>39.15</v>
+        <v>881.1</v>
       </c>
       <c r="F49" t="n">
-        <v>39.7</v>
+        <v>873.1</v>
       </c>
       <c r="G49" t="n">
-        <v>143898</v>
+        <v>13344000</v>
       </c>
       <c r="H49" t="n">
-        <v>157896</v>
+        <v>19199854</v>
       </c>
       <c r="I49" t="n">
-        <v>42.45</v>
+        <v>1025</v>
       </c>
       <c r="J49" t="n">
-        <v>38.5</v>
+        <v>765</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6123,55 +6123,55 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>41000</v>
+        <v>6489767</v>
       </c>
       <c r="M49" t="n">
-        <v>-47024</v>
+        <v>-2035790</v>
       </c>
       <c r="N49" t="n">
-        <v>-69572</v>
+        <v>2257312</v>
       </c>
       <c r="O49" t="n">
-        <v>-172104</v>
+        <v>-2252248</v>
       </c>
       <c r="P49" t="n">
-        <v>42000</v>
+        <v>5749529</v>
       </c>
       <c r="Q49" t="n">
-        <v>-43024</v>
+        <v>1761213</v>
       </c>
       <c r="R49" t="n">
-        <v>-66001</v>
+        <v>7285342</v>
       </c>
       <c r="S49" t="n">
-        <v>-168001</v>
+        <v>2700083</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>764000</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>-3636000</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>-4848000</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>-4370000</v>
       </c>
       <c r="X49" t="n">
-        <v>-1000</v>
+        <v>-23762</v>
       </c>
       <c r="Y49" t="n">
-        <v>-4000</v>
+        <v>-161003</v>
       </c>
       <c r="Z49" t="n">
-        <v>-3571</v>
+        <v>-180030</v>
       </c>
       <c r="AA49" t="n">
-        <v>-4103</v>
+        <v>-582331</v>
       </c>
       <c r="AB49" t="n">
-        <v>-25</v>
+        <v>10</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
@@ -6185,54 +6185,54 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>5日法人小幅賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>33.75</v>
+        <v>846</v>
       </c>
       <c r="D50" t="n">
-        <v>33.01</v>
+        <v>763.4</v>
       </c>
       <c r="E50" t="n">
-        <v>34.1</v>
+        <v>689</v>
       </c>
       <c r="F50" t="n">
-        <v>36.06</v>
+        <v>556.75</v>
       </c>
       <c r="G50" t="n">
-        <v>12317380</v>
+        <v>21537000</v>
       </c>
       <c r="H50" t="n">
-        <v>10046723</v>
+        <v>26520041</v>
       </c>
       <c r="I50" t="n">
-        <v>44.05</v>
+        <v>847</v>
       </c>
       <c r="J50" t="n">
-        <v>31.1</v>
+        <v>331</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6240,55 +6240,55 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>401986</v>
+        <v>2783607</v>
       </c>
       <c r="M50" t="n">
-        <v>-968923</v>
+        <v>-2766212</v>
       </c>
       <c r="N50" t="n">
-        <v>-1382569</v>
+        <v>-7325603</v>
       </c>
       <c r="O50" t="n">
-        <v>-9625536</v>
+        <v>2033666</v>
       </c>
       <c r="P50" t="n">
-        <v>403001</v>
+        <v>2259367</v>
       </c>
       <c r="Q50" t="n">
-        <v>-710013</v>
+        <v>-4591005</v>
       </c>
       <c r="R50" t="n">
-        <v>-1258658</v>
+        <v>-11733299</v>
       </c>
       <c r="S50" t="n">
-        <v>-9492626</v>
+        <v>-24723912</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>291532</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>456740</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>21227740</v>
       </c>
       <c r="X50" t="n">
-        <v>-1015</v>
+        <v>537240</v>
       </c>
       <c r="Y50" t="n">
-        <v>-258910</v>
+        <v>1533261</v>
       </c>
       <c r="Z50" t="n">
-        <v>-123911</v>
+        <v>3950956</v>
       </c>
       <c r="AA50" t="n">
-        <v>-132910</v>
+        <v>5529838</v>
       </c>
       <c r="AB50" t="n">
-        <v>-25</v>
+        <v>5</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -6302,54 +6302,54 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>89.5</v>
+        <v>56.2</v>
       </c>
       <c r="D51" t="n">
-        <v>86.42</v>
+        <v>51.98</v>
       </c>
       <c r="E51" t="n">
-        <v>80.98999999999999</v>
+        <v>47.69</v>
       </c>
       <c r="F51" t="n">
-        <v>71.8</v>
+        <v>40.86</v>
       </c>
       <c r="G51" t="n">
-        <v>48207223</v>
+        <v>1153961000</v>
       </c>
       <c r="H51" t="n">
-        <v>44364436</v>
+        <v>1031901630</v>
       </c>
       <c r="I51" t="n">
-        <v>94.90000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="J51" t="n">
-        <v>58.1</v>
+        <v>26.8</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6357,55 +6357,55 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-1055982</v>
+        <v>85817793</v>
       </c>
       <c r="M51" t="n">
-        <v>-12178704</v>
+        <v>-59168312</v>
       </c>
       <c r="N51" t="n">
-        <v>-7168837</v>
+        <v>-246655070</v>
       </c>
       <c r="O51" t="n">
-        <v>2700112</v>
+        <v>-172216579</v>
       </c>
       <c r="P51" t="n">
-        <v>-1636146</v>
+        <v>80703305</v>
       </c>
       <c r="Q51" t="n">
-        <v>-11349452</v>
+        <v>-45385303</v>
       </c>
       <c r="R51" t="n">
-        <v>-6189868</v>
+        <v>-216619387</v>
       </c>
       <c r="S51" t="n">
-        <v>1485814</v>
+        <v>-142650779</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>5100000</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>5217221</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>-3025475</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>-2020364</v>
       </c>
       <c r="X51" t="n">
-        <v>580164</v>
+        <v>14488</v>
       </c>
       <c r="Y51" t="n">
-        <v>-829252</v>
+        <v>-19000230</v>
       </c>
       <c r="Z51" t="n">
-        <v>-978969</v>
+        <v>-27010208</v>
       </c>
       <c r="AA51" t="n">
-        <v>1214298</v>
+        <v>-27545436</v>
       </c>
       <c r="AB51" t="n">
-        <v>-25</v>
+        <v>5</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -6424,49 +6424,49 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>282</v>
+        <v>2425</v>
       </c>
       <c r="D52" t="n">
-        <v>278.4</v>
+        <v>2484</v>
       </c>
       <c r="E52" t="n">
-        <v>273.75</v>
+        <v>2488.5</v>
       </c>
       <c r="F52" t="n">
-        <v>262.2</v>
+        <v>2496</v>
       </c>
       <c r="G52" t="n">
-        <v>72392478</v>
+        <v>3595000</v>
       </c>
       <c r="H52" t="n">
-        <v>88077285</v>
+        <v>4472284</v>
       </c>
       <c r="I52" t="n">
-        <v>305.5</v>
+        <v>2695</v>
       </c>
       <c r="J52" t="n">
-        <v>233.5</v>
+        <v>2305</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6474,55 +6474,55 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-13602165</v>
+        <v>324990</v>
       </c>
       <c r="M52" t="n">
-        <v>-24542154</v>
+        <v>-446327</v>
       </c>
       <c r="N52" t="n">
-        <v>-52766993</v>
+        <v>291378</v>
       </c>
       <c r="O52" t="n">
-        <v>-6377479</v>
+        <v>296867</v>
       </c>
       <c r="P52" t="n">
-        <v>-13708813</v>
+        <v>356765</v>
       </c>
       <c r="Q52" t="n">
-        <v>-19162159</v>
+        <v>193259</v>
       </c>
       <c r="R52" t="n">
-        <v>-38360704</v>
+        <v>717536</v>
       </c>
       <c r="S52" t="n">
-        <v>3177875</v>
+        <v>1053276</v>
       </c>
       <c r="T52" t="n">
-        <v>25000</v>
+        <v>33000</v>
       </c>
       <c r="U52" t="n">
-        <v>-3363000</v>
+        <v>-482677</v>
       </c>
       <c r="V52" t="n">
-        <v>-10645000</v>
+        <v>-254072</v>
       </c>
       <c r="W52" t="n">
-        <v>-6615000</v>
+        <v>-361630</v>
       </c>
       <c r="X52" t="n">
-        <v>81648</v>
+        <v>-64775</v>
       </c>
       <c r="Y52" t="n">
-        <v>-2016995</v>
+        <v>-156909</v>
       </c>
       <c r="Z52" t="n">
-        <v>-3761289</v>
+        <v>-172086</v>
       </c>
       <c r="AA52" t="n">
-        <v>-2940354</v>
+        <v>-394779</v>
       </c>
       <c r="AB52" t="n">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -6536,54 +6536,54 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7769.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7515</v>
+        <v>92</v>
       </c>
       <c r="D53" t="n">
-        <v>7835</v>
+        <v>87.34</v>
       </c>
       <c r="E53" t="n">
-        <v>7580.5</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>7027.25</v>
+        <v>73.28</v>
       </c>
       <c r="G53" t="n">
-        <v>1264343</v>
+        <v>49559000</v>
       </c>
       <c r="H53" t="n">
-        <v>1056621</v>
+        <v>49070206</v>
       </c>
       <c r="I53" t="n">
-        <v>8465</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>5370</v>
+        <v>58.1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6591,55 +6591,55 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-372998</v>
+        <v>-1055982</v>
       </c>
       <c r="M53" t="n">
-        <v>-43384</v>
+        <v>-12178704</v>
       </c>
       <c r="N53" t="n">
-        <v>-157277</v>
+        <v>-7168837</v>
       </c>
       <c r="O53" t="n">
-        <v>-130635</v>
+        <v>2700112</v>
       </c>
       <c r="P53" t="n">
-        <v>-409313</v>
+        <v>-1636146</v>
       </c>
       <c r="Q53" t="n">
-        <v>-624960</v>
+        <v>-11349452</v>
       </c>
       <c r="R53" t="n">
-        <v>-695082</v>
+        <v>-6189868</v>
       </c>
       <c r="S53" t="n">
-        <v>-519645</v>
+        <v>1485814</v>
       </c>
       <c r="T53" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>590504</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>541853</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>401853</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>-685</v>
+        <v>580164</v>
       </c>
       <c r="Y53" t="n">
-        <v>-8928</v>
+        <v>-829252</v>
       </c>
       <c r="Z53" t="n">
-        <v>-4048</v>
+        <v>-978969</v>
       </c>
       <c r="AA53" t="n">
-        <v>-12843</v>
+        <v>1214298</v>
       </c>
       <c r="AB53" t="n">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -6653,54 +6653,54 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>57.2</v>
+        <v>39.65</v>
       </c>
       <c r="D54" t="n">
-        <v>56.52</v>
+        <v>39.12</v>
       </c>
       <c r="E54" t="n">
-        <v>54.54</v>
+        <v>39.18</v>
       </c>
       <c r="F54" t="n">
-        <v>52.29</v>
+        <v>39.62</v>
       </c>
       <c r="G54" t="n">
-        <v>11246181</v>
+        <v>88000</v>
       </c>
       <c r="H54" t="n">
-        <v>12250047</v>
+        <v>158310</v>
       </c>
       <c r="I54" t="n">
-        <v>61.4</v>
+        <v>42.45</v>
       </c>
       <c r="J54" t="n">
-        <v>45.45</v>
+        <v>38.5</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -6708,28 +6708,28 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-3130536</v>
+        <v>41000</v>
       </c>
       <c r="M54" t="n">
-        <v>-3121889</v>
+        <v>-47024</v>
       </c>
       <c r="N54" t="n">
-        <v>-2012275</v>
+        <v>-69572</v>
       </c>
       <c r="O54" t="n">
-        <v>12234349</v>
+        <v>-172104</v>
       </c>
       <c r="P54" t="n">
-        <v>-3219650</v>
+        <v>42000</v>
       </c>
       <c r="Q54" t="n">
-        <v>-3438638</v>
+        <v>-43024</v>
       </c>
       <c r="R54" t="n">
-        <v>-2331789</v>
+        <v>-66001</v>
       </c>
       <c r="S54" t="n">
-        <v>11018660</v>
+        <v>-168001</v>
       </c>
       <c r="T54" t="n">
         <v>0</v>
@@ -6744,19 +6744,19 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>89114</v>
+        <v>-1000</v>
       </c>
       <c r="Y54" t="n">
-        <v>316749</v>
+        <v>-4000</v>
       </c>
       <c r="Z54" t="n">
-        <v>319514</v>
+        <v>-3571</v>
       </c>
       <c r="AA54" t="n">
-        <v>1215689</v>
+        <v>-4103</v>
       </c>
       <c r="AB54" t="n">
-        <v>-35</v>
+        <v>-25</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>5日法人小幅賣超</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -6831,10 +6831,10 @@
         <v>-5119788</v>
       </c>
       <c r="N55" t="n">
-        <v>-4575742</v>
+        <v>-331680</v>
       </c>
       <c r="O55" t="n">
-        <v>-193549</v>
+        <v>4050513</v>
       </c>
       <c r="P55" t="n">
         <v>516617</v>
@@ -6843,10 +6843,10 @@
         <v>-3090648</v>
       </c>
       <c r="R55" t="n">
-        <v>-2909949</v>
+        <v>357439</v>
       </c>
       <c r="S55" t="n">
-        <v>-4937545</v>
+        <v>-1670157</v>
       </c>
       <c r="T55" t="n">
         <v>-26441</v>
@@ -6855,10 +6855,10 @@
         <v>-1574325</v>
       </c>
       <c r="V55" t="n">
-        <v>-1210766</v>
+        <v>-1040767</v>
       </c>
       <c r="W55" t="n">
-        <v>3170501</v>
+        <v>3340500</v>
       </c>
       <c r="X55" t="n">
         <v>110068</v>
@@ -6867,13 +6867,13 @@
         <v>-454815</v>
       </c>
       <c r="Z55" t="n">
-        <v>-455027</v>
+        <v>351648</v>
       </c>
       <c r="AA55" t="n">
-        <v>1573495</v>
+        <v>2380170</v>
       </c>
       <c r="AB55" t="n">
-        <v>-45</v>
+        <v>-40</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -6892,49 +6892,49 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2002.TW</t>
+          <t>7769.TW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>19.1</v>
+        <v>7175</v>
       </c>
       <c r="D56" t="n">
-        <v>19.13</v>
+        <v>7690</v>
       </c>
       <c r="E56" t="n">
-        <v>18.82</v>
+        <v>7638</v>
       </c>
       <c r="F56" t="n">
-        <v>18.67</v>
+        <v>7106</v>
       </c>
       <c r="G56" t="n">
-        <v>66981679</v>
+        <v>1090000</v>
       </c>
       <c r="H56" t="n">
-        <v>122093397</v>
+        <v>1215249</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>8465</v>
       </c>
       <c r="J56" t="n">
-        <v>18.05</v>
+        <v>5435</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -6942,55 +6942,55 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-6821957</v>
+        <v>-372998</v>
       </c>
       <c r="M56" t="n">
-        <v>-19778248</v>
+        <v>-43384</v>
       </c>
       <c r="N56" t="n">
-        <v>-73161846</v>
+        <v>-157277</v>
       </c>
       <c r="O56" t="n">
-        <v>-80580628</v>
+        <v>-130635</v>
       </c>
       <c r="P56" t="n">
-        <v>-7595418</v>
+        <v>-409313</v>
       </c>
       <c r="Q56" t="n">
-        <v>-19948956</v>
+        <v>-624960</v>
       </c>
       <c r="R56" t="n">
-        <v>-71816977</v>
+        <v>-695082</v>
       </c>
       <c r="S56" t="n">
-        <v>-84800855</v>
+        <v>-519645</v>
       </c>
       <c r="T56" t="n">
-        <v>5000</v>
+        <v>37000</v>
       </c>
       <c r="U56" t="n">
-        <v>-8475</v>
+        <v>590504</v>
       </c>
       <c r="V56" t="n">
-        <v>21525</v>
+        <v>541853</v>
       </c>
       <c r="W56" t="n">
-        <v>1075525</v>
+        <v>401853</v>
       </c>
       <c r="X56" t="n">
-        <v>768461</v>
+        <v>-685</v>
       </c>
       <c r="Y56" t="n">
-        <v>179183</v>
+        <v>-8928</v>
       </c>
       <c r="Z56" t="n">
-        <v>-1366394</v>
+        <v>-4048</v>
       </c>
       <c r="AA56" t="n">
-        <v>3144702</v>
+        <v>-12843</v>
       </c>
       <c r="AB56" t="n">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -7009,49 +7009,49 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>40.6</v>
+        <v>141.5</v>
       </c>
       <c r="D57" t="n">
-        <v>38.92</v>
+        <v>143.5</v>
       </c>
       <c r="E57" t="n">
-        <v>35.03</v>
+        <v>131.1</v>
       </c>
       <c r="F57" t="n">
-        <v>31.79</v>
+        <v>116.51</v>
       </c>
       <c r="G57" t="n">
-        <v>120797558</v>
+        <v>375458000</v>
       </c>
       <c r="H57" t="n">
-        <v>152210323</v>
+        <v>345958172</v>
       </c>
       <c r="I57" t="n">
-        <v>42</v>
+        <v>155.5</v>
       </c>
       <c r="J57" t="n">
-        <v>26.65</v>
+        <v>87.8</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7059,55 +7059,55 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-5247740</v>
+        <v>-17686627</v>
       </c>
       <c r="M57" t="n">
-        <v>-18740272</v>
+        <v>-105850437</v>
       </c>
       <c r="N57" t="n">
-        <v>-15756947</v>
+        <v>-51398250</v>
       </c>
       <c r="O57" t="n">
-        <v>61167815</v>
+        <v>-72620473</v>
       </c>
       <c r="P57" t="n">
-        <v>-6375791</v>
+        <v>20426659</v>
       </c>
       <c r="Q57" t="n">
-        <v>-20229217</v>
+        <v>-7732185</v>
       </c>
       <c r="R57" t="n">
-        <v>-13311206</v>
+        <v>85668280</v>
       </c>
       <c r="S57" t="n">
-        <v>73546299</v>
+        <v>81129521</v>
       </c>
       <c r="T57" t="n">
-        <v>593000</v>
+        <v>-38025561</v>
       </c>
       <c r="U57" t="n">
-        <v>593000</v>
+        <v>-101199533</v>
       </c>
       <c r="V57" t="n">
-        <v>-2179000</v>
+        <v>-139902383</v>
       </c>
       <c r="W57" t="n">
-        <v>-17161000</v>
+        <v>-158631125</v>
       </c>
       <c r="X57" t="n">
-        <v>535051</v>
+        <v>-87725</v>
       </c>
       <c r="Y57" t="n">
-        <v>895945</v>
+        <v>3081281</v>
       </c>
       <c r="Z57" t="n">
-        <v>-266741</v>
+        <v>2835853</v>
       </c>
       <c r="AA57" t="n">
-        <v>4782516</v>
+        <v>4881131</v>
       </c>
       <c r="AB57" t="n">
-        <v>-55</v>
+        <v>-40</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -7121,54 +7121,54 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1060</v>
+        <v>520</v>
       </c>
       <c r="D58" t="n">
-        <v>1092</v>
+        <v>520.2</v>
       </c>
       <c r="E58" t="n">
-        <v>1071.2</v>
+        <v>509.45</v>
       </c>
       <c r="F58" t="n">
-        <v>1058.6</v>
+        <v>461.52</v>
       </c>
       <c r="G58" t="n">
-        <v>2924000</v>
+        <v>11337000</v>
       </c>
       <c r="H58" t="n">
-        <v>4078000</v>
+        <v>19866157</v>
       </c>
       <c r="I58" t="n">
-        <v>1300</v>
+        <v>568</v>
       </c>
       <c r="J58" t="n">
-        <v>865</v>
+        <v>372</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7176,55 +7176,55 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-420978</v>
+        <v>278726</v>
       </c>
       <c r="M58" t="n">
-        <v>-1582664</v>
+        <v>-1703916</v>
       </c>
       <c r="N58" t="n">
-        <v>-3053059</v>
+        <v>-3261558</v>
       </c>
       <c r="O58" t="n">
-        <v>-4332525</v>
+        <v>10240061</v>
       </c>
       <c r="P58" t="n">
-        <v>60766</v>
+        <v>1967821</v>
       </c>
       <c r="Q58" t="n">
-        <v>-94694</v>
+        <v>3439317</v>
       </c>
       <c r="R58" t="n">
-        <v>-285732</v>
+        <v>3959418</v>
       </c>
       <c r="S58" t="n">
-        <v>-2406108</v>
+        <v>-441163</v>
       </c>
       <c r="T58" t="n">
-        <v>-478000</v>
+        <v>-1331000</v>
       </c>
       <c r="U58" t="n">
-        <v>-1475050</v>
+        <v>-4785592</v>
       </c>
       <c r="V58" t="n">
-        <v>-2737050</v>
+        <v>-6851592</v>
       </c>
       <c r="W58" t="n">
-        <v>-1947050</v>
+        <v>10969976</v>
       </c>
       <c r="X58" t="n">
-        <v>-3744</v>
+        <v>-358095</v>
       </c>
       <c r="Y58" t="n">
-        <v>-12920</v>
+        <v>-357641</v>
       </c>
       <c r="Z58" t="n">
-        <v>-30277</v>
+        <v>-369384</v>
       </c>
       <c r="AA58" t="n">
-        <v>20633</v>
+        <v>-288752</v>
       </c>
       <c r="AB58" t="n">
-        <v>-70</v>
+        <v>-50</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -7243,49 +7243,49 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>601</v>
+        <v>41.3</v>
       </c>
       <c r="D59" t="n">
-        <v>618.4</v>
+        <v>39.18</v>
       </c>
       <c r="E59" t="n">
-        <v>572.8</v>
+        <v>36.38</v>
       </c>
       <c r="F59" t="n">
-        <v>553.65</v>
+        <v>32.45</v>
       </c>
       <c r="G59" t="n">
-        <v>25834856</v>
+        <v>134456000</v>
       </c>
       <c r="H59" t="n">
-        <v>34901676</v>
+        <v>137047937</v>
       </c>
       <c r="I59" t="n">
-        <v>669</v>
+        <v>43.5</v>
       </c>
       <c r="J59" t="n">
-        <v>465</v>
+        <v>26.65</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -7293,55 +7293,55 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-2269811</v>
+        <v>-5247740</v>
       </c>
       <c r="M59" t="n">
-        <v>-18147118</v>
+        <v>-18740272</v>
       </c>
       <c r="N59" t="n">
-        <v>-19887300</v>
+        <v>-15756947</v>
       </c>
       <c r="O59" t="n">
-        <v>-19512205</v>
+        <v>61167815</v>
       </c>
       <c r="P59" t="n">
-        <v>2284150</v>
+        <v>-6375791</v>
       </c>
       <c r="Q59" t="n">
-        <v>-10178887</v>
+        <v>-20229217</v>
       </c>
       <c r="R59" t="n">
-        <v>-10813423</v>
+        <v>-13311206</v>
       </c>
       <c r="S59" t="n">
-        <v>-13545404</v>
+        <v>73546299</v>
       </c>
       <c r="T59" t="n">
-        <v>-4656953</v>
+        <v>593000</v>
       </c>
       <c r="U59" t="n">
-        <v>-8031843</v>
+        <v>593000</v>
       </c>
       <c r="V59" t="n">
-        <v>-8748601</v>
+        <v>-2179000</v>
       </c>
       <c r="W59" t="n">
-        <v>-5686221</v>
+        <v>-17161000</v>
       </c>
       <c r="X59" t="n">
-        <v>102992</v>
+        <v>535051</v>
       </c>
       <c r="Y59" t="n">
-        <v>63612</v>
+        <v>895945</v>
       </c>
       <c r="Z59" t="n">
-        <v>-325276</v>
+        <v>-266741</v>
       </c>
       <c r="AA59" t="n">
-        <v>-280580</v>
+        <v>4782516</v>
       </c>
       <c r="AB59" t="n">
-        <v>-70</v>
+        <v>-55</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -7355,54 +7355,54 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>72.59999999999999</v>
+        <v>18.95</v>
       </c>
       <c r="D60" t="n">
-        <v>73.45999999999999</v>
+        <v>19.02</v>
       </c>
       <c r="E60" t="n">
-        <v>73</v>
+        <v>18.9</v>
       </c>
       <c r="F60" t="n">
-        <v>70.81</v>
+        <v>18.69</v>
       </c>
       <c r="G60" t="n">
-        <v>21901665</v>
+        <v>70047000</v>
       </c>
       <c r="H60" t="n">
-        <v>28640442</v>
+        <v>79737553</v>
       </c>
       <c r="I60" t="n">
-        <v>78.59999999999999</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>64.7</v>
+        <v>18.05</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -7410,55 +7410,55 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-3353884</v>
+        <v>-6821957</v>
       </c>
       <c r="M60" t="n">
-        <v>-1927633</v>
+        <v>-19778248</v>
       </c>
       <c r="N60" t="n">
-        <v>-5620421</v>
+        <v>-73161846</v>
       </c>
       <c r="O60" t="n">
-        <v>-5122068</v>
+        <v>-80580628</v>
       </c>
       <c r="P60" t="n">
-        <v>-3281171</v>
+        <v>-7595418</v>
       </c>
       <c r="Q60" t="n">
-        <v>-1786681</v>
+        <v>-19948956</v>
       </c>
       <c r="R60" t="n">
-        <v>-5657186</v>
+        <v>-71816977</v>
       </c>
       <c r="S60" t="n">
-        <v>-7066444</v>
+        <v>-84800855</v>
       </c>
       <c r="T60" t="n">
-        <v>-3000</v>
+        <v>5000</v>
       </c>
       <c r="U60" t="n">
-        <v>-3000</v>
+        <v>-8475</v>
       </c>
       <c r="V60" t="n">
-        <v>-3000</v>
+        <v>21525</v>
       </c>
       <c r="W60" t="n">
-        <v>-14000</v>
+        <v>1075525</v>
       </c>
       <c r="X60" t="n">
-        <v>-69713</v>
+        <v>768461</v>
       </c>
       <c r="Y60" t="n">
-        <v>-137952</v>
+        <v>179183</v>
       </c>
       <c r="Z60" t="n">
-        <v>39765</v>
+        <v>-1366394</v>
       </c>
       <c r="AA60" t="n">
-        <v>1958376</v>
+        <v>3144702</v>
       </c>
       <c r="AB60" t="n">
-        <v>-70</v>
+        <v>-60</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -7472,54 +7472,54 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>227.5</v>
+        <v>590</v>
       </c>
       <c r="D61" t="n">
-        <v>249.1</v>
+        <v>614.2</v>
       </c>
       <c r="E61" t="n">
-        <v>252.75</v>
+        <v>584.6</v>
       </c>
       <c r="F61" t="n">
-        <v>245.43</v>
+        <v>557.15</v>
       </c>
       <c r="G61" t="n">
-        <v>2817000</v>
+        <v>25304000</v>
       </c>
       <c r="H61" t="n">
-        <v>4227000</v>
+        <v>32036976</v>
       </c>
       <c r="I61" t="n">
-        <v>312.5</v>
+        <v>669</v>
       </c>
       <c r="J61" t="n">
-        <v>220</v>
+        <v>465</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -7527,55 +7527,55 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-27233</v>
+        <v>-2269811</v>
       </c>
       <c r="M61" t="n">
-        <v>-1281879</v>
+        <v>-18147118</v>
       </c>
       <c r="N61" t="n">
-        <v>-2076991</v>
+        <v>-19887300</v>
       </c>
       <c r="O61" t="n">
-        <v>-1310509</v>
+        <v>-19512205</v>
       </c>
       <c r="P61" t="n">
-        <v>2802</v>
+        <v>2284150</v>
       </c>
       <c r="Q61" t="n">
-        <v>-1219573</v>
+        <v>-10178887</v>
       </c>
       <c r="R61" t="n">
-        <v>-1991523</v>
+        <v>-10813423</v>
       </c>
       <c r="S61" t="n">
-        <v>-1080981</v>
+        <v>-13545404</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>-4656953</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>-8031843</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>-8748601</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>-5686221</v>
       </c>
       <c r="X61" t="n">
-        <v>-30035</v>
+        <v>102992</v>
       </c>
       <c r="Y61" t="n">
-        <v>-62306</v>
+        <v>63612</v>
       </c>
       <c r="Z61" t="n">
-        <v>-85468</v>
+        <v>-325276</v>
       </c>
       <c r="AA61" t="n">
-        <v>-229528</v>
+        <v>-280580</v>
       </c>
       <c r="AB61" t="n">
-        <v>-85</v>
+        <v>-70</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -7589,54 +7589,54 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>436</v>
+        <v>1060</v>
       </c>
       <c r="D62" t="n">
-        <v>449.5</v>
+        <v>1092</v>
       </c>
       <c r="E62" t="n">
-        <v>412.1</v>
+        <v>1071.2</v>
       </c>
       <c r="F62" t="n">
-        <v>396.05</v>
+        <v>1058.6</v>
       </c>
       <c r="G62" t="n">
-        <v>7911000</v>
+        <v>2924000</v>
       </c>
       <c r="H62" t="n">
-        <v>13922400</v>
+        <v>4078000</v>
       </c>
       <c r="I62" t="n">
-        <v>492.5</v>
+        <v>1300</v>
       </c>
       <c r="J62" t="n">
-        <v>343</v>
+        <v>865</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7644,55 +7644,55 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-683330</v>
+        <v>-420978</v>
       </c>
       <c r="M62" t="n">
-        <v>-4127623</v>
+        <v>-1582664</v>
       </c>
       <c r="N62" t="n">
-        <v>-1931661</v>
+        <v>-2974189</v>
       </c>
       <c r="O62" t="n">
-        <v>4419564</v>
+        <v>-4253655</v>
       </c>
       <c r="P62" t="n">
-        <v>-556866</v>
+        <v>60766</v>
       </c>
       <c r="Q62" t="n">
-        <v>-3731197</v>
+        <v>-94694</v>
       </c>
       <c r="R62" t="n">
-        <v>-1204126</v>
+        <v>-358980</v>
       </c>
       <c r="S62" t="n">
-        <v>9111328</v>
+        <v>-2479356</v>
       </c>
       <c r="T62" t="n">
-        <v>-75000</v>
+        <v>-478000</v>
       </c>
       <c r="U62" t="n">
-        <v>-331000</v>
+        <v>-1475050</v>
       </c>
       <c r="V62" t="n">
-        <v>-405000</v>
+        <v>-2527050</v>
       </c>
       <c r="W62" t="n">
-        <v>-5156631</v>
+        <v>-1737050</v>
       </c>
       <c r="X62" t="n">
-        <v>-51464</v>
+        <v>-3744</v>
       </c>
       <c r="Y62" t="n">
-        <v>-65426</v>
+        <v>-12920</v>
       </c>
       <c r="Z62" t="n">
-        <v>-322535</v>
+        <v>-88159</v>
       </c>
       <c r="AA62" t="n">
-        <v>464867</v>
+        <v>-37249</v>
       </c>
       <c r="AB62" t="n">
-        <v>-95</v>
+        <v>-70</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -7711,49 +7711,49 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>380</v>
+        <v>270.5</v>
       </c>
       <c r="D63" t="n">
-        <v>381.9</v>
+        <v>275.6</v>
       </c>
       <c r="E63" t="n">
-        <v>380.2</v>
+        <v>275.2</v>
       </c>
       <c r="F63" t="n">
-        <v>386.75</v>
+        <v>262</v>
       </c>
       <c r="G63" t="n">
-        <v>1813000</v>
+        <v>44486000</v>
       </c>
       <c r="H63" t="n">
-        <v>2419400</v>
+        <v>79272668</v>
       </c>
       <c r="I63" t="n">
-        <v>439</v>
+        <v>305.5</v>
       </c>
       <c r="J63" t="n">
-        <v>353.5</v>
+        <v>233.5</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7761,55 +7761,55 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-305157</v>
+        <v>-13602165</v>
       </c>
       <c r="M63" t="n">
-        <v>-406036</v>
+        <v>-24542154</v>
       </c>
       <c r="N63" t="n">
-        <v>-1113246</v>
+        <v>-52766993</v>
       </c>
       <c r="O63" t="n">
-        <v>-768189</v>
+        <v>-6377479</v>
       </c>
       <c r="P63" t="n">
-        <v>-320812</v>
+        <v>-13708813</v>
       </c>
       <c r="Q63" t="n">
-        <v>-337057</v>
+        <v>-19162159</v>
       </c>
       <c r="R63" t="n">
-        <v>-1005630</v>
+        <v>-38360704</v>
       </c>
       <c r="S63" t="n">
-        <v>-667187</v>
+        <v>3177875</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="U63" t="n">
-        <v>-22000</v>
+        <v>-3363000</v>
       </c>
       <c r="V63" t="n">
-        <v>-38000</v>
+        <v>-10645000</v>
       </c>
       <c r="W63" t="n">
-        <v>-13000</v>
+        <v>-6615000</v>
       </c>
       <c r="X63" t="n">
-        <v>15655</v>
+        <v>81648</v>
       </c>
       <c r="Y63" t="n">
-        <v>-46979</v>
+        <v>-2016995</v>
       </c>
       <c r="Z63" t="n">
-        <v>-69616</v>
+        <v>-3761289</v>
       </c>
       <c r="AA63" t="n">
-        <v>-88002</v>
+        <v>-2940354</v>
       </c>
       <c r="AB63" t="n">
-        <v>-95</v>
+        <v>-70</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7833,122 +7833,707 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2338.TW</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>光罩</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="E64" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="F64" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8316000</v>
+      </c>
+      <c r="H64" t="n">
+        <v>10768564</v>
+      </c>
+      <c r="I64" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>-3130536</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-3121889</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-2012275</v>
+      </c>
+      <c r="O64" t="n">
+        <v>12234349</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-3219650</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>-3438638</v>
+      </c>
+      <c r="R64" t="n">
+        <v>-2331789</v>
+      </c>
+      <c r="S64" t="n">
+        <v>11018660</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>89114</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>316749</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>319514</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1215689</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>跌破5日線、多頭排列、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4960.TW</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>誠美材</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="D65" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="E65" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="F65" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="G65" t="n">
+        <v>8286000</v>
+      </c>
+      <c r="H65" t="n">
+        <v>9476237</v>
+      </c>
+      <c r="I65" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="J65" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>401986</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-968923</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-1382569</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-9625536</v>
+      </c>
+      <c r="P65" t="n">
+        <v>403001</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>-710013</v>
+      </c>
+      <c r="R65" t="n">
+        <v>-1258658</v>
+      </c>
+      <c r="S65" t="n">
+        <v>-9492626</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>-1015</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>-258910</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-123911</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>-132910</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-85</v>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4908.TWO</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>前鼎</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>249.1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>252.75</v>
+      </c>
+      <c r="F66" t="n">
+        <v>245.43</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2817000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4227000</v>
+      </c>
+      <c r="I66" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>220</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>-27233</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-1281879</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-2871580</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-2105098</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2802</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>-1219573</v>
+      </c>
+      <c r="R66" t="n">
+        <v>-2740760</v>
+      </c>
+      <c r="S66" t="n">
+        <v>-1830218</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>-30035</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>-62306</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-130820</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>-274880</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>-85</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2485.TW</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>兆赫</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D67" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="E67" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="F67" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="G67" t="n">
+        <v>14989000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>25494701</v>
+      </c>
+      <c r="I67" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="J67" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>-3353884</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-1927633</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-5620421</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-5122068</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-3281171</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>-1786681</v>
+      </c>
+      <c r="R67" t="n">
+        <v>-5657186</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-7066444</v>
+      </c>
+      <c r="T67" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="U67" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="V67" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="X67" t="n">
+        <v>-69713</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>-137952</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>39765</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1958376</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>5439.TWO</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>380</v>
+      </c>
+      <c r="D68" t="n">
+        <v>381.9</v>
+      </c>
+      <c r="E68" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="F68" t="n">
+        <v>386.75</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1813000</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2419400</v>
+      </c>
+      <c r="I68" t="n">
+        <v>439</v>
+      </c>
+      <c r="J68" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>-305157</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-406036</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-993095</v>
+      </c>
+      <c r="O68" t="n">
+        <v>-648038</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-320812</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>-337057</v>
+      </c>
+      <c r="R68" t="n">
+        <v>-882971</v>
+      </c>
+      <c r="S68" t="n">
+        <v>-544528</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>-22000</v>
+      </c>
+      <c r="V68" t="n">
+        <v>-38000</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="X68" t="n">
+        <v>15655</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>-46979</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>-72124</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>-90510</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>❌避開</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>觀望</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>跌破5日線、量能未放大</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>3081.TWO</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C69" t="n">
         <v>2685</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D69" t="n">
         <v>2799</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E69" t="n">
         <v>2725.5</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F69" t="n">
         <v>2749.25</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G69" t="n">
         <v>1639000</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H69" t="n">
         <v>2676600</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I69" t="n">
         <v>3215</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J69" t="n">
         <v>2460</v>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>無明顯異常</t>
         </is>
       </c>
-      <c r="L64" t="n">
+      <c r="L69" t="n">
         <v>-152795</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M69" t="n">
         <v>-1422809</v>
       </c>
-      <c r="N64" t="n">
-        <v>-1672277</v>
-      </c>
-      <c r="O64" t="n">
-        <v>-1018978</v>
-      </c>
-      <c r="P64" t="n">
+      <c r="N69" t="n">
+        <v>-1235852</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-582553</v>
+      </c>
+      <c r="P69" t="n">
         <v>10864</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Q69" t="n">
         <v>-835828</v>
       </c>
-      <c r="R64" t="n">
-        <v>-1143057</v>
-      </c>
-      <c r="S64" t="n">
-        <v>-952988</v>
-      </c>
-      <c r="T64" t="n">
+      <c r="R69" t="n">
+        <v>-893214</v>
+      </c>
+      <c r="S69" t="n">
+        <v>-703145</v>
+      </c>
+      <c r="T69" t="n">
         <v>-161400</v>
       </c>
-      <c r="U64" t="n">
+      <c r="U69" t="n">
         <v>-531500</v>
       </c>
-      <c r="V64" t="n">
-        <v>-464300</v>
-      </c>
-      <c r="W64" t="n">
-        <v>-60415</v>
-      </c>
-      <c r="X64" t="n">
+      <c r="V69" t="n">
+        <v>-278822</v>
+      </c>
+      <c r="W69" t="n">
+        <v>125063</v>
+      </c>
+      <c r="X69" t="n">
         <v>-2259</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="Y69" t="n">
         <v>-55481</v>
       </c>
-      <c r="Z64" t="n">
-        <v>-64920</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>-5575</v>
-      </c>
-      <c r="AB64" t="n">
+      <c r="Z69" t="n">
+        <v>-63816</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-4471</v>
+      </c>
+      <c r="AB69" t="n">
         <v>-95</v>
       </c>
-      <c r="AC64" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>❌避開</t>
         </is>
       </c>
-      <c r="AD64" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>觀望</t>
         </is>
       </c>
-      <c r="AE64" t="inlineStr">
+      <c r="AE69" t="inlineStr">
         <is>
           <t>跌破5日線、量能未放大</t>
         </is>
       </c>
-      <c r="AF64" t="inlineStr">
+      <c r="AF69" t="inlineStr">
         <is>
           <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
-      <c r="AG64" t="inlineStr">
+      <c r="AG69" t="inlineStr">
         <is>
           <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -607,10 +607,10 @@
         <v>146.32</v>
       </c>
       <c r="G2" t="n">
-        <v>279090000</v>
+        <v>282187864</v>
       </c>
       <c r="H2" t="n">
-        <v>113431112</v>
+        <v>114050684</v>
       </c>
       <c r="I2" t="n">
         <v>191</v>
@@ -624,52 +624,52 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>25906440</v>
+        <v>110166233</v>
       </c>
       <c r="M2" t="n">
-        <v>49814393</v>
+        <v>155632663</v>
       </c>
       <c r="N2" t="n">
-        <v>52471124</v>
+        <v>159699038</v>
       </c>
       <c r="O2" t="n">
-        <v>110525706</v>
+        <v>227335419</v>
       </c>
       <c r="P2" t="n">
-        <v>24686613</v>
+        <v>91902682</v>
       </c>
       <c r="Q2" t="n">
-        <v>44469682</v>
+        <v>133435632</v>
       </c>
       <c r="R2" t="n">
-        <v>46006122</v>
+        <v>135886232</v>
       </c>
       <c r="S2" t="n">
-        <v>99485352</v>
+        <v>199915300</v>
       </c>
       <c r="T2" t="n">
-        <v>1488000</v>
+        <v>17001000</v>
       </c>
       <c r="U2" t="n">
-        <v>3052568</v>
+        <v>18929000</v>
       </c>
       <c r="V2" t="n">
-        <v>4610098</v>
+        <v>20526000</v>
       </c>
       <c r="W2" t="n">
-        <v>5383814</v>
+        <v>21148246</v>
       </c>
       <c r="X2" t="n">
-        <v>-268173</v>
+        <v>1262551</v>
       </c>
       <c r="Y2" t="n">
-        <v>2292143</v>
+        <v>3268031</v>
       </c>
       <c r="Z2" t="n">
-        <v>1854904</v>
+        <v>3286806</v>
       </c>
       <c r="AA2" t="n">
-        <v>5656540</v>
+        <v>6271873</v>
       </c>
       <c r="AB2" t="n">
         <v>195</v>
@@ -703,93 +703,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>52.8</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>50.67</v>
+        <v>45.86</v>
       </c>
       <c r="E3" t="n">
-        <v>48.59</v>
+        <v>45.72</v>
       </c>
       <c r="F3" t="n">
-        <v>46.7</v>
+        <v>43.9</v>
       </c>
       <c r="G3" t="n">
-        <v>67755000</v>
+        <v>37219368</v>
       </c>
       <c r="H3" t="n">
-        <v>61845972</v>
+        <v>16065718</v>
       </c>
       <c r="I3" t="n">
-        <v>52.8</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>43.16</v>
+        <v>38.65</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12833515</v>
+        <v>9984413</v>
       </c>
       <c r="M3" t="n">
-        <v>51532634</v>
+        <v>13401152</v>
       </c>
       <c r="N3" t="n">
-        <v>87198974</v>
+        <v>16061563</v>
       </c>
       <c r="O3" t="n">
-        <v>193273136</v>
+        <v>17580865</v>
       </c>
       <c r="P3" t="n">
-        <v>6462117</v>
+        <v>8688404</v>
       </c>
       <c r="Q3" t="n">
-        <v>30147060</v>
+        <v>11702979</v>
       </c>
       <c r="R3" t="n">
-        <v>47804655</v>
+        <v>14211979</v>
       </c>
       <c r="S3" t="n">
-        <v>96884073</v>
+        <v>15975318</v>
       </c>
       <c r="T3" t="n">
-        <v>130000</v>
+        <v>-6000</v>
       </c>
       <c r="U3" t="n">
-        <v>230000</v>
+        <v>-6000</v>
       </c>
       <c r="V3" t="n">
-        <v>2090000</v>
+        <v>-8000</v>
       </c>
       <c r="W3" t="n">
-        <v>1990000</v>
+        <v>-28000</v>
       </c>
       <c r="X3" t="n">
-        <v>6241398</v>
+        <v>1302009</v>
       </c>
       <c r="Y3" t="n">
-        <v>21155574</v>
+        <v>1704173</v>
       </c>
       <c r="Z3" t="n">
-        <v>37304319</v>
+        <v>1857584</v>
       </c>
       <c r="AA3" t="n">
-        <v>94399063</v>
+        <v>1633547</v>
       </c>
       <c r="AB3" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,54 +803,54 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>419.5</v>
+        <v>52.8</v>
       </c>
       <c r="D4" t="n">
-        <v>356.8</v>
+        <v>50.67</v>
       </c>
       <c r="E4" t="n">
-        <v>326.2</v>
+        <v>48.59</v>
       </c>
       <c r="F4" t="n">
-        <v>314</v>
+        <v>46.7</v>
       </c>
       <c r="G4" t="n">
-        <v>168804000</v>
+        <v>69462828</v>
       </c>
       <c r="H4" t="n">
-        <v>174354298</v>
+        <v>62187537</v>
       </c>
       <c r="I4" t="n">
-        <v>419.5</v>
+        <v>52.8</v>
       </c>
       <c r="J4" t="n">
-        <v>260</v>
+        <v>43.16</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>29714770</v>
+        <v>25398318</v>
       </c>
       <c r="M4" t="n">
-        <v>117706143</v>
+        <v>73650098</v>
       </c>
       <c r="N4" t="n">
-        <v>126499130</v>
+        <v>99074323</v>
       </c>
       <c r="O4" t="n">
-        <v>78771719</v>
+        <v>216453878</v>
       </c>
       <c r="P4" t="n">
-        <v>27016483</v>
+        <v>20172152</v>
       </c>
       <c r="Q4" t="n">
-        <v>108666843</v>
+        <v>47470733</v>
       </c>
       <c r="R4" t="n">
-        <v>121744282</v>
+        <v>61094393</v>
       </c>
       <c r="S4" t="n">
-        <v>97442183</v>
+        <v>118371139</v>
       </c>
       <c r="T4" t="n">
-        <v>2178001</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>7782331</v>
+        <v>230000</v>
       </c>
       <c r="V4" t="n">
-        <v>4720606</v>
+        <v>2330000</v>
       </c>
       <c r="W4" t="n">
-        <v>-13348559</v>
+        <v>1990000</v>
       </c>
       <c r="X4" t="n">
-        <v>520286</v>
+        <v>5226166</v>
       </c>
       <c r="Y4" t="n">
-        <v>1256969</v>
+        <v>25949365</v>
       </c>
       <c r="Z4" t="n">
-        <v>34242</v>
+        <v>35649930</v>
       </c>
       <c r="AA4" t="n">
-        <v>-5321905</v>
+        <v>96092739</v>
       </c>
       <c r="AB4" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -958,10 +958,10 @@
         <v>131.78</v>
       </c>
       <c r="G5" t="n">
-        <v>267752000</v>
+        <v>270430116</v>
       </c>
       <c r="H5" t="n">
-        <v>322881785</v>
+        <v>323417408</v>
       </c>
       <c r="I5" t="n">
         <v>184.5</v>
@@ -975,52 +975,52 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>146059</v>
+        <v>25833459</v>
       </c>
       <c r="M5" t="n">
-        <v>23904373</v>
+        <v>97816855</v>
       </c>
       <c r="N5" t="n">
-        <v>103702296</v>
+        <v>123740503</v>
       </c>
       <c r="O5" t="n">
-        <v>165431261</v>
+        <v>284701329</v>
       </c>
       <c r="P5" t="n">
-        <v>-6767657</v>
+        <v>12925256</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4918288</v>
+        <v>59740683</v>
       </c>
       <c r="R5" t="n">
-        <v>56728248</v>
+        <v>74514492</v>
       </c>
       <c r="S5" t="n">
-        <v>112812507</v>
+        <v>226449583</v>
       </c>
       <c r="T5" t="n">
-        <v>5952147</v>
+        <v>12930000</v>
       </c>
       <c r="U5" t="n">
-        <v>28060924</v>
+        <v>36135147</v>
       </c>
       <c r="V5" t="n">
-        <v>43096531</v>
+        <v>46806299</v>
       </c>
       <c r="W5" t="n">
-        <v>52047258</v>
+        <v>53900723</v>
       </c>
       <c r="X5" t="n">
-        <v>961569</v>
+        <v>-21797</v>
       </c>
       <c r="Y5" t="n">
-        <v>761737</v>
+        <v>1941025</v>
       </c>
       <c r="Z5" t="n">
-        <v>3877517</v>
+        <v>2419712</v>
       </c>
       <c r="AA5" t="n">
-        <v>571496</v>
+        <v>4351023</v>
       </c>
       <c r="AB5" t="n">
         <v>150</v>
@@ -1075,10 +1075,10 @@
         <v>330.3</v>
       </c>
       <c r="G6" t="n">
-        <v>25117000</v>
+        <v>25610532</v>
       </c>
       <c r="H6" t="n">
-        <v>24735728</v>
+        <v>24834434</v>
       </c>
       <c r="I6" t="n">
         <v>396</v>
@@ -1092,52 +1092,52 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>200379</v>
+        <v>2805857</v>
       </c>
       <c r="M6" t="n">
-        <v>10186160</v>
+        <v>10499859</v>
       </c>
       <c r="N6" t="n">
-        <v>11973950</v>
+        <v>11238323</v>
       </c>
       <c r="O6" t="n">
-        <v>4905137</v>
+        <v>11935285</v>
       </c>
       <c r="P6" t="n">
-        <v>-4462178</v>
+        <v>-415232</v>
       </c>
       <c r="Q6" t="n">
-        <v>1853493</v>
+        <v>490315</v>
       </c>
       <c r="R6" t="n">
-        <v>3409112</v>
+        <v>905865</v>
       </c>
       <c r="S6" t="n">
-        <v>-3558687</v>
+        <v>1076285</v>
       </c>
       <c r="T6" t="n">
-        <v>4171000</v>
+        <v>3252000</v>
       </c>
       <c r="U6" t="n">
-        <v>7080181</v>
+        <v>8962024</v>
       </c>
       <c r="V6" t="n">
-        <v>7312181</v>
+        <v>9204024</v>
       </c>
       <c r="W6" t="n">
-        <v>8119102</v>
+        <v>9837945</v>
       </c>
       <c r="X6" t="n">
-        <v>491557</v>
+        <v>-30911</v>
       </c>
       <c r="Y6" t="n">
-        <v>1252486</v>
+        <v>1047520</v>
       </c>
       <c r="Z6" t="n">
-        <v>1252657</v>
+        <v>1128434</v>
       </c>
       <c r="AA6" t="n">
-        <v>344722</v>
+        <v>1021055</v>
       </c>
       <c r="AB6" t="n">
         <v>150</v>
@@ -1171,90 +1171,90 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2331.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25.6</v>
+        <v>419.5</v>
       </c>
       <c r="D7" t="n">
-        <v>22.59</v>
+        <v>356.8</v>
       </c>
       <c r="E7" t="n">
-        <v>21.5</v>
+        <v>326.2</v>
       </c>
       <c r="F7" t="n">
-        <v>20.79</v>
+        <v>314</v>
       </c>
       <c r="G7" t="n">
-        <v>36432000</v>
+        <v>171631936</v>
       </c>
       <c r="H7" t="n">
-        <v>12702445</v>
+        <v>174919886</v>
       </c>
       <c r="I7" t="n">
-        <v>26.5</v>
+        <v>419.5</v>
       </c>
       <c r="J7" t="n">
-        <v>18.6</v>
+        <v>260</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1377969</v>
+        <v>23790379</v>
       </c>
       <c r="M7" t="n">
-        <v>4043082</v>
+        <v>77991729</v>
       </c>
       <c r="N7" t="n">
-        <v>2610639</v>
+        <v>82243998</v>
       </c>
       <c r="O7" t="n">
-        <v>-1385945</v>
+        <v>66486872</v>
       </c>
       <c r="P7" t="n">
-        <v>1064000</v>
+        <v>18321681</v>
       </c>
       <c r="Q7" t="n">
-        <v>3708885</v>
+        <v>64821550</v>
       </c>
       <c r="R7" t="n">
-        <v>2317990</v>
+        <v>70568527</v>
       </c>
       <c r="S7" t="n">
-        <v>-1718010</v>
+        <v>73972511</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>5366000</v>
       </c>
       <c r="U7" t="n">
-        <v>-13000</v>
+        <v>12339001</v>
       </c>
       <c r="V7" t="n">
-        <v>-23000</v>
+        <v>12297001</v>
       </c>
       <c r="W7" t="n">
-        <v>-94000</v>
+        <v>-5657889</v>
       </c>
       <c r="X7" t="n">
-        <v>313969</v>
+        <v>102698</v>
       </c>
       <c r="Y7" t="n">
-        <v>347197</v>
+        <v>831178</v>
       </c>
       <c r="Z7" t="n">
-        <v>315649</v>
+        <v>-621530</v>
       </c>
       <c r="AA7" t="n">
-        <v>426065</v>
+        <v>-1827750</v>
       </c>
       <c r="AB7" t="n">
         <v>150</v>
@@ -1271,110 +1271,110 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>301.5</v>
       </c>
       <c r="D8" t="n">
-        <v>45.86</v>
+        <v>282.2</v>
       </c>
       <c r="E8" t="n">
-        <v>45.72</v>
+        <v>266.85</v>
       </c>
       <c r="F8" t="n">
-        <v>43.9</v>
+        <v>258.18</v>
       </c>
       <c r="G8" t="n">
-        <v>36966000</v>
+        <v>113076476</v>
       </c>
       <c r="H8" t="n">
-        <v>16015045</v>
+        <v>152099889</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>304.5</v>
       </c>
       <c r="J8" t="n">
-        <v>38.65</v>
+        <v>239.5</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-248474</v>
+        <v>27572146</v>
       </c>
       <c r="M8" t="n">
-        <v>3362503</v>
+        <v>114808214</v>
       </c>
       <c r="N8" t="n">
-        <v>4230839</v>
+        <v>134934212</v>
       </c>
       <c r="O8" t="n">
-        <v>8730275</v>
+        <v>225693771</v>
       </c>
       <c r="P8" t="n">
-        <v>-224389</v>
+        <v>25502562</v>
       </c>
       <c r="Q8" t="n">
-        <v>3328000</v>
+        <v>99266396</v>
       </c>
       <c r="R8" t="n">
-        <v>4484001</v>
+        <v>118882485</v>
       </c>
       <c r="S8" t="n">
-        <v>8296993</v>
+        <v>212312527</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2068000</v>
       </c>
       <c r="U8" t="n">
-        <v>-6000</v>
+        <v>11299000</v>
       </c>
       <c r="V8" t="n">
-        <v>-8000</v>
+        <v>11432866</v>
       </c>
       <c r="W8" t="n">
-        <v>-40000</v>
+        <v>9824449</v>
       </c>
       <c r="X8" t="n">
-        <v>-24085</v>
+        <v>1584</v>
       </c>
       <c r="Y8" t="n">
-        <v>40503</v>
+        <v>4242818</v>
       </c>
       <c r="Z8" t="n">
-        <v>-245162</v>
+        <v>4618861</v>
       </c>
       <c r="AA8" t="n">
-        <v>473282</v>
+        <v>3556795</v>
       </c>
       <c r="AB8" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1388,54 +1388,54 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>231</v>
+        <v>2380</v>
       </c>
       <c r="D9" t="n">
-        <v>218.1</v>
+        <v>2337</v>
       </c>
       <c r="E9" t="n">
-        <v>215.95</v>
+        <v>2293.5</v>
       </c>
       <c r="F9" t="n">
-        <v>212.05</v>
+        <v>2273.75</v>
       </c>
       <c r="G9" t="n">
-        <v>35182000</v>
+        <v>41532527</v>
       </c>
       <c r="H9" t="n">
-        <v>33126359</v>
+        <v>57968955</v>
       </c>
       <c r="I9" t="n">
-        <v>231</v>
+        <v>2415</v>
       </c>
       <c r="J9" t="n">
-        <v>195.5</v>
+        <v>2185</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,52 +1443,52 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>15949739</v>
+        <v>785136</v>
       </c>
       <c r="M9" t="n">
-        <v>21698905</v>
+        <v>12907350</v>
       </c>
       <c r="N9" t="n">
-        <v>20009420</v>
+        <v>22090715</v>
       </c>
       <c r="O9" t="n">
-        <v>57007750</v>
+        <v>14620032</v>
       </c>
       <c r="P9" t="n">
-        <v>2159299</v>
+        <v>391294</v>
       </c>
       <c r="Q9" t="n">
-        <v>-16404349</v>
+        <v>10363903</v>
       </c>
       <c r="R9" t="n">
-        <v>-35593846</v>
+        <v>19174825</v>
       </c>
       <c r="S9" t="n">
-        <v>-3428806</v>
+        <v>6187704</v>
       </c>
       <c r="T9" t="n">
-        <v>12843785</v>
+        <v>-67897</v>
       </c>
       <c r="U9" t="n">
-        <v>36165345</v>
+        <v>739567</v>
       </c>
       <c r="V9" t="n">
-        <v>52647181</v>
+        <v>740799</v>
       </c>
       <c r="W9" t="n">
-        <v>55898201</v>
+        <v>6162807</v>
       </c>
       <c r="X9" t="n">
-        <v>946655</v>
+        <v>461739</v>
       </c>
       <c r="Y9" t="n">
-        <v>1937909</v>
+        <v>1803880</v>
       </c>
       <c r="Z9" t="n">
-        <v>2956085</v>
+        <v>2175091</v>
       </c>
       <c r="AA9" t="n">
-        <v>4538355</v>
+        <v>2269521</v>
       </c>
       <c r="AB9" t="n">
         <v>140</v>
@@ -1505,54 +1505,54 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1145</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>1058</v>
+        <v>218.1</v>
       </c>
       <c r="E10" t="n">
-        <v>1021.5</v>
+        <v>215.95</v>
       </c>
       <c r="F10" t="n">
-        <v>1040.6</v>
+        <v>212.05</v>
       </c>
       <c r="G10" t="n">
-        <v>6075000</v>
+        <v>35901526</v>
       </c>
       <c r="H10" t="n">
-        <v>3574000</v>
+        <v>33270264</v>
       </c>
       <c r="I10" t="n">
-        <v>1210</v>
+        <v>231</v>
       </c>
       <c r="J10" t="n">
-        <v>936</v>
+        <v>195.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,52 +1560,52 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1189926</v>
+        <v>7951915</v>
       </c>
       <c r="M10" t="n">
-        <v>1922078</v>
+        <v>28401326</v>
       </c>
       <c r="N10" t="n">
-        <v>1594701</v>
+        <v>28092687</v>
       </c>
       <c r="O10" t="n">
-        <v>-560819</v>
+        <v>66256282</v>
       </c>
       <c r="P10" t="n">
-        <v>1047554</v>
+        <v>-7856376</v>
       </c>
       <c r="Q10" t="n">
-        <v>1654327</v>
+        <v>-13611460</v>
       </c>
       <c r="R10" t="n">
-        <v>1282771</v>
+        <v>-23562509</v>
       </c>
       <c r="S10" t="n">
-        <v>-427135</v>
+        <v>-2072646</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>14904941</v>
       </c>
       <c r="U10" t="n">
-        <v>10000</v>
+        <v>39750187</v>
       </c>
       <c r="V10" t="n">
-        <v>9617</v>
+        <v>48700678</v>
       </c>
       <c r="W10" t="n">
-        <v>-233427</v>
+        <v>63699163</v>
       </c>
       <c r="X10" t="n">
-        <v>142372</v>
+        <v>903350</v>
       </c>
       <c r="Y10" t="n">
-        <v>257751</v>
+        <v>2262599</v>
       </c>
       <c r="Z10" t="n">
-        <v>302313</v>
+        <v>2954518</v>
       </c>
       <c r="AA10" t="n">
-        <v>99743</v>
+        <v>4629765</v>
       </c>
       <c r="AB10" t="n">
         <v>140</v>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、成交量放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、黃金交叉、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43.65</v>
+        <v>1165</v>
       </c>
       <c r="D11" t="n">
-        <v>42.54</v>
+        <v>1083</v>
       </c>
       <c r="E11" t="n">
-        <v>42.33</v>
+        <v>1041.4</v>
       </c>
       <c r="F11" t="n">
-        <v>40.86</v>
+        <v>1040.35</v>
       </c>
       <c r="G11" t="n">
-        <v>33550000</v>
+        <v>7264000</v>
       </c>
       <c r="H11" t="n">
-        <v>25027453</v>
+        <v>4468600</v>
       </c>
       <c r="I11" t="n">
-        <v>44.75</v>
+        <v>1220</v>
       </c>
       <c r="J11" t="n">
-        <v>37.6</v>
+        <v>936</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>9525842</v>
+        <v>2258596</v>
       </c>
       <c r="M11" t="n">
-        <v>12285874</v>
+        <v>4115203</v>
       </c>
       <c r="N11" t="n">
-        <v>15455905</v>
+        <v>3668360</v>
       </c>
       <c r="O11" t="n">
-        <v>72915018</v>
+        <v>2047412</v>
       </c>
       <c r="P11" t="n">
-        <v>2233303</v>
+        <v>2245986</v>
       </c>
       <c r="Q11" t="n">
-        <v>6940623</v>
+        <v>3765157</v>
       </c>
       <c r="R11" t="n">
-        <v>8488390</v>
+        <v>3395725</v>
       </c>
       <c r="S11" t="n">
-        <v>71670898</v>
+        <v>1973522</v>
       </c>
       <c r="T11" t="n">
-        <v>5724000</v>
+        <v>900</v>
       </c>
       <c r="U11" t="n">
-        <v>5719000</v>
+        <v>2900</v>
       </c>
       <c r="V11" t="n">
-        <v>5210000</v>
+        <v>10900</v>
       </c>
       <c r="W11" t="n">
-        <v>1863000</v>
+        <v>-66915</v>
       </c>
       <c r="X11" t="n">
-        <v>1568539</v>
+        <v>11710</v>
       </c>
       <c r="Y11" t="n">
-        <v>-373749</v>
+        <v>347146</v>
       </c>
       <c r="Z11" t="n">
-        <v>1757515</v>
+        <v>261735</v>
       </c>
       <c r="AA11" t="n">
-        <v>-618880</v>
+        <v>140805</v>
       </c>
       <c r="AB11" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1749,44 +1749,44 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31.45</v>
+        <v>1015</v>
       </c>
       <c r="D12" t="n">
-        <v>30.23</v>
+        <v>905.2</v>
       </c>
       <c r="E12" t="n">
-        <v>29.41</v>
+        <v>794.5</v>
       </c>
       <c r="F12" t="n">
-        <v>28.62</v>
+        <v>770.05</v>
       </c>
       <c r="G12" t="n">
-        <v>9275000</v>
+        <v>11189000</v>
       </c>
       <c r="H12" t="n">
-        <v>7956861</v>
+        <v>12916600</v>
       </c>
       <c r="I12" t="n">
-        <v>32.55</v>
+        <v>1020</v>
       </c>
       <c r="J12" t="n">
-        <v>26.3</v>
+        <v>597</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,55 +1794,55 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4038854</v>
+        <v>162249</v>
       </c>
       <c r="M12" t="n">
-        <v>3654670</v>
+        <v>2631325</v>
       </c>
       <c r="N12" t="n">
-        <v>2441059</v>
+        <v>8154362</v>
       </c>
       <c r="O12" t="n">
-        <v>5292939</v>
+        <v>3673434</v>
       </c>
       <c r="P12" t="n">
-        <v>3928241</v>
+        <v>253787</v>
       </c>
       <c r="Q12" t="n">
-        <v>3532684</v>
+        <v>1586971</v>
       </c>
       <c r="R12" t="n">
-        <v>2297050</v>
+        <v>578662</v>
       </c>
       <c r="S12" t="n">
-        <v>5243514</v>
+        <v>-3954722</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-422744</v>
       </c>
       <c r="U12" t="n">
-        <v>8000</v>
+        <v>-69601</v>
       </c>
       <c r="V12" t="n">
-        <v>6000</v>
+        <v>6737532</v>
       </c>
       <c r="W12" t="n">
-        <v>68000</v>
+        <v>5790882</v>
       </c>
       <c r="X12" t="n">
-        <v>110613</v>
+        <v>331206</v>
       </c>
       <c r="Y12" t="n">
-        <v>113986</v>
+        <v>1113955</v>
       </c>
       <c r="Z12" t="n">
-        <v>138009</v>
+        <v>838168</v>
       </c>
       <c r="AA12" t="n">
-        <v>-18575</v>
+        <v>1837274</v>
       </c>
       <c r="AB12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -1894,10 +1894,10 @@
         <v>90.66</v>
       </c>
       <c r="G13" t="n">
-        <v>150731000</v>
+        <v>151715085</v>
       </c>
       <c r="H13" t="n">
-        <v>125003851</v>
+        <v>125200668</v>
       </c>
       <c r="I13" t="n">
         <v>118</v>
@@ -1911,52 +1911,52 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>15245712</v>
+        <v>17417137</v>
       </c>
       <c r="M13" t="n">
-        <v>53204084</v>
+        <v>96477117</v>
       </c>
       <c r="N13" t="n">
-        <v>135527278</v>
+        <v>143464253</v>
       </c>
       <c r="O13" t="n">
-        <v>134335684</v>
+        <v>190436135</v>
       </c>
       <c r="P13" t="n">
-        <v>13945743</v>
+        <v>16575842</v>
       </c>
       <c r="Q13" t="n">
-        <v>48241698</v>
+        <v>89841244</v>
       </c>
       <c r="R13" t="n">
-        <v>128023662</v>
+        <v>135525546</v>
       </c>
       <c r="S13" t="n">
-        <v>129685447</v>
+        <v>184265443</v>
       </c>
       <c r="T13" t="n">
-        <v>696000</v>
+        <v>2133396</v>
       </c>
       <c r="U13" t="n">
-        <v>3360457</v>
+        <v>5130853</v>
       </c>
       <c r="V13" t="n">
-        <v>3504189</v>
+        <v>6431585</v>
       </c>
       <c r="W13" t="n">
-        <v>3673289</v>
+        <v>5365685</v>
       </c>
       <c r="X13" t="n">
-        <v>603969</v>
+        <v>-1292101</v>
       </c>
       <c r="Y13" t="n">
-        <v>1601929</v>
+        <v>1505020</v>
       </c>
       <c r="Z13" t="n">
-        <v>3999427</v>
+        <v>1507122</v>
       </c>
       <c r="AA13" t="n">
-        <v>976948</v>
+        <v>805007</v>
       </c>
       <c r="AB13" t="n">
         <v>135</v>
@@ -1990,37 +1990,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>668</v>
+        <v>43.65</v>
       </c>
       <c r="D14" t="n">
-        <v>584.4</v>
+        <v>42.54</v>
       </c>
       <c r="E14" t="n">
-        <v>537.6</v>
+        <v>42.33</v>
       </c>
       <c r="F14" t="n">
-        <v>491.52</v>
+        <v>40.86</v>
       </c>
       <c r="G14" t="n">
-        <v>10003000</v>
+        <v>33817082</v>
       </c>
       <c r="H14" t="n">
-        <v>8490200</v>
+        <v>25080870</v>
       </c>
       <c r="I14" t="n">
-        <v>668</v>
+        <v>44.75</v>
       </c>
       <c r="J14" t="n">
-        <v>368</v>
+        <v>37.6</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2028,55 +2028,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-525244</v>
+        <v>2392835</v>
       </c>
       <c r="M14" t="n">
-        <v>-448244</v>
+        <v>13256192</v>
       </c>
       <c r="N14" t="n">
-        <v>1677499</v>
+        <v>25091584</v>
       </c>
       <c r="O14" t="n">
-        <v>11326679</v>
+        <v>64253723</v>
       </c>
       <c r="P14" t="n">
-        <v>-93101</v>
+        <v>7811291</v>
       </c>
       <c r="Q14" t="n">
-        <v>423150</v>
+        <v>11262778</v>
       </c>
       <c r="R14" t="n">
-        <v>2367961</v>
+        <v>20258423</v>
       </c>
       <c r="S14" t="n">
-        <v>11558739</v>
+        <v>65055407</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-5695000</v>
       </c>
       <c r="U14" t="n">
-        <v>15800</v>
+        <v>24000</v>
       </c>
       <c r="V14" t="n">
-        <v>12500</v>
+        <v>24000</v>
       </c>
       <c r="W14" t="n">
-        <v>83300</v>
+        <v>-3180000</v>
       </c>
       <c r="X14" t="n">
-        <v>-432143</v>
+        <v>276544</v>
       </c>
       <c r="Y14" t="n">
-        <v>-887194</v>
+        <v>1969414</v>
       </c>
       <c r="Z14" t="n">
-        <v>-702962</v>
+        <v>4809161</v>
       </c>
       <c r="AA14" t="n">
-        <v>-315360</v>
+        <v>2378316</v>
       </c>
       <c r="AB14" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2090,54 +2090,54 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.55</v>
+        <v>32.49</v>
       </c>
       <c r="D15" t="n">
-        <v>23.01</v>
+        <v>31.16</v>
       </c>
       <c r="E15" t="n">
-        <v>20.11</v>
+        <v>29.78</v>
       </c>
       <c r="F15" t="n">
-        <v>18.5</v>
+        <v>28.8</v>
       </c>
       <c r="G15" t="n">
-        <v>25659000</v>
+        <v>111980868</v>
       </c>
       <c r="H15" t="n">
-        <v>38896094</v>
+        <v>97679491</v>
       </c>
       <c r="I15" t="n">
-        <v>27.55</v>
+        <v>32.5</v>
       </c>
       <c r="J15" t="n">
-        <v>16.6</v>
+        <v>26.9</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,52 +2145,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>109130</v>
+        <v>50989129</v>
       </c>
       <c r="M15" t="n">
-        <v>4838885</v>
+        <v>141750141</v>
       </c>
       <c r="N15" t="n">
-        <v>6388241</v>
+        <v>190010625</v>
       </c>
       <c r="O15" t="n">
-        <v>23449524</v>
+        <v>446290762</v>
       </c>
       <c r="P15" t="n">
-        <v>-530000</v>
+        <v>17420827</v>
       </c>
       <c r="Q15" t="n">
-        <v>1641838</v>
+        <v>60474000</v>
       </c>
       <c r="R15" t="n">
-        <v>2170673</v>
+        <v>111782158</v>
       </c>
       <c r="S15" t="n">
-        <v>18702025</v>
+        <v>279670276</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>486000</v>
+        <v>2500000</v>
       </c>
       <c r="X15" t="n">
-        <v>639130</v>
+        <v>33568302</v>
       </c>
       <c r="Y15" t="n">
-        <v>3201047</v>
+        <v>81276141</v>
       </c>
       <c r="Z15" t="n">
-        <v>4229568</v>
+        <v>78228467</v>
       </c>
       <c r="AA15" t="n">
-        <v>4261499</v>
+        <v>164120486</v>
       </c>
       <c r="AB15" t="n">
         <v>130</v>
@@ -2207,54 +2207,54 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32.49</v>
+        <v>31.4</v>
       </c>
       <c r="D16" t="n">
-        <v>31.16</v>
+        <v>30.36</v>
       </c>
       <c r="E16" t="n">
-        <v>29.78</v>
+        <v>29.89</v>
       </c>
       <c r="F16" t="n">
-        <v>28.8</v>
+        <v>28.67</v>
       </c>
       <c r="G16" t="n">
-        <v>110270000</v>
+        <v>14200637</v>
       </c>
       <c r="H16" t="n">
-        <v>97337318</v>
+        <v>12700714</v>
       </c>
       <c r="I16" t="n">
-        <v>32.5</v>
+        <v>31.95</v>
       </c>
       <c r="J16" t="n">
-        <v>26.9</v>
+        <v>25.55</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,28 +2262,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44716877</v>
+        <v>3608654</v>
       </c>
       <c r="M16" t="n">
-        <v>110402646</v>
+        <v>4771014</v>
       </c>
       <c r="N16" t="n">
-        <v>203656274</v>
+        <v>5613297</v>
       </c>
       <c r="O16" t="n">
-        <v>410699566</v>
+        <v>16373416</v>
       </c>
       <c r="P16" t="n">
-        <v>22071009</v>
+        <v>3649755</v>
       </c>
       <c r="Q16" t="n">
-        <v>40851643</v>
+        <v>4479803</v>
       </c>
       <c r="R16" t="n">
-        <v>99728306</v>
+        <v>5345851</v>
       </c>
       <c r="S16" t="n">
-        <v>256639718</v>
+        <v>15451796</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2295,19 +2295,19 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2500000</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>22645868</v>
+        <v>-41101</v>
       </c>
       <c r="Y16" t="n">
-        <v>69551003</v>
+        <v>291211</v>
       </c>
       <c r="Z16" t="n">
-        <v>103927968</v>
+        <v>267446</v>
       </c>
       <c r="AA16" t="n">
-        <v>151559848</v>
+        <v>921620</v>
       </c>
       <c r="AB16" t="n">
         <v>130</v>
@@ -2341,37 +2341,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>743</v>
+        <v>37.25</v>
       </c>
       <c r="D17" t="n">
-        <v>725.8</v>
+        <v>36.22</v>
       </c>
       <c r="E17" t="n">
-        <v>666.1</v>
+        <v>35.68</v>
       </c>
       <c r="F17" t="n">
-        <v>580.73</v>
+        <v>35.27</v>
       </c>
       <c r="G17" t="n">
-        <v>6058000</v>
+        <v>84389805</v>
       </c>
       <c r="H17" t="n">
-        <v>11696829</v>
+        <v>88777580</v>
       </c>
       <c r="I17" t="n">
-        <v>778</v>
+        <v>37.85</v>
       </c>
       <c r="J17" t="n">
-        <v>445.5</v>
+        <v>33.7</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1303982</v>
+        <v>3007807</v>
       </c>
       <c r="M17" t="n">
-        <v>3071789</v>
+        <v>33011634</v>
       </c>
       <c r="N17" t="n">
-        <v>8648112</v>
+        <v>14678372</v>
       </c>
       <c r="O17" t="n">
-        <v>28251728</v>
+        <v>6369836</v>
       </c>
       <c r="P17" t="n">
-        <v>934957</v>
+        <v>-38331924</v>
       </c>
       <c r="Q17" t="n">
-        <v>2591713</v>
+        <v>-83239905</v>
       </c>
       <c r="R17" t="n">
-        <v>5260467</v>
+        <v>-118612558</v>
       </c>
       <c r="S17" t="n">
-        <v>20174081</v>
+        <v>-175002575</v>
       </c>
       <c r="T17" t="n">
-        <v>15191</v>
+        <v>41577808</v>
       </c>
       <c r="U17" t="n">
-        <v>16572</v>
+        <v>115447051</v>
       </c>
       <c r="V17" t="n">
-        <v>3192763</v>
+        <v>132330184</v>
       </c>
       <c r="W17" t="n">
-        <v>7276237</v>
+        <v>179645474</v>
       </c>
       <c r="X17" t="n">
-        <v>353834</v>
+        <v>-238077</v>
       </c>
       <c r="Y17" t="n">
-        <v>463504</v>
+        <v>804488</v>
       </c>
       <c r="Z17" t="n">
-        <v>194882</v>
+        <v>960746</v>
       </c>
       <c r="AA17" t="n">
-        <v>801410</v>
+        <v>1726937</v>
       </c>
       <c r="AB17" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2441,110 +2441,110 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>2382.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2700</v>
+        <v>400.5</v>
       </c>
       <c r="D18" t="n">
-        <v>2686</v>
+        <v>346.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2611</v>
+        <v>327.95</v>
       </c>
       <c r="F18" t="n">
-        <v>2543.75</v>
+        <v>328.25</v>
       </c>
       <c r="G18" t="n">
-        <v>3832000</v>
+        <v>151608396</v>
       </c>
       <c r="H18" t="n">
-        <v>5550967</v>
+        <v>80579083</v>
       </c>
       <c r="I18" t="n">
-        <v>2835</v>
+        <v>409.5</v>
       </c>
       <c r="J18" t="n">
-        <v>2300</v>
+        <v>288.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>776741</v>
+        <v>21893967</v>
       </c>
       <c r="M18" t="n">
-        <v>883124</v>
+        <v>45194980</v>
       </c>
       <c r="N18" t="n">
-        <v>3077948</v>
+        <v>36660149</v>
       </c>
       <c r="O18" t="n">
-        <v>1234520</v>
+        <v>39893653</v>
       </c>
       <c r="P18" t="n">
-        <v>645540</v>
+        <v>-14582246</v>
       </c>
       <c r="Q18" t="n">
-        <v>418807</v>
+        <v>-15338081</v>
       </c>
       <c r="R18" t="n">
-        <v>1748863</v>
+        <v>-36751663</v>
       </c>
       <c r="S18" t="n">
-        <v>-780799</v>
+        <v>-74470550</v>
       </c>
       <c r="T18" t="n">
-        <v>67001</v>
+        <v>37188225</v>
       </c>
       <c r="U18" t="n">
-        <v>430877</v>
+        <v>59899225</v>
       </c>
       <c r="V18" t="n">
-        <v>1316900</v>
+        <v>72452435</v>
       </c>
       <c r="W18" t="n">
-        <v>2045460</v>
+        <v>114949278</v>
       </c>
       <c r="X18" t="n">
-        <v>64200</v>
+        <v>-712012</v>
       </c>
       <c r="Y18" t="n">
-        <v>33440</v>
+        <v>633836</v>
       </c>
       <c r="Z18" t="n">
-        <v>12185</v>
+        <v>959377</v>
       </c>
       <c r="AA18" t="n">
-        <v>-30141</v>
+        <v>-585075</v>
       </c>
       <c r="AB18" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2558,54 +2558,54 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>53.6</v>
+        <v>175.5</v>
       </c>
       <c r="D19" t="n">
-        <v>53.22</v>
+        <v>165</v>
       </c>
       <c r="E19" t="n">
-        <v>52.43</v>
+        <v>156.95</v>
       </c>
       <c r="F19" t="n">
-        <v>51.02</v>
+        <v>158.75</v>
       </c>
       <c r="G19" t="n">
-        <v>71610000</v>
+        <v>247731538</v>
       </c>
       <c r="H19" t="n">
-        <v>40419855</v>
+        <v>214432696</v>
       </c>
       <c r="I19" t="n">
-        <v>55.7</v>
+        <v>180</v>
       </c>
       <c r="J19" t="n">
-        <v>47.35</v>
+        <v>136.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2613,55 +2613,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>14945901</v>
+        <v>31776921</v>
       </c>
       <c r="M19" t="n">
-        <v>25862263</v>
+        <v>58557120</v>
       </c>
       <c r="N19" t="n">
-        <v>42395795</v>
+        <v>10953707</v>
       </c>
       <c r="O19" t="n">
-        <v>68637305</v>
+        <v>42964367</v>
       </c>
       <c r="P19" t="n">
-        <v>20142573</v>
+        <v>27576860</v>
       </c>
       <c r="Q19" t="n">
-        <v>30966686</v>
+        <v>50133893</v>
       </c>
       <c r="R19" t="n">
-        <v>48820355</v>
+        <v>4442037</v>
       </c>
       <c r="S19" t="n">
-        <v>74717732</v>
+        <v>45182705</v>
       </c>
       <c r="T19" t="n">
-        <v>-6005850</v>
+        <v>3292000</v>
       </c>
       <c r="U19" t="n">
-        <v>-6343542</v>
+        <v>6403000</v>
       </c>
       <c r="V19" t="n">
-        <v>-7845092</v>
+        <v>6243000</v>
       </c>
       <c r="W19" t="n">
-        <v>-7903058</v>
+        <v>-1707000</v>
       </c>
       <c r="X19" t="n">
-        <v>809178</v>
+        <v>908061</v>
       </c>
       <c r="Y19" t="n">
-        <v>1239119</v>
+        <v>2020227</v>
       </c>
       <c r="Z19" t="n">
-        <v>1420532</v>
+        <v>268670</v>
       </c>
       <c r="AA19" t="n">
-        <v>1822631</v>
+        <v>-511338</v>
       </c>
       <c r="AB19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,110 +2675,110 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2382.TW</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>400.5</v>
+        <v>31.45</v>
       </c>
       <c r="D20" t="n">
-        <v>346.5</v>
+        <v>30.23</v>
       </c>
       <c r="E20" t="n">
-        <v>327.95</v>
+        <v>29.41</v>
       </c>
       <c r="F20" t="n">
-        <v>328.25</v>
+        <v>28.62</v>
       </c>
       <c r="G20" t="n">
-        <v>149166000</v>
+        <v>9361391</v>
       </c>
       <c r="H20" t="n">
-        <v>80090604</v>
+        <v>7974139</v>
       </c>
       <c r="I20" t="n">
-        <v>409.5</v>
+        <v>32.55</v>
       </c>
       <c r="J20" t="n">
-        <v>288.5</v>
+        <v>26.3</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4874370</v>
+        <v>-363606</v>
       </c>
       <c r="M20" t="n">
-        <v>18267163</v>
+        <v>3394321</v>
       </c>
       <c r="N20" t="n">
-        <v>6680948</v>
+        <v>2627472</v>
       </c>
       <c r="O20" t="n">
-        <v>2310404</v>
+        <v>5108655</v>
       </c>
       <c r="P20" t="n">
-        <v>-2613127</v>
+        <v>-454166</v>
       </c>
       <c r="Q20" t="n">
-        <v>-18440356</v>
+        <v>3181018</v>
       </c>
       <c r="R20" t="n">
-        <v>-55857239</v>
+        <v>2415018</v>
       </c>
       <c r="S20" t="n">
-        <v>-87301189</v>
+        <v>4818692</v>
       </c>
       <c r="T20" t="n">
-        <v>7281000</v>
+        <v>165000</v>
       </c>
       <c r="U20" t="n">
-        <v>35323352</v>
+        <v>173000</v>
       </c>
       <c r="V20" t="n">
-        <v>60624404</v>
+        <v>173000</v>
       </c>
       <c r="W20" t="n">
-        <v>89314165</v>
+        <v>219000</v>
       </c>
       <c r="X20" t="n">
-        <v>206497</v>
+        <v>-74440</v>
       </c>
       <c r="Y20" t="n">
-        <v>1384167</v>
+        <v>40303</v>
       </c>
       <c r="Z20" t="n">
-        <v>1913783</v>
+        <v>39454</v>
       </c>
       <c r="AA20" t="n">
-        <v>297428</v>
+        <v>70963</v>
       </c>
       <c r="AB20" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -2792,54 +2792,54 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37.25</v>
+        <v>56.2</v>
       </c>
       <c r="D21" t="n">
-        <v>36.22</v>
+        <v>51.98</v>
       </c>
       <c r="E21" t="n">
-        <v>35.68</v>
+        <v>47.69</v>
       </c>
       <c r="F21" t="n">
-        <v>35.27</v>
+        <v>40.86</v>
       </c>
       <c r="G21" t="n">
-        <v>84226000</v>
+        <v>1163170448</v>
       </c>
       <c r="H21" t="n">
-        <v>88744819</v>
+        <v>1033743519</v>
       </c>
       <c r="I21" t="n">
-        <v>37.85</v>
+        <v>58.8</v>
       </c>
       <c r="J21" t="n">
-        <v>33.7</v>
+        <v>26.8</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,55 +2847,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13546260</v>
+        <v>-195611341</v>
       </c>
       <c r="M21" t="n">
-        <v>43363173</v>
+        <v>55247448</v>
       </c>
       <c r="N21" t="n">
-        <v>16657509</v>
+        <v>87686194</v>
       </c>
       <c r="O21" t="n">
-        <v>21226516</v>
+        <v>-906948</v>
       </c>
       <c r="P21" t="n">
-        <v>-24438582</v>
+        <v>-208585325</v>
       </c>
       <c r="Q21" t="n">
-        <v>-60246419</v>
+        <v>35367431</v>
       </c>
       <c r="R21" t="n">
-        <v>-119669352</v>
+        <v>67023143</v>
       </c>
       <c r="S21" t="n">
-        <v>-148193516</v>
+        <v>-16935718</v>
       </c>
       <c r="T21" t="n">
-        <v>37712898</v>
+        <v>24152000</v>
       </c>
       <c r="U21" t="n">
-        <v>102158167</v>
+        <v>29259444</v>
       </c>
       <c r="V21" t="n">
-        <v>133646088</v>
+        <v>23729444</v>
       </c>
       <c r="W21" t="n">
-        <v>166814366</v>
+        <v>20923859</v>
       </c>
       <c r="X21" t="n">
-        <v>271944</v>
+        <v>-11178016</v>
       </c>
       <c r="Y21" t="n">
-        <v>1451425</v>
+        <v>-9379427</v>
       </c>
       <c r="Z21" t="n">
-        <v>2680773</v>
+        <v>-3066393</v>
       </c>
       <c r="AA21" t="n">
-        <v>2605666</v>
+        <v>-4895089</v>
       </c>
       <c r="AB21" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -2909,54 +2909,54 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>175.5</v>
+        <v>10.5</v>
       </c>
       <c r="D22" t="n">
-        <v>165</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>156.95</v>
+        <v>8.01</v>
       </c>
       <c r="F22" t="n">
-        <v>158.75</v>
+        <v>6.86</v>
       </c>
       <c r="G22" t="n">
-        <v>244618000</v>
+        <v>271642439</v>
       </c>
       <c r="H22" t="n">
-        <v>213809989</v>
+        <v>231621898</v>
       </c>
       <c r="I22" t="n">
-        <v>180</v>
+        <v>10.6</v>
       </c>
       <c r="J22" t="n">
-        <v>136.5</v>
+        <v>5.55</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,55 +2964,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>18724442</v>
+        <v>-12357264</v>
       </c>
       <c r="M22" t="n">
-        <v>108932425</v>
+        <v>-3481096</v>
       </c>
       <c r="N22" t="n">
-        <v>93713452</v>
+        <v>2026133</v>
       </c>
       <c r="O22" t="n">
-        <v>40901700</v>
+        <v>44644735</v>
       </c>
       <c r="P22" t="n">
-        <v>14372572</v>
+        <v>-10001479</v>
       </c>
       <c r="Q22" t="n">
-        <v>104191240</v>
+        <v>-2129259</v>
       </c>
       <c r="R22" t="n">
-        <v>87837822</v>
+        <v>8122792</v>
       </c>
       <c r="S22" t="n">
-        <v>51829461</v>
+        <v>40393392</v>
       </c>
       <c r="T22" t="n">
-        <v>3088000</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2964000</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5773000</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-8247000</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1263870</v>
+        <v>-2355785</v>
       </c>
       <c r="Y22" t="n">
-        <v>1777185</v>
+        <v>-1351837</v>
       </c>
       <c r="Z22" t="n">
-        <v>102630</v>
+        <v>-6096659</v>
       </c>
       <c r="AA22" t="n">
-        <v>-2680761</v>
+        <v>4251343</v>
       </c>
       <c r="AB22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -3026,54 +3026,54 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2380</v>
+        <v>2700</v>
       </c>
       <c r="D23" t="n">
-        <v>2337</v>
+        <v>2686</v>
       </c>
       <c r="E23" t="n">
-        <v>2293.5</v>
+        <v>2611</v>
       </c>
       <c r="F23" t="n">
-        <v>2273.75</v>
+        <v>2543.75</v>
       </c>
       <c r="G23" t="n">
-        <v>29548000</v>
+        <v>4220815</v>
       </c>
       <c r="H23" t="n">
-        <v>55572050</v>
+        <v>5628730</v>
       </c>
       <c r="I23" t="n">
-        <v>2415</v>
+        <v>2835</v>
       </c>
       <c r="J23" t="n">
-        <v>2185</v>
+        <v>2300</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,55 +3081,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1931448</v>
+        <v>-395783</v>
       </c>
       <c r="M23" t="n">
-        <v>5975111</v>
+        <v>955784</v>
       </c>
       <c r="N23" t="n">
-        <v>6910399</v>
+        <v>1340822</v>
       </c>
       <c r="O23" t="n">
-        <v>-5215173</v>
+        <v>1692656</v>
       </c>
       <c r="P23" t="n">
-        <v>-3311663</v>
+        <v>-272021</v>
       </c>
       <c r="Q23" t="n">
-        <v>2893994</v>
+        <v>605907</v>
       </c>
       <c r="R23" t="n">
-        <v>3956357</v>
+        <v>812909</v>
       </c>
       <c r="S23" t="n">
-        <v>-18529146</v>
+        <v>-24177</v>
       </c>
       <c r="T23" t="n">
-        <v>458215</v>
+        <v>-118000</v>
       </c>
       <c r="U23" t="n">
-        <v>1272525</v>
+        <v>247877</v>
       </c>
       <c r="V23" t="n">
-        <v>676468</v>
+        <v>538877</v>
       </c>
       <c r="W23" t="n">
-        <v>10840143</v>
+        <v>1674845</v>
       </c>
       <c r="X23" t="n">
-        <v>922000</v>
+        <v>-5762</v>
       </c>
       <c r="Y23" t="n">
-        <v>1808592</v>
+        <v>102000</v>
       </c>
       <c r="Z23" t="n">
-        <v>2277574</v>
+        <v>-10964</v>
       </c>
       <c r="AA23" t="n">
-        <v>2473830</v>
+        <v>41988</v>
       </c>
       <c r="AB23" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3153,44 +3153,44 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>301.5</v>
+        <v>743</v>
       </c>
       <c r="D24" t="n">
-        <v>282.2</v>
+        <v>725.8</v>
       </c>
       <c r="E24" t="n">
-        <v>266.85</v>
+        <v>666.1</v>
       </c>
       <c r="F24" t="n">
-        <v>258.18</v>
+        <v>580.73</v>
       </c>
       <c r="G24" t="n">
-        <v>110029000</v>
+        <v>6753281</v>
       </c>
       <c r="H24" t="n">
-        <v>151490394</v>
+        <v>11835885</v>
       </c>
       <c r="I24" t="n">
-        <v>304.5</v>
+        <v>778</v>
       </c>
       <c r="J24" t="n">
-        <v>239.5</v>
+        <v>445.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,55 +3198,55 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-5143876</v>
+        <v>-543481</v>
       </c>
       <c r="M24" t="n">
-        <v>100059807</v>
+        <v>2949574</v>
       </c>
       <c r="N24" t="n">
-        <v>128543523</v>
+        <v>1946015</v>
       </c>
       <c r="O24" t="n">
-        <v>213173724</v>
+        <v>25371407</v>
       </c>
       <c r="P24" t="n">
-        <v>-6575097</v>
+        <v>159473</v>
       </c>
       <c r="Q24" t="n">
-        <v>86629844</v>
+        <v>2821599</v>
       </c>
       <c r="R24" t="n">
-        <v>115525527</v>
+        <v>1092799</v>
       </c>
       <c r="S24" t="n">
-        <v>204533241</v>
+        <v>18023329</v>
       </c>
       <c r="T24" t="n">
-        <v>1808000</v>
+        <v>-11905</v>
       </c>
       <c r="U24" t="n">
-        <v>9361253</v>
+        <v>2381</v>
       </c>
       <c r="V24" t="n">
-        <v>9249189</v>
+        <v>871572</v>
       </c>
       <c r="W24" t="n">
-        <v>5565896</v>
+        <v>6833572</v>
       </c>
       <c r="X24" t="n">
-        <v>-376779</v>
+        <v>-691049</v>
       </c>
       <c r="Y24" t="n">
-        <v>4068710</v>
+        <v>125594</v>
       </c>
       <c r="Z24" t="n">
-        <v>3768807</v>
+        <v>-18356</v>
       </c>
       <c r="AA24" t="n">
-        <v>3074587</v>
+        <v>514506</v>
       </c>
       <c r="AB24" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3270,44 +3270,44 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1705</v>
+        <v>5475</v>
       </c>
       <c r="D25" t="n">
-        <v>1629</v>
+        <v>5292</v>
       </c>
       <c r="E25" t="n">
-        <v>1495.5</v>
+        <v>5313</v>
       </c>
       <c r="F25" t="n">
-        <v>1433.75</v>
+        <v>5271</v>
       </c>
       <c r="G25" t="n">
-        <v>8984000</v>
+        <v>1953015</v>
       </c>
       <c r="H25" t="n">
-        <v>9020000</v>
+        <v>2328833</v>
       </c>
       <c r="I25" t="n">
-        <v>1815</v>
+        <v>5880</v>
       </c>
       <c r="J25" t="n">
-        <v>1125</v>
+        <v>4630</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,55 +3315,55 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>379477</v>
+        <v>139803</v>
       </c>
       <c r="M25" t="n">
-        <v>1642627</v>
+        <v>903464</v>
       </c>
       <c r="N25" t="n">
-        <v>1754492</v>
+        <v>454800</v>
       </c>
       <c r="O25" t="n">
-        <v>2976180</v>
+        <v>266199</v>
       </c>
       <c r="P25" t="n">
-        <v>-548848</v>
+        <v>201318</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1259270</v>
+        <v>693363</v>
       </c>
       <c r="R25" t="n">
-        <v>-2532759</v>
+        <v>472298</v>
       </c>
       <c r="S25" t="n">
-        <v>-1134176</v>
+        <v>558614</v>
       </c>
       <c r="T25" t="n">
-        <v>968000</v>
+        <v>3000</v>
       </c>
       <c r="U25" t="n">
-        <v>3158000</v>
+        <v>261963</v>
       </c>
       <c r="V25" t="n">
-        <v>4982000</v>
+        <v>141813</v>
       </c>
       <c r="W25" t="n">
-        <v>4975100</v>
+        <v>-220366</v>
       </c>
       <c r="X25" t="n">
-        <v>-39675</v>
+        <v>-64515</v>
       </c>
       <c r="Y25" t="n">
-        <v>-256103</v>
+        <v>-51862</v>
       </c>
       <c r="Z25" t="n">
-        <v>-694749</v>
+        <v>-159311</v>
       </c>
       <c r="AA25" t="n">
-        <v>-864744</v>
+        <v>-72049</v>
       </c>
       <c r="AB25" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -3377,54 +3377,54 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>950</v>
+        <v>53.6</v>
       </c>
       <c r="D26" t="n">
-        <v>937.6</v>
+        <v>53.22</v>
       </c>
       <c r="E26" t="n">
-        <v>819.7</v>
+        <v>52.43</v>
       </c>
       <c r="F26" t="n">
-        <v>787.25</v>
+        <v>51.02</v>
       </c>
       <c r="G26" t="n">
-        <v>4452000</v>
+        <v>71874958</v>
       </c>
       <c r="H26" t="n">
-        <v>12667000</v>
+        <v>40472847</v>
       </c>
       <c r="I26" t="n">
-        <v>1040</v>
+        <v>55.7</v>
       </c>
       <c r="J26" t="n">
-        <v>615</v>
+        <v>47.35</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,55 +3432,55 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>798638</v>
+        <v>-11144966</v>
       </c>
       <c r="M26" t="n">
-        <v>2696041</v>
+        <v>11190396</v>
       </c>
       <c r="N26" t="n">
-        <v>7450242</v>
+        <v>24413548</v>
       </c>
       <c r="O26" t="n">
-        <v>2839260</v>
+        <v>46722261</v>
       </c>
       <c r="P26" t="n">
-        <v>989046</v>
+        <v>19358804</v>
       </c>
       <c r="Q26" t="n">
-        <v>-337021</v>
+        <v>47089739</v>
       </c>
       <c r="R26" t="n">
-        <v>-241872</v>
+        <v>61618385</v>
       </c>
       <c r="S26" t="n">
-        <v>-5316929</v>
+        <v>84170507</v>
       </c>
       <c r="T26" t="n">
-        <v>-792857</v>
+        <v>-30584550</v>
       </c>
       <c r="U26" t="n">
-        <v>2500409</v>
+        <v>-36928324</v>
       </c>
       <c r="V26" t="n">
-        <v>7076238</v>
+        <v>-38412024</v>
       </c>
       <c r="W26" t="n">
-        <v>6501050</v>
+        <v>-38493840</v>
       </c>
       <c r="X26" t="n">
-        <v>602449</v>
+        <v>80780</v>
       </c>
       <c r="Y26" t="n">
-        <v>532653</v>
+        <v>1028981</v>
       </c>
       <c r="Z26" t="n">
-        <v>615876</v>
+        <v>1207187</v>
       </c>
       <c r="AA26" t="n">
-        <v>1655139</v>
+        <v>1045594</v>
       </c>
       <c r="AB26" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -3494,54 +3494,54 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31.4</v>
+        <v>174.5</v>
       </c>
       <c r="D27" t="n">
-        <v>30.36</v>
+        <v>173.1</v>
       </c>
       <c r="E27" t="n">
-        <v>29.89</v>
+        <v>173.15</v>
       </c>
       <c r="F27" t="n">
-        <v>28.67</v>
+        <v>172.62</v>
       </c>
       <c r="G27" t="n">
-        <v>14102000</v>
+        <v>252102</v>
       </c>
       <c r="H27" t="n">
-        <v>12680986</v>
+        <v>236121</v>
       </c>
       <c r="I27" t="n">
-        <v>31.95</v>
+        <v>176.5</v>
       </c>
       <c r="J27" t="n">
-        <v>25.55</v>
+        <v>168.5</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3549,28 +3549,28 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-1578569</v>
+        <v>99000</v>
       </c>
       <c r="M27" t="n">
-        <v>4003880</v>
+        <v>241000</v>
       </c>
       <c r="N27" t="n">
-        <v>5342063</v>
+        <v>281085</v>
       </c>
       <c r="O27" t="n">
-        <v>14183692</v>
+        <v>231866</v>
       </c>
       <c r="P27" t="n">
-        <v>-1656460</v>
+        <v>99000</v>
       </c>
       <c r="Q27" t="n">
-        <v>3489598</v>
+        <v>242000</v>
       </c>
       <c r="R27" t="n">
-        <v>4830671</v>
+        <v>280085</v>
       </c>
       <c r="S27" t="n">
-        <v>13065591</v>
+        <v>231085</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -3585,19 +3585,19 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>77891</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>514282</v>
+        <v>-1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>511392</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>1118101</v>
+        <v>781</v>
       </c>
       <c r="AB27" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -3611,54 +3611,54 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>71</v>
+        <v>82.5</v>
       </c>
       <c r="D28" t="n">
-        <v>72.18000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>70.65000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>69.42</v>
+        <v>81.17</v>
       </c>
       <c r="G28" t="n">
-        <v>148186000</v>
+        <v>14325800</v>
       </c>
       <c r="H28" t="n">
-        <v>142816836</v>
+        <v>15097617</v>
       </c>
       <c r="I28" t="n">
-        <v>81.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>61.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,55 +3666,55 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>36235379</v>
+        <v>-1791149</v>
       </c>
       <c r="M28" t="n">
-        <v>18005086</v>
+        <v>1809752</v>
       </c>
       <c r="N28" t="n">
-        <v>24812582</v>
+        <v>1203067</v>
       </c>
       <c r="O28" t="n">
-        <v>100060322</v>
+        <v>5941752</v>
       </c>
       <c r="P28" t="n">
-        <v>35838589</v>
+        <v>-1607024</v>
       </c>
       <c r="Q28" t="n">
-        <v>17380149</v>
+        <v>1329595</v>
       </c>
       <c r="R28" t="n">
-        <v>21056648</v>
+        <v>813946</v>
       </c>
       <c r="S28" t="n">
-        <v>91577139</v>
+        <v>5531488</v>
       </c>
       <c r="T28" t="n">
-        <v>421000</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1027000</v>
+        <v>-1000</v>
       </c>
       <c r="V28" t="n">
-        <v>2759000</v>
+        <v>-1000</v>
       </c>
       <c r="W28" t="n">
-        <v>2802000</v>
+        <v>-1000</v>
       </c>
       <c r="X28" t="n">
-        <v>-24210</v>
+        <v>-184125</v>
       </c>
       <c r="Y28" t="n">
-        <v>-402063</v>
+        <v>481157</v>
       </c>
       <c r="Z28" t="n">
-        <v>996934</v>
+        <v>390121</v>
       </c>
       <c r="AA28" t="n">
-        <v>5681183</v>
+        <v>411264</v>
       </c>
       <c r="AB28" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -3728,17 +3728,17 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>強勢偏多：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -3754,22 +3754,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>859</v>
+        <v>827</v>
       </c>
       <c r="D29" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="E29" t="n">
-        <v>810.2</v>
+        <v>820.1</v>
       </c>
       <c r="F29" t="n">
-        <v>759.85</v>
+        <v>773.1</v>
       </c>
       <c r="G29" t="n">
-        <v>6258000</v>
+        <v>4610000</v>
       </c>
       <c r="H29" t="n">
-        <v>4776400</v>
+        <v>5370000</v>
       </c>
       <c r="I29" t="n">
         <v>929</v>
@@ -3783,116 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-615906</v>
+        <v>11913</v>
       </c>
       <c r="M29" t="n">
-        <v>317162</v>
+        <v>121167</v>
       </c>
       <c r="N29" t="n">
-        <v>1069118</v>
+        <v>1589915</v>
       </c>
       <c r="O29" t="n">
-        <v>814100</v>
+        <v>810197</v>
       </c>
       <c r="P29" t="n">
-        <v>-931819</v>
+        <v>31444</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1205698</v>
+        <v>-1421000</v>
       </c>
       <c r="R29" t="n">
-        <v>-564120</v>
+        <v>-66042</v>
       </c>
       <c r="S29" t="n">
-        <v>-735635</v>
+        <v>-784088</v>
       </c>
       <c r="T29" t="n">
-        <v>357000</v>
+        <v>9000</v>
       </c>
       <c r="U29" t="n">
-        <v>1549000</v>
+        <v>1561000</v>
       </c>
       <c r="V29" t="n">
-        <v>1533000</v>
+        <v>1558000</v>
       </c>
       <c r="W29" t="n">
-        <v>1333000</v>
+        <v>1344000</v>
       </c>
       <c r="X29" t="n">
-        <v>-41087</v>
+        <v>-28531</v>
       </c>
       <c r="Y29" t="n">
-        <v>-26140</v>
+        <v>-18833</v>
       </c>
       <c r="Z29" t="n">
-        <v>100238</v>
+        <v>97957</v>
       </c>
       <c r="AA29" t="n">
-        <v>216735</v>
+        <v>250285</v>
       </c>
       <c r="AB29" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>174.5</v>
+        <v>26.15</v>
       </c>
       <c r="D30" t="n">
-        <v>173.1</v>
+        <v>23.19</v>
       </c>
       <c r="E30" t="n">
-        <v>173.15</v>
+        <v>22.35</v>
       </c>
       <c r="F30" t="n">
-        <v>172.62</v>
+        <v>20.73</v>
       </c>
       <c r="G30" t="n">
-        <v>243000</v>
+        <v>720567401</v>
       </c>
       <c r="H30" t="n">
-        <v>234301</v>
+        <v>574373597</v>
       </c>
       <c r="I30" t="n">
-        <v>176.5</v>
+        <v>26.15</v>
       </c>
       <c r="J30" t="n">
-        <v>168.5</v>
+        <v>17.5</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,116 +3900,116 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>149000</v>
+        <v>51668289</v>
       </c>
       <c r="M30" t="n">
-        <v>118979</v>
+        <v>8749100</v>
       </c>
       <c r="N30" t="n">
-        <v>180064</v>
+        <v>-78910101</v>
       </c>
       <c r="O30" t="n">
-        <v>203745</v>
+        <v>-55159397</v>
       </c>
       <c r="P30" t="n">
-        <v>149000</v>
+        <v>47814593</v>
       </c>
       <c r="Q30" t="n">
-        <v>121025</v>
+        <v>3801406</v>
       </c>
       <c r="R30" t="n">
-        <v>180110</v>
+        <v>-84520196</v>
       </c>
       <c r="S30" t="n">
-        <v>203110</v>
+        <v>-64382522</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>106000</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>247311</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3851696</v>
       </c>
       <c r="Y30" t="n">
-        <v>-2046</v>
+        <v>4837694</v>
       </c>
       <c r="Z30" t="n">
-        <v>-46</v>
+        <v>5504095</v>
       </c>
       <c r="AA30" t="n">
-        <v>635</v>
+        <v>8975814</v>
       </c>
       <c r="AB30" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4525</v>
+        <v>1590</v>
       </c>
       <c r="D31" t="n">
-        <v>4488</v>
+        <v>1631</v>
       </c>
       <c r="E31" t="n">
-        <v>4159</v>
+        <v>1532</v>
       </c>
       <c r="F31" t="n">
-        <v>3818.25</v>
+        <v>1452.25</v>
       </c>
       <c r="G31" t="n">
-        <v>14126000</v>
+        <v>7939000</v>
       </c>
       <c r="H31" t="n">
-        <v>18402716</v>
+        <v>8698600</v>
       </c>
       <c r="I31" t="n">
-        <v>4970</v>
+        <v>1815</v>
       </c>
       <c r="J31" t="n">
-        <v>3100</v>
+        <v>1160</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,116 +4017,116 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3148836</v>
+        <v>271386</v>
       </c>
       <c r="M31" t="n">
-        <v>-1878848</v>
+        <v>1677669</v>
       </c>
       <c r="N31" t="n">
-        <v>942900</v>
+        <v>2109423</v>
       </c>
       <c r="O31" t="n">
-        <v>-4597456</v>
+        <v>2957821</v>
       </c>
       <c r="P31" t="n">
-        <v>3786804</v>
+        <v>51994</v>
       </c>
       <c r="Q31" t="n">
-        <v>605566</v>
+        <v>-416445</v>
       </c>
       <c r="R31" t="n">
-        <v>4970698</v>
+        <v>-1380385</v>
       </c>
       <c r="S31" t="n">
-        <v>-976834</v>
+        <v>-1408184</v>
       </c>
       <c r="T31" t="n">
-        <v>-461186</v>
+        <v>655000</v>
       </c>
       <c r="U31" t="n">
-        <v>-2105376</v>
+        <v>2600000</v>
       </c>
       <c r="V31" t="n">
-        <v>-3983417</v>
+        <v>4231000</v>
       </c>
       <c r="W31" t="n">
-        <v>-4323474</v>
+        <v>5676700</v>
       </c>
       <c r="X31" t="n">
-        <v>-176782</v>
+        <v>-435608</v>
       </c>
       <c r="Y31" t="n">
-        <v>-379038</v>
+        <v>-505886</v>
       </c>
       <c r="Z31" t="n">
-        <v>-44381</v>
+        <v>-741192</v>
       </c>
       <c r="AA31" t="n">
-        <v>702852</v>
+        <v>-1310695</v>
       </c>
       <c r="AB31" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>975</v>
+        <v>2360</v>
       </c>
       <c r="D32" t="n">
-        <v>1037</v>
+        <v>2427</v>
       </c>
       <c r="E32" t="n">
-        <v>995.8</v>
+        <v>2281.5</v>
       </c>
       <c r="F32" t="n">
-        <v>924.7</v>
+        <v>2213.75</v>
       </c>
       <c r="G32" t="n">
-        <v>25680000</v>
+        <v>12331189</v>
       </c>
       <c r="H32" t="n">
-        <v>23689418</v>
+        <v>12993977</v>
       </c>
       <c r="I32" t="n">
-        <v>1130</v>
+        <v>2585</v>
       </c>
       <c r="J32" t="n">
-        <v>776</v>
+        <v>1880</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,55 +4134,55 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-709629</v>
+        <v>-643318</v>
       </c>
       <c r="M32" t="n">
-        <v>-1610746</v>
+        <v>-604911</v>
       </c>
       <c r="N32" t="n">
-        <v>10872395</v>
+        <v>3203838</v>
       </c>
       <c r="O32" t="n">
-        <v>24914490</v>
+        <v>10063516</v>
       </c>
       <c r="P32" t="n">
-        <v>261132</v>
+        <v>-62543</v>
       </c>
       <c r="Q32" t="n">
-        <v>-544695</v>
+        <v>-724326</v>
       </c>
       <c r="R32" t="n">
-        <v>8333371</v>
+        <v>2791669</v>
       </c>
       <c r="S32" t="n">
-        <v>21412568</v>
+        <v>9284103</v>
       </c>
       <c r="T32" t="n">
-        <v>-917999</v>
+        <v>-400000</v>
       </c>
       <c r="U32" t="n">
-        <v>-674372</v>
+        <v>337387</v>
       </c>
       <c r="V32" t="n">
-        <v>3265628</v>
+        <v>633387</v>
       </c>
       <c r="W32" t="n">
-        <v>3968571</v>
+        <v>-378172</v>
       </c>
       <c r="X32" t="n">
-        <v>-52762</v>
+        <v>-180775</v>
       </c>
       <c r="Y32" t="n">
-        <v>-391679</v>
+        <v>-217972</v>
       </c>
       <c r="Z32" t="n">
-        <v>-726604</v>
+        <v>-221218</v>
       </c>
       <c r="AA32" t="n">
-        <v>-466649</v>
+        <v>1157585</v>
       </c>
       <c r="AB32" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4206,44 +4206,44 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>58.9</v>
+        <v>306</v>
       </c>
       <c r="D33" t="n">
-        <v>59.88</v>
+        <v>310.9</v>
       </c>
       <c r="E33" t="n">
-        <v>57.31</v>
+        <v>301.25</v>
       </c>
       <c r="F33" t="n">
-        <v>57.69</v>
+        <v>283.02</v>
       </c>
       <c r="G33" t="n">
-        <v>15299000</v>
+        <v>13205587</v>
       </c>
       <c r="H33" t="n">
-        <v>25700112</v>
+        <v>23318385</v>
       </c>
       <c r="I33" t="n">
-        <v>64.40000000000001</v>
+        <v>336.5</v>
       </c>
       <c r="J33" t="n">
-        <v>50.2</v>
+        <v>222</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,55 +4251,55 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1051605</v>
+        <v>466343</v>
       </c>
       <c r="M33" t="n">
-        <v>12258933</v>
+        <v>-910778</v>
       </c>
       <c r="N33" t="n">
-        <v>14444946</v>
+        <v>4355234</v>
       </c>
       <c r="O33" t="n">
-        <v>9009446</v>
+        <v>-2914456</v>
       </c>
       <c r="P33" t="n">
-        <v>1587498</v>
+        <v>270014</v>
       </c>
       <c r="Q33" t="n">
-        <v>11720020</v>
+        <v>-1272248</v>
       </c>
       <c r="R33" t="n">
-        <v>13446507</v>
+        <v>2939329</v>
       </c>
       <c r="S33" t="n">
-        <v>8915008</v>
+        <v>2881230</v>
       </c>
       <c r="T33" t="n">
-        <v>12000</v>
+        <v>333000</v>
       </c>
       <c r="U33" t="n">
-        <v>12000</v>
+        <v>624000</v>
       </c>
       <c r="V33" t="n">
-        <v>12000</v>
+        <v>1525000</v>
       </c>
       <c r="W33" t="n">
-        <v>204000</v>
+        <v>-5727404</v>
       </c>
       <c r="X33" t="n">
-        <v>-547893</v>
+        <v>-136671</v>
       </c>
       <c r="Y33" t="n">
-        <v>526913</v>
+        <v>-262530</v>
       </c>
       <c r="Z33" t="n">
-        <v>986439</v>
+        <v>-109095</v>
       </c>
       <c r="AA33" t="n">
-        <v>-109562</v>
+        <v>-68282</v>
       </c>
       <c r="AB33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -4313,54 +4313,54 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2360</v>
+        <v>273</v>
       </c>
       <c r="D34" t="n">
-        <v>2427</v>
+        <v>274.8</v>
       </c>
       <c r="E34" t="n">
-        <v>2281.5</v>
+        <v>266.05</v>
       </c>
       <c r="F34" t="n">
-        <v>2213.75</v>
+        <v>269.93</v>
       </c>
       <c r="G34" t="n">
-        <v>10966000</v>
+        <v>26520106</v>
       </c>
       <c r="H34" t="n">
-        <v>12720939</v>
+        <v>26276561</v>
       </c>
       <c r="I34" t="n">
-        <v>2585</v>
+        <v>322</v>
       </c>
       <c r="J34" t="n">
-        <v>1880</v>
+        <v>230</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,69 +4368,69 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-769525</v>
+        <v>-7536732</v>
       </c>
       <c r="M34" t="n">
-        <v>-1974477</v>
+        <v>8624099</v>
       </c>
       <c r="N34" t="n">
-        <v>4400784</v>
+        <v>13935232</v>
       </c>
       <c r="O34" t="n">
-        <v>6318632</v>
+        <v>13950421</v>
       </c>
       <c r="P34" t="n">
-        <v>-821342</v>
+        <v>-7246250</v>
       </c>
       <c r="Q34" t="n">
-        <v>-2404327</v>
+        <v>8266224</v>
       </c>
       <c r="R34" t="n">
-        <v>3439207</v>
+        <v>13367750</v>
       </c>
       <c r="S34" t="n">
-        <v>7261138</v>
+        <v>12912259</v>
       </c>
       <c r="T34" t="n">
-        <v>133000</v>
+        <v>118000</v>
       </c>
       <c r="U34" t="n">
-        <v>616198</v>
+        <v>115000</v>
       </c>
       <c r="V34" t="n">
-        <v>1073098</v>
+        <v>44000</v>
       </c>
       <c r="W34" t="n">
-        <v>-1265676</v>
+        <v>-127000</v>
       </c>
       <c r="X34" t="n">
-        <v>-81183</v>
+        <v>-408482</v>
       </c>
       <c r="Y34" t="n">
-        <v>-186348</v>
+        <v>242875</v>
       </c>
       <c r="Z34" t="n">
-        <v>-111521</v>
+        <v>523482</v>
       </c>
       <c r="AA34" t="n">
-        <v>323170</v>
+        <v>1165162</v>
       </c>
       <c r="AB34" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4440,44 +4440,44 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>整理觀察：跌破5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>306</v>
+        <v>20.65</v>
       </c>
       <c r="D35" t="n">
-        <v>310.9</v>
+        <v>17.32</v>
       </c>
       <c r="E35" t="n">
-        <v>301.25</v>
+        <v>14.57</v>
       </c>
       <c r="F35" t="n">
-        <v>283.02</v>
+        <v>12.28</v>
       </c>
       <c r="G35" t="n">
-        <v>12811000</v>
+        <v>200560076</v>
       </c>
       <c r="H35" t="n">
-        <v>23239467</v>
+        <v>233594287</v>
       </c>
       <c r="I35" t="n">
-        <v>336.5</v>
+        <v>20.65</v>
       </c>
       <c r="J35" t="n">
-        <v>222</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,116 +4485,116 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-3145576</v>
+        <v>14551105</v>
       </c>
       <c r="M35" t="n">
-        <v>-2096880</v>
+        <v>17008140</v>
       </c>
       <c r="N35" t="n">
-        <v>8442316</v>
+        <v>-1362899</v>
       </c>
       <c r="O35" t="n">
-        <v>-2780785</v>
+        <v>16803068</v>
       </c>
       <c r="P35" t="n">
-        <v>-3049921</v>
+        <v>13971173</v>
       </c>
       <c r="Q35" t="n">
-        <v>-2116785</v>
+        <v>14482349</v>
       </c>
       <c r="R35" t="n">
-        <v>7052430</v>
+        <v>-5991014</v>
       </c>
       <c r="S35" t="n">
-        <v>3656099</v>
+        <v>13197789</v>
       </c>
       <c r="T35" t="n">
-        <v>152000</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>311768</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1427768</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>-5810208</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>-247655</v>
+        <v>579932</v>
       </c>
       <c r="Y35" t="n">
-        <v>-291863</v>
+        <v>2525791</v>
       </c>
       <c r="Z35" t="n">
-        <v>-37882</v>
+        <v>4628115</v>
       </c>
       <c r="AA35" t="n">
-        <v>-626676</v>
+        <v>3605279</v>
       </c>
       <c r="AB35" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2401.TW</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>28.9</v>
+        <v>27.55</v>
       </c>
       <c r="D36" t="n">
-        <v>29.93</v>
+        <v>23.01</v>
       </c>
       <c r="E36" t="n">
-        <v>29.64</v>
+        <v>20.11</v>
       </c>
       <c r="F36" t="n">
-        <v>27.4</v>
+        <v>18.5</v>
       </c>
       <c r="G36" t="n">
-        <v>11749000</v>
+        <v>25800849</v>
       </c>
       <c r="H36" t="n">
-        <v>16666452</v>
+        <v>38924464</v>
       </c>
       <c r="I36" t="n">
-        <v>33</v>
+        <v>27.55</v>
       </c>
       <c r="J36" t="n">
-        <v>23.45</v>
+        <v>16.6</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,55 +4602,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-603883</v>
+        <v>-101324</v>
       </c>
       <c r="M36" t="n">
-        <v>-278540</v>
+        <v>1411927</v>
       </c>
       <c r="N36" t="n">
-        <v>144595</v>
+        <v>-413632</v>
       </c>
       <c r="O36" t="n">
-        <v>-2240107</v>
+        <v>19867934</v>
       </c>
       <c r="P36" t="n">
-        <v>-599884</v>
+        <v>-1353388</v>
       </c>
       <c r="Q36" t="n">
-        <v>112872</v>
+        <v>-2893388</v>
       </c>
       <c r="R36" t="n">
-        <v>376871</v>
+        <v>-5692553</v>
       </c>
       <c r="S36" t="n">
-        <v>-3761253</v>
+        <v>14017799</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="U36" t="n">
-        <v>1000</v>
+        <v>-8000</v>
       </c>
       <c r="V36" t="n">
-        <v>1000</v>
+        <v>-12000</v>
       </c>
       <c r="W36" t="n">
-        <v>234000</v>
+        <v>319000</v>
       </c>
       <c r="X36" t="n">
-        <v>-3999</v>
+        <v>1256064</v>
       </c>
       <c r="Y36" t="n">
-        <v>-392412</v>
+        <v>4313315</v>
       </c>
       <c r="Z36" t="n">
-        <v>-233276</v>
+        <v>5290921</v>
       </c>
       <c r="AA36" t="n">
-        <v>1287146</v>
+        <v>5531135</v>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -4664,54 +4664,54 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6213.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>273</v>
+        <v>4860</v>
       </c>
       <c r="D37" t="n">
-        <v>274.8</v>
+        <v>5082</v>
       </c>
       <c r="E37" t="n">
-        <v>266.05</v>
+        <v>5029.5</v>
       </c>
       <c r="F37" t="n">
-        <v>269.93</v>
+        <v>4912.5</v>
       </c>
       <c r="G37" t="n">
-        <v>25826000</v>
+        <v>2172811</v>
       </c>
       <c r="H37" t="n">
-        <v>26137740</v>
+        <v>2553339</v>
       </c>
       <c r="I37" t="n">
-        <v>322</v>
+        <v>5635</v>
       </c>
       <c r="J37" t="n">
-        <v>230</v>
+        <v>4300</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,55 +4719,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>12348068</v>
+        <v>-196630</v>
       </c>
       <c r="M37" t="n">
-        <v>8160032</v>
+        <v>-192736</v>
       </c>
       <c r="N37" t="n">
-        <v>15069872</v>
+        <v>300883</v>
       </c>
       <c r="O37" t="n">
-        <v>12457873</v>
+        <v>1484851</v>
       </c>
       <c r="P37" t="n">
-        <v>11994537</v>
+        <v>7560</v>
       </c>
       <c r="Q37" t="n">
-        <v>7819120</v>
+        <v>577741</v>
       </c>
       <c r="R37" t="n">
-        <v>13707371</v>
+        <v>930106</v>
       </c>
       <c r="S37" t="n">
-        <v>11456171</v>
+        <v>2367165</v>
       </c>
       <c r="T37" t="n">
-        <v>-3000</v>
+        <v>-141028</v>
       </c>
       <c r="U37" t="n">
-        <v>-3000</v>
+        <v>-703946</v>
       </c>
       <c r="V37" t="n">
-        <v>-241000</v>
+        <v>-560048</v>
       </c>
       <c r="W37" t="n">
-        <v>-251000</v>
+        <v>-692687</v>
       </c>
       <c r="X37" t="n">
-        <v>356531</v>
+        <v>-63162</v>
       </c>
       <c r="Y37" t="n">
-        <v>343912</v>
+        <v>-66531</v>
       </c>
       <c r="Z37" t="n">
-        <v>1603501</v>
+        <v>-69175</v>
       </c>
       <c r="AA37" t="n">
-        <v>1252702</v>
+        <v>-189627</v>
       </c>
       <c r="AB37" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -4781,54 +4781,54 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1905</v>
+        <v>39.65</v>
       </c>
       <c r="D38" t="n">
-        <v>1761</v>
+        <v>39.12</v>
       </c>
       <c r="E38" t="n">
-        <v>1733</v>
+        <v>39.18</v>
       </c>
       <c r="F38" t="n">
-        <v>1710.5</v>
+        <v>39.62</v>
       </c>
       <c r="G38" t="n">
-        <v>4954000</v>
+        <v>89464</v>
       </c>
       <c r="H38" t="n">
-        <v>4262400</v>
+        <v>158603</v>
       </c>
       <c r="I38" t="n">
-        <v>1950</v>
+        <v>42.45</v>
       </c>
       <c r="J38" t="n">
-        <v>1310</v>
+        <v>38.5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,55 +4836,55 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-327662</v>
+        <v>23000</v>
       </c>
       <c r="M38" t="n">
-        <v>321027</v>
+        <v>97000</v>
       </c>
       <c r="N38" t="n">
-        <v>-817069</v>
+        <v>66452</v>
       </c>
       <c r="O38" t="n">
-        <v>-1685578</v>
+        <v>-24080</v>
       </c>
       <c r="P38" t="n">
-        <v>-356590</v>
+        <v>23000</v>
       </c>
       <c r="Q38" t="n">
-        <v>-349587</v>
+        <v>98000</v>
       </c>
       <c r="R38" t="n">
-        <v>-1159255</v>
+        <v>67023</v>
       </c>
       <c r="S38" t="n">
-        <v>-1295494</v>
+        <v>-22977</v>
       </c>
       <c r="T38" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>626500</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>319123</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>-312710</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>5928</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>44114</v>
+        <v>-1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>23063</v>
+        <v>-571</v>
       </c>
       <c r="AA38" t="n">
-        <v>-77374</v>
+        <v>-1103</v>
       </c>
       <c r="AB38" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -4898,54 +4898,54 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人小幅買超</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>20.65</v>
+        <v>1875</v>
       </c>
       <c r="D39" t="n">
-        <v>17.32</v>
+        <v>1529</v>
       </c>
       <c r="E39" t="n">
-        <v>14.57</v>
+        <v>1331</v>
       </c>
       <c r="F39" t="n">
-        <v>12.28</v>
+        <v>1209.4</v>
       </c>
       <c r="G39" t="n">
-        <v>197735000</v>
+        <v>4097000</v>
       </c>
       <c r="H39" t="n">
-        <v>233029272</v>
+        <v>5968800</v>
       </c>
       <c r="I39" t="n">
-        <v>20.65</v>
+        <v>1950</v>
       </c>
       <c r="J39" t="n">
-        <v>8.390000000000001</v>
+        <v>971</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,55 +4953,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-2827260</v>
+        <v>27169</v>
       </c>
       <c r="M39" t="n">
-        <v>9048582</v>
+        <v>-170558</v>
       </c>
       <c r="N39" t="n">
-        <v>-47490059</v>
+        <v>-322749</v>
       </c>
       <c r="O39" t="n">
-        <v>8792749</v>
+        <v>-1754207</v>
       </c>
       <c r="P39" t="n">
-        <v>-3854960</v>
+        <v>-29043</v>
       </c>
       <c r="Q39" t="n">
-        <v>6757407</v>
+        <v>-646165</v>
       </c>
       <c r="R39" t="n">
-        <v>-48015620</v>
+        <v>-998103</v>
       </c>
       <c r="S39" t="n">
-        <v>6500797</v>
+        <v>-1526645</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>73241</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>452741</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>656981</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>-222136</v>
       </c>
       <c r="X39" t="n">
-        <v>1027700</v>
+        <v>-17029</v>
       </c>
       <c r="Y39" t="n">
-        <v>2291175</v>
+        <v>22866</v>
       </c>
       <c r="Z39" t="n">
-        <v>525561</v>
+        <v>18373</v>
       </c>
       <c r="AA39" t="n">
-        <v>2291952</v>
+        <v>-5426</v>
       </c>
       <c r="AB39" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -5015,54 +5015,54 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>347</v>
+        <v>231</v>
       </c>
       <c r="D40" t="n">
-        <v>358</v>
+        <v>223</v>
       </c>
       <c r="E40" t="n">
-        <v>321.8</v>
+        <v>214.8</v>
       </c>
       <c r="F40" t="n">
-        <v>277.15</v>
+        <v>199.38</v>
       </c>
       <c r="G40" t="n">
-        <v>22914000</v>
+        <v>7792000</v>
       </c>
       <c r="H40" t="n">
-        <v>42942610</v>
+        <v>12208400</v>
       </c>
       <c r="I40" t="n">
-        <v>387</v>
+        <v>249.5</v>
       </c>
       <c r="J40" t="n">
-        <v>217.5</v>
+        <v>153</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5070,55 +5070,55 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-1423317</v>
+        <v>177429</v>
       </c>
       <c r="M40" t="n">
-        <v>5682114</v>
+        <v>865412</v>
       </c>
       <c r="N40" t="n">
-        <v>9371560</v>
+        <v>-128264</v>
       </c>
       <c r="O40" t="n">
-        <v>3387386</v>
+        <v>3056820</v>
       </c>
       <c r="P40" t="n">
-        <v>-496203</v>
+        <v>227465</v>
       </c>
       <c r="Q40" t="n">
-        <v>7240655</v>
+        <v>867681</v>
       </c>
       <c r="R40" t="n">
-        <v>9811506</v>
+        <v>-219524</v>
       </c>
       <c r="S40" t="n">
-        <v>8084759</v>
+        <v>2660079</v>
       </c>
       <c r="T40" t="n">
-        <v>-570594</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>-1714782</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>-1000376</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>-4914478</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>-356520</v>
+        <v>-50036</v>
       </c>
       <c r="Y40" t="n">
-        <v>156241</v>
+        <v>-2269</v>
       </c>
       <c r="Z40" t="n">
-        <v>560430</v>
+        <v>91260</v>
       </c>
       <c r="AA40" t="n">
-        <v>217105</v>
+        <v>396741</v>
       </c>
       <c r="AB40" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -5132,171 +5132,171 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人賣超</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>2331.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>436</v>
+        <v>25.6</v>
       </c>
       <c r="D41" t="n">
-        <v>449.5</v>
+        <v>22.59</v>
       </c>
       <c r="E41" t="n">
-        <v>412.1</v>
+        <v>21.5</v>
       </c>
       <c r="F41" t="n">
-        <v>396.05</v>
+        <v>20.79</v>
       </c>
       <c r="G41" t="n">
-        <v>7911000</v>
+        <v>36583316</v>
       </c>
       <c r="H41" t="n">
-        <v>13922400</v>
+        <v>12732709</v>
       </c>
       <c r="I41" t="n">
-        <v>492.5</v>
+        <v>26.5</v>
       </c>
       <c r="J41" t="n">
-        <v>343</v>
+        <v>18.6</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-683330</v>
+        <v>-5054803</v>
       </c>
       <c r="M41" t="n">
-        <v>-4127623</v>
+        <v>-806673</v>
       </c>
       <c r="N41" t="n">
-        <v>2298622</v>
+        <v>-938616</v>
       </c>
       <c r="O41" t="n">
-        <v>8649847</v>
+        <v>-5832004</v>
       </c>
       <c r="P41" t="n">
-        <v>-556866</v>
+        <v>-5074257</v>
       </c>
       <c r="Q41" t="n">
-        <v>-3731197</v>
+        <v>-1166267</v>
       </c>
       <c r="R41" t="n">
-        <v>2723249</v>
+        <v>-1251662</v>
       </c>
       <c r="S41" t="n">
-        <v>13038703</v>
+        <v>-6204162</v>
       </c>
       <c r="T41" t="n">
-        <v>-75000</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>-331000</v>
+        <v>-8000</v>
       </c>
       <c r="V41" t="n">
-        <v>-434000</v>
+        <v>-18000</v>
       </c>
       <c r="W41" t="n">
-        <v>-5185631</v>
+        <v>-68000</v>
       </c>
       <c r="X41" t="n">
-        <v>-51464</v>
+        <v>19454</v>
       </c>
       <c r="Y41" t="n">
-        <v>-65426</v>
+        <v>367594</v>
       </c>
       <c r="Z41" t="n">
-        <v>9373</v>
+        <v>331046</v>
       </c>
       <c r="AA41" t="n">
-        <v>796775</v>
+        <v>440158</v>
       </c>
       <c r="AB41" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5475</v>
+        <v>846</v>
       </c>
       <c r="D42" t="n">
-        <v>5292</v>
+        <v>763.4</v>
       </c>
       <c r="E42" t="n">
-        <v>5313</v>
+        <v>689</v>
       </c>
       <c r="F42" t="n">
-        <v>5271</v>
+        <v>556.75</v>
       </c>
       <c r="G42" t="n">
-        <v>1735000</v>
+        <v>23216094</v>
       </c>
       <c r="H42" t="n">
-        <v>2285230</v>
+        <v>26855860</v>
       </c>
       <c r="I42" t="n">
-        <v>5880</v>
+        <v>847</v>
       </c>
       <c r="J42" t="n">
-        <v>4630</v>
+        <v>331</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5304,116 +5304,116 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-53222</v>
+        <v>1273667</v>
       </c>
       <c r="M42" t="n">
-        <v>656900</v>
+        <v>-564007</v>
       </c>
       <c r="N42" t="n">
-        <v>77693</v>
+        <v>-2699278</v>
       </c>
       <c r="O42" t="n">
-        <v>-83131</v>
+        <v>50682</v>
       </c>
       <c r="P42" t="n">
-        <v>-133821</v>
+        <v>1072706</v>
       </c>
       <c r="Q42" t="n">
-        <v>683080</v>
+        <v>-2105887</v>
       </c>
       <c r="R42" t="n">
-        <v>588871</v>
+        <v>-5496148</v>
       </c>
       <c r="S42" t="n">
-        <v>590076</v>
+        <v>-21084617</v>
       </c>
       <c r="T42" t="n">
-        <v>83002</v>
+        <v>113000</v>
       </c>
       <c r="U42" t="n">
-        <v>66976</v>
+        <v>378110</v>
       </c>
       <c r="V42" t="n">
-        <v>-260347</v>
+        <v>419110</v>
       </c>
       <c r="W42" t="n">
-        <v>-552553</v>
+        <v>15968446</v>
       </c>
       <c r="X42" t="n">
-        <v>-2403</v>
+        <v>87961</v>
       </c>
       <c r="Y42" t="n">
-        <v>-93156</v>
+        <v>1163770</v>
       </c>
       <c r="Z42" t="n">
-        <v>-250831</v>
+        <v>2377760</v>
       </c>
       <c r="AA42" t="n">
-        <v>-120654</v>
+        <v>5166853</v>
       </c>
       <c r="AB42" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>5日法人小幅買超、外資買投信賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、5日法人小幅買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>26.15</v>
+        <v>232</v>
       </c>
       <c r="D43" t="n">
-        <v>23.19</v>
+        <v>209.8</v>
       </c>
       <c r="E43" t="n">
-        <v>22.35</v>
+        <v>196.5</v>
       </c>
       <c r="F43" t="n">
-        <v>20.73</v>
+        <v>168.05</v>
       </c>
       <c r="G43" t="n">
-        <v>717899000</v>
+        <v>3785000</v>
       </c>
       <c r="H43" t="n">
-        <v>573839917</v>
+        <v>1949600</v>
       </c>
       <c r="I43" t="n">
-        <v>26.15</v>
+        <v>249.5</v>
       </c>
       <c r="J43" t="n">
-        <v>17.5</v>
+        <v>102</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5421,116 +5421,116 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-112395402</v>
+        <v>-540940</v>
       </c>
       <c r="M43" t="n">
-        <v>-45567724</v>
+        <v>-1261064</v>
       </c>
       <c r="N43" t="n">
-        <v>-302696130</v>
+        <v>-2617931</v>
       </c>
       <c r="O43" t="n">
-        <v>-109753488</v>
+        <v>-2682038</v>
       </c>
       <c r="P43" t="n">
-        <v>-110354526</v>
+        <v>-542508</v>
       </c>
       <c r="Q43" t="n">
-        <v>-44853879</v>
+        <v>-1220584</v>
       </c>
       <c r="R43" t="n">
-        <v>-299305020</v>
+        <v>-2534031</v>
       </c>
       <c r="S43" t="n">
-        <v>-110957767</v>
+        <v>-2388726</v>
       </c>
       <c r="T43" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>193252</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>311198</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>334507</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>-2139876</v>
+        <v>1568</v>
       </c>
       <c r="Y43" t="n">
-        <v>-907097</v>
+        <v>-40480</v>
       </c>
       <c r="Z43" t="n">
-        <v>-3702308</v>
+        <v>-83900</v>
       </c>
       <c r="AA43" t="n">
-        <v>869772</v>
+        <v>-293312</v>
       </c>
       <c r="AB43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、成交量放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4860</v>
+        <v>862</v>
       </c>
       <c r="D44" t="n">
-        <v>5082</v>
+        <v>874</v>
       </c>
       <c r="E44" t="n">
-        <v>5029.5</v>
+        <v>881.1</v>
       </c>
       <c r="F44" t="n">
-        <v>4912.5</v>
+        <v>873.1</v>
       </c>
       <c r="G44" t="n">
-        <v>1861000</v>
+        <v>14435807</v>
       </c>
       <c r="H44" t="n">
-        <v>2490977</v>
+        <v>19418216</v>
       </c>
       <c r="I44" t="n">
-        <v>5635</v>
+        <v>1025</v>
       </c>
       <c r="J44" t="n">
-        <v>4300</v>
+        <v>765</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5538,69 +5538,69 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>40320</v>
+        <v>-3484177</v>
       </c>
       <c r="M44" t="n">
-        <v>-122468</v>
+        <v>556777</v>
       </c>
       <c r="N44" t="n">
-        <v>166030</v>
+        <v>303458</v>
       </c>
       <c r="O44" t="n">
-        <v>1613933</v>
+        <v>317155</v>
       </c>
       <c r="P44" t="n">
-        <v>718402</v>
+        <v>-3124991</v>
       </c>
       <c r="Q44" t="n">
-        <v>433901</v>
+        <v>2667915</v>
       </c>
       <c r="R44" t="n">
-        <v>716299</v>
+        <v>3244827</v>
       </c>
       <c r="S44" t="n">
-        <v>2524668</v>
+        <v>3737072</v>
       </c>
       <c r="T44" t="n">
-        <v>-654000</v>
+        <v>-199000</v>
       </c>
       <c r="U44" t="n">
-        <v>-514223</v>
+        <v>-1848000</v>
       </c>
       <c r="V44" t="n">
-        <v>-438311</v>
+        <v>-2640000</v>
       </c>
       <c r="W44" t="n">
-        <v>-713363</v>
+        <v>-2756000</v>
       </c>
       <c r="X44" t="n">
-        <v>-24082</v>
+        <v>-160186</v>
       </c>
       <c r="Y44" t="n">
-        <v>-42146</v>
+        <v>-263138</v>
       </c>
       <c r="Z44" t="n">
-        <v>-111958</v>
+        <v>-301369</v>
       </c>
       <c r="AA44" t="n">
-        <v>-197372</v>
+        <v>-663917</v>
       </c>
       <c r="AB44" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5610,44 +5610,44 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>238.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>219.8</v>
+        <v>72.52</v>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>72.75</v>
       </c>
       <c r="F45" t="n">
-        <v>195.62</v>
+        <v>70.87</v>
       </c>
       <c r="G45" t="n">
-        <v>19177000</v>
+        <v>15331008</v>
       </c>
       <c r="H45" t="n">
-        <v>13984200</v>
+        <v>25563103</v>
       </c>
       <c r="I45" t="n">
-        <v>249.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>152</v>
+        <v>64.7</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5655,116 +5655,116 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-1234497</v>
+        <v>-689746</v>
       </c>
       <c r="M45" t="n">
-        <v>349950</v>
+        <v>166710</v>
       </c>
       <c r="N45" t="n">
-        <v>-1644077</v>
+        <v>115839</v>
       </c>
       <c r="O45" t="n">
-        <v>2368303</v>
+        <v>4215966</v>
       </c>
       <c r="P45" t="n">
-        <v>-1242784</v>
+        <v>-461554</v>
       </c>
       <c r="Q45" t="n">
-        <v>172281</v>
+        <v>133867</v>
       </c>
       <c r="R45" t="n">
-        <v>-1748758</v>
+        <v>11310</v>
       </c>
       <c r="S45" t="n">
-        <v>2128596</v>
+        <v>2227920</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="V45" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="X45" t="n">
+        <v>-228192</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>35843</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>107529</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1995046</v>
+      </c>
+      <c r="AB45" t="n">
         <v>0</v>
       </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>8287</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>177669</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>104681</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>239707</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>25</v>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>209.5</v>
+        <v>4525</v>
       </c>
       <c r="D46" t="n">
-        <v>207.7</v>
+        <v>4488</v>
       </c>
       <c r="E46" t="n">
-        <v>207.35</v>
+        <v>4159</v>
       </c>
       <c r="F46" t="n">
-        <v>199.1</v>
+        <v>3818.25</v>
       </c>
       <c r="G46" t="n">
-        <v>14218000</v>
+        <v>15626708</v>
       </c>
       <c r="H46" t="n">
-        <v>14445626</v>
+        <v>18702858</v>
       </c>
       <c r="I46" t="n">
-        <v>231</v>
+        <v>4970</v>
       </c>
       <c r="J46" t="n">
-        <v>173</v>
+        <v>3100</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5772,56 +5772,56 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>638592</v>
+        <v>-1798696</v>
       </c>
       <c r="M46" t="n">
-        <v>805083</v>
+        <v>-2125461</v>
       </c>
       <c r="N46" t="n">
-        <v>-4178927</v>
+        <v>-279858</v>
       </c>
       <c r="O46" t="n">
-        <v>2818703</v>
+        <v>-2958843</v>
       </c>
       <c r="P46" t="n">
-        <v>238712</v>
+        <v>-661060</v>
       </c>
       <c r="Q46" t="n">
-        <v>306561</v>
+        <v>800937</v>
       </c>
       <c r="R46" t="n">
-        <v>-3806044</v>
+        <v>3798772</v>
       </c>
       <c r="S46" t="n">
-        <v>1881767</v>
+        <v>302132</v>
       </c>
       <c r="T46" t="n">
+        <v>-745772</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-2227468</v>
+      </c>
+      <c r="V46" t="n">
+        <v>-3507077</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-3955946</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-391864</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>-698930</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-571553</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>694971</v>
+      </c>
+      <c r="AB46" t="n">
         <v>0</v>
       </c>
-      <c r="U46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="W46" t="n">
-        <v>-55316</v>
-      </c>
-      <c r="X46" t="n">
-        <v>399880</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>496522</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>-374883</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>992252</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>15</v>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
           <t>❌避開</t>
@@ -5839,49 +5839,49 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>82.5</v>
+        <v>209.5</v>
       </c>
       <c r="D47" t="n">
-        <v>81.95999999999999</v>
+        <v>207.7</v>
       </c>
       <c r="E47" t="n">
-        <v>81.84999999999999</v>
+        <v>207.35</v>
       </c>
       <c r="F47" t="n">
-        <v>81.17</v>
+        <v>199.1</v>
       </c>
       <c r="G47" t="n">
-        <v>14116000</v>
+        <v>14574649</v>
       </c>
       <c r="H47" t="n">
-        <v>15055657</v>
+        <v>14516956</v>
       </c>
       <c r="I47" t="n">
-        <v>86.40000000000001</v>
+        <v>231</v>
       </c>
       <c r="J47" t="n">
-        <v>77.09999999999999</v>
+        <v>173</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5889,55 +5889,55 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>525384</v>
+        <v>-351631</v>
       </c>
       <c r="M47" t="n">
-        <v>2970153</v>
+        <v>-2419497</v>
       </c>
       <c r="N47" t="n">
-        <v>-83282</v>
+        <v>-3934873</v>
       </c>
       <c r="O47" t="n">
-        <v>4290817</v>
+        <v>-480416</v>
       </c>
       <c r="P47" t="n">
-        <v>244033</v>
+        <v>-631340</v>
       </c>
       <c r="Q47" t="n">
-        <v>2393134</v>
+        <v>-3108768</v>
       </c>
       <c r="R47" t="n">
-        <v>-482721</v>
+        <v>-4477823</v>
       </c>
       <c r="S47" t="n">
-        <v>4206293</v>
+        <v>-1637103</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>-1000</v>
+        <v>2000</v>
       </c>
       <c r="V47" t="n">
-        <v>-1000</v>
+        <v>2000</v>
       </c>
       <c r="W47" t="n">
-        <v>-1000</v>
+        <v>7000</v>
       </c>
       <c r="X47" t="n">
-        <v>281351</v>
+        <v>279709</v>
       </c>
       <c r="Y47" t="n">
-        <v>578019</v>
+        <v>687271</v>
       </c>
       <c r="Z47" t="n">
-        <v>400439</v>
+        <v>540950</v>
       </c>
       <c r="AA47" t="n">
-        <v>85524</v>
+        <v>1149687</v>
       </c>
       <c r="AB47" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -5951,54 +5951,54 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>5日法人小幅賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人小幅賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2401.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10.5</v>
+        <v>28.9</v>
       </c>
       <c r="D48" t="n">
-        <v>9.210000000000001</v>
+        <v>29.93</v>
       </c>
       <c r="E48" t="n">
-        <v>8.01</v>
+        <v>29.64</v>
       </c>
       <c r="F48" t="n">
-        <v>6.86</v>
+        <v>27.4</v>
       </c>
       <c r="G48" t="n">
-        <v>270390000</v>
+        <v>11825676</v>
       </c>
       <c r="H48" t="n">
-        <v>231371410</v>
+        <v>16681787</v>
       </c>
       <c r="I48" t="n">
-        <v>10.6</v>
+        <v>33</v>
       </c>
       <c r="J48" t="n">
-        <v>5.55</v>
+        <v>23.45</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6006,55 +6006,55 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>17102138</v>
+        <v>2082234</v>
       </c>
       <c r="M48" t="n">
-        <v>-10102801</v>
+        <v>-383861</v>
       </c>
       <c r="N48" t="n">
-        <v>-1903688</v>
+        <v>-3016974</v>
       </c>
       <c r="O48" t="n">
-        <v>32520599</v>
+        <v>-2087771</v>
       </c>
       <c r="P48" t="n">
-        <v>16867220</v>
+        <v>2238069</v>
       </c>
       <c r="Q48" t="n">
-        <v>-10204580</v>
+        <v>-242568</v>
       </c>
       <c r="R48" t="n">
-        <v>395471</v>
+        <v>-2862566</v>
       </c>
       <c r="S48" t="n">
-        <v>26845071</v>
+        <v>-3784693</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>174000</v>
       </c>
       <c r="X48" t="n">
-        <v>234918</v>
+        <v>-155835</v>
       </c>
       <c r="Y48" t="n">
-        <v>101779</v>
+        <v>-142293</v>
       </c>
       <c r="Z48" t="n">
-        <v>-2299159</v>
+        <v>-155408</v>
       </c>
       <c r="AA48" t="n">
-        <v>5675528</v>
+        <v>1522922</v>
       </c>
       <c r="AB48" t="n">
-        <v>15</v>
+        <v>-25</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -6068,54 +6068,54 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>862</v>
+        <v>92</v>
       </c>
       <c r="D49" t="n">
-        <v>874</v>
+        <v>87.34</v>
       </c>
       <c r="E49" t="n">
-        <v>881.1</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>873.1</v>
+        <v>73.28</v>
       </c>
       <c r="G49" t="n">
-        <v>13344000</v>
+        <v>49966718</v>
       </c>
       <c r="H49" t="n">
-        <v>19199854</v>
+        <v>49151750</v>
       </c>
       <c r="I49" t="n">
-        <v>1025</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>765</v>
+        <v>58.1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6123,55 +6123,55 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6489767</v>
+        <v>-4365565</v>
       </c>
       <c r="M49" t="n">
-        <v>-2035790</v>
+        <v>-11883977</v>
       </c>
       <c r="N49" t="n">
-        <v>2257312</v>
+        <v>-12265653</v>
       </c>
       <c r="O49" t="n">
-        <v>-2252248</v>
+        <v>1356791</v>
       </c>
       <c r="P49" t="n">
-        <v>5749529</v>
+        <v>-3981207</v>
       </c>
       <c r="Q49" t="n">
-        <v>1761213</v>
+        <v>-11674894</v>
       </c>
       <c r="R49" t="n">
-        <v>7285342</v>
+        <v>-11837513</v>
       </c>
       <c r="S49" t="n">
-        <v>2700083</v>
+        <v>94554</v>
       </c>
       <c r="T49" t="n">
-        <v>764000</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>-3636000</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>-4848000</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>-4370000</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>-23762</v>
+        <v>-384358</v>
       </c>
       <c r="Y49" t="n">
-        <v>-161003</v>
+        <v>-209083</v>
       </c>
       <c r="Z49" t="n">
-        <v>-180030</v>
+        <v>-428140</v>
       </c>
       <c r="AA49" t="n">
-        <v>-582331</v>
+        <v>1262237</v>
       </c>
       <c r="AB49" t="n">
-        <v>10</v>
+        <v>-25</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
@@ -6185,54 +6185,54 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>846</v>
+        <v>2425</v>
       </c>
       <c r="D50" t="n">
-        <v>763.4</v>
+        <v>2484</v>
       </c>
       <c r="E50" t="n">
-        <v>689</v>
+        <v>2488.5</v>
       </c>
       <c r="F50" t="n">
-        <v>556.75</v>
+        <v>2496</v>
       </c>
       <c r="G50" t="n">
-        <v>21537000</v>
+        <v>3795060</v>
       </c>
       <c r="H50" t="n">
-        <v>26520041</v>
+        <v>4512296</v>
       </c>
       <c r="I50" t="n">
-        <v>847</v>
+        <v>2695</v>
       </c>
       <c r="J50" t="n">
-        <v>331</v>
+        <v>2305</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6240,55 +6240,55 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2783607</v>
+        <v>-314589</v>
       </c>
       <c r="M50" t="n">
-        <v>-2766212</v>
+        <v>139112</v>
       </c>
       <c r="N50" t="n">
-        <v>-7325603</v>
+        <v>180195</v>
       </c>
       <c r="O50" t="n">
-        <v>2033666</v>
+        <v>1067441</v>
       </c>
       <c r="P50" t="n">
-        <v>2259367</v>
+        <v>373206</v>
       </c>
       <c r="Q50" t="n">
-        <v>-4591005</v>
+        <v>1331824</v>
       </c>
       <c r="R50" t="n">
-        <v>-11733299</v>
+        <v>1478892</v>
       </c>
       <c r="S50" t="n">
-        <v>-24723912</v>
+        <v>2546361</v>
       </c>
       <c r="T50" t="n">
-        <v>-13000</v>
+        <v>-512455</v>
       </c>
       <c r="U50" t="n">
-        <v>291532</v>
+        <v>-937132</v>
       </c>
       <c r="V50" t="n">
-        <v>456740</v>
+        <v>-1002722</v>
       </c>
       <c r="W50" t="n">
-        <v>21227740</v>
+        <v>-1022089</v>
       </c>
       <c r="X50" t="n">
-        <v>537240</v>
+        <v>-175340</v>
       </c>
       <c r="Y50" t="n">
-        <v>1533261</v>
+        <v>-255580</v>
       </c>
       <c r="Z50" t="n">
-        <v>3950956</v>
+        <v>-295975</v>
       </c>
       <c r="AA50" t="n">
-        <v>5529838</v>
+        <v>-456831</v>
       </c>
       <c r="AB50" t="n">
-        <v>5</v>
+        <v>-25</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -6302,110 +6302,110 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>56.2</v>
+        <v>627</v>
       </c>
       <c r="D51" t="n">
-        <v>51.98</v>
+        <v>603.2</v>
       </c>
       <c r="E51" t="n">
-        <v>47.69</v>
+        <v>557.4</v>
       </c>
       <c r="F51" t="n">
-        <v>40.86</v>
+        <v>501.23</v>
       </c>
       <c r="G51" t="n">
-        <v>1153961000</v>
+        <v>40568000</v>
       </c>
       <c r="H51" t="n">
-        <v>1031901630</v>
+        <v>16099800</v>
       </c>
       <c r="I51" t="n">
-        <v>58.8</v>
+        <v>687</v>
       </c>
       <c r="J51" t="n">
-        <v>26.8</v>
+        <v>368</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>85817793</v>
+        <v>-1747347</v>
       </c>
       <c r="M51" t="n">
-        <v>-59168312</v>
+        <v>-2354323</v>
       </c>
       <c r="N51" t="n">
-        <v>-246655070</v>
+        <v>-825225</v>
       </c>
       <c r="O51" t="n">
-        <v>-172216579</v>
+        <v>8573611</v>
       </c>
       <c r="P51" t="n">
-        <v>80703305</v>
+        <v>-105436</v>
       </c>
       <c r="Q51" t="n">
-        <v>-45385303</v>
+        <v>80687</v>
       </c>
       <c r="R51" t="n">
-        <v>-216619387</v>
+        <v>1524563</v>
       </c>
       <c r="S51" t="n">
-        <v>-142650779</v>
+        <v>10346864</v>
       </c>
       <c r="T51" t="n">
-        <v>5100000</v>
+        <v>-856656</v>
       </c>
       <c r="U51" t="n">
-        <v>5217221</v>
+        <v>-839656</v>
       </c>
       <c r="V51" t="n">
-        <v>-3025475</v>
+        <v>-842956</v>
       </c>
       <c r="W51" t="n">
-        <v>-2020364</v>
+        <v>-753556</v>
       </c>
       <c r="X51" t="n">
-        <v>14488</v>
+        <v>-785255</v>
       </c>
       <c r="Y51" t="n">
-        <v>-19000230</v>
+        <v>-1595354</v>
       </c>
       <c r="Z51" t="n">
-        <v>-27010208</v>
+        <v>-1506832</v>
       </c>
       <c r="AA51" t="n">
-        <v>-27545436</v>
+        <v>-1019697</v>
       </c>
       <c r="AB51" t="n">
-        <v>5</v>
+        <v>-35</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -6419,54 +6419,54 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2425</v>
+        <v>41.3</v>
       </c>
       <c r="D52" t="n">
-        <v>2484</v>
+        <v>39.18</v>
       </c>
       <c r="E52" t="n">
-        <v>2488.5</v>
+        <v>36.38</v>
       </c>
       <c r="F52" t="n">
-        <v>2496</v>
+        <v>32.45</v>
       </c>
       <c r="G52" t="n">
-        <v>3595000</v>
+        <v>135198121</v>
       </c>
       <c r="H52" t="n">
-        <v>4472284</v>
+        <v>137196362</v>
       </c>
       <c r="I52" t="n">
-        <v>2695</v>
+        <v>43.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2305</v>
+        <v>26.65</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6474,55 +6474,55 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>324990</v>
+        <v>-2878329</v>
       </c>
       <c r="M52" t="n">
-        <v>-446327</v>
+        <v>-15036146</v>
       </c>
       <c r="N52" t="n">
-        <v>291378</v>
+        <v>-40410680</v>
       </c>
       <c r="O52" t="n">
-        <v>296867</v>
+        <v>65083978</v>
       </c>
       <c r="P52" t="n">
-        <v>356765</v>
+        <v>-2705438</v>
       </c>
       <c r="Q52" t="n">
-        <v>193259</v>
+        <v>-16032670</v>
       </c>
       <c r="R52" t="n">
-        <v>717536</v>
+        <v>-39570049</v>
       </c>
       <c r="S52" t="n">
-        <v>1053276</v>
+        <v>75252925</v>
       </c>
       <c r="T52" t="n">
-        <v>33000</v>
+        <v>12000</v>
       </c>
       <c r="U52" t="n">
-        <v>-482677</v>
+        <v>605000</v>
       </c>
       <c r="V52" t="n">
-        <v>-254072</v>
+        <v>605000</v>
       </c>
       <c r="W52" t="n">
-        <v>-361630</v>
+        <v>-14468000</v>
       </c>
       <c r="X52" t="n">
-        <v>-64775</v>
+        <v>-184891</v>
       </c>
       <c r="Y52" t="n">
-        <v>-156909</v>
+        <v>391524</v>
       </c>
       <c r="Z52" t="n">
-        <v>-172086</v>
+        <v>-1445631</v>
       </c>
       <c r="AA52" t="n">
-        <v>-394779</v>
+        <v>4299053</v>
       </c>
       <c r="AB52" t="n">
-        <v>-25</v>
+        <v>-35</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -6536,54 +6536,54 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>7769.TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>92</v>
+        <v>7175</v>
       </c>
       <c r="D53" t="n">
-        <v>87.34</v>
+        <v>7690</v>
       </c>
       <c r="E53" t="n">
-        <v>82.65000000000001</v>
+        <v>7638</v>
       </c>
       <c r="F53" t="n">
-        <v>73.28</v>
+        <v>7106</v>
       </c>
       <c r="G53" t="n">
-        <v>49559000</v>
+        <v>1247463</v>
       </c>
       <c r="H53" t="n">
-        <v>49070206</v>
+        <v>1246741</v>
       </c>
       <c r="I53" t="n">
-        <v>94.90000000000001</v>
+        <v>8465</v>
       </c>
       <c r="J53" t="n">
-        <v>58.1</v>
+        <v>5435</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6591,55 +6591,55 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-1055982</v>
+        <v>-262781</v>
       </c>
       <c r="M53" t="n">
-        <v>-12178704</v>
+        <v>-533311</v>
       </c>
       <c r="N53" t="n">
-        <v>-7168837</v>
+        <v>-628680</v>
       </c>
       <c r="O53" t="n">
-        <v>2700112</v>
+        <v>-667642</v>
       </c>
       <c r="P53" t="n">
-        <v>-1636146</v>
+        <v>-242972</v>
       </c>
       <c r="Q53" t="n">
-        <v>-11349452</v>
+        <v>-701673</v>
       </c>
       <c r="R53" t="n">
-        <v>-6189868</v>
+        <v>-759682</v>
       </c>
       <c r="S53" t="n">
-        <v>1485814</v>
+        <v>-646804</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>180004</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>137504</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>-17647</v>
       </c>
       <c r="X53" t="n">
-        <v>580164</v>
+        <v>-2809</v>
       </c>
       <c r="Y53" t="n">
-        <v>-829252</v>
+        <v>-11642</v>
       </c>
       <c r="Z53" t="n">
-        <v>-978969</v>
+        <v>-6502</v>
       </c>
       <c r="AA53" t="n">
-        <v>1214298</v>
+        <v>-3191</v>
       </c>
       <c r="AB53" t="n">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -6653,54 +6653,54 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>39.65</v>
+        <v>141.5</v>
       </c>
       <c r="D54" t="n">
-        <v>39.12</v>
+        <v>143.5</v>
       </c>
       <c r="E54" t="n">
-        <v>39.18</v>
+        <v>131.1</v>
       </c>
       <c r="F54" t="n">
-        <v>39.62</v>
+        <v>116.51</v>
       </c>
       <c r="G54" t="n">
-        <v>88000</v>
+        <v>380584577</v>
       </c>
       <c r="H54" t="n">
-        <v>158310</v>
+        <v>346983487</v>
       </c>
       <c r="I54" t="n">
-        <v>42.45</v>
+        <v>155.5</v>
       </c>
       <c r="J54" t="n">
-        <v>38.5</v>
+        <v>87.8</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -6708,55 +6708,55 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>41000</v>
+        <v>-52504191</v>
       </c>
       <c r="M54" t="n">
-        <v>-47024</v>
+        <v>-126267680</v>
       </c>
       <c r="N54" t="n">
-        <v>-69572</v>
+        <v>-124346753</v>
       </c>
       <c r="O54" t="n">
-        <v>-172104</v>
+        <v>-111315630</v>
       </c>
       <c r="P54" t="n">
-        <v>42000</v>
+        <v>63633529</v>
       </c>
       <c r="Q54" t="n">
-        <v>-43024</v>
+        <v>55842157</v>
       </c>
       <c r="R54" t="n">
-        <v>-66001</v>
+        <v>77372124</v>
       </c>
       <c r="S54" t="n">
-        <v>-168001</v>
+        <v>156079152</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>-115062289</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>-181777817</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>-200788646</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>-271465917</v>
       </c>
       <c r="X54" t="n">
-        <v>-1000</v>
+        <v>-1075431</v>
       </c>
       <c r="Y54" t="n">
-        <v>-4000</v>
+        <v>-332020</v>
       </c>
       <c r="Z54" t="n">
-        <v>-3571</v>
+        <v>-930231</v>
       </c>
       <c r="AA54" t="n">
-        <v>-4103</v>
+        <v>4071135</v>
       </c>
       <c r="AB54" t="n">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -6770,54 +6770,54 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>5日法人小幅賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>530</v>
+        <v>270.5</v>
       </c>
       <c r="D55" t="n">
-        <v>541.4</v>
+        <v>275.6</v>
       </c>
       <c r="E55" t="n">
-        <v>516.7</v>
+        <v>275.2</v>
       </c>
       <c r="F55" t="n">
-        <v>507.02</v>
+        <v>262</v>
       </c>
       <c r="G55" t="n">
-        <v>23733000</v>
+        <v>46492198</v>
       </c>
       <c r="H55" t="n">
-        <v>36085800</v>
+        <v>79673908</v>
       </c>
       <c r="I55" t="n">
-        <v>588</v>
+        <v>305.5</v>
       </c>
       <c r="J55" t="n">
-        <v>436</v>
+        <v>233.5</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>600244</v>
+        <v>-14211549</v>
       </c>
       <c r="M55" t="n">
-        <v>-5119788</v>
+        <v>570888</v>
       </c>
       <c r="N55" t="n">
-        <v>-331680</v>
+        <v>-10077786</v>
       </c>
       <c r="O55" t="n">
-        <v>4050513</v>
+        <v>9812717</v>
       </c>
       <c r="P55" t="n">
-        <v>516617</v>
+        <v>-11984655</v>
       </c>
       <c r="Q55" t="n">
-        <v>-3090648</v>
+        <v>2595853</v>
       </c>
       <c r="R55" t="n">
-        <v>357439</v>
+        <v>-3373842</v>
       </c>
       <c r="S55" t="n">
-        <v>-1670157</v>
+        <v>18039173</v>
       </c>
       <c r="T55" t="n">
-        <v>-26441</v>
+        <v>-989000</v>
       </c>
       <c r="U55" t="n">
-        <v>-1574325</v>
+        <v>-1351000</v>
       </c>
       <c r="V55" t="n">
-        <v>-1040767</v>
+        <v>-5252000</v>
       </c>
       <c r="W55" t="n">
-        <v>3340500</v>
+        <v>-7936000</v>
       </c>
       <c r="X55" t="n">
-        <v>110068</v>
+        <v>-1237894</v>
       </c>
       <c r="Y55" t="n">
-        <v>-454815</v>
+        <v>-673965</v>
       </c>
       <c r="Z55" t="n">
-        <v>351648</v>
+        <v>-1451944</v>
       </c>
       <c r="AA55" t="n">
-        <v>2380170</v>
+        <v>-290456</v>
       </c>
       <c r="AB55" t="n">
-        <v>-40</v>
+        <v>-45</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -6892,49 +6892,49 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7769.TW</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7175</v>
+        <v>347</v>
       </c>
       <c r="D56" t="n">
-        <v>7690</v>
+        <v>358</v>
       </c>
       <c r="E56" t="n">
-        <v>7638</v>
+        <v>321.8</v>
       </c>
       <c r="F56" t="n">
-        <v>7106</v>
+        <v>277.15</v>
       </c>
       <c r="G56" t="n">
-        <v>1090000</v>
+        <v>24564465</v>
       </c>
       <c r="H56" t="n">
-        <v>1215249</v>
+        <v>43272703</v>
       </c>
       <c r="I56" t="n">
-        <v>8465</v>
+        <v>387</v>
       </c>
       <c r="J56" t="n">
-        <v>5435</v>
+        <v>217.5</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -6942,55 +6942,55 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-372998</v>
+        <v>-4510875</v>
       </c>
       <c r="M56" t="n">
-        <v>-43384</v>
+        <v>-7464913</v>
       </c>
       <c r="N56" t="n">
-        <v>-157277</v>
+        <v>-5183746</v>
       </c>
       <c r="O56" t="n">
-        <v>-130635</v>
+        <v>-546880</v>
       </c>
       <c r="P56" t="n">
-        <v>-409313</v>
+        <v>2897166</v>
       </c>
       <c r="Q56" t="n">
-        <v>-624960</v>
+        <v>578942</v>
       </c>
       <c r="R56" t="n">
-        <v>-695082</v>
+        <v>2436030</v>
       </c>
       <c r="S56" t="n">
-        <v>-519645</v>
+        <v>8302142</v>
       </c>
       <c r="T56" t="n">
-        <v>37000</v>
+        <v>-6992797</v>
       </c>
       <c r="U56" t="n">
-        <v>590504</v>
+        <v>-7663188</v>
       </c>
       <c r="V56" t="n">
-        <v>541853</v>
+        <v>-6858782</v>
       </c>
       <c r="W56" t="n">
-        <v>401853</v>
+        <v>-9716782</v>
       </c>
       <c r="X56" t="n">
-        <v>-685</v>
+        <v>-415244</v>
       </c>
       <c r="Y56" t="n">
-        <v>-8928</v>
+        <v>-380667</v>
       </c>
       <c r="Z56" t="n">
-        <v>-4048</v>
+        <v>-760994</v>
       </c>
       <c r="AA56" t="n">
-        <v>-12843</v>
+        <v>867760</v>
       </c>
       <c r="AB56" t="n">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -7009,49 +7009,49 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>141.5</v>
+        <v>520</v>
       </c>
       <c r="D57" t="n">
-        <v>143.5</v>
+        <v>453.2</v>
       </c>
       <c r="E57" t="n">
-        <v>131.1</v>
+        <v>392.7</v>
       </c>
       <c r="F57" t="n">
-        <v>116.51</v>
+        <v>326.85</v>
       </c>
       <c r="G57" t="n">
-        <v>375458000</v>
+        <v>13270682</v>
       </c>
       <c r="H57" t="n">
-        <v>345958172</v>
+        <v>43892046</v>
       </c>
       <c r="I57" t="n">
-        <v>155.5</v>
+        <v>555</v>
       </c>
       <c r="J57" t="n">
-        <v>87.8</v>
+        <v>219</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7059,55 +7059,55 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-17686627</v>
+        <v>-4100725</v>
       </c>
       <c r="M57" t="n">
-        <v>-105850437</v>
+        <v>-2964859</v>
       </c>
       <c r="N57" t="n">
-        <v>-51398250</v>
+        <v>-8187858</v>
       </c>
       <c r="O57" t="n">
-        <v>-72620473</v>
+        <v>4595648</v>
       </c>
       <c r="P57" t="n">
-        <v>20426659</v>
+        <v>-804207</v>
       </c>
       <c r="Q57" t="n">
-        <v>-7732185</v>
+        <v>2395135</v>
       </c>
       <c r="R57" t="n">
-        <v>85668280</v>
+        <v>-315037</v>
       </c>
       <c r="S57" t="n">
-        <v>81129521</v>
+        <v>-2379773</v>
       </c>
       <c r="T57" t="n">
-        <v>-38025561</v>
+        <v>-2948000</v>
       </c>
       <c r="U57" t="n">
-        <v>-101199533</v>
+        <v>-5115465</v>
       </c>
       <c r="V57" t="n">
-        <v>-139902383</v>
+        <v>-7453465</v>
       </c>
       <c r="W57" t="n">
-        <v>-158631125</v>
+        <v>7087098</v>
       </c>
       <c r="X57" t="n">
-        <v>-87725</v>
+        <v>-348518</v>
       </c>
       <c r="Y57" t="n">
-        <v>3081281</v>
+        <v>-244529</v>
       </c>
       <c r="Z57" t="n">
-        <v>2835853</v>
+        <v>-419356</v>
       </c>
       <c r="AA57" t="n">
-        <v>4881131</v>
+        <v>-111677</v>
       </c>
       <c r="AB57" t="n">
-        <v>-40</v>
+        <v>-55</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -7121,54 +7121,54 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>520</v>
+        <v>18.95</v>
       </c>
       <c r="D58" t="n">
-        <v>520.2</v>
+        <v>19.02</v>
       </c>
       <c r="E58" t="n">
-        <v>509.45</v>
+        <v>18.9</v>
       </c>
       <c r="F58" t="n">
-        <v>461.52</v>
+        <v>18.69</v>
       </c>
       <c r="G58" t="n">
-        <v>11337000</v>
+        <v>70796205</v>
       </c>
       <c r="H58" t="n">
-        <v>19866157</v>
+        <v>79887394</v>
       </c>
       <c r="I58" t="n">
-        <v>568</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>372</v>
+        <v>18.05</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7176,55 +7176,55 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>278726</v>
+        <v>-27285744</v>
       </c>
       <c r="M58" t="n">
-        <v>-1703916</v>
+        <v>-31747337</v>
       </c>
       <c r="N58" t="n">
-        <v>-3261558</v>
+        <v>-59952673</v>
       </c>
       <c r="O58" t="n">
-        <v>10240061</v>
+        <v>-87305626</v>
       </c>
       <c r="P58" t="n">
-        <v>1967821</v>
+        <v>-27915973</v>
       </c>
       <c r="Q58" t="n">
-        <v>3439317</v>
+        <v>-33318321</v>
       </c>
       <c r="R58" t="n">
-        <v>3959418</v>
+        <v>-59774330</v>
       </c>
       <c r="S58" t="n">
-        <v>-441163</v>
+        <v>-92143798</v>
       </c>
       <c r="T58" t="n">
-        <v>-1331000</v>
+        <v>934000</v>
       </c>
       <c r="U58" t="n">
-        <v>-4785592</v>
+        <v>966525</v>
       </c>
       <c r="V58" t="n">
-        <v>-6851592</v>
+        <v>986525</v>
       </c>
       <c r="W58" t="n">
-        <v>10969976</v>
+        <v>1813525</v>
       </c>
       <c r="X58" t="n">
-        <v>-358095</v>
+        <v>-303771</v>
       </c>
       <c r="Y58" t="n">
-        <v>-357641</v>
+        <v>604459</v>
       </c>
       <c r="Z58" t="n">
-        <v>-369384</v>
+        <v>-1164868</v>
       </c>
       <c r="AA58" t="n">
-        <v>-288752</v>
+        <v>3024647</v>
       </c>
       <c r="AB58" t="n">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -7238,54 +7238,54 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>41.3</v>
+        <v>71</v>
       </c>
       <c r="D59" t="n">
-        <v>39.18</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>36.38</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>32.45</v>
+        <v>69.42</v>
       </c>
       <c r="G59" t="n">
-        <v>134456000</v>
+        <v>149651763</v>
       </c>
       <c r="H59" t="n">
-        <v>137047937</v>
+        <v>143109988</v>
       </c>
       <c r="I59" t="n">
-        <v>43.5</v>
+        <v>81.2</v>
       </c>
       <c r="J59" t="n">
-        <v>26.65</v>
+        <v>61.8</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -7293,55 +7293,55 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-5247740</v>
+        <v>-50054063</v>
       </c>
       <c r="M59" t="n">
-        <v>-18740272</v>
+        <v>-21465315</v>
       </c>
       <c r="N59" t="n">
-        <v>-15756947</v>
+        <v>-19282198</v>
       </c>
       <c r="O59" t="n">
-        <v>61167815</v>
+        <v>63176945</v>
       </c>
       <c r="P59" t="n">
-        <v>-6375791</v>
+        <v>-47089851</v>
       </c>
       <c r="Q59" t="n">
-        <v>-20229217</v>
+        <v>-19564811</v>
       </c>
       <c r="R59" t="n">
-        <v>-13311206</v>
+        <v>-18995837</v>
       </c>
       <c r="S59" t="n">
-        <v>73546299</v>
+        <v>57547447</v>
       </c>
       <c r="T59" t="n">
-        <v>593000</v>
+        <v>850000</v>
       </c>
       <c r="U59" t="n">
-        <v>593000</v>
+        <v>1267000</v>
       </c>
       <c r="V59" t="n">
-        <v>-2179000</v>
+        <v>2237000</v>
       </c>
       <c r="W59" t="n">
-        <v>-17161000</v>
+        <v>3042000</v>
       </c>
       <c r="X59" t="n">
-        <v>535051</v>
+        <v>-3814212</v>
       </c>
       <c r="Y59" t="n">
-        <v>895945</v>
+        <v>-3167504</v>
       </c>
       <c r="Z59" t="n">
-        <v>-266741</v>
+        <v>-2523361</v>
       </c>
       <c r="AA59" t="n">
-        <v>4782516</v>
+        <v>2587498</v>
       </c>
       <c r="AB59" t="n">
-        <v>-55</v>
+        <v>-65</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -7355,54 +7355,54 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2002.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>18.95</v>
+        <v>590</v>
       </c>
       <c r="D60" t="n">
-        <v>19.02</v>
+        <v>614.2</v>
       </c>
       <c r="E60" t="n">
-        <v>18.9</v>
+        <v>584.6</v>
       </c>
       <c r="F60" t="n">
-        <v>18.69</v>
+        <v>557.15</v>
       </c>
       <c r="G60" t="n">
-        <v>70047000</v>
+        <v>27769330</v>
       </c>
       <c r="H60" t="n">
-        <v>79737553</v>
+        <v>32530042</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>669</v>
       </c>
       <c r="J60" t="n">
-        <v>18.05</v>
+        <v>465</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -7410,55 +7410,55 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-6821957</v>
+        <v>-3429245</v>
       </c>
       <c r="M60" t="n">
-        <v>-19778248</v>
+        <v>-19537100</v>
       </c>
       <c r="N60" t="n">
-        <v>-73161846</v>
+        <v>-19331218</v>
       </c>
       <c r="O60" t="n">
-        <v>-80580628</v>
+        <v>-17152121</v>
       </c>
       <c r="P60" t="n">
-        <v>-7595418</v>
+        <v>1316315</v>
       </c>
       <c r="Q60" t="n">
-        <v>-19948956</v>
+        <v>-6501112</v>
       </c>
       <c r="R60" t="n">
-        <v>-71816977</v>
+        <v>-5667308</v>
       </c>
       <c r="S60" t="n">
-        <v>-84800855</v>
+        <v>-5892266</v>
       </c>
       <c r="T60" t="n">
-        <v>5000</v>
+        <v>-4724678</v>
       </c>
       <c r="U60" t="n">
-        <v>-8475</v>
+        <v>-13157725</v>
       </c>
       <c r="V60" t="n">
-        <v>21525</v>
+        <v>-13831677</v>
       </c>
       <c r="W60" t="n">
-        <v>1075525</v>
+        <v>-10829800</v>
       </c>
       <c r="X60" t="n">
-        <v>768461</v>
+        <v>-20882</v>
       </c>
       <c r="Y60" t="n">
-        <v>179183</v>
+        <v>121737</v>
       </c>
       <c r="Z60" t="n">
-        <v>-1366394</v>
+        <v>167767</v>
       </c>
       <c r="AA60" t="n">
-        <v>3144702</v>
+        <v>-430055</v>
       </c>
       <c r="AB60" t="n">
-        <v>-60</v>
+        <v>-70</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -7472,54 +7472,54 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>590</v>
+        <v>54.5</v>
       </c>
       <c r="D61" t="n">
-        <v>614.2</v>
+        <v>56.34</v>
       </c>
       <c r="E61" t="n">
-        <v>584.6</v>
+        <v>55.12</v>
       </c>
       <c r="F61" t="n">
-        <v>557.15</v>
+        <v>52.49</v>
       </c>
       <c r="G61" t="n">
-        <v>25304000</v>
+        <v>8447087</v>
       </c>
       <c r="H61" t="n">
-        <v>32036976</v>
+        <v>10794782</v>
       </c>
       <c r="I61" t="n">
-        <v>669</v>
+        <v>61.4</v>
       </c>
       <c r="J61" t="n">
-        <v>465</v>
+        <v>45.45</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -7527,55 +7527,55 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-2269811</v>
+        <v>-356474</v>
       </c>
       <c r="M61" t="n">
-        <v>-18147118</v>
+        <v>-3263068</v>
       </c>
       <c r="N61" t="n">
-        <v>-19887300</v>
+        <v>-2097065</v>
       </c>
       <c r="O61" t="n">
-        <v>-19512205</v>
+        <v>11705605</v>
       </c>
       <c r="P61" t="n">
-        <v>2284150</v>
+        <v>-219995</v>
       </c>
       <c r="Q61" t="n">
-        <v>-10178887</v>
+        <v>-3403433</v>
       </c>
       <c r="R61" t="n">
-        <v>-10813423</v>
+        <v>-2286433</v>
       </c>
       <c r="S61" t="n">
-        <v>-13545404</v>
+        <v>10708865</v>
       </c>
       <c r="T61" t="n">
-        <v>-4656953</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>-8031843</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>-8748601</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>-5686221</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>102992</v>
+        <v>-136479</v>
       </c>
       <c r="Y61" t="n">
-        <v>63612</v>
+        <v>140365</v>
       </c>
       <c r="Z61" t="n">
-        <v>-325276</v>
+        <v>189368</v>
       </c>
       <c r="AA61" t="n">
-        <v>-280580</v>
+        <v>996740</v>
       </c>
       <c r="AB61" t="n">
-        <v>-70</v>
+        <v>-75</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -7594,49 +7594,49 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1060</v>
+        <v>975</v>
       </c>
       <c r="D62" t="n">
-        <v>1092</v>
+        <v>1037</v>
       </c>
       <c r="E62" t="n">
-        <v>1071.2</v>
+        <v>995.8</v>
       </c>
       <c r="F62" t="n">
-        <v>1058.6</v>
+        <v>924.7</v>
       </c>
       <c r="G62" t="n">
-        <v>2924000</v>
+        <v>29360754</v>
       </c>
       <c r="H62" t="n">
-        <v>4078000</v>
+        <v>24425569</v>
       </c>
       <c r="I62" t="n">
-        <v>1300</v>
+        <v>1130</v>
       </c>
       <c r="J62" t="n">
-        <v>865</v>
+        <v>776</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7644,55 +7644,55 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-420978</v>
+        <v>-7296341</v>
       </c>
       <c r="M62" t="n">
-        <v>-1582664</v>
+        <v>-9466247</v>
       </c>
       <c r="N62" t="n">
-        <v>-2974189</v>
+        <v>-8759639</v>
       </c>
       <c r="O62" t="n">
-        <v>-4253655</v>
+        <v>17140676</v>
       </c>
       <c r="P62" t="n">
-        <v>60766</v>
+        <v>-2748858</v>
       </c>
       <c r="Q62" t="n">
-        <v>-94694</v>
+        <v>-3637861</v>
       </c>
       <c r="R62" t="n">
-        <v>-358980</v>
+        <v>-3440200</v>
       </c>
       <c r="S62" t="n">
-        <v>-2479356</v>
+        <v>17854581</v>
       </c>
       <c r="T62" t="n">
-        <v>-478000</v>
+        <v>-4189000</v>
       </c>
       <c r="U62" t="n">
-        <v>-1475050</v>
+        <v>-5332372</v>
       </c>
       <c r="V62" t="n">
-        <v>-2527050</v>
+        <v>-4282372</v>
       </c>
       <c r="W62" t="n">
-        <v>-1737050</v>
+        <v>-173429</v>
       </c>
       <c r="X62" t="n">
-        <v>-3744</v>
+        <v>-358483</v>
       </c>
       <c r="Y62" t="n">
-        <v>-12920</v>
+        <v>-496014</v>
       </c>
       <c r="Z62" t="n">
-        <v>-88159</v>
+        <v>-1037067</v>
       </c>
       <c r="AA62" t="n">
-        <v>-37249</v>
+        <v>-540476</v>
       </c>
       <c r="AB62" t="n">
-        <v>-70</v>
+        <v>-85</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -7706,54 +7706,54 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>270.5</v>
+        <v>988</v>
       </c>
       <c r="D63" t="n">
-        <v>275.6</v>
+        <v>1045.6</v>
       </c>
       <c r="E63" t="n">
-        <v>275.2</v>
+        <v>1080</v>
       </c>
       <c r="F63" t="n">
-        <v>262</v>
+        <v>1047</v>
       </c>
       <c r="G63" t="n">
-        <v>44486000</v>
+        <v>4829000</v>
       </c>
       <c r="H63" t="n">
-        <v>79272668</v>
+        <v>4160800</v>
       </c>
       <c r="I63" t="n">
-        <v>305.5</v>
+        <v>1255</v>
       </c>
       <c r="J63" t="n">
-        <v>233.5</v>
+        <v>865</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7761,55 +7761,55 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-13602165</v>
+        <v>-1437817</v>
       </c>
       <c r="M63" t="n">
-        <v>-24542154</v>
+        <v>-2617249</v>
       </c>
       <c r="N63" t="n">
-        <v>-52766993</v>
+        <v>-4490876</v>
       </c>
       <c r="O63" t="n">
-        <v>-6377479</v>
+        <v>-5667128</v>
       </c>
       <c r="P63" t="n">
-        <v>-13708813</v>
+        <v>-1009219</v>
       </c>
       <c r="Q63" t="n">
-        <v>-19162159</v>
+        <v>-1111735</v>
       </c>
       <c r="R63" t="n">
-        <v>-38360704</v>
+        <v>-1294951</v>
       </c>
       <c r="S63" t="n">
-        <v>3177875</v>
+        <v>-3512115</v>
       </c>
       <c r="T63" t="n">
-        <v>25000</v>
+        <v>-426000</v>
       </c>
       <c r="U63" t="n">
-        <v>-3363000</v>
+        <v>-1497000</v>
       </c>
       <c r="V63" t="n">
-        <v>-10645000</v>
+        <v>-3163050</v>
       </c>
       <c r="W63" t="n">
-        <v>-6615000</v>
+        <v>-2117050</v>
       </c>
       <c r="X63" t="n">
-        <v>81648</v>
+        <v>-2598</v>
       </c>
       <c r="Y63" t="n">
-        <v>-2016995</v>
+        <v>-8514</v>
       </c>
       <c r="Z63" t="n">
-        <v>-3761289</v>
+        <v>-32875</v>
       </c>
       <c r="AA63" t="n">
-        <v>-2940354</v>
+        <v>-37963</v>
       </c>
       <c r="AB63" t="n">
-        <v>-70</v>
+        <v>-85</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7833,44 +7833,44 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>54.5</v>
+        <v>519</v>
       </c>
       <c r="D64" t="n">
-        <v>56.34</v>
+        <v>532.8</v>
       </c>
       <c r="E64" t="n">
-        <v>55.12</v>
+        <v>522.95</v>
       </c>
       <c r="F64" t="n">
-        <v>52.49</v>
+        <v>505.23</v>
       </c>
       <c r="G64" t="n">
-        <v>8316000</v>
+        <v>33279000</v>
       </c>
       <c r="H64" t="n">
-        <v>10768564</v>
+        <v>35992400</v>
       </c>
       <c r="I64" t="n">
-        <v>61.4</v>
+        <v>588</v>
       </c>
       <c r="J64" t="n">
-        <v>45.45</v>
+        <v>436</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -7878,55 +7878,55 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-3130536</v>
+        <v>-4465301</v>
       </c>
       <c r="M64" t="n">
-        <v>-3121889</v>
+        <v>-8311835</v>
       </c>
       <c r="N64" t="n">
-        <v>-2012275</v>
+        <v>-9041043</v>
       </c>
       <c r="O64" t="n">
-        <v>12234349</v>
+        <v>368824</v>
       </c>
       <c r="P64" t="n">
-        <v>-3219650</v>
+        <v>-2854261</v>
       </c>
       <c r="Q64" t="n">
-        <v>-3438638</v>
+        <v>-5155762</v>
       </c>
       <c r="R64" t="n">
-        <v>-2331789</v>
+        <v>-5764210</v>
       </c>
       <c r="S64" t="n">
-        <v>11018660</v>
+        <v>-2776980</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>-851722</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>-2368884</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>-2062488</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1626511</v>
       </c>
       <c r="X64" t="n">
-        <v>89114</v>
+        <v>-759318</v>
       </c>
       <c r="Y64" t="n">
-        <v>316749</v>
+        <v>-787189</v>
       </c>
       <c r="Z64" t="n">
-        <v>319514</v>
+        <v>-1214345</v>
       </c>
       <c r="AA64" t="n">
-        <v>1215689</v>
+        <v>1519293</v>
       </c>
       <c r="AB64" t="n">
-        <v>-75</v>
+        <v>-95</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -7945,49 +7945,49 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>32.45</v>
+        <v>422</v>
       </c>
       <c r="D65" t="n">
-        <v>32.65</v>
+        <v>440.1</v>
       </c>
       <c r="E65" t="n">
-        <v>33.89</v>
+        <v>418.4</v>
       </c>
       <c r="F65" t="n">
-        <v>35.56</v>
+        <v>399.02</v>
       </c>
       <c r="G65" t="n">
-        <v>8286000</v>
+        <v>9255000</v>
       </c>
       <c r="H65" t="n">
-        <v>9476237</v>
+        <v>12456400</v>
       </c>
       <c r="I65" t="n">
-        <v>44.05</v>
+        <v>492.5</v>
       </c>
       <c r="J65" t="n">
-        <v>31.1</v>
+        <v>343</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -7995,55 +7995,55 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>401986</v>
+        <v>-2288817</v>
       </c>
       <c r="M65" t="n">
-        <v>-968923</v>
+        <v>-5731678</v>
       </c>
       <c r="N65" t="n">
-        <v>-1382569</v>
+        <v>-4220478</v>
       </c>
       <c r="O65" t="n">
-        <v>-9625536</v>
+        <v>6678578</v>
       </c>
       <c r="P65" t="n">
-        <v>403001</v>
+        <v>-1412036</v>
       </c>
       <c r="Q65" t="n">
-        <v>-710013</v>
+        <v>-4790611</v>
       </c>
       <c r="R65" t="n">
-        <v>-1258658</v>
+        <v>-2616162</v>
       </c>
       <c r="S65" t="n">
-        <v>-9492626</v>
+        <v>11618354</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>-883000</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>-970000</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>-1288000</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>-5782000</v>
       </c>
       <c r="X65" t="n">
-        <v>-1015</v>
+        <v>6219</v>
       </c>
       <c r="Y65" t="n">
-        <v>-258910</v>
+        <v>28933</v>
       </c>
       <c r="Z65" t="n">
-        <v>-123911</v>
+        <v>-316316</v>
       </c>
       <c r="AA65" t="n">
-        <v>-132910</v>
+        <v>842224</v>
       </c>
       <c r="AB65" t="n">
-        <v>-85</v>
+        <v>-95</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
@@ -8057,54 +8057,54 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>227.5</v>
+        <v>58.9</v>
       </c>
       <c r="D66" t="n">
-        <v>249.1</v>
+        <v>59.88</v>
       </c>
       <c r="E66" t="n">
-        <v>252.75</v>
+        <v>57.31</v>
       </c>
       <c r="F66" t="n">
-        <v>245.43</v>
+        <v>57.69</v>
       </c>
       <c r="G66" t="n">
-        <v>2817000</v>
+        <v>15484189</v>
       </c>
       <c r="H66" t="n">
-        <v>4227000</v>
+        <v>25737150</v>
       </c>
       <c r="I66" t="n">
-        <v>312.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>220</v>
+        <v>50.2</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8112,55 +8112,55 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-27233</v>
+        <v>-2441375</v>
       </c>
       <c r="M66" t="n">
-        <v>-1281879</v>
+        <v>-2142221</v>
       </c>
       <c r="N66" t="n">
-        <v>-2871580</v>
+        <v>-2092627</v>
       </c>
       <c r="O66" t="n">
-        <v>-2105098</v>
+        <v>224630</v>
       </c>
       <c r="P66" t="n">
-        <v>2802</v>
+        <v>-1939521</v>
       </c>
       <c r="Q66" t="n">
-        <v>-1219573</v>
+        <v>-1846793</v>
       </c>
       <c r="R66" t="n">
-        <v>-2740760</v>
+        <v>-1922226</v>
       </c>
       <c r="S66" t="n">
-        <v>-1830218</v>
+        <v>-133425</v>
       </c>
       <c r="T66" t="n">
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>164000</v>
       </c>
       <c r="X66" t="n">
-        <v>-30035</v>
+        <v>-501854</v>
       </c>
       <c r="Y66" t="n">
-        <v>-62306</v>
+        <v>-307428</v>
       </c>
       <c r="Z66" t="n">
-        <v>-130820</v>
+        <v>-182401</v>
       </c>
       <c r="AA66" t="n">
-        <v>-274880</v>
+        <v>194055</v>
       </c>
       <c r="AB66" t="n">
-        <v>-85</v>
+        <v>-100</v>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
@@ -8174,54 +8174,54 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>69.90000000000001</v>
+        <v>374</v>
       </c>
       <c r="D67" t="n">
-        <v>72.52</v>
+        <v>378.5</v>
       </c>
       <c r="E67" t="n">
-        <v>72.75</v>
+        <v>379.7</v>
       </c>
       <c r="F67" t="n">
-        <v>70.87</v>
+        <v>385.3</v>
       </c>
       <c r="G67" t="n">
-        <v>14989000</v>
+        <v>1987000</v>
       </c>
       <c r="H67" t="n">
-        <v>25494701</v>
+        <v>2318600</v>
       </c>
       <c r="I67" t="n">
-        <v>78.59999999999999</v>
+        <v>439</v>
       </c>
       <c r="J67" t="n">
-        <v>64.7</v>
+        <v>353.5</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8229,55 +8229,55 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-3353884</v>
+        <v>-201127</v>
       </c>
       <c r="M67" t="n">
-        <v>-1927633</v>
+        <v>-88446</v>
       </c>
       <c r="N67" t="n">
-        <v>-5620421</v>
+        <v>-1314373</v>
       </c>
       <c r="O67" t="n">
-        <v>-5122068</v>
+        <v>-708266</v>
       </c>
       <c r="P67" t="n">
-        <v>-3281171</v>
+        <v>-233420</v>
       </c>
       <c r="Q67" t="n">
-        <v>-1786681</v>
+        <v>-150593</v>
       </c>
       <c r="R67" t="n">
-        <v>-5657186</v>
+        <v>-1239050</v>
       </c>
       <c r="S67" t="n">
-        <v>-7066444</v>
+        <v>-693282</v>
       </c>
       <c r="T67" t="n">
-        <v>-3000</v>
+        <v>50000</v>
       </c>
       <c r="U67" t="n">
-        <v>-3000</v>
+        <v>28000</v>
       </c>
       <c r="V67" t="n">
-        <v>-3000</v>
+        <v>12000</v>
       </c>
       <c r="W67" t="n">
-        <v>-14000</v>
+        <v>57000</v>
       </c>
       <c r="X67" t="n">
-        <v>-69713</v>
+        <v>-17707</v>
       </c>
       <c r="Y67" t="n">
-        <v>-137952</v>
+        <v>34147</v>
       </c>
       <c r="Z67" t="n">
-        <v>39765</v>
+        <v>-87323</v>
       </c>
       <c r="AA67" t="n">
-        <v>1958376</v>
+        <v>-71984</v>
       </c>
       <c r="AB67" t="n">
-        <v>-95</v>
+        <v>-100</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
@@ -8291,54 +8291,54 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>380</v>
+        <v>32.45</v>
       </c>
       <c r="D68" t="n">
-        <v>381.9</v>
+        <v>32.65</v>
       </c>
       <c r="E68" t="n">
-        <v>380.2</v>
+        <v>33.89</v>
       </c>
       <c r="F68" t="n">
-        <v>386.75</v>
+        <v>35.56</v>
       </c>
       <c r="G68" t="n">
-        <v>1813000</v>
+        <v>8378567</v>
       </c>
       <c r="H68" t="n">
-        <v>2419400</v>
+        <v>9494751</v>
       </c>
       <c r="I68" t="n">
-        <v>439</v>
+        <v>44.05</v>
       </c>
       <c r="J68" t="n">
-        <v>353.5</v>
+        <v>31.1</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -8346,55 +8346,55 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-305157</v>
+        <v>-591639</v>
       </c>
       <c r="M68" t="n">
-        <v>-406036</v>
+        <v>-1020528</v>
       </c>
       <c r="N68" t="n">
-        <v>-993095</v>
+        <v>-1438298</v>
       </c>
       <c r="O68" t="n">
-        <v>-648038</v>
+        <v>-8393054</v>
       </c>
       <c r="P68" t="n">
-        <v>-320812</v>
+        <v>-594105</v>
       </c>
       <c r="Q68" t="n">
-        <v>-337057</v>
+        <v>-865083</v>
       </c>
       <c r="R68" t="n">
-        <v>-882971</v>
+        <v>-1284851</v>
       </c>
       <c r="S68" t="n">
-        <v>-544528</v>
+        <v>-8370609</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>-22000</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>-38000</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>15655</v>
+        <v>2466</v>
       </c>
       <c r="Y68" t="n">
-        <v>-46979</v>
+        <v>-155445</v>
       </c>
       <c r="Z68" t="n">
-        <v>-72124</v>
+        <v>-153447</v>
       </c>
       <c r="AA68" t="n">
-        <v>-90510</v>
+        <v>-22445</v>
       </c>
       <c r="AB68" t="n">
-        <v>-95</v>
+        <v>-110</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
@@ -8408,17 +8408,17 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -8434,22 +8434,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2685</v>
+        <v>2575</v>
       </c>
       <c r="D69" t="n">
-        <v>2799</v>
+        <v>2682</v>
       </c>
       <c r="E69" t="n">
-        <v>2725.5</v>
+        <v>2734</v>
       </c>
       <c r="F69" t="n">
-        <v>2749.25</v>
+        <v>2737.25</v>
       </c>
       <c r="G69" t="n">
-        <v>1639000</v>
+        <v>2674000</v>
       </c>
       <c r="H69" t="n">
-        <v>2676600</v>
+        <v>2585400</v>
       </c>
       <c r="I69" t="n">
         <v>3215</v>
@@ -8463,55 +8463,55 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-152795</v>
+        <v>-522690</v>
       </c>
       <c r="M69" t="n">
-        <v>-1422809</v>
+        <v>-1204996</v>
       </c>
       <c r="N69" t="n">
-        <v>-1235852</v>
+        <v>-2194967</v>
       </c>
       <c r="O69" t="n">
-        <v>-582553</v>
+        <v>-1058221</v>
       </c>
       <c r="P69" t="n">
-        <v>10864</v>
+        <v>-291999</v>
       </c>
       <c r="Q69" t="n">
-        <v>-835828</v>
+        <v>-560965</v>
       </c>
       <c r="R69" t="n">
-        <v>-893214</v>
+        <v>-1435056</v>
       </c>
       <c r="S69" t="n">
-        <v>-703145</v>
+        <v>-1190083</v>
       </c>
       <c r="T69" t="n">
-        <v>-161400</v>
+        <v>-192100</v>
       </c>
       <c r="U69" t="n">
-        <v>-531500</v>
+        <v>-587500</v>
       </c>
       <c r="V69" t="n">
-        <v>-278822</v>
+        <v>-656400</v>
       </c>
       <c r="W69" t="n">
-        <v>125063</v>
+        <v>133436</v>
       </c>
       <c r="X69" t="n">
-        <v>-2259</v>
+        <v>-38591</v>
       </c>
       <c r="Y69" t="n">
-        <v>-55481</v>
+        <v>-56531</v>
       </c>
       <c r="Z69" t="n">
-        <v>-63816</v>
+        <v>-103511</v>
       </c>
       <c r="AA69" t="n">
-        <v>-4471</v>
+        <v>-1574</v>
       </c>
       <c r="AB69" t="n">
-        <v>-95</v>
+        <v>-145</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、死亡交叉、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、死亡交叉、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -586,37 +586,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>191</v>
+        <v>1280</v>
       </c>
       <c r="D2" t="n">
-        <v>162.6</v>
+        <v>1132</v>
       </c>
       <c r="E2" t="n">
-        <v>152.5</v>
+        <v>1075.5</v>
       </c>
       <c r="F2" t="n">
-        <v>146.32</v>
+        <v>1049.1</v>
       </c>
       <c r="G2" t="n">
-        <v>282187864</v>
+        <v>9226000</v>
       </c>
       <c r="H2" t="n">
-        <v>114050684</v>
+        <v>5738800</v>
       </c>
       <c r="I2" t="n">
-        <v>191</v>
+        <v>1280</v>
       </c>
       <c r="J2" t="n">
-        <v>132</v>
+        <v>936</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -624,55 +624,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>110166233</v>
+        <v>2687525</v>
       </c>
       <c r="M2" t="n">
-        <v>155632663</v>
+        <v>6136047</v>
       </c>
       <c r="N2" t="n">
-        <v>159699038</v>
+        <v>6868199</v>
       </c>
       <c r="O2" t="n">
-        <v>227335419</v>
+        <v>5082453</v>
       </c>
       <c r="P2" t="n">
-        <v>91902682</v>
+        <v>2612382</v>
       </c>
       <c r="Q2" t="n">
-        <v>133435632</v>
+        <v>5905922</v>
       </c>
       <c r="R2" t="n">
-        <v>135886232</v>
+        <v>6512695</v>
       </c>
       <c r="S2" t="n">
-        <v>199915300</v>
+        <v>4575967</v>
       </c>
       <c r="T2" t="n">
-        <v>17001000</v>
+        <v>1000</v>
       </c>
       <c r="U2" t="n">
-        <v>18929000</v>
+        <v>1900</v>
       </c>
       <c r="V2" t="n">
-        <v>20526000</v>
+        <v>11900</v>
       </c>
       <c r="W2" t="n">
-        <v>21148246</v>
+        <v>-14914</v>
       </c>
       <c r="X2" t="n">
-        <v>1262551</v>
+        <v>74143</v>
       </c>
       <c r="Y2" t="n">
-        <v>3268031</v>
+        <v>228225</v>
       </c>
       <c r="Z2" t="n">
-        <v>3286806</v>
+        <v>343604</v>
       </c>
       <c r="AA2" t="n">
-        <v>6271873</v>
+        <v>521400</v>
       </c>
       <c r="AB2" t="n">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -696,100 +696,100 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="D3" t="n">
-        <v>45.86</v>
+        <v>51.51</v>
       </c>
       <c r="E3" t="n">
-        <v>45.72</v>
+        <v>49.56</v>
       </c>
       <c r="F3" t="n">
-        <v>43.9</v>
+        <v>47.19</v>
       </c>
       <c r="G3" t="n">
-        <v>37219368</v>
+        <v>48338648</v>
       </c>
       <c r="H3" t="n">
-        <v>16065718</v>
+        <v>59521716</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="J3" t="n">
-        <v>38.65</v>
+        <v>43.66</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9984413</v>
+        <v>5626550</v>
       </c>
       <c r="M3" t="n">
-        <v>13401152</v>
+        <v>43858383</v>
       </c>
       <c r="N3" t="n">
-        <v>16061563</v>
+        <v>82557502</v>
       </c>
       <c r="O3" t="n">
-        <v>17580865</v>
+        <v>207325792</v>
       </c>
       <c r="P3" t="n">
-        <v>8688404</v>
+        <v>3799493</v>
       </c>
       <c r="Q3" t="n">
-        <v>11702979</v>
+        <v>30433762</v>
       </c>
       <c r="R3" t="n">
-        <v>14211979</v>
+        <v>54118705</v>
       </c>
       <c r="S3" t="n">
-        <v>15975318</v>
+        <v>114025664</v>
       </c>
       <c r="T3" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-6000</v>
+        <v>130000</v>
       </c>
       <c r="V3" t="n">
-        <v>-8000</v>
+        <v>230000</v>
       </c>
       <c r="W3" t="n">
-        <v>-28000</v>
+        <v>2330000</v>
       </c>
       <c r="X3" t="n">
-        <v>1302009</v>
+        <v>1827057</v>
       </c>
       <c r="Y3" t="n">
-        <v>1704173</v>
+        <v>13294621</v>
       </c>
       <c r="Z3" t="n">
-        <v>1857584</v>
+        <v>28208797</v>
       </c>
       <c r="AA3" t="n">
-        <v>1633547</v>
+        <v>90970128</v>
       </c>
       <c r="AB3" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,54 +803,54 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、爆量、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>52.8</v>
+        <v>309</v>
       </c>
       <c r="D4" t="n">
-        <v>50.67</v>
+        <v>291.2</v>
       </c>
       <c r="E4" t="n">
-        <v>48.59</v>
+        <v>273.75</v>
       </c>
       <c r="F4" t="n">
-        <v>46.7</v>
+        <v>261.02</v>
       </c>
       <c r="G4" t="n">
-        <v>69462828</v>
+        <v>149620933</v>
       </c>
       <c r="H4" t="n">
-        <v>62187537</v>
+        <v>166353505</v>
       </c>
       <c r="I4" t="n">
-        <v>52.8</v>
+        <v>314</v>
       </c>
       <c r="J4" t="n">
-        <v>43.16</v>
+        <v>239.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>25398318</v>
+        <v>31792458</v>
       </c>
       <c r="M4" t="n">
-        <v>73650098</v>
+        <v>54220728</v>
       </c>
       <c r="N4" t="n">
-        <v>99074323</v>
+        <v>159424411</v>
       </c>
       <c r="O4" t="n">
-        <v>216453878</v>
+        <v>281241388</v>
       </c>
       <c r="P4" t="n">
-        <v>20172152</v>
+        <v>28019626</v>
       </c>
       <c r="Q4" t="n">
-        <v>47470733</v>
+        <v>46947091</v>
       </c>
       <c r="R4" t="n">
-        <v>61094393</v>
+        <v>140152032</v>
       </c>
       <c r="S4" t="n">
-        <v>118371139</v>
+        <v>256678336</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2775440</v>
       </c>
       <c r="U4" t="n">
-        <v>230000</v>
+        <v>6651440</v>
       </c>
       <c r="V4" t="n">
-        <v>2330000</v>
+        <v>14204693</v>
       </c>
       <c r="W4" t="n">
-        <v>1990000</v>
+        <v>15302932</v>
       </c>
       <c r="X4" t="n">
-        <v>5226166</v>
+        <v>997392</v>
       </c>
       <c r="Y4" t="n">
-        <v>25949365</v>
+        <v>622197</v>
       </c>
       <c r="Z4" t="n">
-        <v>35649930</v>
+        <v>5067686</v>
       </c>
       <c r="AA4" t="n">
-        <v>96092739</v>
+        <v>9260120</v>
       </c>
       <c r="AB4" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -930,44 +930,44 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>184.5</v>
+        <v>1890</v>
       </c>
       <c r="D5" t="n">
-        <v>161.9</v>
+        <v>1836</v>
       </c>
       <c r="E5" t="n">
-        <v>143.35</v>
+        <v>1769</v>
       </c>
       <c r="F5" t="n">
-        <v>131.78</v>
+        <v>1754</v>
       </c>
       <c r="G5" t="n">
-        <v>270430116</v>
+        <v>4598000</v>
       </c>
       <c r="H5" t="n">
-        <v>323417408</v>
+        <v>4534800</v>
       </c>
       <c r="I5" t="n">
-        <v>184.5</v>
+        <v>1980</v>
       </c>
       <c r="J5" t="n">
-        <v>103.5</v>
+        <v>1510</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -975,55 +975,55 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>25833459</v>
+        <v>578472</v>
       </c>
       <c r="M5" t="n">
-        <v>97816855</v>
+        <v>277979</v>
       </c>
       <c r="N5" t="n">
-        <v>123740503</v>
+        <v>926668</v>
       </c>
       <c r="O5" t="n">
-        <v>284701329</v>
+        <v>-918565</v>
       </c>
       <c r="P5" t="n">
-        <v>12925256</v>
+        <v>582134</v>
       </c>
       <c r="Q5" t="n">
-        <v>59740683</v>
+        <v>196501</v>
       </c>
       <c r="R5" t="n">
-        <v>74514492</v>
+        <v>203504</v>
       </c>
       <c r="S5" t="n">
-        <v>226449583</v>
+        <v>-895725</v>
       </c>
       <c r="T5" t="n">
-        <v>12930000</v>
+        <v>-2300</v>
       </c>
       <c r="U5" t="n">
-        <v>36135147</v>
+        <v>93941</v>
       </c>
       <c r="V5" t="n">
-        <v>46806299</v>
+        <v>697441</v>
       </c>
       <c r="W5" t="n">
-        <v>53900723</v>
+        <v>-34936</v>
       </c>
       <c r="X5" t="n">
-        <v>-21797</v>
+        <v>-1362</v>
       </c>
       <c r="Y5" t="n">
-        <v>1941025</v>
+        <v>-12463</v>
       </c>
       <c r="Z5" t="n">
-        <v>2419712</v>
+        <v>25723</v>
       </c>
       <c r="AA5" t="n">
-        <v>4351023</v>
+        <v>12096</v>
       </c>
       <c r="AB5" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1047,44 +1047,44 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>390.5</v>
+        <v>194</v>
       </c>
       <c r="D6" t="n">
-        <v>363.5</v>
+        <v>172.4</v>
       </c>
       <c r="E6" t="n">
-        <v>343.1</v>
+        <v>158.65</v>
       </c>
       <c r="F6" t="n">
-        <v>330.3</v>
+        <v>148.7</v>
       </c>
       <c r="G6" t="n">
-        <v>25610532</v>
+        <v>175481303</v>
       </c>
       <c r="H6" t="n">
-        <v>24834434</v>
+        <v>141634285</v>
       </c>
       <c r="I6" t="n">
-        <v>396</v>
+        <v>201</v>
       </c>
       <c r="J6" t="n">
-        <v>283</v>
+        <v>132</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1092,55 +1092,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2805857</v>
+        <v>6685241</v>
       </c>
       <c r="M6" t="n">
-        <v>10499859</v>
+        <v>142757914</v>
       </c>
       <c r="N6" t="n">
-        <v>11238323</v>
+        <v>166665867</v>
       </c>
       <c r="O6" t="n">
-        <v>11935285</v>
+        <v>246141728</v>
       </c>
       <c r="P6" t="n">
-        <v>-415232</v>
+        <v>-11394797</v>
       </c>
       <c r="Q6" t="n">
-        <v>490315</v>
+        <v>105194498</v>
       </c>
       <c r="R6" t="n">
-        <v>905865</v>
+        <v>124977567</v>
       </c>
       <c r="S6" t="n">
-        <v>1076285</v>
+        <v>199208731</v>
       </c>
       <c r="T6" t="n">
-        <v>3252000</v>
+        <v>18857358</v>
       </c>
       <c r="U6" t="n">
-        <v>8962024</v>
+        <v>37346358</v>
       </c>
       <c r="V6" t="n">
-        <v>9204024</v>
+        <v>38910926</v>
       </c>
       <c r="W6" t="n">
-        <v>9837945</v>
+        <v>40933642</v>
       </c>
       <c r="X6" t="n">
-        <v>-30911</v>
+        <v>-777320</v>
       </c>
       <c r="Y6" t="n">
-        <v>1047520</v>
+        <v>217058</v>
       </c>
       <c r="Z6" t="n">
-        <v>1128434</v>
+        <v>2777374</v>
       </c>
       <c r="AA6" t="n">
-        <v>1021055</v>
+        <v>5999355</v>
       </c>
       <c r="AB6" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1164,44 +1164,44 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>419.5</v>
+        <v>2855</v>
       </c>
       <c r="D7" t="n">
-        <v>356.8</v>
+        <v>2717</v>
       </c>
       <c r="E7" t="n">
-        <v>326.2</v>
+        <v>2662.5</v>
       </c>
       <c r="F7" t="n">
-        <v>314</v>
+        <v>2564.75</v>
       </c>
       <c r="G7" t="n">
-        <v>171631936</v>
+        <v>6908395</v>
       </c>
       <c r="H7" t="n">
-        <v>174919886</v>
+        <v>6133567</v>
       </c>
       <c r="I7" t="n">
-        <v>419.5</v>
+        <v>2965</v>
       </c>
       <c r="J7" t="n">
-        <v>260</v>
+        <v>2300</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1209,55 +1209,55 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>23790379</v>
+        <v>1698983</v>
       </c>
       <c r="M7" t="n">
-        <v>77991729</v>
+        <v>2079941</v>
       </c>
       <c r="N7" t="n">
-        <v>82243998</v>
+        <v>2186324</v>
       </c>
       <c r="O7" t="n">
-        <v>66486872</v>
+        <v>1923369</v>
       </c>
       <c r="P7" t="n">
-        <v>18321681</v>
+        <v>1667080</v>
       </c>
       <c r="Q7" t="n">
-        <v>64821550</v>
+        <v>2040599</v>
       </c>
       <c r="R7" t="n">
-        <v>70568527</v>
+        <v>1813866</v>
       </c>
       <c r="S7" t="n">
-        <v>73972511</v>
+        <v>876338</v>
       </c>
       <c r="T7" t="n">
-        <v>5366000</v>
+        <v>52632</v>
       </c>
       <c r="U7" t="n">
-        <v>12339001</v>
+        <v>1633</v>
       </c>
       <c r="V7" t="n">
-        <v>12297001</v>
+        <v>365509</v>
       </c>
       <c r="W7" t="n">
-        <v>-5657889</v>
+        <v>1033454</v>
       </c>
       <c r="X7" t="n">
-        <v>102698</v>
+        <v>-20729</v>
       </c>
       <c r="Y7" t="n">
-        <v>831178</v>
+        <v>37709</v>
       </c>
       <c r="Z7" t="n">
-        <v>-621530</v>
+        <v>6949</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1827750</v>
+        <v>13577</v>
       </c>
       <c r="AB7" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1281,44 +1281,44 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>301.5</v>
+        <v>33.3</v>
       </c>
       <c r="D8" t="n">
-        <v>282.2</v>
+        <v>31.71</v>
       </c>
       <c r="E8" t="n">
-        <v>266.85</v>
+        <v>30.42</v>
       </c>
       <c r="F8" t="n">
-        <v>258.18</v>
+        <v>29.1</v>
       </c>
       <c r="G8" t="n">
-        <v>113076476</v>
+        <v>103127309</v>
       </c>
       <c r="H8" t="n">
-        <v>152099889</v>
+        <v>96210350</v>
       </c>
       <c r="I8" t="n">
-        <v>304.5</v>
+        <v>33.4</v>
       </c>
       <c r="J8" t="n">
-        <v>239.5</v>
+        <v>26.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1326,55 +1326,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>27572146</v>
+        <v>32380516</v>
       </c>
       <c r="M8" t="n">
-        <v>114808214</v>
+        <v>128086522</v>
       </c>
       <c r="N8" t="n">
-        <v>134934212</v>
+        <v>193772291</v>
       </c>
       <c r="O8" t="n">
-        <v>225693771</v>
+        <v>445121961</v>
       </c>
       <c r="P8" t="n">
-        <v>25502562</v>
+        <v>4199891</v>
       </c>
       <c r="Q8" t="n">
-        <v>99266396</v>
+        <v>43691727</v>
       </c>
       <c r="R8" t="n">
-        <v>118882485</v>
+        <v>62472361</v>
       </c>
       <c r="S8" t="n">
-        <v>212312527</v>
+        <v>270653888</v>
       </c>
       <c r="T8" t="n">
-        <v>2068000</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>11299000</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11432866</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>9824449</v>
+        <v>2500000</v>
       </c>
       <c r="X8" t="n">
-        <v>1584</v>
+        <v>28180625</v>
       </c>
       <c r="Y8" t="n">
-        <v>4242818</v>
+        <v>84394795</v>
       </c>
       <c r="Z8" t="n">
-        <v>4618861</v>
+        <v>131299930</v>
       </c>
       <c r="AA8" t="n">
-        <v>3556795</v>
+        <v>171968073</v>
       </c>
       <c r="AB8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1388,54 +1388,54 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2380</v>
+        <v>5600</v>
       </c>
       <c r="D9" t="n">
-        <v>2337</v>
+        <v>5397</v>
       </c>
       <c r="E9" t="n">
-        <v>2293.5</v>
+        <v>5382</v>
       </c>
       <c r="F9" t="n">
-        <v>2273.75</v>
+        <v>5302.5</v>
       </c>
       <c r="G9" t="n">
-        <v>41532527</v>
+        <v>1716435</v>
       </c>
       <c r="H9" t="n">
-        <v>57968955</v>
+        <v>2272550</v>
       </c>
       <c r="I9" t="n">
-        <v>2415</v>
+        <v>5880</v>
       </c>
       <c r="J9" t="n">
-        <v>2185</v>
+        <v>4775</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>785136</v>
+        <v>72503</v>
       </c>
       <c r="M9" t="n">
-        <v>12907350</v>
+        <v>159084</v>
       </c>
       <c r="N9" t="n">
-        <v>22090715</v>
+        <v>869206</v>
       </c>
       <c r="O9" t="n">
-        <v>14620032</v>
+        <v>517567</v>
       </c>
       <c r="P9" t="n">
-        <v>391294</v>
+        <v>91027</v>
       </c>
       <c r="Q9" t="n">
-        <v>10363903</v>
+        <v>158524</v>
       </c>
       <c r="R9" t="n">
-        <v>19174825</v>
+        <v>975425</v>
       </c>
       <c r="S9" t="n">
-        <v>6187704</v>
+        <v>749655</v>
       </c>
       <c r="T9" t="n">
-        <v>-67897</v>
+        <v>-35022</v>
       </c>
       <c r="U9" t="n">
-        <v>739567</v>
+        <v>50980</v>
       </c>
       <c r="V9" t="n">
-        <v>740799</v>
+        <v>34954</v>
       </c>
       <c r="W9" t="n">
-        <v>6162807</v>
+        <v>-119202</v>
       </c>
       <c r="X9" t="n">
-        <v>461739</v>
+        <v>16498</v>
       </c>
       <c r="Y9" t="n">
-        <v>1803880</v>
+        <v>-50420</v>
       </c>
       <c r="Z9" t="n">
-        <v>2175091</v>
+        <v>-141173</v>
       </c>
       <c r="AA9" t="n">
-        <v>2269521</v>
+        <v>-112886</v>
       </c>
       <c r="AB9" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1515,44 +1515,44 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>32.6</v>
       </c>
       <c r="D10" t="n">
-        <v>218.1</v>
+        <v>30.91</v>
       </c>
       <c r="E10" t="n">
-        <v>215.95</v>
+        <v>30.01</v>
       </c>
       <c r="F10" t="n">
-        <v>212.05</v>
+        <v>28.69</v>
       </c>
       <c r="G10" t="n">
-        <v>35901526</v>
+        <v>8734341</v>
       </c>
       <c r="H10" t="n">
-        <v>33270264</v>
+        <v>8956445</v>
       </c>
       <c r="I10" t="n">
-        <v>231</v>
+        <v>33.4</v>
       </c>
       <c r="J10" t="n">
-        <v>195.5</v>
+        <v>26.3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,55 +1560,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7951915</v>
+        <v>1019391</v>
       </c>
       <c r="M10" t="n">
-        <v>28401326</v>
+        <v>4694639</v>
       </c>
       <c r="N10" t="n">
-        <v>28092687</v>
+        <v>4310455</v>
       </c>
       <c r="O10" t="n">
-        <v>66256282</v>
+        <v>6594526</v>
       </c>
       <c r="P10" t="n">
-        <v>-7856376</v>
+        <v>958346</v>
       </c>
       <c r="Q10" t="n">
-        <v>-13611460</v>
+        <v>4432421</v>
       </c>
       <c r="R10" t="n">
-        <v>-23562509</v>
+        <v>4036864</v>
       </c>
       <c r="S10" t="n">
-        <v>-2072646</v>
+        <v>6298172</v>
       </c>
       <c r="T10" t="n">
-        <v>14904941</v>
+        <v>13000</v>
       </c>
       <c r="U10" t="n">
-        <v>39750187</v>
+        <v>178000</v>
       </c>
       <c r="V10" t="n">
-        <v>48700678</v>
+        <v>186000</v>
       </c>
       <c r="W10" t="n">
-        <v>63699163</v>
+        <v>203000</v>
       </c>
       <c r="X10" t="n">
-        <v>903350</v>
+        <v>48045</v>
       </c>
       <c r="Y10" t="n">
-        <v>2262599</v>
+        <v>84218</v>
       </c>
       <c r="Z10" t="n">
-        <v>2954518</v>
+        <v>87591</v>
       </c>
       <c r="AA10" t="n">
-        <v>4629765</v>
+        <v>93354</v>
       </c>
       <c r="AB10" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1165</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>1083</v>
+        <v>104.32</v>
       </c>
       <c r="E11" t="n">
-        <v>1041.4</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1040.35</v>
+        <v>91.61</v>
       </c>
       <c r="G11" t="n">
-        <v>7264000</v>
+        <v>77820950</v>
       </c>
       <c r="H11" t="n">
-        <v>4468600</v>
+        <v>116059088</v>
       </c>
       <c r="I11" t="n">
-        <v>1220</v>
+        <v>118.5</v>
       </c>
       <c r="J11" t="n">
-        <v>936</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2258596</v>
+        <v>1088601</v>
       </c>
       <c r="M11" t="n">
-        <v>4115203</v>
+        <v>33751450</v>
       </c>
       <c r="N11" t="n">
-        <v>3668360</v>
+        <v>71709822</v>
       </c>
       <c r="O11" t="n">
-        <v>2047412</v>
+        <v>140552744</v>
       </c>
       <c r="P11" t="n">
-        <v>2245986</v>
+        <v>-1466154</v>
       </c>
       <c r="Q11" t="n">
-        <v>3765157</v>
+        <v>29055431</v>
       </c>
       <c r="R11" t="n">
-        <v>3395725</v>
+        <v>63351386</v>
       </c>
       <c r="S11" t="n">
-        <v>1973522</v>
+        <v>130155973</v>
       </c>
       <c r="T11" t="n">
-        <v>900</v>
+        <v>3087362</v>
       </c>
       <c r="U11" t="n">
-        <v>2900</v>
+        <v>5916758</v>
       </c>
       <c r="V11" t="n">
-        <v>10900</v>
+        <v>8581215</v>
       </c>
       <c r="W11" t="n">
-        <v>-66915</v>
+        <v>10347648</v>
       </c>
       <c r="X11" t="n">
-        <v>11710</v>
+        <v>-532607</v>
       </c>
       <c r="Y11" t="n">
-        <v>347146</v>
+        <v>-1220739</v>
       </c>
       <c r="Z11" t="n">
-        <v>261735</v>
+        <v>-222779</v>
       </c>
       <c r="AA11" t="n">
-        <v>140805</v>
+        <v>49123</v>
       </c>
       <c r="AB11" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1749,44 +1749,44 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1015</v>
+        <v>176.5</v>
       </c>
       <c r="D12" t="n">
-        <v>905.2</v>
+        <v>173.8</v>
       </c>
       <c r="E12" t="n">
-        <v>794.5</v>
+        <v>173.5</v>
       </c>
       <c r="F12" t="n">
-        <v>770.05</v>
+        <v>172.95</v>
       </c>
       <c r="G12" t="n">
-        <v>11189000</v>
+        <v>296837</v>
       </c>
       <c r="H12" t="n">
-        <v>12916600</v>
+        <v>260571</v>
       </c>
       <c r="I12" t="n">
-        <v>1020</v>
+        <v>176.5</v>
       </c>
       <c r="J12" t="n">
-        <v>597</v>
+        <v>169</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,55 +1794,55 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>162249</v>
+        <v>74290</v>
       </c>
       <c r="M12" t="n">
-        <v>2631325</v>
+        <v>322290</v>
       </c>
       <c r="N12" t="n">
-        <v>8154362</v>
+        <v>292269</v>
       </c>
       <c r="O12" t="n">
-        <v>3673434</v>
+        <v>271146</v>
       </c>
       <c r="P12" t="n">
-        <v>253787</v>
+        <v>63290</v>
       </c>
       <c r="Q12" t="n">
-        <v>1586971</v>
+        <v>311290</v>
       </c>
       <c r="R12" t="n">
-        <v>578662</v>
+        <v>283315</v>
       </c>
       <c r="S12" t="n">
-        <v>-3954722</v>
+        <v>260400</v>
       </c>
       <c r="T12" t="n">
-        <v>-422744</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-69601</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6737532</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>5790882</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>331206</v>
+        <v>11000</v>
       </c>
       <c r="Y12" t="n">
-        <v>1113955</v>
+        <v>11000</v>
       </c>
       <c r="Z12" t="n">
-        <v>838168</v>
+        <v>8954</v>
       </c>
       <c r="AA12" t="n">
-        <v>1837274</v>
+        <v>10746</v>
       </c>
       <c r="AB12" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,54 +1856,54 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、接近20日低點、法人連續偏買、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>112.5</v>
+        <v>43.85</v>
       </c>
       <c r="D13" t="n">
-        <v>100.82</v>
+        <v>42.82</v>
       </c>
       <c r="E13" t="n">
-        <v>93.68000000000001</v>
+        <v>42.6</v>
       </c>
       <c r="F13" t="n">
-        <v>90.66</v>
+        <v>41.13</v>
       </c>
       <c r="G13" t="n">
-        <v>151715085</v>
+        <v>35447430</v>
       </c>
       <c r="H13" t="n">
-        <v>125200668</v>
+        <v>26728337</v>
       </c>
       <c r="I13" t="n">
-        <v>118</v>
+        <v>44.75</v>
       </c>
       <c r="J13" t="n">
-        <v>80.40000000000001</v>
+        <v>37.6</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>17417137</v>
+        <v>5737228</v>
       </c>
       <c r="M13" t="n">
-        <v>96477117</v>
+        <v>17655905</v>
       </c>
       <c r="N13" t="n">
-        <v>143464253</v>
+        <v>20415937</v>
       </c>
       <c r="O13" t="n">
-        <v>190436135</v>
+        <v>60680061</v>
       </c>
       <c r="P13" t="n">
-        <v>16575842</v>
+        <v>13673850</v>
       </c>
       <c r="Q13" t="n">
-        <v>89841244</v>
+        <v>23718444</v>
       </c>
       <c r="R13" t="n">
-        <v>135525546</v>
+        <v>28425764</v>
       </c>
       <c r="S13" t="n">
-        <v>184265443</v>
+        <v>68397503</v>
       </c>
       <c r="T13" t="n">
-        <v>2133396</v>
+        <v>-8447000</v>
       </c>
       <c r="U13" t="n">
-        <v>5130853</v>
+        <v>-8418000</v>
       </c>
       <c r="V13" t="n">
-        <v>6431585</v>
+        <v>-8423000</v>
       </c>
       <c r="W13" t="n">
-        <v>5365685</v>
+        <v>-9799000</v>
       </c>
       <c r="X13" t="n">
-        <v>-1292101</v>
+        <v>510378</v>
       </c>
       <c r="Y13" t="n">
-        <v>1505020</v>
+        <v>2355461</v>
       </c>
       <c r="Z13" t="n">
-        <v>1507122</v>
+        <v>413173</v>
       </c>
       <c r="AA13" t="n">
-        <v>805007</v>
+        <v>2081558</v>
       </c>
       <c r="AB13" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1978,49 +1978,49 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>2382.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>43.65</v>
+        <v>417</v>
       </c>
       <c r="D14" t="n">
-        <v>42.54</v>
+        <v>367.5</v>
       </c>
       <c r="E14" t="n">
-        <v>42.33</v>
+        <v>340.65</v>
       </c>
       <c r="F14" t="n">
-        <v>40.86</v>
+        <v>331.77</v>
       </c>
       <c r="G14" t="n">
-        <v>33817082</v>
+        <v>111020362</v>
       </c>
       <c r="H14" t="n">
-        <v>25080870</v>
+        <v>94064841</v>
       </c>
       <c r="I14" t="n">
-        <v>44.75</v>
+        <v>438</v>
       </c>
       <c r="J14" t="n">
-        <v>37.6</v>
+        <v>288.5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2028,55 +2028,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2392835</v>
+        <v>8317826</v>
       </c>
       <c r="M14" t="n">
-        <v>13256192</v>
+        <v>35086163</v>
       </c>
       <c r="N14" t="n">
-        <v>25091584</v>
+        <v>48478956</v>
       </c>
       <c r="O14" t="n">
-        <v>64253723</v>
+        <v>49254361</v>
       </c>
       <c r="P14" t="n">
-        <v>7811291</v>
+        <v>-24200224</v>
       </c>
       <c r="Q14" t="n">
-        <v>11262778</v>
+        <v>-41395597</v>
       </c>
       <c r="R14" t="n">
-        <v>20258423</v>
+        <v>-57222826</v>
       </c>
       <c r="S14" t="n">
-        <v>65055407</v>
+        <v>-100755558</v>
       </c>
       <c r="T14" t="n">
-        <v>-5695000</v>
+        <v>33418611</v>
       </c>
       <c r="U14" t="n">
-        <v>24000</v>
+        <v>77887836</v>
       </c>
       <c r="V14" t="n">
-        <v>24000</v>
+        <v>105930188</v>
       </c>
       <c r="W14" t="n">
-        <v>-3180000</v>
+        <v>150386305</v>
       </c>
       <c r="X14" t="n">
-        <v>276544</v>
+        <v>-900561</v>
       </c>
       <c r="Y14" t="n">
-        <v>1969414</v>
+        <v>-1406076</v>
       </c>
       <c r="Z14" t="n">
-        <v>4809161</v>
+        <v>-228406</v>
       </c>
       <c r="AA14" t="n">
-        <v>2378316</v>
+        <v>-376386</v>
       </c>
       <c r="AB14" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2095,49 +2095,49 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32.49</v>
+        <v>237</v>
       </c>
       <c r="D15" t="n">
-        <v>31.16</v>
+        <v>223.2</v>
       </c>
       <c r="E15" t="n">
-        <v>29.78</v>
+        <v>218.4</v>
       </c>
       <c r="F15" t="n">
-        <v>28.8</v>
+        <v>213.3</v>
       </c>
       <c r="G15" t="n">
-        <v>111980868</v>
+        <v>38862223</v>
       </c>
       <c r="H15" t="n">
-        <v>97679491</v>
+        <v>34252377</v>
       </c>
       <c r="I15" t="n">
-        <v>32.5</v>
+        <v>242.5</v>
       </c>
       <c r="J15" t="n">
-        <v>26.9</v>
+        <v>195.5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,55 +2145,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50989129</v>
+        <v>6531031</v>
       </c>
       <c r="M15" t="n">
-        <v>141750141</v>
+        <v>30432685</v>
       </c>
       <c r="N15" t="n">
-        <v>190010625</v>
+        <v>36181851</v>
       </c>
       <c r="O15" t="n">
-        <v>446290762</v>
+        <v>51959237</v>
       </c>
       <c r="P15" t="n">
-        <v>17420827</v>
+        <v>-6268756</v>
       </c>
       <c r="Q15" t="n">
-        <v>60474000</v>
+        <v>-11965833</v>
       </c>
       <c r="R15" t="n">
-        <v>111782158</v>
+        <v>-30529481</v>
       </c>
       <c r="S15" t="n">
-        <v>279670276</v>
+        <v>-35322746</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>12281589</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>40030315</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>63351875</v>
       </c>
       <c r="W15" t="n">
-        <v>2500000</v>
+        <v>82210158</v>
       </c>
       <c r="X15" t="n">
-        <v>33568302</v>
+        <v>518198</v>
       </c>
       <c r="Y15" t="n">
-        <v>81276141</v>
+        <v>2368203</v>
       </c>
       <c r="Z15" t="n">
-        <v>78228467</v>
+        <v>3359457</v>
       </c>
       <c r="AA15" t="n">
-        <v>164120486</v>
+        <v>5071825</v>
       </c>
       <c r="AB15" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -2207,54 +2207,54 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31.4</v>
+        <v>2425</v>
       </c>
       <c r="D16" t="n">
-        <v>30.36</v>
+        <v>2362</v>
       </c>
       <c r="E16" t="n">
-        <v>29.89</v>
+        <v>2317.5</v>
       </c>
       <c r="F16" t="n">
-        <v>28.67</v>
+        <v>2282.5</v>
       </c>
       <c r="G16" t="n">
-        <v>14200637</v>
+        <v>29219904</v>
       </c>
       <c r="H16" t="n">
-        <v>12700714</v>
+        <v>55758466</v>
       </c>
       <c r="I16" t="n">
-        <v>31.95</v>
+        <v>2440</v>
       </c>
       <c r="J16" t="n">
-        <v>25.55</v>
+        <v>2185</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,55 +2262,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3608654</v>
+        <v>771034</v>
       </c>
       <c r="M16" t="n">
-        <v>4771014</v>
+        <v>-375278</v>
       </c>
       <c r="N16" t="n">
-        <v>5613297</v>
+        <v>7531281</v>
       </c>
       <c r="O16" t="n">
-        <v>16373416</v>
+        <v>26591070</v>
       </c>
       <c r="P16" t="n">
-        <v>3649755</v>
+        <v>-103827</v>
       </c>
       <c r="Q16" t="n">
-        <v>4479803</v>
+        <v>-3024196</v>
       </c>
       <c r="R16" t="n">
-        <v>5345851</v>
+        <v>3181461</v>
       </c>
       <c r="S16" t="n">
-        <v>15451796</v>
+        <v>17052312</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>647975</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1038293</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1852603</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>6149335</v>
       </c>
       <c r="X16" t="n">
-        <v>-41101</v>
+        <v>226886</v>
       </c>
       <c r="Y16" t="n">
-        <v>291211</v>
+        <v>1610625</v>
       </c>
       <c r="Z16" t="n">
-        <v>267446</v>
+        <v>2497217</v>
       </c>
       <c r="AA16" t="n">
-        <v>921620</v>
+        <v>3389423</v>
       </c>
       <c r="AB16" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2324,54 +2324,54 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37.25</v>
+        <v>399</v>
       </c>
       <c r="D17" t="n">
-        <v>36.22</v>
+        <v>376.8</v>
       </c>
       <c r="E17" t="n">
-        <v>35.68</v>
+        <v>352.8</v>
       </c>
       <c r="F17" t="n">
-        <v>35.27</v>
+        <v>335.2</v>
       </c>
       <c r="G17" t="n">
-        <v>84389805</v>
+        <v>23444363</v>
       </c>
       <c r="H17" t="n">
-        <v>88777580</v>
+        <v>27716252</v>
       </c>
       <c r="I17" t="n">
-        <v>37.85</v>
+        <v>402</v>
       </c>
       <c r="J17" t="n">
-        <v>33.7</v>
+        <v>300</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3007807</v>
+        <v>-683516</v>
       </c>
       <c r="M17" t="n">
-        <v>33011634</v>
+        <v>2322720</v>
       </c>
       <c r="N17" t="n">
-        <v>14678372</v>
+        <v>12308501</v>
       </c>
       <c r="O17" t="n">
-        <v>6369836</v>
+        <v>13980353</v>
       </c>
       <c r="P17" t="n">
-        <v>-38331924</v>
+        <v>-1412433</v>
       </c>
       <c r="Q17" t="n">
-        <v>-83239905</v>
+        <v>-6289843</v>
       </c>
       <c r="R17" t="n">
-        <v>-118612558</v>
+        <v>25828</v>
       </c>
       <c r="S17" t="n">
-        <v>-175002575</v>
+        <v>1037823</v>
       </c>
       <c r="T17" t="n">
-        <v>41577808</v>
+        <v>921000</v>
       </c>
       <c r="U17" t="n">
-        <v>115447051</v>
+        <v>8344000</v>
       </c>
       <c r="V17" t="n">
-        <v>132330184</v>
+        <v>11253181</v>
       </c>
       <c r="W17" t="n">
-        <v>179645474</v>
+        <v>11517102</v>
       </c>
       <c r="X17" t="n">
-        <v>-238077</v>
+        <v>-192083</v>
       </c>
       <c r="Y17" t="n">
-        <v>804488</v>
+        <v>268563</v>
       </c>
       <c r="Z17" t="n">
-        <v>960746</v>
+        <v>1029492</v>
       </c>
       <c r="AA17" t="n">
-        <v>1726937</v>
+        <v>1425428</v>
       </c>
       <c r="AB17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2446,105 +2446,105 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2382.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>400.5</v>
+        <v>30.95</v>
       </c>
       <c r="D18" t="n">
-        <v>346.5</v>
+        <v>30.71</v>
       </c>
       <c r="E18" t="n">
-        <v>327.95</v>
+        <v>30.18</v>
       </c>
       <c r="F18" t="n">
-        <v>328.25</v>
+        <v>28.91</v>
       </c>
       <c r="G18" t="n">
-        <v>151608396</v>
+        <v>9645717</v>
       </c>
       <c r="H18" t="n">
-        <v>80579083</v>
+        <v>12831097</v>
       </c>
       <c r="I18" t="n">
-        <v>409.5</v>
+        <v>31.95</v>
       </c>
       <c r="J18" t="n">
-        <v>288.5</v>
+        <v>26.2</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>21893967</v>
+        <v>252712</v>
       </c>
       <c r="M18" t="n">
-        <v>45194980</v>
+        <v>2282797</v>
       </c>
       <c r="N18" t="n">
-        <v>36660149</v>
+        <v>7865246</v>
       </c>
       <c r="O18" t="n">
-        <v>39893653</v>
+        <v>17467691</v>
       </c>
       <c r="P18" t="n">
-        <v>-14582246</v>
+        <v>429024</v>
       </c>
       <c r="Q18" t="n">
-        <v>-15338081</v>
+        <v>2422319</v>
       </c>
       <c r="R18" t="n">
-        <v>-36751663</v>
+        <v>7568377</v>
       </c>
       <c r="S18" t="n">
-        <v>-74470550</v>
+        <v>16576745</v>
       </c>
       <c r="T18" t="n">
-        <v>37188225</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>59899225</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>72452435</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>114949278</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-712012</v>
+        <v>-176312</v>
       </c>
       <c r="Y18" t="n">
-        <v>633836</v>
+        <v>-139522</v>
       </c>
       <c r="Z18" t="n">
-        <v>959377</v>
+        <v>296869</v>
       </c>
       <c r="AA18" t="n">
-        <v>-585075</v>
+        <v>890946</v>
       </c>
       <c r="AB18" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2558,54 +2558,54 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>175.5</v>
+        <v>1695</v>
       </c>
       <c r="D19" t="n">
-        <v>165</v>
+        <v>1644</v>
       </c>
       <c r="E19" t="n">
-        <v>156.95</v>
+        <v>1581</v>
       </c>
       <c r="F19" t="n">
-        <v>158.75</v>
+        <v>1471.25</v>
       </c>
       <c r="G19" t="n">
-        <v>247731538</v>
+        <v>6905000</v>
       </c>
       <c r="H19" t="n">
-        <v>214432696</v>
+        <v>8434000</v>
       </c>
       <c r="I19" t="n">
-        <v>180</v>
+        <v>1815</v>
       </c>
       <c r="J19" t="n">
-        <v>136.5</v>
+        <v>1190</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2613,55 +2613,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31776921</v>
+        <v>960021</v>
       </c>
       <c r="M19" t="n">
-        <v>58557120</v>
+        <v>1610884</v>
       </c>
       <c r="N19" t="n">
-        <v>10953707</v>
+        <v>2874034</v>
       </c>
       <c r="O19" t="n">
-        <v>42964367</v>
+        <v>3955152</v>
       </c>
       <c r="P19" t="n">
-        <v>27576860</v>
+        <v>708546</v>
       </c>
       <c r="Q19" t="n">
-        <v>50133893</v>
+        <v>211692</v>
       </c>
       <c r="R19" t="n">
-        <v>4442037</v>
+        <v>-498730</v>
       </c>
       <c r="S19" t="n">
-        <v>45182705</v>
+        <v>-868530</v>
       </c>
       <c r="T19" t="n">
-        <v>3292000</v>
+        <v>419850</v>
       </c>
       <c r="U19" t="n">
-        <v>6403000</v>
+        <v>2042850</v>
       </c>
       <c r="V19" t="n">
-        <v>6243000</v>
+        <v>4232850</v>
       </c>
       <c r="W19" t="n">
-        <v>-1707000</v>
+        <v>6061550</v>
       </c>
       <c r="X19" t="n">
-        <v>908061</v>
+        <v>-168375</v>
       </c>
       <c r="Y19" t="n">
-        <v>2020227</v>
+        <v>-643658</v>
       </c>
       <c r="Z19" t="n">
-        <v>268670</v>
+        <v>-860086</v>
       </c>
       <c r="AA19" t="n">
-        <v>-511338</v>
+        <v>-1237868</v>
       </c>
       <c r="AB19" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2675,54 +2675,54 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>31.45</v>
+        <v>2455</v>
       </c>
       <c r="D20" t="n">
-        <v>30.23</v>
+        <v>2414</v>
       </c>
       <c r="E20" t="n">
-        <v>29.41</v>
+        <v>2335.5</v>
       </c>
       <c r="F20" t="n">
-        <v>28.62</v>
+        <v>2226</v>
       </c>
       <c r="G20" t="n">
-        <v>9361391</v>
+        <v>10882344</v>
       </c>
       <c r="H20" t="n">
-        <v>7974139</v>
+        <v>12390908</v>
       </c>
       <c r="I20" t="n">
-        <v>32.55</v>
+        <v>2585</v>
       </c>
       <c r="J20" t="n">
-        <v>26.3</v>
+        <v>1880</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,52 +2730,52 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-363606</v>
+        <v>2704114</v>
       </c>
       <c r="M20" t="n">
-        <v>3394321</v>
+        <v>1291271</v>
       </c>
       <c r="N20" t="n">
-        <v>2627472</v>
+        <v>86319</v>
       </c>
       <c r="O20" t="n">
-        <v>5108655</v>
+        <v>9168995</v>
       </c>
       <c r="P20" t="n">
-        <v>-454166</v>
+        <v>2633111</v>
       </c>
       <c r="Q20" t="n">
-        <v>3181018</v>
+        <v>1749226</v>
       </c>
       <c r="R20" t="n">
-        <v>2415018</v>
+        <v>166241</v>
       </c>
       <c r="S20" t="n">
-        <v>4818692</v>
+        <v>7745280</v>
       </c>
       <c r="T20" t="n">
-        <v>165000</v>
+        <v>41815</v>
       </c>
       <c r="U20" t="n">
-        <v>173000</v>
+        <v>-225185</v>
       </c>
       <c r="V20" t="n">
-        <v>173000</v>
+        <v>258013</v>
       </c>
       <c r="W20" t="n">
-        <v>219000</v>
+        <v>391754</v>
       </c>
       <c r="X20" t="n">
-        <v>-74440</v>
+        <v>29188</v>
       </c>
       <c r="Y20" t="n">
-        <v>40303</v>
+        <v>-232770</v>
       </c>
       <c r="Z20" t="n">
-        <v>39454</v>
+        <v>-337935</v>
       </c>
       <c r="AA20" t="n">
-        <v>70963</v>
+        <v>1031961</v>
       </c>
       <c r="AB20" t="n">
         <v>105</v>
@@ -2792,54 +2792,54 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人小幅買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人小幅買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>56.2</v>
+        <v>739</v>
       </c>
       <c r="D21" t="n">
-        <v>51.98</v>
+        <v>733.2</v>
       </c>
       <c r="E21" t="n">
-        <v>47.69</v>
+        <v>689.6</v>
       </c>
       <c r="F21" t="n">
-        <v>40.86</v>
+        <v>593.55</v>
       </c>
       <c r="G21" t="n">
-        <v>1163170448</v>
+        <v>4661433</v>
       </c>
       <c r="H21" t="n">
-        <v>1033743519</v>
+        <v>6635594</v>
       </c>
       <c r="I21" t="n">
-        <v>58.8</v>
+        <v>778</v>
       </c>
       <c r="J21" t="n">
-        <v>26.8</v>
+        <v>445.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,52 +2847,52 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-195611341</v>
+        <v>213520</v>
       </c>
       <c r="M21" t="n">
-        <v>55247448</v>
+        <v>974021</v>
       </c>
       <c r="N21" t="n">
-        <v>87686194</v>
+        <v>2741828</v>
       </c>
       <c r="O21" t="n">
-        <v>-906948</v>
+        <v>19235025</v>
       </c>
       <c r="P21" t="n">
-        <v>-208585325</v>
+        <v>1265234</v>
       </c>
       <c r="Q21" t="n">
-        <v>35367431</v>
+        <v>2359664</v>
       </c>
       <c r="R21" t="n">
-        <v>67023143</v>
+        <v>4016420</v>
       </c>
       <c r="S21" t="n">
-        <v>-16935718</v>
+        <v>15586113</v>
       </c>
       <c r="T21" t="n">
-        <v>24152000</v>
+        <v>-905744</v>
       </c>
       <c r="U21" t="n">
-        <v>29259444</v>
+        <v>-902458</v>
       </c>
       <c r="V21" t="n">
-        <v>23729444</v>
+        <v>-901077</v>
       </c>
       <c r="W21" t="n">
-        <v>20923859</v>
+        <v>3488114</v>
       </c>
       <c r="X21" t="n">
-        <v>-11178016</v>
+        <v>-145970</v>
       </c>
       <c r="Y21" t="n">
-        <v>-9379427</v>
+        <v>-483185</v>
       </c>
       <c r="Z21" t="n">
-        <v>-3066393</v>
+        <v>-373515</v>
       </c>
       <c r="AA21" t="n">
-        <v>-4895089</v>
+        <v>160798</v>
       </c>
       <c r="AB21" t="n">
         <v>105</v>
@@ -2909,54 +2909,54 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10.5</v>
+        <v>22.7</v>
       </c>
       <c r="D22" t="n">
-        <v>9.210000000000001</v>
+        <v>18.96</v>
       </c>
       <c r="E22" t="n">
-        <v>8.01</v>
+        <v>15.86</v>
       </c>
       <c r="F22" t="n">
-        <v>6.86</v>
+        <v>12.99</v>
       </c>
       <c r="G22" t="n">
-        <v>271642439</v>
+        <v>108791284</v>
       </c>
       <c r="H22" t="n">
-        <v>231621898</v>
+        <v>196689733</v>
       </c>
       <c r="I22" t="n">
-        <v>10.6</v>
+        <v>22.7</v>
       </c>
       <c r="J22" t="n">
-        <v>5.55</v>
+        <v>8.51</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,28 +2964,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-12357264</v>
+        <v>-3871814</v>
       </c>
       <c r="M22" t="n">
-        <v>-3481096</v>
+        <v>7852031</v>
       </c>
       <c r="N22" t="n">
-        <v>2026133</v>
+        <v>19727873</v>
       </c>
       <c r="O22" t="n">
-        <v>44644735</v>
+        <v>60872125</v>
       </c>
       <c r="P22" t="n">
-        <v>-10001479</v>
+        <v>-3529814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2129259</v>
+        <v>6586399</v>
       </c>
       <c r="R22" t="n">
-        <v>8122792</v>
+        <v>17198766</v>
       </c>
       <c r="S22" t="n">
-        <v>40393392</v>
+        <v>53552870</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -3000,16 +3000,16 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2355785</v>
+        <v>-342000</v>
       </c>
       <c r="Y22" t="n">
-        <v>-1351837</v>
+        <v>1265632</v>
       </c>
       <c r="Z22" t="n">
-        <v>-6096659</v>
+        <v>2529107</v>
       </c>
       <c r="AA22" t="n">
-        <v>4251343</v>
+        <v>7319255</v>
       </c>
       <c r="AB22" t="n">
         <v>100</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3036,44 +3036,44 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2700</v>
+        <v>401.5</v>
       </c>
       <c r="D23" t="n">
-        <v>2686</v>
+        <v>374.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2611</v>
+        <v>338.85</v>
       </c>
       <c r="F23" t="n">
-        <v>2543.75</v>
+        <v>319.98</v>
       </c>
       <c r="G23" t="n">
-        <v>4220815</v>
+        <v>151116427</v>
       </c>
       <c r="H23" t="n">
-        <v>5628730</v>
+        <v>163899843</v>
       </c>
       <c r="I23" t="n">
-        <v>2835</v>
+        <v>430.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2300</v>
+        <v>260</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,52 +3081,52 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-395783</v>
+        <v>-14285203</v>
       </c>
       <c r="M23" t="n">
-        <v>955784</v>
+        <v>39219946</v>
       </c>
       <c r="N23" t="n">
-        <v>1340822</v>
+        <v>127211319</v>
       </c>
       <c r="O23" t="n">
-        <v>1692656</v>
+        <v>117278183</v>
       </c>
       <c r="P23" t="n">
-        <v>-272021</v>
+        <v>-14402588</v>
       </c>
       <c r="Q23" t="n">
-        <v>605907</v>
+        <v>30935576</v>
       </c>
       <c r="R23" t="n">
-        <v>812909</v>
+        <v>112585936</v>
       </c>
       <c r="S23" t="n">
-        <v>-24177</v>
+        <v>115503118</v>
       </c>
       <c r="T23" t="n">
-        <v>-118000</v>
+        <v>964764</v>
       </c>
       <c r="U23" t="n">
-        <v>247877</v>
+        <v>8508765</v>
       </c>
       <c r="V23" t="n">
-        <v>538877</v>
+        <v>14113095</v>
       </c>
       <c r="W23" t="n">
-        <v>1674845</v>
+        <v>1875930</v>
       </c>
       <c r="X23" t="n">
-        <v>-5762</v>
+        <v>-847379</v>
       </c>
       <c r="Y23" t="n">
-        <v>102000</v>
+        <v>-224395</v>
       </c>
       <c r="Z23" t="n">
-        <v>-10964</v>
+        <v>512288</v>
       </c>
       <c r="AA23" t="n">
-        <v>41988</v>
+        <v>-100865</v>
       </c>
       <c r="AB23" t="n">
         <v>95</v>
@@ -3160,37 +3160,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>743</v>
+        <v>37.7</v>
       </c>
       <c r="D24" t="n">
-        <v>725.8</v>
+        <v>36.8</v>
       </c>
       <c r="E24" t="n">
-        <v>666.1</v>
+        <v>36.02</v>
       </c>
       <c r="F24" t="n">
-        <v>580.73</v>
+        <v>35.46</v>
       </c>
       <c r="G24" t="n">
-        <v>6753281</v>
+        <v>81050445</v>
       </c>
       <c r="H24" t="n">
-        <v>11835885</v>
+        <v>91523678</v>
       </c>
       <c r="I24" t="n">
-        <v>778</v>
+        <v>38.45</v>
       </c>
       <c r="J24" t="n">
-        <v>445.5</v>
+        <v>34.1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,55 +3198,55 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-543481</v>
+        <v>-5992154</v>
       </c>
       <c r="M24" t="n">
-        <v>2949574</v>
+        <v>10561913</v>
       </c>
       <c r="N24" t="n">
-        <v>1946015</v>
+        <v>40378826</v>
       </c>
       <c r="O24" t="n">
-        <v>25371407</v>
+        <v>29453033</v>
       </c>
       <c r="P24" t="n">
-        <v>159473</v>
+        <v>-38676291</v>
       </c>
       <c r="Q24" t="n">
-        <v>2821599</v>
+        <v>-101446797</v>
       </c>
       <c r="R24" t="n">
-        <v>1092799</v>
+        <v>-137254634</v>
       </c>
       <c r="S24" t="n">
-        <v>18023329</v>
+        <v>-197554213</v>
       </c>
       <c r="T24" t="n">
-        <v>-11905</v>
+        <v>32622579</v>
       </c>
       <c r="U24" t="n">
-        <v>2381</v>
+        <v>111913285</v>
       </c>
       <c r="V24" t="n">
-        <v>871572</v>
+        <v>176358554</v>
       </c>
       <c r="W24" t="n">
-        <v>6833572</v>
+        <v>225320632</v>
       </c>
       <c r="X24" t="n">
-        <v>-691049</v>
+        <v>61558</v>
       </c>
       <c r="Y24" t="n">
-        <v>125594</v>
+        <v>95425</v>
       </c>
       <c r="Z24" t="n">
-        <v>-18356</v>
+        <v>1274906</v>
       </c>
       <c r="AA24" t="n">
-        <v>514506</v>
+        <v>1686614</v>
       </c>
       <c r="AB24" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -3260,54 +3260,54 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5475</v>
+        <v>254</v>
       </c>
       <c r="D25" t="n">
-        <v>5292</v>
+        <v>232.4</v>
       </c>
       <c r="E25" t="n">
-        <v>5313</v>
+        <v>221.25</v>
       </c>
       <c r="F25" t="n">
-        <v>5271</v>
+        <v>203.75</v>
       </c>
       <c r="G25" t="n">
-        <v>1953015</v>
+        <v>10842000</v>
       </c>
       <c r="H25" t="n">
-        <v>2328833</v>
+        <v>12038000</v>
       </c>
       <c r="I25" t="n">
-        <v>5880</v>
+        <v>254</v>
       </c>
       <c r="J25" t="n">
-        <v>4630</v>
+        <v>159.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,52 +3315,52 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>139803</v>
+        <v>-167885</v>
       </c>
       <c r="M25" t="n">
-        <v>903464</v>
+        <v>-1224953</v>
       </c>
       <c r="N25" t="n">
-        <v>454800</v>
+        <v>359494</v>
       </c>
       <c r="O25" t="n">
-        <v>266199</v>
+        <v>2868501</v>
       </c>
       <c r="P25" t="n">
-        <v>201318</v>
+        <v>-259830</v>
       </c>
       <c r="Q25" t="n">
-        <v>693363</v>
+        <v>-1275149</v>
       </c>
       <c r="R25" t="n">
-        <v>472298</v>
+        <v>139916</v>
       </c>
       <c r="S25" t="n">
-        <v>558614</v>
+        <v>2474189</v>
       </c>
       <c r="T25" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>261963</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>141813</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-220366</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-64515</v>
+        <v>91945</v>
       </c>
       <c r="Y25" t="n">
-        <v>-51862</v>
+        <v>50196</v>
       </c>
       <c r="Z25" t="n">
-        <v>-159311</v>
+        <v>219578</v>
       </c>
       <c r="AA25" t="n">
-        <v>-72049</v>
+        <v>394312</v>
       </c>
       <c r="AB25" t="n">
         <v>90</v>
@@ -3377,54 +3377,54 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>53.6</v>
+        <v>49.95</v>
       </c>
       <c r="D26" t="n">
-        <v>53.22</v>
+        <v>46.92</v>
       </c>
       <c r="E26" t="n">
-        <v>52.43</v>
+        <v>46.16</v>
       </c>
       <c r="F26" t="n">
-        <v>51.02</v>
+        <v>44.39</v>
       </c>
       <c r="G26" t="n">
-        <v>71874958</v>
+        <v>39697448</v>
       </c>
       <c r="H26" t="n">
-        <v>40472847</v>
+        <v>21233789</v>
       </c>
       <c r="I26" t="n">
-        <v>55.7</v>
+        <v>52.4</v>
       </c>
       <c r="J26" t="n">
-        <v>47.35</v>
+        <v>38.65</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,52 +3432,52 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-11144966</v>
+        <v>-4888236</v>
       </c>
       <c r="M26" t="n">
-        <v>11190396</v>
+        <v>4847703</v>
       </c>
       <c r="N26" t="n">
-        <v>24413548</v>
+        <v>8458680</v>
       </c>
       <c r="O26" t="n">
-        <v>46722261</v>
+        <v>15447652</v>
       </c>
       <c r="P26" t="n">
-        <v>19358804</v>
+        <v>-5411924</v>
       </c>
       <c r="Q26" t="n">
-        <v>47089739</v>
+        <v>3052091</v>
       </c>
       <c r="R26" t="n">
-        <v>61618385</v>
+        <v>6604480</v>
       </c>
       <c r="S26" t="n">
-        <v>84170507</v>
+        <v>13213818</v>
       </c>
       <c r="T26" t="n">
-        <v>-30584550</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>-36928324</v>
+        <v>-6000</v>
       </c>
       <c r="V26" t="n">
-        <v>-38412024</v>
+        <v>-12000</v>
       </c>
       <c r="W26" t="n">
-        <v>-38493840</v>
+        <v>-34000</v>
       </c>
       <c r="X26" t="n">
-        <v>80780</v>
+        <v>523688</v>
       </c>
       <c r="Y26" t="n">
-        <v>1028981</v>
+        <v>1801612</v>
       </c>
       <c r="Z26" t="n">
-        <v>1207187</v>
+        <v>1866200</v>
       </c>
       <c r="AA26" t="n">
-        <v>1045594</v>
+        <v>2267834</v>
       </c>
       <c r="AB26" t="n">
         <v>90</v>
@@ -3511,37 +3511,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>174.5</v>
+        <v>950</v>
       </c>
       <c r="D27" t="n">
-        <v>173.1</v>
+        <v>956.4</v>
       </c>
       <c r="E27" t="n">
-        <v>173.15</v>
+        <v>878.4</v>
       </c>
       <c r="F27" t="n">
-        <v>172.62</v>
+        <v>812.4</v>
       </c>
       <c r="G27" t="n">
-        <v>252102</v>
+        <v>1612000</v>
       </c>
       <c r="H27" t="n">
-        <v>236121</v>
+        <v>8231600</v>
       </c>
       <c r="I27" t="n">
-        <v>176.5</v>
+        <v>1040</v>
       </c>
       <c r="J27" t="n">
-        <v>168.5</v>
+        <v>630</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3549,52 +3549,52 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>99000</v>
+        <v>49937</v>
       </c>
       <c r="M27" t="n">
-        <v>241000</v>
+        <v>1010824</v>
       </c>
       <c r="N27" t="n">
-        <v>281085</v>
+        <v>2908227</v>
       </c>
       <c r="O27" t="n">
-        <v>231866</v>
+        <v>4521125</v>
       </c>
       <c r="P27" t="n">
-        <v>99000</v>
+        <v>221342</v>
       </c>
       <c r="Q27" t="n">
-        <v>242000</v>
+        <v>1464175</v>
       </c>
       <c r="R27" t="n">
-        <v>280085</v>
+        <v>138108</v>
       </c>
       <c r="S27" t="n">
-        <v>231085</v>
+        <v>-2958386</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>-444294</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>-1659895</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1633371</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>5317588</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>272889</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1000</v>
+        <v>1206544</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>1136748</v>
       </c>
       <c r="AA27" t="n">
-        <v>781</v>
+        <v>2161923</v>
       </c>
       <c r="AB27" t="n">
         <v>85</v>
@@ -3611,54 +3611,54 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2374.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>82.5</v>
+        <v>53.7</v>
       </c>
       <c r="D28" t="n">
-        <v>81.95999999999999</v>
+        <v>53.44</v>
       </c>
       <c r="E28" t="n">
-        <v>81.84999999999999</v>
+        <v>52.77</v>
       </c>
       <c r="F28" t="n">
-        <v>81.17</v>
+        <v>51.17</v>
       </c>
       <c r="G28" t="n">
-        <v>14325800</v>
+        <v>61465906</v>
       </c>
       <c r="H28" t="n">
-        <v>15097617</v>
+        <v>46201172</v>
       </c>
       <c r="I28" t="n">
-        <v>86.40000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="J28" t="n">
-        <v>77.09999999999999</v>
+        <v>47.35</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,55 +3666,55 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-1791149</v>
+        <v>-1332646</v>
       </c>
       <c r="M28" t="n">
-        <v>1809752</v>
+        <v>2468289</v>
       </c>
       <c r="N28" t="n">
-        <v>1203067</v>
+        <v>13384651</v>
       </c>
       <c r="O28" t="n">
-        <v>5941752</v>
+        <v>47625575</v>
       </c>
       <c r="P28" t="n">
-        <v>-1607024</v>
+        <v>27805782</v>
       </c>
       <c r="Q28" t="n">
-        <v>1329595</v>
+        <v>67307159</v>
       </c>
       <c r="R28" t="n">
-        <v>813946</v>
+        <v>78131272</v>
       </c>
       <c r="S28" t="n">
-        <v>5531488</v>
+        <v>113779420</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>-29387700</v>
       </c>
       <c r="U28" t="n">
-        <v>-1000</v>
+        <v>-65978100</v>
       </c>
       <c r="V28" t="n">
-        <v>-1000</v>
+        <v>-66315792</v>
       </c>
       <c r="W28" t="n">
-        <v>-1000</v>
+        <v>-67841458</v>
       </c>
       <c r="X28" t="n">
-        <v>-184125</v>
+        <v>249272</v>
       </c>
       <c r="Y28" t="n">
-        <v>481157</v>
+        <v>1139230</v>
       </c>
       <c r="Z28" t="n">
-        <v>390121</v>
+        <v>1569171</v>
       </c>
       <c r="AA28" t="n">
-        <v>411264</v>
+        <v>1687613</v>
       </c>
       <c r="AB28" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3738,44 +3738,44 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>1409.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>827</v>
+        <v>30.3</v>
       </c>
       <c r="D29" t="n">
-        <v>847</v>
+        <v>25.29</v>
       </c>
       <c r="E29" t="n">
-        <v>820.1</v>
+        <v>21.48</v>
       </c>
       <c r="F29" t="n">
-        <v>773.1</v>
+        <v>19.17</v>
       </c>
       <c r="G29" t="n">
-        <v>4610000</v>
+        <v>10278195</v>
       </c>
       <c r="H29" t="n">
-        <v>5370000</v>
+        <v>29503887</v>
       </c>
       <c r="I29" t="n">
-        <v>929</v>
+        <v>30.3</v>
       </c>
       <c r="J29" t="n">
-        <v>553</v>
+        <v>16.6</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,116 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>11913</v>
+        <v>-410733</v>
       </c>
       <c r="M29" t="n">
-        <v>121167</v>
+        <v>-402927</v>
       </c>
       <c r="N29" t="n">
-        <v>1589915</v>
+        <v>4326828</v>
       </c>
       <c r="O29" t="n">
-        <v>810197</v>
+        <v>19468574</v>
       </c>
       <c r="P29" t="n">
-        <v>31444</v>
+        <v>-1477000</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1421000</v>
+        <v>-3360388</v>
       </c>
       <c r="R29" t="n">
-        <v>-66042</v>
+        <v>-1188550</v>
       </c>
       <c r="S29" t="n">
-        <v>-784088</v>
+        <v>12500637</v>
       </c>
       <c r="T29" t="n">
-        <v>9000</v>
+        <v>-4000</v>
       </c>
       <c r="U29" t="n">
-        <v>1561000</v>
+        <v>-8000</v>
       </c>
       <c r="V29" t="n">
-        <v>1558000</v>
+        <v>-12000</v>
       </c>
       <c r="W29" t="n">
-        <v>1344000</v>
+        <v>156000</v>
       </c>
       <c r="X29" t="n">
-        <v>-28531</v>
+        <v>1070267</v>
       </c>
       <c r="Y29" t="n">
-        <v>-18833</v>
+        <v>2965461</v>
       </c>
       <c r="Z29" t="n">
-        <v>97957</v>
+        <v>5527378</v>
       </c>
       <c r="AA29" t="n">
-        <v>250285</v>
+        <v>6811937</v>
       </c>
       <c r="AB29" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯買超、外資投信同步賣超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.15</v>
+        <v>904</v>
       </c>
       <c r="D30" t="n">
-        <v>23.19</v>
+        <v>873.8</v>
       </c>
       <c r="E30" t="n">
-        <v>22.35</v>
+        <v>888.6</v>
       </c>
       <c r="F30" t="n">
-        <v>20.73</v>
+        <v>871.3</v>
       </c>
       <c r="G30" t="n">
-        <v>720567401</v>
+        <v>17486574</v>
       </c>
       <c r="H30" t="n">
-        <v>574373597</v>
+        <v>18364724</v>
       </c>
       <c r="I30" t="n">
-        <v>26.15</v>
+        <v>980</v>
       </c>
       <c r="J30" t="n">
-        <v>17.5</v>
+        <v>765</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,116 +3900,116 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>51668289</v>
+        <v>7651341</v>
       </c>
       <c r="M30" t="n">
-        <v>8749100</v>
+        <v>10656931</v>
       </c>
       <c r="N30" t="n">
-        <v>-78910101</v>
+        <v>2131374</v>
       </c>
       <c r="O30" t="n">
-        <v>-55159397</v>
+        <v>-2934219</v>
       </c>
       <c r="P30" t="n">
-        <v>47814593</v>
+        <v>8066510</v>
       </c>
       <c r="Q30" t="n">
-        <v>3801406</v>
+        <v>10691048</v>
       </c>
       <c r="R30" t="n">
-        <v>-84520196</v>
+        <v>6702732</v>
       </c>
       <c r="S30" t="n">
-        <v>-64382522</v>
+        <v>2094737</v>
       </c>
       <c r="T30" t="n">
-        <v>2000</v>
+        <v>-441000</v>
       </c>
       <c r="U30" t="n">
-        <v>110000</v>
+        <v>124000</v>
       </c>
       <c r="V30" t="n">
-        <v>106000</v>
+        <v>-4276000</v>
       </c>
       <c r="W30" t="n">
-        <v>247311</v>
+        <v>-4773000</v>
       </c>
       <c r="X30" t="n">
-        <v>3851696</v>
+        <v>25831</v>
       </c>
       <c r="Y30" t="n">
-        <v>4837694</v>
+        <v>-158117</v>
       </c>
       <c r="Z30" t="n">
-        <v>5504095</v>
+        <v>-295358</v>
       </c>
       <c r="AA30" t="n">
-        <v>8975814</v>
+        <v>-255956</v>
       </c>
       <c r="AB30" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>🔥強勢</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>強勢觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1590</v>
+        <v>58.8</v>
       </c>
       <c r="D31" t="n">
-        <v>1631</v>
+        <v>59.94</v>
       </c>
       <c r="E31" t="n">
-        <v>1532</v>
+        <v>58.05</v>
       </c>
       <c r="F31" t="n">
-        <v>1452.25</v>
+        <v>57.51</v>
       </c>
       <c r="G31" t="n">
-        <v>7939000</v>
+        <v>9780335</v>
       </c>
       <c r="H31" t="n">
-        <v>8698600</v>
+        <v>23115101</v>
       </c>
       <c r="I31" t="n">
-        <v>1815</v>
+        <v>63.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1160</v>
+        <v>50.2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,55 +4017,55 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>271386</v>
+        <v>563271</v>
       </c>
       <c r="M31" t="n">
-        <v>1677669</v>
+        <v>-826499</v>
       </c>
       <c r="N31" t="n">
-        <v>2109423</v>
+        <v>10380829</v>
       </c>
       <c r="O31" t="n">
-        <v>2957821</v>
+        <v>12257724</v>
       </c>
       <c r="P31" t="n">
-        <v>51994</v>
+        <v>226598</v>
       </c>
       <c r="Q31" t="n">
-        <v>-416445</v>
+        <v>-125425</v>
       </c>
       <c r="R31" t="n">
-        <v>-1380385</v>
+        <v>10007097</v>
       </c>
       <c r="S31" t="n">
-        <v>-1408184</v>
+        <v>11492217</v>
       </c>
       <c r="T31" t="n">
-        <v>655000</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2600000</v>
+        <v>12000</v>
       </c>
       <c r="V31" t="n">
-        <v>4231000</v>
+        <v>12000</v>
       </c>
       <c r="W31" t="n">
-        <v>5676700</v>
+        <v>126000</v>
       </c>
       <c r="X31" t="n">
-        <v>-435608</v>
+        <v>336673</v>
       </c>
       <c r="Y31" t="n">
-        <v>-505886</v>
+        <v>-713074</v>
       </c>
       <c r="Z31" t="n">
-        <v>-741192</v>
+        <v>361732</v>
       </c>
       <c r="AA31" t="n">
-        <v>-1310695</v>
+        <v>639507</v>
       </c>
       <c r="AB31" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -4084,49 +4084,49 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2360</v>
+        <v>162</v>
       </c>
       <c r="D32" t="n">
-        <v>2427</v>
+        <v>166.3</v>
       </c>
       <c r="E32" t="n">
-        <v>2281.5</v>
+        <v>159.05</v>
       </c>
       <c r="F32" t="n">
-        <v>2213.75</v>
+        <v>158.25</v>
       </c>
       <c r="G32" t="n">
-        <v>12331189</v>
+        <v>58191754</v>
       </c>
       <c r="H32" t="n">
-        <v>12993977</v>
+        <v>177507099</v>
       </c>
       <c r="I32" t="n">
-        <v>2585</v>
+        <v>180</v>
       </c>
       <c r="J32" t="n">
-        <v>1880</v>
+        <v>136.5</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,52 +4134,52 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-643318</v>
+        <v>-9163967</v>
       </c>
       <c r="M32" t="n">
-        <v>-604911</v>
+        <v>41337396</v>
       </c>
       <c r="N32" t="n">
-        <v>3203838</v>
+        <v>131545379</v>
       </c>
       <c r="O32" t="n">
-        <v>10063516</v>
+        <v>80142662</v>
       </c>
       <c r="P32" t="n">
-        <v>-62543</v>
+        <v>-6930989</v>
       </c>
       <c r="Q32" t="n">
-        <v>-724326</v>
+        <v>35018443</v>
       </c>
       <c r="R32" t="n">
-        <v>2791669</v>
+        <v>124837111</v>
       </c>
       <c r="S32" t="n">
-        <v>9284103</v>
+        <v>77508110</v>
       </c>
       <c r="T32" t="n">
-        <v>-400000</v>
+        <v>-6000</v>
       </c>
       <c r="U32" t="n">
-        <v>337387</v>
+        <v>6374000</v>
       </c>
       <c r="V32" t="n">
-        <v>633387</v>
+        <v>6250000</v>
       </c>
       <c r="W32" t="n">
-        <v>-378172</v>
+        <v>3094000</v>
       </c>
       <c r="X32" t="n">
-        <v>-180775</v>
+        <v>-2226978</v>
       </c>
       <c r="Y32" t="n">
-        <v>-217972</v>
+        <v>-55047</v>
       </c>
       <c r="Z32" t="n">
-        <v>-221218</v>
+        <v>458268</v>
       </c>
       <c r="AA32" t="n">
-        <v>1157585</v>
+        <v>-459448</v>
       </c>
       <c r="AB32" t="n">
         <v>55</v>
@@ -4213,37 +4213,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>306</v>
+        <v>59.4</v>
       </c>
       <c r="D33" t="n">
-        <v>310.9</v>
+        <v>53.82</v>
       </c>
       <c r="E33" t="n">
-        <v>301.25</v>
+        <v>49.94</v>
       </c>
       <c r="F33" t="n">
-        <v>283.02</v>
+        <v>42.42</v>
       </c>
       <c r="G33" t="n">
-        <v>13205587</v>
+        <v>972688727</v>
       </c>
       <c r="H33" t="n">
-        <v>23318385</v>
+        <v>954198998</v>
       </c>
       <c r="I33" t="n">
-        <v>336.5</v>
+        <v>60.5</v>
       </c>
       <c r="J33" t="n">
-        <v>222</v>
+        <v>28.15</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,116 +4251,116 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>466343</v>
+        <v>80140919</v>
       </c>
       <c r="M33" t="n">
-        <v>-910778</v>
+        <v>-29652629</v>
       </c>
       <c r="N33" t="n">
-        <v>4355234</v>
+        <v>-174638734</v>
       </c>
       <c r="O33" t="n">
-        <v>-2914456</v>
+        <v>-20966710</v>
       </c>
       <c r="P33" t="n">
-        <v>270014</v>
+        <v>48121131</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1272248</v>
+        <v>-79760889</v>
       </c>
       <c r="R33" t="n">
-        <v>2939329</v>
+        <v>-205849497</v>
       </c>
       <c r="S33" t="n">
-        <v>2881230</v>
+        <v>-68229396</v>
       </c>
       <c r="T33" t="n">
-        <v>333000</v>
+        <v>30478000</v>
       </c>
       <c r="U33" t="n">
-        <v>624000</v>
+        <v>59730000</v>
       </c>
       <c r="V33" t="n">
-        <v>1525000</v>
+        <v>59847221</v>
       </c>
       <c r="W33" t="n">
-        <v>-5727404</v>
+        <v>54248332</v>
       </c>
       <c r="X33" t="n">
-        <v>-136671</v>
+        <v>1541788</v>
       </c>
       <c r="Y33" t="n">
-        <v>-262530</v>
+        <v>-9621740</v>
       </c>
       <c r="Z33" t="n">
-        <v>-109095</v>
+        <v>-28636458</v>
       </c>
       <c r="AA33" t="n">
-        <v>-68282</v>
+        <v>-6985646</v>
       </c>
       <c r="AB33" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6213.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>273</v>
+        <v>11.55</v>
       </c>
       <c r="D34" t="n">
-        <v>274.8</v>
+        <v>9.81</v>
       </c>
       <c r="E34" t="n">
-        <v>266.05</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>269.93</v>
+        <v>7.15</v>
       </c>
       <c r="G34" t="n">
-        <v>26520106</v>
+        <v>120669604</v>
       </c>
       <c r="H34" t="n">
-        <v>26276561</v>
+        <v>187778094</v>
       </c>
       <c r="I34" t="n">
-        <v>322</v>
+        <v>11.55</v>
       </c>
       <c r="J34" t="n">
-        <v>230</v>
+        <v>5.55</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,52 +4368,52 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-7536732</v>
+        <v>-2436751</v>
       </c>
       <c r="M34" t="n">
-        <v>8624099</v>
+        <v>2308123</v>
       </c>
       <c r="N34" t="n">
-        <v>13935232</v>
+        <v>-24896816</v>
       </c>
       <c r="O34" t="n">
-        <v>13950421</v>
+        <v>22226928</v>
       </c>
       <c r="P34" t="n">
-        <v>-7246250</v>
+        <v>-3092500</v>
       </c>
       <c r="Q34" t="n">
-        <v>8266224</v>
+        <v>3773241</v>
       </c>
       <c r="R34" t="n">
-        <v>13367750</v>
+        <v>-23298559</v>
       </c>
       <c r="S34" t="n">
-        <v>12912259</v>
+        <v>20474092</v>
       </c>
       <c r="T34" t="n">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>-127000</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>-408482</v>
+        <v>655749</v>
       </c>
       <c r="Y34" t="n">
-        <v>242875</v>
+        <v>-1465118</v>
       </c>
       <c r="Z34" t="n">
-        <v>523482</v>
+        <v>-1598257</v>
       </c>
       <c r="AA34" t="n">
-        <v>1165162</v>
+        <v>1752836</v>
       </c>
       <c r="AB34" t="n">
         <v>40</v>
@@ -4430,54 +4430,54 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>20.65</v>
+        <v>39.75</v>
       </c>
       <c r="D35" t="n">
-        <v>17.32</v>
+        <v>39.27</v>
       </c>
       <c r="E35" t="n">
-        <v>14.57</v>
+        <v>39.23</v>
       </c>
       <c r="F35" t="n">
-        <v>12.28</v>
+        <v>39.52</v>
       </c>
       <c r="G35" t="n">
-        <v>200560076</v>
+        <v>126939</v>
       </c>
       <c r="H35" t="n">
-        <v>233594287</v>
+        <v>147218</v>
       </c>
       <c r="I35" t="n">
-        <v>20.65</v>
+        <v>40.95</v>
       </c>
       <c r="J35" t="n">
-        <v>8.390000000000001</v>
+        <v>38.5</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,28 +4485,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>14551105</v>
+        <v>51000</v>
       </c>
       <c r="M35" t="n">
-        <v>17008140</v>
+        <v>115000</v>
       </c>
       <c r="N35" t="n">
-        <v>-1362899</v>
+        <v>26976</v>
       </c>
       <c r="O35" t="n">
-        <v>16803068</v>
+        <v>-86104</v>
       </c>
       <c r="P35" t="n">
-        <v>13971173</v>
+        <v>50000</v>
       </c>
       <c r="Q35" t="n">
-        <v>14482349</v>
+        <v>115000</v>
       </c>
       <c r="R35" t="n">
-        <v>-5991014</v>
+        <v>29976</v>
       </c>
       <c r="S35" t="n">
-        <v>13197789</v>
+        <v>-83001</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -4521,16 +4521,16 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>579932</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>2525791</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4628115</v>
+        <v>-3000</v>
       </c>
       <c r="AA35" t="n">
-        <v>3605279</v>
+        <v>-3103</v>
       </c>
       <c r="AB35" t="n">
         <v>40</v>
@@ -4547,54 +4547,54 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏買</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日低點、法人連續偏買。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>27.55</v>
+        <v>33.9</v>
       </c>
       <c r="D36" t="n">
-        <v>23.01</v>
+        <v>32.8</v>
       </c>
       <c r="E36" t="n">
-        <v>20.11</v>
+        <v>33.96</v>
       </c>
       <c r="F36" t="n">
-        <v>18.5</v>
+        <v>35.2</v>
       </c>
       <c r="G36" t="n">
-        <v>25800849</v>
+        <v>9279196</v>
       </c>
       <c r="H36" t="n">
-        <v>38924464</v>
+        <v>9361446</v>
       </c>
       <c r="I36" t="n">
-        <v>27.55</v>
+        <v>44.05</v>
       </c>
       <c r="J36" t="n">
-        <v>16.6</v>
+        <v>31.1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,55 +4602,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-101324</v>
+        <v>1652195</v>
       </c>
       <c r="M36" t="n">
-        <v>1411927</v>
+        <v>1462542</v>
       </c>
       <c r="N36" t="n">
-        <v>-413632</v>
+        <v>91633</v>
       </c>
       <c r="O36" t="n">
-        <v>19867934</v>
+        <v>-4823087</v>
       </c>
       <c r="P36" t="n">
-        <v>-1353388</v>
+        <v>1652123</v>
       </c>
       <c r="Q36" t="n">
-        <v>-2893388</v>
+        <v>1461019</v>
       </c>
       <c r="R36" t="n">
-        <v>-5692553</v>
+        <v>348005</v>
       </c>
       <c r="S36" t="n">
-        <v>14017799</v>
+        <v>-4565714</v>
       </c>
       <c r="T36" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>319000</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1256064</v>
+        <v>72</v>
       </c>
       <c r="Y36" t="n">
-        <v>4313315</v>
+        <v>1523</v>
       </c>
       <c r="Z36" t="n">
-        <v>5290921</v>
+        <v>-256372</v>
       </c>
       <c r="AA36" t="n">
-        <v>5531135</v>
+        <v>-257373</v>
       </c>
       <c r="AB36" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -4664,54 +4664,54 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資投信同步賣超</t>
+          <t>法人連續偏買、5日法人小幅買超</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人賣超、外資投信同步賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2383.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4860</v>
+        <v>4545</v>
       </c>
       <c r="D37" t="n">
-        <v>5082</v>
+        <v>4469</v>
       </c>
       <c r="E37" t="n">
-        <v>5029.5</v>
+        <v>4290.5</v>
       </c>
       <c r="F37" t="n">
-        <v>4912.5</v>
+        <v>3874</v>
       </c>
       <c r="G37" t="n">
-        <v>2172811</v>
+        <v>10480184</v>
       </c>
       <c r="H37" t="n">
-        <v>2553339</v>
+        <v>17146726</v>
       </c>
       <c r="I37" t="n">
-        <v>5635</v>
+        <v>4970</v>
       </c>
       <c r="J37" t="n">
-        <v>4300</v>
+        <v>3100</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,55 +4719,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-196630</v>
+        <v>-137996</v>
       </c>
       <c r="M37" t="n">
-        <v>-192736</v>
+        <v>1212144</v>
       </c>
       <c r="N37" t="n">
-        <v>300883</v>
+        <v>-3815540</v>
       </c>
       <c r="O37" t="n">
-        <v>1484851</v>
+        <v>-4067295</v>
       </c>
       <c r="P37" t="n">
-        <v>7560</v>
+        <v>707096</v>
       </c>
       <c r="Q37" t="n">
-        <v>577741</v>
+        <v>3832840</v>
       </c>
       <c r="R37" t="n">
-        <v>930106</v>
+        <v>651602</v>
       </c>
       <c r="S37" t="n">
-        <v>2367165</v>
+        <v>473754</v>
       </c>
       <c r="T37" t="n">
-        <v>-141028</v>
+        <v>-908215</v>
       </c>
       <c r="U37" t="n">
-        <v>-703946</v>
+        <v>-2115173</v>
       </c>
       <c r="V37" t="n">
-        <v>-560048</v>
+        <v>-3759363</v>
       </c>
       <c r="W37" t="n">
-        <v>-692687</v>
+        <v>-4863411</v>
       </c>
       <c r="X37" t="n">
-        <v>-63162</v>
+        <v>63123</v>
       </c>
       <c r="Y37" t="n">
-        <v>-66531</v>
+        <v>-505523</v>
       </c>
       <c r="Z37" t="n">
-        <v>-69175</v>
+        <v>-707779</v>
       </c>
       <c r="AA37" t="n">
-        <v>-189627</v>
+        <v>322362</v>
       </c>
       <c r="AB37" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -4781,54 +4781,54 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>2401.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>39.65</v>
+        <v>29.35</v>
       </c>
       <c r="D38" t="n">
-        <v>39.12</v>
+        <v>29.59</v>
       </c>
       <c r="E38" t="n">
-        <v>39.18</v>
+        <v>29.88</v>
       </c>
       <c r="F38" t="n">
-        <v>39.62</v>
+        <v>27.61</v>
       </c>
       <c r="G38" t="n">
-        <v>89464</v>
+        <v>6818588</v>
       </c>
       <c r="H38" t="n">
-        <v>158603</v>
+        <v>11914699</v>
       </c>
       <c r="I38" t="n">
-        <v>42.45</v>
+        <v>33</v>
       </c>
       <c r="J38" t="n">
-        <v>38.5</v>
+        <v>23.45</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,28 +4836,28 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>23000</v>
+        <v>-35174</v>
       </c>
       <c r="M38" t="n">
-        <v>97000</v>
+        <v>1443177</v>
       </c>
       <c r="N38" t="n">
-        <v>66452</v>
+        <v>1768520</v>
       </c>
       <c r="O38" t="n">
-        <v>-24080</v>
+        <v>-8588031</v>
       </c>
       <c r="P38" t="n">
-        <v>23000</v>
+        <v>-27351</v>
       </c>
       <c r="Q38" t="n">
-        <v>98000</v>
+        <v>1610834</v>
       </c>
       <c r="R38" t="n">
-        <v>67023</v>
+        <v>2323590</v>
       </c>
       <c r="S38" t="n">
-        <v>-22977</v>
+        <v>-8742162</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -4866,25 +4866,25 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>-7823</v>
       </c>
       <c r="Y38" t="n">
-        <v>-1000</v>
+        <v>-167657</v>
       </c>
       <c r="Z38" t="n">
-        <v>-571</v>
+        <v>-556070</v>
       </c>
       <c r="AA38" t="n">
-        <v>-1103</v>
+        <v>53131</v>
       </c>
       <c r="AB38" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -4898,54 +4898,54 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1875</v>
+        <v>19.4</v>
       </c>
       <c r="D39" t="n">
-        <v>1529</v>
+        <v>19.08</v>
       </c>
       <c r="E39" t="n">
-        <v>1331</v>
+        <v>19.03</v>
       </c>
       <c r="F39" t="n">
-        <v>1209.4</v>
+        <v>18.72</v>
       </c>
       <c r="G39" t="n">
-        <v>4097000</v>
+        <v>111692995</v>
       </c>
       <c r="H39" t="n">
-        <v>5968800</v>
+        <v>82795166</v>
       </c>
       <c r="I39" t="n">
-        <v>1950</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>971</v>
+        <v>18.05</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,52 +4953,52 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>27169</v>
+        <v>19175064</v>
       </c>
       <c r="M39" t="n">
-        <v>-170558</v>
+        <v>-14932637</v>
       </c>
       <c r="N39" t="n">
-        <v>-322749</v>
+        <v>-27888928</v>
       </c>
       <c r="O39" t="n">
-        <v>-1754207</v>
+        <v>-51696009</v>
       </c>
       <c r="P39" t="n">
-        <v>-29043</v>
+        <v>17749990</v>
       </c>
       <c r="Q39" t="n">
-        <v>-646165</v>
+        <v>-17761401</v>
       </c>
       <c r="R39" t="n">
-        <v>-998103</v>
+        <v>-30114939</v>
       </c>
       <c r="S39" t="n">
-        <v>-1526645</v>
+        <v>-55998428</v>
       </c>
       <c r="T39" t="n">
-        <v>73241</v>
+        <v>73654</v>
       </c>
       <c r="U39" t="n">
-        <v>452741</v>
+        <v>1012654</v>
       </c>
       <c r="V39" t="n">
-        <v>656981</v>
+        <v>999179</v>
       </c>
       <c r="W39" t="n">
-        <v>-222136</v>
+        <v>1055179</v>
       </c>
       <c r="X39" t="n">
-        <v>-17029</v>
+        <v>1351420</v>
       </c>
       <c r="Y39" t="n">
-        <v>22866</v>
+        <v>1816110</v>
       </c>
       <c r="Z39" t="n">
-        <v>18373</v>
+        <v>1226832</v>
       </c>
       <c r="AA39" t="n">
-        <v>-5426</v>
+        <v>3247240</v>
       </c>
       <c r="AB39" t="n">
         <v>25</v>
@@ -5015,54 +5015,54 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>231</v>
+        <v>28.75</v>
       </c>
       <c r="D40" t="n">
-        <v>223</v>
+        <v>24.58</v>
       </c>
       <c r="E40" t="n">
-        <v>214.8</v>
+        <v>23.35</v>
       </c>
       <c r="F40" t="n">
-        <v>199.38</v>
+        <v>21.26</v>
       </c>
       <c r="G40" t="n">
-        <v>7792000</v>
+        <v>706729442</v>
       </c>
       <c r="H40" t="n">
-        <v>12208400</v>
+        <v>602484432</v>
       </c>
       <c r="I40" t="n">
-        <v>249.5</v>
+        <v>28.75</v>
       </c>
       <c r="J40" t="n">
-        <v>153</v>
+        <v>17.75</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5070,173 +5070,173 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>177429</v>
+        <v>-29968047</v>
       </c>
       <c r="M40" t="n">
-        <v>865412</v>
+        <v>-90695160</v>
       </c>
       <c r="N40" t="n">
-        <v>-128264</v>
+        <v>-23867482</v>
       </c>
       <c r="O40" t="n">
-        <v>3056820</v>
+        <v>100077771</v>
       </c>
       <c r="P40" t="n">
-        <v>227465</v>
+        <v>-31128755</v>
       </c>
       <c r="Q40" t="n">
-        <v>867681</v>
+        <v>-93668688</v>
       </c>
       <c r="R40" t="n">
-        <v>-219524</v>
+        <v>-28168041</v>
       </c>
       <c r="S40" t="n">
-        <v>2660079</v>
+        <v>86594336</v>
       </c>
       <c r="T40" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="U40" t="n">
+        <v>95000</v>
+      </c>
+      <c r="V40" t="n">
+        <v>189252</v>
+      </c>
+      <c r="W40" t="n">
+        <v>210015</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1166708</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2878528</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4111307</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>13273420</v>
+      </c>
+      <c r="AB40" t="n">
         <v>0</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>-50036</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>-2269</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>91260</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>396741</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>25</v>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>5日法人賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2331.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25.6</v>
+        <v>43.4</v>
       </c>
       <c r="D41" t="n">
-        <v>22.59</v>
+        <v>40.39</v>
       </c>
       <c r="E41" t="n">
-        <v>21.5</v>
+        <v>37.89</v>
       </c>
       <c r="F41" t="n">
-        <v>20.79</v>
+        <v>33.22</v>
       </c>
       <c r="G41" t="n">
-        <v>36583316</v>
+        <v>167087498</v>
       </c>
       <c r="H41" t="n">
-        <v>12732709</v>
+        <v>137463762</v>
       </c>
       <c r="I41" t="n">
-        <v>26.5</v>
+        <v>44.4</v>
       </c>
       <c r="J41" t="n">
-        <v>18.6</v>
+        <v>26.65</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-5054803</v>
+        <v>5718208</v>
       </c>
       <c r="M41" t="n">
-        <v>-806673</v>
+        <v>-2407861</v>
       </c>
       <c r="N41" t="n">
-        <v>-938616</v>
+        <v>-15900393</v>
       </c>
       <c r="O41" t="n">
-        <v>-5832004</v>
+        <v>29650275</v>
       </c>
       <c r="P41" t="n">
-        <v>-5074257</v>
+        <v>4087543</v>
       </c>
       <c r="Q41" t="n">
-        <v>-1166267</v>
+        <v>-4993686</v>
       </c>
       <c r="R41" t="n">
-        <v>-1251662</v>
+        <v>-18847112</v>
       </c>
       <c r="S41" t="n">
-        <v>-6204162</v>
+        <v>34713093</v>
       </c>
       <c r="T41" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U41" t="n">
+        <v>607000</v>
+      </c>
+      <c r="V41" t="n">
+        <v>607000</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-9201000</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1628665</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1978825</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2339719</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4138182</v>
+      </c>
+      <c r="AB41" t="n">
         <v>0</v>
       </c>
-      <c r="U41" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="V41" t="n">
-        <v>-18000</v>
-      </c>
-      <c r="W41" t="n">
-        <v>-68000</v>
-      </c>
-      <c r="X41" t="n">
-        <v>19454</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>367594</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>331046</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>440158</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>15</v>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
           <t>❌避開</t>
@@ -5249,54 +5249,54 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2327.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>846</v>
+        <v>251</v>
       </c>
       <c r="D42" t="n">
-        <v>763.4</v>
+        <v>236.5</v>
       </c>
       <c r="E42" t="n">
-        <v>689</v>
+        <v>253.2</v>
       </c>
       <c r="F42" t="n">
-        <v>556.75</v>
+        <v>244.75</v>
       </c>
       <c r="G42" t="n">
-        <v>23216094</v>
+        <v>5139000</v>
       </c>
       <c r="H42" t="n">
-        <v>26855860</v>
+        <v>3967200</v>
       </c>
       <c r="I42" t="n">
-        <v>847</v>
+        <v>312.5</v>
       </c>
       <c r="J42" t="n">
-        <v>331</v>
+        <v>220</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5304,55 +5304,55 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1273667</v>
+        <v>70509</v>
       </c>
       <c r="M42" t="n">
-        <v>-564007</v>
+        <v>-497664</v>
       </c>
       <c r="N42" t="n">
-        <v>-2699278</v>
+        <v>-1752310</v>
       </c>
       <c r="O42" t="n">
-        <v>50682</v>
+        <v>-2835529</v>
       </c>
       <c r="P42" t="n">
-        <v>1072706</v>
+        <v>54733</v>
       </c>
       <c r="Q42" t="n">
-        <v>-2105887</v>
+        <v>-484973</v>
       </c>
       <c r="R42" t="n">
-        <v>-5496148</v>
+        <v>-1707348</v>
       </c>
       <c r="S42" t="n">
-        <v>-21084617</v>
+        <v>-2563993</v>
       </c>
       <c r="T42" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>378110</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>419110</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>15968446</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>87961</v>
+        <v>15776</v>
       </c>
       <c r="Y42" t="n">
-        <v>1163770</v>
+        <v>-12691</v>
       </c>
       <c r="Z42" t="n">
-        <v>2377760</v>
+        <v>-44962</v>
       </c>
       <c r="AA42" t="n">
-        <v>5166853</v>
+        <v>-271536</v>
       </c>
       <c r="AB42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -5366,54 +5366,54 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、接近20日高點、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>232</v>
+        <v>2585</v>
       </c>
       <c r="D43" t="n">
-        <v>209.8</v>
+        <v>2477</v>
       </c>
       <c r="E43" t="n">
-        <v>196.5</v>
+        <v>2511.5</v>
       </c>
       <c r="F43" t="n">
-        <v>168.05</v>
+        <v>2501</v>
       </c>
       <c r="G43" t="n">
-        <v>3785000</v>
+        <v>4091539</v>
       </c>
       <c r="H43" t="n">
-        <v>1949600</v>
+        <v>4539515</v>
       </c>
       <c r="I43" t="n">
-        <v>249.5</v>
+        <v>2695</v>
       </c>
       <c r="J43" t="n">
-        <v>102</v>
+        <v>2305</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5421,56 +5421,56 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-540940</v>
+        <v>642450</v>
       </c>
       <c r="M43" t="n">
-        <v>-1261064</v>
+        <v>652851</v>
       </c>
       <c r="N43" t="n">
-        <v>-2617931</v>
+        <v>-118466</v>
       </c>
       <c r="O43" t="n">
-        <v>-2682038</v>
+        <v>106813</v>
       </c>
       <c r="P43" t="n">
-        <v>-542508</v>
+        <v>652090</v>
       </c>
       <c r="Q43" t="n">
-        <v>-1220584</v>
+        <v>1382061</v>
       </c>
       <c r="R43" t="n">
-        <v>-2534031</v>
+        <v>1218555</v>
       </c>
       <c r="S43" t="n">
-        <v>-2388726</v>
+        <v>1996945</v>
       </c>
       <c r="T43" t="n">
+        <v>-28332</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-507787</v>
+      </c>
+      <c r="V43" t="n">
+        <v>-1023464</v>
+      </c>
+      <c r="W43" t="n">
+        <v>-1500281</v>
+      </c>
+      <c r="X43" t="n">
+        <v>18692</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-221423</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-313557</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-389851</v>
+      </c>
+      <c r="AB43" t="n">
         <v>0</v>
       </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1568</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>-40480</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>-83900</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>-293312</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>5</v>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
           <t>❌避開</t>
@@ -5483,54 +5483,54 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、成交量放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>862</v>
+        <v>94</v>
       </c>
       <c r="D44" t="n">
-        <v>874</v>
+        <v>88.56</v>
       </c>
       <c r="E44" t="n">
-        <v>881.1</v>
+        <v>84.88</v>
       </c>
       <c r="F44" t="n">
-        <v>873.1</v>
+        <v>75</v>
       </c>
       <c r="G44" t="n">
-        <v>14435807</v>
+        <v>55556531</v>
       </c>
       <c r="H44" t="n">
-        <v>19418216</v>
+        <v>47262320</v>
       </c>
       <c r="I44" t="n">
-        <v>1025</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>765</v>
+        <v>58.5</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5538,52 +5538,52 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-3484177</v>
+        <v>-3853899</v>
       </c>
       <c r="M44" t="n">
-        <v>556777</v>
+        <v>-9275446</v>
       </c>
       <c r="N44" t="n">
-        <v>303458</v>
+        <v>-20398168</v>
       </c>
       <c r="O44" t="n">
-        <v>317155</v>
+        <v>-12774847</v>
       </c>
       <c r="P44" t="n">
-        <v>-3124991</v>
+        <v>-4881890</v>
       </c>
       <c r="Q44" t="n">
-        <v>2667915</v>
+        <v>-10499243</v>
       </c>
       <c r="R44" t="n">
-        <v>3244827</v>
+        <v>-20212549</v>
       </c>
       <c r="S44" t="n">
-        <v>3737072</v>
+        <v>-14166410</v>
       </c>
       <c r="T44" t="n">
-        <v>-199000</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>-1848000</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>-2640000</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>-2756000</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>-160186</v>
+        <v>1027991</v>
       </c>
       <c r="Y44" t="n">
-        <v>-263138</v>
+        <v>1223797</v>
       </c>
       <c r="Z44" t="n">
-        <v>-301369</v>
+        <v>-185619</v>
       </c>
       <c r="AA44" t="n">
-        <v>-663917</v>
+        <v>1391563</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -5600,54 +5600,54 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>2331.TW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>69.90000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="D45" t="n">
-        <v>72.52</v>
+        <v>23.4</v>
       </c>
       <c r="E45" t="n">
-        <v>72.75</v>
+        <v>22.09</v>
       </c>
       <c r="F45" t="n">
-        <v>70.87</v>
+        <v>20.96</v>
       </c>
       <c r="G45" t="n">
-        <v>15331008</v>
+        <v>12147649</v>
       </c>
       <c r="H45" t="n">
-        <v>25563103</v>
+        <v>14358568</v>
       </c>
       <c r="I45" t="n">
-        <v>78.59999999999999</v>
+        <v>26.5</v>
       </c>
       <c r="J45" t="n">
-        <v>64.7</v>
+        <v>18.6</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5655,55 +5655,55 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-689746</v>
+        <v>93361</v>
       </c>
       <c r="M45" t="n">
-        <v>166710</v>
+        <v>-3583473</v>
       </c>
       <c r="N45" t="n">
-        <v>115839</v>
+        <v>-918360</v>
       </c>
       <c r="O45" t="n">
-        <v>4215966</v>
+        <v>-4636315</v>
       </c>
       <c r="P45" t="n">
-        <v>-461554</v>
+        <v>120000</v>
       </c>
       <c r="Q45" t="n">
-        <v>133867</v>
+        <v>-3890257</v>
       </c>
       <c r="R45" t="n">
-        <v>11310</v>
+        <v>-1245372</v>
       </c>
       <c r="S45" t="n">
-        <v>2227920</v>
+        <v>-5002767</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>-26000</v>
       </c>
       <c r="U45" t="n">
-        <v>-3000</v>
+        <v>-26000</v>
       </c>
       <c r="V45" t="n">
-        <v>-3000</v>
+        <v>-39000</v>
       </c>
       <c r="W45" t="n">
-        <v>-7000</v>
+        <v>-91000</v>
       </c>
       <c r="X45" t="n">
-        <v>-228192</v>
+        <v>-639</v>
       </c>
       <c r="Y45" t="n">
-        <v>35843</v>
+        <v>332784</v>
       </c>
       <c r="Z45" t="n">
-        <v>107529</v>
+        <v>366012</v>
       </c>
       <c r="AA45" t="n">
-        <v>1995046</v>
+        <v>457452</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -5717,54 +5717,54 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4525</v>
+        <v>618</v>
       </c>
       <c r="D46" t="n">
-        <v>4488</v>
+        <v>609.4</v>
       </c>
       <c r="E46" t="n">
-        <v>4159</v>
+        <v>598.8</v>
       </c>
       <c r="F46" t="n">
-        <v>3818.25</v>
+        <v>561.85</v>
       </c>
       <c r="G46" t="n">
-        <v>15626708</v>
+        <v>28543715</v>
       </c>
       <c r="H46" t="n">
-        <v>18702858</v>
+        <v>32237644</v>
       </c>
       <c r="I46" t="n">
-        <v>4970</v>
+        <v>669</v>
       </c>
       <c r="J46" t="n">
-        <v>3100</v>
+        <v>465</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5772,55 +5772,55 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-1798696</v>
+        <v>4060745</v>
       </c>
       <c r="M46" t="n">
-        <v>-2125461</v>
+        <v>-1638311</v>
       </c>
       <c r="N46" t="n">
-        <v>-279858</v>
+        <v>-17515618</v>
       </c>
       <c r="O46" t="n">
-        <v>-2958843</v>
+        <v>-12911108</v>
       </c>
       <c r="P46" t="n">
-        <v>-661060</v>
+        <v>7524603</v>
       </c>
       <c r="Q46" t="n">
-        <v>800937</v>
+        <v>11125068</v>
       </c>
       <c r="R46" t="n">
-        <v>3798772</v>
+        <v>-1337969</v>
       </c>
       <c r="S46" t="n">
-        <v>302132</v>
+        <v>1585727</v>
       </c>
       <c r="T46" t="n">
-        <v>-745772</v>
+        <v>-3719275</v>
       </c>
       <c r="U46" t="n">
-        <v>-2227468</v>
+        <v>-13100906</v>
       </c>
       <c r="V46" t="n">
-        <v>-3507077</v>
+        <v>-16475796</v>
       </c>
       <c r="W46" t="n">
-        <v>-3955946</v>
+        <v>-14793065</v>
       </c>
       <c r="X46" t="n">
-        <v>-391864</v>
+        <v>255417</v>
       </c>
       <c r="Y46" t="n">
-        <v>-698930</v>
+        <v>337527</v>
       </c>
       <c r="Z46" t="n">
-        <v>-571553</v>
+        <v>298147</v>
       </c>
       <c r="AA46" t="n">
-        <v>694971</v>
+        <v>296230</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -5839,49 +5839,49 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超、外資買投信賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>209.5</v>
+        <v>820</v>
       </c>
       <c r="D47" t="n">
-        <v>207.7</v>
+        <v>787.2</v>
       </c>
       <c r="E47" t="n">
-        <v>207.35</v>
+        <v>719</v>
       </c>
       <c r="F47" t="n">
-        <v>199.1</v>
+        <v>580.85</v>
       </c>
       <c r="G47" t="n">
-        <v>14574649</v>
+        <v>16771572</v>
       </c>
       <c r="H47" t="n">
-        <v>14516956</v>
+        <v>25216301</v>
       </c>
       <c r="I47" t="n">
-        <v>231</v>
+        <v>847</v>
       </c>
       <c r="J47" t="n">
-        <v>173</v>
+        <v>337.5</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5889,55 +5889,55 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-351631</v>
+        <v>-5648768</v>
       </c>
       <c r="M47" t="n">
-        <v>-2419497</v>
+        <v>-1591494</v>
       </c>
       <c r="N47" t="n">
-        <v>-3934873</v>
+        <v>-7141313</v>
       </c>
       <c r="O47" t="n">
-        <v>-480416</v>
+        <v>-5386676</v>
       </c>
       <c r="P47" t="n">
-        <v>-631340</v>
+        <v>-5655076</v>
       </c>
       <c r="Q47" t="n">
-        <v>-3108768</v>
+        <v>-2323003</v>
       </c>
       <c r="R47" t="n">
-        <v>-4477823</v>
+        <v>-9173375</v>
       </c>
       <c r="S47" t="n">
-        <v>-1637103</v>
+        <v>-16304460</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>-326326</v>
       </c>
       <c r="U47" t="n">
-        <v>2000</v>
+        <v>-226326</v>
       </c>
       <c r="V47" t="n">
-        <v>2000</v>
+        <v>78206</v>
       </c>
       <c r="W47" t="n">
-        <v>7000</v>
+        <v>5496655</v>
       </c>
       <c r="X47" t="n">
-        <v>279709</v>
+        <v>332634</v>
       </c>
       <c r="Y47" t="n">
-        <v>687271</v>
+        <v>957835</v>
       </c>
       <c r="Z47" t="n">
-        <v>540950</v>
+        <v>1953856</v>
       </c>
       <c r="AA47" t="n">
-        <v>1149687</v>
+        <v>5421129</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5961,44 +5961,44 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2401.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28.9</v>
+        <v>270</v>
       </c>
       <c r="D48" t="n">
-        <v>29.93</v>
+        <v>273.5</v>
       </c>
       <c r="E48" t="n">
-        <v>29.64</v>
+        <v>269.4</v>
       </c>
       <c r="F48" t="n">
-        <v>27.4</v>
+        <v>269.18</v>
       </c>
       <c r="G48" t="n">
-        <v>11825676</v>
+        <v>12618497</v>
       </c>
       <c r="H48" t="n">
-        <v>16681787</v>
+        <v>24611890</v>
       </c>
       <c r="I48" t="n">
-        <v>33</v>
+        <v>322</v>
       </c>
       <c r="J48" t="n">
-        <v>23.45</v>
+        <v>230</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6006,55 +6006,55 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2082234</v>
+        <v>-2724193</v>
       </c>
       <c r="M48" t="n">
-        <v>-383861</v>
+        <v>2087143</v>
       </c>
       <c r="N48" t="n">
-        <v>-3016974</v>
+        <v>-2100893</v>
       </c>
       <c r="O48" t="n">
-        <v>-2087771</v>
+        <v>-277451</v>
       </c>
       <c r="P48" t="n">
-        <v>2238069</v>
+        <v>-2502933</v>
       </c>
       <c r="Q48" t="n">
-        <v>-242568</v>
+        <v>2245354</v>
       </c>
       <c r="R48" t="n">
-        <v>-2862566</v>
+        <v>-1930063</v>
       </c>
       <c r="S48" t="n">
-        <v>-3784693</v>
+        <v>-589078</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="U48" t="n">
-        <v>1000</v>
+        <v>110000</v>
       </c>
       <c r="V48" t="n">
-        <v>1000</v>
+        <v>110000</v>
       </c>
       <c r="W48" t="n">
-        <v>174000</v>
+        <v>35000</v>
       </c>
       <c r="X48" t="n">
-        <v>-155835</v>
+        <v>-216260</v>
       </c>
       <c r="Y48" t="n">
-        <v>-142293</v>
+        <v>-268211</v>
       </c>
       <c r="Z48" t="n">
-        <v>-155408</v>
+        <v>-280830</v>
       </c>
       <c r="AA48" t="n">
-        <v>1522922</v>
+        <v>276627</v>
       </c>
       <c r="AB48" t="n">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -6073,49 +6073,49 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>92</v>
+        <v>177.5</v>
       </c>
       <c r="D49" t="n">
-        <v>87.34</v>
+        <v>166.4</v>
       </c>
       <c r="E49" t="n">
-        <v>82.65000000000001</v>
+        <v>149.55</v>
       </c>
       <c r="F49" t="n">
-        <v>73.28</v>
+        <v>135.22</v>
       </c>
       <c r="G49" t="n">
-        <v>49966718</v>
+        <v>332157125</v>
       </c>
       <c r="H49" t="n">
-        <v>49151750</v>
+        <v>302043253</v>
       </c>
       <c r="I49" t="n">
-        <v>94.90000000000001</v>
+        <v>193</v>
       </c>
       <c r="J49" t="n">
-        <v>58.1</v>
+        <v>103.5</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6123,52 +6123,52 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-4365565</v>
+        <v>-52090473</v>
       </c>
       <c r="M49" t="n">
-        <v>-11883977</v>
+        <v>-26110955</v>
       </c>
       <c r="N49" t="n">
-        <v>-12265653</v>
+        <v>-2352641</v>
       </c>
       <c r="O49" t="n">
-        <v>1356791</v>
+        <v>120258409</v>
       </c>
       <c r="P49" t="n">
-        <v>-3981207</v>
+        <v>-49530918</v>
       </c>
       <c r="Q49" t="n">
-        <v>-11674894</v>
+        <v>-43373319</v>
       </c>
       <c r="R49" t="n">
-        <v>-11837513</v>
+        <v>-41523950</v>
       </c>
       <c r="S49" t="n">
-        <v>94554</v>
+        <v>65587446</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1842783</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>20724930</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>42833707</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>54488828</v>
       </c>
       <c r="X49" t="n">
-        <v>-384358</v>
+        <v>-4402338</v>
       </c>
       <c r="Y49" t="n">
-        <v>-209083</v>
+        <v>-3462566</v>
       </c>
       <c r="Z49" t="n">
-        <v>-428140</v>
+        <v>-3662398</v>
       </c>
       <c r="AA49" t="n">
-        <v>1262237</v>
+        <v>182135</v>
       </c>
       <c r="AB49" t="n">
         <v>-25</v>
@@ -6190,49 +6190,49 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2425</v>
+        <v>306</v>
       </c>
       <c r="D50" t="n">
-        <v>2484</v>
+        <v>309.8</v>
       </c>
       <c r="E50" t="n">
-        <v>2488.5</v>
+        <v>303.95</v>
       </c>
       <c r="F50" t="n">
-        <v>2496</v>
+        <v>286.68</v>
       </c>
       <c r="G50" t="n">
-        <v>3795060</v>
+        <v>10693104</v>
       </c>
       <c r="H50" t="n">
-        <v>4512296</v>
+        <v>19595192</v>
       </c>
       <c r="I50" t="n">
-        <v>2695</v>
+        <v>336.5</v>
       </c>
       <c r="J50" t="n">
-        <v>2305</v>
+        <v>237</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6240,52 +6240,52 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-314589</v>
+        <v>60309</v>
       </c>
       <c r="M50" t="n">
-        <v>139112</v>
+        <v>-2618924</v>
       </c>
       <c r="N50" t="n">
-        <v>180195</v>
+        <v>-1570228</v>
       </c>
       <c r="O50" t="n">
-        <v>1067441</v>
+        <v>-1158008</v>
       </c>
       <c r="P50" t="n">
-        <v>373206</v>
+        <v>26315</v>
       </c>
       <c r="Q50" t="n">
-        <v>1331824</v>
+        <v>-2753592</v>
       </c>
       <c r="R50" t="n">
-        <v>1478892</v>
+        <v>-1820456</v>
       </c>
       <c r="S50" t="n">
-        <v>2546361</v>
+        <v>2002875</v>
       </c>
       <c r="T50" t="n">
-        <v>-512455</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>-937132</v>
+        <v>485000</v>
       </c>
       <c r="V50" t="n">
-        <v>-1002722</v>
+        <v>644768</v>
       </c>
       <c r="W50" t="n">
-        <v>-1022089</v>
+        <v>-3366232</v>
       </c>
       <c r="X50" t="n">
-        <v>-175340</v>
+        <v>33994</v>
       </c>
       <c r="Y50" t="n">
-        <v>-255580</v>
+        <v>-350332</v>
       </c>
       <c r="Z50" t="n">
-        <v>-295975</v>
+        <v>-394540</v>
       </c>
       <c r="AA50" t="n">
-        <v>-456831</v>
+        <v>205349</v>
       </c>
       <c r="AB50" t="n">
         <v>-25</v>
@@ -6302,110 +6302,110 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8358.TWO</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>627</v>
+        <v>2830</v>
       </c>
       <c r="D51" t="n">
-        <v>603.2</v>
+        <v>2671</v>
       </c>
       <c r="E51" t="n">
-        <v>557.4</v>
+        <v>2759</v>
       </c>
       <c r="F51" t="n">
-        <v>501.23</v>
+        <v>2746</v>
       </c>
       <c r="G51" t="n">
-        <v>40568000</v>
+        <v>1499000</v>
       </c>
       <c r="H51" t="n">
-        <v>16099800</v>
+        <v>2201800</v>
       </c>
       <c r="I51" t="n">
-        <v>687</v>
+        <v>3215</v>
       </c>
       <c r="J51" t="n">
-        <v>368</v>
+        <v>2460</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-1747347</v>
+        <v>614866</v>
       </c>
       <c r="M51" t="n">
-        <v>-2354323</v>
+        <v>-60619</v>
       </c>
       <c r="N51" t="n">
-        <v>-825225</v>
+        <v>-1330633</v>
       </c>
       <c r="O51" t="n">
-        <v>8573611</v>
+        <v>-701350</v>
       </c>
       <c r="P51" t="n">
-        <v>-105436</v>
+        <v>381569</v>
       </c>
       <c r="Q51" t="n">
-        <v>80687</v>
+        <v>100434</v>
       </c>
       <c r="R51" t="n">
-        <v>1524563</v>
+        <v>-746258</v>
       </c>
       <c r="S51" t="n">
-        <v>10346864</v>
+        <v>-1001529</v>
       </c>
       <c r="T51" t="n">
-        <v>-856656</v>
+        <v>72000</v>
       </c>
       <c r="U51" t="n">
-        <v>-839656</v>
+        <v>-281500</v>
       </c>
       <c r="V51" t="n">
-        <v>-842956</v>
+        <v>-651600</v>
       </c>
       <c r="W51" t="n">
-        <v>-753556</v>
+        <v>126136</v>
       </c>
       <c r="X51" t="n">
-        <v>-785255</v>
+        <v>161297</v>
       </c>
       <c r="Y51" t="n">
-        <v>-1595354</v>
+        <v>120447</v>
       </c>
       <c r="Z51" t="n">
-        <v>-1506832</v>
+        <v>67225</v>
       </c>
       <c r="AA51" t="n">
-        <v>-1019697</v>
+        <v>174043</v>
       </c>
       <c r="AB51" t="n">
-        <v>-35</v>
+        <v>-30</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -6419,54 +6419,54 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>41.3</v>
+        <v>1085</v>
       </c>
       <c r="D52" t="n">
-        <v>39.18</v>
+        <v>1042.6</v>
       </c>
       <c r="E52" t="n">
-        <v>36.38</v>
+        <v>1093.3</v>
       </c>
       <c r="F52" t="n">
-        <v>32.45</v>
+        <v>1044.5</v>
       </c>
       <c r="G52" t="n">
-        <v>135198121</v>
+        <v>1537000</v>
       </c>
       <c r="H52" t="n">
-        <v>137196362</v>
+        <v>3294200</v>
       </c>
       <c r="I52" t="n">
-        <v>43.5</v>
+        <v>1255</v>
       </c>
       <c r="J52" t="n">
-        <v>26.65</v>
+        <v>865</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6474,55 +6474,55 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-2878329</v>
+        <v>357053</v>
       </c>
       <c r="M52" t="n">
-        <v>-15036146</v>
+        <v>-1501742</v>
       </c>
       <c r="N52" t="n">
-        <v>-40410680</v>
+        <v>-2663428</v>
       </c>
       <c r="O52" t="n">
-        <v>65083978</v>
+        <v>-5092737</v>
       </c>
       <c r="P52" t="n">
-        <v>-2705438</v>
+        <v>235886</v>
       </c>
       <c r="Q52" t="n">
-        <v>-16032670</v>
+        <v>-712567</v>
       </c>
       <c r="R52" t="n">
-        <v>-39570049</v>
+        <v>-868027</v>
       </c>
       <c r="S52" t="n">
-        <v>75252925</v>
+        <v>-3100189</v>
       </c>
       <c r="T52" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>605000</v>
+        <v>-904000</v>
       </c>
       <c r="V52" t="n">
-        <v>605000</v>
+        <v>-1901050</v>
       </c>
       <c r="W52" t="n">
-        <v>-14468000</v>
+        <v>-2084050</v>
       </c>
       <c r="X52" t="n">
-        <v>-184891</v>
+        <v>121167</v>
       </c>
       <c r="Y52" t="n">
-        <v>391524</v>
+        <v>114825</v>
       </c>
       <c r="Z52" t="n">
-        <v>-1445631</v>
+        <v>105649</v>
       </c>
       <c r="AA52" t="n">
-        <v>4299053</v>
+        <v>91502</v>
       </c>
       <c r="AB52" t="n">
-        <v>-35</v>
+        <v>-30</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -6536,17 +6536,17 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -6562,28 +6562,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7175</v>
+        <v>7525</v>
       </c>
       <c r="D53" t="n">
-        <v>7690</v>
+        <v>7635</v>
       </c>
       <c r="E53" t="n">
-        <v>7638</v>
+        <v>7692.5</v>
       </c>
       <c r="F53" t="n">
-        <v>7106</v>
+        <v>7197</v>
       </c>
       <c r="G53" t="n">
-        <v>1247463</v>
+        <v>714515</v>
       </c>
       <c r="H53" t="n">
-        <v>1246741</v>
+        <v>1323970</v>
       </c>
       <c r="I53" t="n">
         <v>8465</v>
       </c>
       <c r="J53" t="n">
-        <v>5435</v>
+        <v>5770</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6591,52 +6591,52 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-262781</v>
+        <v>41243</v>
       </c>
       <c r="M53" t="n">
-        <v>-533311</v>
+        <v>-594536</v>
       </c>
       <c r="N53" t="n">
-        <v>-628680</v>
+        <v>-264922</v>
       </c>
       <c r="O53" t="n">
-        <v>-667642</v>
+        <v>-440328</v>
       </c>
       <c r="P53" t="n">
-        <v>-242972</v>
+        <v>-82533</v>
       </c>
       <c r="Q53" t="n">
-        <v>-701673</v>
+        <v>-734818</v>
       </c>
       <c r="R53" t="n">
-        <v>-759682</v>
+        <v>-950465</v>
       </c>
       <c r="S53" t="n">
-        <v>-646804</v>
+        <v>-934919</v>
       </c>
       <c r="T53" t="n">
-        <v>-17000</v>
+        <v>121988</v>
       </c>
       <c r="U53" t="n">
-        <v>180004</v>
+        <v>141988</v>
       </c>
       <c r="V53" t="n">
-        <v>137504</v>
+        <v>695492</v>
       </c>
       <c r="W53" t="n">
-        <v>-17647</v>
+        <v>497992</v>
       </c>
       <c r="X53" t="n">
-        <v>-2809</v>
+        <v>1788</v>
       </c>
       <c r="Y53" t="n">
-        <v>-11642</v>
+        <v>-1706</v>
       </c>
       <c r="Z53" t="n">
-        <v>-6502</v>
+        <v>-9949</v>
       </c>
       <c r="AA53" t="n">
-        <v>-3191</v>
+        <v>-3401</v>
       </c>
       <c r="AB53" t="n">
         <v>-40</v>
@@ -6653,17 +6653,17 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -6679,28 +6679,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>141.5</v>
+        <v>130.5</v>
       </c>
       <c r="D54" t="n">
-        <v>143.5</v>
+        <v>140.9</v>
       </c>
       <c r="E54" t="n">
-        <v>131.1</v>
+        <v>133.35</v>
       </c>
       <c r="F54" t="n">
-        <v>116.51</v>
+        <v>118.46</v>
       </c>
       <c r="G54" t="n">
-        <v>380584577</v>
+        <v>379788969</v>
       </c>
       <c r="H54" t="n">
-        <v>346983487</v>
+        <v>366888888</v>
       </c>
       <c r="I54" t="n">
         <v>155.5</v>
       </c>
       <c r="J54" t="n">
-        <v>87.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -6708,52 +6708,52 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-52504191</v>
+        <v>-64266642</v>
       </c>
       <c r="M54" t="n">
-        <v>-126267680</v>
+        <v>-134457460</v>
       </c>
       <c r="N54" t="n">
-        <v>-124346753</v>
+        <v>-222621270</v>
       </c>
       <c r="O54" t="n">
-        <v>-111315630</v>
+        <v>-222679408</v>
       </c>
       <c r="P54" t="n">
-        <v>63633529</v>
+        <v>74044941</v>
       </c>
       <c r="Q54" t="n">
-        <v>55842157</v>
+        <v>158105129</v>
       </c>
       <c r="R54" t="n">
-        <v>77372124</v>
+        <v>129946285</v>
       </c>
       <c r="S54" t="n">
-        <v>156079152</v>
+        <v>213438189</v>
       </c>
       <c r="T54" t="n">
-        <v>-115062289</v>
+        <v>-140693597</v>
       </c>
       <c r="U54" t="n">
-        <v>-181777817</v>
+        <v>-293781447</v>
       </c>
       <c r="V54" t="n">
-        <v>-200788646</v>
+        <v>-356955419</v>
       </c>
       <c r="W54" t="n">
-        <v>-271465917</v>
+        <v>-448217399</v>
       </c>
       <c r="X54" t="n">
-        <v>-1075431</v>
+        <v>2382014</v>
       </c>
       <c r="Y54" t="n">
-        <v>-332020</v>
+        <v>1218858</v>
       </c>
       <c r="Z54" t="n">
-        <v>-930231</v>
+        <v>4387864</v>
       </c>
       <c r="AA54" t="n">
-        <v>4071135</v>
+        <v>12099802</v>
       </c>
       <c r="AB54" t="n">
         <v>-40</v>
@@ -6787,37 +6787,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2313.TW</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>270.5</v>
+        <v>805</v>
       </c>
       <c r="D55" t="n">
-        <v>275.6</v>
+        <v>834</v>
       </c>
       <c r="E55" t="n">
-        <v>275.2</v>
+        <v>824.9</v>
       </c>
       <c r="F55" t="n">
-        <v>262</v>
+        <v>784.65</v>
       </c>
       <c r="G55" t="n">
-        <v>46492198</v>
+        <v>5308000</v>
       </c>
       <c r="H55" t="n">
-        <v>79673908</v>
+        <v>5701000</v>
       </c>
       <c r="I55" t="n">
-        <v>305.5</v>
+        <v>929</v>
       </c>
       <c r="J55" t="n">
-        <v>233.5</v>
+        <v>577</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-14211549</v>
+        <v>-588015</v>
       </c>
       <c r="M55" t="n">
-        <v>570888</v>
+        <v>-1192008</v>
       </c>
       <c r="N55" t="n">
-        <v>-10077786</v>
+        <v>-258940</v>
       </c>
       <c r="O55" t="n">
-        <v>9812717</v>
+        <v>-75337</v>
       </c>
       <c r="P55" t="n">
-        <v>-11984655</v>
+        <v>-353994</v>
       </c>
       <c r="Q55" t="n">
-        <v>2595853</v>
+        <v>-1254369</v>
       </c>
       <c r="R55" t="n">
-        <v>-3373842</v>
+        <v>-1528248</v>
       </c>
       <c r="S55" t="n">
-        <v>18039173</v>
+        <v>-1383672</v>
       </c>
       <c r="T55" t="n">
-        <v>-989000</v>
+        <v>-214000</v>
       </c>
       <c r="U55" t="n">
-        <v>-1351000</v>
+        <v>152000</v>
       </c>
       <c r="V55" t="n">
-        <v>-5252000</v>
+        <v>1344000</v>
       </c>
       <c r="W55" t="n">
-        <v>-7936000</v>
+        <v>1127000</v>
       </c>
       <c r="X55" t="n">
-        <v>-1237894</v>
+        <v>-20021</v>
       </c>
       <c r="Y55" t="n">
-        <v>-673965</v>
+        <v>-89639</v>
       </c>
       <c r="Z55" t="n">
-        <v>-1451944</v>
+        <v>-74692</v>
       </c>
       <c r="AA55" t="n">
-        <v>-290456</v>
+        <v>181335</v>
       </c>
       <c r="AB55" t="n">
-        <v>-45</v>
+        <v>-40</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -6892,49 +6892,49 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>347</v>
+        <v>464</v>
       </c>
       <c r="D56" t="n">
-        <v>358</v>
+        <v>440.1</v>
       </c>
       <c r="E56" t="n">
-        <v>321.8</v>
+        <v>430.1</v>
       </c>
       <c r="F56" t="n">
-        <v>277.15</v>
+        <v>403.5</v>
       </c>
       <c r="G56" t="n">
-        <v>24564465</v>
+        <v>16630000</v>
       </c>
       <c r="H56" t="n">
-        <v>43272703</v>
+        <v>11933800</v>
       </c>
       <c r="I56" t="n">
-        <v>387</v>
+        <v>492.5</v>
       </c>
       <c r="J56" t="n">
-        <v>217.5</v>
+        <v>343</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -6942,55 +6942,55 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-4510875</v>
+        <v>-276083</v>
       </c>
       <c r="M56" t="n">
-        <v>-7464913</v>
+        <v>-3248230</v>
       </c>
       <c r="N56" t="n">
-        <v>-5183746</v>
+        <v>-6692523</v>
       </c>
       <c r="O56" t="n">
-        <v>-546880</v>
+        <v>7767138</v>
       </c>
       <c r="P56" t="n">
-        <v>2897166</v>
+        <v>-20892</v>
       </c>
       <c r="Q56" t="n">
-        <v>578942</v>
+        <v>-1989794</v>
       </c>
       <c r="R56" t="n">
-        <v>2436030</v>
+        <v>-5164125</v>
       </c>
       <c r="S56" t="n">
-        <v>8302142</v>
+        <v>11815168</v>
       </c>
       <c r="T56" t="n">
-        <v>-6992797</v>
+        <v>-848000</v>
       </c>
       <c r="U56" t="n">
-        <v>-7663188</v>
+        <v>-1806000</v>
       </c>
       <c r="V56" t="n">
-        <v>-6858782</v>
+        <v>-2062000</v>
       </c>
       <c r="W56" t="n">
-        <v>-9716782</v>
+        <v>-5390000</v>
       </c>
       <c r="X56" t="n">
-        <v>-415244</v>
+        <v>592809</v>
       </c>
       <c r="Y56" t="n">
-        <v>-380667</v>
+        <v>547564</v>
       </c>
       <c r="Z56" t="n">
-        <v>-760994</v>
+        <v>533602</v>
       </c>
       <c r="AA56" t="n">
-        <v>867760</v>
+        <v>1341970</v>
       </c>
       <c r="AB56" t="n">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -7004,54 +7004,54 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="D57" t="n">
-        <v>453.2</v>
+        <v>1021</v>
       </c>
       <c r="E57" t="n">
-        <v>392.7</v>
+        <v>1013.5</v>
       </c>
       <c r="F57" t="n">
-        <v>326.85</v>
+        <v>931.8</v>
       </c>
       <c r="G57" t="n">
-        <v>13270682</v>
+        <v>19513439</v>
       </c>
       <c r="H57" t="n">
-        <v>43892046</v>
+        <v>22855178</v>
       </c>
       <c r="I57" t="n">
-        <v>555</v>
+        <v>1130</v>
       </c>
       <c r="J57" t="n">
-        <v>219</v>
+        <v>776</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7059,55 +7059,55 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-4100725</v>
+        <v>1358837</v>
       </c>
       <c r="M57" t="n">
-        <v>-2964859</v>
+        <v>-6647133</v>
       </c>
       <c r="N57" t="n">
-        <v>-8187858</v>
+        <v>-7548250</v>
       </c>
       <c r="O57" t="n">
-        <v>4595648</v>
+        <v>7954444</v>
       </c>
       <c r="P57" t="n">
-        <v>-804207</v>
+        <v>3333271</v>
       </c>
       <c r="Q57" t="n">
-        <v>2395135</v>
+        <v>845545</v>
       </c>
       <c r="R57" t="n">
-        <v>-315037</v>
+        <v>39718</v>
       </c>
       <c r="S57" t="n">
-        <v>-2379773</v>
+        <v>13491572</v>
       </c>
       <c r="T57" t="n">
-        <v>-2948000</v>
+        <v>-1907280</v>
       </c>
       <c r="U57" t="n">
-        <v>-5115465</v>
+        <v>-7014279</v>
       </c>
       <c r="V57" t="n">
-        <v>-7453465</v>
+        <v>-6770652</v>
       </c>
       <c r="W57" t="n">
-        <v>7087098</v>
+        <v>-4988709</v>
       </c>
       <c r="X57" t="n">
-        <v>-348518</v>
+        <v>-67154</v>
       </c>
       <c r="Y57" t="n">
-        <v>-244529</v>
+        <v>-478399</v>
       </c>
       <c r="Z57" t="n">
-        <v>-419356</v>
+        <v>-817316</v>
       </c>
       <c r="AA57" t="n">
-        <v>-111677</v>
+        <v>-548419</v>
       </c>
       <c r="AB57" t="n">
-        <v>-55</v>
+        <v>-50</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -7121,54 +7121,54 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2002.TW</t>
+          <t>8358.TWO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>18.95</v>
+        <v>615</v>
       </c>
       <c r="D58" t="n">
-        <v>19.02</v>
+        <v>614.2</v>
       </c>
       <c r="E58" t="n">
-        <v>18.9</v>
+        <v>572.9</v>
       </c>
       <c r="F58" t="n">
-        <v>18.69</v>
+        <v>509.05</v>
       </c>
       <c r="G58" t="n">
-        <v>70796205</v>
+        <v>18009000</v>
       </c>
       <c r="H58" t="n">
-        <v>79887394</v>
+        <v>18796000</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>687</v>
       </c>
       <c r="J58" t="n">
-        <v>18.05</v>
+        <v>368</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7176,55 +7176,55 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-27285744</v>
+        <v>-3550792</v>
       </c>
       <c r="M58" t="n">
-        <v>-31747337</v>
+        <v>-5823383</v>
       </c>
       <c r="N58" t="n">
-        <v>-59952673</v>
+        <v>-5746383</v>
       </c>
       <c r="O58" t="n">
-        <v>-87305626</v>
+        <v>679148</v>
       </c>
       <c r="P58" t="n">
-        <v>-27915973</v>
+        <v>-2895662</v>
       </c>
       <c r="Q58" t="n">
-        <v>-33318321</v>
+        <v>-3094199</v>
       </c>
       <c r="R58" t="n">
-        <v>-59774330</v>
+        <v>-2577948</v>
       </c>
       <c r="S58" t="n">
-        <v>-92143798</v>
+        <v>3456612</v>
       </c>
       <c r="T58" t="n">
-        <v>934000</v>
+        <v>-5800</v>
       </c>
       <c r="U58" t="n">
-        <v>966525</v>
+        <v>-862456</v>
       </c>
       <c r="V58" t="n">
-        <v>986525</v>
+        <v>-846656</v>
       </c>
       <c r="W58" t="n">
-        <v>1813525</v>
+        <v>-813356</v>
       </c>
       <c r="X58" t="n">
-        <v>-303771</v>
+        <v>-649330</v>
       </c>
       <c r="Y58" t="n">
-        <v>604459</v>
+        <v>-1866728</v>
       </c>
       <c r="Z58" t="n">
-        <v>-1164868</v>
+        <v>-2321779</v>
       </c>
       <c r="AA58" t="n">
-        <v>3024647</v>
+        <v>-1964108</v>
       </c>
       <c r="AB58" t="n">
-        <v>-60</v>
+        <v>-55</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -7238,54 +7238,54 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>71</v>
+        <v>4830</v>
       </c>
       <c r="D59" t="n">
-        <v>72.18000000000001</v>
+        <v>4987</v>
       </c>
       <c r="E59" t="n">
-        <v>70.65000000000001</v>
+        <v>5073</v>
       </c>
       <c r="F59" t="n">
-        <v>69.42</v>
+        <v>4906.5</v>
       </c>
       <c r="G59" t="n">
-        <v>149651763</v>
+        <v>2199236</v>
       </c>
       <c r="H59" t="n">
-        <v>143109988</v>
+        <v>2524721</v>
       </c>
       <c r="I59" t="n">
-        <v>81.2</v>
+        <v>5635</v>
       </c>
       <c r="J59" t="n">
-        <v>61.8</v>
+        <v>4300</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -7293,52 +7293,52 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-50054063</v>
+        <v>133776</v>
       </c>
       <c r="M59" t="n">
-        <v>-21465315</v>
+        <v>-22534</v>
       </c>
       <c r="N59" t="n">
-        <v>-19282198</v>
+        <v>-185322</v>
       </c>
       <c r="O59" t="n">
-        <v>63176945</v>
+        <v>1662839</v>
       </c>
       <c r="P59" t="n">
-        <v>-47089851</v>
+        <v>201629</v>
       </c>
       <c r="Q59" t="n">
-        <v>-19564811</v>
+        <v>927591</v>
       </c>
       <c r="R59" t="n">
-        <v>-18995837</v>
+        <v>643090</v>
       </c>
       <c r="S59" t="n">
-        <v>57547447</v>
+        <v>2143190</v>
       </c>
       <c r="T59" t="n">
-        <v>850000</v>
+        <v>-76388</v>
       </c>
       <c r="U59" t="n">
-        <v>1267000</v>
+        <v>-871416</v>
       </c>
       <c r="V59" t="n">
-        <v>2237000</v>
+        <v>-731639</v>
       </c>
       <c r="W59" t="n">
-        <v>3042000</v>
+        <v>-483067</v>
       </c>
       <c r="X59" t="n">
-        <v>-3814212</v>
+        <v>8535</v>
       </c>
       <c r="Y59" t="n">
-        <v>-3167504</v>
+        <v>-78709</v>
       </c>
       <c r="Z59" t="n">
-        <v>-2523361</v>
+        <v>-96773</v>
       </c>
       <c r="AA59" t="n">
-        <v>2587498</v>
+        <v>2716</v>
       </c>
       <c r="AB59" t="n">
         <v>-65</v>
@@ -7355,54 +7355,54 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、中期買超轉短線賣壓、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>590</v>
+        <v>71.8</v>
       </c>
       <c r="D60" t="n">
-        <v>614.2</v>
+        <v>71.98</v>
       </c>
       <c r="E60" t="n">
-        <v>584.6</v>
+        <v>71.44</v>
       </c>
       <c r="F60" t="n">
-        <v>557.15</v>
+        <v>69.45</v>
       </c>
       <c r="G60" t="n">
-        <v>27769330</v>
+        <v>59799502</v>
       </c>
       <c r="H60" t="n">
-        <v>32530042</v>
+        <v>124243064</v>
       </c>
       <c r="I60" t="n">
-        <v>669</v>
+        <v>81.2</v>
       </c>
       <c r="J60" t="n">
-        <v>465</v>
+        <v>61.8</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -7410,55 +7410,55 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-3429245</v>
+        <v>-2874196</v>
       </c>
       <c r="M60" t="n">
-        <v>-19537100</v>
+        <v>-16692880</v>
       </c>
       <c r="N60" t="n">
-        <v>-19331218</v>
+        <v>-34923173</v>
       </c>
       <c r="O60" t="n">
-        <v>-17152121</v>
+        <v>55462430</v>
       </c>
       <c r="P60" t="n">
-        <v>1316315</v>
+        <v>-2789702</v>
       </c>
       <c r="Q60" t="n">
-        <v>-6501112</v>
+        <v>-14040964</v>
       </c>
       <c r="R60" t="n">
-        <v>-5667308</v>
+        <v>-32499404</v>
       </c>
       <c r="S60" t="n">
-        <v>-5892266</v>
+        <v>53392776</v>
       </c>
       <c r="T60" t="n">
-        <v>-4724678</v>
+        <v>-1000</v>
       </c>
       <c r="U60" t="n">
-        <v>-13157725</v>
+        <v>1270000</v>
       </c>
       <c r="V60" t="n">
-        <v>-13831677</v>
+        <v>1876000</v>
       </c>
       <c r="W60" t="n">
-        <v>-10829800</v>
+        <v>2890000</v>
       </c>
       <c r="X60" t="n">
-        <v>-20882</v>
+        <v>-83494</v>
       </c>
       <c r="Y60" t="n">
-        <v>121737</v>
+        <v>-3921916</v>
       </c>
       <c r="Z60" t="n">
-        <v>167767</v>
+        <v>-4299769</v>
       </c>
       <c r="AA60" t="n">
-        <v>-430055</v>
+        <v>-820346</v>
       </c>
       <c r="AB60" t="n">
-        <v>-70</v>
+        <v>-75</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -7498,22 +7498,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="D61" t="n">
-        <v>56.34</v>
+        <v>55.7</v>
       </c>
       <c r="E61" t="n">
-        <v>55.12</v>
+        <v>55.44</v>
       </c>
       <c r="F61" t="n">
-        <v>52.49</v>
+        <v>52.67</v>
       </c>
       <c r="G61" t="n">
-        <v>8447087</v>
+        <v>6829173</v>
       </c>
       <c r="H61" t="n">
-        <v>10794782</v>
+        <v>10454648</v>
       </c>
       <c r="I61" t="n">
         <v>61.4</v>
@@ -7527,28 +7527,28 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-356474</v>
+        <v>-2035298</v>
       </c>
       <c r="M61" t="n">
-        <v>-3263068</v>
+        <v>-5522308</v>
       </c>
       <c r="N61" t="n">
-        <v>-2097065</v>
+        <v>-5513661</v>
       </c>
       <c r="O61" t="n">
-        <v>11705605</v>
+        <v>8661751</v>
       </c>
       <c r="P61" t="n">
-        <v>-219995</v>
+        <v>-2011705</v>
       </c>
       <c r="Q61" t="n">
-        <v>-3403433</v>
+        <v>-5451350</v>
       </c>
       <c r="R61" t="n">
-        <v>-2286433</v>
+        <v>-5670338</v>
       </c>
       <c r="S61" t="n">
-        <v>10708865</v>
+        <v>7770111</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -7563,16 +7563,16 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>-136479</v>
+        <v>-23593</v>
       </c>
       <c r="Y61" t="n">
-        <v>140365</v>
+        <v>-70958</v>
       </c>
       <c r="Z61" t="n">
-        <v>189368</v>
+        <v>156677</v>
       </c>
       <c r="AA61" t="n">
-        <v>996740</v>
+        <v>891640</v>
       </c>
       <c r="AB61" t="n">
         <v>-75</v>
@@ -7606,37 +7606,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>975</v>
+        <v>510</v>
       </c>
       <c r="D62" t="n">
-        <v>1037</v>
+        <v>515.8</v>
       </c>
       <c r="E62" t="n">
-        <v>995.8</v>
+        <v>516.55</v>
       </c>
       <c r="F62" t="n">
-        <v>924.7</v>
+        <v>466.43</v>
       </c>
       <c r="G62" t="n">
-        <v>29360754</v>
+        <v>8477422</v>
       </c>
       <c r="H62" t="n">
-        <v>24425569</v>
+        <v>13312561</v>
       </c>
       <c r="I62" t="n">
-        <v>1130</v>
+        <v>568</v>
       </c>
       <c r="J62" t="n">
-        <v>776</v>
+        <v>372</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -7644,55 +7644,55 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-7296341</v>
+        <v>-2670345</v>
       </c>
       <c r="M62" t="n">
-        <v>-9466247</v>
+        <v>-6492344</v>
       </c>
       <c r="N62" t="n">
-        <v>-8759639</v>
+        <v>-8474986</v>
       </c>
       <c r="O62" t="n">
-        <v>17140676</v>
+        <v>-15189011</v>
       </c>
       <c r="P62" t="n">
-        <v>-2748858</v>
+        <v>-3594</v>
       </c>
       <c r="Q62" t="n">
-        <v>-3637861</v>
+        <v>1160020</v>
       </c>
       <c r="R62" t="n">
-        <v>-3440200</v>
+        <v>2631516</v>
       </c>
       <c r="S62" t="n">
-        <v>17854581</v>
+        <v>-10185742</v>
       </c>
       <c r="T62" t="n">
-        <v>-4189000</v>
+        <v>-2664780</v>
       </c>
       <c r="U62" t="n">
-        <v>-5332372</v>
+        <v>-6943780</v>
       </c>
       <c r="V62" t="n">
-        <v>-4282372</v>
+        <v>-10398372</v>
       </c>
       <c r="W62" t="n">
-        <v>-173429</v>
+        <v>-4228809</v>
       </c>
       <c r="X62" t="n">
-        <v>-358483</v>
+        <v>-1971</v>
       </c>
       <c r="Y62" t="n">
-        <v>-496014</v>
+        <v>-708584</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1037067</v>
+        <v>-708130</v>
       </c>
       <c r="AA62" t="n">
-        <v>-540476</v>
+        <v>-774460</v>
       </c>
       <c r="AB62" t="n">
-        <v>-85</v>
+        <v>-75</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -7706,54 +7706,54 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>6239.TW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>988</v>
+        <v>343</v>
       </c>
       <c r="D63" t="n">
-        <v>1045.6</v>
+        <v>358.5</v>
       </c>
       <c r="E63" t="n">
-        <v>1080</v>
+        <v>332.65</v>
       </c>
       <c r="F63" t="n">
-        <v>1047</v>
+        <v>282.57</v>
       </c>
       <c r="G63" t="n">
-        <v>4829000</v>
+        <v>15557902</v>
       </c>
       <c r="H63" t="n">
-        <v>4160800</v>
+        <v>31080497</v>
       </c>
       <c r="I63" t="n">
-        <v>1255</v>
+        <v>387</v>
       </c>
       <c r="J63" t="n">
-        <v>865</v>
+        <v>217.5</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -7761,55 +7761,55 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-1437817</v>
+        <v>-3289176</v>
       </c>
       <c r="M63" t="n">
-        <v>-2617249</v>
+        <v>-9223368</v>
       </c>
       <c r="N63" t="n">
-        <v>-4490876</v>
+        <v>-2117937</v>
       </c>
       <c r="O63" t="n">
-        <v>-5667128</v>
+        <v>2610</v>
       </c>
       <c r="P63" t="n">
-        <v>-1009219</v>
+        <v>1324677</v>
       </c>
       <c r="Q63" t="n">
-        <v>-1111735</v>
+        <v>3725640</v>
       </c>
       <c r="R63" t="n">
-        <v>-1294951</v>
+        <v>11462498</v>
       </c>
       <c r="S63" t="n">
-        <v>-3512115</v>
+        <v>13957672</v>
       </c>
       <c r="T63" t="n">
-        <v>-426000</v>
+        <v>-4956458</v>
       </c>
       <c r="U63" t="n">
-        <v>-1497000</v>
+        <v>-12519849</v>
       </c>
       <c r="V63" t="n">
-        <v>-3163050</v>
+        <v>-13664037</v>
       </c>
       <c r="W63" t="n">
-        <v>-2117050</v>
+        <v>-14420631</v>
       </c>
       <c r="X63" t="n">
-        <v>-2598</v>
+        <v>342605</v>
       </c>
       <c r="Y63" t="n">
-        <v>-8514</v>
+        <v>-429159</v>
       </c>
       <c r="Z63" t="n">
-        <v>-32875</v>
+        <v>83602</v>
       </c>
       <c r="AA63" t="n">
-        <v>-37963</v>
+        <v>465569</v>
       </c>
       <c r="AB63" t="n">
-        <v>-85</v>
+        <v>-75</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -7823,17 +7823,17 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -7849,22 +7849,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D64" t="n">
-        <v>532.8</v>
+        <v>523.8</v>
       </c>
       <c r="E64" t="n">
-        <v>522.95</v>
+        <v>529.8</v>
       </c>
       <c r="F64" t="n">
-        <v>505.23</v>
+        <v>505.98</v>
       </c>
       <c r="G64" t="n">
-        <v>33279000</v>
+        <v>40451000</v>
       </c>
       <c r="H64" t="n">
-        <v>35992400</v>
+        <v>34445800</v>
       </c>
       <c r="I64" t="n">
         <v>588</v>
@@ -7878,55 +7878,55 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-4465301</v>
+        <v>-4621048</v>
       </c>
       <c r="M64" t="n">
-        <v>-8311835</v>
+        <v>-8486105</v>
       </c>
       <c r="N64" t="n">
-        <v>-9041043</v>
+        <v>-14206137</v>
       </c>
       <c r="O64" t="n">
-        <v>368824</v>
+        <v>-1592727</v>
       </c>
       <c r="P64" t="n">
-        <v>-2854261</v>
+        <v>-4144734</v>
       </c>
       <c r="Q64" t="n">
-        <v>-5155762</v>
+        <v>-6482378</v>
       </c>
       <c r="R64" t="n">
-        <v>-5764210</v>
+        <v>-10089643</v>
       </c>
       <c r="S64" t="n">
-        <v>-2776980</v>
+        <v>-3186759</v>
       </c>
       <c r="T64" t="n">
-        <v>-851722</v>
+        <v>-268539</v>
       </c>
       <c r="U64" t="n">
-        <v>-2368884</v>
+        <v>-1146702</v>
       </c>
       <c r="V64" t="n">
-        <v>-2062488</v>
+        <v>-2694586</v>
       </c>
       <c r="W64" t="n">
-        <v>1626511</v>
+        <v>-68028</v>
       </c>
       <c r="X64" t="n">
-        <v>-759318</v>
+        <v>-207775</v>
       </c>
       <c r="Y64" t="n">
-        <v>-787189</v>
+        <v>-857025</v>
       </c>
       <c r="Z64" t="n">
-        <v>-1214345</v>
+        <v>-1421908</v>
       </c>
       <c r="AA64" t="n">
-        <v>1519293</v>
+        <v>1662060</v>
       </c>
       <c r="AB64" t="n">
-        <v>-95</v>
+        <v>-85</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -7940,54 +7940,54 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>2313.TW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>422</v>
+        <v>266.5</v>
       </c>
       <c r="D65" t="n">
-        <v>440.1</v>
+        <v>272.5</v>
       </c>
       <c r="E65" t="n">
-        <v>418.4</v>
+        <v>276.35</v>
       </c>
       <c r="F65" t="n">
-        <v>399.02</v>
+        <v>262.82</v>
       </c>
       <c r="G65" t="n">
-        <v>9255000</v>
+        <v>35476485</v>
       </c>
       <c r="H65" t="n">
-        <v>12456400</v>
+        <v>70594101</v>
       </c>
       <c r="I65" t="n">
-        <v>492.5</v>
+        <v>305.5</v>
       </c>
       <c r="J65" t="n">
-        <v>343</v>
+        <v>233.5</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -7995,52 +7995,52 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-2288817</v>
+        <v>-13520259</v>
       </c>
       <c r="M65" t="n">
-        <v>-5731678</v>
+        <v>-41333973</v>
       </c>
       <c r="N65" t="n">
-        <v>-4220478</v>
+        <v>-52273962</v>
       </c>
       <c r="O65" t="n">
-        <v>6678578</v>
+        <v>-20308824</v>
       </c>
       <c r="P65" t="n">
-        <v>-1412036</v>
+        <v>-12351104</v>
       </c>
       <c r="Q65" t="n">
-        <v>-4790611</v>
+        <v>-38044572</v>
       </c>
       <c r="R65" t="n">
-        <v>-2616162</v>
+        <v>-43497918</v>
       </c>
       <c r="S65" t="n">
-        <v>11618354</v>
+        <v>-11452468</v>
       </c>
       <c r="T65" t="n">
-        <v>-883000</v>
+        <v>-785000</v>
       </c>
       <c r="U65" t="n">
-        <v>-970000</v>
+        <v>-1749000</v>
       </c>
       <c r="V65" t="n">
-        <v>-1288000</v>
+        <v>-5137000</v>
       </c>
       <c r="W65" t="n">
-        <v>-5782000</v>
+        <v>-8492000</v>
       </c>
       <c r="X65" t="n">
-        <v>6219</v>
+        <v>-384155</v>
       </c>
       <c r="Y65" t="n">
-        <v>28933</v>
+        <v>-1540401</v>
       </c>
       <c r="Z65" t="n">
-        <v>-316316</v>
+        <v>-3639044</v>
       </c>
       <c r="AA65" t="n">
-        <v>842224</v>
+        <v>-364356</v>
       </c>
       <c r="AB65" t="n">
         <v>-95</v>
@@ -8057,54 +8057,54 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>58.9</v>
+        <v>203</v>
       </c>
       <c r="D66" t="n">
-        <v>59.88</v>
+        <v>207.8</v>
       </c>
       <c r="E66" t="n">
-        <v>57.31</v>
+        <v>208.7</v>
       </c>
       <c r="F66" t="n">
-        <v>57.69</v>
+        <v>200.18</v>
       </c>
       <c r="G66" t="n">
-        <v>15484189</v>
+        <v>9487831</v>
       </c>
       <c r="H66" t="n">
-        <v>25737150</v>
+        <v>13060022</v>
       </c>
       <c r="I66" t="n">
-        <v>64.40000000000001</v>
+        <v>231</v>
       </c>
       <c r="J66" t="n">
-        <v>50.2</v>
+        <v>173</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8112,52 +8112,52 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-2441375</v>
+        <v>-2257743</v>
       </c>
       <c r="M66" t="n">
-        <v>-2142221</v>
+        <v>-1970782</v>
       </c>
       <c r="N66" t="n">
-        <v>-2092627</v>
+        <v>-1804291</v>
       </c>
       <c r="O66" t="n">
-        <v>224630</v>
+        <v>3051752</v>
       </c>
       <c r="P66" t="n">
-        <v>-1939521</v>
+        <v>-2202249</v>
       </c>
       <c r="Q66" t="n">
-        <v>-1846793</v>
+        <v>-2594877</v>
       </c>
       <c r="R66" t="n">
-        <v>-1922226</v>
+        <v>-2527028</v>
       </c>
       <c r="S66" t="n">
-        <v>-133425</v>
+        <v>1474987</v>
       </c>
       <c r="T66" t="n">
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="W66" t="n">
-        <v>164000</v>
+        <v>7000</v>
       </c>
       <c r="X66" t="n">
-        <v>-501854</v>
+        <v>-55494</v>
       </c>
       <c r="Y66" t="n">
-        <v>-307428</v>
+        <v>624095</v>
       </c>
       <c r="Z66" t="n">
-        <v>-182401</v>
+        <v>720737</v>
       </c>
       <c r="AA66" t="n">
-        <v>194055</v>
+        <v>1569765</v>
       </c>
       <c r="AB66" t="n">
         <v>-100</v>
@@ -8191,37 +8191,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>2374.TW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>374</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D67" t="n">
-        <v>378.5</v>
+        <v>82.12</v>
       </c>
       <c r="E67" t="n">
-        <v>379.7</v>
+        <v>82.13</v>
       </c>
       <c r="F67" t="n">
-        <v>385.3</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1987000</v>
+        <v>7506823</v>
       </c>
       <c r="H67" t="n">
-        <v>2318600</v>
+        <v>14667251</v>
       </c>
       <c r="I67" t="n">
-        <v>439</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>353.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8229,52 +8229,52 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-201127</v>
+        <v>-1236645</v>
       </c>
       <c r="M67" t="n">
-        <v>-88446</v>
+        <v>-2502410</v>
       </c>
       <c r="N67" t="n">
-        <v>-1314373</v>
+        <v>-57641</v>
       </c>
       <c r="O67" t="n">
-        <v>-708266</v>
+        <v>6441781</v>
       </c>
       <c r="P67" t="n">
-        <v>-233420</v>
+        <v>-1055466</v>
       </c>
       <c r="Q67" t="n">
-        <v>-150593</v>
+        <v>-2418457</v>
       </c>
       <c r="R67" t="n">
-        <v>-1239050</v>
+        <v>-269356</v>
       </c>
       <c r="S67" t="n">
-        <v>-693282</v>
+        <v>6072600</v>
       </c>
       <c r="T67" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>12000</v>
+        <v>-1000</v>
       </c>
       <c r="W67" t="n">
-        <v>57000</v>
+        <v>-1000</v>
       </c>
       <c r="X67" t="n">
-        <v>-17707</v>
+        <v>-181179</v>
       </c>
       <c r="Y67" t="n">
-        <v>34147</v>
+        <v>-83953</v>
       </c>
       <c r="Z67" t="n">
-        <v>-87323</v>
+        <v>212715</v>
       </c>
       <c r="AA67" t="n">
-        <v>-71984</v>
+        <v>370181</v>
       </c>
       <c r="AB67" t="n">
         <v>-100</v>
@@ -8291,54 +8291,54 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>32.45</v>
+        <v>375</v>
       </c>
       <c r="D68" t="n">
-        <v>32.65</v>
+        <v>376.4</v>
       </c>
       <c r="E68" t="n">
-        <v>33.89</v>
+        <v>380.75</v>
       </c>
       <c r="F68" t="n">
-        <v>35.56</v>
+        <v>383.75</v>
       </c>
       <c r="G68" t="n">
-        <v>8378567</v>
+        <v>1558000</v>
       </c>
       <c r="H68" t="n">
-        <v>9494751</v>
+        <v>2027800</v>
       </c>
       <c r="I68" t="n">
-        <v>44.05</v>
+        <v>439</v>
       </c>
       <c r="J68" t="n">
-        <v>31.1</v>
+        <v>353.5</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -8346,55 +8346,55 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-591639</v>
+        <v>-25668</v>
       </c>
       <c r="M68" t="n">
-        <v>-1020528</v>
+        <v>-531952</v>
       </c>
       <c r="N68" t="n">
-        <v>-1438298</v>
+        <v>-632831</v>
       </c>
       <c r="O68" t="n">
-        <v>-8393054</v>
+        <v>-372423</v>
       </c>
       <c r="P68" t="n">
-        <v>-594105</v>
+        <v>-84836</v>
       </c>
       <c r="Q68" t="n">
-        <v>-865083</v>
+        <v>-639068</v>
       </c>
       <c r="R68" t="n">
-        <v>-1284851</v>
+        <v>-655313</v>
       </c>
       <c r="S68" t="n">
-        <v>-8370609</v>
+        <v>-431165</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="X68" t="n">
-        <v>2466</v>
+        <v>9168</v>
       </c>
       <c r="Y68" t="n">
-        <v>-155445</v>
+        <v>7116</v>
       </c>
       <c r="Z68" t="n">
-        <v>-153447</v>
+        <v>-55518</v>
       </c>
       <c r="AA68" t="n">
-        <v>-22445</v>
+        <v>16742</v>
       </c>
       <c r="AB68" t="n">
-        <v>-110</v>
+        <v>-100</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
@@ -8408,54 +8408,54 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2575</v>
+        <v>69.2</v>
       </c>
       <c r="D69" t="n">
-        <v>2682</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>2734</v>
+        <v>72.61</v>
       </c>
       <c r="F69" t="n">
-        <v>2737.25</v>
+        <v>71</v>
       </c>
       <c r="G69" t="n">
-        <v>2674000</v>
+        <v>12006225</v>
       </c>
       <c r="H69" t="n">
-        <v>2585400</v>
+        <v>22952796</v>
       </c>
       <c r="I69" t="n">
-        <v>3215</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>2460</v>
+        <v>66</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -8463,55 +8463,55 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-522690</v>
+        <v>-476519</v>
       </c>
       <c r="M69" t="n">
-        <v>-1204996</v>
+        <v>-4520149</v>
       </c>
       <c r="N69" t="n">
-        <v>-2194967</v>
+        <v>-3093898</v>
       </c>
       <c r="O69" t="n">
-        <v>-1058221</v>
+        <v>5170814</v>
       </c>
       <c r="P69" t="n">
-        <v>-291999</v>
+        <v>-395076</v>
       </c>
       <c r="Q69" t="n">
-        <v>-560965</v>
+        <v>-4137801</v>
       </c>
       <c r="R69" t="n">
-        <v>-1435056</v>
+        <v>-2643311</v>
       </c>
       <c r="S69" t="n">
-        <v>-1190083</v>
+        <v>4106741</v>
       </c>
       <c r="T69" t="n">
-        <v>-192100</v>
+        <v>-4000</v>
       </c>
       <c r="U69" t="n">
-        <v>-587500</v>
+        <v>-7000</v>
       </c>
       <c r="V69" t="n">
-        <v>-656400</v>
+        <v>-7000</v>
       </c>
       <c r="W69" t="n">
-        <v>133436</v>
+        <v>-11000</v>
       </c>
       <c r="X69" t="n">
-        <v>-38591</v>
+        <v>-77443</v>
       </c>
       <c r="Y69" t="n">
-        <v>-56531</v>
+        <v>-375348</v>
       </c>
       <c r="Z69" t="n">
-        <v>-103511</v>
+        <v>-443587</v>
       </c>
       <c r="AA69" t="n">
-        <v>-1574</v>
+        <v>1075073</v>
       </c>
       <c r="AB69" t="n">
-        <v>-145</v>
+        <v>-130</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
@@ -8525,17 +8525,17 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、死亡交叉、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、死亡交叉、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/stock_analysis_result.xlsx
+++ b/output/stock_analysis_result.xlsx
@@ -586,37 +586,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1280</v>
+        <v>180</v>
       </c>
       <c r="D2" t="n">
-        <v>1132</v>
+        <v>175.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1075.5</v>
+        <v>174.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1049.1</v>
+        <v>173.45</v>
       </c>
       <c r="G2" t="n">
-        <v>9226000</v>
+        <v>491119</v>
       </c>
       <c r="H2" t="n">
-        <v>5738800</v>
+        <v>319971</v>
       </c>
       <c r="I2" t="n">
-        <v>1280</v>
+        <v>180.5</v>
       </c>
       <c r="J2" t="n">
-        <v>936</v>
+        <v>170</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -624,55 +624,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2687525</v>
+        <v>146000</v>
       </c>
       <c r="M2" t="n">
-        <v>6136047</v>
+        <v>319290</v>
       </c>
       <c r="N2" t="n">
-        <v>6868199</v>
+        <v>461290</v>
       </c>
       <c r="O2" t="n">
-        <v>5082453</v>
+        <v>449252</v>
       </c>
       <c r="P2" t="n">
-        <v>2612382</v>
+        <v>145000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5905922</v>
+        <v>307290</v>
       </c>
       <c r="R2" t="n">
-        <v>6512695</v>
+        <v>450290</v>
       </c>
       <c r="S2" t="n">
-        <v>4575967</v>
+        <v>434400</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>1000</v>
       </c>
-      <c r="U2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V2" t="n">
-        <v>11900</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-14914</v>
-      </c>
-      <c r="X2" t="n">
-        <v>74143</v>
-      </c>
       <c r="Y2" t="n">
-        <v>228225</v>
+        <v>12000</v>
       </c>
       <c r="Z2" t="n">
-        <v>343604</v>
+        <v>11000</v>
       </c>
       <c r="AA2" t="n">
-        <v>521400</v>
+        <v>14852</v>
       </c>
       <c r="AB2" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -686,110 +686,110 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、突破20日高點、帶量突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.8</v>
+        <v>260</v>
       </c>
       <c r="D3" t="n">
-        <v>51.51</v>
+        <v>242.6</v>
       </c>
       <c r="E3" t="n">
-        <v>49.56</v>
+        <v>227.95</v>
       </c>
       <c r="F3" t="n">
-        <v>47.19</v>
+        <v>208.55</v>
       </c>
       <c r="G3" t="n">
-        <v>48338648</v>
+        <v>24253000</v>
       </c>
       <c r="H3" t="n">
-        <v>59521716</v>
+        <v>14627200</v>
       </c>
       <c r="I3" t="n">
-        <v>53.8</v>
+        <v>274</v>
       </c>
       <c r="J3" t="n">
-        <v>43.66</v>
+        <v>159.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5626550</v>
+        <v>722695</v>
       </c>
       <c r="M3" t="n">
-        <v>43858383</v>
+        <v>732239</v>
       </c>
       <c r="N3" t="n">
-        <v>82557502</v>
+        <v>1420222</v>
       </c>
       <c r="O3" t="n">
-        <v>207325792</v>
+        <v>3676229</v>
       </c>
       <c r="P3" t="n">
-        <v>3799493</v>
+        <v>829349</v>
       </c>
       <c r="Q3" t="n">
-        <v>30433762</v>
+        <v>796984</v>
       </c>
       <c r="R3" t="n">
-        <v>54118705</v>
+        <v>1437200</v>
       </c>
       <c r="S3" t="n">
-        <v>114025664</v>
+        <v>3486508</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2330000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1827057</v>
+        <v>-106654</v>
       </c>
       <c r="Y3" t="n">
-        <v>13294621</v>
+        <v>-64745</v>
       </c>
       <c r="Z3" t="n">
-        <v>28208797</v>
+        <v>-16978</v>
       </c>
       <c r="AA3" t="n">
-        <v>90970128</v>
+        <v>189721</v>
       </c>
       <c r="AB3" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -803,54 +803,54 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、成交量放大、帶量突破20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2748.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>309</v>
+        <v>40.45</v>
       </c>
       <c r="D4" t="n">
-        <v>291.2</v>
+        <v>39.61</v>
       </c>
       <c r="E4" t="n">
-        <v>273.75</v>
+        <v>39.34</v>
       </c>
       <c r="F4" t="n">
-        <v>261.02</v>
+        <v>39.52</v>
       </c>
       <c r="G4" t="n">
-        <v>149620933</v>
+        <v>398931</v>
       </c>
       <c r="H4" t="n">
-        <v>166353505</v>
+        <v>179400</v>
       </c>
       <c r="I4" t="n">
-        <v>314</v>
+        <v>40.95</v>
       </c>
       <c r="J4" t="n">
-        <v>239.5</v>
+        <v>38.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -858,55 +858,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>31792458</v>
+        <v>41000</v>
       </c>
       <c r="M4" t="n">
-        <v>54220728</v>
+        <v>115000</v>
       </c>
       <c r="N4" t="n">
-        <v>159424411</v>
+        <v>189000</v>
       </c>
       <c r="O4" t="n">
-        <v>281241388</v>
+        <v>-15572</v>
       </c>
       <c r="P4" t="n">
-        <v>28019626</v>
+        <v>40000</v>
       </c>
       <c r="Q4" t="n">
-        <v>46947091</v>
+        <v>113000</v>
       </c>
       <c r="R4" t="n">
-        <v>140152032</v>
+        <v>188000</v>
       </c>
       <c r="S4" t="n">
-        <v>256678336</v>
+        <v>-15001</v>
       </c>
       <c r="T4" t="n">
-        <v>2775440</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>6651440</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>14204693</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>15302932</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>997392</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>622197</v>
+        <v>2000</v>
       </c>
       <c r="Z4" t="n">
-        <v>5067686</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>9260120</v>
+        <v>-571</v>
       </c>
       <c r="AB4" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -920,54 +920,54 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、黃金交叉、爆量、接近20日高點</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、黃金交叉、爆量、接近20日高點、法人連續偏買、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5289.TWO</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1890</v>
+        <v>2425</v>
       </c>
       <c r="D5" t="n">
-        <v>1836</v>
+        <v>2421</v>
       </c>
       <c r="E5" t="n">
-        <v>1769</v>
+        <v>2375</v>
       </c>
       <c r="F5" t="n">
-        <v>1754</v>
+        <v>2233.25</v>
       </c>
       <c r="G5" t="n">
-        <v>4598000</v>
+        <v>9416420</v>
       </c>
       <c r="H5" t="n">
-        <v>4534800</v>
+        <v>11929980</v>
       </c>
       <c r="I5" t="n">
-        <v>1980</v>
+        <v>2585</v>
       </c>
       <c r="J5" t="n">
-        <v>1510</v>
+        <v>1880</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -975,55 +975,55 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>578472</v>
+        <v>194639</v>
       </c>
       <c r="M5" t="n">
-        <v>277979</v>
+        <v>2255435</v>
       </c>
       <c r="N5" t="n">
-        <v>926668</v>
+        <v>2293842</v>
       </c>
       <c r="O5" t="n">
-        <v>-918565</v>
+        <v>11389340</v>
       </c>
       <c r="P5" t="n">
-        <v>582134</v>
+        <v>-154500</v>
       </c>
       <c r="Q5" t="n">
-        <v>196501</v>
+        <v>2416068</v>
       </c>
       <c r="R5" t="n">
-        <v>203504</v>
+        <v>1754285</v>
       </c>
       <c r="S5" t="n">
-        <v>-895725</v>
+        <v>10063933</v>
       </c>
       <c r="T5" t="n">
-        <v>-2300</v>
+        <v>221595</v>
       </c>
       <c r="U5" t="n">
-        <v>93941</v>
+        <v>-136590</v>
       </c>
       <c r="V5" t="n">
-        <v>697441</v>
+        <v>600797</v>
       </c>
       <c r="W5" t="n">
-        <v>-34936</v>
+        <v>1027540</v>
       </c>
       <c r="X5" t="n">
-        <v>-1362</v>
+        <v>127544</v>
       </c>
       <c r="Y5" t="n">
-        <v>-12463</v>
+        <v>-24043</v>
       </c>
       <c r="Z5" t="n">
-        <v>25723</v>
+        <v>-61240</v>
       </c>
       <c r="AA5" t="n">
-        <v>12096</v>
+        <v>297867</v>
       </c>
       <c r="AB5" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1047,44 +1047,44 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="D6" t="n">
-        <v>172.4</v>
+        <v>108.42</v>
       </c>
       <c r="E6" t="n">
-        <v>158.65</v>
+        <v>99.27</v>
       </c>
       <c r="F6" t="n">
-        <v>148.7</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>175481303</v>
+        <v>55044623</v>
       </c>
       <c r="H6" t="n">
-        <v>141634285</v>
+        <v>109395284</v>
       </c>
       <c r="I6" t="n">
-        <v>201</v>
+        <v>118.5</v>
       </c>
       <c r="J6" t="n">
-        <v>132</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1092,55 +1092,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6685241</v>
+        <v>3100650</v>
       </c>
       <c r="M6" t="n">
-        <v>142757914</v>
+        <v>21606388</v>
       </c>
       <c r="N6" t="n">
-        <v>166665867</v>
+        <v>100666368</v>
       </c>
       <c r="O6" t="n">
-        <v>246141728</v>
+        <v>145552222</v>
       </c>
       <c r="P6" t="n">
-        <v>-11394797</v>
+        <v>-763250</v>
       </c>
       <c r="Q6" t="n">
-        <v>105194498</v>
+        <v>14346438</v>
       </c>
       <c r="R6" t="n">
-        <v>124977567</v>
+        <v>87611840</v>
       </c>
       <c r="S6" t="n">
-        <v>199208731</v>
+        <v>130549204</v>
       </c>
       <c r="T6" t="n">
-        <v>18857358</v>
+        <v>3862966</v>
       </c>
       <c r="U6" t="n">
-        <v>37346358</v>
+        <v>9083724</v>
       </c>
       <c r="V6" t="n">
-        <v>38910926</v>
+        <v>12081181</v>
       </c>
       <c r="W6" t="n">
-        <v>40933642</v>
+        <v>12749614</v>
       </c>
       <c r="X6" t="n">
-        <v>-777320</v>
+        <v>934</v>
       </c>
       <c r="Y6" t="n">
-        <v>217058</v>
+        <v>-1823774</v>
       </c>
       <c r="Z6" t="n">
-        <v>2777374</v>
+        <v>973347</v>
       </c>
       <c r="AA6" t="n">
-        <v>5999355</v>
+        <v>2253404</v>
       </c>
       <c r="AB6" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1164,44 +1164,44 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3017.TW</t>
+          <t>5289.TWO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2855</v>
+        <v>1905</v>
       </c>
       <c r="D7" t="n">
-        <v>2717</v>
+        <v>1877</v>
       </c>
       <c r="E7" t="n">
-        <v>2662.5</v>
+        <v>1788.5</v>
       </c>
       <c r="F7" t="n">
-        <v>2564.75</v>
+        <v>1770.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6908395</v>
+        <v>2956000</v>
       </c>
       <c r="H7" t="n">
-        <v>6133567</v>
+        <v>4345000</v>
       </c>
       <c r="I7" t="n">
-        <v>2965</v>
+        <v>1980</v>
       </c>
       <c r="J7" t="n">
-        <v>2300</v>
+        <v>1510</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1209,55 +1209,55 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1698983</v>
+        <v>121339</v>
       </c>
       <c r="M7" t="n">
-        <v>2079941</v>
+        <v>726980</v>
       </c>
       <c r="N7" t="n">
-        <v>2186324</v>
+        <v>529253</v>
       </c>
       <c r="O7" t="n">
-        <v>1923369</v>
+        <v>-402387</v>
       </c>
       <c r="P7" t="n">
-        <v>1667080</v>
+        <v>143791</v>
       </c>
       <c r="Q7" t="n">
-        <v>2040599</v>
+        <v>696882</v>
       </c>
       <c r="R7" t="n">
-        <v>1813866</v>
+        <v>79760</v>
       </c>
       <c r="S7" t="n">
-        <v>876338</v>
+        <v>-520046</v>
       </c>
       <c r="T7" t="n">
-        <v>52632</v>
+        <v>-2000</v>
       </c>
       <c r="U7" t="n">
-        <v>1633</v>
+        <v>68941</v>
       </c>
       <c r="V7" t="n">
-        <v>365509</v>
+        <v>448441</v>
       </c>
       <c r="W7" t="n">
-        <v>1033454</v>
+        <v>128064</v>
       </c>
       <c r="X7" t="n">
-        <v>-20729</v>
+        <v>-20452</v>
       </c>
       <c r="Y7" t="n">
-        <v>37709</v>
+        <v>-38843</v>
       </c>
       <c r="Z7" t="n">
-        <v>6949</v>
+        <v>1052</v>
       </c>
       <c r="AA7" t="n">
-        <v>13577</v>
+        <v>-10405</v>
       </c>
       <c r="AB7" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1281,44 +1281,44 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00878.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33.3</v>
+        <v>37.9</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71</v>
+        <v>37.32</v>
       </c>
       <c r="E8" t="n">
-        <v>30.42</v>
+        <v>36.29</v>
       </c>
       <c r="F8" t="n">
-        <v>29.1</v>
+        <v>35.58</v>
       </c>
       <c r="G8" t="n">
-        <v>103127309</v>
+        <v>59159507</v>
       </c>
       <c r="H8" t="n">
-        <v>96210350</v>
+        <v>86107568</v>
       </c>
       <c r="I8" t="n">
-        <v>33.4</v>
+        <v>38.45</v>
       </c>
       <c r="J8" t="n">
-        <v>26.9</v>
+        <v>34.1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1326,55 +1326,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>32380516</v>
+        <v>10954915</v>
       </c>
       <c r="M8" t="n">
-        <v>128086522</v>
+        <v>7970568</v>
       </c>
       <c r="N8" t="n">
-        <v>193772291</v>
+        <v>37974395</v>
       </c>
       <c r="O8" t="n">
-        <v>445121961</v>
+        <v>18913283</v>
       </c>
       <c r="P8" t="n">
-        <v>4199891</v>
+        <v>-17770471</v>
       </c>
       <c r="Q8" t="n">
-        <v>43691727</v>
+        <v>-94778686</v>
       </c>
       <c r="R8" t="n">
-        <v>62472361</v>
+        <v>-139686667</v>
       </c>
       <c r="S8" t="n">
-        <v>270653888</v>
+        <v>-240911850</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>28363820</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>102564207</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>176433450</v>
       </c>
       <c r="W8" t="n">
-        <v>2500000</v>
+        <v>256429682</v>
       </c>
       <c r="X8" t="n">
-        <v>28180625</v>
+        <v>361566</v>
       </c>
       <c r="Y8" t="n">
-        <v>84394795</v>
+        <v>185047</v>
       </c>
       <c r="Z8" t="n">
-        <v>131299930</v>
+        <v>1227612</v>
       </c>
       <c r="AA8" t="n">
-        <v>171968073</v>
+        <v>3395451</v>
       </c>
       <c r="AB8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1388,54 +1388,54 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>2027.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5600</v>
+        <v>44.1</v>
       </c>
       <c r="D9" t="n">
-        <v>5397</v>
+        <v>42.5</v>
       </c>
       <c r="E9" t="n">
-        <v>5382</v>
+        <v>39.8</v>
       </c>
       <c r="F9" t="n">
-        <v>5302.5</v>
+        <v>38.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1716435</v>
+        <v>26108921</v>
       </c>
       <c r="H9" t="n">
-        <v>2272550</v>
+        <v>28691980</v>
       </c>
       <c r="I9" t="n">
-        <v>5880</v>
+        <v>44.35</v>
       </c>
       <c r="J9" t="n">
-        <v>4775</v>
+        <v>35.9</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>72503</v>
+        <v>4073432</v>
       </c>
       <c r="M9" t="n">
-        <v>159084</v>
+        <v>12203495</v>
       </c>
       <c r="N9" t="n">
-        <v>869206</v>
+        <v>23066852</v>
       </c>
       <c r="O9" t="n">
-        <v>517567</v>
+        <v>41362268</v>
       </c>
       <c r="P9" t="n">
-        <v>91027</v>
+        <v>13480013</v>
       </c>
       <c r="Q9" t="n">
-        <v>158524</v>
+        <v>34965154</v>
       </c>
       <c r="R9" t="n">
-        <v>975425</v>
+        <v>38416641</v>
       </c>
       <c r="S9" t="n">
-        <v>749655</v>
+        <v>59545235</v>
       </c>
       <c r="T9" t="n">
-        <v>-35022</v>
+        <v>-8937000</v>
       </c>
       <c r="U9" t="n">
-        <v>50980</v>
+        <v>-23079000</v>
       </c>
       <c r="V9" t="n">
-        <v>34954</v>
+        <v>-17360000</v>
       </c>
       <c r="W9" t="n">
-        <v>-119202</v>
+        <v>-18922000</v>
       </c>
       <c r="X9" t="n">
-        <v>16498</v>
+        <v>-469581</v>
       </c>
       <c r="Y9" t="n">
-        <v>-50420</v>
+        <v>317341</v>
       </c>
       <c r="Z9" t="n">
-        <v>-141173</v>
+        <v>2010211</v>
       </c>
       <c r="AA9" t="n">
-        <v>-112886</v>
+        <v>739033</v>
       </c>
       <c r="AB9" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1505,54 +1505,54 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32.6</v>
+        <v>52.65</v>
       </c>
       <c r="D10" t="n">
-        <v>30.91</v>
+        <v>52.27</v>
       </c>
       <c r="E10" t="n">
-        <v>30.01</v>
+        <v>50.28</v>
       </c>
       <c r="F10" t="n">
-        <v>28.69</v>
+        <v>47.59</v>
       </c>
       <c r="G10" t="n">
-        <v>8734341</v>
+        <v>66916789</v>
       </c>
       <c r="H10" t="n">
-        <v>8956445</v>
+        <v>60369324</v>
       </c>
       <c r="I10" t="n">
-        <v>33.4</v>
+        <v>53.8</v>
       </c>
       <c r="J10" t="n">
-        <v>26.3</v>
+        <v>43.66</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1560,55 +1560,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1019391</v>
+        <v>-4626731</v>
       </c>
       <c r="M10" t="n">
-        <v>4694639</v>
+        <v>26398137</v>
       </c>
       <c r="N10" t="n">
-        <v>4310455</v>
+        <v>74649917</v>
       </c>
       <c r="O10" t="n">
-        <v>6594526</v>
+        <v>181083870</v>
       </c>
       <c r="P10" t="n">
-        <v>958346</v>
+        <v>-8393964</v>
       </c>
       <c r="Q10" t="n">
-        <v>4432421</v>
+        <v>15577681</v>
       </c>
       <c r="R10" t="n">
-        <v>4036864</v>
+        <v>42876262</v>
       </c>
       <c r="S10" t="n">
-        <v>6298172</v>
+        <v>99568546</v>
       </c>
       <c r="T10" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>178000</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>186000</v>
+        <v>230000</v>
       </c>
       <c r="W10" t="n">
-        <v>203000</v>
+        <v>2090000</v>
       </c>
       <c r="X10" t="n">
-        <v>48045</v>
+        <v>3767233</v>
       </c>
       <c r="Y10" t="n">
-        <v>84218</v>
+        <v>10820456</v>
       </c>
       <c r="Z10" t="n">
-        <v>87591</v>
+        <v>31543655</v>
       </c>
       <c r="AA10" t="n">
-        <v>93354</v>
+        <v>79425324</v>
       </c>
       <c r="AB10" t="n">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -1622,54 +1622,54 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>1185</v>
       </c>
       <c r="D11" t="n">
-        <v>104.32</v>
+        <v>1168</v>
       </c>
       <c r="E11" t="n">
-        <v>96.90000000000001</v>
+        <v>1094</v>
       </c>
       <c r="F11" t="n">
-        <v>91.61</v>
+        <v>1054.85</v>
       </c>
       <c r="G11" t="n">
-        <v>77820950</v>
+        <v>7021000</v>
       </c>
       <c r="H11" t="n">
-        <v>116059088</v>
+        <v>6500600</v>
       </c>
       <c r="I11" t="n">
-        <v>118.5</v>
+        <v>1295</v>
       </c>
       <c r="J11" t="n">
-        <v>80.40000000000001</v>
+        <v>936</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1677,55 +1677,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1088601</v>
+        <v>-584892</v>
       </c>
       <c r="M11" t="n">
-        <v>33751450</v>
+        <v>4361229</v>
       </c>
       <c r="N11" t="n">
-        <v>71709822</v>
+        <v>6217836</v>
       </c>
       <c r="O11" t="n">
-        <v>140552744</v>
+        <v>4664601</v>
       </c>
       <c r="P11" t="n">
-        <v>-1466154</v>
+        <v>-448913</v>
       </c>
       <c r="Q11" t="n">
-        <v>29055431</v>
+        <v>4409455</v>
       </c>
       <c r="R11" t="n">
-        <v>63351386</v>
+        <v>5928626</v>
       </c>
       <c r="S11" t="n">
-        <v>130155973</v>
+        <v>4454403</v>
       </c>
       <c r="T11" t="n">
-        <v>3087362</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>5916758</v>
+        <v>1900</v>
       </c>
       <c r="V11" t="n">
-        <v>8581215</v>
+        <v>3900</v>
       </c>
       <c r="W11" t="n">
-        <v>10347648</v>
+        <v>-5567</v>
       </c>
       <c r="X11" t="n">
-        <v>-532607</v>
+        <v>-135979</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1220739</v>
+        <v>-50126</v>
       </c>
       <c r="Z11" t="n">
-        <v>-222779</v>
+        <v>285310</v>
       </c>
       <c r="AA11" t="n">
-        <v>49123</v>
+        <v>215765</v>
       </c>
       <c r="AB11" t="n">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -1739,54 +1739,54 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>176.5</v>
+        <v>20.45</v>
       </c>
       <c r="D12" t="n">
-        <v>173.8</v>
+        <v>19.94</v>
       </c>
       <c r="E12" t="n">
-        <v>173.5</v>
+        <v>16.82</v>
       </c>
       <c r="F12" t="n">
-        <v>172.95</v>
+        <v>13.54</v>
       </c>
       <c r="G12" t="n">
-        <v>296837</v>
+        <v>43646780</v>
       </c>
       <c r="H12" t="n">
-        <v>260571</v>
+        <v>140134518</v>
       </c>
       <c r="I12" t="n">
-        <v>176.5</v>
+        <v>22.7</v>
       </c>
       <c r="J12" t="n">
-        <v>169</v>
+        <v>9.02</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1794,28 +1794,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>74290</v>
+        <v>1053379</v>
       </c>
       <c r="M12" t="n">
-        <v>322290</v>
+        <v>11732670</v>
       </c>
       <c r="N12" t="n">
-        <v>292269</v>
+        <v>14189705</v>
       </c>
       <c r="O12" t="n">
-        <v>271146</v>
+        <v>-8342340</v>
       </c>
       <c r="P12" t="n">
-        <v>63290</v>
+        <v>947879</v>
       </c>
       <c r="Q12" t="n">
-        <v>311290</v>
+        <v>11389238</v>
       </c>
       <c r="R12" t="n">
-        <v>283315</v>
+        <v>11900414</v>
       </c>
       <c r="S12" t="n">
-        <v>260400</v>
+        <v>-11609915</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1830,19 +1830,19 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>11000</v>
+        <v>105500</v>
       </c>
       <c r="Y12" t="n">
-        <v>11000</v>
+        <v>343432</v>
       </c>
       <c r="Z12" t="n">
-        <v>8954</v>
+        <v>2289291</v>
       </c>
       <c r="AA12" t="n">
-        <v>10746</v>
+        <v>3267575</v>
       </c>
       <c r="AB12" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -1856,54 +1856,54 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、突破20日高點、接近20日低點、法人連續偏買、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2027.TW</t>
+          <t>00878.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43.85</v>
+        <v>32.68</v>
       </c>
       <c r="D13" t="n">
-        <v>42.82</v>
+        <v>32.24</v>
       </c>
       <c r="E13" t="n">
-        <v>42.6</v>
+        <v>30.91</v>
       </c>
       <c r="F13" t="n">
-        <v>41.13</v>
+        <v>29.34</v>
       </c>
       <c r="G13" t="n">
-        <v>35447430</v>
+        <v>78525133</v>
       </c>
       <c r="H13" t="n">
-        <v>26728337</v>
+        <v>93740035</v>
       </c>
       <c r="I13" t="n">
-        <v>44.75</v>
+        <v>33.4</v>
       </c>
       <c r="J13" t="n">
-        <v>37.6</v>
+        <v>26.9</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1911,55 +1911,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5737228</v>
+        <v>178741</v>
       </c>
       <c r="M13" t="n">
-        <v>17655905</v>
+        <v>83548386</v>
       </c>
       <c r="N13" t="n">
-        <v>20415937</v>
+        <v>174309398</v>
       </c>
       <c r="O13" t="n">
-        <v>60680061</v>
+        <v>444185941</v>
       </c>
       <c r="P13" t="n">
-        <v>13673850</v>
+        <v>-9230252</v>
       </c>
       <c r="Q13" t="n">
-        <v>23718444</v>
+        <v>12390466</v>
       </c>
       <c r="R13" t="n">
-        <v>28425764</v>
+        <v>55443639</v>
       </c>
       <c r="S13" t="n">
-        <v>68397503</v>
+        <v>233144669</v>
       </c>
       <c r="T13" t="n">
-        <v>-8447000</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-8418000</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-8423000</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-9799000</v>
+        <v>2500000</v>
       </c>
       <c r="X13" t="n">
-        <v>510378</v>
+        <v>9408993</v>
       </c>
       <c r="Y13" t="n">
-        <v>2355461</v>
+        <v>71157920</v>
       </c>
       <c r="Z13" t="n">
-        <v>413173</v>
+        <v>118865759</v>
       </c>
       <c r="AA13" t="n">
-        <v>2081558</v>
+        <v>208541272</v>
       </c>
       <c r="AB13" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
@@ -1999,22 +1999,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="D14" t="n">
-        <v>367.5</v>
+        <v>386.6</v>
       </c>
       <c r="E14" t="n">
-        <v>340.65</v>
+        <v>350.25</v>
       </c>
       <c r="F14" t="n">
-        <v>331.77</v>
+        <v>334.77</v>
       </c>
       <c r="G14" t="n">
-        <v>111020362</v>
+        <v>73706806</v>
       </c>
       <c r="H14" t="n">
-        <v>94064841</v>
+        <v>100164107</v>
       </c>
       <c r="I14" t="n">
         <v>438</v>
@@ -2028,55 +2028,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8317826</v>
+        <v>1107695</v>
       </c>
       <c r="M14" t="n">
-        <v>35086163</v>
+        <v>31319488</v>
       </c>
       <c r="N14" t="n">
-        <v>48478956</v>
+        <v>54620501</v>
       </c>
       <c r="O14" t="n">
-        <v>49254361</v>
+        <v>36755497</v>
       </c>
       <c r="P14" t="n">
-        <v>-24200224</v>
+        <v>-32713378</v>
       </c>
       <c r="Q14" t="n">
-        <v>-41395597</v>
+        <v>-71495848</v>
       </c>
       <c r="R14" t="n">
-        <v>-57222826</v>
+        <v>-72251683</v>
       </c>
       <c r="S14" t="n">
-        <v>-100755558</v>
+        <v>-150769070</v>
       </c>
       <c r="T14" t="n">
-        <v>33418611</v>
+        <v>33871446</v>
       </c>
       <c r="U14" t="n">
-        <v>77887836</v>
+        <v>104478282</v>
       </c>
       <c r="V14" t="n">
-        <v>105930188</v>
+        <v>127189282</v>
       </c>
       <c r="W14" t="n">
-        <v>150386305</v>
+        <v>187566593</v>
       </c>
       <c r="X14" t="n">
-        <v>-900561</v>
+        <v>-50373</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1406076</v>
+        <v>-1662946</v>
       </c>
       <c r="Z14" t="n">
-        <v>-228406</v>
+        <v>-317098</v>
       </c>
       <c r="AA14" t="n">
-        <v>-376386</v>
+        <v>-42026</v>
       </c>
       <c r="AB14" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2100,44 +2100,44 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>237</v>
+        <v>5570</v>
       </c>
       <c r="D15" t="n">
-        <v>223.2</v>
+        <v>5521</v>
       </c>
       <c r="E15" t="n">
-        <v>218.4</v>
+        <v>5404.5</v>
       </c>
       <c r="F15" t="n">
-        <v>213.3</v>
+        <v>5337</v>
       </c>
       <c r="G15" t="n">
-        <v>38862223</v>
+        <v>1704775</v>
       </c>
       <c r="H15" t="n">
-        <v>34252377</v>
+        <v>2181939</v>
       </c>
       <c r="I15" t="n">
-        <v>242.5</v>
+        <v>5880</v>
       </c>
       <c r="J15" t="n">
-        <v>195.5</v>
+        <v>4775</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2145,55 +2145,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6531031</v>
+        <v>-146407</v>
       </c>
       <c r="M15" t="n">
-        <v>30432685</v>
+        <v>65899</v>
       </c>
       <c r="N15" t="n">
-        <v>36181851</v>
+        <v>829560</v>
       </c>
       <c r="O15" t="n">
-        <v>51959237</v>
+        <v>295298</v>
       </c>
       <c r="P15" t="n">
-        <v>-6268756</v>
+        <v>-192489</v>
       </c>
       <c r="Q15" t="n">
-        <v>-11965833</v>
+        <v>99856</v>
       </c>
       <c r="R15" t="n">
-        <v>-30529481</v>
+        <v>591901</v>
       </c>
       <c r="S15" t="n">
-        <v>-35322746</v>
+        <v>891422</v>
       </c>
       <c r="T15" t="n">
-        <v>12281589</v>
+        <v>35968</v>
       </c>
       <c r="U15" t="n">
-        <v>40030315</v>
+        <v>3946</v>
       </c>
       <c r="V15" t="n">
-        <v>63351875</v>
+        <v>262909</v>
       </c>
       <c r="W15" t="n">
-        <v>82210158</v>
+        <v>-362407</v>
       </c>
       <c r="X15" t="n">
-        <v>518198</v>
+        <v>10114</v>
       </c>
       <c r="Y15" t="n">
-        <v>2368203</v>
+        <v>-37903</v>
       </c>
       <c r="Z15" t="n">
-        <v>3359457</v>
+        <v>-25250</v>
       </c>
       <c r="AA15" t="n">
-        <v>5071825</v>
+        <v>-233717</v>
       </c>
       <c r="AB15" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -2207,54 +2207,54 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2425</v>
+        <v>1695</v>
       </c>
       <c r="D16" t="n">
-        <v>2362</v>
+        <v>1675</v>
       </c>
       <c r="E16" t="n">
-        <v>2317.5</v>
+        <v>1618</v>
       </c>
       <c r="F16" t="n">
-        <v>2282.5</v>
+        <v>1483.75</v>
       </c>
       <c r="G16" t="n">
-        <v>29219904</v>
+        <v>3450000</v>
       </c>
       <c r="H16" t="n">
-        <v>55758466</v>
+        <v>7393200</v>
       </c>
       <c r="I16" t="n">
-        <v>2440</v>
+        <v>1815</v>
       </c>
       <c r="J16" t="n">
-        <v>2185</v>
+        <v>1190</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2262,55 +2262,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>771034</v>
+        <v>-143834</v>
       </c>
       <c r="M16" t="n">
-        <v>-375278</v>
+        <v>1087573</v>
       </c>
       <c r="N16" t="n">
-        <v>7531281</v>
+        <v>2493856</v>
       </c>
       <c r="O16" t="n">
-        <v>26591070</v>
+        <v>3586319</v>
       </c>
       <c r="P16" t="n">
-        <v>-103827</v>
+        <v>-221230</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3024196</v>
+        <v>539310</v>
       </c>
       <c r="R16" t="n">
-        <v>3181461</v>
+        <v>70871</v>
       </c>
       <c r="S16" t="n">
-        <v>17052312</v>
+        <v>-1354727</v>
       </c>
       <c r="T16" t="n">
-        <v>647975</v>
+        <v>208000</v>
       </c>
       <c r="U16" t="n">
-        <v>1038293</v>
+        <v>1282850</v>
       </c>
       <c r="V16" t="n">
-        <v>1852603</v>
+        <v>3227850</v>
       </c>
       <c r="W16" t="n">
-        <v>6149335</v>
+        <v>6316550</v>
       </c>
       <c r="X16" t="n">
-        <v>226886</v>
+        <v>-130604</v>
       </c>
       <c r="Y16" t="n">
-        <v>1610625</v>
+        <v>-734587</v>
       </c>
       <c r="Z16" t="n">
-        <v>2497217</v>
+        <v>-804865</v>
       </c>
       <c r="AA16" t="n">
-        <v>3389423</v>
+        <v>-1375504</v>
       </c>
       <c r="AB16" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2334,44 +2334,44 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>399</v>
+        <v>55.8</v>
       </c>
       <c r="D17" t="n">
-        <v>376.8</v>
+        <v>55.7</v>
       </c>
       <c r="E17" t="n">
-        <v>352.8</v>
+        <v>51.46</v>
       </c>
       <c r="F17" t="n">
-        <v>335.2</v>
+        <v>43.72</v>
       </c>
       <c r="G17" t="n">
-        <v>23444363</v>
+        <v>170430089</v>
       </c>
       <c r="H17" t="n">
-        <v>27716252</v>
+        <v>736347046</v>
       </c>
       <c r="I17" t="n">
-        <v>402</v>
+        <v>60.5</v>
       </c>
       <c r="J17" t="n">
-        <v>300</v>
+        <v>28.65</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2379,55 +2379,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-683516</v>
+        <v>-10007082</v>
       </c>
       <c r="M17" t="n">
-        <v>2322720</v>
+        <v>-125477504</v>
       </c>
       <c r="N17" t="n">
-        <v>12308501</v>
+        <v>125381285</v>
       </c>
       <c r="O17" t="n">
-        <v>13980353</v>
+        <v>-360084035</v>
       </c>
       <c r="P17" t="n">
-        <v>-1412433</v>
+        <v>-7769798</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6289843</v>
+        <v>-168233992</v>
       </c>
       <c r="R17" t="n">
-        <v>25828</v>
+        <v>75718764</v>
       </c>
       <c r="S17" t="n">
-        <v>1037823</v>
+        <v>-376977939</v>
       </c>
       <c r="T17" t="n">
-        <v>921000</v>
+        <v>196000</v>
       </c>
       <c r="U17" t="n">
-        <v>8344000</v>
+        <v>54826000</v>
       </c>
       <c r="V17" t="n">
-        <v>11253181</v>
+        <v>59933444</v>
       </c>
       <c r="W17" t="n">
-        <v>11517102</v>
+        <v>51770636</v>
       </c>
       <c r="X17" t="n">
-        <v>-192083</v>
+        <v>-2433284</v>
       </c>
       <c r="Y17" t="n">
-        <v>268563</v>
+        <v>-12069512</v>
       </c>
       <c r="Z17" t="n">
-        <v>1029492</v>
+        <v>-10270923</v>
       </c>
       <c r="AA17" t="n">
-        <v>1425428</v>
+        <v>-34876732</v>
       </c>
       <c r="AB17" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2451,44 +2451,44 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30.95</v>
+        <v>395</v>
       </c>
       <c r="D18" t="n">
-        <v>30.71</v>
+        <v>388.9</v>
       </c>
       <c r="E18" t="n">
-        <v>30.18</v>
+        <v>349.05</v>
       </c>
       <c r="F18" t="n">
-        <v>28.91</v>
+        <v>325.38</v>
       </c>
       <c r="G18" t="n">
-        <v>9645717</v>
+        <v>115749814</v>
       </c>
       <c r="H18" t="n">
-        <v>12831097</v>
+        <v>141706746</v>
       </c>
       <c r="I18" t="n">
-        <v>31.95</v>
+        <v>430.5</v>
       </c>
       <c r="J18" t="n">
-        <v>26.2</v>
+        <v>260</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2496,55 +2496,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>252712</v>
+        <v>-13700277</v>
       </c>
       <c r="M18" t="n">
-        <v>2282797</v>
+        <v>-4195101</v>
       </c>
       <c r="N18" t="n">
-        <v>7865246</v>
+        <v>50006249</v>
       </c>
       <c r="O18" t="n">
-        <v>17467691</v>
+        <v>108634938</v>
       </c>
       <c r="P18" t="n">
-        <v>429024</v>
+        <v>-11907678</v>
       </c>
       <c r="Q18" t="n">
-        <v>2422319</v>
+        <v>-7988585</v>
       </c>
       <c r="R18" t="n">
-        <v>7568377</v>
+        <v>38511284</v>
       </c>
       <c r="S18" t="n">
-        <v>16576745</v>
+        <v>112144923</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-270236</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>6060528</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>13033529</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-1198031</v>
       </c>
       <c r="X18" t="n">
-        <v>-176312</v>
+        <v>-1522363</v>
       </c>
       <c r="Y18" t="n">
-        <v>-139522</v>
+        <v>-2267044</v>
       </c>
       <c r="Z18" t="n">
-        <v>296869</v>
+        <v>-1538564</v>
       </c>
       <c r="AA18" t="n">
-        <v>890946</v>
+        <v>-2311954</v>
       </c>
       <c r="AB18" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2563,49 +2563,49 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1695</v>
+        <v>179.5</v>
       </c>
       <c r="D19" t="n">
-        <v>1644</v>
+        <v>173.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1581</v>
+        <v>156.1</v>
       </c>
       <c r="F19" t="n">
-        <v>1471.25</v>
+        <v>138.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6905000</v>
+        <v>227016133</v>
       </c>
       <c r="H19" t="n">
-        <v>8434000</v>
+        <v>274934897</v>
       </c>
       <c r="I19" t="n">
-        <v>1815</v>
+        <v>193</v>
       </c>
       <c r="J19" t="n">
-        <v>1190</v>
+        <v>103.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2613,55 +2613,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>960021</v>
+        <v>-8347722</v>
       </c>
       <c r="M19" t="n">
-        <v>1610884</v>
+        <v>-34604736</v>
       </c>
       <c r="N19" t="n">
-        <v>2874034</v>
+        <v>37378660</v>
       </c>
       <c r="O19" t="n">
-        <v>3955152</v>
+        <v>198879253</v>
       </c>
       <c r="P19" t="n">
-        <v>708546</v>
+        <v>-9552020</v>
       </c>
       <c r="Q19" t="n">
-        <v>211692</v>
+        <v>-46157682</v>
       </c>
       <c r="R19" t="n">
-        <v>-498730</v>
+        <v>657745</v>
       </c>
       <c r="S19" t="n">
-        <v>-868530</v>
+        <v>134104578</v>
       </c>
       <c r="T19" t="n">
-        <v>419850</v>
+        <v>1104346</v>
       </c>
       <c r="U19" t="n">
-        <v>2042850</v>
+        <v>15877129</v>
       </c>
       <c r="V19" t="n">
-        <v>4232850</v>
+        <v>39082276</v>
       </c>
       <c r="W19" t="n">
-        <v>6061550</v>
+        <v>63033629</v>
       </c>
       <c r="X19" t="n">
-        <v>-168375</v>
+        <v>99952</v>
       </c>
       <c r="Y19" t="n">
-        <v>-643658</v>
+        <v>-4324183</v>
       </c>
       <c r="Z19" t="n">
-        <v>-860086</v>
+        <v>-2361361</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1237868</v>
+        <v>1741046</v>
       </c>
       <c r="AB19" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -2680,49 +2680,49 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2455</v>
+        <v>2385</v>
       </c>
       <c r="D20" t="n">
-        <v>2414</v>
+        <v>2380</v>
       </c>
       <c r="E20" t="n">
-        <v>2335.5</v>
+        <v>2333</v>
       </c>
       <c r="F20" t="n">
-        <v>2226</v>
+        <v>2286.25</v>
       </c>
       <c r="G20" t="n">
-        <v>10882344</v>
+        <v>32542948</v>
       </c>
       <c r="H20" t="n">
-        <v>12390908</v>
+        <v>53804400</v>
       </c>
       <c r="I20" t="n">
-        <v>2585</v>
+        <v>2440</v>
       </c>
       <c r="J20" t="n">
-        <v>1880</v>
+        <v>2185</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2730,55 +2730,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2704114</v>
+        <v>-9619150</v>
       </c>
       <c r="M20" t="n">
-        <v>1291271</v>
+        <v>-8062980</v>
       </c>
       <c r="N20" t="n">
-        <v>86319</v>
+        <v>4059234</v>
       </c>
       <c r="O20" t="n">
-        <v>9168995</v>
+        <v>7574798</v>
       </c>
       <c r="P20" t="n">
-        <v>2633111</v>
+        <v>-11256052</v>
       </c>
       <c r="Q20" t="n">
-        <v>1749226</v>
+        <v>-10968585</v>
       </c>
       <c r="R20" t="n">
-        <v>166241</v>
+        <v>-995976</v>
       </c>
       <c r="S20" t="n">
-        <v>7745280</v>
+        <v>-2233663</v>
       </c>
       <c r="T20" t="n">
-        <v>41815</v>
+        <v>537838</v>
       </c>
       <c r="U20" t="n">
-        <v>-225185</v>
+        <v>1117916</v>
       </c>
       <c r="V20" t="n">
-        <v>258013</v>
+        <v>1925380</v>
       </c>
       <c r="W20" t="n">
-        <v>391754</v>
+        <v>5458036</v>
       </c>
       <c r="X20" t="n">
-        <v>29188</v>
+        <v>1099064</v>
       </c>
       <c r="Y20" t="n">
-        <v>-232770</v>
+        <v>1787689</v>
       </c>
       <c r="Z20" t="n">
-        <v>-337935</v>
+        <v>3129830</v>
       </c>
       <c r="AA20" t="n">
-        <v>1031961</v>
+        <v>4350425</v>
       </c>
       <c r="AB20" t="n">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -2797,49 +2797,49 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人小幅買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>739</v>
+        <v>236</v>
       </c>
       <c r="D21" t="n">
-        <v>733.2</v>
+        <v>228.2</v>
       </c>
       <c r="E21" t="n">
-        <v>689.6</v>
+        <v>220.8</v>
       </c>
       <c r="F21" t="n">
-        <v>593.55</v>
+        <v>214.43</v>
       </c>
       <c r="G21" t="n">
-        <v>4661433</v>
+        <v>27370783</v>
       </c>
       <c r="H21" t="n">
-        <v>6635594</v>
+        <v>34173958</v>
       </c>
       <c r="I21" t="n">
-        <v>778</v>
+        <v>242.5</v>
       </c>
       <c r="J21" t="n">
-        <v>445.5</v>
+        <v>195.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2847,55 +2847,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>213520</v>
+        <v>-471223</v>
       </c>
       <c r="M21" t="n">
-        <v>974021</v>
+        <v>14011723</v>
       </c>
       <c r="N21" t="n">
-        <v>2741828</v>
+        <v>34461134</v>
       </c>
       <c r="O21" t="n">
-        <v>19235025</v>
+        <v>47203515</v>
       </c>
       <c r="P21" t="n">
-        <v>1265234</v>
+        <v>-10045382</v>
       </c>
       <c r="Q21" t="n">
-        <v>2359664</v>
+        <v>-24170514</v>
       </c>
       <c r="R21" t="n">
-        <v>4016420</v>
+        <v>-29925598</v>
       </c>
       <c r="S21" t="n">
-        <v>15586113</v>
+        <v>-56425790</v>
       </c>
       <c r="T21" t="n">
-        <v>-905744</v>
+        <v>9564830</v>
       </c>
       <c r="U21" t="n">
-        <v>-902458</v>
+        <v>36751360</v>
       </c>
       <c r="V21" t="n">
-        <v>-901077</v>
+        <v>61596606</v>
       </c>
       <c r="W21" t="n">
-        <v>3488114</v>
+        <v>98320113</v>
       </c>
       <c r="X21" t="n">
-        <v>-145970</v>
+        <v>9329</v>
       </c>
       <c r="Y21" t="n">
-        <v>-483185</v>
+        <v>1430877</v>
       </c>
       <c r="Z21" t="n">
-        <v>-373515</v>
+        <v>2790126</v>
       </c>
       <c r="AA21" t="n">
-        <v>160798</v>
+        <v>5309192</v>
       </c>
       <c r="AB21" t="n">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -2914,49 +2914,49 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.7</v>
+        <v>47.7</v>
       </c>
       <c r="D22" t="n">
-        <v>18.96</v>
+        <v>47.68</v>
       </c>
       <c r="E22" t="n">
-        <v>15.86</v>
+        <v>46.39</v>
       </c>
       <c r="F22" t="n">
-        <v>12.99</v>
+        <v>44.75</v>
       </c>
       <c r="G22" t="n">
-        <v>108791284</v>
+        <v>17241937</v>
       </c>
       <c r="H22" t="n">
-        <v>196689733</v>
+        <v>22873613</v>
       </c>
       <c r="I22" t="n">
-        <v>22.7</v>
+        <v>52.4</v>
       </c>
       <c r="J22" t="n">
-        <v>8.51</v>
+        <v>38.65</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2964,55 +2964,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-3871814</v>
+        <v>-3099285</v>
       </c>
       <c r="M22" t="n">
-        <v>7852031</v>
+        <v>1996892</v>
       </c>
       <c r="N22" t="n">
-        <v>19727873</v>
+        <v>5413631</v>
       </c>
       <c r="O22" t="n">
-        <v>60872125</v>
+        <v>8479906</v>
       </c>
       <c r="P22" t="n">
-        <v>-3529814</v>
+        <v>-2284866</v>
       </c>
       <c r="Q22" t="n">
-        <v>6586399</v>
+        <v>991614</v>
       </c>
       <c r="R22" t="n">
-        <v>17198766</v>
+        <v>4006189</v>
       </c>
       <c r="S22" t="n">
-        <v>53552870</v>
+        <v>7357334</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="X22" t="n">
-        <v>-342000</v>
+        <v>-813419</v>
       </c>
       <c r="Y22" t="n">
-        <v>1265632</v>
+        <v>1012278</v>
       </c>
       <c r="Z22" t="n">
-        <v>2529107</v>
+        <v>1414442</v>
       </c>
       <c r="AA22" t="n">
-        <v>7319255</v>
+        <v>1137572</v>
       </c>
       <c r="AB22" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -3026,54 +3026,54 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>401.5</v>
+        <v>293</v>
       </c>
       <c r="D23" t="n">
-        <v>374.7</v>
+        <v>297.2</v>
       </c>
       <c r="E23" t="n">
-        <v>338.85</v>
+        <v>278.3</v>
       </c>
       <c r="F23" t="n">
-        <v>319.98</v>
+        <v>263</v>
       </c>
       <c r="G23" t="n">
-        <v>151116427</v>
+        <v>110760779</v>
       </c>
       <c r="H23" t="n">
-        <v>163899843</v>
+        <v>173747207</v>
       </c>
       <c r="I23" t="n">
-        <v>430.5</v>
+        <v>314</v>
       </c>
       <c r="J23" t="n">
-        <v>260</v>
+        <v>239.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3081,69 +3081,69 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-14285203</v>
+        <v>-29600515</v>
       </c>
       <c r="M23" t="n">
-        <v>39219946</v>
+        <v>29764089</v>
       </c>
       <c r="N23" t="n">
-        <v>127211319</v>
+        <v>117000157</v>
       </c>
       <c r="O23" t="n">
-        <v>117278183</v>
+        <v>235126277</v>
       </c>
       <c r="P23" t="n">
-        <v>-14402588</v>
+        <v>-28177601</v>
       </c>
       <c r="Q23" t="n">
-        <v>30935576</v>
+        <v>25344587</v>
       </c>
       <c r="R23" t="n">
-        <v>112585936</v>
+        <v>99108421</v>
       </c>
       <c r="S23" t="n">
-        <v>115503118</v>
+        <v>213737043</v>
       </c>
       <c r="T23" t="n">
-        <v>964764</v>
+        <v>856441</v>
       </c>
       <c r="U23" t="n">
-        <v>8508765</v>
+        <v>5699881</v>
       </c>
       <c r="V23" t="n">
-        <v>14113095</v>
+        <v>14930881</v>
       </c>
       <c r="W23" t="n">
-        <v>1875930</v>
+        <v>16076443</v>
       </c>
       <c r="X23" t="n">
-        <v>-847379</v>
+        <v>-2279355</v>
       </c>
       <c r="Y23" t="n">
-        <v>-224395</v>
+        <v>-1280379</v>
       </c>
       <c r="Z23" t="n">
-        <v>512288</v>
+        <v>2960855</v>
       </c>
       <c r="AA23" t="n">
-        <v>-100865</v>
+        <v>5312791</v>
       </c>
       <c r="AB23" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3153,44 +3153,44 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37.7</v>
+        <v>29.25</v>
       </c>
       <c r="D24" t="n">
-        <v>36.8</v>
+        <v>26.19</v>
       </c>
       <c r="E24" t="n">
-        <v>36.02</v>
+        <v>24.25</v>
       </c>
       <c r="F24" t="n">
-        <v>35.46</v>
+        <v>21.8</v>
       </c>
       <c r="G24" t="n">
-        <v>81050445</v>
+        <v>878685417</v>
       </c>
       <c r="H24" t="n">
-        <v>91523678</v>
+        <v>670480454</v>
       </c>
       <c r="I24" t="n">
-        <v>38.45</v>
+        <v>29.6</v>
       </c>
       <c r="J24" t="n">
-        <v>34.1</v>
+        <v>17.75</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3198,116 +3198,116 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-5992154</v>
+        <v>-6210033</v>
       </c>
       <c r="M24" t="n">
-        <v>10561913</v>
+        <v>15490209</v>
       </c>
       <c r="N24" t="n">
-        <v>40378826</v>
+        <v>-27428980</v>
       </c>
       <c r="O24" t="n">
-        <v>29453033</v>
+        <v>-234846232</v>
       </c>
       <c r="P24" t="n">
-        <v>-38676291</v>
+        <v>-8471246</v>
       </c>
       <c r="Q24" t="n">
-        <v>-101446797</v>
+        <v>8214592</v>
       </c>
       <c r="R24" t="n">
-        <v>-137254634</v>
+        <v>-35798595</v>
       </c>
       <c r="S24" t="n">
-        <v>-197554213</v>
+        <v>-244976007</v>
       </c>
       <c r="T24" t="n">
-        <v>32622579</v>
+        <v>156000</v>
       </c>
       <c r="U24" t="n">
-        <v>111913285</v>
+        <v>152000</v>
       </c>
       <c r="V24" t="n">
-        <v>176358554</v>
+        <v>260000</v>
       </c>
       <c r="W24" t="n">
-        <v>225320632</v>
+        <v>441961</v>
       </c>
       <c r="X24" t="n">
-        <v>61558</v>
+        <v>2105213</v>
       </c>
       <c r="Y24" t="n">
-        <v>95425</v>
+        <v>7123617</v>
       </c>
       <c r="Z24" t="n">
-        <v>1274906</v>
+        <v>8109615</v>
       </c>
       <c r="AA24" t="n">
-        <v>1686614</v>
+        <v>9687814</v>
       </c>
       <c r="AB24" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、投信買外資賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>254</v>
+        <v>30.5</v>
       </c>
       <c r="D25" t="n">
-        <v>232.4</v>
+        <v>31.27</v>
       </c>
       <c r="E25" t="n">
-        <v>221.25</v>
+        <v>30.27</v>
       </c>
       <c r="F25" t="n">
-        <v>203.75</v>
+        <v>28.73</v>
       </c>
       <c r="G25" t="n">
-        <v>10842000</v>
+        <v>3843774</v>
       </c>
       <c r="H25" t="n">
-        <v>12038000</v>
+        <v>9025316</v>
       </c>
       <c r="I25" t="n">
-        <v>254</v>
+        <v>33.4</v>
       </c>
       <c r="J25" t="n">
-        <v>159.5</v>
+        <v>26.3</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3315,116 +3315,116 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-167885</v>
+        <v>-1177827</v>
       </c>
       <c r="M25" t="n">
-        <v>-1224953</v>
+        <v>-522042</v>
       </c>
       <c r="N25" t="n">
-        <v>359494</v>
+        <v>3235885</v>
       </c>
       <c r="O25" t="n">
-        <v>2868501</v>
+        <v>4188367</v>
       </c>
       <c r="P25" t="n">
-        <v>-259830</v>
+        <v>-1266904</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1275149</v>
+        <v>-762724</v>
       </c>
       <c r="R25" t="n">
-        <v>139916</v>
+        <v>2872460</v>
       </c>
       <c r="S25" t="n">
-        <v>2474189</v>
+        <v>3803234</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>263000</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>271000</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>265000</v>
       </c>
       <c r="X25" t="n">
-        <v>91945</v>
+        <v>4077</v>
       </c>
       <c r="Y25" t="n">
-        <v>50196</v>
+        <v>-22318</v>
       </c>
       <c r="Z25" t="n">
-        <v>219578</v>
+        <v>92425</v>
       </c>
       <c r="AA25" t="n">
-        <v>394312</v>
+        <v>120133</v>
       </c>
       <c r="AB25" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>49.95</v>
+        <v>260.5</v>
       </c>
       <c r="D26" t="n">
-        <v>46.92</v>
+        <v>273.4</v>
       </c>
       <c r="E26" t="n">
-        <v>46.16</v>
+        <v>270.8</v>
       </c>
       <c r="F26" t="n">
-        <v>44.39</v>
+        <v>267.23</v>
       </c>
       <c r="G26" t="n">
-        <v>39697448</v>
+        <v>7187932</v>
       </c>
       <c r="H26" t="n">
-        <v>21233789</v>
+        <v>19572249</v>
       </c>
       <c r="I26" t="n">
-        <v>52.4</v>
+        <v>322</v>
       </c>
       <c r="J26" t="n">
-        <v>38.65</v>
+        <v>230</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3432,116 +3432,116 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-4888236</v>
+        <v>-530792</v>
       </c>
       <c r="M26" t="n">
-        <v>4847703</v>
+        <v>-10791717</v>
       </c>
       <c r="N26" t="n">
-        <v>8458680</v>
+        <v>5369114</v>
       </c>
       <c r="O26" t="n">
-        <v>15447652</v>
+        <v>1749012</v>
       </c>
       <c r="P26" t="n">
-        <v>-5411924</v>
+        <v>-179524</v>
       </c>
       <c r="Q26" t="n">
-        <v>3052091</v>
+        <v>-9928707</v>
       </c>
       <c r="R26" t="n">
-        <v>6604480</v>
+        <v>5583767</v>
       </c>
       <c r="S26" t="n">
-        <v>13213818</v>
+        <v>991620</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>-33000</v>
       </c>
       <c r="U26" t="n">
-        <v>-6000</v>
+        <v>80000</v>
       </c>
       <c r="V26" t="n">
-        <v>-12000</v>
+        <v>77000</v>
       </c>
       <c r="W26" t="n">
-        <v>-34000</v>
+        <v>-164000</v>
       </c>
       <c r="X26" t="n">
-        <v>523688</v>
+        <v>-318268</v>
       </c>
       <c r="Y26" t="n">
-        <v>1801612</v>
+        <v>-943010</v>
       </c>
       <c r="Z26" t="n">
-        <v>1866200</v>
+        <v>-291653</v>
       </c>
       <c r="AA26" t="n">
-        <v>2267834</v>
+        <v>921392</v>
       </c>
       <c r="AB26" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、成交量放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>950</v>
+        <v>156.5</v>
       </c>
       <c r="D27" t="n">
-        <v>956.4</v>
+        <v>165.6</v>
       </c>
       <c r="E27" t="n">
-        <v>878.4</v>
+        <v>160.6</v>
       </c>
       <c r="F27" t="n">
-        <v>812.4</v>
+        <v>157.85</v>
       </c>
       <c r="G27" t="n">
-        <v>1612000</v>
+        <v>27236146</v>
       </c>
       <c r="H27" t="n">
-        <v>8231600</v>
+        <v>138913524</v>
       </c>
       <c r="I27" t="n">
-        <v>1040</v>
+        <v>180</v>
       </c>
       <c r="J27" t="n">
-        <v>630</v>
+        <v>136.5</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3549,64 +3549,64 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>49937</v>
+        <v>-11467565</v>
       </c>
       <c r="M27" t="n">
-        <v>1010824</v>
+        <v>11145389</v>
       </c>
       <c r="N27" t="n">
-        <v>2908227</v>
+        <v>37925588</v>
       </c>
       <c r="O27" t="n">
-        <v>4521125</v>
+        <v>126002535</v>
       </c>
       <c r="P27" t="n">
-        <v>221342</v>
+        <v>-9622905</v>
       </c>
       <c r="Q27" t="n">
-        <v>1464175</v>
+        <v>11022966</v>
       </c>
       <c r="R27" t="n">
-        <v>138108</v>
+        <v>33579999</v>
       </c>
       <c r="S27" t="n">
-        <v>-2958386</v>
+        <v>120096126</v>
       </c>
       <c r="T27" t="n">
-        <v>-444294</v>
+        <v>-386000</v>
       </c>
       <c r="U27" t="n">
-        <v>-1659895</v>
+        <v>2900000</v>
       </c>
       <c r="V27" t="n">
-        <v>1633371</v>
+        <v>6011000</v>
       </c>
       <c r="W27" t="n">
-        <v>5317588</v>
+        <v>8038000</v>
       </c>
       <c r="X27" t="n">
-        <v>272889</v>
+        <v>-1458660</v>
       </c>
       <c r="Y27" t="n">
-        <v>1206544</v>
+        <v>-2777577</v>
       </c>
       <c r="Z27" t="n">
-        <v>1136748</v>
+        <v>-1665411</v>
       </c>
       <c r="AA27" t="n">
-        <v>2161923</v>
+        <v>-2131591</v>
       </c>
       <c r="AB27" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -3616,49 +3616,49 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>強勢偏多：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>53.7</v>
+        <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>53.44</v>
+        <v>178.7</v>
       </c>
       <c r="E28" t="n">
-        <v>52.77</v>
+        <v>162.25</v>
       </c>
       <c r="F28" t="n">
-        <v>51.17</v>
+        <v>150.2</v>
       </c>
       <c r="G28" t="n">
-        <v>61465906</v>
+        <v>128624056</v>
       </c>
       <c r="H28" t="n">
-        <v>46201172</v>
+        <v>159008330</v>
       </c>
       <c r="I28" t="n">
-        <v>55.7</v>
+        <v>201</v>
       </c>
       <c r="J28" t="n">
-        <v>47.35</v>
+        <v>132</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3666,116 +3666,116 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-1332646</v>
+        <v>-43316718</v>
       </c>
       <c r="M28" t="n">
-        <v>2468289</v>
+        <v>73534756</v>
       </c>
       <c r="N28" t="n">
-        <v>13384651</v>
+        <v>119001186</v>
       </c>
       <c r="O28" t="n">
-        <v>47625575</v>
+        <v>171581562</v>
       </c>
       <c r="P28" t="n">
-        <v>27805782</v>
+        <v>-43098336</v>
       </c>
       <c r="Q28" t="n">
-        <v>67307159</v>
+        <v>37409549</v>
       </c>
       <c r="R28" t="n">
-        <v>78131272</v>
+        <v>78942499</v>
       </c>
       <c r="S28" t="n">
-        <v>113779420</v>
+        <v>127581384</v>
       </c>
       <c r="T28" t="n">
-        <v>-29387700</v>
+        <v>962358</v>
       </c>
       <c r="U28" t="n">
-        <v>-65978100</v>
+        <v>36820716</v>
       </c>
       <c r="V28" t="n">
-        <v>-66315792</v>
+        <v>38748716</v>
       </c>
       <c r="W28" t="n">
-        <v>-67841458</v>
+        <v>41282530</v>
       </c>
       <c r="X28" t="n">
-        <v>249272</v>
+        <v>-1180740</v>
       </c>
       <c r="Y28" t="n">
-        <v>1139230</v>
+        <v>-695509</v>
       </c>
       <c r="Z28" t="n">
-        <v>1569171</v>
+        <v>1309971</v>
       </c>
       <c r="AA28" t="n">
-        <v>1687613</v>
+        <v>2717648</v>
       </c>
       <c r="AB28" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>3017.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>30.3</v>
+        <v>2710</v>
       </c>
       <c r="D29" t="n">
-        <v>25.29</v>
+        <v>2743</v>
       </c>
       <c r="E29" t="n">
-        <v>21.48</v>
+        <v>2684</v>
       </c>
       <c r="F29" t="n">
-        <v>19.17</v>
+        <v>2579.5</v>
       </c>
       <c r="G29" t="n">
-        <v>10278195</v>
+        <v>4446507</v>
       </c>
       <c r="H29" t="n">
-        <v>29503887</v>
+        <v>6003383</v>
       </c>
       <c r="I29" t="n">
-        <v>30.3</v>
+        <v>2965</v>
       </c>
       <c r="J29" t="n">
-        <v>16.6</v>
+        <v>2300</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3783,116 +3783,116 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-410733</v>
+        <v>-1136179</v>
       </c>
       <c r="M29" t="n">
-        <v>-402927</v>
+        <v>167021</v>
       </c>
       <c r="N29" t="n">
-        <v>4326828</v>
+        <v>1518588</v>
       </c>
       <c r="O29" t="n">
-        <v>19468574</v>
+        <v>2492279</v>
       </c>
       <c r="P29" t="n">
-        <v>-1477000</v>
+        <v>-1164520</v>
       </c>
       <c r="Q29" t="n">
-        <v>-3360388</v>
+        <v>230539</v>
       </c>
       <c r="R29" t="n">
-        <v>-1188550</v>
+        <v>1108467</v>
       </c>
       <c r="S29" t="n">
-        <v>12500637</v>
+        <v>1094724</v>
       </c>
       <c r="T29" t="n">
-        <v>-4000</v>
+        <v>111932</v>
       </c>
       <c r="U29" t="n">
-        <v>-8000</v>
+        <v>46564</v>
       </c>
       <c r="V29" t="n">
-        <v>-12000</v>
+        <v>412441</v>
       </c>
       <c r="W29" t="n">
-        <v>156000</v>
+        <v>1465178</v>
       </c>
       <c r="X29" t="n">
-        <v>1070267</v>
+        <v>-83591</v>
       </c>
       <c r="Y29" t="n">
-        <v>2965461</v>
+        <v>-110082</v>
       </c>
       <c r="Z29" t="n">
-        <v>5527378</v>
+        <v>-2320</v>
       </c>
       <c r="AA29" t="n">
-        <v>6811937</v>
+        <v>-67623</v>
       </c>
       <c r="AB29" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>👀觀察</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>偏多觀察</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步賣超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯買超、外資投信同步賣超。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8046.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>904</v>
+        <v>53.2</v>
       </c>
       <c r="D30" t="n">
-        <v>873.8</v>
+        <v>53.62</v>
       </c>
       <c r="E30" t="n">
-        <v>888.6</v>
+        <v>52.98</v>
       </c>
       <c r="F30" t="n">
-        <v>871.3</v>
+        <v>51.3</v>
       </c>
       <c r="G30" t="n">
-        <v>17486574</v>
+        <v>54851079</v>
       </c>
       <c r="H30" t="n">
-        <v>18364724</v>
+        <v>53931840</v>
       </c>
       <c r="I30" t="n">
-        <v>980</v>
+        <v>55.7</v>
       </c>
       <c r="J30" t="n">
-        <v>765</v>
+        <v>47.35</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3900,116 +3900,116 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>7651341</v>
+        <v>-8431048</v>
       </c>
       <c r="M30" t="n">
-        <v>10656931</v>
+        <v>-20908660</v>
       </c>
       <c r="N30" t="n">
-        <v>2131374</v>
+        <v>1426702</v>
       </c>
       <c r="O30" t="n">
-        <v>-2934219</v>
+        <v>31336869</v>
       </c>
       <c r="P30" t="n">
-        <v>8066510</v>
+        <v>20265998</v>
       </c>
       <c r="Q30" t="n">
-        <v>10691048</v>
+        <v>67430584</v>
       </c>
       <c r="R30" t="n">
-        <v>6702732</v>
+        <v>95161519</v>
       </c>
       <c r="S30" t="n">
-        <v>2094737</v>
+        <v>126408261</v>
       </c>
       <c r="T30" t="n">
-        <v>-441000</v>
+        <v>-28976400</v>
       </c>
       <c r="U30" t="n">
-        <v>124000</v>
+        <v>-88948650</v>
       </c>
       <c r="V30" t="n">
-        <v>-4276000</v>
+        <v>-95292424</v>
       </c>
       <c r="W30" t="n">
-        <v>-4773000</v>
+        <v>-96796708</v>
       </c>
       <c r="X30" t="n">
-        <v>25831</v>
+        <v>279354</v>
       </c>
       <c r="Y30" t="n">
-        <v>-158117</v>
+        <v>609406</v>
       </c>
       <c r="Z30" t="n">
-        <v>-295358</v>
+        <v>1557607</v>
       </c>
       <c r="AA30" t="n">
-        <v>-255956</v>
+        <v>1725316</v>
       </c>
       <c r="AB30" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>🔥強勢</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>強勢觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>強勢偏多：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。可列入優先觀察，但仍需留意乖離與量能是否過熱。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>8046.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>58.8</v>
+        <v>878</v>
       </c>
       <c r="D31" t="n">
-        <v>59.94</v>
+        <v>879.4</v>
       </c>
       <c r="E31" t="n">
-        <v>58.05</v>
+        <v>889.2</v>
       </c>
       <c r="F31" t="n">
-        <v>57.51</v>
+        <v>867.85</v>
       </c>
       <c r="G31" t="n">
-        <v>9780335</v>
+        <v>8813911</v>
       </c>
       <c r="H31" t="n">
-        <v>23115101</v>
+        <v>16021868</v>
       </c>
       <c r="I31" t="n">
-        <v>63.7</v>
+        <v>966</v>
       </c>
       <c r="J31" t="n">
-        <v>50.2</v>
+        <v>765</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4017,116 +4017,116 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>563271</v>
+        <v>67871</v>
       </c>
       <c r="M31" t="n">
-        <v>-826499</v>
+        <v>4235035</v>
       </c>
       <c r="N31" t="n">
-        <v>10380829</v>
+        <v>8275989</v>
       </c>
       <c r="O31" t="n">
-        <v>12257724</v>
+        <v>1377568</v>
       </c>
       <c r="P31" t="n">
-        <v>226598</v>
+        <v>24793</v>
       </c>
       <c r="Q31" t="n">
-        <v>-125425</v>
+        <v>4966312</v>
       </c>
       <c r="R31" t="n">
-        <v>10007097</v>
+        <v>10759218</v>
       </c>
       <c r="S31" t="n">
-        <v>11492217</v>
+        <v>7880181</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>133000</v>
       </c>
       <c r="U31" t="n">
-        <v>12000</v>
+        <v>-507000</v>
       </c>
       <c r="V31" t="n">
-        <v>12000</v>
+        <v>-2156000</v>
       </c>
       <c r="W31" t="n">
-        <v>126000</v>
+        <v>-6120000</v>
       </c>
       <c r="X31" t="n">
-        <v>336673</v>
+        <v>-89922</v>
       </c>
       <c r="Y31" t="n">
-        <v>-713074</v>
+        <v>-224277</v>
       </c>
       <c r="Z31" t="n">
-        <v>361732</v>
+        <v>-327229</v>
       </c>
       <c r="AA31" t="n">
-        <v>639507</v>
+        <v>-382613</v>
       </c>
       <c r="AB31" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>整理觀察：跌破5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>162</v>
+        <v>2510</v>
       </c>
       <c r="D32" t="n">
-        <v>166.3</v>
+        <v>2492</v>
       </c>
       <c r="E32" t="n">
-        <v>159.05</v>
+        <v>2514.5</v>
       </c>
       <c r="F32" t="n">
-        <v>158.25</v>
+        <v>2498.5</v>
       </c>
       <c r="G32" t="n">
-        <v>58191754</v>
+        <v>2462108</v>
       </c>
       <c r="H32" t="n">
-        <v>177507099</v>
+        <v>4021713</v>
       </c>
       <c r="I32" t="n">
-        <v>180</v>
+        <v>2695</v>
       </c>
       <c r="J32" t="n">
-        <v>136.5</v>
+        <v>2305</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4134,116 +4134,116 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-9163967</v>
+        <v>-490443</v>
       </c>
       <c r="M32" t="n">
-        <v>41337396</v>
+        <v>-162582</v>
       </c>
       <c r="N32" t="n">
-        <v>131545379</v>
+        <v>291119</v>
       </c>
       <c r="O32" t="n">
-        <v>80142662</v>
+        <v>-30992</v>
       </c>
       <c r="P32" t="n">
-        <v>-6930989</v>
+        <v>-351958</v>
       </c>
       <c r="Q32" t="n">
-        <v>35018443</v>
+        <v>673338</v>
       </c>
       <c r="R32" t="n">
-        <v>124837111</v>
+        <v>1631956</v>
       </c>
       <c r="S32" t="n">
-        <v>77508110</v>
+        <v>1601564</v>
       </c>
       <c r="T32" t="n">
-        <v>-6000</v>
+        <v>10896</v>
       </c>
       <c r="U32" t="n">
-        <v>6374000</v>
+        <v>-529891</v>
       </c>
       <c r="V32" t="n">
-        <v>6250000</v>
+        <v>-954568</v>
       </c>
       <c r="W32" t="n">
-        <v>3094000</v>
+        <v>-1174190</v>
       </c>
       <c r="X32" t="n">
-        <v>-2226978</v>
+        <v>-149381</v>
       </c>
       <c r="Y32" t="n">
-        <v>-55047</v>
+        <v>-306029</v>
       </c>
       <c r="Z32" t="n">
-        <v>458268</v>
+        <v>-386269</v>
       </c>
       <c r="AA32" t="n">
-        <v>-459448</v>
+        <v>-458366</v>
       </c>
       <c r="AB32" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>👀觀察</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>偏多觀察</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>偏多觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>59.4</v>
+        <v>692</v>
       </c>
       <c r="D33" t="n">
-        <v>53.82</v>
+        <v>735.4</v>
       </c>
       <c r="E33" t="n">
-        <v>49.94</v>
+        <v>703.4</v>
       </c>
       <c r="F33" t="n">
-        <v>42.42</v>
+        <v>603.52</v>
       </c>
       <c r="G33" t="n">
-        <v>972688727</v>
+        <v>6144218</v>
       </c>
       <c r="H33" t="n">
-        <v>954198998</v>
+        <v>6226970</v>
       </c>
       <c r="I33" t="n">
-        <v>60.5</v>
+        <v>778</v>
       </c>
       <c r="J33" t="n">
-        <v>28.15</v>
+        <v>445.5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4251,55 +4251,55 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>80140919</v>
+        <v>-2049696</v>
       </c>
       <c r="M33" t="n">
-        <v>-29652629</v>
+        <v>-2379657</v>
       </c>
       <c r="N33" t="n">
-        <v>-174638734</v>
+        <v>1113398</v>
       </c>
       <c r="O33" t="n">
-        <v>-20966710</v>
+        <v>9066428</v>
       </c>
       <c r="P33" t="n">
-        <v>48121131</v>
+        <v>-602905</v>
       </c>
       <c r="Q33" t="n">
-        <v>-79760889</v>
+        <v>821802</v>
       </c>
       <c r="R33" t="n">
-        <v>-205849497</v>
+        <v>3483928</v>
       </c>
       <c r="S33" t="n">
-        <v>-68229396</v>
+        <v>7461646</v>
       </c>
       <c r="T33" t="n">
-        <v>30478000</v>
+        <v>-890804</v>
       </c>
       <c r="U33" t="n">
-        <v>59730000</v>
+        <v>-1808453</v>
       </c>
       <c r="V33" t="n">
-        <v>59847221</v>
+        <v>-1794167</v>
       </c>
       <c r="W33" t="n">
-        <v>54248332</v>
+        <v>3127310</v>
       </c>
       <c r="X33" t="n">
-        <v>1541788</v>
+        <v>-555987</v>
       </c>
       <c r="Y33" t="n">
-        <v>-9621740</v>
+        <v>-1393006</v>
       </c>
       <c r="Z33" t="n">
-        <v>-28636458</v>
+        <v>-576363</v>
       </c>
       <c r="AA33" t="n">
-        <v>-6985646</v>
+        <v>-1522528</v>
       </c>
       <c r="AB33" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -4313,54 +4313,54 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11.55</v>
+        <v>374</v>
       </c>
       <c r="D34" t="n">
-        <v>9.81</v>
+        <v>384.1</v>
       </c>
       <c r="E34" t="n">
-        <v>8.609999999999999</v>
+        <v>358.55</v>
       </c>
       <c r="F34" t="n">
-        <v>7.15</v>
+        <v>338.45</v>
       </c>
       <c r="G34" t="n">
-        <v>120669604</v>
+        <v>22721974</v>
       </c>
       <c r="H34" t="n">
-        <v>187778094</v>
+        <v>28825656</v>
       </c>
       <c r="I34" t="n">
-        <v>11.55</v>
+        <v>402</v>
       </c>
       <c r="J34" t="n">
-        <v>5.55</v>
+        <v>300</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4368,55 +4368,55 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>-2436751</v>
+        <v>-1866574</v>
       </c>
       <c r="M34" t="n">
-        <v>2308123</v>
+        <v>255767</v>
       </c>
       <c r="N34" t="n">
-        <v>-24896816</v>
+        <v>7949769</v>
       </c>
       <c r="O34" t="n">
-        <v>22226928</v>
+        <v>14342539</v>
       </c>
       <c r="P34" t="n">
-        <v>-3092500</v>
+        <v>-2511285</v>
       </c>
       <c r="Q34" t="n">
-        <v>3773241</v>
+        <v>-4338950</v>
       </c>
       <c r="R34" t="n">
-        <v>-23298559</v>
+        <v>-3433403</v>
       </c>
       <c r="S34" t="n">
-        <v>20474092</v>
+        <v>594202</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1191000</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>5364000</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>11074024</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>13176102</v>
       </c>
       <c r="X34" t="n">
-        <v>655749</v>
+        <v>-546289</v>
       </c>
       <c r="Y34" t="n">
-        <v>-1465118</v>
+        <v>-769283</v>
       </c>
       <c r="Z34" t="n">
-        <v>-1598257</v>
+        <v>309148</v>
       </c>
       <c r="AA34" t="n">
-        <v>1752836</v>
+        <v>572235</v>
       </c>
       <c r="AB34" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -4430,54 +4430,54 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2748.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>39.75</v>
+        <v>29.55</v>
       </c>
       <c r="D35" t="n">
-        <v>39.27</v>
+        <v>30.74</v>
       </c>
       <c r="E35" t="n">
-        <v>39.23</v>
+        <v>30.29</v>
       </c>
       <c r="F35" t="n">
-        <v>39.52</v>
+        <v>29.06</v>
       </c>
       <c r="G35" t="n">
-        <v>126939</v>
+        <v>8407612</v>
       </c>
       <c r="H35" t="n">
-        <v>147218</v>
+        <v>11906761</v>
       </c>
       <c r="I35" t="n">
-        <v>40.95</v>
+        <v>31.95</v>
       </c>
       <c r="J35" t="n">
-        <v>38.5</v>
+        <v>26.55</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4485,28 +4485,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>51000</v>
+        <v>-636457</v>
       </c>
       <c r="M35" t="n">
-        <v>115000</v>
+        <v>3224909</v>
       </c>
       <c r="N35" t="n">
-        <v>26976</v>
+        <v>4387269</v>
       </c>
       <c r="O35" t="n">
-        <v>-86104</v>
+        <v>15626208</v>
       </c>
       <c r="P35" t="n">
-        <v>50000</v>
+        <v>-541877</v>
       </c>
       <c r="Q35" t="n">
-        <v>115000</v>
+        <v>3536902</v>
       </c>
       <c r="R35" t="n">
-        <v>29976</v>
+        <v>4366950</v>
       </c>
       <c r="S35" t="n">
-        <v>-83001</v>
+        <v>14792873</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -4521,19 +4521,19 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>-94580</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>-311993</v>
       </c>
       <c r="Z35" t="n">
-        <v>-3000</v>
+        <v>20319</v>
       </c>
       <c r="AA35" t="n">
-        <v>-3103</v>
+        <v>833335</v>
       </c>
       <c r="AB35" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -4547,54 +4547,54 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>法人連續偏買</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日低點、法人連續偏買。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>33.9</v>
+        <v>870</v>
       </c>
       <c r="D36" t="n">
-        <v>32.8</v>
+        <v>945</v>
       </c>
       <c r="E36" t="n">
-        <v>33.96</v>
+        <v>895.3</v>
       </c>
       <c r="F36" t="n">
-        <v>35.2</v>
+        <v>816.25</v>
       </c>
       <c r="G36" t="n">
-        <v>9279196</v>
+        <v>1538000</v>
       </c>
       <c r="H36" t="n">
-        <v>9361446</v>
+        <v>4193400</v>
       </c>
       <c r="I36" t="n">
-        <v>44.05</v>
+        <v>1040</v>
       </c>
       <c r="J36" t="n">
-        <v>31.1</v>
+        <v>630</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4602,52 +4602,52 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1652195</v>
+        <v>-209599</v>
       </c>
       <c r="M36" t="n">
-        <v>1462542</v>
+        <v>2587</v>
       </c>
       <c r="N36" t="n">
-        <v>91633</v>
+        <v>2471663</v>
       </c>
       <c r="O36" t="n">
-        <v>-4823087</v>
+        <v>5433544</v>
       </c>
       <c r="P36" t="n">
-        <v>1652123</v>
+        <v>-18335</v>
       </c>
       <c r="Q36" t="n">
-        <v>1461019</v>
+        <v>456794</v>
       </c>
       <c r="R36" t="n">
-        <v>348005</v>
+        <v>1789978</v>
       </c>
       <c r="S36" t="n">
-        <v>-4565714</v>
+        <v>-2472514</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>-66804</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>-933842</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>-580699</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>5930784</v>
       </c>
       <c r="X36" t="n">
-        <v>72</v>
+        <v>-124460</v>
       </c>
       <c r="Y36" t="n">
-        <v>1523</v>
+        <v>479635</v>
       </c>
       <c r="Z36" t="n">
-        <v>-256372</v>
+        <v>1262384</v>
       </c>
       <c r="AA36" t="n">
-        <v>-257373</v>
+        <v>1975274</v>
       </c>
       <c r="AB36" t="n">
         <v>35</v>
@@ -4664,54 +4664,54 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4545</v>
+        <v>12.7</v>
       </c>
       <c r="D37" t="n">
-        <v>4469</v>
+        <v>10.65</v>
       </c>
       <c r="E37" t="n">
-        <v>4290.5</v>
+        <v>9.26</v>
       </c>
       <c r="F37" t="n">
-        <v>3874</v>
+        <v>7.5</v>
       </c>
       <c r="G37" t="n">
-        <v>10480184</v>
+        <v>84356677</v>
       </c>
       <c r="H37" t="n">
-        <v>17146726</v>
+        <v>157914281</v>
       </c>
       <c r="I37" t="n">
-        <v>4970</v>
+        <v>12.7</v>
       </c>
       <c r="J37" t="n">
-        <v>3100</v>
+        <v>5.55</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4719,116 +4719,116 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-137996</v>
+        <v>3595372</v>
       </c>
       <c r="M37" t="n">
-        <v>1212144</v>
+        <v>-11198643</v>
       </c>
       <c r="N37" t="n">
-        <v>-3815540</v>
+        <v>-2322475</v>
       </c>
       <c r="O37" t="n">
-        <v>-4067295</v>
+        <v>10580600</v>
       </c>
       <c r="P37" t="n">
-        <v>707096</v>
+        <v>3488264</v>
       </c>
       <c r="Q37" t="n">
-        <v>3832840</v>
+        <v>-9605715</v>
       </c>
       <c r="R37" t="n">
-        <v>651602</v>
+        <v>-1733495</v>
       </c>
       <c r="S37" t="n">
-        <v>473754</v>
+        <v>6595656</v>
       </c>
       <c r="T37" t="n">
-        <v>-908215</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>-2115173</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>-3759363</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>-4863411</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>63123</v>
+        <v>107108</v>
       </c>
       <c r="Y37" t="n">
-        <v>-505523</v>
+        <v>-1592928</v>
       </c>
       <c r="Z37" t="n">
-        <v>-707779</v>
+        <v>-588980</v>
       </c>
       <c r="AA37" t="n">
-        <v>322362</v>
+        <v>3984944</v>
       </c>
       <c r="AB37" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資買投信賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2401.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>29.35</v>
+        <v>19.25</v>
       </c>
       <c r="D38" t="n">
-        <v>29.59</v>
+        <v>19.16</v>
       </c>
       <c r="E38" t="n">
-        <v>29.88</v>
+        <v>19.13</v>
       </c>
       <c r="F38" t="n">
-        <v>27.61</v>
+        <v>18.74</v>
       </c>
       <c r="G38" t="n">
-        <v>6818588</v>
+        <v>75211768</v>
       </c>
       <c r="H38" t="n">
-        <v>11914699</v>
+        <v>80808172</v>
       </c>
       <c r="I38" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>23.45</v>
+        <v>18.05</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4836,116 +4836,116 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-35174</v>
+        <v>4712134</v>
       </c>
       <c r="M38" t="n">
-        <v>1443177</v>
+        <v>-3398546</v>
       </c>
       <c r="N38" t="n">
-        <v>1768520</v>
+        <v>-7860139</v>
       </c>
       <c r="O38" t="n">
-        <v>-8588031</v>
+        <v>-61631262</v>
       </c>
       <c r="P38" t="n">
-        <v>-27351</v>
+        <v>3592384</v>
       </c>
       <c r="Q38" t="n">
-        <v>1610834</v>
+        <v>-6573599</v>
       </c>
       <c r="R38" t="n">
-        <v>2323590</v>
+        <v>-11975947</v>
       </c>
       <c r="S38" t="n">
-        <v>-8742162</v>
+        <v>-67192835</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>499655</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1507309</v>
       </c>
       <c r="V38" t="n">
-        <v>1000</v>
+        <v>1539834</v>
       </c>
       <c r="W38" t="n">
-        <v>101000</v>
+        <v>1466834</v>
       </c>
       <c r="X38" t="n">
-        <v>-7823</v>
+        <v>620095</v>
       </c>
       <c r="Y38" t="n">
-        <v>-167657</v>
+        <v>1667744</v>
       </c>
       <c r="Z38" t="n">
-        <v>-556070</v>
+        <v>2575974</v>
       </c>
       <c r="AA38" t="n">
-        <v>53131</v>
+        <v>4094739</v>
       </c>
       <c r="AB38" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2002.TW</t>
+          <t>2383.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>19.4</v>
+        <v>4830</v>
       </c>
       <c r="D39" t="n">
-        <v>19.08</v>
+        <v>4942</v>
       </c>
       <c r="E39" t="n">
-        <v>19.03</v>
+        <v>5087</v>
       </c>
       <c r="F39" t="n">
-        <v>18.72</v>
+        <v>4900</v>
       </c>
       <c r="G39" t="n">
-        <v>111692995</v>
+        <v>1722407</v>
       </c>
       <c r="H39" t="n">
-        <v>82795166</v>
+        <v>2411205</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>5635</v>
       </c>
       <c r="J39" t="n">
-        <v>18.05</v>
+        <v>4300</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4953,116 +4953,116 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>19175064</v>
+        <v>63950</v>
       </c>
       <c r="M39" t="n">
-        <v>-14932637</v>
+        <v>1096</v>
       </c>
       <c r="N39" t="n">
-        <v>-27888928</v>
+        <v>4990</v>
       </c>
       <c r="O39" t="n">
-        <v>-51696009</v>
+        <v>1031283</v>
       </c>
       <c r="P39" t="n">
-        <v>17749990</v>
+        <v>52353</v>
       </c>
       <c r="Q39" t="n">
-        <v>-17761401</v>
+        <v>261542</v>
       </c>
       <c r="R39" t="n">
-        <v>-30114939</v>
+        <v>831723</v>
       </c>
       <c r="S39" t="n">
-        <v>-55998428</v>
+        <v>1565495</v>
       </c>
       <c r="T39" t="n">
-        <v>73654</v>
+        <v>-963</v>
       </c>
       <c r="U39" t="n">
-        <v>1012654</v>
+        <v>-218379</v>
       </c>
       <c r="V39" t="n">
-        <v>999179</v>
+        <v>-781297</v>
       </c>
       <c r="W39" t="n">
-        <v>1055179</v>
+        <v>-436856</v>
       </c>
       <c r="X39" t="n">
-        <v>1351420</v>
+        <v>12560</v>
       </c>
       <c r="Y39" t="n">
-        <v>1816110</v>
+        <v>-42067</v>
       </c>
       <c r="Z39" t="n">
-        <v>1226832</v>
+        <v>-45436</v>
       </c>
       <c r="AA39" t="n">
-        <v>3247240</v>
+        <v>-97356</v>
       </c>
       <c r="AB39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏買、外資買投信賣</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>28.75</v>
+        <v>454</v>
       </c>
       <c r="D40" t="n">
-        <v>24.58</v>
+        <v>442.4</v>
       </c>
       <c r="E40" t="n">
-        <v>23.35</v>
+        <v>440.2</v>
       </c>
       <c r="F40" t="n">
-        <v>21.26</v>
+        <v>407</v>
       </c>
       <c r="G40" t="n">
-        <v>706729442</v>
+        <v>18589000</v>
       </c>
       <c r="H40" t="n">
-        <v>602484432</v>
+        <v>12648600</v>
       </c>
       <c r="I40" t="n">
-        <v>28.75</v>
+        <v>492.5</v>
       </c>
       <c r="J40" t="n">
-        <v>17.75</v>
+        <v>343</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5070,55 +5070,55 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-29968047</v>
+        <v>709158</v>
       </c>
       <c r="M40" t="n">
-        <v>-90695160</v>
+        <v>-1855742</v>
       </c>
       <c r="N40" t="n">
-        <v>-23867482</v>
+        <v>-5298603</v>
       </c>
       <c r="O40" t="n">
-        <v>100077771</v>
+        <v>9079470</v>
       </c>
       <c r="P40" t="n">
-        <v>-31128755</v>
+        <v>1534533</v>
       </c>
       <c r="Q40" t="n">
-        <v>-93668688</v>
+        <v>101605</v>
       </c>
       <c r="R40" t="n">
-        <v>-28168041</v>
+        <v>-3276970</v>
       </c>
       <c r="S40" t="n">
-        <v>86594336</v>
+        <v>12885288</v>
       </c>
       <c r="T40" t="n">
-        <v>-6000</v>
+        <v>-692000</v>
       </c>
       <c r="U40" t="n">
-        <v>95000</v>
+        <v>-2423000</v>
       </c>
       <c r="V40" t="n">
-        <v>189252</v>
+        <v>-2510000</v>
       </c>
       <c r="W40" t="n">
-        <v>210015</v>
+        <v>-4938000</v>
       </c>
       <c r="X40" t="n">
-        <v>1166708</v>
+        <v>-133375</v>
       </c>
       <c r="Y40" t="n">
-        <v>2878528</v>
+        <v>465653</v>
       </c>
       <c r="Z40" t="n">
-        <v>4111307</v>
+        <v>488367</v>
       </c>
       <c r="AA40" t="n">
-        <v>13273420</v>
+        <v>1132182</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -5132,54 +5132,54 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>43.4</v>
+        <v>296</v>
       </c>
       <c r="D41" t="n">
-        <v>40.39</v>
+        <v>308.2</v>
       </c>
       <c r="E41" t="n">
-        <v>37.89</v>
+        <v>305.5</v>
       </c>
       <c r="F41" t="n">
-        <v>33.22</v>
+        <v>288.68</v>
       </c>
       <c r="G41" t="n">
-        <v>167087498</v>
+        <v>11401407</v>
       </c>
       <c r="H41" t="n">
-        <v>137463762</v>
+        <v>15728378</v>
       </c>
       <c r="I41" t="n">
-        <v>44.4</v>
+        <v>336.5</v>
       </c>
       <c r="J41" t="n">
-        <v>26.65</v>
+        <v>241.5</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5187,55 +5187,55 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5718208</v>
+        <v>-431470</v>
       </c>
       <c r="M41" t="n">
-        <v>-2407861</v>
+        <v>95182</v>
       </c>
       <c r="N41" t="n">
-        <v>-15900393</v>
+        <v>-1281939</v>
       </c>
       <c r="O41" t="n">
-        <v>29650275</v>
+        <v>7688386</v>
       </c>
       <c r="P41" t="n">
-        <v>4087543</v>
+        <v>-266838</v>
       </c>
       <c r="Q41" t="n">
-        <v>-4993686</v>
+        <v>29491</v>
       </c>
       <c r="R41" t="n">
-        <v>-18847112</v>
+        <v>-1512771</v>
       </c>
       <c r="S41" t="n">
-        <v>34713093</v>
+        <v>8863108</v>
       </c>
       <c r="T41" t="n">
-        <v>2000</v>
+        <v>-67000</v>
       </c>
       <c r="U41" t="n">
-        <v>607000</v>
+        <v>266000</v>
       </c>
       <c r="V41" t="n">
-        <v>607000</v>
+        <v>557000</v>
       </c>
       <c r="W41" t="n">
-        <v>-9201000</v>
+        <v>-1518232</v>
       </c>
       <c r="X41" t="n">
-        <v>1628665</v>
+        <v>-97632</v>
       </c>
       <c r="Y41" t="n">
-        <v>1978825</v>
+        <v>-200309</v>
       </c>
       <c r="Z41" t="n">
-        <v>2339719</v>
+        <v>-326168</v>
       </c>
       <c r="AA41" t="n">
-        <v>4138182</v>
+        <v>343510</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -5249,54 +5249,54 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2401.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>251</v>
+        <v>28.1</v>
       </c>
       <c r="D42" t="n">
-        <v>236.5</v>
+        <v>29.2</v>
       </c>
       <c r="E42" t="n">
-        <v>253.2</v>
+        <v>29.74</v>
       </c>
       <c r="F42" t="n">
-        <v>244.75</v>
+        <v>27.75</v>
       </c>
       <c r="G42" t="n">
-        <v>5139000</v>
+        <v>7060925</v>
       </c>
       <c r="H42" t="n">
-        <v>3967200</v>
+        <v>9617244</v>
       </c>
       <c r="I42" t="n">
-        <v>312.5</v>
+        <v>33</v>
       </c>
       <c r="J42" t="n">
-        <v>220</v>
+        <v>23.45</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5304,28 +5304,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>70509</v>
+        <v>-1429044</v>
       </c>
       <c r="M42" t="n">
-        <v>-497664</v>
+        <v>618016</v>
       </c>
       <c r="N42" t="n">
-        <v>-1752310</v>
+        <v>-1848079</v>
       </c>
       <c r="O42" t="n">
-        <v>-2835529</v>
+        <v>-10431340</v>
       </c>
       <c r="P42" t="n">
-        <v>54733</v>
+        <v>-1301987</v>
       </c>
       <c r="Q42" t="n">
-        <v>-484973</v>
+        <v>908731</v>
       </c>
       <c r="R42" t="n">
-        <v>-1707348</v>
+        <v>-1571906</v>
       </c>
       <c r="S42" t="n">
-        <v>-2563993</v>
+        <v>-9096767</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -5334,25 +5334,25 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="X42" t="n">
-        <v>15776</v>
+        <v>-127057</v>
       </c>
       <c r="Y42" t="n">
-        <v>-12691</v>
+        <v>-290715</v>
       </c>
       <c r="Z42" t="n">
-        <v>-44962</v>
+        <v>-277173</v>
       </c>
       <c r="AA42" t="n">
-        <v>-271536</v>
+        <v>-1435573</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -5366,54 +5366,54 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2585</v>
+        <v>125</v>
       </c>
       <c r="D43" t="n">
-        <v>2477</v>
+        <v>137.5</v>
       </c>
       <c r="E43" t="n">
-        <v>2511.5</v>
+        <v>134.25</v>
       </c>
       <c r="F43" t="n">
-        <v>2501</v>
+        <v>119.89</v>
       </c>
       <c r="G43" t="n">
-        <v>4091539</v>
+        <v>380918568</v>
       </c>
       <c r="H43" t="n">
-        <v>4539515</v>
+        <v>359415315</v>
       </c>
       <c r="I43" t="n">
-  